--- a/output/daily_screen_latest.xlsx
+++ b/output/daily_screen_latest.xlsx
@@ -662,24 +662,24 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>73.59999999999999</v>
+        <v>63.8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Sell</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>700000</v>
+        <v>485000</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K2" t="b">
         <v>0</v>
@@ -691,10 +691,10 @@
         <v>700000</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>-215000</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>-0.3071428571428572</v>
       </c>
       <c r="P2" t="n">
         <v>1330</v>
@@ -703,7 +703,7 @@
         <v>1330</v>
       </c>
       <c r="R2" t="n">
-        <v>5050252</v>
+        <v>4943644</v>
       </c>
       <c r="S2" t="n">
         <v>1288</v>
@@ -721,13 +721,13 @@
         <v>39.90773424780309</v>
       </c>
       <c r="X2" t="n">
-        <v>32.83570320214118</v>
+        <v>32.8357032021411</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.072031045661916</v>
+        <v>7.072031045661994</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.684694423661924</v>
+        <v>5.684694423662027</v>
       </c>
       <c r="AA2" t="b">
         <v>1</v>
@@ -804,20 +804,20 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>59</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2477000</v>
+        <v>2512000</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
@@ -833,10 +833,10 @@
         <v>2477000</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>0.0141299959628583</v>
       </c>
       <c r="P3" t="n">
         <v>5765</v>
@@ -845,7 +845,7 @@
         <v>5765</v>
       </c>
       <c r="R3" t="n">
-        <v>707334</v>
+        <v>671341</v>
       </c>
       <c r="S3" t="n">
         <v>5704</v>
@@ -944,20 +944,20 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>54.40000000000001</v>
+        <v>64.2</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>372000</v>
+        <v>413000</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
@@ -973,10 +973,10 @@
         <v>372000</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>41000</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>0.1102150537634409</v>
       </c>
       <c r="P4" t="n">
         <v>6120</v>
@@ -985,7 +985,7 @@
         <v>6120</v>
       </c>
       <c r="R4" t="n">
-        <v>1476663</v>
+        <v>1425347</v>
       </c>
       <c r="S4" t="n">
         <v>6033</v>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1125,7 +1125,7 @@
         <v>140.5</v>
       </c>
       <c r="R5" t="n">
-        <v>120621193</v>
+        <v>119260816</v>
       </c>
       <c r="S5" t="n">
         <v>140.9</v>
@@ -1140,16 +1140,16 @@
         <v>137.1627202351888</v>
       </c>
       <c r="W5" t="n">
-        <v>4.690909053504299</v>
+        <v>4.690909053504328</v>
       </c>
       <c r="X5" t="n">
-        <v>2.962828799205447</v>
+        <v>2.962828799205475</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.728080254298852</v>
+        <v>1.728080254298853</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.167341712366061</v>
+        <v>2.167341712366063</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1267,7 +1267,7 @@
         <v>2310</v>
       </c>
       <c r="R6" t="n">
-        <v>1888918</v>
+        <v>1627022</v>
       </c>
       <c r="S6" t="n">
         <v>2362</v>
@@ -1282,16 +1282,16 @@
         <v>1955.745255533854</v>
       </c>
       <c r="W6" t="n">
-        <v>43.80731406619134</v>
+        <v>43.80731406619088</v>
       </c>
       <c r="X6" t="n">
-        <v>85.59262024075896</v>
+        <v>85.59262024075835</v>
       </c>
       <c r="Y6" t="n">
-        <v>-41.78530617456762</v>
+        <v>-41.78530617456747</v>
       </c>
       <c r="Z6" t="n">
-        <v>-36.142077953157</v>
+        <v>-36.1420779531568</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1405,7 +1405,7 @@
         <v>6660</v>
       </c>
       <c r="R7" t="n">
-        <v>1980286</v>
+        <v>1858248</v>
       </c>
       <c r="S7" t="n">
         <v>6682</v>
@@ -1423,13 +1423,13 @@
         <v>278.6948379755941</v>
       </c>
       <c r="X7" t="n">
-        <v>458.1673203770637</v>
+        <v>458.1673203770636</v>
       </c>
       <c r="Y7" t="n">
-        <v>-179.4724824014697</v>
+        <v>-179.4724824014696</v>
       </c>
       <c r="Z7" t="n">
-        <v>-166.4546906656735</v>
+        <v>-166.4546906656734</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1543,7 +1543,7 @@
         <v>2150</v>
       </c>
       <c r="R8" t="n">
-        <v>1017797</v>
+        <v>991243</v>
       </c>
       <c r="S8" t="n">
         <v>2211</v>
@@ -1558,16 +1558,16 @@
         <v>1718.324682617188</v>
       </c>
       <c r="W8" t="n">
-        <v>81.72624149239118</v>
+        <v>81.72624149239073</v>
       </c>
       <c r="X8" t="n">
-        <v>107.6367292446171</v>
+        <v>107.6367292446166</v>
       </c>
       <c r="Y8" t="n">
-        <v>-25.91048775222588</v>
+        <v>-25.91048775222589</v>
       </c>
       <c r="Z8" t="n">
-        <v>-16.94700402976784</v>
+        <v>-16.94700402976785</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1683,7 +1683,7 @@
         <v>101</v>
       </c>
       <c r="R9" t="n">
-        <v>6774857</v>
+        <v>6754463</v>
       </c>
       <c r="S9" t="n">
         <v>99.85999908447266</v>
@@ -1701,13 +1701,13 @@
         <v>2.548482324952374</v>
       </c>
       <c r="X9" t="n">
-        <v>2.541357232987988</v>
+        <v>2.541357232987986</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.007125091964386154</v>
+        <v>0.007125091964388375</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.02675220142829859</v>
+        <v>0.02675220142830126</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1825,7 +1825,7 @@
         <v>263</v>
       </c>
       <c r="R10" t="n">
-        <v>17729240</v>
+        <v>16992490</v>
       </c>
       <c r="S10" t="n">
         <v>269.2</v>
@@ -1843,13 +1843,13 @@
         <v>4.809530175251439</v>
       </c>
       <c r="X10" t="n">
-        <v>4.577638248231361</v>
+        <v>4.577638248231355</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.2318919270200777</v>
+        <v>0.2318919270200839</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.382907551939251</v>
+        <v>1.382907551939258</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
@@ -1912,12 +1912,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1926,7 +1926,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>44.2</v>
+        <v>43</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1935,15 +1935,15 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>637000</v>
+        <v>5186000</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="K11" t="b">
         <v>0</v>
@@ -1952,7 +1952,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>637000</v>
+        <v>5186000</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1961,61 +1961,61 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3480</v>
+        <v>4585</v>
       </c>
       <c r="Q11" t="n">
-        <v>3480</v>
+        <v>4585</v>
       </c>
       <c r="R11" t="n">
-        <v>1104551</v>
+        <v>6841032</v>
       </c>
       <c r="S11" t="n">
-        <v>3570</v>
+        <v>4680</v>
       </c>
       <c r="T11" t="n">
-        <v>3052</v>
+        <v>4161.75</v>
       </c>
       <c r="U11" t="n">
-        <v>3027.5</v>
+        <v>4143</v>
       </c>
       <c r="V11" t="n">
-        <v>2927.079142252604</v>
+        <v>3986.717415364583</v>
       </c>
       <c r="W11" t="n">
-        <v>210.4160916274091</v>
+        <v>197.1743621014048</v>
       </c>
       <c r="X11" t="n">
-        <v>165.3148866757768</v>
+        <v>155.950178214217</v>
       </c>
       <c r="Y11" t="n">
-        <v>45.1012049516323</v>
+        <v>41.22418388718773</v>
       </c>
       <c r="Z11" t="n">
-        <v>76.13910869752343</v>
+        <v>66.74904199942983</v>
       </c>
       <c r="AA11" t="b">
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.1638795986622072</v>
+        <v>0.0890736342042755</v>
       </c>
       <c r="AC11" t="n">
-        <v>-0.03081196953418652</v>
+        <v>0.05065948181334012</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.1557191186875424</v>
+        <v>0.08091315422961065</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.03751376606863144</v>
+        <v>0.04395768527889521</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.1932328847561738</v>
+        <v>0.03695546895071544</v>
       </c>
       <c r="AG11" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AH11" t="n">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="AI11" t="b">
         <v>1</v>
@@ -2054,12 +2054,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2068,7 +2068,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>43</v>
+        <v>42.8</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2077,24 +2077,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5186000</v>
+        <v>16811000</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="K12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="b">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>5186000</v>
+        <v>16811000</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -2103,61 +2103,61 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>4585</v>
+        <v>618</v>
       </c>
       <c r="Q12" t="n">
-        <v>4585</v>
+        <v>618</v>
       </c>
       <c r="R12" t="n">
-        <v>7568846</v>
+        <v>21540625</v>
       </c>
       <c r="S12" t="n">
-        <v>4680</v>
+        <v>629.4</v>
       </c>
       <c r="T12" t="n">
-        <v>4161.75</v>
+        <v>604.35</v>
       </c>
       <c r="U12" t="n">
-        <v>4143</v>
+        <v>604.25</v>
       </c>
       <c r="V12" t="n">
-        <v>3986.717415364583</v>
+        <v>621.1943979899089</v>
       </c>
       <c r="W12" t="n">
-        <v>197.1743621014057</v>
+        <v>8.168661987707651</v>
       </c>
       <c r="X12" t="n">
-        <v>155.950178214218</v>
+        <v>3.518014378830946</v>
       </c>
       <c r="Y12" t="n">
-        <v>41.22418388718768</v>
+        <v>4.650647608876705</v>
       </c>
       <c r="Z12" t="n">
-        <v>66.74904199942978</v>
+        <v>7.157082383841484</v>
       </c>
       <c r="AA12" t="b">
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.0890736342042755</v>
+        <v>0.003246753246753276</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.05065948181334012</v>
+        <v>0.01737144639336097</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.08091315422961065</v>
+        <v>-0.004913726727911572</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.04395768527889521</v>
+        <v>0.01066964985891605</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.03695546895071544</v>
+        <v>-0.01558337658682762</v>
       </c>
       <c r="AG12" t="n">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="AH12" t="n">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI12" t="b">
         <v>1</v>
@@ -2196,12 +2196,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2219,15 +2219,15 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>16811000</v>
+        <v>11864000</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K13" t="b">
         <v>1</v>
@@ -2236,7 +2236,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>16811000</v>
+        <v>11864000</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -2245,84 +2245,82 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>618</v>
+        <v>2410</v>
       </c>
       <c r="Q13" t="n">
-        <v>618</v>
+        <v>2410</v>
       </c>
       <c r="R13" t="n">
-        <v>22638149</v>
+        <v>18149016</v>
       </c>
       <c r="S13" t="n">
-        <v>629.4</v>
+        <v>2451</v>
       </c>
       <c r="T13" t="n">
-        <v>604.35</v>
+        <v>2411</v>
       </c>
       <c r="U13" t="n">
-        <v>604.25</v>
+        <v>2410.25</v>
       </c>
       <c r="V13" t="n">
-        <v>621.1943979899089</v>
+        <v>2399.75</v>
       </c>
       <c r="W13" t="n">
-        <v>8.168661987707651</v>
+        <v>12.57621423813816</v>
       </c>
       <c r="X13" t="n">
-        <v>3.518014378830951</v>
+        <v>12.66069475230742</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.650647608876699</v>
+        <v>-0.08448051416925395</v>
       </c>
       <c r="Z13" t="n">
-        <v>7.157082383841478</v>
+        <v>5.141822621183577</v>
       </c>
       <c r="AA13" t="b">
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.003246753246753276</v>
+        <v>0.006263048016701411</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.01737144639336097</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0.004913726727911572</v>
+        <v>-0.001897431957963436</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.01066964985891605</v>
+        <v>-0.006701796534444915</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.01558337658682762</v>
+        <v>0.004804364576481479</v>
       </c>
       <c r="AG13" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AH13" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="AI13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="b">
         <v>1</v>
       </c>
       <c r="AK13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="b">
         <v>0</v>
       </c>
       <c r="AN13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>2414.82</v>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
@@ -2338,12 +2336,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2352,7 +2350,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>42.8</v>
+        <v>41.6</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2361,24 +2359,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>11864000</v>
+        <v>5949000</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="K14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="b">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>11864000</v>
+        <v>5949000</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2387,64 +2385,64 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2410</v>
+        <v>3370</v>
       </c>
       <c r="Q14" t="n">
-        <v>2410</v>
+        <v>3370</v>
       </c>
       <c r="R14" t="n">
-        <v>20883341</v>
+        <v>2005532</v>
       </c>
       <c r="S14" t="n">
-        <v>2451</v>
+        <v>3383</v>
       </c>
       <c r="T14" t="n">
-        <v>2411</v>
+        <v>3234.176245117188</v>
       </c>
       <c r="U14" t="n">
-        <v>2410.25</v>
+        <v>3226.472351074219</v>
       </c>
       <c r="V14" t="n">
-        <v>2399.75</v>
+        <v>2723.961385091146</v>
       </c>
       <c r="W14" t="n">
-        <v>12.57621423813634</v>
+        <v>105.335889759589</v>
       </c>
       <c r="X14" t="n">
-        <v>12.66069475230379</v>
+        <v>130.5570063572081</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.08448051416744384</v>
+        <v>-25.22111659761913</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.141822621185385</v>
+        <v>-18.00179342998683</v>
       </c>
       <c r="AA14" t="b">
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.006263048016701411</v>
+        <v>0.04791094906880033</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>0.4124966090818585</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0.001897431957963436</v>
+        <v>0.03975046909413549</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0.006701796534444915</v>
+        <v>0.4057948125474136</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.004804364576481479</v>
+        <v>-0.3660443434532781</v>
       </c>
       <c r="AG14" t="n">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="AH14" t="n">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="AI14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ14" t="b">
         <v>1</v>
@@ -2462,7 +2460,7 @@
         <v>1</v>
       </c>
       <c r="AO14" t="n">
-        <v>2414.82</v>
+        <v>3659.82</v>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
@@ -2478,12 +2476,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>6271</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2492,7 +2490,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>41.6</v>
+        <v>40.8</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2501,15 +2499,15 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>5949000</v>
+        <v>2222000</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="K15" t="b">
         <v>0</v>
@@ -2518,7 +2516,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>5949000</v>
+        <v>2222000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2527,61 +2525,61 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3370</v>
+        <v>220</v>
       </c>
       <c r="Q15" t="n">
-        <v>3370</v>
+        <v>220</v>
       </c>
       <c r="R15" t="n">
-        <v>2108980</v>
+        <v>2216922</v>
       </c>
       <c r="S15" t="n">
-        <v>3383</v>
+        <v>225.8</v>
       </c>
       <c r="T15" t="n">
-        <v>3234.176245117188</v>
+        <v>212.425</v>
       </c>
       <c r="U15" t="n">
-        <v>3226.472351074219</v>
+        <v>211.125</v>
       </c>
       <c r="V15" t="n">
-        <v>2723.961385091146</v>
+        <v>216.1166666666667</v>
       </c>
       <c r="W15" t="n">
-        <v>105.335889759589</v>
+        <v>6.068834410018638</v>
       </c>
       <c r="X15" t="n">
-        <v>130.5570063572082</v>
+        <v>6.737541555554651</v>
       </c>
       <c r="Y15" t="n">
-        <v>-25.22111659761919</v>
+        <v>-0.668707145536013</v>
       </c>
       <c r="Z15" t="n">
-        <v>-18.00179342998689</v>
+        <v>0.439375949514023</v>
       </c>
       <c r="AA15" t="b">
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.04791094906880033</v>
+        <v>0.134020618556701</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.4124966090818585</v>
+        <v>-0.09278350515463918</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.03975046909413549</v>
+        <v>0.1258601385820362</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.4057948125474136</v>
+        <v>-0.09948530168908409</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.3660443434532781</v>
+        <v>0.2253454402711202</v>
       </c>
       <c r="AG15" t="n">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="AH15" t="n">
-        <v>98</v>
+        <v>42</v>
       </c>
       <c r="AI15" t="b">
         <v>1</v>
@@ -2602,7 +2600,7 @@
         <v>1</v>
       </c>
       <c r="AO15" t="n">
-        <v>3659.82</v>
+        <v>227.92</v>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
@@ -2618,12 +2616,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2632,7 +2630,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>40.8</v>
+        <v>39.4</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2641,15 +2639,15 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>2222000</v>
+        <v>5000</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="K16" t="b">
         <v>0</v>
@@ -2658,7 +2656,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2222000</v>
+        <v>5000</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2667,61 +2665,61 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>220</v>
+        <v>150</v>
       </c>
       <c r="Q16" t="n">
-        <v>220</v>
+        <v>150</v>
       </c>
       <c r="R16" t="n">
-        <v>2275150</v>
+        <v>27000650</v>
       </c>
       <c r="S16" t="n">
-        <v>225.8</v>
+        <v>153.4</v>
       </c>
       <c r="T16" t="n">
-        <v>212.425</v>
+        <v>147.45</v>
       </c>
       <c r="U16" t="n">
-        <v>211.125</v>
+        <v>146.85</v>
       </c>
       <c r="V16" t="n">
-        <v>216.1166666666667</v>
+        <v>157.8916666666667</v>
       </c>
       <c r="W16" t="n">
-        <v>6.068834410018638</v>
+        <v>2.493686222751734</v>
       </c>
       <c r="X16" t="n">
-        <v>6.737541555554656</v>
+        <v>2.90857006187582</v>
       </c>
       <c r="Y16" t="n">
-        <v>-0.6687071455360174</v>
+        <v>-0.4148838391240863</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.4393759495140168</v>
+        <v>0.1642919784818218</v>
       </c>
       <c r="AA16" t="b">
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.134020618556701</v>
+        <v>0.08695652173913038</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0.09278350515463918</v>
+        <v>-0.0625</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.1258601385820362</v>
+        <v>0.07879604176446553</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0.09948530168908409</v>
+        <v>-0.06920179653444491</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.2253454402711202</v>
+        <v>0.1479978382989104</v>
       </c>
       <c r="AG16" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AH16" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="AI16" t="b">
         <v>1</v>
@@ -2742,7 +2740,7 @@
         <v>1</v>
       </c>
       <c r="AO16" t="n">
-        <v>227.92</v>
+        <v>154.8</v>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
@@ -2758,12 +2756,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2772,7 +2770,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>39.4</v>
+        <v>39</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2781,15 +2779,15 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>5000</v>
+        <v>3248000</v>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="K17" t="b">
         <v>0</v>
@@ -2798,7 +2796,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>5000</v>
+        <v>3248000</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2807,64 +2805,64 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>150</v>
+        <v>186.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>150</v>
+        <v>186.5</v>
       </c>
       <c r="R17" t="n">
-        <v>27240867</v>
+        <v>2109075</v>
       </c>
       <c r="S17" t="n">
-        <v>153.4</v>
+        <v>191</v>
       </c>
       <c r="T17" t="n">
-        <v>147.45</v>
+        <v>190.075</v>
       </c>
       <c r="U17" t="n">
-        <v>146.85</v>
+        <v>189.4</v>
       </c>
       <c r="V17" t="n">
-        <v>157.8916666666667</v>
+        <v>180.113899230957</v>
       </c>
       <c r="W17" t="n">
-        <v>2.493686222751734</v>
+        <v>2.21500964183187</v>
       </c>
       <c r="X17" t="n">
-        <v>2.90857006187582</v>
+        <v>4.819424623145751</v>
       </c>
       <c r="Y17" t="n">
-        <v>-0.4148838391240863</v>
+        <v>-2.604414981313881</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.1642919784818218</v>
+        <v>-2.119228753447062</v>
       </c>
       <c r="AA17" t="b">
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.08695652173913038</v>
+        <v>0.07803468208092479</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.0625</v>
+        <v>-0.06191761106456184</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.07879604176446553</v>
+        <v>0.06987420210625994</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0.06920179653444491</v>
+        <v>-0.06861940759900675</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.1479978382989104</v>
+        <v>0.1384936097052667</v>
       </c>
       <c r="AG17" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AH17" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AI17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="b">
         <v>1</v>
@@ -2882,7 +2880,7 @@
         <v>1</v>
       </c>
       <c r="AO17" t="n">
-        <v>154.8</v>
+        <v>215.97</v>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
@@ -2898,12 +2896,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2912,7 +2910,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>39</v>
+        <v>37.8</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2921,24 +2919,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>3248000</v>
+        <v>20300000</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="K18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="b">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3248000</v>
+        <v>20300000</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2947,67 +2945,67 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>186.5</v>
+        <v>977</v>
       </c>
       <c r="Q18" t="n">
-        <v>186.5</v>
+        <v>977</v>
       </c>
       <c r="R18" t="n">
-        <v>2168432</v>
+        <v>11021738</v>
       </c>
       <c r="S18" t="n">
-        <v>191</v>
+        <v>973.4</v>
       </c>
       <c r="T18" t="n">
-        <v>190.075</v>
+        <v>1043.75</v>
       </c>
       <c r="U18" t="n">
-        <v>189.4</v>
+        <v>1045.9</v>
       </c>
       <c r="V18" t="n">
-        <v>180.113899230957</v>
+        <v>954.378163655599</v>
       </c>
       <c r="W18" t="n">
-        <v>2.21500964183187</v>
+        <v>-15.22422037337219</v>
       </c>
       <c r="X18" t="n">
-        <v>4.819424623145729</v>
+        <v>-7.956888759828145</v>
       </c>
       <c r="Y18" t="n">
-        <v>-2.604414981313859</v>
+        <v>-7.267331613544046</v>
       </c>
       <c r="Z18" t="n">
-        <v>-2.119228753447034</v>
+        <v>-10.2807709018258</v>
       </c>
       <c r="AA18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.07803468208092479</v>
+        <v>-0.042156862745098</v>
       </c>
       <c r="AC18" t="n">
-        <v>-0.06191761106456184</v>
+        <v>0.01136422295068207</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.06987420210625994</v>
+        <v>-0.05031734271976285</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0.06861940759900675</v>
+        <v>0.004662426416237153</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.1384936097052667</v>
+        <v>-0.054979769136</v>
       </c>
       <c r="AG18" t="n">
-        <v>78</v>
+        <v>34</v>
       </c>
       <c r="AH18" t="n">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="AI18" t="b">
         <v>0</v>
       </c>
       <c r="AJ18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="b">
         <v>0</v>
@@ -3016,18 +3014,16 @@
         <v>0</v>
       </c>
       <c r="AM18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN18" t="b">
         <v>1</v>
       </c>
       <c r="AO18" t="n">
-        <v>215.97</v>
-      </c>
-      <c r="AP18" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>1059.07</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1190.26</v>
       </c>
     </row>
     <row r="19">
@@ -3038,12 +3034,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3052,7 +3048,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>37.8</v>
+        <v>36.6</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3061,24 +3057,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>20300000</v>
+        <v>5028000</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="K19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="b">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>20300000</v>
+        <v>5028000</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -3087,85 +3083,89 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>977</v>
+        <v>230.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>977</v>
+        <v>230.5</v>
       </c>
       <c r="R19" t="n">
-        <v>11402888</v>
+        <v>6490514</v>
       </c>
       <c r="S19" t="n">
-        <v>973.4</v>
+        <v>231.1</v>
       </c>
       <c r="T19" t="n">
-        <v>1043.75</v>
+        <v>222.275</v>
       </c>
       <c r="U19" t="n">
-        <v>1045.9</v>
+        <v>222.025</v>
       </c>
       <c r="V19" t="n">
-        <v>954.378163655599</v>
+        <v>218.5139709472656</v>
       </c>
       <c r="W19" t="n">
-        <v>-15.22422037337219</v>
+        <v>4.54476695639687</v>
       </c>
       <c r="X19" t="n">
-        <v>-7.956888759828141</v>
+        <v>4.419014901357135</v>
       </c>
       <c r="Y19" t="n">
-        <v>-7.26733161354405</v>
+        <v>0.1257520550397349</v>
       </c>
       <c r="Z19" t="n">
-        <v>-10.28077090182581</v>
+        <v>0.7171665199265824</v>
       </c>
       <c r="AA19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>-0.042156862745098</v>
+        <v>0.02217294900221733</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.01136422295068207</v>
+        <v>0.01110383392943382</v>
       </c>
       <c r="AD19" t="n">
-        <v>-0.05031734271976285</v>
+        <v>0.01401246902755249</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.004662426416237153</v>
+        <v>0.0044020373949889</v>
       </c>
       <c r="AF19" t="n">
-        <v>-0.054979769136</v>
+        <v>0.009610431632563587</v>
       </c>
       <c r="AG19" t="n">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="AH19" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AI19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>1059.07</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>1190.26</v>
+        <v>0</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3199,15 +3199,15 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5028000</v>
+        <v>1000</v>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="K20" t="b">
         <v>0</v>
@@ -3216,7 +3216,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>5028000</v>
+        <v>1000</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -3225,61 +3225,61 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>230.5</v>
+        <v>485</v>
       </c>
       <c r="Q20" t="n">
-        <v>230.5</v>
+        <v>485</v>
       </c>
       <c r="R20" t="n">
-        <v>6599333</v>
+        <v>13838378</v>
       </c>
       <c r="S20" t="n">
-        <v>231.1</v>
+        <v>513.4</v>
       </c>
       <c r="T20" t="n">
-        <v>222.275</v>
+        <v>476.7</v>
       </c>
       <c r="U20" t="n">
-        <v>222.025</v>
+        <v>473.875</v>
       </c>
       <c r="V20" t="n">
-        <v>218.5139709472656</v>
+        <v>462.8774480183919</v>
       </c>
       <c r="W20" t="n">
-        <v>4.54476695639687</v>
+        <v>18.27184947733946</v>
       </c>
       <c r="X20" t="n">
-        <v>4.419014901357135</v>
+        <v>23.08834182168413</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.1257520550397349</v>
+        <v>-4.816492344344674</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.7171665199265824</v>
+        <v>-0.6158480075517936</v>
       </c>
       <c r="AA20" t="b">
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.02217294900221733</v>
+        <v>0.1318553092182031</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.01110383392943382</v>
+        <v>-0.3039718654059238</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.01401246902755249</v>
+        <v>0.1236948292435383</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.0044020373949889</v>
+        <v>-0.3106736619403687</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.009610431632563587</v>
+        <v>0.434368491183907</v>
       </c>
       <c r="AG20" t="n">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="AH20" t="n">
-        <v>72</v>
+        <v>6</v>
       </c>
       <c r="AI20" t="b">
         <v>1</v>
@@ -3288,21 +3288,19 @@
         <v>1</v>
       </c>
       <c r="AK20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="b">
         <v>0</v>
       </c>
       <c r="AN20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>539.3200000000001</v>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
@@ -3318,12 +3316,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3332,7 +3330,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>36.6</v>
+        <v>34.8</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3341,7 +3339,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -3349,7 +3347,7 @@
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="K21" t="b">
         <v>0</v>
@@ -3367,61 +3365,61 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>485</v>
+        <v>336.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>485</v>
+        <v>336.5</v>
       </c>
       <c r="R21" t="n">
-        <v>14656857</v>
+        <v>10850704</v>
       </c>
       <c r="S21" t="n">
-        <v>513.4</v>
+        <v>338</v>
       </c>
       <c r="T21" t="n">
-        <v>476.7</v>
+        <v>333.975</v>
       </c>
       <c r="U21" t="n">
-        <v>473.875</v>
+        <v>333.525</v>
       </c>
       <c r="V21" t="n">
-        <v>462.8774480183919</v>
+        <v>334.3058400472005</v>
       </c>
       <c r="W21" t="n">
-        <v>18.27184947733946</v>
+        <v>2.73096366220733</v>
       </c>
       <c r="X21" t="n">
-        <v>23.08834182168414</v>
+        <v>3.584727047892501</v>
       </c>
       <c r="Y21" t="n">
-        <v>-4.816492344344681</v>
+        <v>-0.8537633856851707</v>
       </c>
       <c r="Z21" t="n">
-        <v>-0.6158480075518042</v>
+        <v>-0.6029421409144229</v>
       </c>
       <c r="AA21" t="b">
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.1318553092182031</v>
+        <v>0.02748091603053426</v>
       </c>
       <c r="AC21" t="n">
-        <v>-0.3039718654059238</v>
+        <v>-0.06684531260895965</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.1236948292435383</v>
+        <v>0.01932043605586942</v>
       </c>
       <c r="AE21" t="n">
-        <v>-0.3106736619403687</v>
+        <v>-0.07354710914340457</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.434368491183907</v>
+        <v>0.09286754519927398</v>
       </c>
       <c r="AG21" t="n">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="AH21" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="AI21" t="b">
         <v>1</v>
@@ -3442,7 +3440,7 @@
         <v>1</v>
       </c>
       <c r="AO21" t="n">
-        <v>539.3200000000001</v>
+        <v>346.6</v>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
@@ -3458,12 +3456,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3476,20 +3474,20 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Sell</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1000</v>
+        <v>446000</v>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="K22" t="b">
         <v>0</v>
@@ -3498,70 +3496,70 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1000</v>
+        <v>637000</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>-191000</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>-0.2998430141287284</v>
       </c>
       <c r="P22" t="n">
-        <v>336.5</v>
+        <v>3480</v>
       </c>
       <c r="Q22" t="n">
-        <v>336.5</v>
+        <v>3480</v>
       </c>
       <c r="R22" t="n">
-        <v>10997504</v>
+        <v>1060301</v>
       </c>
       <c r="S22" t="n">
-        <v>338</v>
+        <v>3570</v>
       </c>
       <c r="T22" t="n">
-        <v>333.975</v>
+        <v>3052</v>
       </c>
       <c r="U22" t="n">
-        <v>333.525</v>
+        <v>3027.5</v>
       </c>
       <c r="V22" t="n">
-        <v>334.3058400472005</v>
+        <v>2927.079142252604</v>
       </c>
       <c r="W22" t="n">
-        <v>2.73096366220733</v>
+        <v>210.4160916274086</v>
       </c>
       <c r="X22" t="n">
-        <v>3.584727047892501</v>
+        <v>165.3148866757759</v>
       </c>
       <c r="Y22" t="n">
-        <v>-0.8537633856851707</v>
+        <v>45.10120495163272</v>
       </c>
       <c r="Z22" t="n">
-        <v>-0.6029421409144229</v>
+        <v>76.13910869752348</v>
       </c>
       <c r="AA22" t="b">
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.02748091603053426</v>
+        <v>0.1638795986622072</v>
       </c>
       <c r="AC22" t="n">
-        <v>-0.06684531260895965</v>
+        <v>-0.03081196953418652</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.01932043605586942</v>
+        <v>0.1557191186875424</v>
       </c>
       <c r="AE22" t="n">
-        <v>-0.07354710914340457</v>
+        <v>-0.03751376606863144</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.09286754519927398</v>
+        <v>0.1932328847561738</v>
       </c>
       <c r="AG22" t="n">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="AH22" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="AI22" t="b">
         <v>1</v>
@@ -3570,19 +3568,21 @@
         <v>1</v>
       </c>
       <c r="AK22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM22" t="b">
         <v>0</v>
       </c>
       <c r="AN22" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>346.6</v>
+        <v>0</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -3653,7 +3653,7 @@
         <v>17885</v>
       </c>
       <c r="R23" t="n">
-        <v>229307</v>
+        <v>206906</v>
       </c>
       <c r="S23" t="n">
         <v>18725</v>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -3795,7 +3795,7 @@
         <v>531</v>
       </c>
       <c r="R24" t="n">
-        <v>1934780</v>
+        <v>1776618</v>
       </c>
       <c r="S24" t="n">
         <v>581.4</v>
@@ -3813,13 +3813,13 @@
         <v>4.542231291026837</v>
       </c>
       <c r="X24" t="n">
-        <v>18.69904312455205</v>
+        <v>18.69904312455204</v>
       </c>
       <c r="Y24" t="n">
         <v>-14.15681183352521</v>
       </c>
       <c r="Z24" t="n">
-        <v>-9.085081964823583</v>
+        <v>-9.085081964823576</v>
       </c>
       <c r="AA24" t="b">
         <v>0</v>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K25" t="b">
         <v>0</v>
@@ -3933,7 +3933,7 @@
         <v>221.5</v>
       </c>
       <c r="R25" t="n">
-        <v>9309091</v>
+        <v>8951713</v>
       </c>
       <c r="S25" t="n">
         <v>229.2</v>
@@ -4039,7 +4039,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -4071,7 +4071,7 @@
         <v>1080</v>
       </c>
       <c r="R26" t="n">
-        <v>6332246</v>
+        <v>6190632</v>
       </c>
       <c r="S26" t="n">
         <v>1067</v>
@@ -4089,13 +4089,13 @@
         <v>-28.25392534665025</v>
       </c>
       <c r="X26" t="n">
-        <v>-15.05066810371136</v>
+        <v>-15.05066810371143</v>
       </c>
       <c r="Y26" t="n">
-        <v>-13.20325724293889</v>
+        <v>-13.20325724293882</v>
       </c>
       <c r="Z26" t="n">
-        <v>-17.55514346907307</v>
+        <v>-17.55514346907299</v>
       </c>
       <c r="AA26" t="b">
         <v>1</v>
@@ -4177,7 +4177,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -4209,7 +4209,7 @@
         <v>18.89999961853027</v>
       </c>
       <c r="R27" t="n">
-        <v>26774343</v>
+        <v>26719960</v>
       </c>
       <c r="S27" t="n">
         <v>19.07000007629394</v>
@@ -4227,13 +4227,13 @@
         <v>-0.02029280309746895</v>
       </c>
       <c r="X27" t="n">
-        <v>-0.004584705488016895</v>
+        <v>-0.00458470548801689</v>
       </c>
       <c r="Y27" t="n">
-        <v>-0.01570809760945205</v>
+        <v>-0.01570809760945206</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.003710652179192185</v>
+        <v>0.003710652179192178</v>
       </c>
       <c r="AA27" t="b">
         <v>0</v>
@@ -4315,7 +4315,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -4347,7 +4347,7 @@
         <v>1250</v>
       </c>
       <c r="R28" t="n">
-        <v>1654954</v>
+        <v>1568860</v>
       </c>
       <c r="S28" t="n">
         <v>1323</v>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -4483,7 +4483,7 @@
         <v>493</v>
       </c>
       <c r="R29" t="n">
-        <v>38361401</v>
+        <v>36289746</v>
       </c>
       <c r="S29" t="n">
         <v>515.8</v>
@@ -4498,16 +4498,16 @@
         <v>461.0137659708659</v>
       </c>
       <c r="W29" t="n">
-        <v>3.08743414741798</v>
+        <v>3.087434147418037</v>
       </c>
       <c r="X29" t="n">
-        <v>8.592254632288753</v>
+        <v>8.592254632288817</v>
       </c>
       <c r="Y29" t="n">
-        <v>-5.504820484870773</v>
+        <v>-5.50482048487078</v>
       </c>
       <c r="Z29" t="n">
-        <v>-3.555447643126836</v>
+        <v>-3.555447643126843</v>
       </c>
       <c r="AA29" t="b">
         <v>0</v>
@@ -4589,7 +4589,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -4621,7 +4621,7 @@
         <v>6890</v>
       </c>
       <c r="R30" t="n">
-        <v>477442</v>
+        <v>439537</v>
       </c>
       <c r="S30" t="n">
         <v>7213</v>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -4763,7 +4763,7 @@
         <v>1030</v>
       </c>
       <c r="R31" t="n">
-        <v>4392806</v>
+        <v>4200828</v>
       </c>
       <c r="S31" t="n">
         <v>1074</v>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -4903,7 +4903,7 @@
         <v>495</v>
       </c>
       <c r="R32" t="n">
-        <v>18704156</v>
+        <v>18333613</v>
       </c>
       <c r="S32" t="n">
         <v>499.5</v>
@@ -5013,7 +5013,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -5045,7 +5045,7 @@
         <v>76.5</v>
       </c>
       <c r="R33" t="n">
-        <v>742720</v>
+        <v>730131</v>
       </c>
       <c r="S33" t="n">
         <v>76.31999969482422</v>
@@ -5063,13 +5063,13 @@
         <v>-0.3923867331361492</v>
       </c>
       <c r="X33" t="n">
-        <v>-0.2160973872349223</v>
+        <v>-0.2160973872349232</v>
       </c>
       <c r="Y33" t="n">
-        <v>-0.176289345901227</v>
+        <v>-0.1762893459012261</v>
       </c>
       <c r="Z33" t="n">
-        <v>-0.2149443420343282</v>
+        <v>-0.2149443420343271</v>
       </c>
       <c r="AA33" t="b">
         <v>1</v>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -5183,7 +5183,7 @@
         <v>157.5</v>
       </c>
       <c r="R34" t="n">
-        <v>8916668</v>
+        <v>8835730</v>
       </c>
       <c r="S34" t="n">
         <v>156.8</v>
@@ -5201,13 +5201,13 @@
         <v>1.022531623645705</v>
       </c>
       <c r="X34" t="n">
-        <v>-0.3608630683825204</v>
+        <v>-0.3608630683825206</v>
       </c>
       <c r="Y34" t="n">
         <v>1.383394692028225</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.531623059900007</v>
+        <v>1.531623059900008</v>
       </c>
       <c r="AA34" t="b">
         <v>0</v>
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -5323,7 +5323,7 @@
         <v>183</v>
       </c>
       <c r="R35" t="n">
-        <v>6099711</v>
+        <v>5939599</v>
       </c>
       <c r="S35" t="n">
         <v>197.7</v>
@@ -5338,16 +5338,16 @@
         <v>190.8137947082519</v>
       </c>
       <c r="W35" t="n">
-        <v>-0.5061848703785756</v>
+        <v>-0.5061848703786325</v>
       </c>
       <c r="X35" t="n">
-        <v>3.391017077474064</v>
+        <v>3.391017077474009</v>
       </c>
       <c r="Y35" t="n">
-        <v>-3.89720194785264</v>
+        <v>-3.897201947852642</v>
       </c>
       <c r="Z35" t="n">
-        <v>-2.538479135708376</v>
+        <v>-2.538479135708378</v>
       </c>
       <c r="AA35" t="b">
         <v>0</v>
@@ -5427,7 +5427,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -5459,7 +5459,7 @@
         <v>544</v>
       </c>
       <c r="R36" t="n">
-        <v>35425208</v>
+        <v>33780557</v>
       </c>
       <c r="S36" t="n">
         <v>567.4</v>
@@ -5567,7 +5567,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -5599,7 +5599,7 @@
         <v>248</v>
       </c>
       <c r="R37" t="n">
-        <v>24087118</v>
+        <v>23496234</v>
       </c>
       <c r="S37" t="n">
         <v>251.7</v>
@@ -5617,13 +5617,13 @@
         <v>-0.194215886037</v>
       </c>
       <c r="X37" t="n">
-        <v>0.09963341641249436</v>
+        <v>0.09963341641249028</v>
       </c>
       <c r="Y37" t="n">
-        <v>-0.2938493024494944</v>
+        <v>-0.2938493024494903</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.103580516305714</v>
+        <v>0.1035805163057191</v>
       </c>
       <c r="AA37" t="b">
         <v>0</v>
@@ -5705,7 +5705,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -5737,7 +5737,7 @@
         <v>1620</v>
       </c>
       <c r="R38" t="n">
-        <v>15864605</v>
+        <v>13791960</v>
       </c>
       <c r="S38" t="n">
         <v>1749</v>
@@ -5755,13 +5755,13 @@
         <v>-22.02418909344351</v>
       </c>
       <c r="X38" t="n">
-        <v>0.5316347932180951</v>
+        <v>0.5316347932180774</v>
       </c>
       <c r="Y38" t="n">
-        <v>-22.55582388666161</v>
+        <v>-22.55582388666159</v>
       </c>
       <c r="Z38" t="n">
-        <v>-11.6528857795805</v>
+        <v>-11.65288577958048</v>
       </c>
       <c r="AA38" t="b">
         <v>0</v>
@@ -5843,7 +5843,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -5875,7 +5875,7 @@
         <v>82.30000305175781</v>
       </c>
       <c r="R39" t="n">
-        <v>979637</v>
+        <v>962201</v>
       </c>
       <c r="S39" t="n">
         <v>82.38000030517578</v>
@@ -5893,13 +5893,13 @@
         <v>-0.5113076913983434</v>
       </c>
       <c r="X39" t="n">
-        <v>-0.6317935496088432</v>
+        <v>-0.6317935496088464</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.1204858582104997</v>
+        <v>0.1204858582105029</v>
       </c>
       <c r="Z39" t="n">
-        <v>0.1203361515534197</v>
+        <v>0.1203361515534237</v>
       </c>
       <c r="AA39" t="b">
         <v>1</v>
@@ -5983,7 +5983,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -6015,7 +6015,7 @@
         <v>1885</v>
       </c>
       <c r="R40" t="n">
-        <v>3754695</v>
+        <v>3345431</v>
       </c>
       <c r="S40" t="n">
         <v>1984</v>
@@ -6033,13 +6033,13 @@
         <v>-55.49182145008945</v>
       </c>
       <c r="X40" t="n">
-        <v>-36.5421283528112</v>
+        <v>-36.54212835281149</v>
       </c>
       <c r="Y40" t="n">
-        <v>-18.94969309727825</v>
+        <v>-18.94969309727796</v>
       </c>
       <c r="Z40" t="n">
-        <v>-11.28142977941302</v>
+        <v>-11.28142977941265</v>
       </c>
       <c r="AA40" t="b">
         <v>0</v>
@@ -6121,7 +6121,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -6153,7 +6153,7 @@
         <v>2160</v>
       </c>
       <c r="R41" t="n">
-        <v>2244731</v>
+        <v>2196224</v>
       </c>
       <c r="S41" t="n">
         <v>2234</v>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -6293,7 +6293,7 @@
         <v>86.69999694824219</v>
       </c>
       <c r="R42" t="n">
-        <v>22151183</v>
+        <v>21780838</v>
       </c>
       <c r="S42" t="n">
         <v>90.14000091552734</v>
@@ -6311,13 +6311,13 @@
         <v>-0.1504473050209327</v>
       </c>
       <c r="X42" t="n">
-        <v>0.06893441592339129</v>
+        <v>0.06893441592339755</v>
       </c>
       <c r="Y42" t="n">
-        <v>-0.219381720944324</v>
+        <v>-0.2193817209443303</v>
       </c>
       <c r="Z42" t="n">
-        <v>0.1996662006369617</v>
+        <v>0.1996662006369538</v>
       </c>
       <c r="AA42" t="b">
         <v>0</v>
@@ -6399,7 +6399,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -6431,7 +6431,7 @@
         <v>1285</v>
       </c>
       <c r="R43" t="n">
-        <v>1172895</v>
+        <v>1155113</v>
       </c>
       <c r="S43" t="n">
         <v>1325</v>
@@ -6446,16 +6446,16 @@
         <v>1390.675382486979</v>
       </c>
       <c r="W43" t="n">
-        <v>-38.34298079699261</v>
+        <v>-38.34298079699283</v>
       </c>
       <c r="X43" t="n">
-        <v>-22.40858140587961</v>
+        <v>-22.40858140587989</v>
       </c>
       <c r="Y43" t="n">
-        <v>-15.934399391113</v>
+        <v>-15.93439939111294</v>
       </c>
       <c r="Z43" t="n">
-        <v>-15.25202152236529</v>
+        <v>-15.25202152236522</v>
       </c>
       <c r="AA43" t="b">
         <v>0</v>
@@ -6537,7 +6537,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -6569,7 +6569,7 @@
         <v>5365</v>
       </c>
       <c r="R44" t="n">
-        <v>1091759</v>
+        <v>1026967</v>
       </c>
       <c r="S44" t="n">
         <v>5390</v>
@@ -6587,13 +6587,13 @@
         <v>-46.36179370292848</v>
       </c>
       <c r="X44" t="n">
-        <v>-12.48951245917342</v>
+        <v>-12.48951245917341</v>
       </c>
       <c r="Y44" t="n">
-        <v>-33.87228124375506</v>
+        <v>-33.87228124375507</v>
       </c>
       <c r="Z44" t="n">
-        <v>-40.73263141229518</v>
+        <v>-40.73263141229519</v>
       </c>
       <c r="AA44" t="b">
         <v>1</v>
@@ -6675,7 +6675,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -6707,7 +6707,7 @@
         <v>528</v>
       </c>
       <c r="R45" t="n">
-        <v>339481</v>
+        <v>304420</v>
       </c>
       <c r="S45" t="n">
         <v>546.2</v>
@@ -6725,13 +6725,13 @@
         <v>-9.930945072670511</v>
       </c>
       <c r="X45" t="n">
-        <v>-5.218066277923405</v>
+        <v>-5.218066277923453</v>
       </c>
       <c r="Y45" t="n">
-        <v>-4.712878794747106</v>
+        <v>-4.712878794747057</v>
       </c>
       <c r="Z45" t="n">
-        <v>-3.500110160440482</v>
+        <v>-3.50011016044042</v>
       </c>
       <c r="AA45" t="b">
         <v>0</v>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="H46" t="n">
@@ -6845,7 +6845,7 @@
         <v>902</v>
       </c>
       <c r="R46" t="n">
-        <v>4732383</v>
+        <v>4384025</v>
       </c>
       <c r="S46" t="n">
         <v>940</v>
@@ -6860,16 +6860,16 @@
         <v>1047.686532592773</v>
       </c>
       <c r="W46" t="n">
-        <v>-13.5536782224533</v>
+        <v>-13.55367822245341</v>
       </c>
       <c r="X46" t="n">
-        <v>-8.069000559767273</v>
+        <v>-8.069000559767488</v>
       </c>
       <c r="Y46" t="n">
-        <v>-5.484677662686027</v>
+        <v>-5.484677662685925</v>
       </c>
       <c r="Z46" t="n">
-        <v>-2.415558947232716</v>
+        <v>-2.41555894723259</v>
       </c>
       <c r="AA46" t="b">
         <v>0</v>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="H47" t="n">
@@ -6983,7 +6983,7 @@
         <v>900</v>
       </c>
       <c r="R47" t="n">
-        <v>748149</v>
+        <v>662890</v>
       </c>
       <c r="S47" t="n">
         <v>914</v>
@@ -7089,7 +7089,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="H48" t="n">
@@ -7121,7 +7121,7 @@
         <v>5620</v>
       </c>
       <c r="R48" t="n">
-        <v>737868</v>
+        <v>682671</v>
       </c>
       <c r="S48" t="n">
         <v>5628</v>
@@ -7229,7 +7229,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="H49" t="n">
@@ -7261,7 +7261,7 @@
         <v>3650</v>
       </c>
       <c r="R49" t="n">
-        <v>5577395</v>
+        <v>4843755</v>
       </c>
       <c r="S49" t="n">
         <v>3936</v>
@@ -7276,16 +7276,16 @@
         <v>3842.62412516276</v>
       </c>
       <c r="W49" t="n">
-        <v>8.454417129689773</v>
+        <v>8.454417129688409</v>
       </c>
       <c r="X49" t="n">
-        <v>65.33279409402078</v>
+        <v>65.33279409401921</v>
       </c>
       <c r="Y49" t="n">
-        <v>-56.87837696433101</v>
+        <v>-56.8783769643308</v>
       </c>
       <c r="Z49" t="n">
-        <v>-22.6162914770495</v>
+        <v>-22.61629147704922</v>
       </c>
       <c r="AA49" t="b">
         <v>0</v>
@@ -7367,7 +7367,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="H50" t="n">
@@ -7399,7 +7399,7 @@
         <v>1875</v>
       </c>
       <c r="R50" t="n">
-        <v>1894326</v>
+        <v>1729263</v>
       </c>
       <c r="S50" t="n">
         <v>1957</v>
@@ -7503,7 +7503,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -7535,7 +7535,7 @@
         <v>1365</v>
       </c>
       <c r="R51" t="n">
-        <v>4601278</v>
+        <v>4438145</v>
       </c>
       <c r="S51" t="n">
         <v>1364</v>
@@ -7553,10 +7553,10 @@
         <v>-28.33139062945816</v>
       </c>
       <c r="X51" t="n">
-        <v>-20.39418930163114</v>
+        <v>-20.39418930163115</v>
       </c>
       <c r="Y51" t="n">
-        <v>-7.937201327827012</v>
+        <v>-7.937201327827005</v>
       </c>
       <c r="Z51" t="n">
         <v>-10.82961256345573</v>

--- a/output/daily_screen_latest.xlsx
+++ b/output/daily_screen_latest.xlsx
@@ -648,12 +648,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -662,24 +662,24 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>13138450</v>
+        <v>6628000</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K2" t="b">
         <v>1</v>
@@ -688,70 +688,70 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>12818450</v>
+        <v>6628000</v>
       </c>
       <c r="N2" t="n">
-        <v>320000</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0.02496401671028868</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>291.5</v>
+        <v>268.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>291.5</v>
+        <v>268.5</v>
       </c>
       <c r="R2" t="n">
-        <v>60882971</v>
+        <v>28876533</v>
       </c>
       <c r="S2" t="n">
-        <v>267.3</v>
+        <v>236.9</v>
       </c>
       <c r="T2" t="n">
-        <v>262.6</v>
+        <v>229.125</v>
       </c>
       <c r="U2" t="n">
-        <v>259.625</v>
+        <v>225.85</v>
       </c>
       <c r="V2" t="n">
-        <v>264.8771377563477</v>
+        <v>219.4216664632162</v>
       </c>
       <c r="W2" t="n">
-        <v>4.90951589695112</v>
+        <v>7.157331818098015</v>
       </c>
       <c r="X2" t="n">
-        <v>3.616993575845766</v>
+        <v>4.149254290737223</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.292522321105354</v>
+        <v>3.008077527360792</v>
       </c>
       <c r="Z2" t="n">
-        <v>-1.290442307315957</v>
+        <v>-0.06954122606925317</v>
       </c>
       <c r="AA2" t="b">
         <v>1</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.2564655172413792</v>
+        <v>0.3226600985221675</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.002455046170491415</v>
+        <v>0.2766291981904738</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.2132042304846948</v>
+        <v>0.2793988117654831</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.02246332732296497</v>
+        <v>0.2566209170380003</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.2356675578076598</v>
+        <v>0.02277789472748282</v>
       </c>
       <c r="AG2" t="n">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="AH2" t="n">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="AI2" t="b">
         <v>1</v>
@@ -790,12 +790,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -813,15 +813,15 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>6628000</v>
+        <v>89118000</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K3" t="b">
         <v>1</v>
@@ -830,7 +830,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>6628000</v>
+        <v>89118000</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -839,61 +839,61 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>268.5</v>
+        <v>156</v>
       </c>
       <c r="Q3" t="n">
-        <v>268.5</v>
+        <v>156</v>
       </c>
       <c r="R3" t="n">
-        <v>29318025</v>
+        <v>301927693</v>
       </c>
       <c r="S3" t="n">
-        <v>236.9</v>
+        <v>145.3</v>
       </c>
       <c r="T3" t="n">
-        <v>229.125</v>
+        <v>134.7</v>
       </c>
       <c r="U3" t="n">
-        <v>225.85</v>
+        <v>132.725</v>
       </c>
       <c r="V3" t="n">
-        <v>219.4216664632162</v>
+        <v>135.3345667521159</v>
       </c>
       <c r="W3" t="n">
-        <v>7.157331818098015</v>
+        <v>5.85870226863986</v>
       </c>
       <c r="X3" t="n">
-        <v>4.149254290737224</v>
+        <v>4.271703269031681</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.008077527360792</v>
+        <v>1.586998999608179</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.06954122606925406</v>
+        <v>0.8331355950464547</v>
       </c>
       <c r="AA3" t="b">
         <v>1</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3226600985221675</v>
+        <v>0.3390557939914163</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.2766291981904738</v>
+        <v>-0.03250101068831279</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.2793988117654831</v>
+        <v>0.2957945072347319</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.2566209170380003</v>
+        <v>-0.05250929184078634</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.02277789472748282</v>
+        <v>0.3483037990755182</v>
       </c>
       <c r="AG3" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="AH3" t="n">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="AI3" t="b">
         <v>1</v>
@@ -932,12 +932,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>94.2</v>
+        <v>91.2</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,15 +955,15 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>89118000</v>
+        <v>13138450</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K4" t="b">
         <v>1</v>
@@ -972,7 +972,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>89118000</v>
+        <v>13138450</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -981,61 +981,61 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>156</v>
+        <v>291.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>156</v>
+        <v>291.5</v>
       </c>
       <c r="R4" t="n">
-        <v>304492774</v>
+        <v>57571978</v>
       </c>
       <c r="S4" t="n">
-        <v>145.3</v>
+        <v>267.3</v>
       </c>
       <c r="T4" t="n">
-        <v>134.7</v>
+        <v>262.6</v>
       </c>
       <c r="U4" t="n">
-        <v>132.725</v>
+        <v>259.625</v>
       </c>
       <c r="V4" t="n">
-        <v>135.3345667521159</v>
+        <v>264.8771377563477</v>
       </c>
       <c r="W4" t="n">
-        <v>5.85870226863986</v>
+        <v>4.90951589695112</v>
       </c>
       <c r="X4" t="n">
-        <v>4.271703269031672</v>
+        <v>3.616993575845758</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.586998999608188</v>
+        <v>1.292522321105362</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.8331355950464654</v>
+        <v>-1.290442307315947</v>
       </c>
       <c r="AA4" t="b">
         <v>1</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3390557939914163</v>
+        <v>0.2564655172413792</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.03250101068831279</v>
+        <v>-0.002455046170491415</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.2957945072347319</v>
+        <v>0.2132042304846948</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.05250929184078634</v>
+        <v>-0.02246332732296497</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.3483037990755182</v>
+        <v>0.2356675578076598</v>
       </c>
       <c r="AG4" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="AH4" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="AI4" t="b">
         <v>1</v>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>86.8</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1129,7 +1129,7 @@
         <v>7150</v>
       </c>
       <c r="R5" t="n">
-        <v>2665795</v>
+        <v>2507803</v>
       </c>
       <c r="S5" t="n">
         <v>6451</v>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>86.2</v>
+        <v>87</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1271,7 +1271,7 @@
         <v>638</v>
       </c>
       <c r="R6" t="n">
-        <v>26277732</v>
+        <v>24914833</v>
       </c>
       <c r="S6" t="n">
         <v>612.2</v>
@@ -1289,13 +1289,13 @@
         <v>4.54865328040853</v>
       </c>
       <c r="X6" t="n">
-        <v>3.361785660942133</v>
+        <v>3.361785660942132</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.186867619466397</v>
+        <v>1.186867619466398</v>
       </c>
       <c r="Z6" t="n">
-        <v>-1.26328025977577</v>
+        <v>-1.263280259775768</v>
       </c>
       <c r="AA6" t="b">
         <v>1</v>
@@ -1372,7 +1372,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>84.60000000000001</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1413,7 +1413,7 @@
         <v>1430</v>
       </c>
       <c r="R7" t="n">
-        <v>2470296</v>
+        <v>2284855</v>
       </c>
       <c r="S7" t="n">
         <v>1297</v>
@@ -1514,7 +1514,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>84.39999999999999</v>
+        <v>85.19999999999999</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1555,7 +1555,7 @@
         <v>19290</v>
       </c>
       <c r="R8" t="n">
-        <v>258325</v>
+        <v>226587</v>
       </c>
       <c r="S8" t="n">
         <v>18263</v>
@@ -1573,13 +1573,13 @@
         <v>501.2090599220355</v>
       </c>
       <c r="X8" t="n">
-        <v>498.3696675948676</v>
+        <v>498.3696675948691</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.8393923271679</v>
+        <v>2.839392327166422</v>
       </c>
       <c r="Z8" t="n">
-        <v>-86.09304502013049</v>
+        <v>-86.09304502013237</v>
       </c>
       <c r="AA8" t="b">
         <v>1</v>
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>80.40000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1697,7 +1697,7 @@
         <v>2460</v>
       </c>
       <c r="R9" t="n">
-        <v>37087655</v>
+        <v>35352856</v>
       </c>
       <c r="S9" t="n">
         <v>2403.2029296875</v>
@@ -1712,16 +1712,16 @@
         <v>2391.566548665365</v>
       </c>
       <c r="W9" t="n">
-        <v>6.683577550756127</v>
+        <v>6.683577553562827</v>
       </c>
       <c r="X9" t="n">
-        <v>5.805527534525496</v>
+        <v>5.805527540120512</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.8780500162306311</v>
+        <v>0.8780500134423157</v>
       </c>
       <c r="Z9" t="n">
-        <v>-4.850089968250263</v>
+        <v>-4.850089971385047</v>
       </c>
       <c r="AA9" t="b">
         <v>1</v>
@@ -1798,7 +1798,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>80.40000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1839,7 +1839,7 @@
         <v>168.5</v>
       </c>
       <c r="R10" t="n">
-        <v>39800574</v>
+        <v>39566848</v>
       </c>
       <c r="S10" t="n">
         <v>162.5</v>
@@ -1857,13 +1857,13 @@
         <v>4.841302244193912</v>
       </c>
       <c r="X10" t="n">
-        <v>3.603842163751634</v>
+        <v>3.603842163751633</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.237460080442278</v>
+        <v>1.237460080442279</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.882380615828207</v>
+        <v>0.8823806158282088</v>
       </c>
       <c r="AA10" t="b">
         <v>1</v>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>78.2</v>
+        <v>79</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1981,7 +1981,7 @@
         <v>2290</v>
       </c>
       <c r="R11" t="n">
-        <v>2561193</v>
+        <v>2467978</v>
       </c>
       <c r="S11" t="n">
         <v>2137</v>
@@ -2002,10 +2002,10 @@
         <v>17.73224598950311</v>
       </c>
       <c r="Y11" t="n">
-        <v>6.019440368839227</v>
+        <v>6.019440368839231</v>
       </c>
       <c r="Z11" t="n">
-        <v>-10.7947947427672</v>
+        <v>-10.79479474276719</v>
       </c>
       <c r="AA11" t="b">
         <v>1</v>
@@ -2082,7 +2082,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>74.2</v>
+        <v>75</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -2123,7 +2123,7 @@
         <v>94</v>
       </c>
       <c r="R12" t="n">
-        <v>41307139</v>
+        <v>40838185</v>
       </c>
       <c r="S12" t="n">
         <v>87.75999908447265</v>
@@ -2141,13 +2141,13 @@
         <v>-0.1445699702847065</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.4191349979368822</v>
+        <v>-0.4191349979368845</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.2745650276521757</v>
+        <v>0.274565027652178</v>
       </c>
       <c r="Z12" t="n">
-        <v>-0.4784430208420858</v>
+        <v>-0.478443020842083</v>
       </c>
       <c r="AA12" t="b">
         <v>1</v>
@@ -2224,7 +2224,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>73.39999999999999</v>
+        <v>74.19999999999999</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -2265,7 +2265,7 @@
         <v>172</v>
       </c>
       <c r="R13" t="n">
-        <v>32376510</v>
+        <v>32080817</v>
       </c>
       <c r="S13" t="n">
         <v>161.6</v>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>72.8</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -2407,7 +2407,7 @@
         <v>343</v>
       </c>
       <c r="R14" t="n">
-        <v>21472344</v>
+        <v>21255470</v>
       </c>
       <c r="S14" t="n">
         <v>338.6</v>
@@ -2425,13 +2425,13 @@
         <v>2.63249156037142</v>
       </c>
       <c r="X14" t="n">
-        <v>2.594405376900291</v>
+        <v>2.594405376900235</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.03808618347112969</v>
+        <v>0.03808618347118564</v>
       </c>
       <c r="Z14" t="n">
-        <v>-0.2171913959405547</v>
+        <v>-0.2171913959404845</v>
       </c>
       <c r="AA14" t="b">
         <v>1</v>
@@ -2494,12 +2494,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2508,7 +2508,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>69.59999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2517,15 +2517,15 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2546000</v>
+        <v>1000</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="K15" t="b">
         <v>0</v>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2546000</v>
+        <v>1000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2543,61 +2543,61 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>5800</v>
+        <v>568</v>
       </c>
       <c r="Q15" t="n">
-        <v>5800</v>
+        <v>568</v>
       </c>
       <c r="R15" t="n">
-        <v>819542</v>
+        <v>790739</v>
       </c>
       <c r="S15" t="n">
-        <v>5587</v>
+        <v>545</v>
       </c>
       <c r="T15" t="n">
-        <v>5421.5</v>
+        <v>559.15</v>
       </c>
       <c r="U15" t="n">
-        <v>5404.75</v>
+        <v>559.05</v>
       </c>
       <c r="V15" t="n">
-        <v>5859.152449544271</v>
+        <v>583.5542490641276</v>
       </c>
       <c r="W15" t="n">
-        <v>40.07770455340778</v>
+        <v>-4.520297081422996</v>
       </c>
       <c r="X15" t="n">
-        <v>-9.399118806738633</v>
+        <v>-7.327279189040619</v>
       </c>
       <c r="Y15" t="n">
-        <v>49.47682336014642</v>
+        <v>2.806982107617623</v>
       </c>
       <c r="Z15" t="n">
-        <v>32.49559175977198</v>
+        <v>0.06981058845947175</v>
       </c>
       <c r="AA15" t="b">
         <v>1</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.06129917657822515</v>
+        <v>0.003533568904593665</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.1046431035983798</v>
+        <v>-0.05131173484512697</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.01803788982154075</v>
+        <v>-0.03972771785209073</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0.1246513847508534</v>
+        <v>-0.07132001599760052</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.1426892745723941</v>
+        <v>0.03159229814550979</v>
       </c>
       <c r="AG15" t="n">
-        <v>57.99999999999999</v>
+        <v>36</v>
       </c>
       <c r="AH15" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="AI15" t="b">
         <v>1</v>
@@ -2636,12 +2636,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>64.40000000000001</v>
+        <v>64</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2659,15 +2659,15 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1000</v>
+        <v>3988000</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="K16" t="b">
         <v>0</v>
@@ -2676,7 +2676,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1000</v>
+        <v>3988000</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2685,61 +2685,61 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>568</v>
+        <v>83.19999694824219</v>
       </c>
       <c r="Q16" t="n">
-        <v>568</v>
+        <v>83.19999694824219</v>
       </c>
       <c r="R16" t="n">
-        <v>823895</v>
+        <v>926007</v>
       </c>
       <c r="S16" t="n">
-        <v>545</v>
+        <v>82.21999816894531</v>
       </c>
       <c r="T16" t="n">
-        <v>559.15</v>
+        <v>82.51499938964844</v>
       </c>
       <c r="U16" t="n">
-        <v>559.05</v>
+        <v>82.45499954223632</v>
       </c>
       <c r="V16" t="n">
-        <v>583.5542490641276</v>
+        <v>88.16086870829264</v>
       </c>
       <c r="W16" t="n">
-        <v>-4.520297081422996</v>
+        <v>-0.2671380369940124</v>
       </c>
       <c r="X16" t="n">
-        <v>-7.327279189040595</v>
+        <v>-0.4930699499440507</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.8069821076176</v>
+        <v>0.2259319129500383</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.06981058845944332</v>
+        <v>0.1261968535915994</v>
       </c>
       <c r="AA16" t="b">
         <v>1</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.003533568904593665</v>
+        <v>0.0146341091249047</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0.05131173484512697</v>
+        <v>-0.1512215814011411</v>
       </c>
       <c r="AD16" t="n">
-        <v>-0.03972771785209073</v>
+        <v>-0.02862717763177969</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0.07132001599760052</v>
+        <v>-0.1712298625536146</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.03159229814550979</v>
+        <v>0.1426026849218349</v>
       </c>
       <c r="AG16" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AH16" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="AI16" t="b">
         <v>1</v>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2792,24 +2792,24 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>63.2</v>
+        <v>61.2</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Sell</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>3988000</v>
+        <v>2544000</v>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K17" t="b">
         <v>0</v>
@@ -2818,70 +2818,70 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3988000</v>
+        <v>2546000</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>-0.0007855459544383347</v>
       </c>
       <c r="P17" t="n">
-        <v>83.19999694824219</v>
+        <v>5800</v>
       </c>
       <c r="Q17" t="n">
-        <v>83.19999694824219</v>
+        <v>5800</v>
       </c>
       <c r="R17" t="n">
-        <v>936837</v>
+        <v>743553</v>
       </c>
       <c r="S17" t="n">
-        <v>82.21999816894531</v>
+        <v>5587</v>
       </c>
       <c r="T17" t="n">
-        <v>82.51499938964844</v>
+        <v>5421.5</v>
       </c>
       <c r="U17" t="n">
-        <v>82.45499954223632</v>
+        <v>5404.75</v>
       </c>
       <c r="V17" t="n">
-        <v>88.16086870829264</v>
+        <v>5859.152449544271</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.2671380369940124</v>
+        <v>40.07770455340778</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.4930699499440415</v>
+        <v>-9.399118806739123</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.2259319129500291</v>
+        <v>49.47682336014691</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.1261968535915878</v>
+        <v>32.49559175977259</v>
       </c>
       <c r="AA17" t="b">
         <v>1</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.0146341091249047</v>
+        <v>0.06129917657822515</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.1512215814011411</v>
+        <v>-0.1046431035983798</v>
       </c>
       <c r="AD17" t="n">
-        <v>-0.02862717763177969</v>
+        <v>0.01803788982154075</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0.1712298625536146</v>
+        <v>-0.1246513847508534</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.1426026849218349</v>
+        <v>0.1426892745723941</v>
       </c>
       <c r="AG17" t="n">
-        <v>40</v>
+        <v>57.99999999999999</v>
       </c>
       <c r="AH17" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="AI17" t="b">
         <v>1</v>
@@ -2934,16 +2934,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>65.8</v>
+        <v>57.39999999999999</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -2960,13 +2960,13 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1731000</v>
+        <v>1773000</v>
       </c>
       <c r="N18" t="n">
-        <v>42000</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0.02426343154246101</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
         <v>2295</v>
@@ -2975,7 +2975,7 @@
         <v>2295</v>
       </c>
       <c r="R18" t="n">
-        <v>1513886</v>
+        <v>1430448</v>
       </c>
       <c r="S18" t="n">
         <v>2124</v>
@@ -2993,13 +2993,13 @@
         <v>40.19777325642099</v>
       </c>
       <c r="X18" t="n">
-        <v>61.2215812731859</v>
+        <v>61.22158127318583</v>
       </c>
       <c r="Y18" t="n">
-        <v>-21.02380801676491</v>
+        <v>-21.02380801676484</v>
       </c>
       <c r="Z18" t="n">
-        <v>-43.73238480091425</v>
+        <v>-43.73238480091416</v>
       </c>
       <c r="AA18" t="b">
         <v>1</v>
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>56.4</v>
+        <v>57.2</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -3115,7 +3115,7 @@
         <v>3520</v>
       </c>
       <c r="R19" t="n">
-        <v>481719</v>
+        <v>450137</v>
       </c>
       <c r="S19" t="n">
         <v>3316</v>
@@ -3130,16 +3130,16 @@
         <v>2916.045678710937</v>
       </c>
       <c r="W19" t="n">
-        <v>92.58585385772358</v>
+        <v>92.58585385772449</v>
       </c>
       <c r="X19" t="n">
-        <v>128.3061201234458</v>
+        <v>128.3061201234465</v>
       </c>
       <c r="Y19" t="n">
-        <v>-35.72026626572224</v>
+        <v>-35.72026626572199</v>
       </c>
       <c r="Z19" t="n">
-        <v>-58.27059034016247</v>
+        <v>-58.27059034016261</v>
       </c>
       <c r="AA19" t="b">
         <v>1</v>
@@ -3214,7 +3214,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53.6</v>
+        <v>54.40000000000001</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K20" t="b">
         <v>0</v>
@@ -3255,7 +3255,7 @@
         <v>3430</v>
       </c>
       <c r="R20" t="n">
-        <v>3710579</v>
+        <v>3510469</v>
       </c>
       <c r="S20" t="n">
         <v>3243</v>
@@ -3273,13 +3273,13 @@
         <v>34.24072461730566</v>
       </c>
       <c r="X20" t="n">
-        <v>68.38340982289499</v>
+        <v>68.38340982289496</v>
       </c>
       <c r="Y20" t="n">
-        <v>-34.14268520558933</v>
+        <v>-34.1426852055893</v>
       </c>
       <c r="Z20" t="n">
-        <v>-60.21748888459419</v>
+        <v>-60.21748888459415</v>
       </c>
       <c r="AA20" t="b">
         <v>1</v>
@@ -3354,7 +3354,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>52.59999999999999</v>
+        <v>53.39999999999999</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -3395,7 +3395,7 @@
         <v>4710</v>
       </c>
       <c r="R21" t="n">
-        <v>9902031</v>
+        <v>9019674</v>
       </c>
       <c r="S21" t="n">
         <v>4546</v>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>45.8</v>
+        <v>46.59999999999999</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -3535,7 +3535,7 @@
         <v>229.5</v>
       </c>
       <c r="R22" t="n">
-        <v>3288686</v>
+        <v>3236175</v>
       </c>
       <c r="S22" t="n">
         <v>224.7</v>
@@ -3553,13 +3553,13 @@
         <v>4.324383270149951</v>
       </c>
       <c r="X22" t="n">
-        <v>5.164658162088113</v>
+        <v>5.164658162088111</v>
       </c>
       <c r="Y22" t="n">
-        <v>-0.8402748919381615</v>
+        <v>-0.8402748919381597</v>
       </c>
       <c r="Z22" t="n">
-        <v>-1.221708814993867</v>
+        <v>-1.221708814993865</v>
       </c>
       <c r="AA22" t="b">
         <v>1</v>
@@ -3634,7 +3634,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>45.2</v>
+        <v>46</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -3675,7 +3675,7 @@
         <v>611</v>
       </c>
       <c r="R23" t="n">
-        <v>10006571</v>
+        <v>9566954</v>
       </c>
       <c r="S23" t="n">
         <v>554</v>
@@ -3693,13 +3693,13 @@
         <v>0.08787589625183045</v>
       </c>
       <c r="X23" t="n">
-        <v>3.415872853763298</v>
+        <v>3.415872853763296</v>
       </c>
       <c r="Y23" t="n">
-        <v>-3.327996957511467</v>
+        <v>-3.327996957511466</v>
       </c>
       <c r="Z23" t="n">
-        <v>-10.98015130813657</v>
+        <v>-10.98015130813656</v>
       </c>
       <c r="AA23" t="b">
         <v>1</v>
@@ -3774,7 +3774,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>44.2</v>
+        <v>45</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -3815,7 +3815,7 @@
         <v>499.5</v>
       </c>
       <c r="R24" t="n">
-        <v>4517729</v>
+        <v>4292625</v>
       </c>
       <c r="S24" t="n">
         <v>497.6</v>
@@ -3830,16 +3830,16 @@
         <v>451.4860285441081</v>
       </c>
       <c r="W24" t="n">
-        <v>7.50141690379121</v>
+        <v>7.501416903791153</v>
       </c>
       <c r="X24" t="n">
-        <v>14.75768191543658</v>
+        <v>14.7576819154365</v>
       </c>
       <c r="Y24" t="n">
-        <v>-7.25626501164537</v>
+        <v>-7.256265011645343</v>
       </c>
       <c r="Z24" t="n">
-        <v>-8.316435980138333</v>
+        <v>-8.316435980138301</v>
       </c>
       <c r="AA24" t="b">
         <v>1</v>
@@ -3914,7 +3914,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>42.40000000000001</v>
+        <v>43.2</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -3955,7 +3955,7 @@
         <v>196</v>
       </c>
       <c r="R25" t="n">
-        <v>3899723</v>
+        <v>3831061</v>
       </c>
       <c r="S25" t="n">
         <v>185.8</v>
@@ -3973,13 +3973,13 @@
         <v>0.3198034157382779</v>
       </c>
       <c r="X25" t="n">
-        <v>1.54174508841428</v>
+        <v>1.541745088414272</v>
       </c>
       <c r="Y25" t="n">
-        <v>-1.221941672676002</v>
+        <v>-1.221941672675994</v>
       </c>
       <c r="Z25" t="n">
-        <v>-2.689292851735097</v>
+        <v>-2.689292851735087</v>
       </c>
       <c r="AA25" t="b">
         <v>1</v>
@@ -4054,7 +4054,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>38.8</v>
+        <v>39.60000000000001</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -4095,7 +4095,7 @@
         <v>102</v>
       </c>
       <c r="R26" t="n">
-        <v>2100526</v>
+        <v>2085504</v>
       </c>
       <c r="S26" t="n">
         <v>100.8800003051758</v>
@@ -4113,13 +4113,13 @@
         <v>2.066400656835398</v>
       </c>
       <c r="X26" t="n">
-        <v>2.24761560500442</v>
+        <v>2.247615605004416</v>
       </c>
       <c r="Y26" t="n">
-        <v>-0.1812149481690222</v>
+        <v>-0.1812149481690177</v>
       </c>
       <c r="Z26" t="n">
-        <v>-0.187520899788967</v>
+        <v>-0.1875208997889617</v>
       </c>
       <c r="AA26" t="b">
         <v>1</v>
@@ -4192,7 +4192,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>38.8</v>
+        <v>39.6</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -4233,7 +4233,7 @@
         <v>250.5</v>
       </c>
       <c r="R27" t="n">
-        <v>44422531</v>
+        <v>43948586</v>
       </c>
       <c r="S27" t="n">
         <v>248.8</v>
@@ -4251,13 +4251,13 @@
         <v>-0.5114268311859291</v>
       </c>
       <c r="X27" t="n">
-        <v>-0.4261924078338075</v>
+        <v>-0.4261924078338091</v>
       </c>
       <c r="Y27" t="n">
-        <v>-0.08523442335212161</v>
+        <v>-0.08523442335212</v>
       </c>
       <c r="Z27" t="n">
-        <v>-0.291258863486621</v>
+        <v>-0.291258863486619</v>
       </c>
       <c r="AA27" t="b">
         <v>1</v>
@@ -4332,7 +4332,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>35.8</v>
+        <v>36.59999999999999</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -4373,7 +4373,7 @@
         <v>525</v>
       </c>
       <c r="R28" t="n">
-        <v>79318936</v>
+        <v>76407003</v>
       </c>
       <c r="S28" t="n">
         <v>488.8</v>
@@ -4470,7 +4470,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>33.8</v>
+        <v>34.6</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -4511,7 +4511,7 @@
         <v>2210</v>
       </c>
       <c r="R29" t="n">
-        <v>6443131</v>
+        <v>5964833</v>
       </c>
       <c r="S29" t="n">
         <v>2030</v>
@@ -4610,7 +4610,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>41.6</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -4651,7 +4651,7 @@
         <v>6430</v>
       </c>
       <c r="R30" t="n">
-        <v>2808375</v>
+        <v>2691196</v>
       </c>
       <c r="S30" t="n">
         <v>6145</v>
@@ -4669,13 +4669,13 @@
         <v>-1.35643354784861</v>
       </c>
       <c r="X30" t="n">
-        <v>173.6438704748119</v>
+        <v>173.6438704748116</v>
       </c>
       <c r="Y30" t="n">
-        <v>-175.0003040226605</v>
+        <v>-175.0003040226602</v>
       </c>
       <c r="Z30" t="n">
-        <v>-229.6430961567775</v>
+        <v>-229.6430961567771</v>
       </c>
       <c r="AA30" t="b">
         <v>1</v>
@@ -4734,12 +4734,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4748,24 +4748,24 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>37.6</v>
+        <v>35.4</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1234000</v>
+        <v>501000</v>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K31" t="b">
         <v>0</v>
@@ -4774,70 +4774,70 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>219000</v>
+        <v>501000</v>
       </c>
       <c r="N31" t="n">
-        <v>1015000</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>4.634703196347032</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1020</v>
+        <v>228.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>1020</v>
+        <v>228.5</v>
       </c>
       <c r="R31" t="n">
-        <v>11121177</v>
+        <v>25619855</v>
       </c>
       <c r="S31" t="n">
-        <v>990.8</v>
+        <v>222.3</v>
       </c>
       <c r="T31" t="n">
-        <v>1057.65</v>
+        <v>231.475</v>
       </c>
       <c r="U31" t="n">
-        <v>1054.9</v>
+        <v>230.725</v>
       </c>
       <c r="V31" t="n">
-        <v>1021.366666666667</v>
+        <v>218.375</v>
       </c>
       <c r="W31" t="n">
-        <v>-17.91455955000981</v>
+        <v>-1.247059460996297</v>
       </c>
       <c r="X31" t="n">
-        <v>-1.791765994811171</v>
+        <v>0.8791686726365886</v>
       </c>
       <c r="Y31" t="n">
-        <v>-16.12279355519864</v>
+        <v>-2.126228133632886</v>
       </c>
       <c r="Z31" t="n">
-        <v>-23.31903874399093</v>
+        <v>-3.319347823319499</v>
       </c>
       <c r="AA31" t="b">
         <v>1</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.05699481865284972</v>
+        <v>0.07025761124121788</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0.1428571428571429</v>
+        <v>0.02696629213483148</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.01373353189616533</v>
+        <v>0.02699632448453348</v>
       </c>
       <c r="AE31" t="n">
-        <v>-0.1628654240096165</v>
+        <v>0.006958010982357932</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.1765989559057818</v>
+        <v>0.02003831350217555</v>
       </c>
       <c r="AG31" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="AH31" t="n">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="AI31" t="b">
         <v>0</v>
@@ -4855,10 +4855,10 @@
         <v>1</v>
       </c>
       <c r="AN31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO31" t="n">
-        <v>1201.56</v>
+        <v>252.72</v>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
@@ -4874,12 +4874,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4888,7 +4888,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>34.59999999999999</v>
+        <v>35.2</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4897,15 +4897,15 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>501000</v>
+        <v>2512000</v>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K32" t="b">
         <v>0</v>
@@ -4914,7 +4914,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>501000</v>
+        <v>2512000</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -4923,61 +4923,61 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>228.5</v>
+        <v>5525</v>
       </c>
       <c r="Q32" t="n">
-        <v>228.5</v>
+        <v>5525</v>
       </c>
       <c r="R32" t="n">
-        <v>25747122</v>
+        <v>1008538</v>
       </c>
       <c r="S32" t="n">
-        <v>222.3</v>
+        <v>5450</v>
       </c>
       <c r="T32" t="n">
-        <v>231.475</v>
+        <v>5621</v>
       </c>
       <c r="U32" t="n">
-        <v>230.725</v>
+        <v>5614.5</v>
       </c>
       <c r="V32" t="n">
-        <v>218.375</v>
+        <v>4428.819962565104</v>
       </c>
       <c r="W32" t="n">
-        <v>-1.247059460996297</v>
+        <v>20.61735946063436</v>
       </c>
       <c r="X32" t="n">
-        <v>0.8791686726365886</v>
+        <v>123.7119118084013</v>
       </c>
       <c r="Y32" t="n">
-        <v>-2.126228133632886</v>
+        <v>-103.0945523477669</v>
       </c>
       <c r="Z32" t="n">
-        <v>-3.319347823319499</v>
+        <v>-127.9880141951272</v>
       </c>
       <c r="AA32" t="b">
         <v>1</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.07025761124121788</v>
+        <v>0.02409638554216875</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.02696629213483148</v>
+        <v>0.6326885157363356</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.02699632448453348</v>
+        <v>-0.01916490121451564</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.006958010982357932</v>
+        <v>0.612680234583862</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.02003831350217555</v>
+        <v>-0.6318451357983776</v>
       </c>
       <c r="AG32" t="n">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="AH32" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="AI32" t="b">
         <v>0</v>
@@ -4995,11 +4995,9 @@
         <v>1</v>
       </c>
       <c r="AN32" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>252.72</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO32" t="inlineStr"/>
       <c r="AP32" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -5014,12 +5012,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5028,7 +5026,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>34.4</v>
+        <v>33.40000000000001</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5037,15 +5035,15 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>2512000</v>
+        <v>1000</v>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="n">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="K33" t="b">
         <v>0</v>
@@ -5054,7 +5052,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>2512000</v>
+        <v>1000</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
@@ -5063,61 +5061,61 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>5525</v>
+        <v>1250</v>
       </c>
       <c r="Q33" t="n">
-        <v>5525</v>
+        <v>1250</v>
       </c>
       <c r="R33" t="n">
-        <v>1045790</v>
+        <v>995532</v>
       </c>
       <c r="S33" t="n">
-        <v>5450</v>
+        <v>1224</v>
       </c>
       <c r="T33" t="n">
-        <v>5621</v>
+        <v>1298.5</v>
       </c>
       <c r="U33" t="n">
-        <v>5614.5</v>
+        <v>1295.75</v>
       </c>
       <c r="V33" t="n">
-        <v>4428.819962565104</v>
+        <v>1138.089337158203</v>
       </c>
       <c r="W33" t="n">
-        <v>20.61735946063436</v>
+        <v>-14.00170947505671</v>
       </c>
       <c r="X33" t="n">
-        <v>123.7119118084014</v>
+        <v>4.868739271976048</v>
       </c>
       <c r="Y33" t="n">
-        <v>-103.094552347767</v>
+        <v>-18.87044874703276</v>
       </c>
       <c r="Z33" t="n">
-        <v>-127.9880141951273</v>
+        <v>-25.27951942064689</v>
       </c>
       <c r="AA33" t="b">
         <v>1</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.02409638554216875</v>
+        <v>0.04602510460251041</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.6326885157363356</v>
+        <v>0.1775713143627822</v>
       </c>
       <c r="AD33" t="n">
-        <v>-0.01916490121451564</v>
+        <v>0.002763817845826022</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.612680234583862</v>
+        <v>0.1575630332103086</v>
       </c>
       <c r="AF33" t="n">
-        <v>-0.6318451357983776</v>
+        <v>-0.1547992153644826</v>
       </c>
       <c r="AG33" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AH33" t="n">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="AI33" t="b">
         <v>0</v>
@@ -5137,7 +5135,9 @@
       <c r="AN33" t="b">
         <v>0</v>
       </c>
-      <c r="AO33" t="inlineStr"/>
+      <c r="AO33" t="n">
+        <v>1462.5</v>
+      </c>
       <c r="AP33" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -5152,12 +5152,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5166,7 +5166,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>32.6</v>
+        <v>31.8</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5175,24 +5175,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1000</v>
+        <v>7240000</v>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="K34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" t="b">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1000</v>
+        <v>7240000</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -5201,67 +5201,67 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1250</v>
+        <v>1735</v>
       </c>
       <c r="Q34" t="n">
-        <v>1250</v>
+        <v>1735</v>
       </c>
       <c r="R34" t="n">
-        <v>1017579</v>
+        <v>12081302</v>
       </c>
       <c r="S34" t="n">
-        <v>1224</v>
+        <v>1684</v>
       </c>
       <c r="T34" t="n">
-        <v>1298.5</v>
+        <v>1749</v>
       </c>
       <c r="U34" t="n">
-        <v>1295.75</v>
+        <v>1749.75</v>
       </c>
       <c r="V34" t="n">
-        <v>1138.089337158203</v>
+        <v>1784.833333333333</v>
       </c>
       <c r="W34" t="n">
-        <v>-14.00170947505671</v>
+        <v>-21.55731083348405</v>
       </c>
       <c r="X34" t="n">
-        <v>4.868739271976094</v>
+        <v>-18.67907128338327</v>
       </c>
       <c r="Y34" t="n">
-        <v>-18.87044874703281</v>
+        <v>-2.87823955010078</v>
       </c>
       <c r="Z34" t="n">
-        <v>-25.27951942064695</v>
+        <v>-10.58539700714683</v>
       </c>
       <c r="AA34" t="b">
         <v>1</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.04602510460251041</v>
+        <v>-0.008571428571428563</v>
       </c>
       <c r="AC34" t="n">
-        <v>0.1775713143627822</v>
+        <v>-0.04143646408839774</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.002763817845826022</v>
+        <v>-0.05183271532811295</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.1575630332103086</v>
+        <v>-0.06144474524087129</v>
       </c>
       <c r="AF34" t="n">
-        <v>-0.1547992153644826</v>
+        <v>0.009612029912758335</v>
       </c>
       <c r="AG34" t="n">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="AH34" t="n">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="AI34" t="b">
         <v>0</v>
       </c>
       <c r="AJ34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="b">
         <v>0</v>
@@ -5273,15 +5273,13 @@
         <v>1</v>
       </c>
       <c r="AN34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO34" t="n">
-        <v>1462.5</v>
-      </c>
-      <c r="AP34" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>1769.7</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1749.74</v>
       </c>
     </row>
     <row r="35">
@@ -5292,12 +5290,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5315,24 +5313,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>7240000</v>
+        <v>2712000</v>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="K35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" t="b">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>7240000</v>
+        <v>2712000</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -5341,67 +5339,67 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1735</v>
+        <v>473</v>
       </c>
       <c r="Q35" t="n">
-        <v>1735</v>
+        <v>473</v>
       </c>
       <c r="R35" t="n">
-        <v>12673351</v>
+        <v>28806674</v>
       </c>
       <c r="S35" t="n">
-        <v>1684</v>
+        <v>481.9</v>
       </c>
       <c r="T35" t="n">
-        <v>1749</v>
+        <v>483.3</v>
       </c>
       <c r="U35" t="n">
-        <v>1749.75</v>
+        <v>481.7</v>
       </c>
       <c r="V35" t="n">
-        <v>1784.833333333333</v>
+        <v>503.5833333333333</v>
       </c>
       <c r="W35" t="n">
-        <v>-21.55731083348405</v>
+        <v>-0.6202561138278497</v>
       </c>
       <c r="X35" t="n">
-        <v>-18.67907128338327</v>
+        <v>2.564723127082567</v>
       </c>
       <c r="Y35" t="n">
-        <v>-2.878239550100783</v>
+        <v>-3.184979240910416</v>
       </c>
       <c r="Z35" t="n">
-        <v>-10.58539700714684</v>
+        <v>-2.320708026354942</v>
       </c>
       <c r="AA35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>-0.008571428571428563</v>
+        <v>0.07256235827664392</v>
       </c>
       <c r="AC35" t="n">
-        <v>-0.04143646408839774</v>
+        <v>-0.1844827586206896</v>
       </c>
       <c r="AD35" t="n">
-        <v>-0.05183271532811295</v>
+        <v>0.02930107151995953</v>
       </c>
       <c r="AE35" t="n">
-        <v>-0.06144474524087129</v>
+        <v>-0.2044910397731632</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.009612029912758335</v>
+        <v>0.2337921112931227</v>
       </c>
       <c r="AG35" t="n">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="AH35" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="AI35" t="b">
         <v>0</v>
       </c>
       <c r="AJ35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK35" t="b">
         <v>0</v>
@@ -5410,16 +5408,18 @@
         <v>0</v>
       </c>
       <c r="AM35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN35" t="b">
         <v>1</v>
       </c>
       <c r="AO35" t="n">
-        <v>1769.7</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>1749.74</v>
+        <v>508.95</v>
+      </c>
+      <c r="AP35" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5444,7 +5444,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>30.2</v>
+        <v>28.8</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5453,24 +5453,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>2712000</v>
+        <v>24987000</v>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="K36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" t="b">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>2712000</v>
+        <v>24987000</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -5479,87 +5479,87 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>473</v>
+        <v>550</v>
       </c>
       <c r="Q36" t="n">
-        <v>473</v>
+        <v>550</v>
       </c>
       <c r="R36" t="n">
-        <v>29733954</v>
+        <v>25526267</v>
       </c>
       <c r="S36" t="n">
-        <v>481.9</v>
+        <v>539.4</v>
       </c>
       <c r="T36" t="n">
-        <v>483.3</v>
+        <v>552.2</v>
       </c>
       <c r="U36" t="n">
-        <v>481.7</v>
+        <v>552.4</v>
       </c>
       <c r="V36" t="n">
-        <v>503.5833333333333</v>
+        <v>661.4083333333333</v>
       </c>
       <c r="W36" t="n">
-        <v>-0.6202561138278497</v>
+        <v>-8.230428016433621</v>
       </c>
       <c r="X36" t="n">
-        <v>2.564723127082567</v>
+        <v>-8.65843188349889</v>
       </c>
       <c r="Y36" t="n">
-        <v>-3.184979240910417</v>
+        <v>0.4280038670652697</v>
       </c>
       <c r="Z36" t="n">
-        <v>-2.320708026354943</v>
+        <v>-1.218632180882587</v>
       </c>
       <c r="AA36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.07256235827664392</v>
+        <v>-0.007220216606498187</v>
       </c>
       <c r="AC36" t="n">
-        <v>-0.1844827586206896</v>
+        <v>-0.458128078817734</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.02930107151995953</v>
+        <v>-0.05048150336318258</v>
       </c>
       <c r="AE36" t="n">
-        <v>-0.2044910397731632</v>
+        <v>-0.4781363599702075</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.2337921112931227</v>
+        <v>0.427654856607025</v>
       </c>
       <c r="AG36" t="n">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="AH36" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AI36" t="b">
         <v>0</v>
       </c>
       <c r="AJ36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN36" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>508.95</v>
-      </c>
-      <c r="AP36" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
+      </c>
+      <c r="AP36" t="n">
+        <v>553.3200000000001</v>
       </c>
     </row>
     <row r="37">
@@ -5570,12 +5570,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5584,7 +5584,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>30</v>
+        <v>28.4</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5593,24 +5593,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>9426000</v>
+        <v>1234000</v>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="K37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" t="b">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>9426000</v>
+        <v>1234000</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -5619,73 +5619,73 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>1100</v>
+        <v>1020</v>
       </c>
       <c r="Q37" t="n">
-        <v>1100</v>
+        <v>1020</v>
       </c>
       <c r="R37" t="n">
-        <v>10156130</v>
+        <v>10826832</v>
       </c>
       <c r="S37" t="n">
-        <v>1082</v>
+        <v>990.8</v>
       </c>
       <c r="T37" t="n">
-        <v>1127.25</v>
+        <v>1057.65</v>
       </c>
       <c r="U37" t="n">
-        <v>1129</v>
+        <v>1054.9</v>
       </c>
       <c r="V37" t="n">
-        <v>1139</v>
+        <v>1021.366666666667</v>
       </c>
       <c r="W37" t="n">
-        <v>-17.74030052988269</v>
+        <v>-17.91455955000981</v>
       </c>
       <c r="X37" t="n">
-        <v>-19.86038036342022</v>
+        <v>-1.791765994811183</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.120079833537535</v>
+        <v>-16.12279355519863</v>
       </c>
       <c r="Z37" t="n">
-        <v>-1.480635292806117</v>
+        <v>-23.31903874399091</v>
       </c>
       <c r="AA37" t="b">
         <v>1</v>
       </c>
       <c r="AB37" t="n">
-        <v>-0.03083700440528636</v>
+        <v>0.05699481865284972</v>
       </c>
       <c r="AC37" t="n">
-        <v>-0.02222222222222225</v>
+        <v>-0.1428571428571429</v>
       </c>
       <c r="AD37" t="n">
-        <v>-0.07409829116197075</v>
+        <v>0.01373353189616533</v>
       </c>
       <c r="AE37" t="n">
-        <v>-0.0422305033746958</v>
+        <v>-0.1628654240096165</v>
       </c>
       <c r="AF37" t="n">
-        <v>-0.03186778778727495</v>
+        <v>0.1765989559057818</v>
       </c>
       <c r="AG37" t="n">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="AH37" t="n">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="AI37" t="b">
         <v>0</v>
       </c>
       <c r="AJ37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM37" t="b">
         <v>1</v>
@@ -5693,13 +5693,13 @@
       <c r="AN37" t="b">
         <v>0</v>
       </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
-      <c r="AP37" t="n">
-        <v>1163.68</v>
+      <c r="AO37" t="n">
+        <v>1201.56</v>
+      </c>
+      <c r="AP37" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5733,15 +5733,15 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>24987000</v>
+        <v>20300000</v>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K38" t="b">
         <v>1</v>
@@ -5750,7 +5750,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>24987000</v>
+        <v>20300000</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -5759,61 +5759,61 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>550</v>
+        <v>981</v>
       </c>
       <c r="Q38" t="n">
-        <v>550</v>
+        <v>981</v>
       </c>
       <c r="R38" t="n">
-        <v>26151583</v>
+        <v>13722988</v>
       </c>
       <c r="S38" t="n">
-        <v>539.4</v>
+        <v>960.6</v>
       </c>
       <c r="T38" t="n">
-        <v>552.2</v>
+        <v>1002.9</v>
       </c>
       <c r="U38" t="n">
-        <v>552.4</v>
+        <v>1008.1</v>
       </c>
       <c r="V38" t="n">
-        <v>661.4083333333333</v>
+        <v>952.8452178955079</v>
       </c>
       <c r="W38" t="n">
-        <v>-8.230428016433621</v>
+        <v>-13.45221730330491</v>
       </c>
       <c r="X38" t="n">
-        <v>-8.658431883498887</v>
+        <v>-12.96256747875982</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.4280038670652662</v>
+        <v>-0.4896498245450864</v>
       </c>
       <c r="Z38" t="n">
-        <v>-1.21863218088259</v>
+        <v>-4.49436641753198</v>
       </c>
       <c r="AA38" t="b">
         <v>1</v>
       </c>
       <c r="AB38" t="n">
-        <v>-0.007220216606498187</v>
+        <v>-0.09585253456221199</v>
       </c>
       <c r="AC38" t="n">
-        <v>-0.458128078817734</v>
+        <v>0.008214088321632396</v>
       </c>
       <c r="AD38" t="n">
-        <v>-0.05048150336318258</v>
+        <v>-0.1391138213188964</v>
       </c>
       <c r="AE38" t="n">
-        <v>-0.4781363599702075</v>
+        <v>-0.01179419283084115</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.427654856607025</v>
+        <v>-0.1273196284880552</v>
       </c>
       <c r="AG38" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="AH38" t="n">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="AI38" t="b">
         <v>0</v>
@@ -5822,24 +5822,22 @@
         <v>0</v>
       </c>
       <c r="AK38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM38" t="b">
         <v>1</v>
       </c>
       <c r="AN38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>986.89</v>
       </c>
       <c r="AP38" t="n">
-        <v>553.3200000000001</v>
+        <v>1098.05</v>
       </c>
     </row>
     <row r="39">
@@ -5850,12 +5848,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5864,7 +5862,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>27.2</v>
+        <v>26.6</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5873,24 +5871,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>20300000</v>
+        <v>1000</v>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="K39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" t="b">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>20300000</v>
+        <v>1000</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -5899,85 +5897,89 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>981</v>
+        <v>944</v>
       </c>
       <c r="Q39" t="n">
-        <v>981</v>
+        <v>944</v>
       </c>
       <c r="R39" t="n">
-        <v>14413731</v>
+        <v>15371023</v>
       </c>
       <c r="S39" t="n">
-        <v>960.6</v>
+        <v>921.4</v>
       </c>
       <c r="T39" t="n">
-        <v>1002.9</v>
+        <v>947.85</v>
       </c>
       <c r="U39" t="n">
-        <v>1008.1</v>
+        <v>947.7</v>
       </c>
       <c r="V39" t="n">
-        <v>952.8452178955079</v>
+        <v>1040.361715698242</v>
       </c>
       <c r="W39" t="n">
-        <v>-13.45221730330491</v>
+        <v>-10.50465947284795</v>
       </c>
       <c r="X39" t="n">
-        <v>-12.96256747875982</v>
+        <v>-11.80607739887391</v>
       </c>
       <c r="Y39" t="n">
-        <v>-0.4896498245450882</v>
+        <v>1.301417926025962</v>
       </c>
       <c r="Z39" t="n">
-        <v>-4.494366417531984</v>
+        <v>-1.980802628388833</v>
       </c>
       <c r="AA39" t="b">
         <v>1</v>
       </c>
       <c r="AB39" t="n">
-        <v>-0.09585253456221199</v>
+        <v>0.003188097768331621</v>
       </c>
       <c r="AC39" t="n">
-        <v>0.008214088321632396</v>
+        <v>0.01244628793164226</v>
       </c>
       <c r="AD39" t="n">
-        <v>-0.1391138213188964</v>
+        <v>-0.04007318898835277</v>
       </c>
       <c r="AE39" t="n">
-        <v>-0.01179419283084115</v>
+        <v>-0.007561993220831287</v>
       </c>
       <c r="AF39" t="n">
-        <v>-0.1273196284880552</v>
+        <v>-0.03251119576752148</v>
       </c>
       <c r="AG39" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="AH39" t="n">
-        <v>54</v>
+        <v>56.00000000000001</v>
       </c>
       <c r="AI39" t="b">
         <v>0</v>
       </c>
       <c r="AJ39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM39" t="b">
         <v>1</v>
       </c>
       <c r="AN39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>986.89</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>1098.05</v>
+        <v>0</v>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
+      </c>
+      <c r="AP39" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -5988,12 +5990,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6002,24 +6004,24 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>25.8</v>
+        <v>24.6</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1000</v>
+        <v>5546000</v>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="n">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="K40" t="b">
         <v>0</v>
@@ -6028,76 +6030,76 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1000</v>
+        <v>5398000</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>148000</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>0.02741756206002223</v>
       </c>
       <c r="P40" t="n">
-        <v>944</v>
+        <v>1370</v>
       </c>
       <c r="Q40" t="n">
-        <v>944</v>
+        <v>1370</v>
       </c>
       <c r="R40" t="n">
-        <v>15847436</v>
+        <v>9259785</v>
       </c>
       <c r="S40" t="n">
-        <v>921.4</v>
+        <v>1377</v>
       </c>
       <c r="T40" t="n">
-        <v>947.85</v>
+        <v>1405.75</v>
       </c>
       <c r="U40" t="n">
-        <v>947.7</v>
+        <v>1412</v>
       </c>
       <c r="V40" t="n">
-        <v>1040.361715698242</v>
+        <v>1430.583333333333</v>
       </c>
       <c r="W40" t="n">
-        <v>-10.50465947284783</v>
+        <v>-19.92599234664908</v>
       </c>
       <c r="X40" t="n">
-        <v>-11.80607739887374</v>
+        <v>-20.167640543832</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.301417926025909</v>
+        <v>0.2416481971829185</v>
       </c>
       <c r="Z40" t="n">
-        <v>-1.980802628388902</v>
+        <v>-1.561773602172792</v>
       </c>
       <c r="AA40" t="b">
         <v>1</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.003188097768331621</v>
+        <v>-0.08361204013377932</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.01244628793164226</v>
+        <v>-0.1329113924050633</v>
       </c>
       <c r="AD40" t="n">
-        <v>-0.04007318898835277</v>
+        <v>-0.1268733268904637</v>
       </c>
       <c r="AE40" t="n">
-        <v>-0.007561993220831287</v>
+        <v>-0.1529196735575369</v>
       </c>
       <c r="AF40" t="n">
-        <v>-0.03251119576752148</v>
+        <v>0.02604634666707317</v>
       </c>
       <c r="AG40" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="AH40" t="n">
-        <v>56.00000000000001</v>
+        <v>16</v>
       </c>
       <c r="AI40" t="b">
         <v>0</v>
       </c>
       <c r="AJ40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="b">
         <v>1</v>
@@ -6116,10 +6118,8 @@
           <t>Already &gt; 0</t>
         </is>
       </c>
-      <c r="AP40" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+      <c r="AP40" t="n">
+        <v>1492.63</v>
       </c>
     </row>
     <row r="41">
@@ -6144,7 +6144,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>23</v>
+        <v>23.8</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -6185,7 +6185,7 @@
         <v>1855</v>
       </c>
       <c r="R41" t="n">
-        <v>5824801</v>
+        <v>5621672</v>
       </c>
       <c r="S41" t="n">
         <v>1842</v>
@@ -6203,13 +6203,13 @@
         <v>-76.36644509874714</v>
       </c>
       <c r="X41" t="n">
-        <v>-62.46110935546267</v>
+        <v>-62.46110935546268</v>
       </c>
       <c r="Y41" t="n">
-        <v>-13.90533574328446</v>
+        <v>-13.90533574328445</v>
       </c>
       <c r="Z41" t="n">
-        <v>-21.8923560943823</v>
+        <v>-21.89235609438229</v>
       </c>
       <c r="AA41" t="b">
         <v>1</v>
@@ -6282,7 +6282,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>23</v>
+        <v>23.4</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6291,15 +6291,15 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>5972561</v>
+        <v>5656561</v>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K42" t="b">
         <v>0</v>
@@ -6308,13 +6308,13 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>6332561</v>
+        <v>5972561</v>
       </c>
       <c r="N42" t="n">
-        <v>-360000</v>
+        <v>-316000</v>
       </c>
       <c r="O42" t="n">
-        <v>-0.05684903785372142</v>
+        <v>-0.05290862663437008</v>
       </c>
       <c r="P42" t="n">
         <v>2140</v>
@@ -6323,7 +6323,7 @@
         <v>2140</v>
       </c>
       <c r="R42" t="n">
-        <v>4248107</v>
+        <v>3936746</v>
       </c>
       <c r="S42" t="n">
         <v>2205</v>
@@ -6341,13 +6341,13 @@
         <v>-32.50102851928614</v>
       </c>
       <c r="X42" t="n">
-        <v>22.22598285444398</v>
+        <v>22.22598285444369</v>
       </c>
       <c r="Y42" t="n">
-        <v>-54.72701137373012</v>
+        <v>-54.72701137372982</v>
       </c>
       <c r="Z42" t="n">
-        <v>-56.63304740793645</v>
+        <v>-56.63304740793608</v>
       </c>
       <c r="AA42" t="b">
         <v>1</v>
@@ -6420,7 +6420,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>22.2</v>
+        <v>23</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -6461,7 +6461,7 @@
         <v>6435</v>
       </c>
       <c r="R43" t="n">
-        <v>417753</v>
+        <v>390164</v>
       </c>
       <c r="S43" t="n">
         <v>6335</v>
@@ -6558,7 +6558,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>21.8</v>
+        <v>22.6</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -6599,7 +6599,7 @@
         <v>78.19999694824219</v>
       </c>
       <c r="R44" t="n">
-        <v>1032638</v>
+        <v>1020179</v>
       </c>
       <c r="S44" t="n">
         <v>77.88000030517578</v>
@@ -6617,13 +6617,13 @@
         <v>0.1691209063025383</v>
       </c>
       <c r="X44" t="n">
-        <v>-0.09211058242719503</v>
+        <v>-0.09211058242720732</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.2612314887297333</v>
+        <v>0.2612314887297456</v>
       </c>
       <c r="Z44" t="n">
-        <v>0.2730037064359315</v>
+        <v>0.2730037064359469</v>
       </c>
       <c r="AA44" t="b">
         <v>0</v>
@@ -6698,7 +6698,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>20</v>
+        <v>20.8</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -6739,7 +6739,7 @@
         <v>179</v>
       </c>
       <c r="R45" t="n">
-        <v>2484813</v>
+        <v>2446811</v>
       </c>
       <c r="S45" t="n">
         <v>177</v>
@@ -6754,16 +6754,16 @@
         <v>189.1351603190104</v>
       </c>
       <c r="W45" t="n">
-        <v>-5.903432483795655</v>
+        <v>-5.903432483795683</v>
       </c>
       <c r="X45" t="n">
-        <v>-2.360449861354156</v>
+        <v>-2.360449861354219</v>
       </c>
       <c r="Y45" t="n">
-        <v>-3.542982622441498</v>
+        <v>-3.542982622441464</v>
       </c>
       <c r="Z45" t="n">
-        <v>-4.52754738361339</v>
+        <v>-4.527547383613348</v>
       </c>
       <c r="AA45" t="b">
         <v>1</v>
@@ -6820,12 +6820,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6834,96 +6834,96 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>19.2</v>
+        <v>20.4</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Sell</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>5163000</v>
+        <v>9037000</v>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="K46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" t="b">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>5163000</v>
+        <v>9426000</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>-389000</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>-0.04126883089327393</v>
       </c>
       <c r="P46" t="n">
-        <v>18.75</v>
+        <v>1100</v>
       </c>
       <c r="Q46" t="n">
-        <v>18.75</v>
+        <v>1100</v>
       </c>
       <c r="R46" t="n">
-        <v>25223586</v>
+        <v>9955173</v>
       </c>
       <c r="S46" t="n">
-        <v>18.70999984741211</v>
+        <v>1082</v>
       </c>
       <c r="T46" t="n">
-        <v>18.99249992370606</v>
+        <v>1127.25</v>
       </c>
       <c r="U46" t="n">
-        <v>19.02749996185303</v>
+        <v>1129</v>
       </c>
       <c r="V46" t="n">
-        <v>18.91010268529256</v>
+        <v>1139</v>
       </c>
       <c r="W46" t="n">
-        <v>-0.1057587888602889</v>
+        <v>-17.74030052988269</v>
       </c>
       <c r="X46" t="n">
-        <v>-0.06542483415428357</v>
+        <v>-19.86038036342023</v>
       </c>
       <c r="Y46" t="n">
-        <v>-0.04033395470600531</v>
+        <v>2.120079833537545</v>
       </c>
       <c r="Z46" t="n">
-        <v>-0.05398517956514894</v>
+        <v>-1.480635292806102</v>
       </c>
       <c r="AA46" t="b">
         <v>1</v>
       </c>
       <c r="AB46" t="n">
-        <v>-0.0359897550376066</v>
+        <v>-0.03083700440528636</v>
       </c>
       <c r="AC46" t="n">
-        <v>-0.005346525497051058</v>
+        <v>-0.02222222222222225</v>
       </c>
       <c r="AD46" t="n">
-        <v>-0.07925104179429099</v>
+        <v>-0.07409829116197075</v>
       </c>
       <c r="AE46" t="n">
-        <v>-0.02535480664952461</v>
+        <v>-0.0422305033746958</v>
       </c>
       <c r="AF46" t="n">
-        <v>-0.05389623514476638</v>
+        <v>-0.03186778778727495</v>
       </c>
       <c r="AG46" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AH46" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AI46" t="b">
         <v>0</v>
@@ -6932,22 +6932,24 @@
         <v>0</v>
       </c>
       <c r="AK46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM46" t="b">
         <v>1</v>
       </c>
       <c r="AN46" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO46" t="n">
-        <v>19.24</v>
+        <v>0</v>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP46" t="n">
-        <v>19.46</v>
+        <v>1163.68</v>
       </c>
     </row>
     <row r="47">
@@ -6958,12 +6960,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6972,7 +6974,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>17.8</v>
+        <v>20</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6981,15 +6983,15 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>1000</v>
+        <v>5163000</v>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="K47" t="b">
         <v>0</v>
@@ -6998,7 +7000,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>1000</v>
+        <v>5163000</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
@@ -7007,61 +7009,61 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>3540</v>
+        <v>18.75</v>
       </c>
       <c r="Q47" t="n">
-        <v>3540</v>
+        <v>18.75</v>
       </c>
       <c r="R47" t="n">
-        <v>5089299</v>
+        <v>25162810</v>
       </c>
       <c r="S47" t="n">
-        <v>3425</v>
+        <v>18.70999984741211</v>
       </c>
       <c r="T47" t="n">
-        <v>3843.58193359375</v>
+        <v>18.99249992370606</v>
       </c>
       <c r="U47" t="n">
-        <v>3850.148107910156</v>
+        <v>19.02749996185303</v>
       </c>
       <c r="V47" t="n">
-        <v>3778.603556315104</v>
+        <v>18.91010268529256</v>
       </c>
       <c r="W47" t="n">
-        <v>-136.3553533146433</v>
+        <v>-0.1057587888602889</v>
       </c>
       <c r="X47" t="n">
-        <v>-56.42673552923905</v>
+        <v>-0.06542483415428357</v>
       </c>
       <c r="Y47" t="n">
-        <v>-79.9286177854042</v>
+        <v>-0.04033395470600531</v>
       </c>
       <c r="Z47" t="n">
-        <v>-111.8986719358526</v>
+        <v>-0.05398517956514892</v>
       </c>
       <c r="AA47" t="b">
         <v>1</v>
       </c>
       <c r="AB47" t="n">
-        <v>-0.03577006679394201</v>
+        <v>-0.0359897550376066</v>
       </c>
       <c r="AC47" t="n">
-        <v>-0.07812646527852174</v>
+        <v>-0.005346525497051058</v>
       </c>
       <c r="AD47" t="n">
-        <v>-0.0790313535506264</v>
+        <v>-0.07925104179429099</v>
       </c>
       <c r="AE47" t="n">
-        <v>-0.09813474643099529</v>
+        <v>-0.02535480664952461</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.01910339288036889</v>
+        <v>-0.05389623514476638</v>
       </c>
       <c r="AG47" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AH47" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AI47" t="b">
         <v>0</v>
@@ -7079,11 +7081,13 @@
         <v>1</v>
       </c>
       <c r="AN47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO47" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>19.24</v>
+      </c>
       <c r="AP47" t="n">
-        <v>4025.61</v>
+        <v>19.46</v>
       </c>
     </row>
     <row r="48">
@@ -7094,12 +7098,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7108,7 +7112,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>14.6</v>
+        <v>18.6</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -7117,15 +7121,15 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>5398000</v>
+        <v>1000</v>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="n">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="K48" t="b">
         <v>0</v>
@@ -7134,7 +7138,7 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>5398000</v>
+        <v>1000</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
@@ -7143,61 +7147,61 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>1370</v>
+        <v>3540</v>
       </c>
       <c r="Q48" t="n">
-        <v>1370</v>
+        <v>3540</v>
       </c>
       <c r="R48" t="n">
-        <v>9606533</v>
+        <v>4889572</v>
       </c>
       <c r="S48" t="n">
-        <v>1377</v>
+        <v>3425</v>
       </c>
       <c r="T48" t="n">
-        <v>1405.75</v>
+        <v>3843.573815917969</v>
       </c>
       <c r="U48" t="n">
-        <v>1412</v>
+        <v>3850.139050292969</v>
       </c>
       <c r="V48" t="n">
-        <v>1430.583333333333</v>
+        <v>3778.5880859375</v>
       </c>
       <c r="W48" t="n">
-        <v>-19.92599234664908</v>
+        <v>-136.3515085222648</v>
       </c>
       <c r="X48" t="n">
-        <v>-20.167640543832</v>
+        <v>-56.42263399700656</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.2416481971829185</v>
+        <v>-79.92887452525824</v>
       </c>
       <c r="Z48" t="n">
-        <v>-1.561773602172792</v>
+        <v>-111.898673946805</v>
       </c>
       <c r="AA48" t="b">
         <v>1</v>
       </c>
       <c r="AB48" t="n">
-        <v>-0.08361204013377932</v>
+        <v>-0.03576512947755717</v>
       </c>
       <c r="AC48" t="n">
-        <v>-0.1329113924050633</v>
+        <v>-0.07812171775920829</v>
       </c>
       <c r="AD48" t="n">
-        <v>-0.1268733268904637</v>
+        <v>-0.07902641623424156</v>
       </c>
       <c r="AE48" t="n">
-        <v>-0.1529196735575369</v>
+        <v>-0.09812999891168184</v>
       </c>
       <c r="AF48" t="n">
-        <v>0.02604634666707317</v>
+        <v>0.01910358267744028</v>
       </c>
       <c r="AG48" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AH48" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="AI48" t="b">
         <v>0</v>
@@ -7206,10 +7210,10 @@
         <v>0</v>
       </c>
       <c r="AK48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM48" t="b">
         <v>1</v>
@@ -7217,13 +7221,9 @@
       <c r="AN48" t="b">
         <v>0</v>
       </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
+      <c r="AO48" t="inlineStr"/>
       <c r="AP48" t="n">
-        <v>1492.63</v>
+        <v>4025.58</v>
       </c>
     </row>
     <row r="49">
@@ -7248,7 +7248,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>14.4</v>
+        <v>15.2</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -7257,7 +7257,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H49" t="n">
@@ -7289,7 +7289,7 @@
         <v>4890</v>
       </c>
       <c r="R49" t="n">
-        <v>3618480</v>
+        <v>3392081</v>
       </c>
       <c r="S49" t="n">
         <v>5026</v>
@@ -7307,13 +7307,13 @@
         <v>-160.5139129580921</v>
       </c>
       <c r="X49" t="n">
-        <v>-83.51504636773939</v>
+        <v>-83.5150463677395</v>
       </c>
       <c r="Y49" t="n">
-        <v>-76.99886659035269</v>
+        <v>-76.99886659035258</v>
       </c>
       <c r="Z49" t="n">
-        <v>-83.95358408476221</v>
+        <v>-83.95358408476207</v>
       </c>
       <c r="AA49" t="b">
         <v>1</v>
@@ -7386,7 +7386,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>13.2</v>
+        <v>14</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H50" t="n">
@@ -7427,7 +7427,7 @@
         <v>1220</v>
       </c>
       <c r="R50" t="n">
-        <v>1422506</v>
+        <v>1414053</v>
       </c>
       <c r="S50" t="n">
         <v>1251</v>
@@ -7442,13 +7442,13 @@
         <v>1382.257293701172</v>
       </c>
       <c r="W50" t="n">
-        <v>-49.78210545852244</v>
+        <v>-49.78210545852198</v>
       </c>
       <c r="X50" t="n">
-        <v>-38.73110277324523</v>
+        <v>-38.73110277324496</v>
       </c>
       <c r="Y50" t="n">
-        <v>-11.0510026852772</v>
+        <v>-11.05100268527702</v>
       </c>
       <c r="Z50" t="n">
         <v>-11.58266004238281</v>
@@ -7524,7 +7524,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4.8</v>
+        <v>5.199999999999999</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7533,15 +7533,15 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1364000</v>
+        <v>1159000</v>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K51" t="b">
         <v>0</v>
@@ -7550,13 +7550,13 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>1516000</v>
+        <v>1364000</v>
       </c>
       <c r="N51" t="n">
-        <v>-152000</v>
+        <v>-205000</v>
       </c>
       <c r="O51" t="n">
-        <v>-0.1002638522427441</v>
+        <v>-0.1502932551319648</v>
       </c>
       <c r="P51" t="n">
         <v>902</v>
@@ -7565,7 +7565,7 @@
         <v>902</v>
       </c>
       <c r="R51" t="n">
-        <v>1069844</v>
+        <v>1006864</v>
       </c>
       <c r="S51" t="n">
         <v>887.2</v>
@@ -7586,10 +7586,10 @@
         <v>-27.06376278695161</v>
       </c>
       <c r="Y51" t="n">
-        <v>2.02197627463449</v>
+        <v>2.021976274634493</v>
       </c>
       <c r="Z51" t="n">
-        <v>-0.7750007364018998</v>
+        <v>-0.7750007364018963</v>
       </c>
       <c r="AA51" t="b">
         <v>1</v>

--- a/output/daily_screen_latest.xlsx
+++ b/output/daily_screen_latest.xlsx
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>87.59999999999999</v>
+        <v>87.8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -703,7 +703,7 @@
         <v>6895</v>
       </c>
       <c r="R2" t="n">
-        <v>1655929</v>
+        <v>1591830</v>
       </c>
       <c r="S2" t="n">
         <v>6369</v>
@@ -739,13 +739,13 @@
         <v>1.02859958568814</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.1472997259097635</v>
+        <v>0.1638058005062069</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.007212199059683</v>
+        <v>1.009606822136877</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.8599124731499193</v>
+        <v>-0.8458010216306706</v>
       </c>
       <c r="AG2" t="n">
         <v>92</v>
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>83.2</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -845,7 +845,7 @@
         <v>1270</v>
       </c>
       <c r="R3" t="n">
-        <v>9198391</v>
+        <v>8867403</v>
       </c>
       <c r="S3" t="n">
         <v>1189</v>
@@ -881,13 +881,13 @@
         <v>0.07172995780590719</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.02038226589328662</v>
+        <v>-0.003876191296843245</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.05034257117744989</v>
+        <v>0.05273719425464463</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.07072483707073651</v>
+        <v>-0.05661338555148787</v>
       </c>
       <c r="AG3" t="n">
         <v>54</v>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>80.60000000000001</v>
+        <v>80.80000000000001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -987,7 +987,7 @@
         <v>2445</v>
       </c>
       <c r="R4" t="n">
-        <v>4550271</v>
+        <v>4308131</v>
       </c>
       <c r="S4" t="n">
         <v>2334</v>
@@ -1023,13 +1023,13 @@
         <v>0.2363031465504604</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.0372825927992626</v>
+        <v>0.05378866739570598</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.2149157599220031</v>
+        <v>0.2173103829991978</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.1776331671227405</v>
+        <v>-0.1635217156034918</v>
       </c>
       <c r="AG4" t="n">
         <v>74</v>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>80.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1129,7 +1129,7 @@
         <v>178.5</v>
       </c>
       <c r="R5" t="n">
-        <v>34211681</v>
+        <v>33763957</v>
       </c>
       <c r="S5" t="n">
         <v>173.4</v>
@@ -1165,13 +1165,13 @@
         <v>-0.05568660955828064</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.1220908523862834</v>
+        <v>0.1385969269827267</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.07707399618673794</v>
+        <v>-0.0746793731095432</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.1991648485730213</v>
+        <v>0.2132763000922699</v>
       </c>
       <c r="AG5" t="n">
         <v>86</v>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>71.2</v>
+        <v>78</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1239,15 +1239,15 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3483000</v>
+        <v>2674000</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K6" t="b">
         <v>0</v>
@@ -1256,7 +1256,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3483000</v>
+        <v>2674000</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1265,61 +1265,61 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>498.5</v>
+        <v>216</v>
       </c>
       <c r="Q6" t="n">
-        <v>498.5</v>
+        <v>216</v>
       </c>
       <c r="R6" t="n">
-        <v>41882089</v>
+        <v>11046647</v>
       </c>
       <c r="S6" t="n">
-        <v>481.2</v>
+        <v>209</v>
       </c>
       <c r="T6" t="n">
-        <v>489.1</v>
+        <v>195.975</v>
       </c>
       <c r="U6" t="n">
-        <v>488.2</v>
+        <v>195.25</v>
       </c>
       <c r="V6" t="n">
-        <v>493.4</v>
+        <v>179.7979118347168</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1396022943689559</v>
+        <v>6.658701056388509</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0007145187042290509</v>
+        <v>3.766365760948625</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.1388877756647268</v>
+        <v>2.892335295439884</v>
       </c>
       <c r="Z6" t="n">
-        <v>-2.202645883787668</v>
+        <v>2.605450449051671</v>
       </c>
       <c r="AA6" t="b">
         <v>1</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.03746097814776284</v>
+        <v>0.07196029776674928</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.1867862969004894</v>
+        <v>0.04802908408167728</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.007114836132620539</v>
+        <v>0.04389055808280928</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.2081736835289467</v>
+        <v>0.02903632053041472</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.2010588473963262</v>
+        <v>0.01485423755239457</v>
       </c>
       <c r="AG6" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="AH6" t="n">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="AI6" t="b">
         <v>1</v>
@@ -1358,12 +1358,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1372,96 +1372,96 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>68.59999999999999</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Heavy Sell</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2674000</v>
+        <v>3483000</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
+        <v>19</v>
+      </c>
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" t="b">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3483000</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>498.5</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>498.5</v>
+      </c>
+      <c r="R7" t="n">
+        <v>40884370</v>
+      </c>
+      <c r="S7" t="n">
+        <v>481.2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>489.1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>488.2</v>
+      </c>
+      <c r="V7" t="n">
+        <v>493.4</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.1396022943689559</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.0007145187042290509</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.1388877756647268</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-2.202645883787668</v>
+      </c>
+      <c r="AA7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.03746097814776284</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-0.1867862969004894</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.009391238463822837</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>-0.205779060451752</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.2151702989155748</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>64</v>
+      </c>
+      <c r="AH7" t="n">
         <v>20</v>
-      </c>
-      <c r="K7" t="b">
-        <v>0</v>
-      </c>
-      <c r="L7" t="b">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>3193000</v>
-      </c>
-      <c r="N7" t="n">
-        <v>-519000</v>
-      </c>
-      <c r="O7" t="n">
-        <v>-0.1625430629502036</v>
-      </c>
-      <c r="P7" t="n">
-        <v>216</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>216</v>
-      </c>
-      <c r="R7" t="n">
-        <v>11282373</v>
-      </c>
-      <c r="S7" t="n">
-        <v>209</v>
-      </c>
-      <c r="T7" t="n">
-        <v>195.975</v>
-      </c>
-      <c r="U7" t="n">
-        <v>195.25</v>
-      </c>
-      <c r="V7" t="n">
-        <v>179.7979118347168</v>
-      </c>
-      <c r="W7" t="n">
-        <v>6.658701056388509</v>
-      </c>
-      <c r="X7" t="n">
-        <v>3.766365760948625</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.892335295439884</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.605450449051671</v>
-      </c>
-      <c r="AA7" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0.07196029776674928</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0.04802908408167728</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0.02738448348636591</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0.02664169745321998</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0.0007427860331459257</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>70</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>68</v>
       </c>
       <c r="AI7" t="b">
         <v>1</v>
@@ -1500,12 +1500,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1514,7 +1514,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>47.40000000000001</v>
+        <v>45.8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1523,15 +1523,15 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>121000</v>
+        <v>2483000</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="K8" t="b">
         <v>0</v>
@@ -1540,70 +1540,70 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1000</v>
+        <v>2022000</v>
       </c>
       <c r="N8" t="n">
-        <v>120000</v>
+        <v>461000</v>
       </c>
       <c r="O8" t="n">
-        <v>120</v>
+        <v>0.2279920870425322</v>
       </c>
       <c r="P8" t="n">
-        <v>1310</v>
+        <v>1120</v>
       </c>
       <c r="Q8" t="n">
-        <v>1310</v>
+        <v>1120</v>
       </c>
       <c r="R8" t="n">
-        <v>3497503</v>
+        <v>8611300</v>
       </c>
       <c r="S8" t="n">
-        <v>1232</v>
+        <v>1090</v>
       </c>
       <c r="T8" t="n">
-        <v>1278</v>
+        <v>1074.2</v>
       </c>
       <c r="U8" t="n">
-        <v>1280.75</v>
+        <v>1074.7</v>
       </c>
       <c r="V8" t="n">
-        <v>1157.184970092773</v>
+        <v>1010.283333333333</v>
       </c>
       <c r="W8" t="n">
-        <v>-8.482500372270351</v>
+        <v>15.44991409719159</v>
       </c>
       <c r="X8" t="n">
-        <v>-8.492960901690422</v>
+        <v>2.798912882849386</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.01046052942007059</v>
+        <v>12.65100121434221</v>
       </c>
       <c r="Z8" t="n">
-        <v>-11.81469275014517</v>
+        <v>10.5978825348422</v>
       </c>
       <c r="AA8" t="b">
         <v>1</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.04029304029304026</v>
+        <v>-0.008849557522123908</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.2880115114876634</v>
+        <v>-0.1417624521072797</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0.08486885457342364</v>
+        <v>-0.03691929720606391</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.2666241248592061</v>
+        <v>-0.1607552156585422</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.3514929794326297</v>
+        <v>0.1238359184524783</v>
       </c>
       <c r="AG8" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="AH8" t="n">
-        <v>92</v>
+        <v>32</v>
       </c>
       <c r="AI8" t="b">
         <v>1</v>
@@ -1629,7 +1629,7 @@
         </is>
       </c>
       <c r="AP8" t="n">
-        <v>1311.32</v>
+        <v>1116.79</v>
       </c>
     </row>
     <row r="9">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1654,24 +1654,24 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>45.8</v>
+        <v>38.40000000000001</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2022000</v>
+        <v>121000</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="K9" t="b">
         <v>0</v>
@@ -1680,70 +1680,70 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1634000</v>
+        <v>121000</v>
       </c>
       <c r="N9" t="n">
-        <v>388000</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2374541003671971</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1120</v>
+        <v>1310</v>
       </c>
       <c r="Q9" t="n">
-        <v>1120</v>
+        <v>1310</v>
       </c>
       <c r="R9" t="n">
-        <v>8798725</v>
+        <v>3324760</v>
       </c>
       <c r="S9" t="n">
-        <v>1090</v>
+        <v>1232</v>
       </c>
       <c r="T9" t="n">
-        <v>1074.2</v>
+        <v>1278</v>
       </c>
       <c r="U9" t="n">
-        <v>1074.7</v>
+        <v>1280.75</v>
       </c>
       <c r="V9" t="n">
-        <v>1010.283333333333</v>
+        <v>1157.184970092773</v>
       </c>
       <c r="W9" t="n">
-        <v>15.44991409719159</v>
+        <v>-8.482500372270351</v>
       </c>
       <c r="X9" t="n">
-        <v>2.798912882849386</v>
+        <v>-8.492960901690422</v>
       </c>
       <c r="Y9" t="n">
-        <v>12.65100121434221</v>
+        <v>0.01046052942007059</v>
       </c>
       <c r="Z9" t="n">
-        <v>10.5978825348422</v>
+        <v>-11.81469275014517</v>
       </c>
       <c r="AA9" t="b">
         <v>1</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0.008849557522123908</v>
+        <v>-0.04029304029304026</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.1417624521072797</v>
+        <v>0.2880115114876634</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0.05342537180250728</v>
+        <v>-0.06836277997698026</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.163149838735737</v>
+        <v>0.2690187479364008</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.1097244669332297</v>
+        <v>-0.3373815279133811</v>
       </c>
       <c r="AG9" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="AH9" t="n">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="AI9" t="b">
         <v>1</v>
@@ -1769,7 +1769,7 @@
         </is>
       </c>
       <c r="AP9" t="n">
-        <v>1116.79</v>
+        <v>1311.32</v>
       </c>
     </row>
     <row r="10">
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>51.2</v>
+        <v>51.4</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1835,7 +1835,7 @@
         <v>153.5</v>
       </c>
       <c r="R10" t="n">
-        <v>111348972</v>
+        <v>110638385</v>
       </c>
       <c r="S10" t="n">
         <v>156.9</v>
@@ -1871,13 +1871,13 @@
         <v>-0.08429881578813225</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.1361934164888474</v>
+        <v>0.1526994910852908</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.1056862024165895</v>
+        <v>-0.1032915793393948</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.241879618905437</v>
+        <v>0.2559910704246856</v>
       </c>
       <c r="AG10" t="n">
         <v>90</v>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>49.8</v>
+        <v>50</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1977,7 +1977,7 @@
         <v>7925</v>
       </c>
       <c r="R11" t="n">
-        <v>1061923</v>
+        <v>979594</v>
       </c>
       <c r="S11" t="n">
         <v>8165</v>
@@ -2013,13 +2013,13 @@
         <v>0.5724206349206349</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.2729636703413956</v>
+        <v>0.2894697449378389</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.5510332482921776</v>
+        <v>0.5534278713693723</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.278069577950782</v>
+        <v>-0.2639581264315334</v>
       </c>
       <c r="AG11" t="n">
         <v>100</v>
@@ -2078,7 +2078,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>47.8</v>
+        <v>48</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K12" t="b">
         <v>1</v>
@@ -2119,7 +2119,7 @@
         <v>294.5</v>
       </c>
       <c r="R12" t="n">
-        <v>29691511</v>
+        <v>28180195</v>
       </c>
       <c r="S12" t="n">
         <v>305.6</v>
@@ -2155,13 +2155,13 @@
         <v>-0.07341519200743485</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.04616492646035741</v>
+        <v>0.06267100105680079</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.09480257863589214</v>
+        <v>-0.09240795555869741</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.1409675050962496</v>
+        <v>0.1550789566154982</v>
       </c>
       <c r="AG12" t="n">
         <v>78</v>
@@ -2220,7 +2220,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>47.6</v>
+        <v>47.8</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -2261,7 +2261,7 @@
         <v>1165</v>
       </c>
       <c r="R13" t="n">
-        <v>10788550</v>
+        <v>10469722</v>
       </c>
       <c r="S13" t="n">
         <v>1130</v>
@@ -2297,13 +2297,13 @@
         <v>0.2047322672366025</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.004973735269166113</v>
+        <v>0.02147980986560949</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.1833448806081452</v>
+        <v>0.18573950368534</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.1783711453389791</v>
+        <v>-0.1642596938197305</v>
       </c>
       <c r="AG13" t="n">
         <v>66</v>
@@ -2348,12 +2348,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2362,96 +2362,96 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>47</v>
+        <v>47.2</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>7389000</v>
+        <v>168900</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="K14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="b">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>7320000</v>
+        <v>168900</v>
       </c>
       <c r="N14" t="n">
-        <v>69000</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.009426229508196722</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1835</v>
+        <v>19395</v>
       </c>
       <c r="Q14" t="n">
-        <v>1835</v>
+        <v>19395</v>
       </c>
       <c r="R14" t="n">
-        <v>13773563</v>
+        <v>229955</v>
       </c>
       <c r="S14" t="n">
-        <v>1884</v>
+        <v>20047</v>
       </c>
       <c r="T14" t="n">
-        <v>1780.25</v>
+        <v>18570.25</v>
       </c>
       <c r="U14" t="n">
-        <v>1780</v>
+        <v>18382</v>
       </c>
       <c r="V14" t="n">
-        <v>1777</v>
+        <v>16246.68181966146</v>
       </c>
       <c r="W14" t="n">
-        <v>33.07665985345807</v>
+        <v>681.6505405317366</v>
       </c>
       <c r="X14" t="n">
-        <v>11.58825139616999</v>
+        <v>661.1887770537031</v>
       </c>
       <c r="Y14" t="n">
-        <v>21.48840845728808</v>
+        <v>20.4617634780335</v>
       </c>
       <c r="Z14" t="n">
-        <v>30.30151505953038</v>
+        <v>124.9044452154969</v>
       </c>
       <c r="AA14" t="b">
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.002732240437158362</v>
+        <v>0.2408829174664107</v>
       </c>
       <c r="AC14" t="n">
-        <v>-0.1156626506024097</v>
+        <v>0.2357081148782567</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0.04184357384322501</v>
+        <v>0.2128131777824707</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0.137050037230867</v>
+        <v>0.2167153513269942</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.09520646338764194</v>
+        <v>-0.003902173544523491</v>
       </c>
       <c r="AG14" t="n">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="AH14" t="n">
-        <v>38</v>
+        <v>82</v>
       </c>
       <c r="AI14" t="b">
         <v>1</v>
@@ -2490,12 +2490,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>47</v>
+        <v>46.8</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2513,15 +2513,15 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>168900</v>
+        <v>476000</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="K15" t="b">
         <v>0</v>
@@ -2530,7 +2530,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>168900</v>
+        <v>476000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2539,61 +2539,61 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>19395</v>
+        <v>1585</v>
       </c>
       <c r="Q15" t="n">
-        <v>19395</v>
+        <v>1585</v>
       </c>
       <c r="R15" t="n">
-        <v>258047</v>
+        <v>4986784</v>
       </c>
       <c r="S15" t="n">
-        <v>20047</v>
+        <v>1563</v>
       </c>
       <c r="T15" t="n">
-        <v>18570.25</v>
+        <v>1342</v>
       </c>
       <c r="U15" t="n">
-        <v>18382</v>
+        <v>1326</v>
       </c>
       <c r="V15" t="n">
-        <v>16246.68181966146</v>
+        <v>1192.783333333333</v>
       </c>
       <c r="W15" t="n">
-        <v>681.6505405317366</v>
+        <v>91.03166828477333</v>
       </c>
       <c r="X15" t="n">
-        <v>661.1887770537031</v>
+        <v>66.63569507951343</v>
       </c>
       <c r="Y15" t="n">
-        <v>20.4617634780335</v>
+        <v>24.39597320525991</v>
       </c>
       <c r="Z15" t="n">
-        <v>124.9044452154969</v>
+        <v>26.89554554167307</v>
       </c>
       <c r="AA15" t="b">
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.2408829174664107</v>
+        <v>0.2529644268774704</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.2357081148782567</v>
+        <v>0.1485507246376812</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.1963071031860273</v>
+        <v>0.2248946871935305</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.2143207282497994</v>
+        <v>0.1295579610864186</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.01801362506377213</v>
+        <v>0.09533672610711186</v>
       </c>
       <c r="AG15" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AH15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="AI15" t="b">
         <v>1</v>
@@ -2632,12 +2632,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2646,7 +2646,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>46.6</v>
+        <v>45.8</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2655,15 +2655,15 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>476000</v>
+        <v>5086000</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="K16" t="b">
         <v>0</v>
@@ -2672,7 +2672,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>476000</v>
+        <v>5086000</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2681,61 +2681,61 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1585</v>
+        <v>4910</v>
       </c>
       <c r="Q16" t="n">
-        <v>1585</v>
+        <v>4910</v>
       </c>
       <c r="R16" t="n">
-        <v>5079374</v>
+        <v>11051455</v>
       </c>
       <c r="S16" t="n">
-        <v>1563</v>
+        <v>5114</v>
       </c>
       <c r="T16" t="n">
-        <v>1342</v>
+        <v>4648.5</v>
       </c>
       <c r="U16" t="n">
-        <v>1326</v>
+        <v>4602.25</v>
       </c>
       <c r="V16" t="n">
-        <v>1192.783333333333</v>
+        <v>4087.508333333333</v>
       </c>
       <c r="W16" t="n">
-        <v>91.03166828477333</v>
+        <v>214.5734033226527</v>
       </c>
       <c r="X16" t="n">
-        <v>66.63569507951343</v>
+        <v>191.9008320589306</v>
       </c>
       <c r="Y16" t="n">
-        <v>24.39597320525991</v>
+        <v>22.67257126372203</v>
       </c>
       <c r="Z16" t="n">
-        <v>26.89554554167307</v>
+        <v>61.15996141600954</v>
       </c>
       <c r="AA16" t="b">
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.2529644268774704</v>
+        <v>0.232120451693852</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.1485507246376812</v>
+        <v>0.177434319883583</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.2083886125970871</v>
+        <v>0.204050712009912</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.1271633380092239</v>
+        <v>0.1584415563323205</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.08122527458786322</v>
+        <v>0.0456091556775915</v>
       </c>
       <c r="AG16" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="AH16" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AI16" t="b">
         <v>1</v>
@@ -2774,12 +2774,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2788,24 +2788,24 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>45.8</v>
+        <v>43.40000000000001</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>6151000</v>
+        <v>11464000</v>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K17" t="b">
         <v>1</v>
@@ -2814,76 +2814,76 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>5886000</v>
+        <v>11464000</v>
       </c>
       <c r="N17" t="n">
-        <v>265000</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0.04502208630648998</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1485</v>
+        <v>2475</v>
       </c>
       <c r="Q17" t="n">
-        <v>1485</v>
+        <v>2475</v>
       </c>
       <c r="R17" t="n">
-        <v>5912851</v>
+        <v>24637205</v>
       </c>
       <c r="S17" t="n">
-        <v>1463</v>
+        <v>2478</v>
       </c>
       <c r="T17" t="n">
-        <v>1401.25</v>
+        <v>2430.986926269531</v>
       </c>
       <c r="U17" t="n">
-        <v>1401.5</v>
+        <v>2427.881787109375</v>
       </c>
       <c r="V17" t="n">
-        <v>1412.416666666667</v>
+        <v>2395.413081868489</v>
       </c>
       <c r="W17" t="n">
-        <v>16.75624182819433</v>
+        <v>19.99968999227895</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.188644010547854</v>
+        <v>14.22732978166766</v>
       </c>
       <c r="Y17" t="n">
-        <v>18.94488583874219</v>
+        <v>5.772360210611286</v>
       </c>
       <c r="Z17" t="n">
-        <v>19.0215381971915</v>
+        <v>7.452008552691755</v>
       </c>
       <c r="AA17" t="b">
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0.003355704697986628</v>
+        <v>0.02573784857921413</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.1703910614525139</v>
+        <v>0.01524967584937387</v>
       </c>
       <c r="AD17" t="n">
-        <v>-0.04793151897837</v>
+        <v>-0.002331891104725869</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0.1917784480809712</v>
+        <v>-0.003743087701888692</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.1438469291026012</v>
+        <v>0.001411196597162823</v>
       </c>
       <c r="AG17" t="n">
-        <v>46</v>
+        <v>56.00000000000001</v>
       </c>
       <c r="AH17" t="n">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="AI17" t="b">
         <v>1</v>
       </c>
       <c r="AJ17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK17" t="b">
         <v>1</v>
@@ -2902,8 +2902,10 @@
           <t>Already &gt; 0</t>
         </is>
       </c>
-      <c r="AP17" t="n">
-        <v>1346.84</v>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -2914,12 +2916,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2928,7 +2930,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>45.6</v>
+        <v>41.6</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2937,15 +2939,15 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>5086000</v>
+        <v>251000</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="K18" t="b">
         <v>0</v>
@@ -2954,7 +2956,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>5086000</v>
+        <v>251000</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2963,73 +2965,73 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>4910</v>
+        <v>3140</v>
       </c>
       <c r="Q18" t="n">
-        <v>4910</v>
+        <v>3140</v>
       </c>
       <c r="R18" t="n">
-        <v>13191812</v>
+        <v>692318</v>
       </c>
       <c r="S18" t="n">
-        <v>5114</v>
+        <v>3422</v>
       </c>
       <c r="T18" t="n">
-        <v>4648.5</v>
+        <v>3382.25</v>
       </c>
       <c r="U18" t="n">
-        <v>4602.25</v>
+        <v>3359.25</v>
       </c>
       <c r="V18" t="n">
-        <v>4087.508333333333</v>
+        <v>2937.38525390625</v>
       </c>
       <c r="W18" t="n">
-        <v>214.5734033226527</v>
+        <v>38.22946124147575</v>
       </c>
       <c r="X18" t="n">
-        <v>191.9008320589305</v>
+        <v>96.27406748320537</v>
       </c>
       <c r="Y18" t="n">
-        <v>22.6725712637222</v>
+        <v>-58.04460624172962</v>
       </c>
       <c r="Z18" t="n">
-        <v>61.15996141600971</v>
+        <v>-31.68615021447238</v>
       </c>
       <c r="AA18" t="b">
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.232120451693852</v>
+        <v>0.1716417910447761</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.177434319883583</v>
+        <v>-0.0491159431872682</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.1875446374134686</v>
+        <v>0.1435720513608361</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.1560469332551258</v>
+        <v>-0.06810870673853076</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.03149770415834285</v>
+        <v>0.2116807580993668</v>
       </c>
       <c r="AG18" t="n">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="AH18" t="n">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="AI18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="b">
         <v>1</v>
       </c>
       <c r="AK18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="b">
         <v>0</v>
@@ -3037,11 +3039,7 @@
       <c r="AN18" t="b">
         <v>0</v>
       </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
+      <c r="AO18" t="inlineStr"/>
       <c r="AP18" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -3056,12 +3054,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3070,7 +3068,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>43.2</v>
+        <v>41.4</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3079,24 +3077,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>11464000</v>
+        <v>1673000</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="K19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="b">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>11464000</v>
+        <v>1673000</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -3105,61 +3103,61 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2475</v>
+        <v>2515</v>
       </c>
       <c r="Q19" t="n">
-        <v>2475</v>
+        <v>2515</v>
       </c>
       <c r="R19" t="n">
-        <v>25532143</v>
+        <v>1014163</v>
       </c>
       <c r="S19" t="n">
-        <v>2478</v>
+        <v>2512</v>
       </c>
       <c r="T19" t="n">
-        <v>2430.986926269531</v>
+        <v>2261.5</v>
       </c>
       <c r="U19" t="n">
-        <v>2427.881787109375</v>
+        <v>2253</v>
       </c>
       <c r="V19" t="n">
-        <v>2395.413081868489</v>
+        <v>1821.885439046224</v>
       </c>
       <c r="W19" t="n">
-        <v>19.99968999071962</v>
+        <v>123.0591685427753</v>
       </c>
       <c r="X19" t="n">
-        <v>14.22732977855515</v>
+        <v>93.50206457801306</v>
       </c>
       <c r="Y19" t="n">
-        <v>5.772360212164466</v>
+        <v>29.55710396476223</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.452008554438146</v>
+        <v>36.56152320720935</v>
       </c>
       <c r="AA19" t="b">
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.02573784857921413</v>
+        <v>0.07249466950959493</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.01524967584937387</v>
+        <v>0.5537346219685011</v>
       </c>
       <c r="AD19" t="n">
-        <v>-0.01883796570116925</v>
+        <v>0.04442492982565494</v>
       </c>
       <c r="AE19" t="n">
-        <v>-0.006137710779083427</v>
+        <v>0.5347418584172385</v>
       </c>
       <c r="AF19" t="n">
-        <v>-0.01270025492208582</v>
+        <v>-0.4903169285915836</v>
       </c>
       <c r="AG19" t="n">
-        <v>56.00000000000001</v>
+        <v>72</v>
       </c>
       <c r="AH19" t="n">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="AI19" t="b">
         <v>1</v>
@@ -3198,12 +3196,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3212,7 +3210,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>41.4</v>
+        <v>41.2</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3221,15 +3219,15 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>251000</v>
+        <v>1000</v>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="K20" t="b">
         <v>0</v>
@@ -3238,7 +3236,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>251000</v>
+        <v>1000</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -3247,73 +3245,73 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>3140</v>
+        <v>104.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>3140</v>
+        <v>104.5</v>
       </c>
       <c r="R20" t="n">
-        <v>768231</v>
+        <v>52740037</v>
       </c>
       <c r="S20" t="n">
-        <v>3422</v>
+        <v>106.4</v>
       </c>
       <c r="T20" t="n">
-        <v>3382.25</v>
+        <v>93.65999946594238</v>
       </c>
       <c r="U20" t="n">
-        <v>3359.25</v>
+        <v>92.95999946594239</v>
       </c>
       <c r="V20" t="n">
-        <v>2937.38525390625</v>
+        <v>94.34833323160807</v>
       </c>
       <c r="W20" t="n">
-        <v>38.22946124147575</v>
+        <v>4.790189329418197</v>
       </c>
       <c r="X20" t="n">
-        <v>96.27406748320537</v>
+        <v>2.493172617357349</v>
       </c>
       <c r="Y20" t="n">
-        <v>-58.04460624172962</v>
+        <v>2.297016712060849</v>
       </c>
       <c r="Z20" t="n">
-        <v>-31.68615021447238</v>
+        <v>3.020558977502503</v>
       </c>
       <c r="AA20" t="b">
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.1716417910447761</v>
+        <v>0.1546961325966851</v>
       </c>
       <c r="AC20" t="n">
-        <v>-0.0491159431872682</v>
+        <v>-0.004761904761904745</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.1270659767643927</v>
+        <v>0.1266263929127451</v>
       </c>
       <c r="AE20" t="n">
-        <v>-0.07050332981572549</v>
+        <v>-0.0237546683131673</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.1975693065801182</v>
+        <v>0.1503810612259124</v>
       </c>
       <c r="AG20" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="AH20" t="n">
-        <v>50</v>
+        <v>57.99999999999999</v>
       </c>
       <c r="AI20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ20" t="b">
         <v>1</v>
       </c>
       <c r="AK20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM20" t="b">
         <v>0</v>
@@ -3321,7 +3319,11 @@
       <c r="AN20" t="b">
         <v>0</v>
       </c>
-      <c r="AO20" t="inlineStr"/>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
+      </c>
       <c r="AP20" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -3336,12 +3338,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3350,96 +3352,96 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>41.2</v>
+        <v>40.59999999999999</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Sell</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1673000</v>
+        <v>12526000</v>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="K21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="b">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1673000</v>
+        <v>12966000</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>-440000</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>-0.03393490667900663</v>
       </c>
       <c r="P21" t="n">
-        <v>2515</v>
+        <v>687</v>
       </c>
       <c r="Q21" t="n">
-        <v>2515</v>
+        <v>687</v>
       </c>
       <c r="R21" t="n">
-        <v>1045457</v>
+        <v>13784732</v>
       </c>
       <c r="S21" t="n">
-        <v>2512</v>
+        <v>687</v>
       </c>
       <c r="T21" t="n">
-        <v>2261.5</v>
+        <v>630.15</v>
       </c>
       <c r="U21" t="n">
-        <v>2253</v>
+        <v>626.85</v>
       </c>
       <c r="V21" t="n">
-        <v>1821.885439046224</v>
+        <v>619.0166666666667</v>
       </c>
       <c r="W21" t="n">
-        <v>123.0591685427753</v>
+        <v>22.3859817273509</v>
       </c>
       <c r="X21" t="n">
-        <v>93.50206457801306</v>
+        <v>13.93385791776243</v>
       </c>
       <c r="Y21" t="n">
-        <v>29.55710396476223</v>
+        <v>8.452123809588464</v>
       </c>
       <c r="Z21" t="n">
-        <v>36.56152320720935</v>
+        <v>10.42840216651905</v>
       </c>
       <c r="AA21" t="b">
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.07249466950959493</v>
+        <v>0.106280193236715</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.5537346219685011</v>
+        <v>0.007331378299120228</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.02791885522921156</v>
+        <v>0.07821045355277501</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.5323472353400438</v>
+        <v>-0.01166138525214233</v>
       </c>
       <c r="AF21" t="n">
-        <v>-0.5044283801108322</v>
+        <v>0.08987183880491734</v>
       </c>
       <c r="AG21" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="AH21" t="n">
-        <v>96</v>
+        <v>62</v>
       </c>
       <c r="AI21" t="b">
         <v>1</v>
@@ -3478,12 +3480,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3492,7 +3494,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>41</v>
+        <v>38.4</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3501,24 +3503,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1000</v>
+        <v>7389000</v>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="K22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" t="b">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1000</v>
+        <v>7389000</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -3527,61 +3529,61 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>104.5</v>
+        <v>1835</v>
       </c>
       <c r="Q22" t="n">
-        <v>104.5</v>
+        <v>1835</v>
       </c>
       <c r="R22" t="n">
-        <v>53107330</v>
+        <v>12874206</v>
       </c>
       <c r="S22" t="n">
-        <v>106.4</v>
+        <v>1884</v>
       </c>
       <c r="T22" t="n">
-        <v>93.65999946594238</v>
+        <v>1780.25</v>
       </c>
       <c r="U22" t="n">
-        <v>92.95999946594239</v>
+        <v>1780</v>
       </c>
       <c r="V22" t="n">
-        <v>94.34833323160807</v>
+        <v>1777</v>
       </c>
       <c r="W22" t="n">
-        <v>4.790189329418197</v>
+        <v>33.07665985345807</v>
       </c>
       <c r="X22" t="n">
-        <v>2.493172617357349</v>
+        <v>11.58825139616999</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.297016712060849</v>
+        <v>21.48840845728808</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.020558977502503</v>
+        <v>30.30151505953038</v>
       </c>
       <c r="AA22" t="b">
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.1546961325966851</v>
+        <v>0.002732240437158362</v>
       </c>
       <c r="AC22" t="n">
-        <v>-0.004761904761904745</v>
+        <v>-0.1156626506024097</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.1101203183163018</v>
+        <v>-0.02533749924678164</v>
       </c>
       <c r="AE22" t="n">
-        <v>-0.02614929139036204</v>
+        <v>-0.1346554141536722</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.1362696097066638</v>
+        <v>0.1093179149068906</v>
       </c>
       <c r="AG22" t="n">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="AH22" t="n">
-        <v>57.99999999999999</v>
+        <v>38</v>
       </c>
       <c r="AI22" t="b">
         <v>1</v>
@@ -3620,12 +3622,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3634,96 +3636,96 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>40.59999999999999</v>
+        <v>38.2</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Heavy Sell</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>12966000</v>
+        <v>1000</v>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="K23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="b">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>13966000</v>
+        <v>1000</v>
       </c>
       <c r="N23" t="n">
-        <v>-1000000</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.07160246312473149</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>687</v>
+        <v>2185</v>
       </c>
       <c r="Q23" t="n">
-        <v>687</v>
+        <v>2185</v>
       </c>
       <c r="R23" t="n">
-        <v>14223216</v>
+        <v>2293204</v>
       </c>
       <c r="S23" t="n">
-        <v>687</v>
+        <v>2324</v>
       </c>
       <c r="T23" t="n">
-        <v>630.15</v>
+        <v>2174.25</v>
       </c>
       <c r="U23" t="n">
-        <v>626.85</v>
+        <v>2165.5</v>
       </c>
       <c r="V23" t="n">
-        <v>619.0166666666667</v>
+        <v>2072.583333333333</v>
       </c>
       <c r="W23" t="n">
-        <v>22.3859817273509</v>
+        <v>44.31469793968517</v>
       </c>
       <c r="X23" t="n">
-        <v>13.93385791776243</v>
+        <v>43.49191492007922</v>
       </c>
       <c r="Y23" t="n">
-        <v>8.452123809588464</v>
+        <v>0.8227830196059571</v>
       </c>
       <c r="Z23" t="n">
-        <v>10.42840216651905</v>
+        <v>18.1601972229389</v>
       </c>
       <c r="AA23" t="b">
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.106280193236715</v>
+        <v>0.08706467661691542</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.007331378299120228</v>
+        <v>-0.03532008830022071</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.06170437895633163</v>
+        <v>0.05899493693297542</v>
       </c>
       <c r="AE23" t="n">
-        <v>-0.01405600832933707</v>
+        <v>-0.05431285185148327</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.0757603872856687</v>
+        <v>0.1133077887844587</v>
       </c>
       <c r="AG23" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AH23" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="AI23" t="b">
         <v>1</v>
@@ -3762,12 +3764,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>慧洋-KY</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3776,7 +3778,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>38</v>
+        <v>37.8</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3785,7 +3787,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -3793,7 +3795,7 @@
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="K24" t="b">
         <v>0</v>
@@ -3811,84 +3813,82 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2185</v>
+        <v>95</v>
       </c>
       <c r="Q24" t="n">
-        <v>2185</v>
+        <v>95</v>
       </c>
       <c r="R24" t="n">
-        <v>2400440</v>
+        <v>4419115</v>
       </c>
       <c r="S24" t="n">
-        <v>2324</v>
+        <v>99.8</v>
       </c>
       <c r="T24" t="n">
-        <v>2174.25</v>
+        <v>99.41500015258789</v>
       </c>
       <c r="U24" t="n">
-        <v>2165.5</v>
+        <v>99.27000007629394</v>
       </c>
       <c r="V24" t="n">
-        <v>2072.583333333333</v>
+        <v>90.17666676839193</v>
       </c>
       <c r="W24" t="n">
-        <v>44.31469793968517</v>
+        <v>0.5228938906103764</v>
       </c>
       <c r="X24" t="n">
-        <v>43.49191492007922</v>
+        <v>1.591292314344823</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.8227830196059571</v>
+        <v>-1.068398423734447</v>
       </c>
       <c r="Z24" t="n">
-        <v>18.1601972229389</v>
+        <v>-0.5503008803853495</v>
       </c>
       <c r="AA24" t="b">
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.08706467661691542</v>
+        <v>0.03148753066150989</v>
       </c>
       <c r="AC24" t="n">
-        <v>-0.03532008830022071</v>
+        <v>0.2786002166624737</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.04248886233653204</v>
+        <v>0.00341779097756989</v>
       </c>
       <c r="AE24" t="n">
-        <v>-0.056707474928678</v>
+        <v>0.2596074531112111</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.09919633726521004</v>
+        <v>-0.2561896621336412</v>
       </c>
       <c r="AG24" t="n">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="AH24" t="n">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="AI24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="b">
         <v>1</v>
       </c>
       <c r="AK24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="b">
         <v>0</v>
       </c>
       <c r="AN24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>107.16</v>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
@@ -3904,12 +3904,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3918,7 +3918,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>37.59999999999999</v>
+        <v>37.4</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3927,15 +3927,15 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="K25" t="b">
         <v>0</v>
@@ -3944,7 +3944,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3953,82 +3953,84 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>95</v>
+        <v>175.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>95</v>
+        <v>175.5</v>
       </c>
       <c r="R25" t="n">
-        <v>4489109</v>
+        <v>20459060</v>
       </c>
       <c r="S25" t="n">
-        <v>99.8</v>
+        <v>172.4</v>
       </c>
       <c r="T25" t="n">
-        <v>99.41500015258789</v>
+        <v>160.475</v>
       </c>
       <c r="U25" t="n">
-        <v>99.27000007629394</v>
+        <v>159.4</v>
       </c>
       <c r="V25" t="n">
-        <v>90.17666676839193</v>
+        <v>154.2166666666667</v>
       </c>
       <c r="W25" t="n">
-        <v>0.5228938906103764</v>
+        <v>6.314317891986974</v>
       </c>
       <c r="X25" t="n">
-        <v>1.591292314344823</v>
+        <v>5.170831844702452</v>
       </c>
       <c r="Y25" t="n">
-        <v>-1.068398423734447</v>
+        <v>1.143486047284522</v>
       </c>
       <c r="Z25" t="n">
-        <v>-0.5503008803853495</v>
+        <v>1.281645156583237</v>
       </c>
       <c r="AA25" t="b">
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.03148753066150989</v>
+        <v>0.1396103896103895</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.2786002166624737</v>
+        <v>-0.1521739130434783</v>
       </c>
       <c r="AD25" t="n">
-        <v>-0.01308828361887349</v>
+        <v>0.1115406499264495</v>
       </c>
       <c r="AE25" t="n">
-        <v>0.2572128300340164</v>
+        <v>-0.1711666765947408</v>
       </c>
       <c r="AF25" t="n">
-        <v>-0.2703011136528899</v>
+        <v>0.2827073265211903</v>
       </c>
       <c r="AG25" t="n">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="AH25" t="n">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="AI25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ25" t="b">
         <v>1</v>
       </c>
       <c r="AK25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM25" t="b">
         <v>0</v>
       </c>
       <c r="AN25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>107.16</v>
+        <v>0</v>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
@@ -4044,12 +4046,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4058,7 +4060,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>37.2</v>
+        <v>36.4</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4067,24 +4069,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>5000</v>
+        <v>6151000</v>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="K26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="b">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>5000</v>
+        <v>6151000</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -4093,67 +4095,67 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>175.5</v>
+        <v>1485</v>
       </c>
       <c r="Q26" t="n">
-        <v>175.5</v>
+        <v>1485</v>
       </c>
       <c r="R26" t="n">
-        <v>20579836</v>
+        <v>5656430</v>
       </c>
       <c r="S26" t="n">
-        <v>172.4</v>
+        <v>1463</v>
       </c>
       <c r="T26" t="n">
-        <v>160.475</v>
+        <v>1401.25</v>
       </c>
       <c r="U26" t="n">
-        <v>159.4</v>
+        <v>1401.5</v>
       </c>
       <c r="V26" t="n">
-        <v>154.2166666666667</v>
+        <v>1412.416666666667</v>
       </c>
       <c r="W26" t="n">
-        <v>6.314317891986974</v>
+        <v>16.75624182819433</v>
       </c>
       <c r="X26" t="n">
-        <v>5.170831844702452</v>
+        <v>-2.188644010547854</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.143486047284522</v>
+        <v>18.94488583874219</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.281645156583237</v>
+        <v>19.0215381971915</v>
       </c>
       <c r="AA26" t="b">
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.1396103896103895</v>
+        <v>-0.003355704697986628</v>
       </c>
       <c r="AC26" t="n">
-        <v>-0.1521739130434783</v>
+        <v>-0.1703910614525139</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.09503457533000614</v>
+        <v>-0.03142544438192663</v>
       </c>
       <c r="AE26" t="n">
-        <v>-0.1735612996719356</v>
+        <v>-0.1893838250037765</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.2685958750019417</v>
+        <v>0.1579583806218499</v>
       </c>
       <c r="AG26" t="n">
-        <v>82</v>
+        <v>46</v>
       </c>
       <c r="AH26" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI26" t="b">
         <v>1</v>
       </c>
       <c r="AJ26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="b">
         <v>1</v>
@@ -4172,10 +4174,8 @@
           <t>Already &gt; 0</t>
         </is>
       </c>
-      <c r="AP26" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+      <c r="AP26" t="n">
+        <v>1346.84</v>
       </c>
     </row>
     <row r="27">
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>33.6</v>
+        <v>33.8</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -4241,7 +4241,7 @@
         <v>3400</v>
       </c>
       <c r="R27" t="n">
-        <v>3706504</v>
+        <v>3431524</v>
       </c>
       <c r="S27" t="n">
         <v>3446</v>
@@ -4277,13 +4277,13 @@
         <v>0.2391919732279579</v>
       </c>
       <c r="AD27" t="n">
-        <v>-0.03267105237562151</v>
+        <v>-0.01616497777917814</v>
       </c>
       <c r="AE27" t="n">
-        <v>0.2178045865995006</v>
+        <v>0.2201992096766954</v>
       </c>
       <c r="AF27" t="n">
-        <v>-0.2504756389751222</v>
+        <v>-0.2363641874558735</v>
       </c>
       <c r="AG27" t="n">
         <v>50</v>
@@ -4342,7 +4342,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>32.8</v>
+        <v>33</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -4383,7 +4383,7 @@
         <v>241.5</v>
       </c>
       <c r="R28" t="n">
-        <v>10617645</v>
+        <v>10373702</v>
       </c>
       <c r="S28" t="n">
         <v>260</v>
@@ -4419,13 +4419,13 @@
         <v>-0.02226720647773284</v>
       </c>
       <c r="AD28" t="n">
-        <v>-0.01691623981229817</v>
+        <v>-0.0004101652158547964</v>
       </c>
       <c r="AE28" t="n">
-        <v>-0.04365459310619013</v>
+        <v>-0.0412599700289954</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.02673835329389196</v>
+        <v>0.0408498048131406</v>
       </c>
       <c r="AG28" t="n">
         <v>57.99999999999999</v>
@@ -4482,7 +4482,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>32.59999999999999</v>
+        <v>32.8</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K29" t="b">
         <v>0</v>
@@ -4523,7 +4523,7 @@
         <v>227</v>
       </c>
       <c r="R29" t="n">
-        <v>1227422</v>
+        <v>1194459</v>
       </c>
       <c r="S29" t="n">
         <v>228.5</v>
@@ -4559,13 +4559,13 @@
         <v>-0.1863799283154122</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.01123813920798877</v>
+        <v>0.02774421380443215</v>
       </c>
       <c r="AE29" t="n">
-        <v>-0.2077673149438695</v>
+        <v>-0.2053726918666747</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.2190054541518582</v>
+        <v>0.2331169056711069</v>
       </c>
       <c r="AG29" t="n">
         <v>68</v>
@@ -4622,7 +4622,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>30.2</v>
+        <v>30.4</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -4663,7 +4663,7 @@
         <v>336.5</v>
       </c>
       <c r="R30" t="n">
-        <v>9816683</v>
+        <v>9674015</v>
       </c>
       <c r="S30" t="n">
         <v>340.6</v>
@@ -4699,13 +4699,13 @@
         <v>-0.0693204989110987</v>
       </c>
       <c r="AD30" t="n">
-        <v>-0.03254573909241354</v>
+        <v>-0.01603966449597016</v>
       </c>
       <c r="AE30" t="n">
-        <v>-0.090707885539556</v>
+        <v>-0.08831326246236126</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.05816214644714246</v>
+        <v>0.0722735979663911</v>
       </c>
       <c r="AG30" t="n">
         <v>52</v>
@@ -4762,7 +4762,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>29</v>
+        <v>29.2</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -4803,7 +4803,7 @@
         <v>5185</v>
       </c>
       <c r="R31" t="n">
-        <v>1124797</v>
+        <v>976210</v>
       </c>
       <c r="S31" t="n">
         <v>5412</v>
@@ -4839,13 +4839,13 @@
         <v>-0.2950246126757454</v>
       </c>
       <c r="AD31" t="n">
-        <v>-0.01376070493644699</v>
+        <v>0.002745369659996388</v>
       </c>
       <c r="AE31" t="n">
-        <v>-0.3164119993042027</v>
+        <v>-0.314017376227008</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.3026512943677557</v>
+        <v>0.3167627458870044</v>
       </c>
       <c r="AG31" t="n">
         <v>60</v>
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>28.6</v>
+        <v>28.8</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -4943,7 +4943,7 @@
         <v>250.5</v>
       </c>
       <c r="R32" t="n">
-        <v>30593394</v>
+        <v>30194485</v>
       </c>
       <c r="S32" t="n">
         <v>252</v>
@@ -4979,13 +4979,13 @@
         <v>0.04158004158004158</v>
       </c>
       <c r="AD32" t="n">
-        <v>-0.05445723720528461</v>
+        <v>-0.03795116260884124</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.02019265495158429</v>
+        <v>0.02258727802877902</v>
       </c>
       <c r="AF32" t="n">
-        <v>-0.0746498921568689</v>
+        <v>-0.06053844063762026</v>
       </c>
       <c r="AG32" t="n">
         <v>40</v>
@@ -5042,7 +5042,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>27.4</v>
+        <v>27.6</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -5083,7 +5083,7 @@
         <v>18.79999923706055</v>
       </c>
       <c r="R33" t="n">
-        <v>36555448</v>
+        <v>36481292</v>
       </c>
       <c r="S33" t="n">
         <v>18.67999954223633</v>
@@ -5119,13 +5119,13 @@
         <v>-6.279652717955386e-05</v>
       </c>
       <c r="AD33" t="n">
-        <v>-0.05769917438601746</v>
+        <v>-0.04119309978957408</v>
       </c>
       <c r="AE33" t="n">
-        <v>-0.02145018315563685</v>
+        <v>-0.01905556007844211</v>
       </c>
       <c r="AF33" t="n">
-        <v>-0.03624899123038061</v>
+        <v>-0.02213753971113197</v>
       </c>
       <c r="AG33" t="n">
         <v>38</v>
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>27.2</v>
+        <v>27.4</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -5223,7 +5223,7 @@
         <v>78.09999847412109</v>
       </c>
       <c r="R34" t="n">
-        <v>1216944</v>
+        <v>1207246</v>
       </c>
       <c r="S34" t="n">
         <v>78.19999847412109</v>
@@ -5259,13 +5259,13 @@
         <v>-0.1085829664639786</v>
       </c>
       <c r="AD34" t="n">
-        <v>-0.04967137511960507</v>
+        <v>-0.03316530052316169</v>
       </c>
       <c r="AE34" t="n">
-        <v>-0.1299703530924359</v>
+        <v>-0.1275757300152411</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.08029897797283081</v>
+        <v>0.09441042949207945</v>
       </c>
       <c r="AG34" t="n">
         <v>44</v>
@@ -5322,7 +5322,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>26.8</v>
+        <v>27</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -5363,7 +5363,7 @@
         <v>548</v>
       </c>
       <c r="R35" t="n">
-        <v>41035274</v>
+        <v>39224107</v>
       </c>
       <c r="S35" t="n">
         <v>565.8</v>
@@ -5399,13 +5399,13 @@
         <v>-0.4755980861244019</v>
       </c>
       <c r="AD35" t="n">
-        <v>-0.1266528662066815</v>
+        <v>-0.1101467916102381</v>
       </c>
       <c r="AE35" t="n">
-        <v>-0.4969854727528592</v>
+        <v>-0.4945908496756645</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.3703326065461777</v>
+        <v>0.3844440580654264</v>
       </c>
       <c r="AG35" t="n">
         <v>22</v>
@@ -5462,7 +5462,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>26.6</v>
+        <v>26.8</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -5503,7 +5503,7 @@
         <v>506</v>
       </c>
       <c r="R36" t="n">
-        <v>24890762</v>
+        <v>24327412</v>
       </c>
       <c r="S36" t="n">
         <v>507.4</v>
@@ -5539,13 +5539,13 @@
         <v>0.2396246362848151</v>
       </c>
       <c r="AD36" t="n">
-        <v>-0.1075387772433464</v>
+        <v>-0.091032702646903</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.2182372496563578</v>
+        <v>0.2206318727335526</v>
       </c>
       <c r="AF36" t="n">
-        <v>-0.3257760268997042</v>
+        <v>-0.3116645753804556</v>
       </c>
       <c r="AG36" t="n">
         <v>26</v>
@@ -5602,7 +5602,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>25.2</v>
+        <v>25.4</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -5643,7 +5643,7 @@
         <v>567</v>
       </c>
       <c r="R37" t="n">
-        <v>951235</v>
+        <v>925273</v>
       </c>
       <c r="S37" t="n">
         <v>588.6</v>
@@ -5679,13 +5679,13 @@
         <v>0.2164972861756815</v>
       </c>
       <c r="AD37" t="n">
-        <v>-0.1150676175590719</v>
+        <v>-0.09856154296262853</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.1951098995472242</v>
+        <v>0.197504522624419</v>
       </c>
       <c r="AF37" t="n">
-        <v>-0.3101775171062962</v>
+        <v>-0.2960660655870475</v>
       </c>
       <c r="AG37" t="n">
         <v>24</v>
@@ -5740,7 +5740,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>24</v>
+        <v>24.2</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5749,7 +5749,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -5781,7 +5781,7 @@
         <v>226</v>
       </c>
       <c r="R38" t="n">
-        <v>10020552</v>
+        <v>9861253</v>
       </c>
       <c r="S38" t="n">
         <v>223.3</v>
@@ -5817,13 +5817,13 @@
         <v>-0.01525054466230935</v>
       </c>
       <c r="AD38" t="n">
-        <v>-0.1068164781807983</v>
+        <v>-0.09031040358435494</v>
       </c>
       <c r="AE38" t="n">
-        <v>-0.03663793129076665</v>
+        <v>-0.03424330821357191</v>
       </c>
       <c r="AF38" t="n">
-        <v>-0.07017854689003167</v>
+        <v>-0.05606709537078303</v>
       </c>
       <c r="AG38" t="n">
         <v>28</v>
@@ -5878,7 +5878,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>23.8</v>
+        <v>24</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5887,7 +5887,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -5919,7 +5919,7 @@
         <v>569</v>
       </c>
       <c r="R39" t="n">
-        <v>232543</v>
+        <v>220236</v>
       </c>
       <c r="S39" t="n">
         <v>570.8</v>
@@ -5934,16 +5934,16 @@
         <v>578.7163747151693</v>
       </c>
       <c r="W39" t="n">
-        <v>2.905234999841696</v>
+        <v>2.905234999840673</v>
       </c>
       <c r="X39" t="n">
-        <v>-1.264685839276776</v>
+        <v>-1.264685839278743</v>
       </c>
       <c r="Y39" t="n">
-        <v>4.169920839118472</v>
+        <v>4.169920839119415</v>
       </c>
       <c r="Z39" t="n">
-        <v>4.879444149136265</v>
+        <v>4.879444149137329</v>
       </c>
       <c r="AA39" t="b">
         <v>0</v>
@@ -5955,13 +5955,13 @@
         <v>-0.1164863388211188</v>
       </c>
       <c r="AD39" t="n">
-        <v>-0.07026074578723274</v>
+        <v>-0.05375467119078936</v>
       </c>
       <c r="AE39" t="n">
-        <v>-0.1378737254495761</v>
+        <v>-0.1354791023723814</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.06761297966234336</v>
+        <v>0.08172443118159201</v>
       </c>
       <c r="AG39" t="n">
         <v>34</v>
@@ -6018,7 +6018,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -6059,7 +6059,7 @@
         <v>83.09999847412109</v>
       </c>
       <c r="R40" t="n">
-        <v>1035348</v>
+        <v>1025747</v>
       </c>
       <c r="S40" t="n">
         <v>83.14000091552734</v>
@@ -6095,13 +6095,13 @@
         <v>-0.2111138094373449</v>
       </c>
       <c r="AD40" t="n">
-        <v>-0.06346599765428373</v>
+        <v>-0.04695992305784036</v>
       </c>
       <c r="AE40" t="n">
-        <v>-0.2325011960658022</v>
+        <v>-0.2301065729886075</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.1690351984115185</v>
+        <v>0.1831466499307671</v>
       </c>
       <c r="AG40" t="n">
         <v>36</v>
@@ -6158,7 +6158,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -6199,7 +6199,7 @@
         <v>1810</v>
       </c>
       <c r="R41" t="n">
-        <v>4153316</v>
+        <v>3767665</v>
       </c>
       <c r="S41" t="n">
         <v>1870</v>
@@ -6235,13 +6235,13 @@
         <v>-0.3329699668417579</v>
       </c>
       <c r="AD41" t="n">
-        <v>-0.1928111083980304</v>
+        <v>-0.176305033801587</v>
       </c>
       <c r="AE41" t="n">
-        <v>-0.3543573534702152</v>
+        <v>-0.3519627303930205</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.1615462450721848</v>
+        <v>0.1756576965914335</v>
       </c>
       <c r="AG41" t="n">
         <v>4</v>
@@ -6298,7 +6298,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>21.2</v>
+        <v>21.4</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -6339,7 +6339,7 @@
         <v>6020</v>
       </c>
       <c r="R42" t="n">
-        <v>1778124</v>
+        <v>1514869</v>
       </c>
       <c r="S42" t="n">
         <v>6252</v>
@@ -6354,16 +6354,16 @@
         <v>5252.736177571614</v>
       </c>
       <c r="W42" t="n">
-        <v>-54.19210189352088</v>
+        <v>-54.1921018935227</v>
       </c>
       <c r="X42" t="n">
-        <v>41.14392880557755</v>
+        <v>41.14392880557538</v>
       </c>
       <c r="Y42" t="n">
-        <v>-95.33603069909844</v>
+        <v>-95.33603069909807</v>
       </c>
       <c r="Z42" t="n">
-        <v>-88.88242318529913</v>
+        <v>-88.88242318529869</v>
       </c>
       <c r="AA42" t="b">
         <v>0</v>
@@ -6375,13 +6375,13 @@
         <v>0.4361668978356548</v>
       </c>
       <c r="AD42" t="n">
-        <v>-0.1924880577340281</v>
+        <v>-0.1759819831375847</v>
       </c>
       <c r="AE42" t="n">
-        <v>0.4147795112071975</v>
+        <v>0.4171741342843922</v>
       </c>
       <c r="AF42" t="n">
-        <v>-0.6072675689412256</v>
+        <v>-0.5931561174219769</v>
       </c>
       <c r="AG42" t="n">
         <v>6</v>
@@ -6436,7 +6436,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -6477,7 +6477,7 @@
         <v>945</v>
       </c>
       <c r="R43" t="n">
-        <v>9147468</v>
+        <v>8858935</v>
       </c>
       <c r="S43" t="n">
         <v>949</v>
@@ -6513,13 +6513,13 @@
         <v>-0.2441006881505237</v>
       </c>
       <c r="AD43" t="n">
-        <v>-0.07235359205816116</v>
+        <v>-0.05584751746171779</v>
       </c>
       <c r="AE43" t="n">
-        <v>-0.265488074778981</v>
+        <v>-0.2630934517017862</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.1931344827208198</v>
+        <v>0.2072459342400684</v>
       </c>
       <c r="AG43" t="n">
         <v>32</v>
@@ -6562,12 +6562,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6576,7 +6576,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>18.8</v>
+        <v>20.8</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6585,15 +6585,15 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>1000</v>
+        <v>4812561</v>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="K44" t="b">
         <v>0</v>
@@ -6602,7 +6602,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>1000</v>
+        <v>4812561</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
@@ -6611,61 +6611,61 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>498</v>
+        <v>2100</v>
       </c>
       <c r="Q44" t="n">
-        <v>498</v>
+        <v>2100</v>
       </c>
       <c r="R44" t="n">
-        <v>13754919</v>
+        <v>1491509</v>
       </c>
       <c r="S44" t="n">
-        <v>497.8</v>
+        <v>2117</v>
       </c>
       <c r="T44" t="n">
-        <v>504.15</v>
+        <v>2303.181958007813</v>
       </c>
       <c r="U44" t="n">
-        <v>506.4</v>
+        <v>2318.874145507812</v>
       </c>
       <c r="V44" t="n">
-        <v>444.9723617553711</v>
+        <v>2049.523036702474</v>
       </c>
       <c r="W44" t="n">
-        <v>4.732626012677144</v>
+        <v>-53.14595567825836</v>
       </c>
       <c r="X44" t="n">
-        <v>8.169927233199608</v>
+        <v>-26.07044988566617</v>
       </c>
       <c r="Y44" t="n">
-        <v>-3.437301220522464</v>
+        <v>-27.07550579259219</v>
       </c>
       <c r="Z44" t="n">
-        <v>-3.543413592575728</v>
+        <v>-32.71960656973074</v>
       </c>
       <c r="AA44" t="b">
         <v>1</v>
       </c>
       <c r="AB44" t="n">
-        <v>-0.08287292817679559</v>
+        <v>-0.130018254081276</v>
       </c>
       <c r="AC44" t="n">
-        <v>-0.1520691926783012</v>
+        <v>0.1897186762636975</v>
       </c>
       <c r="AD44" t="n">
-        <v>-0.127448742457179</v>
+        <v>-0.158087993765216</v>
       </c>
       <c r="AE44" t="n">
-        <v>-0.1734565793067585</v>
+        <v>0.170725912712435</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.04600783684957954</v>
+        <v>-0.328813906477651</v>
       </c>
       <c r="AG44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AH44" t="n">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="AI44" t="b">
         <v>0</v>
@@ -6686,10 +6686,10 @@
         <v>1</v>
       </c>
       <c r="AO44" t="n">
-        <v>536.84</v>
+        <v>2406.6</v>
       </c>
       <c r="AP44" t="n">
-        <v>546.47</v>
+        <v>2592.52</v>
       </c>
     </row>
     <row r="45">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6714,7 +6714,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="K45" t="b">
         <v>0</v>
@@ -6749,61 +6749,61 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>3685</v>
+        <v>498</v>
       </c>
       <c r="Q45" t="n">
-        <v>3685</v>
+        <v>498</v>
       </c>
       <c r="R45" t="n">
-        <v>1173328</v>
+        <v>13255069</v>
       </c>
       <c r="S45" t="n">
-        <v>3719</v>
+        <v>497.8</v>
       </c>
       <c r="T45" t="n">
-        <v>3806.133447265625</v>
+        <v>504.15</v>
       </c>
       <c r="U45" t="n">
-        <v>3823.557153320312</v>
+        <v>506.4</v>
       </c>
       <c r="V45" t="n">
-        <v>3722.035770670573</v>
+        <v>444.9723617553711</v>
       </c>
       <c r="W45" t="n">
-        <v>-34.62518804981619</v>
+        <v>4.732626012677144</v>
       </c>
       <c r="X45" t="n">
-        <v>-57.22502843566262</v>
+        <v>8.169927233199608</v>
       </c>
       <c r="Y45" t="n">
-        <v>22.59984038584643</v>
+        <v>-3.437301220522464</v>
       </c>
       <c r="Z45" t="n">
-        <v>22.952187296328</v>
+        <v>-3.543413592575728</v>
       </c>
       <c r="AA45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB45" t="n">
-        <v>-0.08639552669281902</v>
+        <v>-0.08287292817679559</v>
       </c>
       <c r="AC45" t="n">
-        <v>-0.2013328334043964</v>
+        <v>-0.1520691926783012</v>
       </c>
       <c r="AD45" t="n">
-        <v>-0.1309713409732024</v>
+        <v>-0.1109426678607356</v>
       </c>
       <c r="AE45" t="n">
-        <v>-0.2227202200328537</v>
+        <v>-0.1710619562295638</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.09174887905965134</v>
+        <v>0.06011928836882818</v>
       </c>
       <c r="AG45" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AH45" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="AI45" t="b">
         <v>0</v>
@@ -6812,24 +6812,22 @@
         <v>0</v>
       </c>
       <c r="AK45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>536.84</v>
       </c>
       <c r="AP45" t="n">
-        <v>4170.91</v>
+        <v>546.47</v>
       </c>
     </row>
     <row r="46">
@@ -6840,12 +6838,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6854,7 +6852,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>16</v>
+        <v>17.2</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6863,88 +6861,88 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>4650000</v>
+        <v>1000</v>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="n">
+        <v>46</v>
+      </c>
+      <c r="K46" t="b">
+        <v>0</v>
+      </c>
+      <c r="L46" t="b">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>3685</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>3685</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1049644</v>
+      </c>
+      <c r="S46" t="n">
+        <v>3719</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3806.133447265625</v>
+      </c>
+      <c r="U46" t="n">
+        <v>3823.557153320312</v>
+      </c>
+      <c r="V46" t="n">
+        <v>3722.035770670573</v>
+      </c>
+      <c r="W46" t="n">
+        <v>-34.62518804981619</v>
+      </c>
+      <c r="X46" t="n">
+        <v>-57.22502843566262</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>22.59984038584643</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>22.952187296328</v>
+      </c>
+      <c r="AA46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>-0.08639552669281902</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>-0.2013328334043964</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>-0.114465266376759</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>-0.220325596955659</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>0.1058603305789</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH46" t="n">
         <v>16</v>
       </c>
-      <c r="K46" t="b">
-        <v>0</v>
-      </c>
-      <c r="L46" t="b">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>4650000</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>4920</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>4920</v>
-      </c>
-      <c r="R46" t="n">
-        <v>2141504</v>
-      </c>
-      <c r="S46" t="n">
-        <v>4949</v>
-      </c>
-      <c r="T46" t="n">
-        <v>5205</v>
-      </c>
-      <c r="U46" t="n">
-        <v>5233.5</v>
-      </c>
-      <c r="V46" t="n">
-        <v>5222.410237630208</v>
-      </c>
-      <c r="W46" t="n">
-        <v>-122.985475366906</v>
-      </c>
-      <c r="X46" t="n">
-        <v>-121.5310149093981</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>-1.454460457507963</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>-4.91659458514917</v>
-      </c>
-      <c r="AA46" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>-0.1038251366120219</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>-0.1870944663359106</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>-0.1484009508924052</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>-0.2084818529643679</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>0.06008090207196271</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>18</v>
-      </c>
       <c r="AI46" t="b">
         <v>0</v>
       </c>
@@ -6952,22 +6950,24 @@
         <v>0</v>
       </c>
       <c r="AK46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN46" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO46" t="n">
-        <v>4939.68</v>
+        <v>0</v>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP46" t="n">
-        <v>5785</v>
+        <v>4170.91</v>
       </c>
     </row>
     <row r="47">
@@ -6978,12 +6978,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6992,7 +6992,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>15.8</v>
+        <v>16.2</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -7001,15 +7001,15 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>1000</v>
+        <v>4650000</v>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="K47" t="b">
         <v>0</v>
@@ -7018,7 +7018,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>1000</v>
+        <v>4650000</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
@@ -7027,61 +7027,61 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>1210</v>
+        <v>4920</v>
       </c>
       <c r="Q47" t="n">
-        <v>1210</v>
+        <v>4920</v>
       </c>
       <c r="R47" t="n">
-        <v>781428</v>
+        <v>1885375</v>
       </c>
       <c r="S47" t="n">
-        <v>1230</v>
+        <v>4949</v>
       </c>
       <c r="T47" t="n">
-        <v>1303.25</v>
+        <v>5205</v>
       </c>
       <c r="U47" t="n">
-        <v>1313.5</v>
+        <v>5233.5</v>
       </c>
       <c r="V47" t="n">
-        <v>1372.252374267578</v>
+        <v>5222.410237630208</v>
       </c>
       <c r="W47" t="n">
-        <v>-41.92936277646072</v>
+        <v>-122.985475366906</v>
       </c>
       <c r="X47" t="n">
-        <v>-41.63566438906444</v>
+        <v>-121.5310149093981</v>
       </c>
       <c r="Y47" t="n">
-        <v>-0.293698387396276</v>
+        <v>-1.454460457507963</v>
       </c>
       <c r="Z47" t="n">
-        <v>-1.080270568222282</v>
+        <v>-4.91659458514917</v>
       </c>
       <c r="AA47" t="b">
         <v>1</v>
       </c>
       <c r="AB47" t="n">
-        <v>-0.1448763250883393</v>
+        <v>-0.1038251366120219</v>
       </c>
       <c r="AC47" t="n">
-        <v>-0.1417093287088268</v>
+        <v>-0.1870944663359106</v>
       </c>
       <c r="AD47" t="n">
-        <v>-0.1894521393687226</v>
+        <v>-0.1318948762959619</v>
       </c>
       <c r="AE47" t="n">
-        <v>-0.1630967153372841</v>
+        <v>-0.2060872298871732</v>
       </c>
       <c r="AF47" t="n">
-        <v>-0.02635542403143853</v>
+        <v>0.07419235359121135</v>
       </c>
       <c r="AG47" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AH47" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="AI47" t="b">
         <v>0</v>
@@ -7102,10 +7102,10 @@
         <v>1</v>
       </c>
       <c r="AO47" t="n">
-        <v>1214.84</v>
+        <v>4939.68</v>
       </c>
       <c r="AP47" t="n">
-        <v>1523.16</v>
+        <v>5785</v>
       </c>
     </row>
     <row r="48">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7130,7 +7130,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>15.2</v>
+        <v>16</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -7139,88 +7139,88 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>93000</v>
+        <v>1000</v>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="n">
+        <v>40</v>
+      </c>
+      <c r="K48" t="b">
+        <v>0</v>
+      </c>
+      <c r="L48" t="b">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>1210</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>1210</v>
+      </c>
+      <c r="R48" t="n">
+        <v>769126</v>
+      </c>
+      <c r="S48" t="n">
+        <v>1230</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1303.25</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1313.5</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1372.252374267578</v>
+      </c>
+      <c r="W48" t="n">
+        <v>-41.92936277646072</v>
+      </c>
+      <c r="X48" t="n">
+        <v>-41.63566438906444</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>-0.293698387396276</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>-1.080270568222282</v>
+      </c>
+      <c r="AA48" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>-0.1448763250883393</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>-0.1417093287088268</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>-0.1729460647722793</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>-0.1607020922600894</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>-0.01224397251218989</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH48" t="n">
         <v>34</v>
       </c>
-      <c r="K48" t="b">
-        <v>0</v>
-      </c>
-      <c r="L48" t="b">
-        <v>0</v>
-      </c>
-      <c r="M48" t="n">
-        <v>93000</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
-        <v>5675</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>5675</v>
-      </c>
-      <c r="R48" t="n">
-        <v>382921</v>
-      </c>
-      <c r="S48" t="n">
-        <v>5816</v>
-      </c>
-      <c r="T48" t="n">
-        <v>6557</v>
-      </c>
-      <c r="U48" t="n">
-        <v>6585.75</v>
-      </c>
-      <c r="V48" t="n">
-        <v>6612.443286132812</v>
-      </c>
-      <c r="W48" t="n">
-        <v>-256.1836741605221</v>
-      </c>
-      <c r="X48" t="n">
-        <v>-150.7218537727582</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>-105.4618203877638</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>-110.1137434607653</v>
-      </c>
-      <c r="AA48" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>-0.09199999999999997</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>-0.4225288094645175</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>-0.1365758142803833</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>-0.4439161960929748</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>0.3073403818125915</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>4</v>
-      </c>
       <c r="AI48" t="b">
         <v>0</v>
       </c>
@@ -7237,11 +7237,13 @@
         <v>1</v>
       </c>
       <c r="AN48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO48" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>1214.84</v>
+      </c>
       <c r="AP48" t="n">
-        <v>7213.42</v>
+        <v>1523.16</v>
       </c>
     </row>
     <row r="49">
@@ -7252,12 +7254,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -7266,7 +7268,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>14.4</v>
+        <v>15.4</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -7275,15 +7277,15 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1139000</v>
+        <v>93000</v>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="K49" t="b">
         <v>0</v>
@@ -7292,7 +7294,7 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>1139000</v>
+        <v>93000</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
@@ -7301,61 +7303,61 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>877</v>
+        <v>5675</v>
       </c>
       <c r="Q49" t="n">
-        <v>877</v>
+        <v>5675</v>
       </c>
       <c r="R49" t="n">
-        <v>1135012</v>
+        <v>300592</v>
       </c>
       <c r="S49" t="n">
-        <v>892.8</v>
+        <v>5816</v>
       </c>
       <c r="T49" t="n">
-        <v>916.55</v>
+        <v>6557</v>
       </c>
       <c r="U49" t="n">
-        <v>922.2</v>
+        <v>6585.75</v>
       </c>
       <c r="V49" t="n">
-        <v>1023.7</v>
+        <v>6612.443286132812</v>
       </c>
       <c r="W49" t="n">
-        <v>-17.351247899604</v>
+        <v>-256.1836741605221</v>
       </c>
       <c r="X49" t="n">
-        <v>-21.35119356877836</v>
+        <v>-150.7218537727582</v>
       </c>
       <c r="Y49" t="n">
-        <v>3.999945669174359</v>
+        <v>-105.4618203877638</v>
       </c>
       <c r="Z49" t="n">
-        <v>5.458706615243454</v>
+        <v>-110.1137434607653</v>
       </c>
       <c r="AA49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB49" t="n">
-        <v>-0.1141414141414141</v>
+        <v>-0.09199999999999997</v>
       </c>
       <c r="AC49" t="n">
-        <v>-0.3279693486590038</v>
+        <v>-0.4225288094645175</v>
       </c>
       <c r="AD49" t="n">
-        <v>-0.1587172284217975</v>
+        <v>-0.12006973968394</v>
       </c>
       <c r="AE49" t="n">
-        <v>-0.3493567352874611</v>
+        <v>-0.4415215730157801</v>
       </c>
       <c r="AF49" t="n">
-        <v>0.1906395068656637</v>
+        <v>0.3214518333318401</v>
       </c>
       <c r="AG49" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AH49" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AI49" t="b">
         <v>0</v>
@@ -7364,24 +7366,20 @@
         <v>0</v>
       </c>
       <c r="AK49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN49" t="b">
         <v>0</v>
       </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
+      <c r="AO49" t="inlineStr"/>
       <c r="AP49" t="n">
-        <v>1010.63</v>
+        <v>7213.42</v>
       </c>
     </row>
     <row r="50">
@@ -7392,12 +7390,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>新日興</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7406,7 +7404,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>13.6</v>
+        <v>14.6</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7415,15 +7413,15 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1740000</v>
+        <v>1139000</v>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K50" t="b">
         <v>0</v>
@@ -7432,7 +7430,7 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>1740000</v>
+        <v>1139000</v>
       </c>
       <c r="N50" t="n">
         <v>0</v>
@@ -7441,61 +7439,61 @@
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>171.5</v>
+        <v>877</v>
       </c>
       <c r="Q50" t="n">
-        <v>171.5</v>
+        <v>877</v>
       </c>
       <c r="R50" t="n">
-        <v>2073642</v>
+        <v>1021144</v>
       </c>
       <c r="S50" t="n">
-        <v>175.9</v>
+        <v>892.8</v>
       </c>
       <c r="T50" t="n">
-        <v>190.15</v>
+        <v>916.55</v>
       </c>
       <c r="U50" t="n">
-        <v>192.425</v>
+        <v>922.2</v>
       </c>
       <c r="V50" t="n">
-        <v>187.6991394042969</v>
+        <v>1023.7</v>
       </c>
       <c r="W50" t="n">
-        <v>-5.655320692459924</v>
+        <v>-17.351247899604</v>
       </c>
       <c r="X50" t="n">
-        <v>-4.491815215724384</v>
+        <v>-21.35119356877836</v>
       </c>
       <c r="Y50" t="n">
-        <v>-1.16350547673554</v>
+        <v>3.999945669174359</v>
       </c>
       <c r="Z50" t="n">
-        <v>-1.2357231122222</v>
+        <v>5.458706615243454</v>
       </c>
       <c r="AA50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>-0.2096774193548387</v>
+        <v>-0.1141414141414141</v>
       </c>
       <c r="AC50" t="n">
-        <v>-0.1428375103461536</v>
+        <v>-0.3279693486590038</v>
       </c>
       <c r="AD50" t="n">
-        <v>-0.2542532336352221</v>
+        <v>-0.1422111538253541</v>
       </c>
       <c r="AE50" t="n">
-        <v>-0.1642248969746108</v>
+        <v>-0.3469621122102664</v>
       </c>
       <c r="AF50" t="n">
-        <v>-0.09002833666061127</v>
+        <v>0.2047509583849123</v>
       </c>
       <c r="AG50" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="AH50" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="AI50" t="b">
         <v>0</v>
@@ -7504,22 +7502,24 @@
         <v>0</v>
       </c>
       <c r="AK50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN50" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO50" t="n">
-        <v>184.88</v>
+        <v>0</v>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP50" t="n">
-        <v>233.63</v>
+        <v>1010.63</v>
       </c>
     </row>
     <row r="51">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3376</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>新日興</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7544,24 +7544,24 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>11.8</v>
+        <v>13.8</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Heavy Sell</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>4812561</v>
+        <v>1740000</v>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="K51" t="b">
         <v>0</v>
@@ -7570,70 +7570,70 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>4873561</v>
+        <v>1740000</v>
       </c>
       <c r="N51" t="n">
-        <v>-61000</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>-0.01251651513133826</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>2100</v>
+        <v>171.5</v>
       </c>
       <c r="Q51" t="n">
-        <v>2100</v>
+        <v>171.5</v>
       </c>
       <c r="R51" t="n">
-        <v>1633262</v>
+        <v>2015119</v>
       </c>
       <c r="S51" t="n">
-        <v>2117</v>
+        <v>175.9</v>
       </c>
       <c r="T51" t="n">
-        <v>2303.181958007813</v>
+        <v>190.15</v>
       </c>
       <c r="U51" t="n">
-        <v>2318.874145507812</v>
+        <v>192.425</v>
       </c>
       <c r="V51" t="n">
-        <v>2049.523036702474</v>
+        <v>187.6991394042969</v>
       </c>
       <c r="W51" t="n">
-        <v>-53.14595567825836</v>
+        <v>-5.655320692459924</v>
       </c>
       <c r="X51" t="n">
-        <v>-26.07044988566617</v>
+        <v>-4.491815215724384</v>
       </c>
       <c r="Y51" t="n">
-        <v>-27.07550579259219</v>
+        <v>-1.16350547673554</v>
       </c>
       <c r="Z51" t="n">
-        <v>-32.71960656973074</v>
+        <v>-1.2357231122222</v>
       </c>
       <c r="AA51" t="b">
         <v>1</v>
       </c>
       <c r="AB51" t="n">
-        <v>-0.130018254081276</v>
+        <v>-0.2096774193548387</v>
       </c>
       <c r="AC51" t="n">
-        <v>0.1897186762636975</v>
+        <v>-0.1428375103461536</v>
       </c>
       <c r="AD51" t="n">
-        <v>-0.1745940683616594</v>
+        <v>-0.2377471590387787</v>
       </c>
       <c r="AE51" t="n">
-        <v>0.1683312896352402</v>
+        <v>-0.1618302738974161</v>
       </c>
       <c r="AF51" t="n">
-        <v>-0.3429253579968996</v>
+        <v>-0.07591688514136263</v>
       </c>
       <c r="AG51" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AH51" t="n">
-        <v>76</v>
+        <v>30</v>
       </c>
       <c r="AI51" t="b">
         <v>0</v>
@@ -7654,10 +7654,10 @@
         <v>1</v>
       </c>
       <c r="AO51" t="n">
-        <v>2406.6</v>
+        <v>184.88</v>
       </c>
       <c r="AP51" t="n">
-        <v>2592.52</v>
+        <v>233.63</v>
       </c>
     </row>
   </sheetData>

--- a/output/daily_screen_latest.xlsx
+++ b/output/daily_screen_latest.xlsx
@@ -643,17 +643,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>87.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -671,15 +671,15 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>3741000</v>
+        <v>576000</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K2" t="b">
         <v>0</v>
@@ -688,70 +688,70 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>3420000</v>
+        <v>476000</v>
       </c>
       <c r="N2" t="n">
-        <v>321000</v>
+        <v>100000</v>
       </c>
       <c r="O2" t="n">
-        <v>0.09385964912280702</v>
+        <v>0.2100840336134454</v>
       </c>
       <c r="P2" t="n">
-        <v>1245</v>
+        <v>1710</v>
       </c>
       <c r="Q2" t="n">
-        <v>1245</v>
+        <v>1710</v>
       </c>
       <c r="R2" t="n">
-        <v>11085964</v>
+        <v>1005302</v>
       </c>
       <c r="S2" t="n">
-        <v>1184</v>
+        <v>1612</v>
       </c>
       <c r="T2" t="n">
-        <v>1084.7</v>
+        <v>1475.25</v>
       </c>
       <c r="U2" t="n">
-        <v>1078.45</v>
+        <v>1451</v>
       </c>
       <c r="V2" t="n">
-        <v>1015.866666666667</v>
+        <v>1230.7</v>
       </c>
       <c r="W2" t="n">
-        <v>47.70557665332512</v>
+        <v>82.97786803840927</v>
       </c>
       <c r="X2" t="n">
-        <v>25.20899436439355</v>
+        <v>77.0385210835143</v>
       </c>
       <c r="Y2" t="n">
-        <v>22.49658228893157</v>
+        <v>5.939346954894972</v>
       </c>
       <c r="Z2" t="n">
-        <v>22.23927612397038</v>
+        <v>0.7257809581076344</v>
       </c>
       <c r="AA2" t="b">
         <v>1</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.1116071428571428</v>
+        <v>0.3959183673469389</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.1913875598086126</v>
+        <v>0.4553191489361703</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.05920281039940778</v>
+        <v>0.3510169107621723</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.09385999493681196</v>
+        <v>0.3748842768153884</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.03465718453740418</v>
+        <v>-0.02386736605321604</v>
       </c>
       <c r="AG2" t="n">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="AH2" t="n">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="AI2" t="b">
         <v>1</v>
@@ -785,17 +785,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>85.8</v>
+        <v>85</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -813,15 +813,15 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>476000</v>
+        <v>1000</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="K3" t="b">
         <v>0</v>
@@ -830,7 +830,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>476000</v>
+        <v>1000</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -839,61 +839,61 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1645</v>
+        <v>248</v>
       </c>
       <c r="Q3" t="n">
-        <v>1645</v>
+        <v>248</v>
       </c>
       <c r="R3" t="n">
-        <v>1039407</v>
+        <v>21328932</v>
       </c>
       <c r="S3" t="n">
-        <v>1583</v>
+        <v>233.9</v>
       </c>
       <c r="T3" t="n">
-        <v>1451</v>
+        <v>207.475</v>
       </c>
       <c r="U3" t="n">
-        <v>1430.75</v>
+        <v>204.5</v>
       </c>
       <c r="V3" t="n">
-        <v>1221.783333333333</v>
+        <v>184.3166666666667</v>
       </c>
       <c r="W3" t="n">
-        <v>76.29115384803117</v>
+        <v>13.03030260938419</v>
       </c>
       <c r="X3" t="n">
-        <v>75.57682035967345</v>
+        <v>8.753144333719984</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.7143334883577239</v>
+        <v>4.27715827566421</v>
       </c>
       <c r="Z3" t="n">
-        <v>-1.072222229941517</v>
+        <v>4.106425522885155</v>
       </c>
       <c r="AA3" t="b">
         <v>1</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3266129032258065</v>
+        <v>0.3156498673740054</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.3266129032258065</v>
+        <v>0.4376811594202898</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.2742085707680715</v>
+        <v>0.2707484107892388</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.2290853383540059</v>
+        <v>0.3572462872995079</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.04512323241406557</v>
+        <v>-0.08649787651026908</v>
       </c>
       <c r="AG3" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AH3" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="AI3" t="b">
         <v>1</v>
@@ -927,17 +927,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>85.60000000000001</v>
+        <v>80</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,15 +955,15 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1000</v>
+        <v>3741000</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="K4" t="b">
         <v>0</v>
@@ -972,7 +972,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1000</v>
+        <v>3741000</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -981,61 +981,61 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>250.5</v>
+        <v>1285</v>
       </c>
       <c r="Q4" t="n">
-        <v>250.5</v>
+        <v>1285</v>
       </c>
       <c r="R4" t="n">
-        <v>21689405</v>
+        <v>9367345</v>
       </c>
       <c r="S4" t="n">
-        <v>227.6</v>
+        <v>1222</v>
       </c>
       <c r="T4" t="n">
-        <v>204.5</v>
+        <v>1095.2</v>
       </c>
       <c r="U4" t="n">
-        <v>201.725</v>
+        <v>1084.7</v>
       </c>
       <c r="V4" t="n">
-        <v>183.0583333333333</v>
+        <v>1020.366666666667</v>
       </c>
       <c r="W4" t="n">
-        <v>11.7902171266328</v>
+        <v>55.02725394546769</v>
       </c>
       <c r="X4" t="n">
-        <v>7.683730923238082</v>
+        <v>31.15292878370841</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.106486203394715</v>
+        <v>23.87432516175928</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.516629002774192</v>
+        <v>22.50880917369348</v>
       </c>
       <c r="AA4" t="b">
         <v>1</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.2846153846153847</v>
+        <v>0.1953488372093024</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.3878116343490305</v>
+        <v>0.2660098522167487</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.2322110521576497</v>
+        <v>0.1504473806245359</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.29028406947723</v>
+        <v>0.1855749800959667</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.05807301731958026</v>
+        <v>-0.03512759947143085</v>
       </c>
       <c r="AG4" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="AH4" t="n">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="AI4" t="b">
         <v>1</v>
@@ -1069,17 +1069,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>81.40000000000001</v>
+        <v>74.80000000000001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1097,24 +1097,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>121000</v>
+        <v>6264000</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="K5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="b">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>121000</v>
+        <v>6264000</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -1123,61 +1123,61 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1535</v>
+        <v>2070</v>
       </c>
       <c r="Q5" t="n">
-        <v>1535</v>
+        <v>2070</v>
       </c>
       <c r="R5" t="n">
-        <v>2289037</v>
+        <v>4215519</v>
       </c>
       <c r="S5" t="n">
-        <v>1438</v>
+        <v>2035</v>
       </c>
       <c r="T5" t="n">
-        <v>1301.25</v>
+        <v>1913.75</v>
       </c>
       <c r="U5" t="n">
-        <v>1293</v>
+        <v>1908</v>
       </c>
       <c r="V5" t="n">
-        <v>1198.477523803711</v>
+        <v>2079.181504313151</v>
       </c>
       <c r="W5" t="n">
-        <v>64.86865454841268</v>
+        <v>26.49924756545602</v>
       </c>
       <c r="X5" t="n">
-        <v>24.89709443374188</v>
+        <v>-10.61130674659506</v>
       </c>
       <c r="Y5" t="n">
-        <v>39.9715601146708</v>
+        <v>37.11055431205108</v>
       </c>
       <c r="Z5" t="n">
-        <v>38.00198495929377</v>
+        <v>36.87384118988113</v>
       </c>
       <c r="AA5" t="b">
         <v>1</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.1204379562043796</v>
+        <v>0.05882352941176472</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.5019438512513352</v>
+        <v>-0.08491876024900014</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.06803362374664457</v>
+        <v>0.0139220728269982</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.4044162863795346</v>
+        <v>-0.1653536323697821</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.3363826626328901</v>
+        <v>0.1792757051967803</v>
       </c>
       <c r="AG5" t="n">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="AH5" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="AI5" t="b">
         <v>1</v>
@@ -1211,17 +1211,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>6271</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>80.59999999999999</v>
+        <v>71.80000000000001</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1239,24 +1239,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>23519000</v>
+        <v>2185000</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="K6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="b">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>23519000</v>
+        <v>2185000</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1265,61 +1265,61 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>647</v>
+        <v>245.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>647</v>
+        <v>245.5</v>
       </c>
       <c r="R6" t="n">
-        <v>89742092</v>
+        <v>3521276</v>
       </c>
       <c r="S6" t="n">
-        <v>625.2</v>
+        <v>239.7</v>
       </c>
       <c r="T6" t="n">
-        <v>572.4</v>
+        <v>229.75</v>
       </c>
       <c r="U6" t="n">
-        <v>569.5</v>
+        <v>228.625</v>
       </c>
       <c r="V6" t="n">
-        <v>589.175</v>
+        <v>208.6583333333333</v>
       </c>
       <c r="W6" t="n">
-        <v>20.15970441375543</v>
+        <v>5.380381729851706</v>
       </c>
       <c r="X6" t="n">
-        <v>8.99669330121883</v>
+        <v>4.247638080892163</v>
       </c>
       <c r="Y6" t="n">
-        <v>11.1630111125366</v>
+        <v>1.132743648959543</v>
       </c>
       <c r="Z6" t="n">
-        <v>10.34179395521516</v>
+        <v>0.7596951864816601</v>
       </c>
       <c r="AA6" t="b">
         <v>1</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.09847198641765709</v>
+        <v>0.100896860986547</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.2071078431372549</v>
+        <v>0.08869179600886912</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.04606765395992207</v>
+        <v>0.05599540440178052</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.3046354080090555</v>
+        <v>0.008256923888087186</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.3507030619689776</v>
+        <v>0.04773848051369334</v>
       </c>
       <c r="AG6" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="AH6" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="AI6" t="b">
         <v>1</v>
@@ -1353,17 +1353,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1372,7 +1372,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>76.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="K7" t="b">
         <v>0</v>
@@ -1407,61 +1407,61 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>595</v>
+        <v>4345</v>
       </c>
       <c r="Q7" t="n">
-        <v>595</v>
+        <v>4345</v>
       </c>
       <c r="R7" t="n">
-        <v>34170442</v>
+        <v>4365838</v>
       </c>
       <c r="S7" t="n">
-        <v>563.2</v>
+        <v>4095</v>
       </c>
       <c r="T7" t="n">
-        <v>506.75</v>
+        <v>3765.5</v>
       </c>
       <c r="U7" t="n">
-        <v>502.05</v>
+        <v>3749.75</v>
       </c>
       <c r="V7" t="n">
-        <v>490.2166666666666</v>
+        <v>3715.481892903646</v>
       </c>
       <c r="W7" t="n">
-        <v>25.8563838612082</v>
+        <v>128.5875693574299</v>
       </c>
       <c r="X7" t="n">
-        <v>12.68846526699461</v>
+        <v>37.42860111459054</v>
       </c>
       <c r="Y7" t="n">
-        <v>13.16791859421359</v>
+        <v>91.15896824283931</v>
       </c>
       <c r="Z7" t="n">
-        <v>12.15808490916282</v>
+        <v>79.41225003074777</v>
       </c>
       <c r="AA7" t="b">
         <v>1</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.1876247504990021</v>
+        <v>0.07816377171215882</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.07894736842105265</v>
+        <v>0.1755599840679241</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.1352204180412671</v>
+        <v>0.03326231512739231</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.1764749332928532</v>
+        <v>0.09512511194714213</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.3116953513341203</v>
+        <v>-0.06186279681974982</v>
       </c>
       <c r="AG7" t="n">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="AH7" t="n">
-        <v>20</v>
+        <v>56.00000000000001</v>
       </c>
       <c r="AI7" t="b">
         <v>1</v>
@@ -1495,17 +1495,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1514,7 +1514,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>75.2</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1523,15 +1523,15 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1000</v>
+        <v>3921000</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="K8" t="b">
         <v>0</v>
@@ -1540,7 +1540,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1000</v>
+        <v>3921000</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1549,61 +1549,61 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2400</v>
+        <v>87.90000152587891</v>
       </c>
       <c r="Q8" t="n">
-        <v>2400</v>
+        <v>87.90000152587891</v>
       </c>
       <c r="R8" t="n">
-        <v>4933589</v>
+        <v>1839492</v>
       </c>
       <c r="S8" t="n">
-        <v>2269</v>
+        <v>86.56000061035157</v>
       </c>
       <c r="T8" t="n">
-        <v>2236.25</v>
+        <v>83.76500015258789</v>
       </c>
       <c r="U8" t="n">
-        <v>2227.75</v>
+        <v>83.45499992370605</v>
       </c>
       <c r="V8" t="n">
-        <v>2105.75</v>
+        <v>84.62833340962727</v>
       </c>
       <c r="W8" t="n">
-        <v>43.68560024920316</v>
+        <v>1.180500657494377</v>
       </c>
       <c r="X8" t="n">
-        <v>30.14361319008349</v>
+        <v>0.5715802605307824</v>
       </c>
       <c r="Y8" t="n">
-        <v>13.54198705911967</v>
+        <v>0.6089203969635951</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.89094038211692</v>
+        <v>0.5916726558987484</v>
       </c>
       <c r="AA8" t="b">
         <v>1</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.07623318385650224</v>
+        <v>0.07588745176532252</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.2972972972972974</v>
+        <v>-0.08627854143102387</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.02382885139876723</v>
+        <v>0.030985995180556</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.1997697324254968</v>
+        <v>-0.1667134135518058</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.1759408810267296</v>
+        <v>0.1976994087323618</v>
       </c>
       <c r="AG8" t="n">
-        <v>57.99999999999999</v>
+        <v>50</v>
       </c>
       <c r="AH8" t="n">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="AI8" t="b">
         <v>1</v>
@@ -1637,17 +1637,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>美律</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>74.8</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1665,15 +1665,15 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>4650000</v>
+        <v>1000</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="K9" t="b">
         <v>0</v>
@@ -1682,7 +1682,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>4650000</v>
+        <v>1000</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1691,61 +1691,61 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>5950</v>
+        <v>80.59999847412109</v>
       </c>
       <c r="Q9" t="n">
-        <v>5950</v>
+        <v>80.59999847412109</v>
       </c>
       <c r="R9" t="n">
-        <v>2600543</v>
+        <v>4195712</v>
       </c>
       <c r="S9" t="n">
-        <v>5561</v>
+        <v>77.09999847412109</v>
       </c>
       <c r="T9" t="n">
-        <v>5203.5</v>
+        <v>77.41499938964844</v>
       </c>
       <c r="U9" t="n">
-        <v>5180.75</v>
+        <v>77.18999938964843</v>
       </c>
       <c r="V9" t="n">
-        <v>5241.730314127604</v>
+        <v>77.72045682271322</v>
       </c>
       <c r="W9" t="n">
-        <v>156.7309623660094</v>
+        <v>0.1898344106328409</v>
       </c>
       <c r="X9" t="n">
-        <v>-5.801200582856609</v>
+        <v>-0.1164382004989899</v>
       </c>
       <c r="Y9" t="n">
-        <v>162.532162948866</v>
+        <v>0.3062726111318308</v>
       </c>
       <c r="Z9" t="n">
-        <v>148.7611979392224</v>
+        <v>-0.05456562237789048</v>
       </c>
       <c r="AA9" t="b">
         <v>1</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.08280254777070062</v>
+        <v>0.05913272129079328</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.1662768581005256</v>
+        <v>-0.01372645471432254</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.0303982153129656</v>
+        <v>0.01423126470602676</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.06874929322872503</v>
+        <v>-0.09416132683510448</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.03835107791575942</v>
+        <v>0.1083925915411312</v>
       </c>
       <c r="AG9" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AH9" t="n">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="AI9" t="b">
         <v>1</v>
@@ -1779,17 +1779,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1798,7 +1798,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>71.40000000000001</v>
+        <v>64</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="K10" t="b">
         <v>0</v>
@@ -1833,61 +1833,61 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>6845</v>
+        <v>532</v>
       </c>
       <c r="Q10" t="n">
-        <v>6845</v>
+        <v>532</v>
       </c>
       <c r="R10" t="n">
-        <v>1981431</v>
+        <v>62652164</v>
       </c>
       <c r="S10" t="n">
-        <v>6585</v>
+        <v>525.4</v>
       </c>
       <c r="T10" t="n">
-        <v>6380.25</v>
+        <v>508.85</v>
       </c>
       <c r="U10" t="n">
-        <v>6371</v>
+        <v>508.8</v>
       </c>
       <c r="V10" t="n">
-        <v>5500.556530761719</v>
+        <v>481.4833333333333</v>
       </c>
       <c r="W10" t="n">
-        <v>106.4539849318699</v>
+        <v>6.012612400293733</v>
       </c>
       <c r="X10" t="n">
-        <v>28.34434373217844</v>
+        <v>4.377897653998013</v>
       </c>
       <c r="Y10" t="n">
-        <v>78.10964119969141</v>
+        <v>1.63471474629572</v>
       </c>
       <c r="Z10" t="n">
-        <v>60.74988173768728</v>
+        <v>1.044726856239138</v>
       </c>
       <c r="AA10" t="b">
         <v>1</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.02777777777777768</v>
+        <v>0.001883239171374784</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.589763322071164</v>
+        <v>0.1875</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0.02462655467995734</v>
+        <v>-0.04301821741339173</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.4922357571993634</v>
+        <v>0.1070651278792181</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.5168623118793207</v>
+        <v>-0.1500833452926098</v>
       </c>
       <c r="AG10" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AH10" t="n">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="AI10" t="b">
         <v>1</v>
@@ -1921,26 +1921,26 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1949,15 +1949,15 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2185000</v>
+        <v>1000</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="K11" t="b">
         <v>0</v>
@@ -1966,7 +1966,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2185000</v>
+        <v>1000</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1975,61 +1975,61 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>241.5</v>
+        <v>256</v>
       </c>
       <c r="Q11" t="n">
-        <v>241.5</v>
+        <v>256</v>
       </c>
       <c r="R11" t="n">
-        <v>4038002</v>
+        <v>15828004</v>
       </c>
       <c r="S11" t="n">
-        <v>236.7</v>
+        <v>247.7</v>
       </c>
       <c r="T11" t="n">
-        <v>228.625</v>
+        <v>245.775</v>
       </c>
       <c r="U11" t="n">
-        <v>228.175</v>
+        <v>244.225</v>
       </c>
       <c r="V11" t="n">
-        <v>208.325</v>
+        <v>223.3083333333333</v>
       </c>
       <c r="W11" t="n">
-        <v>4.724387634491222</v>
+        <v>3.207807590599231</v>
       </c>
       <c r="X11" t="n">
-        <v>3.964920780266922</v>
+        <v>4.120821403604955</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.7594668542243004</v>
+        <v>-0.9130138130057244</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.4743049943418542</v>
+        <v>-1.878619802900569</v>
       </c>
       <c r="AA11" t="b">
         <v>1</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.03870967741935494</v>
+        <v>0.1377777777777778</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.02330508474576276</v>
+        <v>0.1770114942528735</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0.01369465503838008</v>
+        <v>0.09287632119301126</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.07422248012603783</v>
+        <v>0.09657662213209162</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.06052782508765775</v>
+        <v>-0.003700300939080359</v>
       </c>
       <c r="AG11" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="AH11" t="n">
-        <v>34</v>
+        <v>57.99999999999999</v>
       </c>
       <c r="AI11" t="b">
         <v>1</v>
@@ -2038,21 +2038,19 @@
         <v>1</v>
       </c>
       <c r="AK11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="b">
         <v>1</v>
       </c>
       <c r="AN11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>266.75</v>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
@@ -2063,26 +2061,26 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>67.2</v>
+        <v>45.2</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2091,15 +2089,15 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>3921000</v>
+        <v>4143450</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K12" t="b">
         <v>0</v>
@@ -2108,7 +2106,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3921000</v>
+        <v>4143450</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -2117,61 +2115,61 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>87.5</v>
+        <v>304.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>87.5</v>
+        <v>304.5</v>
       </c>
       <c r="R12" t="n">
-        <v>2072684</v>
+        <v>50698074</v>
       </c>
       <c r="S12" t="n">
-        <v>85.84000091552734</v>
+        <v>298.3</v>
       </c>
       <c r="T12" t="n">
-        <v>83.45499992370605</v>
+        <v>287.55</v>
       </c>
       <c r="U12" t="n">
-        <v>83.22000007629394</v>
+        <v>285.75</v>
       </c>
       <c r="V12" t="n">
-        <v>84.76666666666667</v>
+        <v>264.188899230957</v>
       </c>
       <c r="W12" t="n">
-        <v>1.011003475315903</v>
+        <v>6.829051716343827</v>
       </c>
       <c r="X12" t="n">
-        <v>0.4193096304374752</v>
+        <v>7.862826617558136</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.5916938448784275</v>
+        <v>-1.03377490121431</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.5226552902563752</v>
+        <v>-1.455182243346336</v>
       </c>
       <c r="AA12" t="b">
         <v>1</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.05676324607505445</v>
+        <v>0.1340782122905029</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0.1379310344827587</v>
+        <v>0.1010153697475495</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.004358913617319438</v>
+        <v>0.08917675570573635</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.2354585993545593</v>
+        <v>0.02058049762676761</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.2398175129718787</v>
+        <v>0.06859625807896874</v>
       </c>
       <c r="AG12" t="n">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="AH12" t="n">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="AI12" t="b">
         <v>1</v>
@@ -2180,21 +2178,19 @@
         <v>1</v>
       </c>
       <c r="AK12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="b">
         <v>1</v>
       </c>
       <c r="AN12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>316.68</v>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
@@ -2205,26 +2201,26 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>66.60000000000001</v>
+        <v>31.8</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2233,15 +2229,15 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1000</v>
+        <v>4315561</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="K13" t="b">
         <v>0</v>
@@ -2250,7 +2246,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1000</v>
+        <v>4315561</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -2259,67 +2255,67 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>4190</v>
+        <v>2240</v>
       </c>
       <c r="Q13" t="n">
-        <v>4190</v>
+        <v>2240</v>
       </c>
       <c r="R13" t="n">
-        <v>3223803</v>
+        <v>2004552</v>
       </c>
       <c r="S13" t="n">
-        <v>3979</v>
+        <v>2201</v>
       </c>
       <c r="T13" t="n">
-        <v>3749.75</v>
+        <v>2189.75</v>
       </c>
       <c r="U13" t="n">
-        <v>3742.25</v>
+        <v>2194.75</v>
       </c>
       <c r="V13" t="n">
-        <v>3704.667073567708</v>
+        <v>2107.122220865886</v>
       </c>
       <c r="W13" t="n">
-        <v>94.05681158988773</v>
+        <v>-0.1643745962546745</v>
       </c>
       <c r="X13" t="n">
-        <v>14.65019118704354</v>
+        <v>-23.48913080485683</v>
       </c>
       <c r="Y13" t="n">
-        <v>79.4066204028442</v>
+        <v>23.32475620860216</v>
       </c>
       <c r="Z13" t="n">
-        <v>70.85621125918823</v>
+        <v>21.63347848140634</v>
       </c>
       <c r="AA13" t="b">
         <v>1</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.03712871287128716</v>
+        <v>-0.04273504273504269</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.02122113299573969</v>
+        <v>0.3621732737721026</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0.01527561958644785</v>
+        <v>-0.08763649931980921</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0.0763064318760609</v>
+        <v>0.2817384016513207</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.06103081228961305</v>
+        <v>-0.3693749009711299</v>
       </c>
       <c r="AG13" t="n">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="AH13" t="n">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="AI13" t="b">
         <v>1</v>
       </c>
       <c r="AJ13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="b">
         <v>1</v>
@@ -2338,35 +2334,33 @@
           <t>Already &gt; 0</t>
         </is>
       </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+      <c r="AP13" t="n">
+        <v>2272.11</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>60.8</v>
+        <v>29</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2375,15 +2369,15 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2499000</v>
+        <v>420000</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K14" t="b">
         <v>0</v>
@@ -2392,7 +2386,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2499000</v>
+        <v>420000</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2401,105 +2395,101 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>5530</v>
+        <v>3320</v>
       </c>
       <c r="Q14" t="n">
-        <v>5530</v>
+        <v>3320</v>
       </c>
       <c r="R14" t="n">
-        <v>791694</v>
+        <v>1335112</v>
       </c>
       <c r="S14" t="n">
-        <v>5412</v>
+        <v>3114</v>
       </c>
       <c r="T14" t="n">
-        <v>5491.5</v>
+        <v>3304.25</v>
       </c>
       <c r="U14" t="n">
-        <v>5489.5</v>
+        <v>3319.25</v>
       </c>
       <c r="V14" t="n">
-        <v>5617.833333333333</v>
+        <v>2966.666666666667</v>
       </c>
       <c r="W14" t="n">
-        <v>1.900310329757303</v>
+        <v>-37.47822864447608</v>
       </c>
       <c r="X14" t="n">
-        <v>-32.68706408651053</v>
+        <v>-16.91659066177584</v>
       </c>
       <c r="Y14" t="n">
-        <v>34.58737441626783</v>
+        <v>-20.56163798270023</v>
       </c>
       <c r="Z14" t="n">
-        <v>29.57126454571861</v>
+        <v>-55.36148206138292</v>
       </c>
       <c r="AA14" t="b">
         <v>1</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.007285974499089187</v>
+        <v>-0.08287292817679559</v>
       </c>
       <c r="AC14" t="n">
-        <v>-0.1671686746987951</v>
+        <v>0.2296296296296296</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0.04511835795864583</v>
+        <v>-0.1277743847615621</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0.2646962395705957</v>
+        <v>0.1491947575088477</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.2195778816119499</v>
+        <v>-0.2769691422704098</v>
       </c>
       <c r="AG14" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="AH14" t="n">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="AI14" t="b">
         <v>1</v>
       </c>
       <c r="AJ14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="b">
         <v>1</v>
       </c>
       <c r="AN14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
-      <c r="AP14" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>3552.4</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>3593.42</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2508,7 +2498,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>48.40000000000001</v>
+        <v>25.6</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2517,15 +2507,15 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>692000</v>
+        <v>2504000</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="K15" t="b">
         <v>0</v>
@@ -2534,7 +2524,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>692000</v>
+        <v>2504000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2543,202 +2533,202 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2455</v>
+        <v>5575</v>
       </c>
       <c r="Q15" t="n">
-        <v>2455</v>
+        <v>5575</v>
       </c>
       <c r="R15" t="n">
-        <v>883462</v>
+        <v>471574</v>
       </c>
       <c r="S15" t="n">
-        <v>2404</v>
+        <v>5521</v>
       </c>
       <c r="T15" t="n">
-        <v>2322.25</v>
+        <v>5480.5</v>
       </c>
       <c r="U15" t="n">
-        <v>2312.75</v>
+        <v>5491.5</v>
       </c>
       <c r="V15" t="n">
-        <v>1917.735548909505</v>
+        <v>5605.083333333333</v>
       </c>
       <c r="W15" t="n">
-        <v>63.24377370360526</v>
+        <v>16.33612059439474</v>
       </c>
       <c r="X15" t="n">
-        <v>79.8756592700947</v>
+        <v>-22.81682223276735</v>
       </c>
       <c r="Y15" t="n">
-        <v>-16.63188556648944</v>
+        <v>39.15294282716209</v>
       </c>
       <c r="Z15" t="n">
-        <v>-18.74540796756919</v>
+        <v>34.54669746988481</v>
       </c>
       <c r="AA15" t="b">
         <v>1</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.08388520971302427</v>
+        <v>-0.03796376186367556</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.7533104683167013</v>
+        <v>-0.1206624605678234</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.03148087725528925</v>
+        <v>-0.08286521844844208</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.6557829034449008</v>
+        <v>-0.2010973326886053</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.6243020261896115</v>
+        <v>0.1182321142401632</v>
       </c>
       <c r="AG15" t="n">
-        <v>62</v>
+        <v>16</v>
       </c>
       <c r="AH15" t="n">
-        <v>96</v>
+        <v>12</v>
       </c>
       <c r="AI15" t="b">
         <v>1</v>
       </c>
       <c r="AJ15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM15" t="b">
         <v>1</v>
       </c>
       <c r="AN15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>2646.49</v>
-      </c>
-      <c r="AP15" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
+      </c>
+      <c r="AP15" t="n">
+        <v>5515.53</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>46.4</v>
+        <v>62</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1000</v>
+        <v>6847000</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="K16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="b">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1000</v>
+        <v>6771000</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>76000</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>0.01122433909319155</v>
       </c>
       <c r="P16" t="n">
-        <v>250</v>
+        <v>1740</v>
       </c>
       <c r="Q16" t="n">
-        <v>250</v>
+        <v>1740</v>
       </c>
       <c r="R16" t="n">
-        <v>13755036</v>
+        <v>7551964</v>
       </c>
       <c r="S16" t="n">
-        <v>245.6</v>
+        <v>1723</v>
       </c>
       <c r="T16" t="n">
-        <v>244.225</v>
+        <v>1498.75</v>
       </c>
       <c r="U16" t="n">
-        <v>243.075</v>
+        <v>1479</v>
       </c>
       <c r="V16" t="n">
-        <v>222.6666666666667</v>
+        <v>1424.666666666667</v>
       </c>
       <c r="W16" t="n">
-        <v>2.47012780052529</v>
+        <v>86.18626585246943</v>
       </c>
       <c r="X16" t="n">
-        <v>4.348420685847332</v>
+        <v>53.95313981159023</v>
       </c>
       <c r="Y16" t="n">
-        <v>-1.878292885322042</v>
+        <v>32.2331260408792</v>
       </c>
       <c r="Z16" t="n">
-        <v>-2.538379616273509</v>
+        <v>37.89438774615367</v>
       </c>
       <c r="AA16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.1013215859030836</v>
+        <v>0.2936802973977695</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.1111111111111112</v>
+        <v>0.2473118279569892</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.04891725344534859</v>
+        <v>0.2487788408130029</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.01358354623931057</v>
+        <v>0.1668769558362073</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.03533370720603801</v>
+        <v>0.08190188497679562</v>
       </c>
       <c r="AG16" t="n">
+        <v>88</v>
+      </c>
+      <c r="AH16" t="n">
         <v>68</v>
       </c>
-      <c r="AH16" t="n">
-        <v>57.99999999999999</v>
-      </c>
       <c r="AI16" t="b">
         <v>1</v>
       </c>
@@ -2746,19 +2736,21 @@
         <v>1</v>
       </c>
       <c r="AK16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>271.5</v>
+        <v>0</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
@@ -2769,43 +2761,43 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>43.2</v>
+        <v>55.8</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Heavy Sell</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>8456450</v>
+        <v>18721000</v>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K17" t="b">
         <v>1</v>
@@ -2814,70 +2806,70 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>12938450</v>
+        <v>18721000</v>
       </c>
       <c r="N17" t="n">
-        <v>-4482000</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3464093457871693</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>299.5</v>
+        <v>1270</v>
       </c>
       <c r="Q17" t="n">
-        <v>299.5</v>
+        <v>1270</v>
       </c>
       <c r="R17" t="n">
-        <v>23101918</v>
+        <v>8192303</v>
       </c>
       <c r="S17" t="n">
-        <v>296.6</v>
+        <v>1303</v>
       </c>
       <c r="T17" t="n">
-        <v>285.75</v>
+        <v>1116.1</v>
       </c>
       <c r="U17" t="n">
-        <v>284.425</v>
+        <v>1100.3</v>
       </c>
       <c r="V17" t="n">
-        <v>263.723280843099</v>
+        <v>1009.25</v>
       </c>
       <c r="W17" t="n">
-        <v>6.666954808718629</v>
+        <v>72.79097685392844</v>
       </c>
       <c r="X17" t="n">
-        <v>8.122982068956325</v>
+        <v>59.82847066588712</v>
       </c>
       <c r="Y17" t="n">
-        <v>-1.456027260237697</v>
+        <v>12.96250618804132</v>
       </c>
       <c r="Z17" t="n">
-        <v>-1.490144208775439</v>
+        <v>22.36776821978445</v>
       </c>
       <c r="AA17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.09706959706959717</v>
+        <v>0.3312368972746331</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.02826034956394352</v>
+        <v>0.4530892448512587</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.04466526461186215</v>
+        <v>0.2863354406898666</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0.06926721530785707</v>
+        <v>0.3726543727304767</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.1139324799197192</v>
+        <v>-0.08631893204061014</v>
       </c>
       <c r="AG17" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="AH17" t="n">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="AI17" t="b">
         <v>1</v>
@@ -2886,19 +2878,21 @@
         <v>1</v>
       </c>
       <c r="AK17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>316.27</v>
+        <v>0</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
@@ -2909,26 +2903,26 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>35.40000000000001</v>
+        <v>54.4</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2937,24 +2931,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1000</v>
+        <v>8937000</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="K18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="b">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1000</v>
+        <v>8937000</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2963,199 +2957,203 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>579</v>
+        <v>1475</v>
       </c>
       <c r="Q18" t="n">
-        <v>579</v>
+        <v>1475</v>
       </c>
       <c r="R18" t="n">
-        <v>11894276</v>
+        <v>5186570</v>
       </c>
       <c r="S18" t="n">
-        <v>577.4</v>
+        <v>1483</v>
       </c>
       <c r="T18" t="n">
-        <v>574.3</v>
+        <v>1239.5</v>
       </c>
       <c r="U18" t="n">
-        <v>574.85</v>
+        <v>1217</v>
       </c>
       <c r="V18" t="n">
-        <v>521.5833333333334</v>
+        <v>1174.833333333333</v>
       </c>
       <c r="W18" t="n">
-        <v>1.243445611091488</v>
+        <v>94.89482404399837</v>
       </c>
       <c r="X18" t="n">
-        <v>1.912299346223011</v>
+        <v>69.19340418182574</v>
       </c>
       <c r="Y18" t="n">
-        <v>-0.6688537351315231</v>
+        <v>25.70141986217263</v>
       </c>
       <c r="Z18" t="n">
-        <v>-0.9015346469142496</v>
+        <v>35.0406669860459</v>
       </c>
       <c r="AA18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>-0.01864406779661021</v>
+        <v>0.4390243902439024</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.3890000103226894</v>
+        <v>0.1434108527131783</v>
       </c>
       <c r="AD18" t="n">
-        <v>-0.07104840025434522</v>
+        <v>0.3941229336591359</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.2914724454508888</v>
+        <v>0.0629759805923964</v>
       </c>
       <c r="AF18" t="n">
-        <v>-0.362520845705234</v>
+        <v>0.3311469530667395</v>
       </c>
       <c r="AG18" t="n">
-        <v>22</v>
+        <v>100</v>
       </c>
       <c r="AH18" t="n">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="AI18" t="b">
         <v>1</v>
       </c>
       <c r="AJ18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>587.11</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>600.05</v>
+        <v>0</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>美律</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>33.8</v>
+        <v>51.2</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1000</v>
+        <v>6147000</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="K19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="b">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1000</v>
+        <v>6062000</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>85000</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>0.0140217749917519</v>
       </c>
       <c r="P19" t="n">
-        <v>78.69999694824219</v>
+        <v>3440</v>
       </c>
       <c r="Q19" t="n">
-        <v>78.69999694824219</v>
+        <v>3440</v>
       </c>
       <c r="R19" t="n">
-        <v>4104839</v>
+        <v>2974272</v>
       </c>
       <c r="S19" t="n">
-        <v>76.27999877929688</v>
+        <v>3539</v>
       </c>
       <c r="T19" t="n">
-        <v>77.18999938964843</v>
+        <v>3414.75</v>
       </c>
       <c r="U19" t="n">
-        <v>77.09999961853028</v>
+        <v>3407</v>
       </c>
       <c r="V19" t="n">
-        <v>77.73915265401205</v>
+        <v>3003.297257486979</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.2474554537641609</v>
+        <v>59.45425389528509</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1927753245644698</v>
+        <v>66.5320690986633</v>
       </c>
       <c r="Y19" t="n">
-        <v>-0.05468012919969112</v>
+        <v>-7.077815203378208</v>
       </c>
       <c r="Z19" t="n">
-        <v>-0.3868134546686172</v>
+        <v>8.969634177185867</v>
       </c>
       <c r="AA19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.02340696211504678</v>
+        <v>0.04718417047184165</v>
       </c>
       <c r="AC19" t="n">
-        <v>-0.04804537843121781</v>
+        <v>0.632267608554373</v>
       </c>
       <c r="AD19" t="n">
-        <v>-0.02899737034268823</v>
+        <v>0.002282713887075127</v>
       </c>
       <c r="AE19" t="n">
-        <v>-0.1455729433030184</v>
+        <v>0.5518327364335911</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.1165755729603302</v>
+        <v>-0.549550022546516</v>
       </c>
       <c r="AG19" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AH19" t="n">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="AI19" t="b">
         <v>1</v>
@@ -3170,13 +3168,13 @@
         <v>0</v>
       </c>
       <c r="AM19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="b">
         <v>1</v>
       </c>
       <c r="AO19" t="n">
-        <v>79.33</v>
+        <v>3522.56</v>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
@@ -3187,26 +3185,26 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>31.40000000000001</v>
+        <v>48.6</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3215,24 +3213,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>4315561</v>
+        <v>8348000</v>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="K20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="b">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>4315561</v>
+        <v>8348000</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -3241,67 +3239,67 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2240</v>
+        <v>744</v>
       </c>
       <c r="Q20" t="n">
-        <v>2240</v>
+        <v>744</v>
       </c>
       <c r="R20" t="n">
-        <v>2575934</v>
+        <v>15126846</v>
       </c>
       <c r="S20" t="n">
-        <v>2175</v>
+        <v>735</v>
       </c>
       <c r="T20" t="n">
-        <v>2194.75</v>
+        <v>674.6</v>
       </c>
       <c r="U20" t="n">
-        <v>2207.25</v>
+        <v>668.3</v>
       </c>
       <c r="V20" t="n">
-        <v>2097.196071370442</v>
+        <v>626.8166666666667</v>
       </c>
       <c r="W20" t="n">
-        <v>-7.689649358091174</v>
+        <v>28.72195570530857</v>
       </c>
       <c r="X20" t="n">
-        <v>-29.32590107772711</v>
+        <v>24.9195795682236</v>
       </c>
       <c r="Y20" t="n">
-        <v>21.63625171963593</v>
+        <v>3.80237613708497</v>
       </c>
       <c r="Z20" t="n">
-        <v>16.43878294104545</v>
+        <v>4.818665858427057</v>
       </c>
       <c r="AA20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>-0.1004016064257028</v>
+        <v>0.203883495145631</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.3470685273896377</v>
+        <v>0.1606864274570983</v>
       </c>
       <c r="AD20" t="n">
-        <v>-0.1528059388834379</v>
+        <v>0.1589820385608645</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.2495409625178371</v>
+        <v>0.08025155533631634</v>
       </c>
       <c r="AF20" t="n">
-        <v>-0.4023469014012749</v>
+        <v>0.07873048322454812</v>
       </c>
       <c r="AG20" t="n">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="AH20" t="n">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="AI20" t="b">
         <v>1</v>
       </c>
       <c r="AJ20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK20" t="b">
         <v>1</v>
@@ -3310,7 +3308,7 @@
         <v>1</v>
       </c>
       <c r="AM20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="b">
         <v>0</v>
@@ -3320,14 +3318,16 @@
           <t>Already &gt; 0</t>
         </is>
       </c>
-      <c r="AP20" t="n">
-        <v>2292.37</v>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3346,16 +3346,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>59</v>
+        <v>48.2</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K21" t="b">
         <v>0</v>
@@ -3372,67 +3372,67 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>616000</v>
+        <v>684000</v>
       </c>
       <c r="N21" t="n">
-        <v>68000</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1103896103896104</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>8460</v>
+        <v>8360</v>
       </c>
       <c r="Q21" t="n">
-        <v>8460</v>
+        <v>8360</v>
       </c>
       <c r="R21" t="n">
-        <v>1501082</v>
+        <v>1159259</v>
       </c>
       <c r="S21" t="n">
-        <v>8247</v>
+        <v>8339</v>
       </c>
       <c r="T21" t="n">
+        <v>7449.25</v>
+      </c>
+      <c r="U21" t="n">
         <v>7329.25</v>
       </c>
-      <c r="U21" t="n">
-        <v>7203</v>
-      </c>
       <c r="V21" t="n">
-        <v>5691.666666666667</v>
+        <v>5764</v>
       </c>
       <c r="W21" t="n">
-        <v>507.7828046929435</v>
+        <v>473.5036091335342</v>
       </c>
       <c r="X21" t="n">
-        <v>517.3766209237938</v>
+        <v>508.557983686262</v>
       </c>
       <c r="Y21" t="n">
-        <v>-9.59381623085028</v>
+        <v>-35.05437455272789</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.347893204063894</v>
+        <v>-9.566549806802186</v>
       </c>
       <c r="AA21" t="b">
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.4254422914911542</v>
+        <v>0.4026845637583893</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.9812646370023419</v>
+        <v>1.079601990049751</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.3730379590334192</v>
+        <v>0.3577831071736228</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.8837370721305413</v>
+        <v>0.9991671179289694</v>
       </c>
       <c r="AF21" t="n">
-        <v>-0.5106991130971221</v>
+        <v>-0.6413840107553466</v>
       </c>
       <c r="AG21" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="AH21" t="n">
         <v>98</v>
@@ -3456,7 +3456,7 @@
         <v>1</v>
       </c>
       <c r="AO21" t="n">
-        <v>8578.440000000001</v>
+        <v>8761.280000000001</v>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
@@ -3467,17 +3467,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>56</v>
+        <v>45.6</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3495,24 +3495,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>8937000</v>
+        <v>1000</v>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="K22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" t="b">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>8937000</v>
+        <v>1000</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -3521,61 +3521,61 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1480</v>
+        <v>128</v>
       </c>
       <c r="Q22" t="n">
-        <v>1480</v>
+        <v>128</v>
       </c>
       <c r="R22" t="n">
-        <v>8640811</v>
+        <v>36560090</v>
       </c>
       <c r="S22" t="n">
-        <v>1472</v>
+        <v>127</v>
       </c>
       <c r="T22" t="n">
-        <v>1217</v>
+        <v>105.2449996948242</v>
       </c>
       <c r="U22" t="n">
-        <v>1195.5</v>
+        <v>103.3599998474121</v>
       </c>
       <c r="V22" t="n">
-        <v>1171.75</v>
+        <v>95.69833323160807</v>
       </c>
       <c r="W22" t="n">
-        <v>97.79562940436176</v>
+        <v>9.055134634424562</v>
       </c>
       <c r="X22" t="n">
-        <v>62.74206330377237</v>
+        <v>7.134456094994352</v>
       </c>
       <c r="Y22" t="n">
-        <v>35.05356610058939</v>
+        <v>1.920678539430209</v>
       </c>
       <c r="Z22" t="n">
-        <v>43.73331955313263</v>
+        <v>2.494050303769871</v>
       </c>
       <c r="AA22" t="b">
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.4095238095238096</v>
+        <v>0.4174971835453145</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.1653543307086613</v>
+        <v>0.2307692307692308</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.3571194770660746</v>
+        <v>0.372595726960548</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.06782676583686076</v>
+        <v>0.1503343586484489</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.2892927112292139</v>
+        <v>0.2222613683120991</v>
       </c>
       <c r="AG22" t="n">
         <v>98</v>
       </c>
       <c r="AH22" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="AI22" t="b">
         <v>1</v>
@@ -3609,17 +3609,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3628,24 +3628,24 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>52.2</v>
+        <v>45.4</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>6467000</v>
+        <v>12188000</v>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K23" t="b">
         <v>1</v>
@@ -3654,70 +3654,70 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>6467000</v>
+        <v>11824000</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>364000</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>0.03078484438430311</v>
       </c>
       <c r="P23" t="n">
-        <v>1720</v>
+        <v>2550</v>
       </c>
       <c r="Q23" t="n">
-        <v>1720</v>
+        <v>2550</v>
       </c>
       <c r="R23" t="n">
-        <v>11612143</v>
+        <v>20325120</v>
       </c>
       <c r="S23" t="n">
-        <v>1682</v>
+        <v>2559</v>
       </c>
       <c r="T23" t="n">
-        <v>1479</v>
+        <v>2474.725793457031</v>
       </c>
       <c r="U23" t="n">
-        <v>1461.5</v>
+        <v>2470.363317871094</v>
       </c>
       <c r="V23" t="n">
-        <v>1418.916666666667</v>
+        <v>2408.414017740885</v>
       </c>
       <c r="W23" t="n">
-        <v>83.79524516025549</v>
+        <v>37.10945381653937</v>
       </c>
       <c r="X23" t="n">
-        <v>45.9067315457287</v>
+        <v>29.03768616698488</v>
       </c>
       <c r="Y23" t="n">
-        <v>37.88851361452679</v>
+        <v>8.071767649554491</v>
       </c>
       <c r="Z23" t="n">
-        <v>44.11608609069786</v>
+        <v>12.79821421109786</v>
       </c>
       <c r="AA23" t="b">
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.2554744525547445</v>
+        <v>0.03542767005180503</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.1096774193548387</v>
+        <v>0.05682081368767511</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.2030701200970095</v>
+        <v>-0.009473786532961492</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.01214985448303807</v>
+        <v>-0.02361405843310682</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.1909202656139715</v>
+        <v>0.01414027190014533</v>
       </c>
       <c r="AG23" t="n">
-        <v>88</v>
+        <v>40</v>
       </c>
       <c r="AH23" t="n">
-        <v>56.00000000000001</v>
+        <v>34</v>
       </c>
       <c r="AI23" t="b">
         <v>1</v>
@@ -3751,17 +3751,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3770,96 +3770,96 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>49.4</v>
+        <v>45.4</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>11824000</v>
+        <v>2502000</v>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="K24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" t="b">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>11464000</v>
+        <v>2502000</v>
       </c>
       <c r="N24" t="n">
-        <v>360000</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>0.0314026517794836</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2585</v>
+        <v>7165</v>
       </c>
       <c r="Q24" t="n">
-        <v>2585</v>
+        <v>7165</v>
       </c>
       <c r="R24" t="n">
-        <v>14466183</v>
+        <v>1552383</v>
       </c>
       <c r="S24" t="n">
-        <v>2551</v>
+        <v>7011</v>
       </c>
       <c r="T24" t="n">
-        <v>2470.363317871094</v>
+        <v>6257</v>
       </c>
       <c r="U24" t="n">
-        <v>2463.752319335938</v>
+        <v>6176.25</v>
       </c>
       <c r="V24" t="n">
-        <v>2406.128971354167</v>
+        <v>5118.542277018229</v>
       </c>
       <c r="W24" t="n">
-        <v>39.81815303346866</v>
+        <v>355.3071810284428</v>
       </c>
       <c r="X24" t="n">
-        <v>27.02009698466608</v>
+        <v>327.1895572321868</v>
       </c>
       <c r="Y24" t="n">
-        <v>12.79805604880258</v>
+        <v>28.11762379625594</v>
       </c>
       <c r="Z24" t="n">
-        <v>12.86818276963391</v>
+        <v>32.19417750518028</v>
       </c>
       <c r="AA24" t="b">
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.05390616733822151</v>
+        <v>0.2909909909909909</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.06254478842602351</v>
+        <v>1.34836713657204</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.001501834880486497</v>
+        <v>0.2460895344062244</v>
       </c>
       <c r="AE24" t="n">
-        <v>-0.03498277644577708</v>
+        <v>1.267932264451259</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.03648461132626357</v>
+        <v>-1.021842730045034</v>
       </c>
       <c r="AG24" t="n">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="AH24" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="AI24" t="b">
         <v>1</v>
@@ -3893,17 +3893,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3912,96 +3912,96 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>48.2</v>
+        <v>41.8</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Heavy Sell</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>18721000</v>
+        <v>2887848</v>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="K25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" t="b">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>19300000</v>
+        <v>2887848</v>
       </c>
       <c r="N25" t="n">
-        <v>-579000</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1305</v>
+        <v>2360</v>
       </c>
       <c r="Q25" t="n">
-        <v>1305</v>
+        <v>2360</v>
       </c>
       <c r="R25" t="n">
-        <v>8885686</v>
+        <v>3516661</v>
       </c>
       <c r="S25" t="n">
-        <v>1292</v>
+        <v>2405</v>
       </c>
       <c r="T25" t="n">
-        <v>1100.3</v>
+        <v>2238.75</v>
       </c>
       <c r="U25" t="n">
-        <v>1082.5</v>
+        <v>2217.5</v>
       </c>
       <c r="V25" t="n">
-        <v>1002.65</v>
+        <v>2166.916666666667</v>
       </c>
       <c r="W25" t="n">
-        <v>78.9609912300657</v>
+        <v>60.47533387328531</v>
       </c>
       <c r="X25" t="n">
-        <v>56.59852047794951</v>
+        <v>76.7143271302707</v>
       </c>
       <c r="Y25" t="n">
-        <v>22.3624707521162</v>
+        <v>-16.2389932569854</v>
       </c>
       <c r="Z25" t="n">
-        <v>28.42562208760214</v>
+        <v>-9.069575089941623</v>
       </c>
       <c r="AA25" t="b">
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.3751317175974711</v>
+        <v>0.2196382428940569</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.4451827242524917</v>
+        <v>0.3412281669347996</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.3227273851397361</v>
+        <v>0.1747367863092903</v>
       </c>
       <c r="AE25" t="n">
-        <v>0.3476551593806911</v>
+        <v>0.2607932948140177</v>
       </c>
       <c r="AF25" t="n">
-        <v>-0.02492777424095505</v>
+        <v>-0.08605650850472735</v>
       </c>
       <c r="AG25" t="n">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH25" t="n">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="AI25" t="b">
         <v>1</v>
@@ -4010,21 +4010,19 @@
         <v>1</v>
       </c>
       <c r="AK25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="b">
         <v>0</v>
       </c>
       <c r="AN25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>2544.08</v>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
@@ -4035,17 +4033,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4054,7 +4052,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>45</v>
+        <v>40.2</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4063,24 +4061,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1000</v>
+        <v>7389000</v>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="K26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="b">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1000</v>
+        <v>7389000</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -4089,61 +4087,61 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>128.5</v>
+        <v>1965</v>
       </c>
       <c r="Q26" t="n">
-        <v>128.5</v>
+        <v>1965</v>
       </c>
       <c r="R26" t="n">
-        <v>34612323</v>
+        <v>4855304</v>
       </c>
       <c r="S26" t="n">
-        <v>124.5</v>
+        <v>1979</v>
       </c>
       <c r="T26" t="n">
-        <v>103.3599998474121</v>
+        <v>1831</v>
       </c>
       <c r="U26" t="n">
-        <v>101.5</v>
+        <v>1823</v>
       </c>
       <c r="V26" t="n">
-        <v>95.29833323160807</v>
+        <v>1783.916666666667</v>
       </c>
       <c r="W26" t="n">
-        <v>9.147267308533472</v>
+        <v>56.50518476774346</v>
       </c>
       <c r="X26" t="n">
-        <v>6.65216370666665</v>
+        <v>43.76389631303759</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.495103601866822</v>
+        <v>12.74128845470587</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.846472653520266</v>
+        <v>20.22750847362659</v>
       </c>
       <c r="AA26" t="b">
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.4074479266682343</v>
+        <v>0.08864265927977844</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.1173913043478261</v>
+        <v>0.059299191374663</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.3550435942104992</v>
+        <v>0.04374120269501192</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.01986373947602549</v>
+        <v>-0.02113568074611893</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.3351798547344738</v>
+        <v>0.06487688344113085</v>
       </c>
       <c r="AG26" t="n">
-        <v>96</v>
+        <v>56.00000000000001</v>
       </c>
       <c r="AH26" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AI26" t="b">
         <v>1</v>
@@ -4177,17 +4175,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4196,7 +4194,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>44.8</v>
+        <v>39.6</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4205,24 +4203,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>2502000</v>
+        <v>23519000</v>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="K27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="b">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>2502000</v>
+        <v>23519000</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -4231,61 +4229,61 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>6805</v>
+        <v>635</v>
       </c>
       <c r="Q27" t="n">
-        <v>6805</v>
+        <v>635</v>
       </c>
       <c r="R27" t="n">
-        <v>939375</v>
+        <v>45424113</v>
       </c>
       <c r="S27" t="n">
-        <v>6953</v>
+        <v>631.8</v>
       </c>
       <c r="T27" t="n">
-        <v>6176.25</v>
+        <v>575.8</v>
       </c>
       <c r="U27" t="n">
-        <v>6118.75</v>
+        <v>572.4</v>
       </c>
       <c r="V27" t="n">
-        <v>5049.976546223958</v>
+        <v>586.7916666666666</v>
       </c>
       <c r="W27" t="n">
-        <v>352.3745472627297</v>
+        <v>20.82060837135532</v>
       </c>
       <c r="X27" t="n">
-        <v>320.200354140695</v>
+        <v>11.35230141046161</v>
       </c>
       <c r="Y27" t="n">
-        <v>32.17419312203469</v>
+        <v>9.468306960893706</v>
       </c>
       <c r="Z27" t="n">
-        <v>81.22223768112298</v>
+        <v>11.16867895820584</v>
       </c>
       <c r="AA27" t="b">
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.2033598585322722</v>
+        <v>0.1199294532627866</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.143114771858178</v>
+        <v>-0.1838046272493573</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.1509555260745372</v>
+        <v>0.07502799667802007</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.045587206986378</v>
+        <v>-0.2642394993701392</v>
       </c>
       <c r="AF27" t="n">
-        <v>-0.8946316809118406</v>
+        <v>0.3392674960481593</v>
       </c>
       <c r="AG27" t="n">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="AH27" t="n">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="AI27" t="b">
         <v>1</v>
@@ -4319,17 +4317,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4338,7 +4336,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>41.2</v>
+        <v>38.8</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4347,24 +4345,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>7389000</v>
+        <v>1000</v>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="K28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" t="b">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>7389000</v>
+        <v>1000</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -4373,61 +4371,61 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1990</v>
+        <v>186.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>1990</v>
+        <v>186.5</v>
       </c>
       <c r="R28" t="n">
-        <v>9007514</v>
+        <v>10373801</v>
       </c>
       <c r="S28" t="n">
-        <v>1967</v>
+        <v>187.7</v>
       </c>
       <c r="T28" t="n">
-        <v>1823</v>
+        <v>172.75</v>
       </c>
       <c r="U28" t="n">
-        <v>1816</v>
+        <v>171.025</v>
       </c>
       <c r="V28" t="n">
-        <v>1782.083333333333</v>
+        <v>161.2666666666667</v>
       </c>
       <c r="W28" t="n">
-        <v>60.81643121862339</v>
+        <v>7.088929669332032</v>
       </c>
       <c r="X28" t="n">
-        <v>40.59914819779851</v>
+        <v>6.42704532598117</v>
       </c>
       <c r="Y28" t="n">
-        <v>20.21728302082488</v>
+        <v>0.6618843433508621</v>
       </c>
       <c r="Z28" t="n">
-        <v>25.30433552897995</v>
+        <v>1.362418315135592</v>
       </c>
       <c r="AA28" t="b">
         <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.07567567567567557</v>
+        <v>0.2269736842105263</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.05291005291005302</v>
+        <v>0.07183908045977017</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.02327134321794055</v>
+        <v>0.1820722276257598</v>
       </c>
       <c r="AE28" t="n">
-        <v>-0.04461751196174757</v>
+        <v>-0.008595791661011765</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.06788885517968812</v>
+        <v>0.1906680192867716</v>
       </c>
       <c r="AG28" t="n">
-        <v>56.00000000000001</v>
+        <v>84</v>
       </c>
       <c r="AH28" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AI28" t="b">
         <v>1</v>
@@ -4461,17 +4459,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4480,7 +4478,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>40</v>
+        <v>37.8</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4489,24 +4487,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1000</v>
+        <v>79618000</v>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="K29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" t="b">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1000</v>
+        <v>79618000</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -4515,73 +4513,73 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>190</v>
+        <v>147.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>190</v>
+        <v>147.5</v>
       </c>
       <c r="R29" t="n">
-        <v>18391889</v>
+        <v>81139424</v>
       </c>
       <c r="S29" t="n">
-        <v>187.3</v>
+        <v>151.5</v>
       </c>
       <c r="T29" t="n">
-        <v>171.025</v>
+        <v>150.45</v>
       </c>
       <c r="U29" t="n">
-        <v>169.325</v>
+        <v>149.925</v>
       </c>
       <c r="V29" t="n">
-        <v>161.0583333333333</v>
+        <v>134.3916666666667</v>
       </c>
       <c r="W29" t="n">
-        <v>7.6248419890957</v>
+        <v>1.706312721761321</v>
       </c>
       <c r="X29" t="n">
-        <v>6.263254212814348</v>
+        <v>4.183670763234528</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.361587776281351</v>
+        <v>-2.477358041473207</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.641235618325496</v>
+        <v>-2.244279537122019</v>
       </c>
       <c r="AA29" t="b">
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.2179487179487178</v>
+        <v>0.07664233576642343</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.06442577030812324</v>
+        <v>-0.02317880794701987</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.1655443854909828</v>
+        <v>0.03174087918165691</v>
       </c>
       <c r="AE29" t="n">
-        <v>-0.03310179456367734</v>
+        <v>-0.1036136800678018</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.1986461800546602</v>
+        <v>0.1353545592494587</v>
       </c>
       <c r="AG29" t="n">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="AH29" t="n">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="AI29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="b">
         <v>1</v>
       </c>
       <c r="AK29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM29" t="b">
         <v>0</v>
@@ -4589,10 +4587,8 @@
       <c r="AN29" t="b">
         <v>0</v>
       </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+      <c r="AO29" t="n">
+        <v>175.53</v>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
@@ -4603,17 +4599,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4622,96 +4618,96 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>39.4</v>
+        <v>37.2</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Heavy Sell</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>8348000</v>
+        <v>121000</v>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="K30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" t="b">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>9276000</v>
+        <v>121000</v>
       </c>
       <c r="N30" t="n">
-        <v>-928000</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>-0.1000431220353601</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>732</v>
+        <v>1525</v>
       </c>
       <c r="Q30" t="n">
-        <v>732</v>
+        <v>1525</v>
       </c>
       <c r="R30" t="n">
-        <v>7697926</v>
+        <v>2890449</v>
       </c>
       <c r="S30" t="n">
-        <v>728.2</v>
+        <v>1488</v>
       </c>
       <c r="T30" t="n">
-        <v>668.3</v>
+        <v>1308.25</v>
       </c>
       <c r="U30" t="n">
-        <v>662.75</v>
+        <v>1301.25</v>
       </c>
       <c r="V30" t="n">
-        <v>625.1</v>
+        <v>1207.683582560221</v>
       </c>
       <c r="W30" t="n">
-        <v>28.78507656333466</v>
+        <v>70.42619172063269</v>
       </c>
       <c r="X30" t="n">
-        <v>23.96386550334922</v>
+        <v>34.00287491907147</v>
       </c>
       <c r="Y30" t="n">
-        <v>4.821211059985437</v>
+        <v>36.42331680156121</v>
       </c>
       <c r="Z30" t="n">
-        <v>7.021657232439502</v>
+        <v>39.97160545982104</v>
       </c>
       <c r="AA30" t="b">
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.1787439613526569</v>
+        <v>0.1010830324909748</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.09253731343283578</v>
+        <v>0.5679033634970991</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.1263396288949219</v>
+        <v>0.05618157590620831</v>
       </c>
       <c r="AE30" t="n">
-        <v>-0.00499025143896481</v>
+        <v>0.4874684913763172</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.1313298803338867</v>
+        <v>-0.4312869154701089</v>
       </c>
       <c r="AG30" t="n">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="AH30" t="n">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="AI30" t="b">
         <v>1</v>
@@ -4745,17 +4741,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4764,7 +4760,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>39</v>
+        <v>36.6</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4773,15 +4769,15 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>3039848</v>
+        <v>499000</v>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="K31" t="b">
         <v>0</v>
@@ -4790,7 +4786,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3039848</v>
+        <v>499000</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -4799,61 +4795,61 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2315</v>
+        <v>2370</v>
       </c>
       <c r="Q31" t="n">
-        <v>2315</v>
+        <v>2370</v>
       </c>
       <c r="R31" t="n">
-        <v>3363537</v>
+        <v>1635222</v>
       </c>
       <c r="S31" t="n">
-        <v>2444</v>
+        <v>2400</v>
       </c>
       <c r="T31" t="n">
-        <v>2217.5</v>
+        <v>2333</v>
       </c>
       <c r="U31" t="n">
-        <v>2205.25</v>
+        <v>2322.25</v>
       </c>
       <c r="V31" t="n">
-        <v>2156.909688313802</v>
+        <v>1935.388326009115</v>
       </c>
       <c r="W31" t="n">
-        <v>71.71489126425286</v>
+        <v>50.81128336974143</v>
       </c>
       <c r="X31" t="n">
-        <v>80.79471440234843</v>
+        <v>74.03948381092772</v>
       </c>
       <c r="Y31" t="n">
-        <v>-9.079823138095577</v>
+        <v>-23.22820044118629</v>
       </c>
       <c r="Z31" t="n">
-        <v>9.564974435114834</v>
+        <v>-16.61741283313532</v>
       </c>
       <c r="AA31" t="b">
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.1183574879227054</v>
+        <v>0.09976798143851506</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.2521639458672671</v>
+        <v>0.8080101155233668</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.06595315546497038</v>
+        <v>0.05486652485374854</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.1546363809954665</v>
+        <v>0.7275752434025848</v>
       </c>
       <c r="AF31" t="n">
-        <v>-0.08868322553049612</v>
+        <v>-0.6727087185488363</v>
       </c>
       <c r="AG31" t="n">
-        <v>72</v>
+        <v>57.99999999999999</v>
       </c>
       <c r="AH31" t="n">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="AI31" t="b">
         <v>1</v>
@@ -4874,7 +4870,7 @@
         <v>1</v>
       </c>
       <c r="AO31" t="n">
-        <v>2421.49</v>
+        <v>2635.44</v>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
@@ -4885,17 +4881,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4904,7 +4900,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4913,24 +4909,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>79618000</v>
+        <v>1000</v>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="K32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" t="b">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>79618000</v>
+        <v>1000</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -4939,73 +4935,73 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>148.5</v>
+        <v>592</v>
       </c>
       <c r="Q32" t="n">
-        <v>148.5</v>
+        <v>592</v>
       </c>
       <c r="R32" t="n">
-        <v>145796960</v>
+        <v>32667276</v>
       </c>
       <c r="S32" t="n">
-        <v>154.3</v>
+        <v>579.6</v>
       </c>
       <c r="T32" t="n">
-        <v>149.925</v>
+        <v>511.1</v>
       </c>
       <c r="U32" t="n">
-        <v>149.65</v>
+        <v>506.75</v>
       </c>
       <c r="V32" t="n">
-        <v>134.45</v>
+        <v>489.6</v>
       </c>
       <c r="W32" t="n">
-        <v>2.558718886628697</v>
+        <v>27.85934789966677</v>
       </c>
       <c r="X32" t="n">
-        <v>4.802979864089592</v>
+        <v>15.72377549864255</v>
       </c>
       <c r="Y32" t="n">
-        <v>-2.244260977460895</v>
+        <v>12.13557240102422</v>
       </c>
       <c r="Z32" t="n">
-        <v>-1.824463489220888</v>
+        <v>13.16721404350908</v>
       </c>
       <c r="AA32" t="b">
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.03846153846153855</v>
+        <v>0.1722772277227722</v>
       </c>
       <c r="AC32" t="n">
-        <v>-0.03257328990228014</v>
+        <v>-0.05882352941176472</v>
       </c>
       <c r="AD32" t="n">
-        <v>-0.01394279399619647</v>
+        <v>0.1273757711380057</v>
       </c>
       <c r="AE32" t="n">
-        <v>-0.1301008547740807</v>
+        <v>-0.1392584015325466</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.1161580607778843</v>
+        <v>0.2666341726705523</v>
       </c>
       <c r="AG32" t="n">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="AH32" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AI32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ32" t="b">
         <v>1</v>
       </c>
       <c r="AK32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM32" t="b">
         <v>0</v>
@@ -5013,8 +5009,10 @@
       <c r="AN32" t="b">
         <v>0</v>
       </c>
-      <c r="AO32" t="n">
-        <v>174.04</v>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
@@ -5025,17 +5023,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5044,7 +5042,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>36.8</v>
+        <v>32.8</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5053,15 +5051,15 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="K33" t="b">
         <v>0</v>
@@ -5070,7 +5068,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
@@ -5079,61 +5077,61 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1215</v>
+        <v>172.5</v>
       </c>
       <c r="Q33" t="n">
-        <v>1215</v>
+        <v>172.5</v>
       </c>
       <c r="R33" t="n">
-        <v>13317263</v>
+        <v>16302541</v>
       </c>
       <c r="S33" t="n">
-        <v>1175</v>
+        <v>176.4</v>
       </c>
       <c r="T33" t="n">
-        <v>999.55</v>
+        <v>168.125</v>
       </c>
       <c r="U33" t="n">
-        <v>987.35</v>
+        <v>167.125</v>
       </c>
       <c r="V33" t="n">
-        <v>1011.474420166016</v>
+        <v>150.5916666666667</v>
       </c>
       <c r="W33" t="n">
-        <v>68.60667357839475</v>
+        <v>4.378314839581691</v>
       </c>
       <c r="X33" t="n">
-        <v>35.75667719699405</v>
+        <v>5.284386788308912</v>
       </c>
       <c r="Y33" t="n">
-        <v>32.8499963814007</v>
+        <v>-0.9060719487272211</v>
       </c>
       <c r="Z33" t="n">
-        <v>34.99315319015135</v>
+        <v>-0.213892123161445</v>
       </c>
       <c r="AA33" t="b">
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.251287332646756</v>
+        <v>0.1311475409836065</v>
       </c>
       <c r="AC33" t="n">
-        <v>-0.1786549034895085</v>
+        <v>-0.01988636363636365</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.1988830001890209</v>
+        <v>0.08624608439883996</v>
       </c>
       <c r="AE33" t="n">
-        <v>-0.2761824683613091</v>
+        <v>-0.1003212357571456</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.4750654685503301</v>
+        <v>0.1865673201559855</v>
       </c>
       <c r="AG33" t="n">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="AH33" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="AI33" t="b">
         <v>1</v>
@@ -5142,21 +5140,19 @@
         <v>1</v>
       </c>
       <c r="AK33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM33" t="b">
         <v>0</v>
       </c>
       <c r="AN33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>182.85</v>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
@@ -5167,17 +5163,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5186,7 +5182,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>35.40000000000001</v>
+        <v>32.6</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5195,15 +5191,15 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="K34" t="b">
         <v>0</v>
@@ -5212,7 +5208,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -5221,61 +5217,61 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>178.5</v>
+        <v>1130</v>
       </c>
       <c r="Q34" t="n">
-        <v>178.5</v>
+        <v>1130</v>
       </c>
       <c r="R34" t="n">
-        <v>18072442</v>
+        <v>19470973</v>
       </c>
       <c r="S34" t="n">
-        <v>177.4</v>
+        <v>1184</v>
       </c>
       <c r="T34" t="n">
-        <v>167.125</v>
+        <v>1008.3</v>
       </c>
       <c r="U34" t="n">
-        <v>166.1</v>
+        <v>999.55</v>
       </c>
       <c r="V34" t="n">
-        <v>150.65</v>
+        <v>1005.155000813802</v>
       </c>
       <c r="W34" t="n">
-        <v>5.295250898270695</v>
+        <v>61.6813125427218</v>
       </c>
       <c r="X34" t="n">
-        <v>5.507396163941126</v>
+        <v>40.97196798221578</v>
       </c>
       <c r="Y34" t="n">
-        <v>-0.2121452656704319</v>
+        <v>20.70934456050602</v>
       </c>
       <c r="Z34" t="n">
-        <v>-0.09003572502239621</v>
+        <v>32.83115113166608</v>
       </c>
       <c r="AA34" t="b">
         <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.129746835443038</v>
+        <v>0.1832460732984293</v>
       </c>
       <c r="AC34" t="n">
-        <v>-0.0703125</v>
+        <v>-0.2512416605537082</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.07734250298530299</v>
+        <v>0.1383446167136628</v>
       </c>
       <c r="AE34" t="n">
-        <v>-0.1678400648718006</v>
+        <v>-0.3316765326744902</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.2451825678571036</v>
+        <v>0.470021149388153</v>
       </c>
       <c r="AG34" t="n">
         <v>76</v>
       </c>
       <c r="AH34" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="AI34" t="b">
         <v>1</v>
@@ -5284,19 +5280,21 @@
         <v>1</v>
       </c>
       <c r="AK34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM34" t="b">
         <v>0</v>
       </c>
       <c r="AN34" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>181</v>
+        <v>0</v>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
@@ -5307,17 +5305,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5326,7 +5324,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>32.2</v>
+        <v>29</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5335,15 +5333,15 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>6062000</v>
+        <v>1000</v>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="K35" t="b">
         <v>0</v>
@@ -5352,7 +5350,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>6062000</v>
+        <v>1000</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -5361,61 +5359,61 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>3545</v>
+        <v>6660</v>
       </c>
       <c r="Q35" t="n">
-        <v>3545</v>
+        <v>6660</v>
       </c>
       <c r="R35" t="n">
-        <v>2868292</v>
+        <v>1709053</v>
       </c>
       <c r="S35" t="n">
-        <v>3553</v>
+        <v>6676</v>
       </c>
       <c r="T35" t="n">
-        <v>3407</v>
+        <v>6388.25</v>
       </c>
       <c r="U35" t="n">
-        <v>3400.75</v>
+        <v>6380.25</v>
       </c>
       <c r="V35" t="n">
-        <v>2981.088883463542</v>
+        <v>5541.116589355469</v>
       </c>
       <c r="W35" t="n">
-        <v>77.2830168333694</v>
+        <v>108.7493100898646</v>
       </c>
       <c r="X35" t="n">
-        <v>68.32501243098241</v>
+        <v>44.38449983839664</v>
       </c>
       <c r="Y35" t="n">
-        <v>8.95800440238699</v>
+        <v>64.36481025146796</v>
       </c>
       <c r="Z35" t="n">
-        <v>17.33518062495737</v>
+        <v>78.13496384642453</v>
       </c>
       <c r="AA35" t="b">
         <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.03654970760233911</v>
+        <v>0.02461538461538471</v>
       </c>
       <c r="AC35" t="n">
-        <v>0.60271015404884</v>
+        <v>0.5758105101170794</v>
       </c>
       <c r="AD35" t="n">
-        <v>-0.0158546248553959</v>
+        <v>-0.02028607196938181</v>
       </c>
       <c r="AE35" t="n">
-        <v>0.5051825891770394</v>
+        <v>0.4953756379962975</v>
       </c>
       <c r="AF35" t="n">
-        <v>-0.5210372140324353</v>
+        <v>-0.5156617099656793</v>
       </c>
       <c r="AG35" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AH35" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="AI35" t="b">
         <v>1</v>
@@ -5449,17 +5447,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5468,7 +5466,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>31.8</v>
+        <v>28.4</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5477,15 +5475,15 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1000</v>
+        <v>501000</v>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="K36" t="b">
         <v>0</v>
@@ -5494,7 +5492,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1000</v>
+        <v>501000</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -5503,61 +5501,61 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>549</v>
+        <v>248</v>
       </c>
       <c r="Q36" t="n">
-        <v>549</v>
+        <v>248</v>
       </c>
       <c r="R36" t="n">
-        <v>20275450</v>
+        <v>23188404</v>
       </c>
       <c r="S36" t="n">
-        <v>538.8</v>
+        <v>244.1</v>
       </c>
       <c r="T36" t="n">
-        <v>510.9</v>
+        <v>228.725</v>
       </c>
       <c r="U36" t="n">
-        <v>509.2</v>
+        <v>227.875</v>
       </c>
       <c r="V36" t="n">
-        <v>445.4799545288086</v>
+        <v>219.5916666666667</v>
       </c>
       <c r="W36" t="n">
-        <v>15.64747545641137</v>
+        <v>5.759997235116174</v>
       </c>
       <c r="X36" t="n">
-        <v>10.40106966876404</v>
+        <v>2.542632776838465</v>
       </c>
       <c r="Y36" t="n">
-        <v>5.246405787647333</v>
+        <v>3.217364458277709</v>
       </c>
       <c r="Z36" t="n">
-        <v>5.616374078944146</v>
+        <v>3.425934511739225</v>
       </c>
       <c r="AA36" t="b">
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.06601941747572826</v>
+        <v>0.07359307359307365</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.1074550052572869</v>
+        <v>0.0997782705099779</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.01361508501799324</v>
+        <v>0.02869161700830714</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.009927440385486319</v>
+        <v>0.01934339838919596</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.003687644632506926</v>
+        <v>0.00934821861911117</v>
       </c>
       <c r="AG36" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="AH36" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="AI36" t="b">
         <v>1</v>
@@ -5591,17 +5589,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5610,7 +5608,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>27.8</v>
+        <v>27.6</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5619,15 +5617,15 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>5086000</v>
+        <v>1000</v>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="K37" t="b">
         <v>0</v>
@@ -5636,7 +5634,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>5086000</v>
+        <v>1000</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -5645,82 +5643,84 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>4835</v>
+        <v>2330</v>
       </c>
       <c r="Q37" t="n">
-        <v>4835</v>
+        <v>2330</v>
       </c>
       <c r="R37" t="n">
-        <v>5659059</v>
+        <v>1670735</v>
       </c>
       <c r="S37" t="n">
-        <v>4970</v>
+        <v>2319</v>
       </c>
       <c r="T37" t="n">
-        <v>4835.5</v>
+        <v>2239.5</v>
       </c>
       <c r="U37" t="n">
-        <v>4831.75</v>
+        <v>2236.25</v>
       </c>
       <c r="V37" t="n">
-        <v>4187</v>
+        <v>2114.25</v>
       </c>
       <c r="W37" t="n">
-        <v>101.9101805804585</v>
+        <v>43.81936756337473</v>
       </c>
       <c r="X37" t="n">
-        <v>154.2113620240898</v>
+        <v>32.83819442283744</v>
       </c>
       <c r="Y37" t="n">
-        <v>-52.30118144363132</v>
+        <v>10.98117314053729</v>
       </c>
       <c r="Z37" t="n">
-        <v>-34.45925833876728</v>
+        <v>13.56714370826949</v>
       </c>
       <c r="AA37" t="b">
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.01575630252100835</v>
+        <v>0.02869757174392928</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.2640522875816993</v>
+        <v>0.2802197802197801</v>
       </c>
       <c r="AD37" t="n">
-        <v>-0.03664802993672667</v>
+        <v>-0.01620388484083723</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.1665247227098987</v>
+        <v>0.1997849080989982</v>
       </c>
       <c r="AF37" t="n">
-        <v>-0.2031727526466254</v>
+        <v>-0.2159887929398354</v>
       </c>
       <c r="AG37" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AH37" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AI37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ37" t="b">
         <v>1</v>
       </c>
       <c r="AK37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM37" t="b">
         <v>0</v>
       </c>
       <c r="AN37" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>5424.87</v>
+        <v>0</v>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
@@ -5731,17 +5731,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5750,102 +5750,102 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>26.2</v>
+        <v>26.4</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Sell</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>6264000</v>
+        <v>4328000</v>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" t="b">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>6264000</v>
+        <v>4650000</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>-322000</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>-0.06924731182795699</v>
       </c>
       <c r="P38" t="n">
-        <v>2015</v>
+        <v>6000</v>
       </c>
       <c r="Q38" t="n">
-        <v>2015</v>
+        <v>6000</v>
       </c>
       <c r="R38" t="n">
-        <v>4894508</v>
+        <v>1665965</v>
       </c>
       <c r="S38" t="n">
-        <v>2001</v>
+        <v>5766</v>
       </c>
       <c r="T38" t="n">
-        <v>1908</v>
+        <v>5236.5</v>
       </c>
       <c r="U38" t="n">
-        <v>1912.25</v>
+        <v>5203.5</v>
       </c>
       <c r="V38" t="n">
-        <v>2082.383074951172</v>
+        <v>5259.273494466146</v>
       </c>
       <c r="W38" t="n">
-        <v>16.9879069055562</v>
+        <v>196.0214954952326</v>
       </c>
       <c r="X38" t="n">
-        <v>-19.88300686217262</v>
+        <v>34.54955237041199</v>
       </c>
       <c r="Y38" t="n">
-        <v>36.87091376772882</v>
+        <v>161.4719431248206</v>
       </c>
       <c r="Z38" t="n">
-        <v>40.55987037390747</v>
+        <v>162.5406575067177</v>
       </c>
       <c r="AA38" t="b">
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>-0.04047619047619044</v>
+        <v>0.1235955056179776</v>
       </c>
       <c r="AC38" t="n">
-        <v>-0.1555301945041893</v>
+        <v>0.2127559662204828</v>
       </c>
       <c r="AD38" t="n">
-        <v>-0.09288052293392546</v>
+        <v>0.07869404903321109</v>
       </c>
       <c r="AE38" t="n">
-        <v>-0.2530577593759898</v>
+        <v>0.1323210940997008</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.1601772364420644</v>
+        <v>-0.05362704506648974</v>
       </c>
       <c r="AG38" t="n">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="AH38" t="n">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="AI38" t="b">
         <v>1</v>
       </c>
       <c r="AJ38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK38" t="b">
         <v>1</v>
@@ -5864,24 +5864,26 @@
           <t>Already &gt; 0</t>
         </is>
       </c>
-      <c r="AP38" t="n">
-        <v>1842.37</v>
+      <c r="AP38" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5890,7 +5892,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>25.6</v>
+        <v>26.2</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5899,15 +5901,15 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>501000</v>
+        <v>1000</v>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K39" t="b">
         <v>0</v>
@@ -5916,7 +5918,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>501000</v>
+        <v>1000</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -5925,61 +5927,61 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>246</v>
+        <v>535</v>
       </c>
       <c r="Q39" t="n">
-        <v>246</v>
+        <v>535</v>
       </c>
       <c r="R39" t="n">
-        <v>59769877</v>
+        <v>3348518</v>
       </c>
       <c r="S39" t="n">
-        <v>239.4</v>
+        <v>544.8</v>
       </c>
       <c r="T39" t="n">
-        <v>227.875</v>
+        <v>511.65</v>
       </c>
       <c r="U39" t="n">
-        <v>227.575</v>
+        <v>510.9</v>
       </c>
       <c r="V39" t="n">
-        <v>219.2166666666667</v>
+        <v>446.7648824055989</v>
       </c>
       <c r="W39" t="n">
-        <v>5.1651793361209</v>
+        <v>14.35358227217</v>
       </c>
       <c r="X39" t="n">
-        <v>1.740189434391359</v>
+        <v>11.18623510330251</v>
       </c>
       <c r="Y39" t="n">
-        <v>3.424989901729541</v>
+        <v>3.16734716886749</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.556608129937456</v>
+        <v>5.249718200634559</v>
       </c>
       <c r="AA39" t="b">
         <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.02499999999999991</v>
+        <v>0.02884615384615374</v>
       </c>
       <c r="AC39" t="n">
-        <v>0.04680851063829783</v>
+        <v>0.1683663333046532</v>
       </c>
       <c r="AD39" t="n">
-        <v>-0.0274043324577351</v>
+        <v>-0.01605530273861278</v>
       </c>
       <c r="AE39" t="n">
-        <v>-0.05071905423350276</v>
+        <v>0.0879314611838713</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.02331472177576766</v>
+        <v>-0.1039867639224841</v>
       </c>
       <c r="AG39" t="n">
         <v>38</v>
       </c>
       <c r="AH39" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="AI39" t="b">
         <v>1</v>
@@ -6013,17 +6015,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6032,7 +6034,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>25</v>
+        <v>24.8</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -6041,15 +6043,15 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1000</v>
+        <v>5086000</v>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="K40" t="b">
         <v>0</v>
@@ -6058,7 +6060,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1000</v>
+        <v>5086000</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -6067,73 +6069,73 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>514</v>
+        <v>4690</v>
       </c>
       <c r="Q40" t="n">
-        <v>514</v>
+        <v>4690</v>
       </c>
       <c r="R40" t="n">
-        <v>37448206</v>
+        <v>6416655</v>
       </c>
       <c r="S40" t="n">
-        <v>522.8</v>
+        <v>4912</v>
       </c>
       <c r="T40" t="n">
-        <v>508.8</v>
+        <v>4834.5</v>
       </c>
       <c r="U40" t="n">
-        <v>508.95</v>
+        <v>4835.5</v>
       </c>
       <c r="V40" t="n">
-        <v>480.0833333333333</v>
+        <v>4204.166666666667</v>
       </c>
       <c r="W40" t="n">
-        <v>5.012397015169313</v>
+        <v>61.8921663207484</v>
       </c>
       <c r="X40" t="n">
-        <v>3.966147987486565</v>
+        <v>135.7194358341844</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.046249027682748</v>
+        <v>-73.82726951343602</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.576905586658444</v>
+        <v>-52.28377392719844</v>
       </c>
       <c r="AA40" t="b">
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>-0.005802707930367523</v>
+        <v>-0.00424628450106157</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.2151300236406619</v>
+        <v>0.2814207650273224</v>
       </c>
       <c r="AD40" t="n">
-        <v>-0.05820704038810254</v>
+        <v>-0.04914774108582809</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.1176024587688613</v>
+        <v>0.2009858929065405</v>
       </c>
       <c r="AF40" t="n">
-        <v>-0.1758094991569639</v>
+        <v>-0.2501336339923685</v>
       </c>
       <c r="AG40" t="n">
         <v>26</v>
       </c>
       <c r="AH40" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="AI40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ40" t="b">
         <v>0</v>
       </c>
       <c r="AK40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM40" t="b">
         <v>0</v>
@@ -6141,29 +6143,27 @@
       <c r="AN40" t="b">
         <v>0</v>
       </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+      <c r="AO40" t="n">
+        <v>5524.82</v>
       </c>
       <c r="AP40" t="n">
-        <v>525.53</v>
+        <v>4777.11</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>慧洋-KY</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6172,7 +6172,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>22.4</v>
+        <v>24</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -6181,15 +6181,15 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>5163000</v>
+        <v>1000</v>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="n">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="K41" t="b">
         <v>0</v>
@@ -6198,7 +6198,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>5163000</v>
+        <v>1000</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -6207,103 +6207,103 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>18.95000076293945</v>
+        <v>98.40000152587891</v>
       </c>
       <c r="Q41" t="n">
-        <v>18.95000076293945</v>
+        <v>98.40000152587891</v>
       </c>
       <c r="R41" t="n">
-        <v>22310243</v>
+        <v>1687131</v>
       </c>
       <c r="S41" t="n">
-        <v>18.95000038146973</v>
+        <v>98.34000091552734</v>
       </c>
       <c r="T41" t="n">
-        <v>18.8625</v>
+        <v>99.44000053405762</v>
       </c>
       <c r="U41" t="n">
-        <v>18.86499996185303</v>
+        <v>99.42500038146973</v>
       </c>
       <c r="V41" t="n">
-        <v>18.96204630533854</v>
+        <v>92.03500022888184</v>
       </c>
       <c r="W41" t="n">
-        <v>0.01744148270990564</v>
+        <v>-0.1089435152558593</v>
       </c>
       <c r="X41" t="n">
-        <v>-0.01823501567026901</v>
+        <v>0.2470375668089768</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.03567649838017465</v>
+        <v>-0.3559810820648361</v>
       </c>
       <c r="Z41" t="n">
-        <v>0.04121024233231825</v>
+        <v>-0.4924732197200056</v>
       </c>
       <c r="AA41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB41" t="n">
-        <v>-0.002631538792660315</v>
+        <v>0.003058135131744688</v>
       </c>
       <c r="AC41" t="n">
-        <v>0.03804354299352908</v>
+        <v>0.1742243191220842</v>
       </c>
       <c r="AD41" t="n">
-        <v>-0.05503587125039533</v>
+        <v>-0.04184332145302183</v>
       </c>
       <c r="AE41" t="n">
-        <v>-0.05948402187827151</v>
+        <v>0.09378944700130232</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.00444815062787618</v>
+        <v>-0.1356327684543241</v>
       </c>
       <c r="AG41" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AH41" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="AI41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
-      <c r="AP41" t="n">
-        <v>19.01</v>
+        <v>1</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>102.53</v>
+      </c>
+      <c r="AP41" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6312,7 +6312,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>22.4</v>
+        <v>21.4</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -6329,7 +6329,7 @@
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="K42" t="b">
         <v>0</v>
@@ -6347,61 +6347,61 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>96.80000305175781</v>
+        <v>565</v>
       </c>
       <c r="Q42" t="n">
-        <v>96.80000305175781</v>
+        <v>565</v>
       </c>
       <c r="R42" t="n">
-        <v>2651070</v>
+        <v>3426072</v>
       </c>
       <c r="S42" t="n">
-        <v>97.72000122070312</v>
+        <v>579</v>
       </c>
       <c r="T42" t="n">
-        <v>99.42500038146973</v>
+        <v>572.3</v>
       </c>
       <c r="U42" t="n">
-        <v>99.54500007629395</v>
+        <v>574.3</v>
       </c>
       <c r="V42" t="n">
-        <v>91.79166692097982</v>
+        <v>524.2833333333333</v>
       </c>
       <c r="W42" t="n">
-        <v>-0.1569840467052046</v>
+        <v>-0.3008540646583242</v>
       </c>
       <c r="X42" t="n">
-        <v>0.3349549795087695</v>
+        <v>1.463752461506485</v>
       </c>
       <c r="Y42" t="n">
-        <v>-0.4919390262139741</v>
+        <v>-1.764606526164809</v>
       </c>
       <c r="Z42" t="n">
-        <v>-0.4209627587253146</v>
+        <v>-0.6651745070861605</v>
       </c>
       <c r="AA42" t="b">
         <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>-0.02419348760400242</v>
+        <v>-0.06611570247933884</v>
       </c>
       <c r="AC42" t="n">
-        <v>0.1428572200647138</v>
+        <v>0.401985111662531</v>
       </c>
       <c r="AD42" t="n">
-        <v>-0.07659782006173743</v>
+        <v>-0.1110171590641054</v>
       </c>
       <c r="AE42" t="n">
-        <v>0.04532965519291321</v>
+        <v>0.3215502395417491</v>
       </c>
       <c r="AF42" t="n">
-        <v>-0.1219274752546506</v>
+        <v>-0.4325673986058545</v>
       </c>
       <c r="AG42" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AH42" t="n">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="AI42" t="b">
         <v>0</v>
@@ -6422,26 +6422,26 @@
         <v>1</v>
       </c>
       <c r="AO42" t="n">
-        <v>102.41</v>
+        <v>585.34</v>
       </c>
       <c r="AP42" t="n">
-        <v>100.86</v>
+        <v>617.6799999999999</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6450,7 +6450,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>22.2</v>
+        <v>20.8</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -6467,7 +6467,7 @@
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="K43" t="b">
         <v>0</v>
@@ -6485,93 +6485,93 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>252</v>
+        <v>558</v>
       </c>
       <c r="Q43" t="n">
-        <v>252</v>
+        <v>558</v>
       </c>
       <c r="R43" t="n">
-        <v>35038733</v>
+        <v>383366</v>
       </c>
       <c r="S43" t="n">
-        <v>253.4</v>
+        <v>567.4</v>
       </c>
       <c r="T43" t="n">
-        <v>251.25</v>
+        <v>558.85</v>
       </c>
       <c r="U43" t="n">
-        <v>251.45</v>
+        <v>558.3</v>
       </c>
       <c r="V43" t="n">
-        <v>250.4416666666667</v>
+        <v>570.6034210205078</v>
       </c>
       <c r="W43" t="n">
-        <v>0.707629574884777</v>
+        <v>1.036610043898463</v>
       </c>
       <c r="X43" t="n">
-        <v>0.4586382602932627</v>
+        <v>1.838883445649217</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.2489913145915142</v>
+        <v>-0.802273401750754</v>
       </c>
       <c r="Z43" t="n">
-        <v>0.5314470084101708</v>
+        <v>0.4201449755620841</v>
       </c>
       <c r="AA43" t="b">
         <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>-0.015625</v>
+        <v>0.02010968921389389</v>
       </c>
       <c r="AC43" t="n">
-        <v>0.06553911205074003</v>
+        <v>-0.09769513464688384</v>
       </c>
       <c r="AD43" t="n">
-        <v>-0.06802933245773501</v>
+        <v>-0.02479176737087263</v>
       </c>
       <c r="AE43" t="n">
-        <v>-0.03198845282106055</v>
+        <v>-0.1781300067676658</v>
       </c>
       <c r="AF43" t="n">
-        <v>-0.03604087963667446</v>
+        <v>0.1533382393967931</v>
       </c>
       <c r="AG43" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AH43" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="AI43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM43" t="b">
         <v>0</v>
       </c>
       <c r="AN43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
-      <c r="AP43" t="n">
-        <v>250.71</v>
+        <v>1</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>568.04</v>
+      </c>
+      <c r="AP43" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6590,7 +6590,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>21.6</v>
+        <v>19.8</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -6625,58 +6625,58 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>17750</v>
+        <v>17485</v>
       </c>
       <c r="Q44" t="n">
-        <v>17750</v>
+        <v>17485</v>
       </c>
       <c r="R44" t="n">
-        <v>370066</v>
+        <v>1079583</v>
       </c>
       <c r="S44" t="n">
-        <v>18827</v>
+        <v>18516</v>
       </c>
       <c r="T44" t="n">
+        <v>18855.5</v>
+      </c>
+      <c r="U44" t="n">
         <v>18942.25</v>
       </c>
-      <c r="U44" t="n">
-        <v>19015.5</v>
-      </c>
       <c r="V44" t="n">
-        <v>16727.58333333333</v>
+        <v>16802.58333333333</v>
       </c>
       <c r="W44" t="n">
-        <v>85.04017299239786</v>
+        <v>-78.09230247373125</v>
       </c>
       <c r="X44" t="n">
-        <v>383.0055049047485</v>
+        <v>290.5850140168843</v>
       </c>
       <c r="Y44" t="n">
-        <v>-297.9653319123507</v>
+        <v>-368.6773164906156</v>
       </c>
       <c r="Z44" t="n">
-        <v>-182.2863309259865</v>
+        <v>-297.8407122578458</v>
       </c>
       <c r="AA44" t="b">
         <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>-0.07624251886546973</v>
+        <v>-0.090270551508845</v>
       </c>
       <c r="AC44" t="n">
-        <v>0.3128698224852071</v>
+        <v>0.3465537158259531</v>
       </c>
       <c r="AD44" t="n">
-        <v>-0.1286468513232047</v>
+        <v>-0.1351720080936115</v>
       </c>
       <c r="AE44" t="n">
-        <v>0.2153422576134065</v>
+        <v>0.2661188437051711</v>
       </c>
       <c r="AF44" t="n">
-        <v>-0.3439891089366113</v>
+        <v>-0.4012908517987827</v>
       </c>
       <c r="AG44" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AH44" t="n">
         <v>78</v>
@@ -6699,27 +6699,25 @@
       <c r="AN44" t="b">
         <v>0</v>
       </c>
-      <c r="AO44" t="n">
-        <v>21122.5</v>
-      </c>
+      <c r="AO44" t="inlineStr"/>
       <c r="AP44" t="n">
-        <v>20475</v>
+        <v>20047.63</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6728,7 +6726,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>21</v>
+        <v>19.4</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6737,15 +6735,15 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1000</v>
+        <v>5163000</v>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="n">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="K45" t="b">
         <v>0</v>
@@ -6754,7 +6752,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>1000</v>
+        <v>5163000</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
@@ -6763,67 +6761,67 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>568</v>
+        <v>18.95000076293945</v>
       </c>
       <c r="Q45" t="n">
-        <v>568</v>
+        <v>18.95000076293945</v>
       </c>
       <c r="R45" t="n">
-        <v>277321</v>
+        <v>26622757</v>
       </c>
       <c r="S45" t="n">
-        <v>570.2</v>
+        <v>18.95000038146973</v>
       </c>
       <c r="T45" t="n">
-        <v>558.3</v>
+        <v>18.85500001907349</v>
       </c>
       <c r="U45" t="n">
-        <v>558.2</v>
+        <v>18.8625</v>
       </c>
       <c r="V45" t="n">
-        <v>571.6103586832683</v>
+        <v>18.97196779251099</v>
       </c>
       <c r="W45" t="n">
-        <v>2.460025945859002</v>
+        <v>0.01933005598385407</v>
       </c>
       <c r="X45" t="n">
-        <v>2.040316450753692</v>
+        <v>-0.01076000137061569</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.4197094951053102</v>
+        <v>0.03009005735446976</v>
       </c>
       <c r="Z45" t="n">
-        <v>0.8879536071923242</v>
+        <v>0.03570005636272668</v>
       </c>
       <c r="AA45" t="b">
         <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.003533568904593665</v>
+        <v>-0.007853383012274673</v>
       </c>
       <c r="AC45" t="n">
-        <v>-0.1084969867350049</v>
+        <v>0.03243250264596176</v>
       </c>
       <c r="AD45" t="n">
-        <v>-0.04887076355314135</v>
+        <v>-0.05275483959704119</v>
       </c>
       <c r="AE45" t="n">
-        <v>-0.2060245516068054</v>
+        <v>-0.04800236947482017</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.1571537880536641</v>
+        <v>-0.00475247012222102</v>
       </c>
       <c r="AG45" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AH45" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="AI45" t="b">
         <v>1</v>
       </c>
       <c r="AJ45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK45" t="b">
         <v>1</v>
@@ -6842,26 +6840,24 @@
           <t>Already &gt; 0</t>
         </is>
       </c>
-      <c r="AP45" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+      <c r="AP45" t="n">
+        <v>19.15</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6870,7 +6866,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>17.8</v>
+        <v>19.2</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6879,7 +6875,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="H46" t="n">
@@ -6887,7 +6883,7 @@
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="K46" t="b">
         <v>0</v>
@@ -6905,61 +6901,61 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>335</v>
+        <v>249</v>
       </c>
       <c r="Q46" t="n">
-        <v>335</v>
+        <v>249</v>
       </c>
       <c r="R46" t="n">
-        <v>9442843</v>
+        <v>38527797</v>
       </c>
       <c r="S46" t="n">
-        <v>333.1</v>
+        <v>252.4</v>
       </c>
       <c r="T46" t="n">
-        <v>336.875</v>
+        <v>251.125</v>
       </c>
       <c r="U46" t="n">
-        <v>337.5</v>
+        <v>251.25</v>
       </c>
       <c r="V46" t="n">
-        <v>328.9723490397135</v>
+        <v>250.6666666666667</v>
       </c>
       <c r="W46" t="n">
-        <v>-0.9726104521275829</v>
+        <v>0.2040105377760426</v>
       </c>
       <c r="X46" t="n">
-        <v>0.05036618498014497</v>
+        <v>0.4066900643502533</v>
       </c>
       <c r="Y46" t="n">
-        <v>-1.022976637107728</v>
+        <v>-0.2026795265742107</v>
       </c>
       <c r="Z46" t="n">
-        <v>-1.445521486398305</v>
+        <v>0.2496273900292698</v>
       </c>
       <c r="AA46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>-0.03597122302158273</v>
+        <v>-0.00994035785288272</v>
       </c>
       <c r="AC46" t="n">
-        <v>-0.07592025960110949</v>
+        <v>0.0573248407643312</v>
       </c>
       <c r="AD46" t="n">
-        <v>-0.08837555547931775</v>
+        <v>-0.05484181443764924</v>
       </c>
       <c r="AE46" t="n">
-        <v>-0.1734478244729101</v>
+        <v>-0.02311003135645073</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.08507226899359233</v>
+        <v>-0.03173178308119851</v>
       </c>
       <c r="AG46" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AH46" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="AI46" t="b">
         <v>0</v>
@@ -6974,32 +6970,32 @@
         <v>0</v>
       </c>
       <c r="AM46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN46" t="b">
         <v>1</v>
       </c>
       <c r="AO46" t="n">
-        <v>347.06</v>
+        <v>251.49</v>
       </c>
       <c r="AP46" t="n">
-        <v>329.97</v>
+        <v>254.24</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7008,7 +7004,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>17</v>
+        <v>18.2</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -7017,15 +7013,15 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>251000</v>
+        <v>1000</v>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="K47" t="b">
         <v>0</v>
@@ -7034,7 +7030,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>251000</v>
+        <v>1000</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
@@ -7043,61 +7039,61 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>3020</v>
+        <v>325.5</v>
       </c>
       <c r="Q47" t="n">
-        <v>3020</v>
+        <v>325.5</v>
       </c>
       <c r="R47" t="n">
-        <v>354370</v>
+        <v>16798850</v>
       </c>
       <c r="S47" t="n">
-        <v>3050</v>
+        <v>331.4</v>
       </c>
       <c r="T47" t="n">
-        <v>3319.25</v>
+        <v>336.75</v>
       </c>
       <c r="U47" t="n">
-        <v>3341.75</v>
+        <v>336.875</v>
       </c>
       <c r="V47" t="n">
-        <v>2956.333333333333</v>
+        <v>328.323333231608</v>
       </c>
       <c r="W47" t="n">
-        <v>-67.11204988066675</v>
+        <v>-1.888682558653556</v>
       </c>
       <c r="X47" t="n">
-        <v>-11.7252874399771</v>
+        <v>-0.3371748259986893</v>
       </c>
       <c r="Y47" t="n">
-        <v>-55.38676244068965</v>
+        <v>-1.551507732654867</v>
       </c>
       <c r="Z47" t="n">
-        <v>-61.51844684169657</v>
+        <v>-1.023144505352552</v>
       </c>
       <c r="AA47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>-0.1296829971181557</v>
+        <v>-0.007621951219512146</v>
       </c>
       <c r="AC47" t="n">
-        <v>0.08828828828828827</v>
+        <v>-0.1068511885068507</v>
       </c>
       <c r="AD47" t="n">
-        <v>-0.1820873295758907</v>
+        <v>-0.05252340780427867</v>
       </c>
       <c r="AE47" t="n">
-        <v>-0.009239276583512313</v>
+        <v>-0.1872860606276326</v>
       </c>
       <c r="AF47" t="n">
-        <v>-0.1728480529923784</v>
+        <v>0.134762652823354</v>
       </c>
       <c r="AG47" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="AH47" t="n">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="AI47" t="b">
         <v>0</v>
@@ -7112,30 +7108,32 @@
         <v>0</v>
       </c>
       <c r="AM47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO47" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>343.08</v>
+      </c>
       <c r="AP47" t="n">
-        <v>3935</v>
+        <v>353.84</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7144,7 +7142,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>15.2</v>
+        <v>15.4</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -7153,15 +7151,15 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1000</v>
+        <v>478000</v>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="K48" t="b">
         <v>0</v>
@@ -7170,7 +7168,7 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>1000</v>
+        <v>478000</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
@@ -7179,61 +7177,61 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>1230</v>
+        <v>874</v>
       </c>
       <c r="Q48" t="n">
-        <v>1230</v>
+        <v>874</v>
       </c>
       <c r="R48" t="n">
-        <v>574447</v>
+        <v>1402512</v>
       </c>
       <c r="S48" t="n">
-        <v>1194</v>
+        <v>872.4</v>
       </c>
       <c r="T48" t="n">
-        <v>1241.5</v>
+        <v>883.45</v>
       </c>
       <c r="U48" t="n">
-        <v>1248.5</v>
+        <v>885.1</v>
       </c>
       <c r="V48" t="n">
-        <v>1361.380466715495</v>
+        <v>986.8333333333334</v>
       </c>
       <c r="W48" t="n">
-        <v>-29.74141171174756</v>
+        <v>-12.20600999459157</v>
       </c>
       <c r="X48" t="n">
-        <v>-38.36521293621264</v>
+        <v>-17.67174304070923</v>
       </c>
       <c r="Y48" t="n">
-        <v>8.623801224465076</v>
+        <v>5.465733046117663</v>
       </c>
       <c r="Z48" t="n">
-        <v>3.567152488290333</v>
+        <v>5.266299864369223</v>
       </c>
       <c r="AA48" t="b">
         <v>1</v>
       </c>
       <c r="AB48" t="n">
-        <v>-0.1021897810218978</v>
+        <v>-0.03638368246968027</v>
       </c>
       <c r="AC48" t="n">
-        <v>-0.04820658841038949</v>
+        <v>-0.2126126126126127</v>
       </c>
       <c r="AD48" t="n">
-        <v>-0.1545941134796328</v>
+        <v>-0.08128513905444679</v>
       </c>
       <c r="AE48" t="n">
-        <v>-0.1457341532821901</v>
+        <v>-0.2930474847333946</v>
       </c>
       <c r="AF48" t="n">
-        <v>-0.008859960197442729</v>
+        <v>0.2117623456789478</v>
       </c>
       <c r="AG48" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="AH48" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="AI48" t="b">
         <v>0</v>
@@ -7259,23 +7257,23 @@
         </is>
       </c>
       <c r="AP48" t="n">
-        <v>1347.11</v>
+        <v>925.95</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -7284,7 +7282,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>14.8</v>
+        <v>13.8</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -7293,15 +7291,15 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>478000</v>
+        <v>1000</v>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="K49" t="b">
         <v>0</v>
@@ -7310,7 +7308,7 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>478000</v>
+        <v>1000</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
@@ -7319,61 +7317,61 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>872</v>
+        <v>1205</v>
       </c>
       <c r="Q49" t="n">
-        <v>872</v>
+        <v>1205</v>
       </c>
       <c r="R49" t="n">
-        <v>2208054</v>
+        <v>1791155</v>
       </c>
       <c r="S49" t="n">
-        <v>866.6</v>
+        <v>1198</v>
       </c>
       <c r="T49" t="n">
-        <v>885.1</v>
+        <v>1235</v>
       </c>
       <c r="U49" t="n">
-        <v>888.35</v>
+        <v>1241.5</v>
       </c>
       <c r="V49" t="n">
-        <v>990.7666666666667</v>
+        <v>1360.415018717448</v>
       </c>
       <c r="W49" t="n">
-        <v>-13.76355517907393</v>
+        <v>-26.80408035381402</v>
       </c>
       <c r="X49" t="n">
-        <v>-19.02165212059708</v>
+        <v>-36.06320445878771</v>
       </c>
       <c r="Y49" t="n">
-        <v>5.258096941523146</v>
+        <v>9.259124104973694</v>
       </c>
       <c r="Z49" t="n">
-        <v>5.122028202449904</v>
+        <v>8.630122408340895</v>
       </c>
       <c r="AA49" t="b">
         <v>1</v>
       </c>
       <c r="AB49" t="n">
-        <v>-0.06937033084311628</v>
+        <v>-0.09737827715355807</v>
       </c>
       <c r="AC49" t="n">
-        <v>-0.2317180616740088</v>
+        <v>-0.04586716840502081</v>
       </c>
       <c r="AD49" t="n">
-        <v>-0.1217746633008513</v>
+        <v>-0.1422797337383246</v>
       </c>
       <c r="AE49" t="n">
-        <v>-0.3292456265458094</v>
+        <v>-0.1263020405258027</v>
       </c>
       <c r="AF49" t="n">
-        <v>0.2074709632449581</v>
+        <v>-0.01597769321252185</v>
       </c>
       <c r="AG49" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="AH49" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="AI49" t="b">
         <v>0</v>
@@ -7399,13 +7397,13 @@
         </is>
       </c>
       <c r="AP49" t="n">
-        <v>920.79</v>
+        <v>1361.58</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -7424,7 +7422,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>13</v>
+        <v>11.8</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7433,7 +7431,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="H50" t="n">
@@ -7459,61 +7457,61 @@
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>169</v>
+        <v>169.5</v>
       </c>
       <c r="Q50" t="n">
-        <v>169</v>
+        <v>169.5</v>
       </c>
       <c r="R50" t="n">
-        <v>2517289</v>
+        <v>1907173</v>
       </c>
       <c r="S50" t="n">
-        <v>172</v>
+        <v>171.1</v>
       </c>
       <c r="T50" t="n">
+        <v>177.35</v>
+      </c>
+      <c r="U50" t="n">
         <v>179.05</v>
       </c>
-      <c r="U50" t="n">
-        <v>180.925</v>
-      </c>
       <c r="V50" t="n">
-        <v>185.8216262817383</v>
+        <v>185.4261248270671</v>
       </c>
       <c r="W50" t="n">
-        <v>-4.53227695627325</v>
+        <v>-4.40398728722613</v>
       </c>
       <c r="X50" t="n">
-        <v>-4.637402466855557</v>
+        <v>-4.591481634947813</v>
       </c>
       <c r="Y50" t="n">
-        <v>0.1051255105823063</v>
+        <v>0.1874943477216835</v>
       </c>
       <c r="Z50" t="n">
-        <v>0.1874529444021213</v>
+        <v>0.1055989562781781</v>
       </c>
       <c r="AA50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB50" t="n">
-        <v>-0.1815980629539952</v>
+        <v>-0.1670761670761671</v>
       </c>
       <c r="AC50" t="n">
-        <v>-0.1096160416621447</v>
+        <v>-0.1228074137639538</v>
       </c>
       <c r="AD50" t="n">
-        <v>-0.2340023954117302</v>
+        <v>-0.2119776236609336</v>
       </c>
       <c r="AE50" t="n">
-        <v>-0.2071436065339453</v>
+        <v>-0.2032422858847357</v>
       </c>
       <c r="AF50" t="n">
-        <v>-0.02685878887778492</v>
+        <v>-0.008735337776197949</v>
       </c>
       <c r="AG50" t="n">
         <v>4</v>
       </c>
       <c r="AH50" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AI50" t="b">
         <v>0</v>
@@ -7528,7 +7526,7 @@
         <v>1</v>
       </c>
       <c r="AM50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN50" t="b">
         <v>0</v>
@@ -7539,13 +7537,13 @@
         </is>
       </c>
       <c r="AP50" t="n">
-        <v>214.08</v>
+        <v>214.26</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -7564,7 +7562,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>11</v>
+        <v>10.8</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7573,7 +7571,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -7599,61 +7597,61 @@
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>5520</v>
+        <v>5615</v>
       </c>
       <c r="Q51" t="n">
-        <v>5520</v>
+        <v>5615</v>
       </c>
       <c r="R51" t="n">
-        <v>1656572</v>
+        <v>1016758</v>
       </c>
       <c r="S51" t="n">
-        <v>5939</v>
+        <v>5908</v>
       </c>
       <c r="T51" t="n">
+        <v>6168</v>
+      </c>
+      <c r="U51" t="n">
         <v>6272.25</v>
       </c>
-      <c r="U51" t="n">
-        <v>6346.25</v>
-      </c>
       <c r="V51" t="n">
-        <v>6419.510530598958</v>
+        <v>6396.621801757812</v>
       </c>
       <c r="W51" t="n">
-        <v>-164.0603804970815</v>
+        <v>-180.8567208930126</v>
       </c>
       <c r="X51" t="n">
-        <v>-164.8062218245705</v>
+        <v>-168.136781961946</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.7458413274890177</v>
+        <v>-12.71993893106657</v>
       </c>
       <c r="Z51" t="n">
-        <v>46.25658460945172</v>
+        <v>0.8205248754708236</v>
       </c>
       <c r="AA51" t="b">
         <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>-0.2114285714285714</v>
+        <v>-0.2707792207792208</v>
       </c>
       <c r="AC51" t="n">
-        <v>-0.2459907140143043</v>
+        <v>-0.1965169021121798</v>
       </c>
       <c r="AD51" t="n">
-        <v>-0.2638329038863064</v>
+        <v>-0.3156806773639873</v>
       </c>
       <c r="AE51" t="n">
-        <v>-0.3435182788861049</v>
+        <v>-0.2769517742329617</v>
       </c>
       <c r="AF51" t="n">
-        <v>0.07968537499979844</v>
+        <v>-0.03872890313102562</v>
       </c>
       <c r="AG51" t="n">
         <v>2</v>
       </c>
       <c r="AH51" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AI51" t="b">
         <v>0</v>
@@ -7662,24 +7660,22 @@
         <v>0</v>
       </c>
       <c r="AK51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM51" t="b">
         <v>0</v>
       </c>
       <c r="AN51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>5760.99</v>
       </c>
       <c r="AP51" t="n">
-        <v>8491.84</v>
+        <v>7862.11</v>
       </c>
     </row>
   </sheetData>

--- a/output/daily_screen_latest.xlsx
+++ b/output/daily_screen_latest.xlsx
@@ -643,17 +643,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>96.59999999999999</v>
+        <v>92.8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -671,15 +671,15 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>576000</v>
+        <v>5423000</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="K2" t="b">
         <v>0</v>
@@ -688,70 +688,70 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>476000</v>
+        <v>3741000</v>
       </c>
       <c r="N2" t="n">
-        <v>100000</v>
+        <v>1682000</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2100840336134454</v>
+        <v>0.4496124031007752</v>
       </c>
       <c r="P2" t="n">
-        <v>1710</v>
+        <v>1260</v>
       </c>
       <c r="Q2" t="n">
-        <v>1710</v>
+        <v>1260</v>
       </c>
       <c r="R2" t="n">
-        <v>1005302</v>
+        <v>16410298</v>
       </c>
       <c r="S2" t="n">
-        <v>1612</v>
+        <v>1239</v>
       </c>
       <c r="T2" t="n">
-        <v>1475.25</v>
+        <v>1119.7</v>
       </c>
       <c r="U2" t="n">
-        <v>1451</v>
+        <v>1108.2</v>
       </c>
       <c r="V2" t="n">
-        <v>1230.7</v>
+        <v>1032.166666666667</v>
       </c>
       <c r="W2" t="n">
-        <v>82.97786803840927</v>
+        <v>45.52015306233511</v>
       </c>
       <c r="X2" t="n">
-        <v>77.0385210835143</v>
+        <v>38.80155905895673</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.939346954894972</v>
+        <v>6.718594003378385</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.7257809581076344</v>
+        <v>6.251479909388813</v>
       </c>
       <c r="AA2" t="b">
         <v>1</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3959183673469389</v>
+        <v>0.2233009708737863</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.4553191489361703</v>
+        <v>0.3592233009708738</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.3510169107621723</v>
+        <v>0.1704486506883087</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.3748842768153884</v>
+        <v>0.2196783879846498</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.02386736605321604</v>
+        <v>-0.04922973729634106</v>
       </c>
       <c r="AG2" t="n">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="AH2" t="n">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="AI2" t="b">
         <v>1</v>
@@ -785,17 +785,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -804,24 +804,24 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>85</v>
+        <v>89.80000000000001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1000</v>
+        <v>1257000</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="K3" t="b">
         <v>0</v>
@@ -833,67 +833,67 @@
         <v>1000</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1256000</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1256</v>
       </c>
       <c r="P3" t="n">
-        <v>248</v>
+        <v>278</v>
       </c>
       <c r="Q3" t="n">
-        <v>248</v>
+        <v>278</v>
       </c>
       <c r="R3" t="n">
-        <v>21328932</v>
+        <v>32928968</v>
       </c>
       <c r="S3" t="n">
-        <v>233.9</v>
+        <v>265</v>
       </c>
       <c r="T3" t="n">
-        <v>207.475</v>
+        <v>251.55</v>
       </c>
       <c r="U3" t="n">
-        <v>204.5</v>
+        <v>249.175</v>
       </c>
       <c r="V3" t="n">
-        <v>184.3166666666667</v>
+        <v>225.6916666666667</v>
       </c>
       <c r="W3" t="n">
-        <v>13.03030260938419</v>
+        <v>8.03486025970949</v>
       </c>
       <c r="X3" t="n">
-        <v>8.753144333719984</v>
+        <v>5.450384237536567</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.27715827566421</v>
+        <v>2.584476022172923</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.106425522885155</v>
+        <v>1.653064123258493</v>
       </c>
       <c r="AA3" t="b">
         <v>1</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3156498673740054</v>
+        <v>0.2060737527114966</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.4376811594202898</v>
+        <v>0.2990654205607477</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.2707484107892388</v>
+        <v>0.1532214325260191</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.3572462872995079</v>
+        <v>0.1595205075745236</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.08649787651026908</v>
+        <v>-0.006299075048504577</v>
       </c>
       <c r="AG3" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="AH3" t="n">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="AI3" t="b">
         <v>1</v>
@@ -927,17 +927,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>80</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,15 +955,15 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3741000</v>
+        <v>1000</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="K4" t="b">
         <v>0</v>
@@ -972,7 +972,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3741000</v>
+        <v>1000</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -981,61 +981,61 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1285</v>
+        <v>290</v>
       </c>
       <c r="Q4" t="n">
-        <v>1285</v>
+        <v>290</v>
       </c>
       <c r="R4" t="n">
-        <v>9367345</v>
+        <v>12671498</v>
       </c>
       <c r="S4" t="n">
-        <v>1222</v>
+        <v>265</v>
       </c>
       <c r="T4" t="n">
-        <v>1095.2</v>
+        <v>220.225</v>
       </c>
       <c r="U4" t="n">
-        <v>1084.7</v>
+        <v>215.05</v>
       </c>
       <c r="V4" t="n">
-        <v>1020.366666666667</v>
+        <v>189.4416666666667</v>
       </c>
       <c r="W4" t="n">
-        <v>55.02725394546769</v>
+        <v>20.28426362802409</v>
       </c>
       <c r="X4" t="n">
-        <v>31.15292878370841</v>
+        <v>13.37434036417638</v>
       </c>
       <c r="Y4" t="n">
-        <v>23.87432516175928</v>
+        <v>6.909923263847713</v>
       </c>
       <c r="Z4" t="n">
-        <v>22.50880917369348</v>
+        <v>5.546905646867174</v>
       </c>
       <c r="AA4" t="b">
         <v>1</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1953488372093024</v>
+        <v>0.5549597855227881</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.2660098522167487</v>
+        <v>0.762917933130699</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.1504473806245359</v>
+        <v>0.5021074653373105</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.1855749800959667</v>
+        <v>0.6233730201444749</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.03512759947143085</v>
+        <v>-0.1212655548071644</v>
       </c>
       <c r="AG4" t="n">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AH4" t="n">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="AI4" t="b">
         <v>1</v>
@@ -1069,17 +1069,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>美律</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>74.80000000000001</v>
+        <v>66.2</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1097,24 +1097,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>6264000</v>
+        <v>1000</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="K5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="b">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>6264000</v>
+        <v>1000</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -1123,61 +1123,61 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2070</v>
+        <v>81.69999694824219</v>
       </c>
       <c r="Q5" t="n">
-        <v>2070</v>
+        <v>81.69999694824219</v>
       </c>
       <c r="R5" t="n">
-        <v>4215519</v>
+        <v>2468795</v>
       </c>
       <c r="S5" t="n">
-        <v>2035</v>
+        <v>80.67999877929688</v>
       </c>
       <c r="T5" t="n">
-        <v>1913.75</v>
+        <v>78.18999938964843</v>
       </c>
       <c r="U5" t="n">
-        <v>1908</v>
+        <v>77.92999954223633</v>
       </c>
       <c r="V5" t="n">
-        <v>2079.181504313151</v>
+        <v>77.76605288187663</v>
       </c>
       <c r="W5" t="n">
-        <v>26.49924756545602</v>
+        <v>0.998635261325461</v>
       </c>
       <c r="X5" t="n">
-        <v>-10.61130674659506</v>
+        <v>0.3361840202081899</v>
       </c>
       <c r="Y5" t="n">
-        <v>37.11055431205108</v>
+        <v>0.6624512411172711</v>
       </c>
       <c r="Z5" t="n">
-        <v>36.87384118988113</v>
+        <v>0.6292901449636699</v>
       </c>
       <c r="AA5" t="b">
         <v>1</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.05882352941176472</v>
+        <v>0.06797381631689126</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.08491876024900014</v>
+        <v>0.04722423404130893</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.0139220728269982</v>
+        <v>0.01512149613141367</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.1653536323697821</v>
+        <v>-0.09232067894491514</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.1792757051967803</v>
+        <v>0.1074421750763288</v>
       </c>
       <c r="AG5" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AH5" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="AI5" t="b">
         <v>1</v>
@@ -1211,17 +1211,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>慧洋-KY</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>71.80000000000001</v>
+        <v>65</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1239,15 +1239,15 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2185000</v>
+        <v>1000</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="K6" t="b">
         <v>0</v>
@@ -1256,7 +1256,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2185000</v>
+        <v>1000</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1265,61 +1265,61 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>245.5</v>
+        <v>103.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>245.5</v>
+        <v>103.5</v>
       </c>
       <c r="R6" t="n">
-        <v>3521276</v>
+        <v>2142600</v>
       </c>
       <c r="S6" t="n">
-        <v>239.7</v>
+        <v>100.7400009155273</v>
       </c>
       <c r="T6" t="n">
-        <v>229.75</v>
+        <v>99.76500053405762</v>
       </c>
       <c r="U6" t="n">
-        <v>228.625</v>
+        <v>99.64000053405762</v>
       </c>
       <c r="V6" t="n">
-        <v>208.6583333333333</v>
+        <v>93.0800001780192</v>
       </c>
       <c r="W6" t="n">
-        <v>5.380381729851706</v>
+        <v>1.047662876527113</v>
       </c>
       <c r="X6" t="n">
-        <v>4.247638080892163</v>
+        <v>0.4947362912651968</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.132743648959543</v>
+        <v>0.5529265852619162</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.7596951864816601</v>
+        <v>0.3742314709814334</v>
       </c>
       <c r="AA6" t="b">
         <v>1</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.100896860986547</v>
+        <v>0.02475247524752477</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.08869179600886912</v>
+        <v>0.3035264233120469</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.05599540440178052</v>
+        <v>-0.02809984493795281</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.008256923888087186</v>
+        <v>0.1639815103258229</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.04773848051369334</v>
+        <v>-0.1920813552637757</v>
       </c>
       <c r="AG6" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="AH6" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="AI6" t="b">
         <v>1</v>
@@ -1353,17 +1353,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1372,7 +1372,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>71.40000000000001</v>
+        <v>62.40000000000001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1381,15 +1381,15 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1000</v>
+        <v>5163000</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K7" t="b">
         <v>0</v>
@@ -1398,7 +1398,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1000</v>
+        <v>5163000</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1407,61 +1407,61 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>4345</v>
+        <v>19.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>4345</v>
+        <v>19.5</v>
       </c>
       <c r="R7" t="n">
-        <v>4365838</v>
+        <v>103473086</v>
       </c>
       <c r="S7" t="n">
-        <v>4095</v>
+        <v>19.15000038146973</v>
       </c>
       <c r="T7" t="n">
-        <v>3765.5</v>
+        <v>18.88500003814697</v>
       </c>
       <c r="U7" t="n">
-        <v>3749.75</v>
+        <v>18.85500001907349</v>
       </c>
       <c r="V7" t="n">
-        <v>3715.481892903646</v>
+        <v>19.0084774017334</v>
       </c>
       <c r="W7" t="n">
-        <v>128.5875693574299</v>
+        <v>0.1074057745653505</v>
       </c>
       <c r="X7" t="n">
-        <v>37.42860111459054</v>
+        <v>0.03187025101903523</v>
       </c>
       <c r="Y7" t="n">
-        <v>91.15896824283931</v>
+        <v>0.07553552354631526</v>
       </c>
       <c r="Z7" t="n">
-        <v>79.41225003074777</v>
+        <v>0.0480152599160486</v>
       </c>
       <c r="AA7" t="b">
         <v>1</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.07816377171215882</v>
+        <v>0.03174605257036434</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.1755599840679241</v>
+        <v>0.0538527216428597</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.03326231512739231</v>
+        <v>-0.02110626761511325</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.09512511194714213</v>
+        <v>-0.08569219134336437</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.06186279681974982</v>
+        <v>0.06458592372825112</v>
       </c>
       <c r="AG7" t="n">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="AH7" t="n">
-        <v>56.00000000000001</v>
+        <v>32</v>
       </c>
       <c r="AI7" t="b">
         <v>1</v>
@@ -1495,43 +1495,43 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>66.40000000000001</v>
+        <v>56.2</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3921000</v>
+        <v>957000</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="K8" t="b">
         <v>0</v>
@@ -1540,70 +1540,70 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3921000</v>
+        <v>1000</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>956000</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>956</v>
       </c>
       <c r="P8" t="n">
-        <v>87.90000152587891</v>
+        <v>588</v>
       </c>
       <c r="Q8" t="n">
-        <v>87.90000152587891</v>
+        <v>588</v>
       </c>
       <c r="R8" t="n">
-        <v>1839492</v>
+        <v>10276874</v>
       </c>
       <c r="S8" t="n">
-        <v>86.56000061035157</v>
+        <v>569.8</v>
       </c>
       <c r="T8" t="n">
-        <v>83.76500015258789</v>
+        <v>571.95</v>
       </c>
       <c r="U8" t="n">
-        <v>83.45499992370605</v>
+        <v>569.1</v>
       </c>
       <c r="V8" t="n">
-        <v>84.62833340962727</v>
+        <v>533.4</v>
       </c>
       <c r="W8" t="n">
-        <v>1.180500657494377</v>
+        <v>-1.361580484362321</v>
       </c>
       <c r="X8" t="n">
-        <v>0.5715802605307824</v>
+        <v>-0.1158319843365309</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.6089203969635951</v>
+        <v>-1.24574850002579</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.5916726558987484</v>
+        <v>-4.325882074213004</v>
       </c>
       <c r="AA8" t="b">
         <v>1</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.07588745176532252</v>
+        <v>0.1073446327683616</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.08627854143102387</v>
+        <v>0.651685393258427</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.030985995180556</v>
+        <v>0.05449231258288401</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0.1667134135518058</v>
+        <v>0.5121404802722029</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.1976994087323618</v>
+        <v>-0.4576481676893189</v>
       </c>
       <c r="AG8" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AH8" t="n">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="AI8" t="b">
         <v>1</v>
@@ -1612,21 +1612,19 @@
         <v>1</v>
       </c>
       <c r="AK8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="b">
         <v>1</v>
       </c>
       <c r="AN8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>602.11</v>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
@@ -1637,26 +1635,26 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>美律</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>66.40000000000001</v>
+        <v>34</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1665,7 +1663,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1673,7 +1671,7 @@
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="K9" t="b">
         <v>0</v>
@@ -1691,61 +1689,61 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>80.59999847412109</v>
+        <v>561</v>
       </c>
       <c r="Q9" t="n">
-        <v>80.59999847412109</v>
+        <v>561</v>
       </c>
       <c r="R9" t="n">
-        <v>4195712</v>
+        <v>1533903</v>
       </c>
       <c r="S9" t="n">
-        <v>77.09999847412109</v>
+        <v>557.4</v>
       </c>
       <c r="T9" t="n">
-        <v>77.41499938964844</v>
+        <v>561</v>
       </c>
       <c r="U9" t="n">
-        <v>77.18999938964843</v>
+        <v>559.35</v>
       </c>
       <c r="V9" t="n">
-        <v>77.72045682271322</v>
+        <v>567.8911356608073</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1898344106328409</v>
+        <v>-1.852330075783925</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1164382004989899</v>
+        <v>0.141192790863952</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.3062726111318308</v>
+        <v>-1.993522866647877</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.05456562237789048</v>
+        <v>-2.903465704255706</v>
       </c>
       <c r="AA9" t="b">
         <v>1</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.05913272129079328</v>
+        <v>0.0625</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.01372645471432254</v>
+        <v>-0.02616415481018919</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.01423126470602676</v>
+        <v>0.009647679814522414</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.09416132683510448</v>
+        <v>-0.1657090677964133</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.1083925915411312</v>
+        <v>0.1753567476109357</v>
       </c>
       <c r="AG9" t="n">
         <v>46</v>
       </c>
       <c r="AH9" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="AI9" t="b">
         <v>1</v>
@@ -1754,21 +1752,19 @@
         <v>1</v>
       </c>
       <c r="AK9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="b">
         <v>1</v>
       </c>
       <c r="AN9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>583.4400000000001</v>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
@@ -1779,26 +1775,26 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3376</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>新日興</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>64</v>
+        <v>25.8</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1807,15 +1803,15 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1000</v>
+        <v>1740000</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="K10" t="b">
         <v>0</v>
@@ -1824,7 +1820,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1000</v>
+        <v>1740000</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1833,67 +1829,67 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>532</v>
+        <v>179</v>
       </c>
       <c r="Q10" t="n">
-        <v>532</v>
+        <v>179</v>
       </c>
       <c r="R10" t="n">
-        <v>62652164</v>
+        <v>4312080</v>
       </c>
       <c r="S10" t="n">
-        <v>525.4</v>
+        <v>172</v>
       </c>
       <c r="T10" t="n">
-        <v>508.85</v>
+        <v>174.5</v>
       </c>
       <c r="U10" t="n">
-        <v>508.8</v>
+        <v>174.7</v>
       </c>
       <c r="V10" t="n">
-        <v>481.4833333333333</v>
+        <v>184.6438100179036</v>
       </c>
       <c r="W10" t="n">
-        <v>6.012612400293733</v>
+        <v>-2.48259728227336</v>
       </c>
       <c r="X10" t="n">
-        <v>4.377897653998013</v>
+        <v>-3.928997058795846</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.63471474629572</v>
+        <v>1.446399776522485</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.044726856239138</v>
+        <v>0.5842192240967341</v>
       </c>
       <c r="AA10" t="b">
         <v>1</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.001883239171374784</v>
+        <v>-0.02185792349726778</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.1875</v>
+        <v>-0.02162852631582457</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0.04301821741339173</v>
+        <v>-0.07471024368274537</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.1070651278792181</v>
+        <v>-0.1611734393020486</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.1500833452926098</v>
+        <v>0.08646319561930327</v>
       </c>
       <c r="AG10" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="AH10" t="n">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="AI10" t="b">
         <v>1</v>
       </c>
       <c r="AJ10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="b">
         <v>1</v>
@@ -1912,52 +1908,50 @@
           <t>Already &gt; 0</t>
         </is>
       </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+      <c r="AP10" t="n">
+        <v>176.26</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1000</v>
+        <v>751000</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="K11" t="b">
         <v>0</v>
@@ -1966,70 +1960,70 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1000</v>
+        <v>684000</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>67000</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>0.097953216374269</v>
       </c>
       <c r="P11" t="n">
-        <v>256</v>
+        <v>8245</v>
       </c>
       <c r="Q11" t="n">
-        <v>256</v>
+        <v>8245</v>
       </c>
       <c r="R11" t="n">
-        <v>15828004</v>
+        <v>1133985</v>
       </c>
       <c r="S11" t="n">
-        <v>247.7</v>
+        <v>8252</v>
       </c>
       <c r="T11" t="n">
-        <v>245.775</v>
+        <v>7757.75</v>
       </c>
       <c r="U11" t="n">
-        <v>244.225</v>
+        <v>7651.5</v>
       </c>
       <c r="V11" t="n">
-        <v>223.3083333333333</v>
+        <v>5969</v>
       </c>
       <c r="W11" t="n">
-        <v>3.207807590599231</v>
+        <v>323.9931377694083</v>
       </c>
       <c r="X11" t="n">
-        <v>4.120821403604955</v>
+        <v>434.2284243611859</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0.9130138130057244</v>
+        <v>-110.2352865917775</v>
       </c>
       <c r="Z11" t="n">
-        <v>-1.878619802900569</v>
+        <v>-107.6311878784226</v>
       </c>
       <c r="AA11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.1377777777777778</v>
+        <v>0.3472222222222223</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.1770114942528735</v>
+        <v>1.14993481095176</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.09287632119301126</v>
+        <v>0.2943699020367447</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.09657662213209162</v>
+        <v>1.010389897965536</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.003700300939080359</v>
+        <v>-0.7160199959287912</v>
       </c>
       <c r="AG11" t="n">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="AH11" t="n">
-        <v>57.99999999999999</v>
+        <v>98</v>
       </c>
       <c r="AI11" t="b">
         <v>1</v>
@@ -2044,13 +2038,13 @@
         <v>0</v>
       </c>
       <c r="AM11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="b">
         <v>1</v>
       </c>
       <c r="AO11" t="n">
-        <v>266.75</v>
+        <v>9498.24</v>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
@@ -2061,43 +2055,43 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>45.2</v>
+        <v>55</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>4143450</v>
+        <v>696000</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="K12" t="b">
         <v>0</v>
@@ -2106,70 +2100,70 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4143450</v>
+        <v>576000</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>120000</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="P12" t="n">
-        <v>304.5</v>
+        <v>1685</v>
       </c>
       <c r="Q12" t="n">
-        <v>304.5</v>
+        <v>1685</v>
       </c>
       <c r="R12" t="n">
-        <v>50698074</v>
+        <v>3879459</v>
       </c>
       <c r="S12" t="n">
-        <v>298.3</v>
+        <v>1695</v>
       </c>
       <c r="T12" t="n">
-        <v>287.55</v>
+        <v>1532.5</v>
       </c>
       <c r="U12" t="n">
-        <v>285.75</v>
+        <v>1514.75</v>
       </c>
       <c r="V12" t="n">
-        <v>264.188899230957</v>
+        <v>1260.616666666667</v>
       </c>
       <c r="W12" t="n">
-        <v>6.829051716343827</v>
+        <v>80.96075557069071</v>
       </c>
       <c r="X12" t="n">
-        <v>7.862826617558136</v>
+        <v>80.57440751771853</v>
       </c>
       <c r="Y12" t="n">
-        <v>-1.03377490121431</v>
+        <v>0.3863480529721812</v>
       </c>
       <c r="Z12" t="n">
-        <v>-1.455182243346336</v>
+        <v>6.051104642281345</v>
       </c>
       <c r="AA12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.1340782122905029</v>
+        <v>0.2669172932330828</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.1010153697475495</v>
+        <v>0.6600985221674878</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.08917675570573635</v>
+        <v>0.2140649730476052</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.02058049762676761</v>
+        <v>0.5205536091812637</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.06859625807896874</v>
+        <v>-0.3064886361336585</v>
       </c>
       <c r="AG12" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AH12" t="n">
-        <v>46</v>
+        <v>92</v>
       </c>
       <c r="AI12" t="b">
         <v>1</v>
@@ -2178,19 +2172,21 @@
         <v>1</v>
       </c>
       <c r="AK12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>316.68</v>
+        <v>0</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
@@ -2201,26 +2197,26 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>31.8</v>
+        <v>54.59999999999999</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2229,24 +2225,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4315561</v>
+        <v>6847000</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="b">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4315561</v>
+        <v>6847000</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -2255,58 +2251,58 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2240</v>
+        <v>1735</v>
       </c>
       <c r="Q13" t="n">
-        <v>2240</v>
+        <v>1735</v>
       </c>
       <c r="R13" t="n">
-        <v>2004552</v>
+        <v>9715675</v>
       </c>
       <c r="S13" t="n">
-        <v>2201</v>
+        <v>1717</v>
       </c>
       <c r="T13" t="n">
-        <v>2189.75</v>
+        <v>1549.75</v>
       </c>
       <c r="U13" t="n">
-        <v>2194.75</v>
+        <v>1531.25</v>
       </c>
       <c r="V13" t="n">
-        <v>2107.122220865886</v>
+        <v>1445.083333333333</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.1643745962546745</v>
+        <v>72.44399649225033</v>
       </c>
       <c r="X13" t="n">
-        <v>-23.48913080485683</v>
+        <v>64.76664942440942</v>
       </c>
       <c r="Y13" t="n">
-        <v>23.32475620860216</v>
+        <v>7.677347067840913</v>
       </c>
       <c r="Z13" t="n">
-        <v>21.63347848140634</v>
+        <v>10.61132065076194</v>
       </c>
       <c r="AA13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0.04273504273504269</v>
+        <v>0.271062271062271</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.3621732737721026</v>
+        <v>0.482905982905983</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0.08763649931980921</v>
+        <v>0.2182099508767934</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.2817384016513207</v>
+        <v>0.3433610699197589</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.3693749009711299</v>
+        <v>-0.1251511190429655</v>
       </c>
       <c r="AG13" t="n">
-        <v>14</v>
+        <v>92</v>
       </c>
       <c r="AH13" t="n">
         <v>80</v>
@@ -2315,7 +2311,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK13" t="b">
         <v>1</v>
@@ -2324,7 +2320,7 @@
         <v>1</v>
       </c>
       <c r="AM13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="b">
         <v>0</v>
@@ -2334,33 +2330,35 @@
           <t>Already &gt; 0</t>
         </is>
       </c>
-      <c r="AP13" t="n">
-        <v>2272.11</v>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>29</v>
+        <v>53.2</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2369,24 +2367,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>420000</v>
+        <v>8937000</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="K14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="b">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>420000</v>
+        <v>8937000</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2395,67 +2393,67 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>3320</v>
+        <v>1430</v>
       </c>
       <c r="Q14" t="n">
-        <v>3320</v>
+        <v>1430</v>
       </c>
       <c r="R14" t="n">
-        <v>1335112</v>
+        <v>7127829</v>
       </c>
       <c r="S14" t="n">
-        <v>3114</v>
+        <v>1453</v>
       </c>
       <c r="T14" t="n">
-        <v>3304.25</v>
+        <v>1292</v>
       </c>
       <c r="U14" t="n">
-        <v>3319.25</v>
+        <v>1274.5</v>
       </c>
       <c r="V14" t="n">
-        <v>2966.666666666667</v>
+        <v>1182.666666666667</v>
       </c>
       <c r="W14" t="n">
-        <v>-37.47822864447608</v>
+        <v>70.32980500721828</v>
       </c>
       <c r="X14" t="n">
-        <v>-16.91659066177584</v>
+        <v>73.1931760652168</v>
       </c>
       <c r="Y14" t="n">
-        <v>-20.56163798270023</v>
+        <v>-2.863371057998521</v>
       </c>
       <c r="Z14" t="n">
-        <v>-55.36148206138292</v>
+        <v>4.898533654461474</v>
       </c>
       <c r="AA14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0.08287292817679559</v>
+        <v>0.3240740740740742</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.2296296296296296</v>
+        <v>0.2434782608695651</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0.1277743847615621</v>
+        <v>0.2712217538885966</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.1491947575088477</v>
+        <v>0.1039333478833411</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.2769691422704098</v>
+        <v>0.1672884060052555</v>
       </c>
       <c r="AG14" t="n">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="AH14" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="AI14" t="b">
         <v>1</v>
       </c>
       <c r="AJ14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK14" t="b">
         <v>0</v>
@@ -2464,41 +2462,43 @@
         <v>0</v>
       </c>
       <c r="AM14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="b">
         <v>1</v>
       </c>
       <c r="AO14" t="n">
-        <v>3552.4</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>3593.42</v>
+        <v>1464.32</v>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>25.6</v>
+        <v>51.8</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2507,24 +2507,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2504000</v>
+        <v>18721000</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="K15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="b">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2504000</v>
+        <v>18721000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2533,103 +2533,103 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>5575</v>
+        <v>1185</v>
       </c>
       <c r="Q15" t="n">
-        <v>5575</v>
+        <v>1185</v>
       </c>
       <c r="R15" t="n">
-        <v>471574</v>
+        <v>17256069</v>
       </c>
       <c r="S15" t="n">
-        <v>5521</v>
+        <v>1239</v>
       </c>
       <c r="T15" t="n">
-        <v>5480.5</v>
+        <v>1148.9</v>
       </c>
       <c r="U15" t="n">
-        <v>5491.5</v>
+        <v>1138.5</v>
       </c>
       <c r="V15" t="n">
-        <v>5605.083333333333</v>
+        <v>1026.05</v>
       </c>
       <c r="W15" t="n">
-        <v>16.33612059439474</v>
+        <v>38.54525784691191</v>
       </c>
       <c r="X15" t="n">
-        <v>-22.81682223276735</v>
+        <v>54.6349543198464</v>
       </c>
       <c r="Y15" t="n">
-        <v>39.15294282716209</v>
+        <v>-16.08969647293449</v>
       </c>
       <c r="Z15" t="n">
-        <v>34.54669746988481</v>
+        <v>-8.873617902620666</v>
       </c>
       <c r="AA15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0.03796376186367556</v>
+        <v>0.2128966223132036</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.1206624605678234</v>
+        <v>0.4924433249370277</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0.08286521844844208</v>
+        <v>0.160044302127726</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0.2010973326886053</v>
+        <v>0.3528984119508036</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.1182321142401632</v>
+        <v>-0.1928541098230776</v>
       </c>
       <c r="AG15" t="n">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="AH15" t="n">
-        <v>12</v>
+        <v>82</v>
       </c>
       <c r="AI15" t="b">
         <v>1</v>
       </c>
       <c r="AJ15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
-      <c r="AP15" t="n">
-        <v>5515.53</v>
+        <v>1</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1367.49</v>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2638,24 +2638,24 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>62</v>
+        <v>48.6</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>6847000</v>
+        <v>8348000</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K16" t="b">
         <v>1</v>
@@ -2664,70 +2664,70 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>6771000</v>
+        <v>8348000</v>
       </c>
       <c r="N16" t="n">
-        <v>76000</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0.01122433909319155</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1740</v>
+        <v>747</v>
       </c>
       <c r="Q16" t="n">
-        <v>1740</v>
+        <v>747</v>
       </c>
       <c r="R16" t="n">
-        <v>7551964</v>
+        <v>12849867</v>
       </c>
       <c r="S16" t="n">
-        <v>1723</v>
+        <v>745</v>
       </c>
       <c r="T16" t="n">
-        <v>1498.75</v>
+        <v>691.65</v>
       </c>
       <c r="U16" t="n">
-        <v>1479</v>
+        <v>685.2</v>
       </c>
       <c r="V16" t="n">
-        <v>1424.666666666667</v>
+        <v>631.3166666666667</v>
       </c>
       <c r="W16" t="n">
-        <v>86.18626585246943</v>
+        <v>26.13292204039101</v>
       </c>
       <c r="X16" t="n">
-        <v>53.95313981159023</v>
+        <v>26.24426837605197</v>
       </c>
       <c r="Y16" t="n">
-        <v>32.2331260408792</v>
+        <v>-0.1113463356609614</v>
       </c>
       <c r="Z16" t="n">
-        <v>37.89438774615367</v>
+        <v>1.371883322852828</v>
       </c>
       <c r="AA16" t="b">
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.2936802973977695</v>
+        <v>0.2087378640776698</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.2473118279569892</v>
+        <v>0.216612377850163</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.2487788408130029</v>
+        <v>0.1558855438921922</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.1668769558362073</v>
+        <v>0.07706746486393889</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.08190188497679562</v>
+        <v>0.07881807902825333</v>
       </c>
       <c r="AG16" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AH16" t="n">
-        <v>68</v>
+        <v>56.00000000000001</v>
       </c>
       <c r="AI16" t="b">
         <v>1</v>
@@ -2736,21 +2736,19 @@
         <v>1</v>
       </c>
       <c r="AK16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="b">
         <v>0</v>
       </c>
       <c r="AN16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>748.49</v>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
@@ -2761,17 +2759,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2780,7 +2778,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>55.8</v>
+        <v>44.8</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2789,24 +2787,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>18721000</v>
+        <v>2502000</v>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="K17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="b">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>18721000</v>
+        <v>2502000</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2815,61 +2813,61 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1270</v>
+        <v>7070</v>
       </c>
       <c r="Q17" t="n">
-        <v>1270</v>
+        <v>7070</v>
       </c>
       <c r="R17" t="n">
-        <v>8192303</v>
+        <v>1166967</v>
       </c>
       <c r="S17" t="n">
-        <v>1303</v>
+        <v>7038</v>
       </c>
       <c r="T17" t="n">
-        <v>1116.1</v>
+        <v>6452.25</v>
       </c>
       <c r="U17" t="n">
-        <v>1100.3</v>
+        <v>6387</v>
       </c>
       <c r="V17" t="n">
-        <v>1009.25</v>
+        <v>5308.475553385417</v>
       </c>
       <c r="W17" t="n">
-        <v>72.79097685392844</v>
+        <v>294.1159394812348</v>
       </c>
       <c r="X17" t="n">
-        <v>59.82847066588712</v>
+        <v>321.3708312137852</v>
       </c>
       <c r="Y17" t="n">
-        <v>12.96250618804132</v>
+        <v>-27.25489173255033</v>
       </c>
       <c r="Z17" t="n">
-        <v>22.36776821978445</v>
+        <v>-12.68443595476111</v>
       </c>
       <c r="AA17" t="b">
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.3312368972746331</v>
+        <v>0.2263660017346054</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.4530892448512587</v>
+        <v>1.216167287618883</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.2863354406898666</v>
+        <v>0.1735136815491278</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.3726543727304767</v>
+        <v>1.076622374632659</v>
       </c>
       <c r="AF17" t="n">
-        <v>-0.08631893204061014</v>
+        <v>-0.9031086930835315</v>
       </c>
       <c r="AG17" t="n">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="AH17" t="n">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="AI17" t="b">
         <v>1</v>
@@ -2878,21 +2876,19 @@
         <v>1</v>
       </c>
       <c r="AK17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="b">
         <v>0</v>
       </c>
       <c r="AN17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>7381.08</v>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
@@ -2903,17 +2899,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2922,7 +2918,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>54.4</v>
+        <v>44</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2931,24 +2927,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>8937000</v>
+        <v>121000</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="K18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="b">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>8937000</v>
+        <v>121000</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2957,61 +2953,61 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1475</v>
+        <v>1540</v>
       </c>
       <c r="Q18" t="n">
-        <v>1475</v>
+        <v>1540</v>
       </c>
       <c r="R18" t="n">
-        <v>5186570</v>
+        <v>3383472</v>
       </c>
       <c r="S18" t="n">
-        <v>1483</v>
+        <v>1575</v>
       </c>
       <c r="T18" t="n">
-        <v>1239.5</v>
+        <v>1356</v>
       </c>
       <c r="U18" t="n">
-        <v>1217</v>
+        <v>1341.5</v>
       </c>
       <c r="V18" t="n">
-        <v>1174.833333333333</v>
+        <v>1236.421700032552</v>
       </c>
       <c r="W18" t="n">
-        <v>94.89482404399837</v>
+        <v>84.39561651347435</v>
       </c>
       <c r="X18" t="n">
-        <v>69.19340418182574</v>
+        <v>60.36767099556356</v>
       </c>
       <c r="Y18" t="n">
-        <v>25.70141986217263</v>
+        <v>24.02794551791079</v>
       </c>
       <c r="Z18" t="n">
-        <v>35.0406669860459</v>
+        <v>37.27658646366756</v>
       </c>
       <c r="AA18" t="b">
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.4390243902439024</v>
+        <v>0.232</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.1434108527131783</v>
+        <v>0.5995645463044539</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.3941229336591359</v>
+        <v>0.1791476798145224</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.0629759805923964</v>
+        <v>0.4600196333182298</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.3311469530667395</v>
+        <v>-0.2808719535037074</v>
       </c>
       <c r="AG18" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="AH18" t="n">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="AI18" t="b">
         <v>1</v>
@@ -3045,17 +3041,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3064,96 +3060,96 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>51.2</v>
+        <v>41.8</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>6147000</v>
+        <v>1000</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="K19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="b">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>6062000</v>
+        <v>1000</v>
       </c>
       <c r="N19" t="n">
-        <v>85000</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0140217749917519</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>3440</v>
+        <v>117</v>
       </c>
       <c r="Q19" t="n">
-        <v>3440</v>
+        <v>117</v>
       </c>
       <c r="R19" t="n">
-        <v>2974272</v>
+        <v>19316431</v>
       </c>
       <c r="S19" t="n">
-        <v>3539</v>
+        <v>122.5</v>
       </c>
       <c r="T19" t="n">
-        <v>3414.75</v>
+        <v>109.5899997711182</v>
       </c>
       <c r="U19" t="n">
-        <v>3407</v>
+        <v>108.0749996185303</v>
       </c>
       <c r="V19" t="n">
-        <v>3003.297257486979</v>
+        <v>95.84833323160807</v>
       </c>
       <c r="W19" t="n">
-        <v>59.45425389528509</v>
+        <v>5.513674701193992</v>
       </c>
       <c r="X19" t="n">
-        <v>66.5320690986633</v>
+        <v>6.870306420542656</v>
       </c>
       <c r="Y19" t="n">
-        <v>-7.077815203378208</v>
+        <v>-1.356631719348664</v>
       </c>
       <c r="Z19" t="n">
-        <v>8.969634177185867</v>
+        <v>-0.5616496764729142</v>
       </c>
       <c r="AA19" t="b">
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.04718417047184165</v>
+        <v>0.349481016358584</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.632267608554373</v>
+        <v>0.05882352941176472</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.002282713887075127</v>
+        <v>0.2966286961731064</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.5518327364335911</v>
+        <v>-0.08072138357445935</v>
       </c>
       <c r="AF19" t="n">
-        <v>-0.549550022546516</v>
+        <v>0.3773500797475657</v>
       </c>
       <c r="AG19" t="n">
-        <v>42</v>
+        <v>98</v>
       </c>
       <c r="AH19" t="n">
-        <v>94</v>
+        <v>34</v>
       </c>
       <c r="AI19" t="b">
         <v>1</v>
@@ -3174,7 +3170,7 @@
         <v>1</v>
       </c>
       <c r="AO19" t="n">
-        <v>3522.56</v>
+        <v>132.44</v>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
@@ -3185,17 +3181,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3204,7 +3200,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>48.6</v>
+        <v>41.2</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3213,87 +3209,87 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>8348000</v>
+        <v>23519000</v>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" t="b">
+        <v>1</v>
+      </c>
+      <c r="L20" t="b">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>23519000</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>627</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>627</v>
+      </c>
+      <c r="R20" t="n">
+        <v>47584088</v>
+      </c>
+      <c r="S20" t="n">
+        <v>628.8</v>
+      </c>
+      <c r="T20" t="n">
+        <v>584.85</v>
+      </c>
+      <c r="U20" t="n">
+        <v>580.7</v>
+      </c>
+      <c r="V20" t="n">
+        <v>579.9416666666667</v>
+      </c>
+      <c r="W20" t="n">
+        <v>15.82987909852648</v>
+      </c>
+      <c r="X20" t="n">
+        <v>14.2575297092487</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.572349389277775</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.427555285448655</v>
+      </c>
+      <c r="AA20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.1525735294117647</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>-0.1030042918454935</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.09972120922628713</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>-0.2425492048317176</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0.3422704140580047</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>72</v>
+      </c>
+      <c r="AH20" t="n">
         <v>6</v>
-      </c>
-      <c r="K20" t="b">
-        <v>1</v>
-      </c>
-      <c r="L20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>8348000</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>744</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>744</v>
-      </c>
-      <c r="R20" t="n">
-        <v>15126846</v>
-      </c>
-      <c r="S20" t="n">
-        <v>735</v>
-      </c>
-      <c r="T20" t="n">
-        <v>674.6</v>
-      </c>
-      <c r="U20" t="n">
-        <v>668.3</v>
-      </c>
-      <c r="V20" t="n">
-        <v>626.8166666666667</v>
-      </c>
-      <c r="W20" t="n">
-        <v>28.72195570530857</v>
-      </c>
-      <c r="X20" t="n">
-        <v>24.9195795682236</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>3.80237613708497</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>4.818665858427057</v>
-      </c>
-      <c r="AA20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0.203883495145631</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0.1606864274570983</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0.1589820385608645</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0.08025155533631634</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>0.07873048322454812</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>80</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>50</v>
       </c>
       <c r="AI20" t="b">
         <v>1</v>
@@ -3327,17 +3323,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3346,7 +3342,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>48.2</v>
+        <v>38.40000000000001</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3355,15 +3351,15 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>684000</v>
+        <v>2887848</v>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="K21" t="b">
         <v>0</v>
@@ -3372,7 +3368,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>684000</v>
+        <v>2887848</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -3381,64 +3377,64 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>8360</v>
+        <v>2235</v>
       </c>
       <c r="Q21" t="n">
-        <v>8360</v>
+        <v>2235</v>
       </c>
       <c r="R21" t="n">
-        <v>1159259</v>
+        <v>1806449</v>
       </c>
       <c r="S21" t="n">
-        <v>8339</v>
+        <v>2305</v>
       </c>
       <c r="T21" t="n">
-        <v>7449.25</v>
+        <v>2292.25</v>
       </c>
       <c r="U21" t="n">
-        <v>7329.25</v>
+        <v>2274.25</v>
       </c>
       <c r="V21" t="n">
-        <v>5764</v>
+        <v>2187.25</v>
       </c>
       <c r="W21" t="n">
-        <v>473.5036091335342</v>
+        <v>15.6507890384496</v>
       </c>
       <c r="X21" t="n">
-        <v>508.557983686262</v>
+        <v>54.02445790860366</v>
       </c>
       <c r="Y21" t="n">
-        <v>-35.05437455272789</v>
+        <v>-38.37366887015406</v>
       </c>
       <c r="Z21" t="n">
-        <v>-9.566549806802186</v>
+        <v>-31.54489498427109</v>
       </c>
       <c r="AA21" t="b">
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.4026845637583893</v>
+        <v>0.1919999999999999</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.079601990049751</v>
+        <v>0.2662889518413598</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.3577831071736228</v>
+        <v>0.1391476798145224</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.9991671179289694</v>
+        <v>0.1267440388551357</v>
       </c>
       <c r="AF21" t="n">
-        <v>-0.6413840107553466</v>
+        <v>0.01240364095938662</v>
       </c>
       <c r="AG21" t="n">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AH21" t="n">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="AI21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="b">
         <v>1</v>
@@ -3453,10 +3449,10 @@
         <v>0</v>
       </c>
       <c r="AN21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
-        <v>8761.280000000001</v>
+        <v>2668.59</v>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
@@ -3467,17 +3463,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3486,7 +3482,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>45.6</v>
+        <v>38</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3495,24 +3491,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1000</v>
+        <v>7389000</v>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="K22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" t="b">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1000</v>
+        <v>7389000</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -3521,84 +3517,82 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>128</v>
+        <v>1785</v>
       </c>
       <c r="Q22" t="n">
-        <v>128</v>
+        <v>1785</v>
       </c>
       <c r="R22" t="n">
-        <v>36560090</v>
+        <v>9678701</v>
       </c>
       <c r="S22" t="n">
-        <v>127</v>
+        <v>1883</v>
       </c>
       <c r="T22" t="n">
-        <v>105.2449996948242</v>
+        <v>1849.5</v>
       </c>
       <c r="U22" t="n">
-        <v>103.3599998474121</v>
+        <v>1841.25</v>
       </c>
       <c r="V22" t="n">
-        <v>95.69833323160807</v>
+        <v>1782.666666666667</v>
       </c>
       <c r="W22" t="n">
-        <v>9.055134634424562</v>
+        <v>6.564216920404306</v>
       </c>
       <c r="X22" t="n">
-        <v>7.134456094994352</v>
+        <v>32.97346801310261</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.920678539430209</v>
+        <v>-26.40925109269831</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.494050303769871</v>
+        <v>-17.67279507101218</v>
       </c>
       <c r="AA22" t="b">
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.4174971835453145</v>
+        <v>0.1018518518518519</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.2307692307692308</v>
+        <v>0.02586206896551735</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.372595726960548</v>
+        <v>0.04899953166637427</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.1503343586484489</v>
+        <v>-0.1136828440207067</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.2222613683120991</v>
+        <v>0.162682375687081</v>
       </c>
       <c r="AG22" t="n">
-        <v>98</v>
+        <v>56.00000000000001</v>
       </c>
       <c r="AH22" t="n">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="AI22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="b">
         <v>1</v>
       </c>
       <c r="AK22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="b">
         <v>0</v>
       </c>
       <c r="AN22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>2084.88</v>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
@@ -3609,17 +3603,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3628,24 +3622,24 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>45.4</v>
+        <v>36.4</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>12188000</v>
+        <v>6264000</v>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K23" t="b">
         <v>1</v>
@@ -3654,70 +3648,70 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>11824000</v>
+        <v>6264000</v>
       </c>
       <c r="N23" t="n">
-        <v>364000</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>0.03078484438430311</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2550</v>
+        <v>2050</v>
       </c>
       <c r="Q23" t="n">
-        <v>2550</v>
+        <v>2050</v>
       </c>
       <c r="R23" t="n">
-        <v>20325120</v>
+        <v>4423619</v>
       </c>
       <c r="S23" t="n">
-        <v>2559</v>
+        <v>2061</v>
       </c>
       <c r="T23" t="n">
-        <v>2474.725793457031</v>
+        <v>1931.5</v>
       </c>
       <c r="U23" t="n">
-        <v>2470.363317871094</v>
+        <v>1923.25</v>
       </c>
       <c r="V23" t="n">
-        <v>2408.414017740885</v>
+        <v>2071.231679280599</v>
       </c>
       <c r="W23" t="n">
-        <v>37.10945381653937</v>
+        <v>35.46730180492068</v>
       </c>
       <c r="X23" t="n">
-        <v>29.03768616698488</v>
+        <v>12.55649361476018</v>
       </c>
       <c r="Y23" t="n">
-        <v>8.071767649554491</v>
+        <v>22.9108081901605</v>
       </c>
       <c r="Z23" t="n">
-        <v>12.79821421109786</v>
+        <v>29.99979968137937</v>
       </c>
       <c r="AA23" t="b">
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.03542767005180503</v>
+        <v>0.08753315649867366</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.05682081368767511</v>
+        <v>-0.01137470109178762</v>
       </c>
       <c r="AD23" t="n">
-        <v>-0.009473786532961492</v>
+        <v>0.03468083631319607</v>
       </c>
       <c r="AE23" t="n">
-        <v>-0.02361405843310682</v>
+        <v>-0.1509196140780117</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.01414027190014533</v>
+        <v>0.1856004503912078</v>
       </c>
       <c r="AG23" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="AH23" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="AI23" t="b">
         <v>1</v>
@@ -3751,17 +3745,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3770,7 +3764,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>45.4</v>
+        <v>35</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3779,24 +3773,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2502000</v>
+        <v>12188000</v>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="K24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" t="b">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>2502000</v>
+        <v>12188000</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3805,61 +3799,61 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>7165</v>
+        <v>2490</v>
       </c>
       <c r="Q24" t="n">
-        <v>7165</v>
+        <v>2490</v>
       </c>
       <c r="R24" t="n">
-        <v>1552383</v>
+        <v>24699844</v>
       </c>
       <c r="S24" t="n">
-        <v>7011</v>
+        <v>2531</v>
       </c>
       <c r="T24" t="n">
-        <v>6257</v>
+        <v>2485.550732421875</v>
       </c>
       <c r="U24" t="n">
-        <v>6176.25</v>
+        <v>2481.1970703125</v>
       </c>
       <c r="V24" t="n">
-        <v>5118.542277018229</v>
+        <v>2414.099552408854</v>
       </c>
       <c r="W24" t="n">
-        <v>355.3071810284428</v>
+        <v>17.26986115713817</v>
       </c>
       <c r="X24" t="n">
-        <v>327.1895572321868</v>
+        <v>26.43411965319505</v>
       </c>
       <c r="Y24" t="n">
-        <v>28.11762379625594</v>
+        <v>-9.164258496056888</v>
       </c>
       <c r="Z24" t="n">
-        <v>32.19417750518028</v>
+        <v>-4.587469402347715</v>
       </c>
       <c r="AA24" t="b">
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.2909909909909909</v>
+        <v>0.03623632801307974</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.34836713657204</v>
+        <v>0.09053699032645413</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.2460895344062244</v>
+        <v>-0.01661599217239784</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.267932264451259</v>
+        <v>-0.04900792265976994</v>
       </c>
       <c r="AF24" t="n">
-        <v>-1.021842730045034</v>
+        <v>0.0323919304873721</v>
       </c>
       <c r="AG24" t="n">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="AH24" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="AI24" t="b">
         <v>1</v>
@@ -3868,21 +3862,19 @@
         <v>1</v>
       </c>
       <c r="AK24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="b">
         <v>0</v>
       </c>
       <c r="AN24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>2594.58</v>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
@@ -3893,17 +3885,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3912,7 +3904,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>41.8</v>
+        <v>34.8</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3921,15 +3913,15 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2887848</v>
+        <v>3921000</v>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K25" t="b">
         <v>0</v>
@@ -3938,7 +3930,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>2887848</v>
+        <v>3921000</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3947,61 +3939,61 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2360</v>
+        <v>95.40000152587891</v>
       </c>
       <c r="Q25" t="n">
-        <v>2360</v>
+        <v>95.40000152587891</v>
       </c>
       <c r="R25" t="n">
-        <v>3516661</v>
+        <v>8472107</v>
       </c>
       <c r="S25" t="n">
-        <v>2405</v>
+        <v>92.14000091552734</v>
       </c>
       <c r="T25" t="n">
-        <v>2238.75</v>
+        <v>85.66000022888184</v>
       </c>
       <c r="U25" t="n">
-        <v>2217.5</v>
+        <v>85.00500030517578</v>
       </c>
       <c r="V25" t="n">
-        <v>2166.916666666667</v>
+        <v>84.72333348592123</v>
       </c>
       <c r="W25" t="n">
-        <v>60.47533387328531</v>
+        <v>3.010565023820277</v>
       </c>
       <c r="X25" t="n">
-        <v>76.7143271302707</v>
+        <v>1.561947698491662</v>
       </c>
       <c r="Y25" t="n">
-        <v>-16.2389932569854</v>
+        <v>1.448617325328615</v>
       </c>
       <c r="Z25" t="n">
-        <v>-9.069575089941623</v>
+        <v>1.457521106383786</v>
       </c>
       <c r="AA25" t="b">
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.2196382428940569</v>
+        <v>0.1591737301137475</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.3412281669347996</v>
+        <v>0.06950678015419931</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.1747367863092903</v>
+        <v>0.1063214099282699</v>
       </c>
       <c r="AE25" t="n">
-        <v>0.2607932948140177</v>
+        <v>-0.07003813283202476</v>
       </c>
       <c r="AF25" t="n">
-        <v>-0.08605650850472735</v>
+        <v>0.1763595427602946</v>
       </c>
       <c r="AG25" t="n">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="AH25" t="n">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AI25" t="b">
         <v>1</v>
@@ -4010,19 +4002,21 @@
         <v>1</v>
       </c>
       <c r="AK25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM25" t="b">
         <v>0</v>
       </c>
       <c r="AN25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>2544.08</v>
+        <v>0</v>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
@@ -4033,17 +4027,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4052,7 +4046,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>40.2</v>
+        <v>34.6</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4061,15 +4055,15 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>7389000</v>
+        <v>6147000</v>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K26" t="b">
         <v>1</v>
@@ -4078,7 +4072,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>7389000</v>
+        <v>6147000</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -4087,105 +4081,101 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1965</v>
+        <v>3315</v>
       </c>
       <c r="Q26" t="n">
-        <v>1965</v>
+        <v>3315</v>
       </c>
       <c r="R26" t="n">
-        <v>4855304</v>
+        <v>2306874</v>
       </c>
       <c r="S26" t="n">
-        <v>1979</v>
+        <v>3393</v>
       </c>
       <c r="T26" t="n">
-        <v>1831</v>
+        <v>3403.25</v>
       </c>
       <c r="U26" t="n">
-        <v>1823</v>
+        <v>3406</v>
       </c>
       <c r="V26" t="n">
-        <v>1783.916666666667</v>
+        <v>3060.444982910156</v>
       </c>
       <c r="W26" t="n">
-        <v>56.50518476774346</v>
+        <v>-1.529429568854084</v>
       </c>
       <c r="X26" t="n">
-        <v>43.76389631303759</v>
+        <v>40.92713757628405</v>
       </c>
       <c r="Y26" t="n">
-        <v>12.74128845470587</v>
+        <v>-42.45656714513813</v>
       </c>
       <c r="Z26" t="n">
-        <v>20.22750847362659</v>
+        <v>-38.3833256858796</v>
       </c>
       <c r="AA26" t="b">
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.08864265927977844</v>
+        <v>-0.01632047477744802</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.059299191374663</v>
+        <v>0.5157570982460709</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.04374120269501192</v>
+        <v>-0.06917279496292561</v>
       </c>
       <c r="AE26" t="n">
-        <v>-0.02113568074611893</v>
+        <v>0.3762121852598468</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.06487688344113085</v>
+        <v>-0.4453849802227724</v>
       </c>
       <c r="AG26" t="n">
-        <v>56.00000000000001</v>
+        <v>24</v>
       </c>
       <c r="AH26" t="n">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="AI26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM26" t="b">
         <v>0</v>
       </c>
       <c r="AN26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
-      <c r="AP26" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>3798.99</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>3402.89</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4194,7 +4184,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>39.6</v>
+        <v>34.2</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4203,24 +4193,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>23519000</v>
+        <v>501000</v>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="K27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" t="b">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>23519000</v>
+        <v>501000</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -4229,61 +4219,61 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>635</v>
+        <v>250.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>635</v>
+        <v>250.5</v>
       </c>
       <c r="R27" t="n">
-        <v>45424113</v>
+        <v>18919220</v>
       </c>
       <c r="S27" t="n">
-        <v>631.8</v>
+        <v>248</v>
       </c>
       <c r="T27" t="n">
-        <v>575.8</v>
+        <v>232.275</v>
       </c>
       <c r="U27" t="n">
-        <v>572.4</v>
+        <v>230.825</v>
       </c>
       <c r="V27" t="n">
-        <v>586.7916666666666</v>
+        <v>220.4333333333333</v>
       </c>
       <c r="W27" t="n">
-        <v>20.82060837135532</v>
+        <v>6.074382153769676</v>
       </c>
       <c r="X27" t="n">
-        <v>11.35230141046161</v>
+        <v>4.283553713481245</v>
       </c>
       <c r="Y27" t="n">
-        <v>9.468306960893706</v>
+        <v>1.790828440288431</v>
       </c>
       <c r="Z27" t="n">
-        <v>11.16867895820584</v>
+        <v>2.027673024087094</v>
       </c>
       <c r="AA27" t="b">
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.1199294532627866</v>
+        <v>0.1309255079006773</v>
       </c>
       <c r="AC27" t="n">
-        <v>-0.1838046272493573</v>
+        <v>0.1816037735849056</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.07502799667802007</v>
+        <v>0.07807318771519967</v>
       </c>
       <c r="AE27" t="n">
-        <v>-0.2642394993701392</v>
+        <v>0.04205886059868158</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.3392674960481593</v>
+        <v>0.03601432711651809</v>
       </c>
       <c r="AG27" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="AH27" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="AI27" t="b">
         <v>1</v>
@@ -4317,17 +4307,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4336,7 +4326,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>38.8</v>
+        <v>33.8</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4345,7 +4335,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -4353,7 +4343,7 @@
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K28" t="b">
         <v>0</v>
@@ -4371,61 +4361,61 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>186.5</v>
+        <v>567</v>
       </c>
       <c r="Q28" t="n">
-        <v>186.5</v>
+        <v>567</v>
       </c>
       <c r="R28" t="n">
-        <v>10373801</v>
+        <v>16572643</v>
       </c>
       <c r="S28" t="n">
-        <v>187.7</v>
+        <v>577.4</v>
       </c>
       <c r="T28" t="n">
-        <v>172.75</v>
+        <v>521.525</v>
       </c>
       <c r="U28" t="n">
-        <v>171.025</v>
+        <v>517.925</v>
       </c>
       <c r="V28" t="n">
-        <v>161.2666666666667</v>
+        <v>489.3166666666667</v>
       </c>
       <c r="W28" t="n">
-        <v>7.088929669332032</v>
+        <v>21.22417184626079</v>
       </c>
       <c r="X28" t="n">
-        <v>6.42704532598117</v>
+        <v>19.48575299762814</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.6618843433508621</v>
+        <v>1.738418848632652</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.362418315135592</v>
+        <v>4.021701020704047</v>
       </c>
       <c r="AA28" t="b">
         <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.2269736842105263</v>
+        <v>0.1454545454545455</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.07183908045977017</v>
+        <v>0.08829174664107486</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.1820722276257598</v>
+        <v>0.09260222526906792</v>
       </c>
       <c r="AE28" t="n">
-        <v>-0.008595791661011765</v>
+        <v>-0.0512531663451492</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.1906680192867716</v>
+        <v>0.1438553916142171</v>
       </c>
       <c r="AG28" t="n">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="AH28" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AI28" t="b">
         <v>1</v>
@@ -4459,17 +4449,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4478,7 +4468,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>37.8</v>
+        <v>32.4</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4487,24 +4477,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>79618000</v>
+        <v>4143450</v>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="K29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" t="b">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>79618000</v>
+        <v>4143450</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -4513,64 +4503,64 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>147.5</v>
+        <v>296.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>147.5</v>
+        <v>296.5</v>
       </c>
       <c r="R29" t="n">
-        <v>81139424</v>
+        <v>55999416</v>
       </c>
       <c r="S29" t="n">
-        <v>151.5</v>
+        <v>301.1</v>
       </c>
       <c r="T29" t="n">
-        <v>150.45</v>
+        <v>292.4</v>
       </c>
       <c r="U29" t="n">
-        <v>149.925</v>
+        <v>290.725</v>
       </c>
       <c r="V29" t="n">
-        <v>134.3916666666667</v>
+        <v>264.8006866455078</v>
       </c>
       <c r="W29" t="n">
-        <v>1.706312721761321</v>
+        <v>5.200933723366973</v>
       </c>
       <c r="X29" t="n">
-        <v>4.183670763234528</v>
+        <v>6.875214922882925</v>
       </c>
       <c r="Y29" t="n">
-        <v>-2.477358041473207</v>
+        <v>-1.674281199515953</v>
       </c>
       <c r="Z29" t="n">
-        <v>-2.244279537122019</v>
+        <v>-1.004383772877178</v>
       </c>
       <c r="AA29" t="b">
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.07664233576642343</v>
+        <v>0.1273764258555132</v>
       </c>
       <c r="AC29" t="n">
-        <v>-0.02317880794701987</v>
+        <v>0.09079890139956692</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.03174087918165691</v>
+        <v>0.07452410567003565</v>
       </c>
       <c r="AE29" t="n">
-        <v>-0.1036136800678018</v>
+        <v>-0.04874601158665715</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.1353545592494587</v>
+        <v>0.1232701172566928</v>
       </c>
       <c r="AG29" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="AH29" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="AI29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ29" t="b">
         <v>1</v>
@@ -4585,10 +4575,10 @@
         <v>0</v>
       </c>
       <c r="AN29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO29" t="n">
-        <v>175.53</v>
+        <v>315.48</v>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
@@ -4599,17 +4589,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4618,24 +4608,24 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>37.2</v>
+        <v>31</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>121000</v>
+        <v>186900</v>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K30" t="b">
         <v>0</v>
@@ -4644,114 +4634,108 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>121000</v>
+        <v>157900</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>29000</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>0.1836605446485117</v>
       </c>
       <c r="P30" t="n">
-        <v>1525</v>
+        <v>17500</v>
       </c>
       <c r="Q30" t="n">
-        <v>1525</v>
+        <v>17500</v>
       </c>
       <c r="R30" t="n">
-        <v>2890449</v>
+        <v>367989</v>
       </c>
       <c r="S30" t="n">
-        <v>1488</v>
+        <v>17556</v>
       </c>
       <c r="T30" t="n">
-        <v>1308.25</v>
+        <v>18723.25</v>
       </c>
       <c r="U30" t="n">
-        <v>1301.25</v>
+        <v>18742.5</v>
       </c>
       <c r="V30" t="n">
-        <v>1207.683582560221</v>
+        <v>16999.08333333333</v>
       </c>
       <c r="W30" t="n">
-        <v>70.42619172063269</v>
+        <v>-302.5965061577663</v>
       </c>
       <c r="X30" t="n">
-        <v>34.00287491907147</v>
+        <v>25.43756784267589</v>
       </c>
       <c r="Y30" t="n">
-        <v>36.42331680156121</v>
+        <v>-328.0340740004422</v>
       </c>
       <c r="Z30" t="n">
-        <v>39.97160545982104</v>
+        <v>-367.6667200919853</v>
       </c>
       <c r="AA30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.1010830324909748</v>
+        <v>-0.02152641878669281</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.5679033634970991</v>
+        <v>0.3513513513513513</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.05618157590620831</v>
+        <v>-0.0743787389721704</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.4874684913763172</v>
+        <v>0.2118064383651272</v>
       </c>
       <c r="AF30" t="n">
-        <v>-0.4312869154701089</v>
+        <v>-0.2861851773372976</v>
       </c>
       <c r="AG30" t="n">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="AH30" t="n">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="AI30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN30" t="b">
         <v>0</v>
       </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
-      <c r="AP30" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+      <c r="AO30" t="inlineStr"/>
+      <c r="AP30" t="n">
+        <v>19267.63</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4760,7 +4744,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>36.6</v>
+        <v>30.8</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4769,15 +4753,15 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>499000</v>
+        <v>5000</v>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="K31" t="b">
         <v>0</v>
@@ -4786,7 +4770,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>499000</v>
+        <v>5000</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -4795,64 +4779,64 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2370</v>
+        <v>166</v>
       </c>
       <c r="Q31" t="n">
-        <v>2370</v>
+        <v>166</v>
       </c>
       <c r="R31" t="n">
-        <v>1635222</v>
+        <v>11434465</v>
       </c>
       <c r="S31" t="n">
-        <v>2400</v>
+        <v>170</v>
       </c>
       <c r="T31" t="n">
-        <v>2333</v>
+        <v>170.25</v>
       </c>
       <c r="U31" t="n">
-        <v>2322.25</v>
+        <v>169.45</v>
       </c>
       <c r="V31" t="n">
-        <v>1935.388326009115</v>
+        <v>150.6916666666667</v>
       </c>
       <c r="W31" t="n">
-        <v>50.81128336974143</v>
+        <v>0.9693286291989409</v>
       </c>
       <c r="X31" t="n">
-        <v>74.03948381092772</v>
+        <v>3.624013383555756</v>
       </c>
       <c r="Y31" t="n">
-        <v>-23.22820044118629</v>
+        <v>-2.654684754356815</v>
       </c>
       <c r="Z31" t="n">
-        <v>-16.61741283313532</v>
+        <v>-2.534013456853975</v>
       </c>
       <c r="AA31" t="b">
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.09976798143851506</v>
+        <v>0.1066666666666667</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.8080101155233668</v>
+        <v>0.09570957095709565</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.05486652485374854</v>
+        <v>0.0538143464811891</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.7275752434025848</v>
+        <v>-0.04383534202912842</v>
       </c>
       <c r="AF31" t="n">
-        <v>-0.6727087185488363</v>
+        <v>0.09764968851031752</v>
       </c>
       <c r="AG31" t="n">
         <v>57.99999999999999</v>
       </c>
       <c r="AH31" t="n">
-        <v>96</v>
+        <v>44</v>
       </c>
       <c r="AI31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="b">
         <v>1</v>
@@ -4867,10 +4851,10 @@
         <v>0</v>
       </c>
       <c r="AN31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO31" t="n">
-        <v>2635.44</v>
+        <v>195.88</v>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
@@ -4881,17 +4865,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>6271</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4900,7 +4884,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>34</v>
+        <v>30.2</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4909,15 +4893,15 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1000</v>
+        <v>2185000</v>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="n">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="K32" t="b">
         <v>0</v>
@@ -4926,7 +4910,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1000</v>
+        <v>2185000</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -4935,61 +4919,61 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>592</v>
+        <v>242</v>
       </c>
       <c r="Q32" t="n">
-        <v>592</v>
+        <v>242</v>
       </c>
       <c r="R32" t="n">
-        <v>32667276</v>
+        <v>3392094</v>
       </c>
       <c r="S32" t="n">
-        <v>579.6</v>
+        <v>243.3</v>
       </c>
       <c r="T32" t="n">
-        <v>511.1</v>
+        <v>232.55</v>
       </c>
       <c r="U32" t="n">
-        <v>506.75</v>
+        <v>231.45</v>
       </c>
       <c r="V32" t="n">
-        <v>489.6</v>
+        <v>209.9666666666667</v>
       </c>
       <c r="W32" t="n">
-        <v>27.85934789966677</v>
+        <v>4.992515275095315</v>
       </c>
       <c r="X32" t="n">
-        <v>15.72377549864255</v>
+        <v>4.782584651885575</v>
       </c>
       <c r="Y32" t="n">
-        <v>12.13557240102422</v>
+        <v>0.2099306232097398</v>
       </c>
       <c r="Z32" t="n">
-        <v>13.16721404350908</v>
+        <v>0.5892077882679656</v>
       </c>
       <c r="AA32" t="b">
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.1722772277227722</v>
+        <v>0.1000000000000001</v>
       </c>
       <c r="AC32" t="n">
-        <v>-0.05882352941176472</v>
+        <v>0.1921182266009853</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.1273757711380057</v>
+        <v>0.0471476798145225</v>
       </c>
       <c r="AE32" t="n">
-        <v>-0.1392584015325466</v>
+        <v>0.05257331361476125</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.2666341726705523</v>
+        <v>-0.005425633800238749</v>
       </c>
       <c r="AG32" t="n">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="AH32" t="n">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="AI32" t="b">
         <v>1</v>
@@ -5023,17 +5007,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5042,7 +5026,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>32.8</v>
+        <v>30.2</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5051,15 +5035,15 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="K33" t="b">
         <v>0</v>
@@ -5068,7 +5052,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
@@ -5077,61 +5061,61 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>172.5</v>
+        <v>176</v>
       </c>
       <c r="Q33" t="n">
-        <v>172.5</v>
+        <v>176</v>
       </c>
       <c r="R33" t="n">
-        <v>16302541</v>
+        <v>8306342</v>
       </c>
       <c r="S33" t="n">
-        <v>176.4</v>
+        <v>181.7</v>
       </c>
       <c r="T33" t="n">
-        <v>168.125</v>
+        <v>175.55</v>
       </c>
       <c r="U33" t="n">
-        <v>167.125</v>
+        <v>174.625</v>
       </c>
       <c r="V33" t="n">
-        <v>150.5916666666667</v>
+        <v>161.0833333333333</v>
       </c>
       <c r="W33" t="n">
-        <v>4.378314839581691</v>
+        <v>3.210129029492379</v>
       </c>
       <c r="X33" t="n">
-        <v>5.284386788308912</v>
+        <v>5.383351557859127</v>
       </c>
       <c r="Y33" t="n">
-        <v>-0.9060719487272211</v>
+        <v>-2.173222528366749</v>
       </c>
       <c r="Z33" t="n">
-        <v>-0.213892123161445</v>
+        <v>-1.606206873600168</v>
       </c>
       <c r="AA33" t="b">
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.1311475409836065</v>
+        <v>0.1174603174603175</v>
       </c>
       <c r="AC33" t="n">
-        <v>-0.01988636363636365</v>
+        <v>0.04142011834319526</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.08624608439883996</v>
+        <v>0.0646079972748399</v>
       </c>
       <c r="AE33" t="n">
-        <v>-0.1003212357571456</v>
+        <v>-0.09812479464302881</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.1865673201559855</v>
+        <v>0.1627327919178687</v>
       </c>
       <c r="AG33" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="AH33" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI33" t="b">
         <v>1</v>
@@ -5152,7 +5136,7 @@
         <v>1</v>
       </c>
       <c r="AO33" t="n">
-        <v>182.85</v>
+        <v>200.64</v>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
@@ -5163,17 +5147,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5182,7 +5166,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>32.6</v>
+        <v>29.2</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5191,7 +5175,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -5199,7 +5183,7 @@
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="K34" t="b">
         <v>0</v>
@@ -5217,61 +5201,61 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1130</v>
+        <v>6880</v>
       </c>
       <c r="Q34" t="n">
-        <v>1130</v>
+        <v>6880</v>
       </c>
       <c r="R34" t="n">
-        <v>19470973</v>
+        <v>4280756</v>
       </c>
       <c r="S34" t="n">
-        <v>1184</v>
+        <v>6997</v>
       </c>
       <c r="T34" t="n">
-        <v>1008.3</v>
+        <v>6449.75</v>
       </c>
       <c r="U34" t="n">
-        <v>999.55</v>
+        <v>6438.75</v>
       </c>
       <c r="V34" t="n">
-        <v>1005.155000813802</v>
+        <v>5695.806945800781</v>
       </c>
       <c r="W34" t="n">
-        <v>61.6813125427218</v>
+        <v>200.3495903311559</v>
       </c>
       <c r="X34" t="n">
-        <v>40.97196798221578</v>
+        <v>121.5311146753355</v>
       </c>
       <c r="Y34" t="n">
-        <v>20.70934456050602</v>
+        <v>78.81847565582044</v>
       </c>
       <c r="Z34" t="n">
-        <v>32.83115113166608</v>
+        <v>120.0294182362092</v>
       </c>
       <c r="AA34" t="b">
         <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.1832460732984293</v>
+        <v>0.03303303303303307</v>
       </c>
       <c r="AC34" t="n">
-        <v>-0.2512416605537082</v>
+        <v>0.7313819553383563</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.1383446167136628</v>
+        <v>-0.01981928715244452</v>
       </c>
       <c r="AE34" t="n">
-        <v>-0.3316765326744902</v>
+        <v>0.5918370423521322</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.470021149388153</v>
+        <v>-0.6116563295045767</v>
       </c>
       <c r="AG34" t="n">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AH34" t="n">
-        <v>2</v>
+        <v>94</v>
       </c>
       <c r="AI34" t="b">
         <v>1</v>
@@ -5305,17 +5289,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5324,7 +5308,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>29</v>
+        <v>29.2</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5333,7 +5317,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -5341,7 +5325,7 @@
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="K35" t="b">
         <v>0</v>
@@ -5359,84 +5343,82 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>6660</v>
+        <v>1020</v>
       </c>
       <c r="Q35" t="n">
-        <v>6660</v>
+        <v>1020</v>
       </c>
       <c r="R35" t="n">
-        <v>1709053</v>
+        <v>10877612</v>
       </c>
       <c r="S35" t="n">
-        <v>6676</v>
+        <v>1099</v>
       </c>
       <c r="T35" t="n">
-        <v>6388.25</v>
+        <v>1027.1</v>
       </c>
       <c r="U35" t="n">
-        <v>6380.25</v>
+        <v>1021.2</v>
       </c>
       <c r="V35" t="n">
-        <v>5541.116589355469</v>
+        <v>989.5833333333334</v>
       </c>
       <c r="W35" t="n">
-        <v>108.7493100898646</v>
+        <v>22.98491278396568</v>
       </c>
       <c r="X35" t="n">
-        <v>44.38449983839664</v>
+        <v>38.16369765911316</v>
       </c>
       <c r="Y35" t="n">
-        <v>64.36481025146796</v>
+        <v>-15.17878487514748</v>
       </c>
       <c r="Z35" t="n">
-        <v>78.13496384642453</v>
+        <v>-6.22915014741276</v>
       </c>
       <c r="AA35" t="b">
         <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.02461538461538471</v>
+        <v>0.1308203991130821</v>
       </c>
       <c r="AC35" t="n">
-        <v>0.5758105101170794</v>
+        <v>-0.1774193548387096</v>
       </c>
       <c r="AD35" t="n">
-        <v>-0.02028607196938181</v>
+        <v>0.07796807892760449</v>
       </c>
       <c r="AE35" t="n">
-        <v>0.4953756379962975</v>
+        <v>-0.3169642678249337</v>
       </c>
       <c r="AF35" t="n">
-        <v>-0.5156617099656793</v>
+        <v>0.3949323467525382</v>
       </c>
       <c r="AG35" t="n">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="AH35" t="n">
-        <v>92</v>
+        <v>4</v>
       </c>
       <c r="AI35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="b">
         <v>1</v>
       </c>
       <c r="AK35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM35" t="b">
         <v>0</v>
       </c>
       <c r="AN35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>1191.36</v>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
@@ -5447,17 +5429,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5466,7 +5448,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>28.4</v>
+        <v>28.6</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5475,15 +5457,15 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>501000</v>
+        <v>1000</v>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="K36" t="b">
         <v>0</v>
@@ -5492,7 +5474,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>501000</v>
+        <v>1000</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -5501,61 +5483,61 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>248</v>
+        <v>3940</v>
       </c>
       <c r="Q36" t="n">
-        <v>248</v>
+        <v>3940</v>
       </c>
       <c r="R36" t="n">
-        <v>23188404</v>
+        <v>2682393</v>
       </c>
       <c r="S36" t="n">
-        <v>244.1</v>
+        <v>4185</v>
       </c>
       <c r="T36" t="n">
-        <v>228.725</v>
+        <v>3804.5</v>
       </c>
       <c r="U36" t="n">
-        <v>227.875</v>
+        <v>3790</v>
       </c>
       <c r="V36" t="n">
-        <v>219.5916666666667</v>
+        <v>3740.318452962239</v>
       </c>
       <c r="W36" t="n">
-        <v>5.759997235116174</v>
+        <v>99.16455939196248</v>
       </c>
       <c r="X36" t="n">
-        <v>2.542632776838465</v>
+        <v>79.84013542279391</v>
       </c>
       <c r="Y36" t="n">
-        <v>3.217364458277709</v>
+        <v>19.32442396916858</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.425934511739225</v>
+        <v>56.38844843172421</v>
       </c>
       <c r="AA36" t="b">
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.07359307359307365</v>
+        <v>0.07945205479452055</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.0997782705099779</v>
+        <v>0.1410331492138492</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.02869161700830714</v>
+        <v>0.02659973460904297</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.01934339838919596</v>
+        <v>0.001488236227625173</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.00934821861911117</v>
+        <v>0.0251114983814178</v>
       </c>
       <c r="AG36" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AH36" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AI36" t="b">
         <v>1</v>
@@ -5589,17 +5571,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5608,7 +5590,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>27.6</v>
+        <v>28.4</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5617,24 +5599,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1000</v>
+        <v>79618000</v>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="K37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" t="b">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1000</v>
+        <v>79618000</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -5643,85 +5625,81 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2330</v>
+        <v>142</v>
       </c>
       <c r="Q37" t="n">
-        <v>2330</v>
+        <v>142</v>
       </c>
       <c r="R37" t="n">
-        <v>1670735</v>
+        <v>110224887</v>
       </c>
       <c r="S37" t="n">
-        <v>2319</v>
+        <v>145</v>
       </c>
       <c r="T37" t="n">
-        <v>2239.5</v>
+        <v>150.675</v>
       </c>
       <c r="U37" t="n">
-        <v>2236.25</v>
+        <v>150.6</v>
       </c>
       <c r="V37" t="n">
-        <v>2114.25</v>
+        <v>133.7083333333333</v>
       </c>
       <c r="W37" t="n">
-        <v>43.81936756337473</v>
+        <v>-0.8723559090970241</v>
       </c>
       <c r="X37" t="n">
-        <v>32.83819442283744</v>
+        <v>2.044215396009187</v>
       </c>
       <c r="Y37" t="n">
-        <v>10.98117314053729</v>
+        <v>-2.916571305106211</v>
       </c>
       <c r="Z37" t="n">
-        <v>13.56714370826949</v>
+        <v>-2.976420182292489</v>
       </c>
       <c r="AA37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.02869757174392928</v>
+        <v>0.01067615658362997</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.2802197802197801</v>
+        <v>-0.01388888888888884</v>
       </c>
       <c r="AD37" t="n">
-        <v>-0.01620388484083723</v>
+        <v>-0.04217616360184762</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.1997849080989982</v>
+        <v>-0.1534338018751129</v>
       </c>
       <c r="AF37" t="n">
-        <v>-0.2159887929398354</v>
+        <v>0.1112576382732653</v>
       </c>
       <c r="AG37" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="AH37" t="n">
-        <v>72</v>
+        <v>16</v>
       </c>
       <c r="AI37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="b">
         <v>1</v>
       </c>
       <c r="AK37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN37" t="b">
         <v>0</v>
       </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
+      <c r="AO37" t="inlineStr"/>
       <c r="AP37" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -5731,17 +5709,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5750,24 +5728,24 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>26.4</v>
+        <v>27</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Heavy Sell</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>4328000</v>
+        <v>1000</v>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="K38" t="b">
         <v>0</v>
@@ -5776,70 +5754,70 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>4650000</v>
+        <v>1000</v>
       </c>
       <c r="N38" t="n">
-        <v>-322000</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>-0.06924731182795699</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>6000</v>
+        <v>2250</v>
       </c>
       <c r="Q38" t="n">
-        <v>6000</v>
+        <v>2250</v>
       </c>
       <c r="R38" t="n">
-        <v>1665965</v>
+        <v>2512473</v>
       </c>
       <c r="S38" t="n">
-        <v>5766</v>
+        <v>2309</v>
       </c>
       <c r="T38" t="n">
-        <v>5236.5</v>
+        <v>2246.5</v>
       </c>
       <c r="U38" t="n">
-        <v>5203.5</v>
+        <v>2242</v>
       </c>
       <c r="V38" t="n">
-        <v>5259.273494466146</v>
+        <v>2132.083333333333</v>
       </c>
       <c r="W38" t="n">
-        <v>196.0214954952326</v>
+        <v>22.02039136671237</v>
       </c>
       <c r="X38" t="n">
-        <v>34.54955237041199</v>
+        <v>31.88203833536183</v>
       </c>
       <c r="Y38" t="n">
-        <v>161.4719431248206</v>
+        <v>-9.861646968649456</v>
       </c>
       <c r="Z38" t="n">
-        <v>162.5406575067177</v>
+        <v>-5.081578481809196</v>
       </c>
       <c r="AA38" t="b">
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.1235955056179776</v>
+        <v>0.04166666666666674</v>
       </c>
       <c r="AC38" t="n">
-        <v>0.2127559662204828</v>
+        <v>0.2162162162162162</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.07869404903321109</v>
+        <v>-0.01118565351881085</v>
       </c>
       <c r="AE38" t="n">
-        <v>0.1323210940997008</v>
+        <v>0.07667130322999216</v>
       </c>
       <c r="AF38" t="n">
-        <v>-0.05362704506648974</v>
+        <v>-0.08785695674880301</v>
       </c>
       <c r="AG38" t="n">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="AH38" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="AI38" t="b">
         <v>1</v>
@@ -5848,21 +5826,19 @@
         <v>1</v>
       </c>
       <c r="AK38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM38" t="b">
         <v>0</v>
       </c>
       <c r="AN38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>2362.5</v>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
@@ -5873,7 +5849,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5892,7 +5868,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>26.2</v>
+        <v>26.8</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5901,7 +5877,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -5927,84 +5903,82 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>535</v>
+        <v>502</v>
       </c>
       <c r="Q39" t="n">
-        <v>535</v>
+        <v>502</v>
       </c>
       <c r="R39" t="n">
-        <v>3348518</v>
+        <v>1990629</v>
       </c>
       <c r="S39" t="n">
-        <v>544.8</v>
+        <v>520.2</v>
       </c>
       <c r="T39" t="n">
-        <v>511.65</v>
+        <v>510.9</v>
       </c>
       <c r="U39" t="n">
-        <v>510.9</v>
+        <v>510.05</v>
       </c>
       <c r="V39" t="n">
-        <v>446.7648824055989</v>
+        <v>450.45</v>
       </c>
       <c r="W39" t="n">
-        <v>14.35358227217</v>
+        <v>3.423407848656097</v>
       </c>
       <c r="X39" t="n">
-        <v>11.18623510330251</v>
+        <v>8.911526937332471</v>
       </c>
       <c r="Y39" t="n">
-        <v>3.16734716886749</v>
+        <v>-5.488119088676374</v>
       </c>
       <c r="Z39" t="n">
-        <v>5.249718200634559</v>
+        <v>-3.991731241565386</v>
       </c>
       <c r="AA39" t="b">
         <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.02884615384615374</v>
+        <v>0.03505154639175267</v>
       </c>
       <c r="AC39" t="n">
-        <v>0.1683663333046532</v>
+        <v>0.2597239648682559</v>
       </c>
       <c r="AD39" t="n">
-        <v>-0.01605530273861278</v>
+        <v>-0.01780077379372491</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.0879314611838713</v>
+        <v>0.1201790518820318</v>
       </c>
       <c r="AF39" t="n">
-        <v>-0.1039867639224841</v>
+        <v>-0.1379798256757567</v>
       </c>
       <c r="AG39" t="n">
         <v>38</v>
       </c>
       <c r="AH39" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="AI39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ39" t="b">
         <v>1</v>
       </c>
       <c r="AK39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM39" t="b">
         <v>0</v>
       </c>
       <c r="AN39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>564.25</v>
       </c>
       <c r="AP39" t="inlineStr">
         <is>
@@ -6015,17 +5989,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6034,24 +6008,24 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>24.8</v>
+        <v>26.6</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>5086000</v>
+        <v>470000</v>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="K40" t="b">
         <v>0</v>
@@ -6060,70 +6034,70 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>5086000</v>
+        <v>420000</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>0.119047619047619</v>
       </c>
       <c r="P40" t="n">
-        <v>4690</v>
+        <v>3225</v>
       </c>
       <c r="Q40" t="n">
-        <v>4690</v>
+        <v>3225</v>
       </c>
       <c r="R40" t="n">
-        <v>6416655</v>
+        <v>680811</v>
       </c>
       <c r="S40" t="n">
-        <v>4912</v>
+        <v>3252</v>
       </c>
       <c r="T40" t="n">
-        <v>4834.5</v>
+        <v>3262.25</v>
       </c>
       <c r="U40" t="n">
-        <v>4835.5</v>
+        <v>3275</v>
       </c>
       <c r="V40" t="n">
-        <v>4204.166666666667</v>
+        <v>2997.416666666667</v>
       </c>
       <c r="W40" t="n">
-        <v>61.8921663207484</v>
+        <v>0.4778946522515071</v>
       </c>
       <c r="X40" t="n">
-        <v>135.7194358341844</v>
+        <v>-8.946002146545416</v>
       </c>
       <c r="Y40" t="n">
-        <v>-73.82726951343602</v>
+        <v>9.423896798796923</v>
       </c>
       <c r="Z40" t="n">
-        <v>-52.28377392719844</v>
+        <v>12.87433758470597</v>
       </c>
       <c r="AA40" t="b">
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>-0.00424628450106157</v>
+        <v>-0.07327586206896552</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.2814207650273224</v>
+        <v>0.2475822050290135</v>
       </c>
       <c r="AD40" t="n">
-        <v>-0.04914774108582809</v>
+        <v>-0.1261281822544431</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.2009858929065405</v>
+        <v>0.1080372920427894</v>
       </c>
       <c r="AF40" t="n">
-        <v>-0.2501336339923685</v>
+        <v>-0.2341654742972326</v>
       </c>
       <c r="AG40" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="AH40" t="n">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="AI40" t="b">
         <v>0</v>
@@ -6132,10 +6106,10 @@
         <v>0</v>
       </c>
       <c r="AK40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM40" t="b">
         <v>0</v>
@@ -6143,27 +6117,29 @@
       <c r="AN40" t="b">
         <v>0</v>
       </c>
-      <c r="AO40" t="n">
-        <v>5524.82</v>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP40" t="n">
-        <v>4777.11</v>
+        <v>3414.21</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6172,7 +6148,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>24</v>
+        <v>26.2</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -6181,15 +6157,15 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1000</v>
+        <v>499000</v>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="K41" t="b">
         <v>0</v>
@@ -6198,7 +6174,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1000</v>
+        <v>499000</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -6207,61 +6183,61 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>98.40000152587891</v>
+        <v>2195</v>
       </c>
       <c r="Q41" t="n">
-        <v>98.40000152587891</v>
+        <v>2195</v>
       </c>
       <c r="R41" t="n">
-        <v>1687131</v>
+        <v>729621</v>
       </c>
       <c r="S41" t="n">
-        <v>98.34000091552734</v>
+        <v>2300</v>
       </c>
       <c r="T41" t="n">
-        <v>99.44000053405762</v>
+        <v>2335</v>
       </c>
       <c r="U41" t="n">
-        <v>99.42500038146973</v>
+        <v>2332.75</v>
       </c>
       <c r="V41" t="n">
-        <v>92.03500022888184</v>
+        <v>1977.869226074219</v>
       </c>
       <c r="W41" t="n">
-        <v>-0.1089435152558593</v>
+        <v>-9.024428314626221</v>
       </c>
       <c r="X41" t="n">
-        <v>0.2470375668089768</v>
+        <v>41.20096211500317</v>
       </c>
       <c r="Y41" t="n">
-        <v>-0.3559810820648361</v>
+        <v>-50.22539042962939</v>
       </c>
       <c r="Z41" t="n">
-        <v>-0.4924732197200056</v>
+        <v>-45.7854300360147</v>
       </c>
       <c r="AA41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.003058135131744688</v>
+        <v>0.02093023255813953</v>
       </c>
       <c r="AC41" t="n">
-        <v>0.1742243191220842</v>
+        <v>0.6433825562239956</v>
       </c>
       <c r="AD41" t="n">
-        <v>-0.04184332145302183</v>
+        <v>-0.03192208762733806</v>
       </c>
       <c r="AE41" t="n">
-        <v>0.09378944700130232</v>
+        <v>0.5038376432377716</v>
       </c>
       <c r="AF41" t="n">
-        <v>-0.1356327684543241</v>
+        <v>-0.5357597308651096</v>
       </c>
       <c r="AG41" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AH41" t="n">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="AI41" t="b">
         <v>0</v>
@@ -6276,14 +6252,12 @@
         <v>0</v>
       </c>
       <c r="AM41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN41" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO41" t="n">
-        <v>102.53</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO41" t="inlineStr"/>
       <c r="AP41" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -6293,17 +6267,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6312,7 +6286,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>21.4</v>
+        <v>25.2</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6321,127 +6295,131 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1000</v>
+        <v>2504000</v>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="n">
+        <v>19</v>
+      </c>
+      <c r="K42" t="b">
+        <v>0</v>
+      </c>
+      <c r="L42" t="b">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>2504000</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>5885</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>5885</v>
+      </c>
+      <c r="R42" t="n">
+        <v>986684</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5812</v>
+      </c>
+      <c r="T42" t="n">
+        <v>5535.5</v>
+      </c>
+      <c r="U42" t="n">
+        <v>5522.25</v>
+      </c>
+      <c r="V42" t="n">
+        <v>5601.833333333333</v>
+      </c>
+      <c r="W42" t="n">
+        <v>122.548672938955</v>
+      </c>
+      <c r="X42" t="n">
+        <v>42.19621348449871</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>80.35245945445624</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>91.4052926254806</v>
+      </c>
+      <c r="AA42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0.04715302491103213</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0.05089285714285707</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>-0.005699295274445459</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>-0.08865205584336699</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>0.08295276056892154</v>
+      </c>
+      <c r="AG42" t="n">
         <v>44</v>
       </c>
-      <c r="K42" t="b">
-        <v>0</v>
-      </c>
-      <c r="L42" t="b">
-        <v>0</v>
-      </c>
-      <c r="M42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>565</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>565</v>
-      </c>
-      <c r="R42" t="n">
-        <v>3426072</v>
-      </c>
-      <c r="S42" t="n">
-        <v>579</v>
-      </c>
-      <c r="T42" t="n">
-        <v>572.3</v>
-      </c>
-      <c r="U42" t="n">
-        <v>574.3</v>
-      </c>
-      <c r="V42" t="n">
-        <v>524.2833333333333</v>
-      </c>
-      <c r="W42" t="n">
-        <v>-0.3008540646583242</v>
-      </c>
-      <c r="X42" t="n">
-        <v>1.463752461506485</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>-1.764606526164809</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>-0.6651745070861605</v>
-      </c>
-      <c r="AA42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>-0.06611570247933884</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>0.401985111662531</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>-0.1110171590641054</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>0.3215502395417491</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>-0.4325673986058545</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>12</v>
-      </c>
       <c r="AH42" t="n">
-        <v>82</v>
+        <v>30</v>
       </c>
       <c r="AI42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM42" t="b">
         <v>0</v>
       </c>
       <c r="AN42" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO42" t="n">
-        <v>585.34</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>617.6799999999999</v>
+        <v>0</v>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
+      </c>
+      <c r="AP42" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6450,7 +6428,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>20.8</v>
+        <v>24.4</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6459,15 +6437,15 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1000</v>
+        <v>4328000</v>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="n">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="K43" t="b">
         <v>0</v>
@@ -6476,7 +6454,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>1000</v>
+        <v>4328000</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -6485,82 +6463,84 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>558</v>
+        <v>5520</v>
       </c>
       <c r="Q43" t="n">
-        <v>558</v>
+        <v>5520</v>
       </c>
       <c r="R43" t="n">
-        <v>383366</v>
+        <v>2315803</v>
       </c>
       <c r="S43" t="n">
-        <v>567.4</v>
+        <v>5833</v>
       </c>
       <c r="T43" t="n">
-        <v>558.85</v>
+        <v>5291.5</v>
       </c>
       <c r="U43" t="n">
-        <v>558.3</v>
+        <v>5283.75</v>
       </c>
       <c r="V43" t="n">
-        <v>570.6034210205078</v>
+        <v>5304.543562825521</v>
       </c>
       <c r="W43" t="n">
-        <v>1.036610043898463</v>
+        <v>149.6629759085454</v>
       </c>
       <c r="X43" t="n">
-        <v>1.838883445649217</v>
+        <v>107.9368124751547</v>
       </c>
       <c r="Y43" t="n">
-        <v>-0.802273401750754</v>
+        <v>41.7261634333907</v>
       </c>
       <c r="Z43" t="n">
-        <v>0.4201449755620841</v>
+        <v>91.44812537588726</v>
       </c>
       <c r="AA43" t="b">
         <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.02010968921389389</v>
+        <v>0.02889095992544277</v>
       </c>
       <c r="AC43" t="n">
-        <v>-0.09769513464688384</v>
+        <v>0.2336385449190062</v>
       </c>
       <c r="AD43" t="n">
-        <v>-0.02479176737087263</v>
+        <v>-0.02396136026003481</v>
       </c>
       <c r="AE43" t="n">
-        <v>-0.1781300067676658</v>
+        <v>0.09409363193278208</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.1533382393967931</v>
+        <v>-0.1180549921928169</v>
       </c>
       <c r="AG43" t="n">
         <v>32</v>
       </c>
       <c r="AH43" t="n">
-        <v>16</v>
+        <v>57.99999999999999</v>
       </c>
       <c r="AI43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ43" t="b">
         <v>1</v>
       </c>
       <c r="AK43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM43" t="b">
         <v>0</v>
       </c>
       <c r="AN43" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO43" t="n">
-        <v>568.04</v>
+        <v>0</v>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP43" t="inlineStr">
         <is>
@@ -6571,17 +6551,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6590,7 +6570,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>19.8</v>
+        <v>21</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6599,15 +6579,15 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>157900</v>
+        <v>5086000</v>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="K44" t="b">
         <v>0</v>
@@ -6616,7 +6596,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>157900</v>
+        <v>5086000</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
@@ -6625,61 +6605,61 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>17485</v>
+        <v>4475</v>
       </c>
       <c r="Q44" t="n">
-        <v>17485</v>
+        <v>4475</v>
       </c>
       <c r="R44" t="n">
-        <v>1079583</v>
+        <v>7726671</v>
       </c>
       <c r="S44" t="n">
-        <v>18516</v>
+        <v>4630</v>
       </c>
       <c r="T44" t="n">
-        <v>18855.5</v>
+        <v>4819.25</v>
       </c>
       <c r="U44" t="n">
-        <v>18942.25</v>
+        <v>4824.75</v>
       </c>
       <c r="V44" t="n">
-        <v>16802.58333333333</v>
+        <v>4251.083333333333</v>
       </c>
       <c r="W44" t="n">
-        <v>-78.09230247373125</v>
+        <v>-42.21314231572705</v>
       </c>
       <c r="X44" t="n">
-        <v>290.5850140168843</v>
+        <v>62.48055185050528</v>
       </c>
       <c r="Y44" t="n">
-        <v>-368.6773164906156</v>
+        <v>-104.6936941662323</v>
       </c>
       <c r="Z44" t="n">
-        <v>-297.8407122578458</v>
+        <v>-100.0760571833271</v>
       </c>
       <c r="AA44" t="b">
         <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>-0.090270551508845</v>
+        <v>-0.02399127589967287</v>
       </c>
       <c r="AC44" t="n">
-        <v>0.3465537158259531</v>
+        <v>0.327893175074184</v>
       </c>
       <c r="AD44" t="n">
-        <v>-0.1351720080936115</v>
+        <v>-0.07684359608515046</v>
       </c>
       <c r="AE44" t="n">
-        <v>0.2661188437051711</v>
+        <v>0.18834826208796</v>
       </c>
       <c r="AF44" t="n">
-        <v>-0.4012908517987827</v>
+        <v>-0.2651918581731104</v>
       </c>
       <c r="AG44" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AH44" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="AI44" t="b">
         <v>0</v>
@@ -6701,23 +6681,23 @@
       </c>
       <c r="AO44" t="inlineStr"/>
       <c r="AP44" t="n">
-        <v>20047.63</v>
+        <v>4922.37</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6726,7 +6706,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>19.4</v>
+        <v>18.4</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6735,15 +6715,15 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>5163000</v>
+        <v>1000</v>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="K45" t="b">
         <v>0</v>
@@ -6752,7 +6732,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>5163000</v>
+        <v>1000</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
@@ -6761,93 +6741,91 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>18.95000076293945</v>
+        <v>480.5</v>
       </c>
       <c r="Q45" t="n">
-        <v>18.95000076293945</v>
+        <v>480.5</v>
       </c>
       <c r="R45" t="n">
-        <v>26622757</v>
+        <v>54547707</v>
       </c>
       <c r="S45" t="n">
-        <v>18.95000038146973</v>
+        <v>508.3</v>
       </c>
       <c r="T45" t="n">
-        <v>18.85500001907349</v>
+        <v>507.075</v>
       </c>
       <c r="U45" t="n">
-        <v>18.8625</v>
+        <v>507.7</v>
       </c>
       <c r="V45" t="n">
-        <v>18.97196779251099</v>
+        <v>484.4833333333333</v>
       </c>
       <c r="W45" t="n">
-        <v>0.01933005598385407</v>
+        <v>-2.467166759437305</v>
       </c>
       <c r="X45" t="n">
-        <v>-0.01076000137061569</v>
+        <v>2.757236587909675</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.03009005735446976</v>
+        <v>-5.22440334734698</v>
       </c>
       <c r="Z45" t="n">
-        <v>0.03570005636272668</v>
+        <v>-2.555149538642651</v>
       </c>
       <c r="AA45" t="b">
         <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>-0.007853383012274673</v>
+        <v>-0.02535496957403649</v>
       </c>
       <c r="AC45" t="n">
-        <v>0.03243250264596176</v>
+        <v>0.2149178255372945</v>
       </c>
       <c r="AD45" t="n">
-        <v>-0.05275483959704119</v>
+        <v>-0.07820728975951408</v>
       </c>
       <c r="AE45" t="n">
-        <v>-0.04800236947482017</v>
+        <v>0.07537291255107048</v>
       </c>
       <c r="AF45" t="n">
-        <v>-0.00475247012222102</v>
+        <v>-0.1535802023105846</v>
       </c>
       <c r="AG45" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="AH45" t="n">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="AI45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ45" t="b">
         <v>0</v>
       </c>
       <c r="AK45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM45" t="b">
         <v>0</v>
       </c>
       <c r="AN45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>540.08</v>
       </c>
       <c r="AP45" t="n">
-        <v>19.15</v>
+        <v>500.97</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6866,7 +6844,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>19.2</v>
+        <v>18</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6875,7 +6853,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="H46" t="n">
@@ -6883,7 +6861,7 @@
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="K46" t="b">
         <v>0</v>
@@ -6901,61 +6879,61 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="Q46" t="n">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="R46" t="n">
-        <v>38527797</v>
+        <v>33880570</v>
       </c>
       <c r="S46" t="n">
-        <v>252.4</v>
+        <v>245.7</v>
       </c>
       <c r="T46" t="n">
-        <v>251.125</v>
+        <v>249.95</v>
       </c>
       <c r="U46" t="n">
-        <v>251.25</v>
+        <v>250.2</v>
       </c>
       <c r="V46" t="n">
-        <v>250.6666666666667</v>
+        <v>250.8666666666667</v>
       </c>
       <c r="W46" t="n">
-        <v>0.2040105377760426</v>
+        <v>-2.088667488850518</v>
       </c>
       <c r="X46" t="n">
-        <v>0.4066900643502533</v>
+        <v>-0.5681207248432214</v>
       </c>
       <c r="Y46" t="n">
-        <v>-0.2026795265742107</v>
+        <v>-1.520546764007297</v>
       </c>
       <c r="Z46" t="n">
-        <v>0.2496273900292698</v>
+        <v>-1.534333297162695</v>
       </c>
       <c r="AA46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB46" t="n">
-        <v>-0.00994035785288272</v>
+        <v>-0.02016129032258063</v>
       </c>
       <c r="AC46" t="n">
-        <v>0.0573248407643312</v>
+        <v>0.03846153846153855</v>
       </c>
       <c r="AD46" t="n">
-        <v>-0.05484181443764924</v>
+        <v>-0.07301361050805821</v>
       </c>
       <c r="AE46" t="n">
-        <v>-0.02311003135645073</v>
+        <v>-0.1010833745246855</v>
       </c>
       <c r="AF46" t="n">
-        <v>-0.03173178308119851</v>
+        <v>0.02806976401662731</v>
       </c>
       <c r="AG46" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AH46" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="AI46" t="b">
         <v>0</v>
@@ -6970,22 +6948,22 @@
         <v>0</v>
       </c>
       <c r="AM46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN46" t="b">
         <v>1</v>
       </c>
       <c r="AO46" t="n">
-        <v>251.49</v>
+        <v>260.5</v>
       </c>
       <c r="AP46" t="n">
-        <v>254.24</v>
+        <v>255.82</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -7004,7 +6982,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>18.2</v>
+        <v>14.6</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -7013,7 +6991,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="H47" t="n">
@@ -7039,61 +7017,61 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>325.5</v>
+        <v>323</v>
       </c>
       <c r="Q47" t="n">
-        <v>325.5</v>
+        <v>323</v>
       </c>
       <c r="R47" t="n">
-        <v>16798850</v>
+        <v>12017550</v>
       </c>
       <c r="S47" t="n">
-        <v>331.4</v>
+        <v>325.7</v>
       </c>
       <c r="T47" t="n">
-        <v>336.75</v>
+        <v>334.425</v>
       </c>
       <c r="U47" t="n">
-        <v>336.875</v>
+        <v>335.1</v>
       </c>
       <c r="V47" t="n">
-        <v>328.323333231608</v>
+        <v>327.075</v>
       </c>
       <c r="W47" t="n">
-        <v>-1.888682558653556</v>
+        <v>-3.614869315014971</v>
       </c>
       <c r="X47" t="n">
-        <v>-0.3371748259986893</v>
+        <v>-1.79938684810835</v>
       </c>
       <c r="Y47" t="n">
-        <v>-1.551507732654867</v>
+        <v>-1.815482466906621</v>
       </c>
       <c r="Z47" t="n">
-        <v>-1.023144505352552</v>
+        <v>-2.011595644111465</v>
       </c>
       <c r="AA47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB47" t="n">
-        <v>-0.007621951219512146</v>
+        <v>-0.04011887072808318</v>
       </c>
       <c r="AC47" t="n">
-        <v>-0.1068511885068507</v>
+        <v>-0.007680491551459334</v>
       </c>
       <c r="AD47" t="n">
-        <v>-0.05252340780427867</v>
+        <v>-0.09297119091356076</v>
       </c>
       <c r="AE47" t="n">
-        <v>-0.1872860606276326</v>
+        <v>-0.1472254045376834</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.134762652823354</v>
+        <v>0.05425421362412264</v>
       </c>
       <c r="AG47" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="AH47" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AI47" t="b">
         <v>0</v>
@@ -7108,22 +7086,22 @@
         <v>0</v>
       </c>
       <c r="AM47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN47" t="b">
         <v>1</v>
       </c>
       <c r="AO47" t="n">
-        <v>343.08</v>
+        <v>343.67</v>
       </c>
       <c r="AP47" t="n">
-        <v>353.84</v>
+        <v>344.53</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -7142,7 +7120,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>15.4</v>
+        <v>12.2</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -7151,7 +7129,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="H48" t="n">
@@ -7159,7 +7137,7 @@
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K48" t="b">
         <v>0</v>
@@ -7177,61 +7155,61 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>874</v>
+        <v>853</v>
       </c>
       <c r="Q48" t="n">
-        <v>874</v>
+        <v>853</v>
       </c>
       <c r="R48" t="n">
-        <v>1402512</v>
+        <v>1146377</v>
       </c>
       <c r="S48" t="n">
-        <v>872.4</v>
+        <v>859.6</v>
       </c>
       <c r="T48" t="n">
-        <v>883.45</v>
+        <v>874.75</v>
       </c>
       <c r="U48" t="n">
-        <v>885.1</v>
+        <v>877.1</v>
       </c>
       <c r="V48" t="n">
-        <v>986.8333333333334</v>
+        <v>972.45</v>
       </c>
       <c r="W48" t="n">
-        <v>-12.20600999459157</v>
+        <v>-14.12111627183356</v>
       </c>
       <c r="X48" t="n">
-        <v>-17.67174304070923</v>
+        <v>-15.77202644653664</v>
       </c>
       <c r="Y48" t="n">
-        <v>5.465733046117663</v>
+        <v>1.650910174703082</v>
       </c>
       <c r="Z48" t="n">
-        <v>5.266299864369223</v>
+        <v>1.623759485461214</v>
       </c>
       <c r="AA48" t="b">
         <v>1</v>
       </c>
       <c r="AB48" t="n">
-        <v>-0.03638368246968027</v>
+        <v>-0.05222222222222217</v>
       </c>
       <c r="AC48" t="n">
-        <v>-0.2126126126126127</v>
+        <v>-0.2210045662100457</v>
       </c>
       <c r="AD48" t="n">
-        <v>-0.08128513905444679</v>
+        <v>-0.1050745424076998</v>
       </c>
       <c r="AE48" t="n">
-        <v>-0.2930474847333946</v>
+        <v>-0.3605494791962698</v>
       </c>
       <c r="AF48" t="n">
-        <v>0.2117623456789478</v>
+        <v>0.25547493678857</v>
       </c>
       <c r="AG48" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="AH48" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI48" t="b">
         <v>0</v>
@@ -7257,13 +7235,13 @@
         </is>
       </c>
       <c r="AP48" t="n">
-        <v>925.95</v>
+        <v>908.89</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -7282,7 +7260,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>13.8</v>
+        <v>11.8</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -7291,7 +7269,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="H49" t="n">
@@ -7299,7 +7277,7 @@
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="K49" t="b">
         <v>0</v>
@@ -7317,61 +7295,61 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>1205</v>
+        <v>1185</v>
       </c>
       <c r="Q49" t="n">
-        <v>1205</v>
+        <v>1185</v>
       </c>
       <c r="R49" t="n">
-        <v>1791155</v>
+        <v>1051214</v>
       </c>
       <c r="S49" t="n">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="T49" t="n">
-        <v>1235</v>
+        <v>1217.25</v>
       </c>
       <c r="U49" t="n">
-        <v>1241.5</v>
+        <v>1222.25</v>
       </c>
       <c r="V49" t="n">
-        <v>1360.415018717448</v>
+        <v>1354.890482584635</v>
       </c>
       <c r="W49" t="n">
-        <v>-26.80408035381402</v>
+        <v>-23.9936701173051</v>
       </c>
       <c r="X49" t="n">
-        <v>-36.06320445878771</v>
+        <v>-30.30419845288813</v>
       </c>
       <c r="Y49" t="n">
-        <v>9.259124104973694</v>
+        <v>6.31052833558303</v>
       </c>
       <c r="Z49" t="n">
-        <v>8.630122408340895</v>
+        <v>6.716122397234436</v>
       </c>
       <c r="AA49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>-0.09737827715355807</v>
+        <v>-0.0778210116731517</v>
       </c>
       <c r="AC49" t="n">
-        <v>-0.04586716840502081</v>
+        <v>-0.04315997553569872</v>
       </c>
       <c r="AD49" t="n">
-        <v>-0.1422797337383246</v>
+        <v>-0.1306733318586293</v>
       </c>
       <c r="AE49" t="n">
-        <v>-0.1263020405258027</v>
+        <v>-0.1827048885219228</v>
       </c>
       <c r="AF49" t="n">
-        <v>-0.01597769321252185</v>
+        <v>0.05203155666329351</v>
       </c>
       <c r="AG49" t="n">
         <v>6</v>
       </c>
       <c r="AH49" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="AI49" t="b">
         <v>0</v>
@@ -7386,7 +7364,7 @@
         <v>1</v>
       </c>
       <c r="AM49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN49" t="b">
         <v>0</v>
@@ -7397,23 +7375,23 @@
         </is>
       </c>
       <c r="AP49" t="n">
-        <v>1361.58</v>
+        <v>1303.95</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>新日興</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7422,7 +7400,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7431,15 +7409,15 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1740000</v>
+        <v>93000</v>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="K50" t="b">
         <v>0</v>
@@ -7448,7 +7426,7 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>1740000</v>
+        <v>93000</v>
       </c>
       <c r="N50" t="n">
         <v>0</v>
@@ -7457,61 +7435,61 @@
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>169.5</v>
+        <v>5615</v>
       </c>
       <c r="Q50" t="n">
-        <v>169.5</v>
+        <v>5615</v>
       </c>
       <c r="R50" t="n">
-        <v>1907173</v>
+        <v>458344</v>
       </c>
       <c r="S50" t="n">
-        <v>171.1</v>
+        <v>5695</v>
       </c>
       <c r="T50" t="n">
-        <v>177.35</v>
+        <v>5966.75</v>
       </c>
       <c r="U50" t="n">
-        <v>179.05</v>
+        <v>6030.5</v>
       </c>
       <c r="V50" t="n">
-        <v>185.4261248270671</v>
+        <v>6353.25</v>
       </c>
       <c r="W50" t="n">
-        <v>-4.40398728722613</v>
+        <v>-158.3315951329696</v>
       </c>
       <c r="X50" t="n">
-        <v>-4.591481634947813</v>
+        <v>-159.7229612997303</v>
       </c>
       <c r="Y50" t="n">
-        <v>0.1874943477216835</v>
+        <v>1.39136616676069</v>
       </c>
       <c r="Z50" t="n">
-        <v>0.1055989562781781</v>
+        <v>11.67079776438766</v>
       </c>
       <c r="AA50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>-0.1670761670761671</v>
+        <v>-0.1850507982583455</v>
       </c>
       <c r="AC50" t="n">
-        <v>-0.1228074137639538</v>
+        <v>-0.07266721717588764</v>
       </c>
       <c r="AD50" t="n">
-        <v>-0.2119776236609336</v>
+        <v>-0.2379031184438231</v>
       </c>
       <c r="AE50" t="n">
-        <v>-0.2032422858847357</v>
+        <v>-0.2122121301621117</v>
       </c>
       <c r="AF50" t="n">
-        <v>-0.008735337776197949</v>
+        <v>-0.02569098828171135</v>
       </c>
       <c r="AG50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AH50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AI50" t="b">
         <v>0</v>
@@ -7526,7 +7504,7 @@
         <v>1</v>
       </c>
       <c r="AM50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN50" t="b">
         <v>0</v>
@@ -7537,23 +7515,23 @@
         </is>
       </c>
       <c r="AP50" t="n">
-        <v>214.26</v>
+        <v>6970.26</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7562,24 +7540,24 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>10.8</v>
+        <v>9.4</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Sell</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>93000</v>
+        <v>3281561</v>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="K51" t="b">
         <v>0</v>
@@ -7588,70 +7566,70 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>93000</v>
+        <v>4315561</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>-1034000</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>-0.2395980499406682</v>
       </c>
       <c r="P51" t="n">
-        <v>5615</v>
+        <v>2115</v>
       </c>
       <c r="Q51" t="n">
-        <v>5615</v>
+        <v>2115</v>
       </c>
       <c r="R51" t="n">
-        <v>1016758</v>
+        <v>7410219</v>
       </c>
       <c r="S51" t="n">
-        <v>5908</v>
+        <v>2213</v>
       </c>
       <c r="T51" t="n">
-        <v>6168</v>
+        <v>2170</v>
       </c>
       <c r="U51" t="n">
-        <v>6272.25</v>
+        <v>2179.75</v>
       </c>
       <c r="V51" t="n">
-        <v>6396.621801757812</v>
+        <v>2134.008095296224</v>
       </c>
       <c r="W51" t="n">
-        <v>-180.8567208930126</v>
+        <v>-4.884052383353264</v>
       </c>
       <c r="X51" t="n">
-        <v>-168.136781961946</v>
+        <v>-10.88319160410798</v>
       </c>
       <c r="Y51" t="n">
-        <v>-12.71993893106657</v>
+        <v>5.999139220754717</v>
       </c>
       <c r="Z51" t="n">
-        <v>0.8205248754708236</v>
+        <v>18.48988037994293</v>
       </c>
       <c r="AA51" t="b">
         <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>-0.2707792207792208</v>
+        <v>-0.08441558441558439</v>
       </c>
       <c r="AC51" t="n">
-        <v>-0.1965169021121798</v>
+        <v>0.365500120188045</v>
       </c>
       <c r="AD51" t="n">
-        <v>-0.3156806773639873</v>
+        <v>-0.137267904601062</v>
       </c>
       <c r="AE51" t="n">
-        <v>-0.2769517742329617</v>
+        <v>0.2259552072018209</v>
       </c>
       <c r="AF51" t="n">
-        <v>-0.03872890313102562</v>
+        <v>-0.3632231118028829</v>
       </c>
       <c r="AG51" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AH51" t="n">
-        <v>6</v>
+        <v>78</v>
       </c>
       <c r="AI51" t="b">
         <v>0</v>
@@ -7660,22 +7638,24 @@
         <v>0</v>
       </c>
       <c r="AK51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM51" t="b">
         <v>0</v>
       </c>
       <c r="AN51" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO51" t="n">
-        <v>5760.99</v>
+        <v>0</v>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP51" t="n">
-        <v>7862.11</v>
+        <v>2327.89</v>
       </c>
     </row>
   </sheetData>

--- a/output/daily_screen_latest.xlsx
+++ b/output/daily_screen_latest.xlsx
@@ -643,17 +643,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -662,24 +662,24 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>92.8</v>
+        <v>89.19999999999999</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>5423000</v>
+        <v>1000</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="K2" t="b">
         <v>0</v>
@@ -688,70 +688,70 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>3741000</v>
+        <v>1000</v>
       </c>
       <c r="N2" t="n">
-        <v>1682000</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4496124031007752</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1260</v>
+        <v>303</v>
       </c>
       <c r="Q2" t="n">
-        <v>1260</v>
+        <v>303</v>
       </c>
       <c r="R2" t="n">
-        <v>16410298</v>
+        <v>57135196</v>
       </c>
       <c r="S2" t="n">
-        <v>1239</v>
+        <v>275.5</v>
       </c>
       <c r="T2" t="n">
-        <v>1119.7</v>
+        <v>226.1</v>
       </c>
       <c r="U2" t="n">
-        <v>1108.2</v>
+        <v>220.225</v>
       </c>
       <c r="V2" t="n">
-        <v>1032.166666666667</v>
+        <v>191.8666666666667</v>
       </c>
       <c r="W2" t="n">
-        <v>45.52015306233511</v>
+        <v>23.36450294887263</v>
       </c>
       <c r="X2" t="n">
-        <v>38.80155905895673</v>
+        <v>15.37237288111563</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.718594003378385</v>
+        <v>7.992130067756996</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.251479909388813</v>
+        <v>6.909923263847713</v>
       </c>
       <c r="AA2" t="b">
         <v>1</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.2233009708737863</v>
+        <v>0.633423180592992</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.3592233009708738</v>
+        <v>0.9238095238095239</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.1704486506883087</v>
+        <v>0.6092781581690612</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.2196783879846498</v>
+        <v>0.8173265107802243</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.04922973729634106</v>
+        <v>-0.2080483526111632</v>
       </c>
       <c r="AG2" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="AH2" t="n">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AI2" t="b">
         <v>1</v>
@@ -785,43 +785,43 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>3376</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>新日興</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>89.80000000000001</v>
+        <v>31.6</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1257000</v>
+        <v>1740000</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K3" t="b">
         <v>0</v>
@@ -830,76 +830,76 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1000</v>
+        <v>1740000</v>
       </c>
       <c r="N3" t="n">
-        <v>1256000</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1256</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>278</v>
+        <v>176.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>278</v>
+        <v>176.5</v>
       </c>
       <c r="R3" t="n">
-        <v>32928968</v>
+        <v>2139257</v>
       </c>
       <c r="S3" t="n">
-        <v>265</v>
+        <v>173.5</v>
       </c>
       <c r="T3" t="n">
-        <v>251.55</v>
+        <v>174.275</v>
       </c>
       <c r="U3" t="n">
-        <v>249.175</v>
+        <v>174.5</v>
       </c>
       <c r="V3" t="n">
-        <v>225.6916666666667</v>
+        <v>184.5443448384603</v>
       </c>
       <c r="W3" t="n">
-        <v>8.03486025970949</v>
+        <v>-1.853005894968362</v>
       </c>
       <c r="X3" t="n">
-        <v>5.450384237536567</v>
+        <v>-3.513798826030349</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.584476022172923</v>
+        <v>1.660792931061987</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.653064123258493</v>
+        <v>1.446399776522485</v>
       </c>
       <c r="AA3" t="b">
         <v>1</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.2060737527114966</v>
+        <v>-0.02486187845303867</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.2990654205607477</v>
+        <v>-0.03270663176625743</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.1532214325260191</v>
+        <v>-0.04900690087696946</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.1595205075745236</v>
+        <v>-0.139189644795557</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.006299075048504577</v>
+        <v>0.09018274391858749</v>
       </c>
       <c r="AG3" t="n">
-        <v>78</v>
+        <v>34</v>
       </c>
       <c r="AH3" t="n">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="AI3" t="b">
         <v>1</v>
       </c>
       <c r="AJ3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="b">
         <v>1</v>
@@ -918,124 +918,122 @@
           <t>Already &gt; 0</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+      <c r="AP3" t="n">
+        <v>170.66</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>88.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1000</v>
+        <v>7046000</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="K4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="b">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1000</v>
+        <v>6847000</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>199000</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>0.02906382357236746</v>
       </c>
       <c r="P4" t="n">
-        <v>290</v>
+        <v>1625</v>
       </c>
       <c r="Q4" t="n">
-        <v>290</v>
+        <v>1625</v>
       </c>
       <c r="R4" t="n">
-        <v>12671498</v>
+        <v>14219284</v>
       </c>
       <c r="S4" t="n">
-        <v>265</v>
+        <v>1698</v>
       </c>
       <c r="T4" t="n">
-        <v>220.225</v>
+        <v>1560.5</v>
       </c>
       <c r="U4" t="n">
-        <v>215.05</v>
+        <v>1549.75</v>
       </c>
       <c r="V4" t="n">
-        <v>189.4416666666667</v>
+        <v>1453.416666666667</v>
       </c>
       <c r="W4" t="n">
-        <v>20.28426362802409</v>
+        <v>57.73155631103646</v>
       </c>
       <c r="X4" t="n">
-        <v>13.37434036417638</v>
+        <v>63.35963080173483</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.909923263847713</v>
+        <v>-5.628074490698374</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.546905646867174</v>
+        <v>7.677347067840913</v>
       </c>
       <c r="AA4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.5549597855227881</v>
+        <v>0.1524822695035462</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.762917933130699</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.5021074653373105</v>
+        <v>0.1283372470796154</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.6233730201444749</v>
+        <v>0.3379614314151449</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.1212655548071644</v>
+        <v>-0.2096241843355295</v>
       </c>
       <c r="AG4" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="AH4" t="n">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="AI4" t="b">
         <v>1</v>
@@ -1044,21 +1042,19 @@
         <v>1</v>
       </c>
       <c r="AK4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1690</v>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
@@ -1069,139 +1065,135 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>美律</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>66.2</v>
+        <v>61.6</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1000</v>
+        <v>18938000</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="K5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="b">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1000</v>
+        <v>18721000</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>217000</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>0.01159126115057956</v>
       </c>
       <c r="P5" t="n">
-        <v>81.69999694824219</v>
+        <v>1075</v>
       </c>
       <c r="Q5" t="n">
-        <v>81.69999694824219</v>
+        <v>1075</v>
       </c>
       <c r="R5" t="n">
-        <v>2468795</v>
+        <v>29104625</v>
       </c>
       <c r="S5" t="n">
-        <v>80.67999877929688</v>
+        <v>1193</v>
       </c>
       <c r="T5" t="n">
-        <v>78.18999938964843</v>
+        <v>1154.15</v>
       </c>
       <c r="U5" t="n">
-        <v>77.92999954223633</v>
+        <v>1148.9</v>
       </c>
       <c r="V5" t="n">
-        <v>77.76605288187663</v>
+        <v>1031.466666666667</v>
       </c>
       <c r="W5" t="n">
-        <v>0.998635261325461</v>
+        <v>17.60147184379503</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3361840202081899</v>
+        <v>47.22825782463612</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.6624512411172711</v>
+        <v>-29.6267859808411</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.6292901449636699</v>
+        <v>-16.08969647293449</v>
       </c>
       <c r="AA5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.06797381631689126</v>
+        <v>0.1082474226804124</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.04722423404130893</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.01512149613141367</v>
+        <v>0.08410240025648164</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.09232067894491514</v>
+        <v>0.3268503203040338</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.1074421750763288</v>
+        <v>-0.2427479200475522</v>
       </c>
       <c r="AG5" t="n">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="AH5" t="n">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="AI5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="b">
         <v>1</v>
       </c>
       <c r="AK5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="b">
         <v>0</v>
       </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
+      <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -1211,26 +1203,26 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>65</v>
+        <v>55.6</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1239,24 +1231,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1000</v>
+        <v>8937000</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="K6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="b">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1000</v>
+        <v>8937000</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1265,61 +1257,61 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>103.5</v>
+        <v>1345</v>
       </c>
       <c r="Q6" t="n">
-        <v>103.5</v>
+        <v>1345</v>
       </c>
       <c r="R6" t="n">
-        <v>2142600</v>
+        <v>10513585</v>
       </c>
       <c r="S6" t="n">
-        <v>100.7400009155273</v>
+        <v>1426</v>
       </c>
       <c r="T6" t="n">
-        <v>99.76500053405762</v>
+        <v>1306.5</v>
       </c>
       <c r="U6" t="n">
-        <v>99.64000053405762</v>
+        <v>1292</v>
       </c>
       <c r="V6" t="n">
-        <v>93.0800001780192</v>
+        <v>1186.666666666667</v>
       </c>
       <c r="W6" t="n">
-        <v>1.047662876527113</v>
+        <v>53.28766341803134</v>
       </c>
       <c r="X6" t="n">
-        <v>0.4947362912651968</v>
+        <v>69.21207353577972</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5529265852619162</v>
+        <v>-15.92441011774838</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.3742314709814334</v>
+        <v>-2.863371057998521</v>
       </c>
       <c r="AA6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.02475247524752477</v>
+        <v>0.2748815165876777</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.3035264233120469</v>
+        <v>0.2171945701357465</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.02809984493795281</v>
+        <v>0.2507364941637469</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.1639815103258229</v>
+        <v>0.110711557106447</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.1920813552637757</v>
+        <v>0.1400249370572999</v>
       </c>
       <c r="AG6" t="n">
-        <v>30</v>
+        <v>98</v>
       </c>
       <c r="AH6" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="AI6" t="b">
         <v>1</v>
@@ -1328,21 +1320,19 @@
         <v>1</v>
       </c>
       <c r="AK6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1525.23</v>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
@@ -1353,43 +1343,43 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>62.40000000000001</v>
+        <v>54</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>5163000</v>
+        <v>5808000</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K7" t="b">
         <v>0</v>
@@ -1398,70 +1388,70 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>5163000</v>
+        <v>5423000</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>385000</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.07099391480730223</v>
       </c>
       <c r="P7" t="n">
-        <v>19.5</v>
+        <v>1190</v>
       </c>
       <c r="Q7" t="n">
-        <v>19.5</v>
+        <v>1190</v>
       </c>
       <c r="R7" t="n">
-        <v>103473086</v>
+        <v>13734387</v>
       </c>
       <c r="S7" t="n">
-        <v>19.15000038146973</v>
+        <v>1228</v>
       </c>
       <c r="T7" t="n">
-        <v>18.88500003814697</v>
+        <v>1128.2</v>
       </c>
       <c r="U7" t="n">
-        <v>18.85500001907349</v>
+        <v>1119.7</v>
       </c>
       <c r="V7" t="n">
-        <v>19.0084774017334</v>
+        <v>1036.55</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1074057745653505</v>
+        <v>38.10260243500238</v>
       </c>
       <c r="X7" t="n">
-        <v>0.03187025101903523</v>
+        <v>38.66176773416586</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.07553552354631526</v>
+        <v>-0.5591652991634817</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0480152599160486</v>
+        <v>6.718594003378385</v>
       </c>
       <c r="AA7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.03174605257036434</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.0538527216428597</v>
+        <v>0.2837108953613807</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.02110626761511325</v>
+        <v>0.1425216442427359</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.08569219134336437</v>
+        <v>0.1772278823320812</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.06458592372825112</v>
+        <v>-0.03470623808934525</v>
       </c>
       <c r="AG7" t="n">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="AH7" t="n">
-        <v>32</v>
+        <v>76</v>
       </c>
       <c r="AI7" t="b">
         <v>1</v>
@@ -1470,21 +1460,19 @@
         <v>1</v>
       </c>
       <c r="AK7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1197.14</v>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
@@ -1495,118 +1483,118 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>56.2</v>
+        <v>47.6</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>957000</v>
+        <v>8348000</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="K8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="b">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1000</v>
+        <v>8348000</v>
       </c>
       <c r="N8" t="n">
-        <v>956000</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>956</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>588</v>
+        <v>673</v>
       </c>
       <c r="Q8" t="n">
-        <v>588</v>
+        <v>673</v>
       </c>
       <c r="R8" t="n">
-        <v>10276874</v>
+        <v>38892294</v>
       </c>
       <c r="S8" t="n">
-        <v>569.8</v>
+        <v>733.2</v>
       </c>
       <c r="T8" t="n">
-        <v>571.95</v>
+        <v>694.7</v>
       </c>
       <c r="U8" t="n">
-        <v>569.1</v>
+        <v>691.65</v>
       </c>
       <c r="V8" t="n">
-        <v>533.4</v>
+        <v>632.5833333333334</v>
       </c>
       <c r="W8" t="n">
-        <v>-1.361580484362321</v>
+        <v>16.2207547112946</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1158319843365309</v>
+        <v>24.2395656431005</v>
       </c>
       <c r="Y8" t="n">
-        <v>-1.24574850002579</v>
+        <v>-8.018810931805895</v>
       </c>
       <c r="Z8" t="n">
-        <v>-4.325882074213004</v>
+        <v>-0.1113463356609614</v>
       </c>
       <c r="AA8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.1073446327683616</v>
+        <v>0.09967320261437917</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.651685393258427</v>
+        <v>0.1273031825795645</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.05449231258288401</v>
+        <v>0.07552818019044838</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.5121404802722029</v>
+        <v>0.020820169550265</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.4576481676893189</v>
+        <v>0.05470801064018338</v>
       </c>
       <c r="AG8" t="n">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="AH8" t="n">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="AI8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="b">
         <v>1</v>
@@ -1618,13 +1606,13 @@
         <v>0</v>
       </c>
       <c r="AM8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="b">
         <v>1</v>
       </c>
       <c r="AO8" t="n">
-        <v>602.11</v>
+        <v>764.53</v>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
@@ -1635,26 +1623,26 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>34</v>
+        <v>47.2</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1663,15 +1651,15 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1000</v>
+        <v>696000</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="K9" t="b">
         <v>0</v>
@@ -1680,7 +1668,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1000</v>
+        <v>696000</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1689,64 +1677,64 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>561</v>
+        <v>1520</v>
       </c>
       <c r="Q9" t="n">
-        <v>561</v>
+        <v>1520</v>
       </c>
       <c r="R9" t="n">
-        <v>1533903</v>
+        <v>4663196</v>
       </c>
       <c r="S9" t="n">
-        <v>557.4</v>
+        <v>1670</v>
       </c>
       <c r="T9" t="n">
-        <v>561</v>
+        <v>1546.75</v>
       </c>
       <c r="U9" t="n">
-        <v>559.35</v>
+        <v>1532.5</v>
       </c>
       <c r="V9" t="n">
-        <v>567.8911356608073</v>
+        <v>1269.766666666667</v>
       </c>
       <c r="W9" t="n">
-        <v>-1.852330075783925</v>
+        <v>56.77879251635659</v>
       </c>
       <c r="X9" t="n">
-        <v>0.141192790863952</v>
+        <v>75.81528451744614</v>
       </c>
       <c r="Y9" t="n">
-        <v>-1.993522866647877</v>
+        <v>-19.03649200108956</v>
       </c>
       <c r="Z9" t="n">
-        <v>-2.903465704255706</v>
+        <v>0.3863480529721812</v>
       </c>
       <c r="AA9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0625</v>
+        <v>0.2307692307692308</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.02616415481018919</v>
+        <v>0.5653964984552009</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.009647679814522414</v>
+        <v>0.2066242083453</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.1657090677964133</v>
+        <v>0.4589134854259014</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.1753567476109357</v>
+        <v>-0.2522892770806013</v>
       </c>
       <c r="AG9" t="n">
-        <v>46</v>
+        <v>96</v>
       </c>
       <c r="AH9" t="n">
-        <v>12</v>
+        <v>88</v>
       </c>
       <c r="AI9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="b">
         <v>1</v>
@@ -1758,13 +1746,13 @@
         <v>0</v>
       </c>
       <c r="AM9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="b">
         <v>1</v>
       </c>
       <c r="AO9" t="n">
-        <v>583.4400000000001</v>
+        <v>1735.84</v>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
@@ -1775,26 +1763,26 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>新日興</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>25.8</v>
+        <v>47</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1803,15 +1791,15 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1740000</v>
+        <v>751000</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K10" t="b">
         <v>0</v>
@@ -1820,7 +1808,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1740000</v>
+        <v>751000</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1829,103 +1817,101 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>179</v>
+        <v>7670</v>
       </c>
       <c r="Q10" t="n">
-        <v>179</v>
+        <v>7670</v>
       </c>
       <c r="R10" t="n">
-        <v>4312080</v>
+        <v>2351062</v>
       </c>
       <c r="S10" t="n">
-        <v>172</v>
+        <v>8094</v>
       </c>
       <c r="T10" t="n">
-        <v>174.5</v>
+        <v>7821.25</v>
       </c>
       <c r="U10" t="n">
-        <v>174.7</v>
+        <v>7757.75</v>
       </c>
       <c r="V10" t="n">
-        <v>184.6438100179036</v>
+        <v>6034.416666666667</v>
       </c>
       <c r="W10" t="n">
-        <v>-2.48259728227336</v>
+        <v>231.2510412784031</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.928997058795846</v>
+        <v>393.6329477446294</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.446399776522485</v>
+        <v>-162.3819064662263</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.5842192240967341</v>
+        <v>-110.2352865917775</v>
       </c>
       <c r="AA10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.02185792349726778</v>
+        <v>0.1984375</v>
       </c>
       <c r="AC10" t="n">
-        <v>-0.02162852631582457</v>
+        <v>1.048064085447263</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0.07471024368274537</v>
+        <v>0.1742924775760692</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.1611734393020486</v>
+        <v>0.9415810724179636</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.08646319561930327</v>
+        <v>-0.7672885948418944</v>
       </c>
       <c r="AG10" t="n">
-        <v>18</v>
+        <v>92</v>
       </c>
       <c r="AH10" t="n">
-        <v>14</v>
+        <v>98</v>
       </c>
       <c r="AI10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="b">
         <v>0</v>
       </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
-      <c r="AP10" t="n">
-        <v>176.26</v>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1934,24 +1920,24 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>57</v>
+        <v>45.4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>751000</v>
+        <v>2502000</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K11" t="b">
         <v>0</v>
@@ -1960,70 +1946,70 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>684000</v>
+        <v>2502000</v>
       </c>
       <c r="N11" t="n">
-        <v>67000</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.097953216374269</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>8245</v>
+        <v>6765</v>
       </c>
       <c r="Q11" t="n">
-        <v>8245</v>
+        <v>6765</v>
       </c>
       <c r="R11" t="n">
-        <v>1133985</v>
+        <v>1725555</v>
       </c>
       <c r="S11" t="n">
-        <v>8252</v>
+        <v>7030</v>
       </c>
       <c r="T11" t="n">
-        <v>7757.75</v>
+        <v>6499.5</v>
       </c>
       <c r="U11" t="n">
-        <v>7651.5</v>
+        <v>6452.25</v>
       </c>
       <c r="V11" t="n">
-        <v>5969</v>
+        <v>5368.221321614584</v>
       </c>
       <c r="W11" t="n">
-        <v>323.9931377694083</v>
+        <v>238.1808050766131</v>
       </c>
       <c r="X11" t="n">
-        <v>434.2284243611859</v>
+        <v>304.7328259863507</v>
       </c>
       <c r="Y11" t="n">
-        <v>-110.2352865917775</v>
+        <v>-66.55202090973768</v>
       </c>
       <c r="Z11" t="n">
-        <v>-107.6311878784226</v>
+        <v>-27.25489173255033</v>
       </c>
       <c r="AA11" t="b">
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.3472222222222223</v>
+        <v>0.1623711340206186</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.14993481095176</v>
+        <v>1.127188645757205</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.2943699020367447</v>
+        <v>0.1382261115966879</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.010389897965536</v>
+        <v>1.020705632727906</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.7160199959287912</v>
+        <v>-0.882479521131218</v>
       </c>
       <c r="AG11" t="n">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="AH11" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AI11" t="b">
         <v>1</v>
@@ -2044,7 +2030,7 @@
         <v>1</v>
       </c>
       <c r="AO11" t="n">
-        <v>9498.24</v>
+        <v>7522.68</v>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
@@ -2055,17 +2041,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2074,24 +2060,24 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>55</v>
+        <v>44.4</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>696000</v>
+        <v>1257000</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K12" t="b">
         <v>0</v>
@@ -2100,70 +2086,70 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>576000</v>
+        <v>1257000</v>
       </c>
       <c r="N12" t="n">
-        <v>120000</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2083333333333333</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1685</v>
+        <v>268</v>
       </c>
       <c r="Q12" t="n">
-        <v>1685</v>
+        <v>268</v>
       </c>
       <c r="R12" t="n">
-        <v>3879459</v>
+        <v>22397989</v>
       </c>
       <c r="S12" t="n">
-        <v>1695</v>
+        <v>268.6</v>
       </c>
       <c r="T12" t="n">
-        <v>1532.5</v>
+        <v>253.575</v>
       </c>
       <c r="U12" t="n">
-        <v>1514.75</v>
+        <v>251.55</v>
       </c>
       <c r="V12" t="n">
-        <v>1260.616666666667</v>
+        <v>226.8666666666667</v>
       </c>
       <c r="W12" t="n">
-        <v>80.96075557069071</v>
+        <v>7.815996187242945</v>
       </c>
       <c r="X12" t="n">
-        <v>80.57440751771853</v>
+        <v>5.923506627477843</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.3863480529721812</v>
+        <v>1.892489559765102</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.051104642281345</v>
+        <v>2.584476022172923</v>
       </c>
       <c r="AA12" t="b">
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.2669172932330828</v>
+        <v>0.1780219780219781</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.6600985221674878</v>
+        <v>0.3569620253164556</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.2140649730476052</v>
+        <v>0.1538769555980473</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.5205536091812637</v>
+        <v>0.2504790122871561</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.3064886361336585</v>
+        <v>-0.09660205668910882</v>
       </c>
       <c r="AG12" t="n">
         <v>90</v>
       </c>
       <c r="AH12" t="n">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="AI12" t="b">
         <v>1</v>
@@ -2197,17 +2183,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2216,7 +2202,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>54.59999999999999</v>
+        <v>42.8</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2225,24 +2211,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>6847000</v>
+        <v>121000</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="K13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="b">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>6847000</v>
+        <v>121000</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -2251,61 +2237,61 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1735</v>
+        <v>1390</v>
       </c>
       <c r="Q13" t="n">
-        <v>1735</v>
+        <v>1390</v>
       </c>
       <c r="R13" t="n">
-        <v>9715675</v>
+        <v>3407870</v>
       </c>
       <c r="S13" t="n">
-        <v>1717</v>
+        <v>1546</v>
       </c>
       <c r="T13" t="n">
-        <v>1549.75</v>
+        <v>1364.25</v>
       </c>
       <c r="U13" t="n">
-        <v>1531.25</v>
+        <v>1356</v>
       </c>
       <c r="V13" t="n">
-        <v>1445.083333333333</v>
+        <v>1244.200631713867</v>
       </c>
       <c r="W13" t="n">
-        <v>72.44399649225033</v>
+        <v>60.63853146731913</v>
       </c>
       <c r="X13" t="n">
-        <v>64.76664942440942</v>
+        <v>60.42184308991468</v>
       </c>
       <c r="Y13" t="n">
-        <v>7.677347067840913</v>
+        <v>0.216688377404445</v>
       </c>
       <c r="Z13" t="n">
-        <v>10.61132065076194</v>
+        <v>24.02794551791079</v>
       </c>
       <c r="AA13" t="b">
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.271062271062271</v>
+        <v>0.1346938775510205</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.482905982905983</v>
+        <v>0.5055280513162139</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.2182099508767934</v>
+        <v>0.1105488551270897</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.3433610699197589</v>
+        <v>0.3990450382869144</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.1251511190429655</v>
+        <v>-0.2884961831598247</v>
       </c>
       <c r="AG13" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AH13" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="AI13" t="b">
         <v>1</v>
@@ -2339,17 +2325,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2358,7 +2344,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53.2</v>
+        <v>42.4</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2367,24 +2353,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>8937000</v>
+        <v>1000</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="K14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="b">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>8937000</v>
+        <v>1000</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2393,62 +2379,62 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1430</v>
+        <v>6605</v>
       </c>
       <c r="Q14" t="n">
-        <v>1430</v>
+        <v>6605</v>
       </c>
       <c r="R14" t="n">
-        <v>7127829</v>
+        <v>3317049</v>
       </c>
       <c r="S14" t="n">
-        <v>1453</v>
+        <v>6949</v>
       </c>
       <c r="T14" t="n">
-        <v>1292</v>
+        <v>6480.25</v>
       </c>
       <c r="U14" t="n">
-        <v>1274.5</v>
+        <v>6449.75</v>
       </c>
       <c r="V14" t="n">
-        <v>1182.666666666667</v>
+        <v>5741.891507975261</v>
       </c>
       <c r="W14" t="n">
-        <v>70.32980500721828</v>
+        <v>149.9785618622345</v>
       </c>
       <c r="X14" t="n">
-        <v>73.1931760652168</v>
+        <v>127.2206041127149</v>
       </c>
       <c r="Y14" t="n">
-        <v>-2.863371057998521</v>
+        <v>22.75795774951962</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.898533654461474</v>
+        <v>78.81847565582092</v>
       </c>
       <c r="AA14" t="b">
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.3240740740740742</v>
+        <v>0.1017514595496247</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.2434782608695651</v>
+        <v>0.7200851100732957</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.2712217538885966</v>
+        <v>0.07760643712569393</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.1039333478833411</v>
+        <v>0.6136020970439962</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.1672884060052555</v>
+        <v>-0.5359956599183022</v>
       </c>
       <c r="AG14" t="n">
+        <v>78</v>
+      </c>
+      <c r="AH14" t="n">
         <v>94</v>
       </c>
-      <c r="AH14" t="n">
-        <v>60</v>
-      </c>
       <c r="AI14" t="b">
         <v>1</v>
       </c>
@@ -2456,19 +2442,21 @@
         <v>1</v>
       </c>
       <c r="AK14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM14" t="b">
         <v>0</v>
       </c>
       <c r="AN14" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>1464.32</v>
+        <v>0</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
@@ -2479,17 +2467,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2498,7 +2486,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>51.8</v>
+        <v>41.6</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2507,15 +2495,15 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>18721000</v>
+        <v>23519000</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K15" t="b">
         <v>1</v>
@@ -2524,7 +2512,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>18721000</v>
+        <v>23519000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2533,64 +2521,64 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1185</v>
+        <v>573</v>
       </c>
       <c r="Q15" t="n">
-        <v>1185</v>
+        <v>573</v>
       </c>
       <c r="R15" t="n">
-        <v>17256069</v>
+        <v>55840314</v>
       </c>
       <c r="S15" t="n">
-        <v>1239</v>
+        <v>614</v>
       </c>
       <c r="T15" t="n">
-        <v>1148.9</v>
+        <v>586.25</v>
       </c>
       <c r="U15" t="n">
-        <v>1138.5</v>
+        <v>584.85</v>
       </c>
       <c r="V15" t="n">
-        <v>1026.05</v>
+        <v>578.9916666666667</v>
       </c>
       <c r="W15" t="n">
-        <v>38.54525784691191</v>
+        <v>9.119528519109963</v>
       </c>
       <c r="X15" t="n">
-        <v>54.6349543198464</v>
+        <v>13.22992947122095</v>
       </c>
       <c r="Y15" t="n">
-        <v>-16.08969647293449</v>
+        <v>-4.110400952110991</v>
       </c>
       <c r="Z15" t="n">
-        <v>-8.873617902620666</v>
+        <v>1.572349389277775</v>
       </c>
       <c r="AA15" t="b">
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.2128966223132036</v>
+        <v>0.05137614678899083</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.4924433249370277</v>
+        <v>-0.09047619047619049</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.160044302127726</v>
+        <v>0.02723112436506003</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.3528984119508036</v>
+        <v>-0.19695920350549</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.1928541098230776</v>
+        <v>0.22419032787055</v>
       </c>
       <c r="AG15" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="AH15" t="n">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="AI15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="b">
         <v>1</v>
@@ -2608,7 +2596,7 @@
         <v>1</v>
       </c>
       <c r="AO15" t="n">
-        <v>1367.49</v>
+        <v>619.99</v>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
@@ -2619,17 +2607,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2638,7 +2626,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>48.6</v>
+        <v>40.6</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2647,24 +2635,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>8348000</v>
+        <v>1000</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="K16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="b">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>8348000</v>
+        <v>1000</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2673,64 +2661,64 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>747</v>
+        <v>105.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>747</v>
+        <v>105.5</v>
       </c>
       <c r="R16" t="n">
-        <v>12849867</v>
+        <v>29963917</v>
       </c>
       <c r="S16" t="n">
-        <v>745</v>
+        <v>117.9</v>
       </c>
       <c r="T16" t="n">
-        <v>691.65</v>
+        <v>110.5349998474121</v>
       </c>
       <c r="U16" t="n">
-        <v>685.2</v>
+        <v>109.5899997711182</v>
       </c>
       <c r="V16" t="n">
-        <v>631.3166666666667</v>
+        <v>95.88999989827474</v>
       </c>
       <c r="W16" t="n">
-        <v>26.13292204039101</v>
+        <v>3.315660036079052</v>
       </c>
       <c r="X16" t="n">
-        <v>26.24426837605197</v>
+        <v>6.159377143649936</v>
       </c>
       <c r="Y16" t="n">
-        <v>-0.1113463356609614</v>
+        <v>-2.843717107570884</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.371883322852828</v>
+        <v>-1.356631719348664</v>
       </c>
       <c r="AA16" t="b">
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.2087378640776698</v>
+        <v>0.2182448251604396</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.216612377850163</v>
+        <v>0.02427184466019416</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.1558855438921922</v>
+        <v>0.1940998027365088</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.07706746486393889</v>
+        <v>-0.08221116836910536</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.07881807902825333</v>
+        <v>0.2763109711056142</v>
       </c>
       <c r="AG16" t="n">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="AH16" t="n">
-        <v>56.00000000000001</v>
+        <v>28</v>
       </c>
       <c r="AI16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="b">
         <v>1</v>
@@ -2745,11 +2733,9 @@
         <v>0</v>
       </c>
       <c r="AN16" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>748.49</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO16" t="inlineStr"/>
       <c r="AP16" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -2759,17 +2745,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,7 +2764,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>44.8</v>
+        <v>39.40000000000001</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2787,24 +2773,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>2502000</v>
+        <v>12188000</v>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="K17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="b">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2502000</v>
+        <v>12188000</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2813,64 +2799,64 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>7070</v>
+        <v>2440</v>
       </c>
       <c r="Q17" t="n">
-        <v>7070</v>
+        <v>2440</v>
       </c>
       <c r="R17" t="n">
-        <v>1166967</v>
+        <v>57820478</v>
       </c>
       <c r="S17" t="n">
-        <v>7038</v>
+        <v>2502</v>
       </c>
       <c r="T17" t="n">
-        <v>6452.25</v>
+        <v>2488.9</v>
       </c>
       <c r="U17" t="n">
-        <v>6387</v>
+        <v>2485.550732421875</v>
       </c>
       <c r="V17" t="n">
-        <v>5308.475553385417</v>
+        <v>2416.213037109375</v>
       </c>
       <c r="W17" t="n">
-        <v>294.1159394812348</v>
+        <v>6.539743496080519</v>
       </c>
       <c r="X17" t="n">
-        <v>321.3708312137852</v>
+        <v>22.45524442090876</v>
       </c>
       <c r="Y17" t="n">
-        <v>-27.25489173255033</v>
+        <v>-15.91550092482824</v>
       </c>
       <c r="Z17" t="n">
-        <v>-12.68443595476111</v>
+        <v>-9.164258495517888</v>
       </c>
       <c r="AA17" t="b">
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.2263660017346054</v>
+        <v>0.02822795535906453</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.216167287618883</v>
+        <v>0.054819980938972</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.1735136815491278</v>
+        <v>0.004082932935133732</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.076622374632659</v>
+        <v>-0.05166303209032752</v>
       </c>
       <c r="AF17" t="n">
-        <v>-0.9031086930835315</v>
+        <v>0.05574596502546125</v>
       </c>
       <c r="AG17" t="n">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="AH17" t="n">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="AI17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="b">
         <v>1</v>
@@ -2888,7 +2874,7 @@
         <v>1</v>
       </c>
       <c r="AO17" t="n">
-        <v>7381.08</v>
+        <v>2620.56</v>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
@@ -2899,17 +2885,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2918,7 +2904,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>44</v>
+        <v>39.4</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2927,24 +2913,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>121000</v>
+        <v>6264000</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="K18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="b">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>121000</v>
+        <v>6264000</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2953,61 +2939,61 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1540</v>
+        <v>1950</v>
       </c>
       <c r="Q18" t="n">
-        <v>1540</v>
+        <v>1950</v>
       </c>
       <c r="R18" t="n">
-        <v>3383472</v>
+        <v>4607746</v>
       </c>
       <c r="S18" t="n">
-        <v>1575</v>
+        <v>2048</v>
       </c>
       <c r="T18" t="n">
-        <v>1356</v>
+        <v>1935.25</v>
       </c>
       <c r="U18" t="n">
-        <v>1341.5</v>
+        <v>1931.5</v>
       </c>
       <c r="V18" t="n">
-        <v>1236.421700032552</v>
+        <v>2069.171905517578</v>
       </c>
       <c r="W18" t="n">
-        <v>84.39561651347435</v>
+        <v>22.5393164659597</v>
       </c>
       <c r="X18" t="n">
-        <v>60.36767099556356</v>
+        <v>14.55305818500008</v>
       </c>
       <c r="Y18" t="n">
-        <v>24.02794551791079</v>
+        <v>7.986258280959616</v>
       </c>
       <c r="Z18" t="n">
-        <v>37.27658646366756</v>
+        <v>22.9108081901605</v>
       </c>
       <c r="AA18" t="b">
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.232</v>
+        <v>0.04000000000000004</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.5995645463044539</v>
+        <v>-0.05960032542877358</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.1791476798145224</v>
+        <v>0.01585497757606924</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.4600196333182298</v>
+        <v>-0.1660833384580731</v>
       </c>
       <c r="AF18" t="n">
-        <v>-0.2808719535037074</v>
+        <v>0.1819383160341423</v>
       </c>
       <c r="AG18" t="n">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="AH18" t="n">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="AI18" t="b">
         <v>1</v>
@@ -3041,17 +3027,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>6271</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,7 +3046,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>41.8</v>
+        <v>35.6</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3069,15 +3055,15 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1000</v>
+        <v>2185000</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="K19" t="b">
         <v>0</v>
@@ -3086,7 +3072,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1000</v>
+        <v>2185000</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -3095,64 +3081,64 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>117</v>
+        <v>229</v>
       </c>
       <c r="Q19" t="n">
-        <v>117</v>
+        <v>229</v>
       </c>
       <c r="R19" t="n">
-        <v>19316431</v>
+        <v>2458715</v>
       </c>
       <c r="S19" t="n">
-        <v>122.5</v>
+        <v>240.8</v>
       </c>
       <c r="T19" t="n">
-        <v>109.5899997711182</v>
+        <v>233</v>
       </c>
       <c r="U19" t="n">
-        <v>108.0749996185303</v>
+        <v>232.55</v>
       </c>
       <c r="V19" t="n">
-        <v>95.84833323160807</v>
+        <v>210.575</v>
       </c>
       <c r="W19" t="n">
-        <v>5.513674701193992</v>
+        <v>3.198866842150721</v>
       </c>
       <c r="X19" t="n">
-        <v>6.870306420542656</v>
+        <v>4.465841089938604</v>
       </c>
       <c r="Y19" t="n">
-        <v>-1.356631719348664</v>
+        <v>-1.266974247787883</v>
       </c>
       <c r="Z19" t="n">
-        <v>-0.5616496764729142</v>
+        <v>0.2099306232097398</v>
       </c>
       <c r="AA19" t="b">
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.349481016358584</v>
+        <v>0.04090909090909101</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.05882352941176472</v>
+        <v>0.1896103896103896</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.2966286961731064</v>
+        <v>0.01676406848516021</v>
       </c>
       <c r="AE19" t="n">
-        <v>-0.08072138357445935</v>
+        <v>0.08312737658109004</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.3773500797475657</v>
+        <v>-0.06636330809592983</v>
       </c>
       <c r="AG19" t="n">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="AH19" t="n">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="AI19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="b">
         <v>1</v>
@@ -3170,7 +3156,7 @@
         <v>1</v>
       </c>
       <c r="AO19" t="n">
-        <v>132.44</v>
+        <v>243.66</v>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
@@ -3181,17 +3167,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3200,7 +3186,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>41.2</v>
+        <v>35.4</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3209,24 +3195,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>23519000</v>
+        <v>1000</v>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="K20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="b">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>23519000</v>
+        <v>1000</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -3235,84 +3221,82 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>627</v>
+        <v>519</v>
       </c>
       <c r="Q20" t="n">
-        <v>627</v>
+        <v>519</v>
       </c>
       <c r="R20" t="n">
-        <v>47584088</v>
+        <v>24674635</v>
       </c>
       <c r="S20" t="n">
-        <v>628.8</v>
+        <v>562.2</v>
       </c>
       <c r="T20" t="n">
-        <v>584.85</v>
+        <v>523</v>
       </c>
       <c r="U20" t="n">
-        <v>580.7</v>
+        <v>521.525</v>
       </c>
       <c r="V20" t="n">
-        <v>579.9416666666667</v>
+        <v>489.9916666666667</v>
       </c>
       <c r="W20" t="n">
-        <v>15.82987909852648</v>
+        <v>14.08868689011672</v>
       </c>
       <c r="X20" t="n">
-        <v>14.2575297092487</v>
+        <v>18.40633977612585</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.572349389277775</v>
+        <v>-4.317652886009135</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.427555285448655</v>
+        <v>1.738418848632652</v>
       </c>
       <c r="AA20" t="b">
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.1525735294117647</v>
+        <v>0.06026557711950975</v>
       </c>
       <c r="AC20" t="n">
-        <v>-0.1030042918454935</v>
+        <v>0.08463949843260199</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.09972120922628713</v>
+        <v>0.03612055469557895</v>
       </c>
       <c r="AE20" t="n">
-        <v>-0.2425492048317176</v>
+        <v>-0.02184351459669753</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.3422704140580047</v>
+        <v>0.05796406929227649</v>
       </c>
       <c r="AG20" t="n">
         <v>72</v>
       </c>
       <c r="AH20" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="AI20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="b">
         <v>1</v>
       </c>
       <c r="AK20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="b">
         <v>0</v>
       </c>
       <c r="AN20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>567.79</v>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
@@ -3323,17 +3307,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,7 +3326,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>38.40000000000001</v>
+        <v>34.8</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3351,24 +3335,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>2887848</v>
+        <v>7389000</v>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="K21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="b">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>2887848</v>
+        <v>7389000</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -3377,61 +3361,61 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2235</v>
+        <v>1630</v>
       </c>
       <c r="Q21" t="n">
-        <v>2235</v>
+        <v>1630</v>
       </c>
       <c r="R21" t="n">
-        <v>1806449</v>
+        <v>25165431</v>
       </c>
       <c r="S21" t="n">
-        <v>2305</v>
+        <v>1811</v>
       </c>
       <c r="T21" t="n">
-        <v>2292.25</v>
+        <v>1850</v>
       </c>
       <c r="U21" t="n">
-        <v>2274.25</v>
+        <v>1849.5</v>
       </c>
       <c r="V21" t="n">
-        <v>2187.25</v>
+        <v>1781.416666666667</v>
       </c>
       <c r="W21" t="n">
-        <v>15.6507890384496</v>
+        <v>-21.4246656271639</v>
       </c>
       <c r="X21" t="n">
-        <v>54.02445790860366</v>
+        <v>22.09384128504931</v>
       </c>
       <c r="Y21" t="n">
-        <v>-38.37366887015406</v>
+        <v>-43.51850691221321</v>
       </c>
       <c r="Z21" t="n">
-        <v>-31.54489498427109</v>
+        <v>-26.40925109269831</v>
       </c>
       <c r="AA21" t="b">
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.1919999999999999</v>
+        <v>0.006172839506172867</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.2662889518413598</v>
+        <v>-0.04398826979472137</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.1391476798145224</v>
+        <v>-0.01797218291775793</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.1267440388551357</v>
+        <v>-0.1504712828240209</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.01240364095938662</v>
+        <v>0.132499099906263</v>
       </c>
       <c r="AG21" t="n">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="AH21" t="n">
-        <v>66</v>
+        <v>14</v>
       </c>
       <c r="AI21" t="b">
         <v>0</v>
@@ -3451,9 +3435,7 @@
       <c r="AN21" t="b">
         <v>0</v>
       </c>
-      <c r="AO21" t="n">
-        <v>2668.59</v>
-      </c>
+      <c r="AO21" t="inlineStr"/>
       <c r="AP21" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -3463,17 +3445,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3482,7 +3464,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3491,24 +3473,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>7389000</v>
+        <v>3921000</v>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="K22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" t="b">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>7389000</v>
+        <v>3921000</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -3517,82 +3499,84 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1785</v>
+        <v>90</v>
       </c>
       <c r="Q22" t="n">
-        <v>1785</v>
+        <v>90</v>
       </c>
       <c r="R22" t="n">
-        <v>9678701</v>
+        <v>6093412</v>
       </c>
       <c r="S22" t="n">
-        <v>1883</v>
+        <v>92.64000091552734</v>
       </c>
       <c r="T22" t="n">
-        <v>1849.5</v>
+        <v>86.06000022888183</v>
       </c>
       <c r="U22" t="n">
-        <v>1841.25</v>
+        <v>85.66000022888184</v>
       </c>
       <c r="V22" t="n">
-        <v>1782.666666666667</v>
+        <v>84.71500015258789</v>
       </c>
       <c r="W22" t="n">
-        <v>6.564216920404306</v>
+        <v>2.580452518079056</v>
       </c>
       <c r="X22" t="n">
-        <v>32.97346801310261</v>
+        <v>1.765648662409141</v>
       </c>
       <c r="Y22" t="n">
-        <v>-26.40925109269831</v>
+        <v>0.8148038556699149</v>
       </c>
       <c r="Z22" t="n">
-        <v>-17.67279507101218</v>
+        <v>1.448617325328615</v>
       </c>
       <c r="AA22" t="b">
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.1018518518518519</v>
+        <v>0.09756097560975618</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.02586206896551735</v>
+        <v>-0.005524861878453025</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.04899953166637427</v>
+        <v>0.07341595318582539</v>
       </c>
       <c r="AE22" t="n">
-        <v>-0.1136828440207067</v>
+        <v>-0.1120078749077525</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.162682375687081</v>
+        <v>0.1854238280935779</v>
       </c>
       <c r="AG22" t="n">
-        <v>56.00000000000001</v>
+        <v>74</v>
       </c>
       <c r="AH22" t="n">
         <v>22</v>
       </c>
       <c r="AI22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ22" t="b">
         <v>1</v>
       </c>
       <c r="AK22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM22" t="b">
         <v>0</v>
       </c>
       <c r="AN22" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>2084.88</v>
+        <v>0</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
@@ -3603,17 +3587,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3622,7 +3606,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>36.4</v>
+        <v>33.40000000000001</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3631,15 +3615,15 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>6264000</v>
+        <v>6147000</v>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K23" t="b">
         <v>1</v>
@@ -3648,7 +3632,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>6264000</v>
+        <v>6147000</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -3657,73 +3641,73 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2050</v>
+        <v>3085</v>
       </c>
       <c r="Q23" t="n">
-        <v>2050</v>
+        <v>3085</v>
       </c>
       <c r="R23" t="n">
-        <v>4423619</v>
+        <v>4117102</v>
       </c>
       <c r="S23" t="n">
-        <v>2061</v>
+        <v>3301</v>
       </c>
       <c r="T23" t="n">
-        <v>1931.5</v>
+        <v>3392</v>
       </c>
       <c r="U23" t="n">
-        <v>1923.25</v>
+        <v>3403.25</v>
       </c>
       <c r="V23" t="n">
-        <v>2071.231679280599</v>
+        <v>3076.488163248698</v>
       </c>
       <c r="W23" t="n">
-        <v>35.46730180492068</v>
+        <v>-37.20146169987493</v>
       </c>
       <c r="X23" t="n">
-        <v>12.55649361476018</v>
+        <v>25.30141772105226</v>
       </c>
       <c r="Y23" t="n">
-        <v>22.9108081901605</v>
+        <v>-62.50287942092719</v>
       </c>
       <c r="Z23" t="n">
-        <v>29.99979968137937</v>
+        <v>-42.45656714513813</v>
       </c>
       <c r="AA23" t="b">
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.08753315649867366</v>
+        <v>-0.06797583081571001</v>
       </c>
       <c r="AC23" t="n">
-        <v>-0.01137470109178762</v>
+        <v>0.4535368719307133</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.03468083631319607</v>
+        <v>-0.09212085323964081</v>
       </c>
       <c r="AE23" t="n">
-        <v>-0.1509196140780117</v>
+        <v>0.3470538589014138</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.1856004503912078</v>
+        <v>-0.4391747121410546</v>
       </c>
       <c r="AG23" t="n">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="AH23" t="n">
-        <v>18</v>
+        <v>84</v>
       </c>
       <c r="AI23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="b">
         <v>0</v>
@@ -3731,31 +3715,25 @@
       <c r="AN23" t="b">
         <v>0</v>
       </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
-      <c r="AP23" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+      <c r="AO23" t="inlineStr"/>
+      <c r="AP23" t="n">
+        <v>3438.16</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>美律</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3764,7 +3742,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>35</v>
+        <v>33.2</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3773,24 +3751,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>12188000</v>
+        <v>1000</v>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="K24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" t="b">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>12188000</v>
+        <v>1000</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3799,61 +3777,61 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2490</v>
+        <v>80.90000152587891</v>
       </c>
       <c r="Q24" t="n">
-        <v>2490</v>
+        <v>80.90000152587891</v>
       </c>
       <c r="R24" t="n">
-        <v>24699844</v>
+        <v>2756912</v>
       </c>
       <c r="S24" t="n">
-        <v>2531</v>
+        <v>81.11999969482422</v>
       </c>
       <c r="T24" t="n">
-        <v>2485.550732421875</v>
+        <v>78.3699993133545</v>
       </c>
       <c r="U24" t="n">
-        <v>2481.1970703125</v>
+        <v>78.18999938964843</v>
       </c>
       <c r="V24" t="n">
-        <v>2414.099552408854</v>
+        <v>77.81253980000814</v>
       </c>
       <c r="W24" t="n">
-        <v>17.26986115713817</v>
+        <v>1.022513155601047</v>
       </c>
       <c r="X24" t="n">
-        <v>26.43411965319505</v>
+        <v>0.4734498472867613</v>
       </c>
       <c r="Y24" t="n">
-        <v>-9.164258496056888</v>
+        <v>0.5490633083142854</v>
       </c>
       <c r="Z24" t="n">
-        <v>-4.587469402347715</v>
+        <v>0.6624512411172711</v>
       </c>
       <c r="AA24" t="b">
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.03623632801307974</v>
+        <v>0.04657177661054734</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.09053699032645413</v>
+        <v>0.0357084496915796</v>
       </c>
       <c r="AD24" t="n">
-        <v>-0.01661599217239784</v>
+        <v>0.02242675418661655</v>
       </c>
       <c r="AE24" t="n">
-        <v>-0.04900792265976994</v>
+        <v>-0.07077456333771992</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.0323919304873721</v>
+        <v>0.09320131752433647</v>
       </c>
       <c r="AG24" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="AH24" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AI24" t="b">
         <v>1</v>
@@ -3862,19 +3840,21 @@
         <v>1</v>
       </c>
       <c r="AK24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM24" t="b">
         <v>0</v>
       </c>
       <c r="AN24" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>2594.58</v>
+        <v>0</v>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
@@ -3885,17 +3865,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3904,7 +3884,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>34.8</v>
+        <v>32.8</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3913,15 +3893,15 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>3921000</v>
+        <v>4143450</v>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K25" t="b">
         <v>0</v>
@@ -3930,7 +3910,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3921000</v>
+        <v>4143450</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3939,73 +3919,73 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>95.40000152587891</v>
+        <v>272</v>
       </c>
       <c r="Q25" t="n">
-        <v>95.40000152587891</v>
+        <v>272</v>
       </c>
       <c r="R25" t="n">
-        <v>8472107</v>
+        <v>45882595</v>
       </c>
       <c r="S25" t="n">
-        <v>92.14000091552734</v>
+        <v>295.6</v>
       </c>
       <c r="T25" t="n">
-        <v>85.66000022888184</v>
+        <v>292.925</v>
       </c>
       <c r="U25" t="n">
-        <v>85.00500030517578</v>
+        <v>292.4</v>
       </c>
       <c r="V25" t="n">
-        <v>84.72333348592123</v>
+        <v>265.0567036946615</v>
       </c>
       <c r="W25" t="n">
-        <v>3.010565023820277</v>
+        <v>1.59777248717279</v>
       </c>
       <c r="X25" t="n">
-        <v>1.561947698491662</v>
+        <v>5.819726435740899</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.448617325328615</v>
+        <v>-4.221953948568109</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.457521106383786</v>
+        <v>-1.674281199515953</v>
       </c>
       <c r="AA25" t="b">
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.1591737301137475</v>
+        <v>0.04015296367112819</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.06950678015419931</v>
+        <v>0.05985459857167075</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.1063214099282699</v>
+        <v>0.0160079412471974</v>
       </c>
       <c r="AE25" t="n">
-        <v>-0.07003813283202476</v>
+        <v>-0.04662841445762878</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.1763595427602946</v>
+        <v>0.06263635570482617</v>
       </c>
       <c r="AG25" t="n">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="AH25" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AI25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="b">
         <v>1</v>
       </c>
       <c r="AK25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="b">
         <v>0</v>
@@ -4013,10 +3993,8 @@
       <c r="AN25" t="b">
         <v>0</v>
       </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+      <c r="AO25" t="n">
+        <v>319.87</v>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
@@ -4027,17 +4005,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4046,7 +4024,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>34.6</v>
+        <v>32.6</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4055,24 +4033,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>6147000</v>
+        <v>501000</v>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="K26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" t="b">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>6147000</v>
+        <v>501000</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -4081,67 +4059,67 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>3315</v>
+        <v>228</v>
       </c>
       <c r="Q26" t="n">
-        <v>3315</v>
+        <v>228</v>
       </c>
       <c r="R26" t="n">
-        <v>2306874</v>
+        <v>29280281</v>
       </c>
       <c r="S26" t="n">
-        <v>3393</v>
+        <v>244.4</v>
       </c>
       <c r="T26" t="n">
-        <v>3403.25</v>
+        <v>232.625</v>
       </c>
       <c r="U26" t="n">
-        <v>3406</v>
+        <v>232.275</v>
       </c>
       <c r="V26" t="n">
-        <v>3060.444982910156</v>
+        <v>220.9166666666667</v>
       </c>
       <c r="W26" t="n">
-        <v>-1.529429568854084</v>
+        <v>3.570178908878006</v>
       </c>
       <c r="X26" t="n">
-        <v>40.92713757628405</v>
+        <v>4.140878752560598</v>
       </c>
       <c r="Y26" t="n">
-        <v>-42.45656714513813</v>
+        <v>-0.5706998436825916</v>
       </c>
       <c r="Z26" t="n">
-        <v>-38.3833256858796</v>
+        <v>1.790828440288431</v>
       </c>
       <c r="AA26" t="b">
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>-0.01632047477744802</v>
+        <v>0.03167420814479649</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.5157570982460709</v>
+        <v>0.1457286432160805</v>
       </c>
       <c r="AD26" t="n">
-        <v>-0.06917279496292561</v>
+        <v>0.007529185720865694</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.3762121852598468</v>
+        <v>0.03924563018678096</v>
       </c>
       <c r="AF26" t="n">
-        <v>-0.4453849802227724</v>
+        <v>-0.03171644446591526</v>
       </c>
       <c r="AG26" t="n">
-        <v>24</v>
+        <v>57.99999999999999</v>
       </c>
       <c r="AH26" t="n">
-        <v>84</v>
+        <v>56.00000000000001</v>
       </c>
       <c r="AI26" t="b">
         <v>0</v>
       </c>
       <c r="AJ26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK26" t="b">
         <v>0</v>
@@ -4156,26 +4134,28 @@
         <v>1</v>
       </c>
       <c r="AO26" t="n">
-        <v>3798.99</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>3402.89</v>
+        <v>234.84</v>
+      </c>
+      <c r="AP26" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4184,7 +4164,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>34.2</v>
+        <v>32.40000000000001</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4193,15 +4173,15 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>501000</v>
+        <v>1000</v>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="K27" t="b">
         <v>0</v>
@@ -4210,7 +4190,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>501000</v>
+        <v>1000</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -4219,84 +4199,82 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>250.5</v>
+        <v>3705</v>
       </c>
       <c r="Q27" t="n">
-        <v>250.5</v>
+        <v>3705</v>
       </c>
       <c r="R27" t="n">
-        <v>18919220</v>
+        <v>2288438</v>
       </c>
       <c r="S27" t="n">
-        <v>248</v>
+        <v>4088</v>
       </c>
       <c r="T27" t="n">
-        <v>232.275</v>
+        <v>3810.25</v>
       </c>
       <c r="U27" t="n">
-        <v>230.825</v>
+        <v>3804.5</v>
       </c>
       <c r="V27" t="n">
-        <v>220.4333333333333</v>
+        <v>3746.420072428386</v>
       </c>
       <c r="W27" t="n">
-        <v>6.074382153769676</v>
+        <v>48.32045379790452</v>
       </c>
       <c r="X27" t="n">
-        <v>4.283553713481245</v>
+        <v>73.53619909781604</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.790828440288431</v>
+        <v>-25.21574529991152</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.027673024087094</v>
+        <v>19.32442396916858</v>
       </c>
       <c r="AA27" t="b">
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.1309255079006773</v>
+        <v>0.03203342618384397</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.1816037735849056</v>
+        <v>0.1096459485004035</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.07807318771519967</v>
+        <v>0.007888403759913176</v>
       </c>
       <c r="AE27" t="n">
-        <v>0.04205886059868158</v>
+        <v>0.003162935471104023</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.03601432711651809</v>
+        <v>0.004725468288809154</v>
       </c>
       <c r="AG27" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="AH27" t="n">
         <v>48</v>
       </c>
       <c r="AI27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="b">
         <v>1</v>
       </c>
       <c r="AK27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM27" t="b">
         <v>0</v>
       </c>
       <c r="AN27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>3993.99</v>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
@@ -4307,17 +4285,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4326,7 +4304,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>33.8</v>
+        <v>31</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4335,99 +4313,99 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1000</v>
+        <v>2887848</v>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
+        <v>18</v>
+      </c>
+      <c r="K28" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" t="b">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>2887848</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2015</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2015</v>
+      </c>
+      <c r="R28" t="n">
+        <v>3266361</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2245</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2295.25</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2292.25</v>
+      </c>
+      <c r="V28" t="n">
+        <v>2190.5</v>
+      </c>
+      <c r="W28" t="n">
+        <v>-20.5337082438773</v>
+      </c>
+      <c r="X28" t="n">
+        <v>39.11282467810747</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>-59.64653292198476</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-38.37366887015406</v>
+      </c>
+      <c r="AA28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0.03069053708439906</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0.1071428571428572</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.006545514660468266</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0.0006598441135576838</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0.005885670546910582</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>56.00000000000001</v>
+      </c>
+      <c r="AH28" t="n">
         <v>46</v>
       </c>
-      <c r="K28" t="b">
-        <v>0</v>
-      </c>
-      <c r="L28" t="b">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>567</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>567</v>
-      </c>
-      <c r="R28" t="n">
-        <v>16572643</v>
-      </c>
-      <c r="S28" t="n">
-        <v>577.4</v>
-      </c>
-      <c r="T28" t="n">
-        <v>521.525</v>
-      </c>
-      <c r="U28" t="n">
-        <v>517.925</v>
-      </c>
-      <c r="V28" t="n">
-        <v>489.3166666666667</v>
-      </c>
-      <c r="W28" t="n">
-        <v>21.22417184626079</v>
-      </c>
-      <c r="X28" t="n">
-        <v>19.48575299762814</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.738418848632652</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>4.021701020704047</v>
-      </c>
-      <c r="AA28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>0.1454545454545455</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>0.08829174664107486</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0.09260222526906792</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>-0.0512531663451492</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>0.1438553916142171</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>70</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>38</v>
-      </c>
       <c r="AI28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="b">
         <v>1</v>
       </c>
       <c r="AK28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM28" t="b">
         <v>0</v>
@@ -4435,11 +4413,7 @@
       <c r="AN28" t="b">
         <v>0</v>
       </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
+      <c r="AO28" t="inlineStr"/>
       <c r="AP28" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -4449,17 +4423,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4468,7 +4442,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>32.4</v>
+        <v>30.6</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4477,15 +4451,15 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>4143450</v>
+        <v>957000</v>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="K29" t="b">
         <v>0</v>
@@ -4494,7 +4468,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>4143450</v>
+        <v>957000</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -4503,67 +4477,67 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>296.5</v>
+        <v>542</v>
       </c>
       <c r="Q29" t="n">
-        <v>296.5</v>
+        <v>542</v>
       </c>
       <c r="R29" t="n">
-        <v>55999416</v>
+        <v>9211718</v>
       </c>
       <c r="S29" t="n">
-        <v>301.1</v>
+        <v>562.4</v>
       </c>
       <c r="T29" t="n">
-        <v>292.4</v>
+        <v>571.7</v>
       </c>
       <c r="U29" t="n">
-        <v>290.725</v>
+        <v>571.95</v>
       </c>
       <c r="V29" t="n">
-        <v>264.8006866455078</v>
+        <v>536.7666666666667</v>
       </c>
       <c r="W29" t="n">
-        <v>5.200933723366973</v>
+        <v>-4.524911816179042</v>
       </c>
       <c r="X29" t="n">
-        <v>6.875214922882925</v>
+        <v>-0.9976479507050332</v>
       </c>
       <c r="Y29" t="n">
-        <v>-1.674281199515953</v>
+        <v>-3.527263865474009</v>
       </c>
       <c r="Z29" t="n">
-        <v>-1.004383772877178</v>
+        <v>-1.24574850002579</v>
       </c>
       <c r="AA29" t="b">
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.1273764258555132</v>
+        <v>-0.009140767824497242</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.09079890139956692</v>
+        <v>0.5941176470588236</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.07452410567003565</v>
+        <v>-0.03328579024842804</v>
       </c>
       <c r="AE29" t="n">
-        <v>-0.04874601158665715</v>
+        <v>0.4876346340295241</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.1232701172566928</v>
+        <v>-0.5209204242779522</v>
       </c>
       <c r="AG29" t="n">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="AH29" t="n">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="AI29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="b">
         <v>0</v>
@@ -4578,28 +4552,26 @@
         <v>1</v>
       </c>
       <c r="AO29" t="n">
-        <v>315.48</v>
-      </c>
-      <c r="AP29" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>582.11</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>540.26</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4608,24 +4580,24 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>31</v>
+        <v>29.6</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>186900</v>
+        <v>499000</v>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="K30" t="b">
         <v>0</v>
@@ -4634,70 +4606,70 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>157900</v>
+        <v>499000</v>
       </c>
       <c r="N30" t="n">
-        <v>29000</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>0.1836605446485117</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>17500</v>
+        <v>2115</v>
       </c>
       <c r="Q30" t="n">
-        <v>17500</v>
+        <v>2115</v>
       </c>
       <c r="R30" t="n">
-        <v>367989</v>
+        <v>977025</v>
       </c>
       <c r="S30" t="n">
-        <v>17556</v>
+        <v>2232</v>
       </c>
       <c r="T30" t="n">
-        <v>18723.25</v>
+        <v>2332.5</v>
       </c>
       <c r="U30" t="n">
-        <v>18742.5</v>
+        <v>2335</v>
       </c>
       <c r="V30" t="n">
-        <v>16999.08333333333</v>
+        <v>1991.520267740885</v>
       </c>
       <c r="W30" t="n">
-        <v>-302.5965061577663</v>
+        <v>-29.44102573966256</v>
       </c>
       <c r="X30" t="n">
-        <v>25.43756784267589</v>
+        <v>27.07256454407002</v>
       </c>
       <c r="Y30" t="n">
-        <v>-328.0340740004422</v>
+        <v>-56.51359028373258</v>
       </c>
       <c r="Z30" t="n">
-        <v>-367.6667200919853</v>
+        <v>-50.22539042962939</v>
       </c>
       <c r="AA30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>-0.02152641878669281</v>
+        <v>-0.02309468822170901</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.3513513513513513</v>
+        <v>0.6320231492645285</v>
       </c>
       <c r="AD30" t="n">
-        <v>-0.0743787389721704</v>
+        <v>-0.04723971064563981</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.2118064383651272</v>
+        <v>0.525540136235229</v>
       </c>
       <c r="AF30" t="n">
-        <v>-0.2861851773372976</v>
+        <v>-0.5727798468808688</v>
       </c>
       <c r="AG30" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="AH30" t="n">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="AI30" t="b">
         <v>0</v>
@@ -4712,30 +4684,30 @@
         <v>0</v>
       </c>
       <c r="AM30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="b">
         <v>0</v>
       </c>
       <c r="AO30" t="inlineStr"/>
       <c r="AP30" t="n">
-        <v>19267.63</v>
+        <v>2253.95</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>慧洋-KY</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4744,7 +4716,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>30.8</v>
+        <v>29.6</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4753,15 +4725,15 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="K31" t="b">
         <v>0</v>
@@ -4770,7 +4742,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -4779,73 +4751,73 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>166</v>
+        <v>101</v>
       </c>
       <c r="Q31" t="n">
-        <v>166</v>
+        <v>101</v>
       </c>
       <c r="R31" t="n">
-        <v>11434465</v>
+        <v>1980561</v>
       </c>
       <c r="S31" t="n">
-        <v>170</v>
+        <v>101.5800003051758</v>
       </c>
       <c r="T31" t="n">
-        <v>170.25</v>
+        <v>99.76500053405762</v>
       </c>
       <c r="U31" t="n">
-        <v>169.45</v>
+        <v>99.76500053405762</v>
       </c>
       <c r="V31" t="n">
-        <v>150.6916666666667</v>
+        <v>93.44500020345052</v>
       </c>
       <c r="W31" t="n">
-        <v>0.9693286291989409</v>
+        <v>0.9631267387532745</v>
       </c>
       <c r="X31" t="n">
-        <v>3.624013383555756</v>
+        <v>0.5884143807628124</v>
       </c>
       <c r="Y31" t="n">
-        <v>-2.654684754356815</v>
+        <v>0.3747123579904621</v>
       </c>
       <c r="Z31" t="n">
-        <v>-2.534013456853975</v>
+        <v>0.5529265852619162</v>
       </c>
       <c r="AA31" t="b">
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.1066666666666667</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.09570957095709565</v>
+        <v>0.2768647528235271</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.0538143464811891</v>
+        <v>-0.0241450224239308</v>
       </c>
       <c r="AE31" t="n">
-        <v>-0.04383534202912842</v>
+        <v>0.1703817397942275</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.09764968851031752</v>
+        <v>-0.1945267622181583</v>
       </c>
       <c r="AG31" t="n">
-        <v>57.99999999999999</v>
+        <v>42</v>
       </c>
       <c r="AH31" t="n">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="AI31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM31" t="b">
         <v>0</v>
@@ -4853,29 +4825,29 @@
       <c r="AN31" t="b">
         <v>0</v>
       </c>
-      <c r="AO31" t="n">
-        <v>195.88</v>
-      </c>
-      <c r="AP31" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
+      </c>
+      <c r="AP31" t="n">
+        <v>95.59999999999999</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4884,7 +4856,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>30.2</v>
+        <v>28.6</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4893,24 +4865,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>2185000</v>
+        <v>79618000</v>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="K32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" t="b">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>2185000</v>
+        <v>79618000</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -4919,73 +4891,73 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>242</v>
+        <v>133.5</v>
       </c>
       <c r="Q32" t="n">
-        <v>242</v>
+        <v>133.5</v>
       </c>
       <c r="R32" t="n">
-        <v>3392094</v>
+        <v>214575784</v>
       </c>
       <c r="S32" t="n">
-        <v>243.3</v>
+        <v>142</v>
       </c>
       <c r="T32" t="n">
-        <v>232.55</v>
+        <v>150.225</v>
       </c>
       <c r="U32" t="n">
-        <v>231.45</v>
+        <v>150.675</v>
       </c>
       <c r="V32" t="n">
-        <v>209.9666666666667</v>
+        <v>133.7666666666667</v>
       </c>
       <c r="W32" t="n">
-        <v>4.992515275095315</v>
+        <v>-2.257982444045922</v>
       </c>
       <c r="X32" t="n">
-        <v>4.782584651885575</v>
+        <v>1.183775827998165</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.2099306232097398</v>
+        <v>-3.441758272044087</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.5892077882679656</v>
+        <v>-2.916571305106211</v>
       </c>
       <c r="AA32" t="b">
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.1000000000000001</v>
+        <v>-0.06315789473684208</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.1921182266009853</v>
+        <v>0.02692307692307683</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.0471476798145225</v>
+        <v>-0.08730291716077287</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.05257331361476125</v>
+        <v>-0.0795599361062227</v>
       </c>
       <c r="AF32" t="n">
-        <v>-0.005425633800238749</v>
+        <v>-0.00774298105455018</v>
       </c>
       <c r="AG32" t="n">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="AH32" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AI32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM32" t="b">
         <v>0</v>
@@ -4993,31 +4965,25 @@
       <c r="AN32" t="b">
         <v>0</v>
       </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
-      <c r="AP32" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+      <c r="AO32" t="inlineStr"/>
+      <c r="AP32" t="n">
+        <v>156.11</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5026,7 +4992,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>30.2</v>
+        <v>28</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5035,15 +5001,15 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1000</v>
+        <v>5163000</v>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="n">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="K33" t="b">
         <v>0</v>
@@ -5052,7 +5018,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1000</v>
+        <v>5163000</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
@@ -5061,61 +5027,61 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>176</v>
+        <v>19.25</v>
       </c>
       <c r="Q33" t="n">
-        <v>176</v>
+        <v>19.25</v>
       </c>
       <c r="R33" t="n">
-        <v>8306342</v>
+        <v>46513793</v>
       </c>
       <c r="S33" t="n">
-        <v>181.7</v>
+        <v>19.21000022888184</v>
       </c>
       <c r="T33" t="n">
-        <v>175.55</v>
+        <v>18.90750007629395</v>
       </c>
       <c r="U33" t="n">
-        <v>174.625</v>
+        <v>18.88500003814697</v>
       </c>
       <c r="V33" t="n">
-        <v>161.0833333333333</v>
+        <v>19.02257207234701</v>
       </c>
       <c r="W33" t="n">
-        <v>3.210129029492379</v>
+        <v>0.1090578800445208</v>
       </c>
       <c r="X33" t="n">
-        <v>5.383351557859127</v>
+        <v>0.04730777682413234</v>
       </c>
       <c r="Y33" t="n">
-        <v>-2.173222528366749</v>
+        <v>0.06175010322038843</v>
       </c>
       <c r="Z33" t="n">
-        <v>-1.606206873600168</v>
+        <v>0.07553552354631526</v>
       </c>
       <c r="AA33" t="b">
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.1174603174603175</v>
+        <v>0.02393621176602845</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.04142011834319526</v>
+        <v>0.04595009474395906</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.0646079972748399</v>
+        <v>-0.0002088106579023474</v>
       </c>
       <c r="AE33" t="n">
-        <v>-0.09812479464302881</v>
+        <v>-0.06053291828534046</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.1627327919178687</v>
+        <v>0.06032410762743812</v>
       </c>
       <c r="AG33" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="AH33" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AI33" t="b">
         <v>1</v>
@@ -5124,19 +5090,21 @@
         <v>1</v>
       </c>
       <c r="AK33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM33" t="b">
         <v>0</v>
       </c>
       <c r="AN33" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>200.64</v>
+        <v>0</v>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
@@ -5147,17 +5115,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5166,7 +5134,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>29.2</v>
+        <v>27.8</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5175,7 +5143,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -5183,7 +5151,7 @@
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K34" t="b">
         <v>0</v>
@@ -5201,73 +5169,73 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>6880</v>
+        <v>161.5</v>
       </c>
       <c r="Q34" t="n">
-        <v>6880</v>
+        <v>161.5</v>
       </c>
       <c r="R34" t="n">
-        <v>4280756</v>
+        <v>19553094</v>
       </c>
       <c r="S34" t="n">
-        <v>6997</v>
+        <v>176</v>
       </c>
       <c r="T34" t="n">
-        <v>6449.75</v>
+        <v>175.65</v>
       </c>
       <c r="U34" t="n">
-        <v>6438.75</v>
+        <v>175.55</v>
       </c>
       <c r="V34" t="n">
-        <v>5695.806945800781</v>
+        <v>161.2333333333333</v>
       </c>
       <c r="W34" t="n">
-        <v>200.3495903311559</v>
+        <v>0.7521259415534587</v>
       </c>
       <c r="X34" t="n">
-        <v>121.5311146753355</v>
+        <v>4.457106434597994</v>
       </c>
       <c r="Y34" t="n">
-        <v>78.81847565582044</v>
+        <v>-3.704980493044535</v>
       </c>
       <c r="Z34" t="n">
-        <v>120.0294182362092</v>
+        <v>-2.173222528366749</v>
       </c>
       <c r="AA34" t="b">
         <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.03303303303303307</v>
+        <v>0.01253918495297812</v>
       </c>
       <c r="AC34" t="n">
-        <v>0.7313819553383563</v>
+        <v>0.05901639344262288</v>
       </c>
       <c r="AD34" t="n">
-        <v>-0.01981928715244452</v>
+        <v>-0.01160583747095267</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.5918370423521322</v>
+        <v>-0.04746661958667664</v>
       </c>
       <c r="AF34" t="n">
-        <v>-0.6116563295045767</v>
+        <v>0.03586078211572397</v>
       </c>
       <c r="AG34" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AH34" t="n">
-        <v>94</v>
+        <v>38</v>
       </c>
       <c r="AI34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="b">
         <v>1</v>
       </c>
       <c r="AK34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="b">
         <v>0</v>
@@ -5275,11 +5243,7 @@
       <c r="AN34" t="b">
         <v>0</v>
       </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
+      <c r="AO34" t="inlineStr"/>
       <c r="AP34" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -5289,17 +5253,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5308,7 +5272,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>29.2</v>
+        <v>26</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5317,15 +5281,15 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="K35" t="b">
         <v>0</v>
@@ -5334,7 +5298,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -5343,67 +5307,67 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1020</v>
+        <v>155.5</v>
       </c>
       <c r="Q35" t="n">
-        <v>1020</v>
+        <v>155.5</v>
       </c>
       <c r="R35" t="n">
-        <v>10877612</v>
+        <v>15414533</v>
       </c>
       <c r="S35" t="n">
-        <v>1099</v>
+        <v>165.4</v>
       </c>
       <c r="T35" t="n">
-        <v>1027.1</v>
+        <v>170.075</v>
       </c>
       <c r="U35" t="n">
-        <v>1021.2</v>
+        <v>170.25</v>
       </c>
       <c r="V35" t="n">
-        <v>989.5833333333334</v>
+        <v>150.9583333333333</v>
       </c>
       <c r="W35" t="n">
-        <v>22.98491278396568</v>
+        <v>-0.7635335495609468</v>
       </c>
       <c r="X35" t="n">
-        <v>38.16369765911316</v>
+        <v>2.746503996932415</v>
       </c>
       <c r="Y35" t="n">
-        <v>-15.17878487514748</v>
+        <v>-3.510037546493362</v>
       </c>
       <c r="Z35" t="n">
-        <v>-6.22915014741276</v>
+        <v>-2.654684754356815</v>
       </c>
       <c r="AA35" t="b">
         <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.1308203991130821</v>
+        <v>-0.0220125786163522</v>
       </c>
       <c r="AC35" t="n">
-        <v>-0.1774193548387096</v>
+        <v>0.1146953405017921</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.07796807892760449</v>
+        <v>-0.04615760104028299</v>
       </c>
       <c r="AE35" t="n">
-        <v>-0.3169642678249337</v>
+        <v>0.008212327472492564</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.3949323467525382</v>
+        <v>-0.05436992851277556</v>
       </c>
       <c r="AG35" t="n">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="AH35" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="AI35" t="b">
         <v>0</v>
       </c>
       <c r="AJ35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="b">
         <v>0</v>
@@ -5415,31 +5379,27 @@
         <v>0</v>
       </c>
       <c r="AN35" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>1191.36</v>
-      </c>
-      <c r="AP35" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="AO35" t="inlineStr"/>
+      <c r="AP35" t="n">
+        <v>168.84</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5448,7 +5408,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>28.6</v>
+        <v>25.4</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5457,7 +5417,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -5465,7 +5425,7 @@
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K36" t="b">
         <v>0</v>
@@ -5483,73 +5443,73 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>3940</v>
+        <v>923</v>
       </c>
       <c r="Q36" t="n">
-        <v>3940</v>
+        <v>923</v>
       </c>
       <c r="R36" t="n">
-        <v>2682393</v>
+        <v>18824519</v>
       </c>
       <c r="S36" t="n">
-        <v>4185</v>
+        <v>1040.6</v>
       </c>
       <c r="T36" t="n">
-        <v>3804.5</v>
+        <v>1028.25</v>
       </c>
       <c r="U36" t="n">
-        <v>3790</v>
+        <v>1027.1</v>
       </c>
       <c r="V36" t="n">
-        <v>3740.318452962239</v>
+        <v>983.8833333333333</v>
       </c>
       <c r="W36" t="n">
-        <v>99.16455939196248</v>
+        <v>2.828710826272527</v>
       </c>
       <c r="X36" t="n">
-        <v>79.84013542279391</v>
+        <v>31.09670029254504</v>
       </c>
       <c r="Y36" t="n">
-        <v>19.32442396916858</v>
+        <v>-28.26798946627251</v>
       </c>
       <c r="Z36" t="n">
-        <v>56.38844843172421</v>
+        <v>-15.17878487514748</v>
       </c>
       <c r="AA36" t="b">
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.07945205479452055</v>
+        <v>0.02555555555555555</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.1410331492138492</v>
+        <v>-0.2703557312252964</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.02659973460904297</v>
+        <v>0.001410533131624758</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.001488236227625173</v>
+        <v>-0.376838744254596</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.0251114983814178</v>
+        <v>0.3782492773862207</v>
       </c>
       <c r="AG36" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AH36" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="AI36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ36" t="b">
         <v>1</v>
       </c>
       <c r="AK36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM36" t="b">
         <v>0</v>
@@ -5557,11 +5517,7 @@
       <c r="AN36" t="b">
         <v>0</v>
       </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
+      <c r="AO36" t="inlineStr"/>
       <c r="AP36" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -5571,17 +5527,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5590,7 +5546,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>28.4</v>
+        <v>24.6</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5599,24 +5555,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>79618000</v>
+        <v>4328000</v>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="K37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" t="b">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>79618000</v>
+        <v>4328000</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -5625,67 +5581,67 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>142</v>
+        <v>5120</v>
       </c>
       <c r="Q37" t="n">
-        <v>142</v>
+        <v>5120</v>
       </c>
       <c r="R37" t="n">
-        <v>110224887</v>
+        <v>5890083</v>
       </c>
       <c r="S37" t="n">
-        <v>145</v>
+        <v>5667</v>
       </c>
       <c r="T37" t="n">
-        <v>150.675</v>
+        <v>5280.25</v>
       </c>
       <c r="U37" t="n">
-        <v>150.6</v>
+        <v>5291.5</v>
       </c>
       <c r="V37" t="n">
-        <v>133.7083333333333</v>
+        <v>5316.959847005209</v>
       </c>
       <c r="W37" t="n">
-        <v>-0.8723559090970241</v>
+        <v>74.35940143287371</v>
       </c>
       <c r="X37" t="n">
-        <v>2.044215396009187</v>
+        <v>101.2213302666985</v>
       </c>
       <c r="Y37" t="n">
-        <v>-2.916571305106211</v>
+        <v>-26.86192883382478</v>
       </c>
       <c r="Z37" t="n">
-        <v>-2.976420182292489</v>
+        <v>41.7261634333907</v>
       </c>
       <c r="AA37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.01067615658362997</v>
+        <v>-0.04209541627689428</v>
       </c>
       <c r="AC37" t="n">
-        <v>-0.01388888888888884</v>
+        <v>0.1702795755424051</v>
       </c>
       <c r="AD37" t="n">
-        <v>-0.04217616360184762</v>
+        <v>-0.06624043870082508</v>
       </c>
       <c r="AE37" t="n">
-        <v>-0.1534338018751129</v>
+        <v>0.06379656251310561</v>
       </c>
       <c r="AF37" t="n">
-        <v>0.1112576382732653</v>
+        <v>-0.1300370012139307</v>
       </c>
       <c r="AG37" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AH37" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="AI37" t="b">
         <v>0</v>
       </c>
       <c r="AJ37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="b">
         <v>0</v>
@@ -5694,32 +5650,32 @@
         <v>0</v>
       </c>
       <c r="AM37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO37" t="inlineStr"/>
-      <c r="AP37" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>5427.2</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>5283.68</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5728,7 +5684,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>27</v>
+        <v>24.4</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5737,7 +5693,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -5745,7 +5701,7 @@
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="K38" t="b">
         <v>0</v>
@@ -5763,64 +5719,64 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>2250</v>
+        <v>538</v>
       </c>
       <c r="Q38" t="n">
-        <v>2250</v>
+        <v>538</v>
       </c>
       <c r="R38" t="n">
-        <v>2512473</v>
+        <v>944422</v>
       </c>
       <c r="S38" t="n">
-        <v>2309</v>
+        <v>551.4</v>
       </c>
       <c r="T38" t="n">
-        <v>2246.5</v>
+        <v>561.05</v>
       </c>
       <c r="U38" t="n">
-        <v>2242</v>
+        <v>561</v>
       </c>
       <c r="V38" t="n">
-        <v>2132.083333333333</v>
+        <v>567.5520161946614</v>
       </c>
       <c r="W38" t="n">
-        <v>22.02039136671237</v>
+        <v>-4.077612311283474</v>
       </c>
       <c r="X38" t="n">
-        <v>31.88203833536183</v>
+        <v>-0.7025682295655331</v>
       </c>
       <c r="Y38" t="n">
-        <v>-9.861646968649456</v>
+        <v>-3.375044081717941</v>
       </c>
       <c r="Z38" t="n">
-        <v>-5.081578481809196</v>
+        <v>-1.993522866647877</v>
       </c>
       <c r="AA38" t="b">
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.04166666666666674</v>
+        <v>0.001862197392923592</v>
       </c>
       <c r="AC38" t="n">
-        <v>0.2162162162162162</v>
+        <v>-0.03644178592822878</v>
       </c>
       <c r="AD38" t="n">
-        <v>-0.01118565351881085</v>
+        <v>-0.0222828250310072</v>
       </c>
       <c r="AE38" t="n">
-        <v>0.07667130322999216</v>
+        <v>-0.1429247989575283</v>
       </c>
       <c r="AF38" t="n">
-        <v>-0.08785695674880301</v>
+        <v>0.1206419739265211</v>
       </c>
       <c r="AG38" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AH38" t="n">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="AI38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="b">
         <v>1</v>
@@ -5838,7 +5794,7 @@
         <v>1</v>
       </c>
       <c r="AO38" t="n">
-        <v>2362.5</v>
+        <v>576.74</v>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
@@ -5849,17 +5805,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5868,7 +5824,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>26.8</v>
+        <v>21.8</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5877,7 +5833,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -5885,7 +5841,7 @@
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="K39" t="b">
         <v>0</v>
@@ -5903,67 +5859,67 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>502</v>
+        <v>239.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>502</v>
+        <v>239.5</v>
       </c>
       <c r="R39" t="n">
-        <v>1990629</v>
+        <v>48438668</v>
       </c>
       <c r="S39" t="n">
-        <v>520.2</v>
+        <v>243.2</v>
       </c>
       <c r="T39" t="n">
-        <v>510.9</v>
+        <v>249.5</v>
       </c>
       <c r="U39" t="n">
-        <v>510.05</v>
+        <v>249.95</v>
       </c>
       <c r="V39" t="n">
-        <v>450.45</v>
+        <v>250.95</v>
       </c>
       <c r="W39" t="n">
-        <v>3.423407848656097</v>
+        <v>-2.679263462451758</v>
       </c>
       <c r="X39" t="n">
-        <v>8.911526937332471</v>
+        <v>-0.9903492723649286</v>
       </c>
       <c r="Y39" t="n">
-        <v>-5.488119088676374</v>
+        <v>-1.688914190086829</v>
       </c>
       <c r="Z39" t="n">
-        <v>-3.991731241565386</v>
+        <v>-1.520546764007297</v>
       </c>
       <c r="AA39" t="b">
         <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.03505154639175267</v>
+        <v>-0.03621730382293764</v>
       </c>
       <c r="AC39" t="n">
-        <v>0.2597239648682559</v>
+        <v>0.02132196162046918</v>
       </c>
       <c r="AD39" t="n">
-        <v>-0.01780077379372491</v>
+        <v>-0.06036232624686844</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.1201790518820318</v>
+        <v>-0.08516105140883035</v>
       </c>
       <c r="AF39" t="n">
-        <v>-0.1379798256757567</v>
+        <v>0.02479872516196191</v>
       </c>
       <c r="AG39" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AH39" t="n">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="AI39" t="b">
         <v>0</v>
       </c>
       <c r="AJ39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="b">
         <v>0</v>
@@ -5978,28 +5934,26 @@
         <v>1</v>
       </c>
       <c r="AO39" t="n">
-        <v>564.25</v>
-      </c>
-      <c r="AP39" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>258.66</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>257.03</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6008,24 +5962,24 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>26.6</v>
+        <v>21.2</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>470000</v>
+        <v>1000</v>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="K40" t="b">
         <v>0</v>
@@ -6034,70 +5988,70 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>420000</v>
+        <v>1000</v>
       </c>
       <c r="N40" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>0.119047619047619</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>3225</v>
+        <v>2025</v>
       </c>
       <c r="Q40" t="n">
-        <v>3225</v>
+        <v>2025</v>
       </c>
       <c r="R40" t="n">
-        <v>680811</v>
+        <v>4025397</v>
       </c>
       <c r="S40" t="n">
-        <v>3252</v>
+        <v>2234</v>
       </c>
       <c r="T40" t="n">
-        <v>3262.25</v>
+        <v>2240.75</v>
       </c>
       <c r="U40" t="n">
-        <v>3275</v>
+        <v>2246.5</v>
       </c>
       <c r="V40" t="n">
-        <v>2997.416666666667</v>
+        <v>2135.25</v>
       </c>
       <c r="W40" t="n">
-        <v>0.4778946522515071</v>
+        <v>-8.532542899430155</v>
       </c>
       <c r="X40" t="n">
-        <v>-8.946002146545416</v>
+        <v>23.79912208840344</v>
       </c>
       <c r="Y40" t="n">
-        <v>9.423896798796923</v>
+        <v>-32.33166498783359</v>
       </c>
       <c r="Z40" t="n">
-        <v>12.87433758470597</v>
+        <v>-9.861646968649456</v>
       </c>
       <c r="AA40" t="b">
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>-0.07327586206896552</v>
+        <v>-0.05373831775700932</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.2475822050290135</v>
+        <v>0.103542234332425</v>
       </c>
       <c r="AD40" t="n">
-        <v>-0.1261281822544431</v>
+        <v>-0.07788334018094012</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.1080372920427894</v>
+        <v>-0.00294077869687448</v>
       </c>
       <c r="AF40" t="n">
-        <v>-0.2341654742972326</v>
+        <v>-0.07494256148406564</v>
       </c>
       <c r="AG40" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="AH40" t="n">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="AI40" t="b">
         <v>0</v>
@@ -6106,10 +6060,10 @@
         <v>0</v>
       </c>
       <c r="AK40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM40" t="b">
         <v>0</v>
@@ -6117,29 +6071,27 @@
       <c r="AN40" t="b">
         <v>0</v>
       </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+      <c r="AO40" t="n">
+        <v>2389.5</v>
       </c>
       <c r="AP40" t="n">
-        <v>3414.21</v>
+        <v>2307.11</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6148,7 +6100,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>26.2</v>
+        <v>21</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -6157,15 +6109,15 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>499000</v>
+        <v>5086000</v>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="K41" t="b">
         <v>0</v>
@@ -6174,7 +6126,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>499000</v>
+        <v>5086000</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -6183,67 +6135,67 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>2195</v>
+        <v>4165</v>
       </c>
       <c r="Q41" t="n">
-        <v>2195</v>
+        <v>4165</v>
       </c>
       <c r="R41" t="n">
-        <v>729621</v>
+        <v>18514362</v>
       </c>
       <c r="S41" t="n">
-        <v>2300</v>
+        <v>4496</v>
       </c>
       <c r="T41" t="n">
-        <v>2335</v>
+        <v>4799.5</v>
       </c>
       <c r="U41" t="n">
-        <v>2332.75</v>
+        <v>4819.25</v>
       </c>
       <c r="V41" t="n">
-        <v>1977.869226074219</v>
+        <v>4264.833333333333</v>
       </c>
       <c r="W41" t="n">
-        <v>-9.024428314626221</v>
+        <v>-96.90293373225177</v>
       </c>
       <c r="X41" t="n">
-        <v>41.20096211500317</v>
+        <v>30.60385473395387</v>
       </c>
       <c r="Y41" t="n">
-        <v>-50.22539042962939</v>
+        <v>-127.5067884662056</v>
       </c>
       <c r="Z41" t="n">
-        <v>-45.7854300360147</v>
+        <v>-104.6936941662323</v>
       </c>
       <c r="AA41" t="b">
         <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.02093023255813953</v>
+        <v>-0.08662280701754388</v>
       </c>
       <c r="AC41" t="n">
-        <v>0.6433825562239956</v>
+        <v>0.2470059880239521</v>
       </c>
       <c r="AD41" t="n">
-        <v>-0.03192208762733806</v>
+        <v>-0.1107678294414747</v>
       </c>
       <c r="AE41" t="n">
-        <v>0.5038376432377716</v>
+        <v>0.1405229749946526</v>
       </c>
       <c r="AF41" t="n">
-        <v>-0.5357597308651096</v>
+        <v>-0.2512908044361273</v>
       </c>
       <c r="AG41" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="AH41" t="n">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="AI41" t="b">
         <v>0</v>
       </c>
       <c r="AJ41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK41" t="b">
         <v>0</v>
@@ -6258,26 +6210,24 @@
         <v>0</v>
       </c>
       <c r="AO41" t="inlineStr"/>
-      <c r="AP41" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+      <c r="AP41" t="n">
+        <v>5097.89</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6286,7 +6236,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>25.2</v>
+        <v>20.4</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6295,15 +6245,15 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>2504000</v>
+        <v>1000</v>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="K42" t="b">
         <v>0</v>
@@ -6312,7 +6262,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>2504000</v>
+        <v>1000</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
@@ -6321,105 +6271,101 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>5885</v>
+        <v>316.5</v>
       </c>
       <c r="Q42" t="n">
-        <v>5885</v>
+        <v>316.5</v>
       </c>
       <c r="R42" t="n">
-        <v>986684</v>
+        <v>15421586</v>
       </c>
       <c r="S42" t="n">
-        <v>5812</v>
+        <v>322</v>
       </c>
       <c r="T42" t="n">
-        <v>5535.5</v>
+        <v>333.625</v>
       </c>
       <c r="U42" t="n">
-        <v>5522.25</v>
+        <v>334.425</v>
       </c>
       <c r="V42" t="n">
-        <v>5601.833333333333</v>
+        <v>327.0833333333333</v>
       </c>
       <c r="W42" t="n">
-        <v>122.548672938955</v>
+        <v>-4.426038179004934</v>
       </c>
       <c r="X42" t="n">
-        <v>42.19621348449871</v>
+        <v>-2.324717114287667</v>
       </c>
       <c r="Y42" t="n">
-        <v>80.35245945445624</v>
+        <v>-2.101321064717267</v>
       </c>
       <c r="Z42" t="n">
-        <v>91.4052926254806</v>
+        <v>-1.815482466906621</v>
       </c>
       <c r="AA42" t="b">
         <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.04715302491103213</v>
+        <v>-0.04812030075187967</v>
       </c>
       <c r="AC42" t="n">
-        <v>0.05089285714285707</v>
+        <v>0.001582278481012667</v>
       </c>
       <c r="AD42" t="n">
-        <v>-0.005699295274445459</v>
+        <v>-0.07226532317581047</v>
       </c>
       <c r="AE42" t="n">
-        <v>-0.08865205584336699</v>
+        <v>-0.1049007345482869</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.08295276056892154</v>
+        <v>0.03263541137247639</v>
       </c>
       <c r="AG42" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="AH42" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AI42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM42" t="b">
         <v>0</v>
       </c>
       <c r="AN42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
-      <c r="AP42" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>340.55</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>351.03</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6428,7 +6374,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>24.4</v>
+        <v>20.2</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6437,15 +6383,15 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>4328000</v>
+        <v>1000</v>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="K43" t="b">
         <v>0</v>
@@ -6454,7 +6400,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>4328000</v>
+        <v>1000</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -6463,73 +6409,73 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>5520</v>
+        <v>439.5</v>
       </c>
       <c r="Q43" t="n">
-        <v>5520</v>
+        <v>439.5</v>
       </c>
       <c r="R43" t="n">
-        <v>2315803</v>
+        <v>78339384</v>
       </c>
       <c r="S43" t="n">
-        <v>5833</v>
+        <v>493.4</v>
       </c>
       <c r="T43" t="n">
-        <v>5291.5</v>
+        <v>505.4</v>
       </c>
       <c r="U43" t="n">
-        <v>5283.75</v>
+        <v>507.075</v>
       </c>
       <c r="V43" t="n">
-        <v>5304.543562825521</v>
+        <v>485.4583333333333</v>
       </c>
       <c r="W43" t="n">
-        <v>149.6629759085454</v>
+        <v>-9.710197952417786</v>
       </c>
       <c r="X43" t="n">
-        <v>107.9368124751547</v>
+        <v>0.263749679844183</v>
       </c>
       <c r="Y43" t="n">
-        <v>41.7261634333907</v>
+        <v>-9.97394763226197</v>
       </c>
       <c r="Z43" t="n">
-        <v>91.44812537588726</v>
+        <v>-5.22440334734698</v>
       </c>
       <c r="AA43" t="b">
         <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.02889095992544277</v>
+        <v>-0.07082452431289643</v>
       </c>
       <c r="AC43" t="n">
-        <v>0.2336385449190062</v>
+        <v>0.1535433070866141</v>
       </c>
       <c r="AD43" t="n">
-        <v>-0.02396136026003481</v>
+        <v>-0.09496954673682723</v>
       </c>
       <c r="AE43" t="n">
-        <v>0.09409363193278208</v>
+        <v>0.0470602940573146</v>
       </c>
       <c r="AF43" t="n">
-        <v>-0.1180549921928169</v>
+        <v>-0.1420298407941418</v>
       </c>
       <c r="AG43" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="AH43" t="n">
         <v>57.99999999999999</v>
       </c>
       <c r="AI43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM43" t="b">
         <v>0</v>
@@ -6537,31 +6483,25 @@
       <c r="AN43" t="b">
         <v>0</v>
       </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
-      <c r="AP43" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+      <c r="AO43" t="inlineStr"/>
+      <c r="AP43" t="n">
+        <v>534.87</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6570,7 +6510,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>21</v>
+        <v>19.6</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6579,15 +6519,15 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>5086000</v>
+        <v>1000</v>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="K44" t="b">
         <v>0</v>
@@ -6596,7 +6536,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>5086000</v>
+        <v>1000</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
@@ -6605,61 +6545,61 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>4475</v>
+        <v>461.5</v>
       </c>
       <c r="Q44" t="n">
-        <v>4475</v>
+        <v>461.5</v>
       </c>
       <c r="R44" t="n">
-        <v>7726671</v>
+        <v>3844049</v>
       </c>
       <c r="S44" t="n">
-        <v>4630</v>
+        <v>502.7</v>
       </c>
       <c r="T44" t="n">
-        <v>4819.25</v>
+        <v>508.075</v>
       </c>
       <c r="U44" t="n">
-        <v>4824.75</v>
+        <v>510.9</v>
       </c>
       <c r="V44" t="n">
-        <v>4251.083333333333</v>
+        <v>451.9583333333333</v>
       </c>
       <c r="W44" t="n">
-        <v>-42.21314231572705</v>
+        <v>-3.144224279454988</v>
       </c>
       <c r="X44" t="n">
-        <v>62.48055185050528</v>
+        <v>6.50037669397498</v>
       </c>
       <c r="Y44" t="n">
-        <v>-104.6936941662323</v>
+        <v>-9.644600973429968</v>
       </c>
       <c r="Z44" t="n">
-        <v>-100.0760571833271</v>
+        <v>-5.488119088676374</v>
       </c>
       <c r="AA44" t="b">
         <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>-0.02399127589967287</v>
+        <v>-0.109073359073359</v>
       </c>
       <c r="AC44" t="n">
-        <v>0.327893175074184</v>
+        <v>0.2439353099730459</v>
       </c>
       <c r="AD44" t="n">
-        <v>-0.07684359608515046</v>
+        <v>-0.1332183814972898</v>
       </c>
       <c r="AE44" t="n">
-        <v>0.18834826208796</v>
+        <v>0.1374522969437464</v>
       </c>
       <c r="AF44" t="n">
-        <v>-0.2651918581731104</v>
+        <v>-0.2706706784410362</v>
       </c>
       <c r="AG44" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AH44" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="AI44" t="b">
         <v>0</v>
@@ -6681,23 +6621,23 @@
       </c>
       <c r="AO44" t="inlineStr"/>
       <c r="AP44" t="n">
-        <v>4922.37</v>
+        <v>531.03</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6706,7 +6646,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>18.4</v>
+        <v>19.4</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6715,15 +6655,15 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1000</v>
+        <v>2504000</v>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="K45" t="b">
         <v>0</v>
@@ -6732,7 +6672,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>1000</v>
+        <v>2504000</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
@@ -6741,61 +6681,61 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>480.5</v>
+        <v>5300</v>
       </c>
       <c r="Q45" t="n">
-        <v>480.5</v>
+        <v>5300</v>
       </c>
       <c r="R45" t="n">
-        <v>54547707</v>
+        <v>1186784</v>
       </c>
       <c r="S45" t="n">
-        <v>508.3</v>
+        <v>5766</v>
       </c>
       <c r="T45" t="n">
-        <v>507.075</v>
+        <v>5520.75</v>
       </c>
       <c r="U45" t="n">
-        <v>507.7</v>
+        <v>5535.5</v>
       </c>
       <c r="V45" t="n">
-        <v>484.4833333333333</v>
+        <v>5599.25</v>
       </c>
       <c r="W45" t="n">
-        <v>-2.467166759437305</v>
+        <v>60.76939428348669</v>
       </c>
       <c r="X45" t="n">
-        <v>2.757236587909675</v>
+        <v>45.91084964429631</v>
       </c>
       <c r="Y45" t="n">
-        <v>-5.22440334734698</v>
+        <v>14.85854463919038</v>
       </c>
       <c r="Z45" t="n">
-        <v>-2.555149538642651</v>
+        <v>80.35245945445624</v>
       </c>
       <c r="AA45" t="b">
         <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>-0.02535496957403649</v>
+        <v>-0.05272564789991063</v>
       </c>
       <c r="AC45" t="n">
-        <v>0.2149178255372945</v>
+        <v>-0.0284142988084326</v>
       </c>
       <c r="AD45" t="n">
-        <v>-0.07820728975951408</v>
+        <v>-0.07687067032384143</v>
       </c>
       <c r="AE45" t="n">
-        <v>0.07537291255107048</v>
+        <v>-0.1348973118377321</v>
       </c>
       <c r="AF45" t="n">
-        <v>-0.1535802023105846</v>
+        <v>0.0580266415138907</v>
       </c>
       <c r="AG45" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="AH45" t="n">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="AI45" t="b">
         <v>0</v>
@@ -6804,38 +6744,40 @@
         <v>0</v>
       </c>
       <c r="AK45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM45" t="b">
         <v>0</v>
       </c>
       <c r="AN45" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO45" t="n">
-        <v>540.08</v>
+        <v>0</v>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP45" t="n">
-        <v>500.97</v>
+        <v>5672.37</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6844,7 +6786,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>18</v>
+        <v>18.8</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6853,15 +6795,15 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1000</v>
+        <v>186900</v>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="K46" t="b">
         <v>0</v>
@@ -6870,7 +6812,7 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>1000</v>
+        <v>186900</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
@@ -6879,61 +6821,61 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>243</v>
+        <v>15945</v>
       </c>
       <c r="Q46" t="n">
-        <v>243</v>
+        <v>15945</v>
       </c>
       <c r="R46" t="n">
-        <v>33880570</v>
+        <v>725983</v>
       </c>
       <c r="S46" t="n">
-        <v>245.7</v>
+        <v>17195</v>
       </c>
       <c r="T46" t="n">
-        <v>249.95</v>
+        <v>18621.5</v>
       </c>
       <c r="U46" t="n">
-        <v>250.2</v>
+        <v>18723.25</v>
       </c>
       <c r="V46" t="n">
-        <v>250.8666666666667</v>
+        <v>17049.58333333333</v>
       </c>
       <c r="W46" t="n">
-        <v>-2.088667488850518</v>
+        <v>-497.1996647079432</v>
       </c>
       <c r="X46" t="n">
-        <v>-0.5681207248432214</v>
+        <v>-79.08987866744792</v>
       </c>
       <c r="Y46" t="n">
-        <v>-1.520546764007297</v>
+        <v>-418.1097860404952</v>
       </c>
       <c r="Z46" t="n">
-        <v>-1.534333297162695</v>
+        <v>-328.0340740004422</v>
       </c>
       <c r="AA46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>-0.02016129032258063</v>
+        <v>-0.1131813125695217</v>
       </c>
       <c r="AC46" t="n">
-        <v>0.03846153846153855</v>
+        <v>0.2346109175377469</v>
       </c>
       <c r="AD46" t="n">
-        <v>-0.07301361050805821</v>
+        <v>-0.1373263349934525</v>
       </c>
       <c r="AE46" t="n">
-        <v>-0.1010833745246855</v>
+        <v>0.1281279045084474</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.02806976401662731</v>
+        <v>-0.2654542395018998</v>
       </c>
       <c r="AG46" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="AH46" t="n">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="AI46" t="b">
         <v>0</v>
@@ -6948,32 +6890,30 @@
         <v>0</v>
       </c>
       <c r="AM46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN46" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO46" t="n">
-        <v>260.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO46" t="inlineStr"/>
       <c r="AP46" t="n">
-        <v>255.82</v>
+        <v>20337.37</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6982,7 +6922,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>14.6</v>
+        <v>17.2</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6991,15 +6931,15 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>1000</v>
+        <v>3281561</v>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="K47" t="b">
         <v>0</v>
@@ -7008,7 +6948,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>1000</v>
+        <v>3281561</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
@@ -7017,61 +6957,61 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>323</v>
+        <v>1905</v>
       </c>
       <c r="Q47" t="n">
-        <v>323</v>
+        <v>1905</v>
       </c>
       <c r="R47" t="n">
-        <v>12017550</v>
+        <v>10159270</v>
       </c>
       <c r="S47" t="n">
-        <v>325.7</v>
+        <v>2146</v>
       </c>
       <c r="T47" t="n">
-        <v>334.425</v>
+        <v>2151.75</v>
       </c>
       <c r="U47" t="n">
-        <v>335.1</v>
+        <v>2170</v>
       </c>
       <c r="V47" t="n">
-        <v>327.075</v>
+        <v>2139.580183919271</v>
       </c>
       <c r="W47" t="n">
-        <v>-3.614869315014971</v>
+        <v>-35.69547770504778</v>
       </c>
       <c r="X47" t="n">
-        <v>-1.79938684810835</v>
+        <v>-15.84564882429594</v>
       </c>
       <c r="Y47" t="n">
-        <v>-1.815482466906621</v>
+        <v>-19.84982888075184</v>
       </c>
       <c r="Z47" t="n">
-        <v>-2.011595644111465</v>
+        <v>5.999139220754717</v>
       </c>
       <c r="AA47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>-0.04011887072808318</v>
+        <v>-0.1607929515418502</v>
       </c>
       <c r="AC47" t="n">
-        <v>-0.007680491551459334</v>
+        <v>0.2128545911402431</v>
       </c>
       <c r="AD47" t="n">
-        <v>-0.09297119091356076</v>
+        <v>-0.184937973965781</v>
       </c>
       <c r="AE47" t="n">
-        <v>-0.1472254045376834</v>
+        <v>0.1063715781109436</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.05425421362412264</v>
+        <v>-0.2913095520767246</v>
       </c>
       <c r="AG47" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AH47" t="n">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="AI47" t="b">
         <v>0</v>
@@ -7086,32 +7026,32 @@
         <v>0</v>
       </c>
       <c r="AM47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN47" t="b">
         <v>1</v>
       </c>
       <c r="AO47" t="n">
-        <v>343.67</v>
+        <v>2129.79</v>
       </c>
       <c r="AP47" t="n">
-        <v>344.53</v>
+        <v>2574.74</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7120,7 +7060,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>12.2</v>
+        <v>16.8</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -7129,15 +7069,15 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>478000</v>
+        <v>470000</v>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K48" t="b">
         <v>0</v>
@@ -7146,7 +7086,7 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>478000</v>
+        <v>470000</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
@@ -7155,61 +7095,61 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>853</v>
+        <v>2905</v>
       </c>
       <c r="Q48" t="n">
-        <v>853</v>
+        <v>2905</v>
       </c>
       <c r="R48" t="n">
-        <v>1146377</v>
+        <v>795268</v>
       </c>
       <c r="S48" t="n">
-        <v>859.6</v>
+        <v>3229</v>
       </c>
       <c r="T48" t="n">
-        <v>874.75</v>
+        <v>3238.75</v>
       </c>
       <c r="U48" t="n">
-        <v>877.1</v>
+        <v>3262.25</v>
       </c>
       <c r="V48" t="n">
-        <v>972.45</v>
+        <v>3003.083333333333</v>
       </c>
       <c r="W48" t="n">
-        <v>-14.12111627183356</v>
+        <v>-35.84612902839308</v>
       </c>
       <c r="X48" t="n">
-        <v>-15.77202644653664</v>
+        <v>-14.32602752291495</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.650910174703082</v>
+        <v>-21.52010150547813</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.623759485461214</v>
+        <v>9.423896798796923</v>
       </c>
       <c r="AA48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>-0.05222222222222217</v>
+        <v>-0.1392592592592593</v>
       </c>
       <c r="AC48" t="n">
-        <v>-0.2210045662100457</v>
+        <v>0.1325536062378168</v>
       </c>
       <c r="AD48" t="n">
-        <v>-0.1050745424076998</v>
+        <v>-0.1634042816831901</v>
       </c>
       <c r="AE48" t="n">
-        <v>-0.3605494791962698</v>
+        <v>0.02607059320851723</v>
       </c>
       <c r="AF48" t="n">
-        <v>0.25547493678857</v>
+        <v>-0.1894748748917073</v>
       </c>
       <c r="AG48" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AH48" t="n">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="AI48" t="b">
         <v>0</v>
@@ -7218,40 +7158,38 @@
         <v>0</v>
       </c>
       <c r="AK48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>3149.02</v>
       </c>
       <c r="AP48" t="n">
-        <v>908.89</v>
+        <v>3606.32</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -7260,7 +7198,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>11.8</v>
+        <v>16.6</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -7269,15 +7207,15 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1000</v>
+        <v>478000</v>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="K49" t="b">
         <v>0</v>
@@ -7286,7 +7224,7 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>1000</v>
+        <v>478000</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
@@ -7295,61 +7233,61 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>1185</v>
+        <v>833</v>
       </c>
       <c r="Q49" t="n">
-        <v>1185</v>
+        <v>833</v>
       </c>
       <c r="R49" t="n">
-        <v>1051214</v>
+        <v>1786411</v>
       </c>
       <c r="S49" t="n">
-        <v>1200</v>
+        <v>851.8</v>
       </c>
       <c r="T49" t="n">
-        <v>1217.25</v>
+        <v>872.1</v>
       </c>
       <c r="U49" t="n">
-        <v>1222.25</v>
+        <v>874.75</v>
       </c>
       <c r="V49" t="n">
-        <v>1354.890482584635</v>
+        <v>968.3333333333334</v>
       </c>
       <c r="W49" t="n">
-        <v>-23.9936701173051</v>
+        <v>-15.69055561026494</v>
       </c>
       <c r="X49" t="n">
-        <v>-30.30419845288813</v>
+        <v>-15.7557322792823</v>
       </c>
       <c r="Y49" t="n">
-        <v>6.31052833558303</v>
+        <v>0.06517666901736163</v>
       </c>
       <c r="Z49" t="n">
-        <v>6.716122397234436</v>
+        <v>1.650910174703082</v>
       </c>
       <c r="AA49" t="b">
         <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>-0.0778210116731517</v>
+        <v>-0.05981941309255079</v>
       </c>
       <c r="AC49" t="n">
-        <v>-0.04315997553569872</v>
+        <v>-0.2287037037037037</v>
       </c>
       <c r="AD49" t="n">
-        <v>-0.1306733318586293</v>
+        <v>-0.08396443551648158</v>
       </c>
       <c r="AE49" t="n">
-        <v>-0.1827048885219228</v>
+        <v>-0.3351867167330033</v>
       </c>
       <c r="AF49" t="n">
-        <v>0.05203155666329351</v>
+        <v>0.2512222812165217</v>
       </c>
       <c r="AG49" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="AH49" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AI49" t="b">
         <v>0</v>
@@ -7375,23 +7313,23 @@
         </is>
       </c>
       <c r="AP49" t="n">
-        <v>1303.95</v>
+        <v>915.16</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7400,7 +7338,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>10.4</v>
+        <v>14</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7409,15 +7347,15 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>93000</v>
+        <v>1000</v>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="K50" t="b">
         <v>0</v>
@@ -7426,7 +7364,7 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>93000</v>
+        <v>1000</v>
       </c>
       <c r="N50" t="n">
         <v>0</v>
@@ -7435,58 +7373,58 @@
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>5615</v>
+        <v>1155</v>
       </c>
       <c r="Q50" t="n">
-        <v>5615</v>
+        <v>1155</v>
       </c>
       <c r="R50" t="n">
-        <v>458344</v>
+        <v>854729</v>
       </c>
       <c r="S50" t="n">
-        <v>5695</v>
+        <v>1185</v>
       </c>
       <c r="T50" t="n">
-        <v>5966.75</v>
+        <v>1211.5</v>
       </c>
       <c r="U50" t="n">
-        <v>6030.5</v>
+        <v>1217.25</v>
       </c>
       <c r="V50" t="n">
-        <v>6353.25</v>
+        <v>1352.357442220052</v>
       </c>
       <c r="W50" t="n">
-        <v>-158.3315951329696</v>
+        <v>-25.9242692595235</v>
       </c>
       <c r="X50" t="n">
-        <v>-159.7229612997303</v>
+        <v>-29.42821261421521</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.39136616676069</v>
+        <v>3.503943354691707</v>
       </c>
       <c r="Z50" t="n">
-        <v>11.67079776438766</v>
+        <v>6.31052833558303</v>
       </c>
       <c r="AA50" t="b">
         <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>-0.1850507982583455</v>
+        <v>-0.09055118110236215</v>
       </c>
       <c r="AC50" t="n">
-        <v>-0.07266721717588764</v>
+        <v>-0.1162849777711361</v>
       </c>
       <c r="AD50" t="n">
-        <v>-0.2379031184438231</v>
+        <v>-0.114696203526293</v>
       </c>
       <c r="AE50" t="n">
-        <v>-0.2122121301621117</v>
+        <v>-0.2227679908004356</v>
       </c>
       <c r="AF50" t="n">
-        <v>-0.02569098828171135</v>
+        <v>0.1080717872741427</v>
       </c>
       <c r="AG50" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="AH50" t="n">
         <v>8</v>
@@ -7515,23 +7453,23 @@
         </is>
       </c>
       <c r="AP50" t="n">
-        <v>6970.26</v>
+        <v>1339.47</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7540,24 +7478,24 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>9.4</v>
+        <v>10.8</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Heavy Sell</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>3281561</v>
+        <v>93000</v>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="K51" t="b">
         <v>0</v>
@@ -7566,70 +7504,70 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>4315561</v>
+        <v>93000</v>
       </c>
       <c r="N51" t="n">
-        <v>-1034000</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>-0.2395980499406682</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>2115</v>
+        <v>5055</v>
       </c>
       <c r="Q51" t="n">
-        <v>2115</v>
+        <v>5055</v>
       </c>
       <c r="R51" t="n">
-        <v>7410219</v>
+        <v>879953</v>
       </c>
       <c r="S51" t="n">
-        <v>2213</v>
+        <v>5602</v>
       </c>
       <c r="T51" t="n">
-        <v>2170</v>
+        <v>5889.5</v>
       </c>
       <c r="U51" t="n">
-        <v>2179.75</v>
+        <v>5966.75</v>
       </c>
       <c r="V51" t="n">
-        <v>2134.008095296224</v>
+        <v>6336.666666666667</v>
       </c>
       <c r="W51" t="n">
-        <v>-4.884052383353264</v>
+        <v>-223.5106797362596</v>
       </c>
       <c r="X51" t="n">
-        <v>-10.88319160410798</v>
+        <v>-172.4805049870362</v>
       </c>
       <c r="Y51" t="n">
-        <v>5.999139220754717</v>
+        <v>-51.03017474922342</v>
       </c>
       <c r="Z51" t="n">
-        <v>18.48988037994293</v>
+        <v>1.39136616676069</v>
       </c>
       <c r="AA51" t="b">
         <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>-0.08441558441558439</v>
+        <v>-0.2340909090909091</v>
       </c>
       <c r="AC51" t="n">
-        <v>0.365500120188045</v>
+        <v>-0.1644628099173554</v>
       </c>
       <c r="AD51" t="n">
-        <v>-0.137267904601062</v>
+        <v>-0.2582359315148399</v>
       </c>
       <c r="AE51" t="n">
-        <v>0.2259552072018209</v>
+        <v>-0.2709458229466549</v>
       </c>
       <c r="AF51" t="n">
-        <v>-0.3632231118028829</v>
+        <v>0.012709891431815</v>
       </c>
       <c r="AG51" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AH51" t="n">
-        <v>78</v>
+        <v>6</v>
       </c>
       <c r="AI51" t="b">
         <v>0</v>
@@ -7638,24 +7576,22 @@
         <v>0</v>
       </c>
       <c r="AK51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM51" t="b">
         <v>0</v>
       </c>
       <c r="AN51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>5631.27</v>
       </c>
       <c r="AP51" t="n">
-        <v>2327.89</v>
+        <v>7188.42</v>
       </c>
     </row>
   </sheetData>

--- a/output/daily_screen_latest.xlsx
+++ b/output/daily_screen_latest.xlsx
@@ -643,17 +643,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>89.19999999999999</v>
+        <v>68</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -671,15 +671,15 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1000</v>
+        <v>5163000</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="K2" t="b">
         <v>0</v>
@@ -688,7 +688,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1000</v>
+        <v>5163000</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -697,61 +697,61 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>303</v>
+        <v>19.54999923706055</v>
       </c>
       <c r="Q2" t="n">
-        <v>303</v>
+        <v>19.54999923706055</v>
       </c>
       <c r="R2" t="n">
-        <v>57135196</v>
+        <v>65846976</v>
       </c>
       <c r="S2" t="n">
-        <v>275.5</v>
+        <v>19.32999992370605</v>
       </c>
       <c r="T2" t="n">
-        <v>226.1</v>
+        <v>18.95250005722046</v>
       </c>
       <c r="U2" t="n">
-        <v>220.225</v>
+        <v>18.90750007629395</v>
       </c>
       <c r="V2" t="n">
-        <v>191.8666666666667</v>
+        <v>19.03753280639648</v>
       </c>
       <c r="W2" t="n">
-        <v>23.36450294887263</v>
+        <v>0.1408405378258699</v>
       </c>
       <c r="X2" t="n">
-        <v>15.37237288111563</v>
+        <v>0.06601432902447982</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.992130067756996</v>
+        <v>0.0748262088013901</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.909923263847713</v>
+        <v>0.06175010322038849</v>
       </c>
       <c r="AA2" t="b">
         <v>1</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.633423180592992</v>
+        <v>0.04825735318707736</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.9238095238095239</v>
+        <v>0.04812497047306286</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.6092781581690612</v>
+        <v>0.01310637267829273</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.8173265107802243</v>
+        <v>-0.01694859481505406</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.2080483526111632</v>
+        <v>0.0300549674933468</v>
       </c>
       <c r="AG2" t="n">
-        <v>100</v>
+        <v>52</v>
       </c>
       <c r="AH2" t="n">
-        <v>96</v>
+        <v>42</v>
       </c>
       <c r="AI2" t="b">
         <v>1</v>
@@ -785,7 +785,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -800,11 +800,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>31.6</v>
+        <v>61</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K3" t="b">
         <v>0</v>
@@ -839,67 +839,67 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>176.5</v>
+        <v>176</v>
       </c>
       <c r="Q3" t="n">
-        <v>176.5</v>
+        <v>176</v>
       </c>
       <c r="R3" t="n">
-        <v>2139257</v>
+        <v>1711116</v>
       </c>
       <c r="S3" t="n">
-        <v>173.5</v>
+        <v>174.8</v>
       </c>
       <c r="T3" t="n">
+        <v>174.425</v>
+      </c>
+      <c r="U3" t="n">
         <v>174.275</v>
       </c>
-      <c r="U3" t="n">
-        <v>174.5</v>
-      </c>
       <c r="V3" t="n">
-        <v>184.5443448384603</v>
+        <v>184.3876274108887</v>
       </c>
       <c r="W3" t="n">
-        <v>-1.853005894968362</v>
+        <v>-1.427535160659488</v>
       </c>
       <c r="X3" t="n">
-        <v>-3.513798826030349</v>
+        <v>-3.096546092956168</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.660792931061987</v>
+        <v>1.66901093229668</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.446399776522485</v>
+        <v>1.660792931061975</v>
       </c>
       <c r="AA3" t="b">
         <v>1</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.02486187845303867</v>
+        <v>0.01734104046242768</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.03270663176625743</v>
+        <v>-0.05071678095207688</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.04900690087696946</v>
+        <v>-0.01780994004635694</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.139189644795557</v>
+        <v>-0.1157903462401938</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.09018274391858749</v>
+        <v>0.09798040619383686</v>
       </c>
       <c r="AG3" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AH3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AI3" t="b">
         <v>1</v>
       </c>
       <c r="AJ3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK3" t="b">
         <v>1</v>
@@ -918,33 +918,35 @@
           <t>Already &gt; 0</t>
         </is>
       </c>
-      <c r="AP3" t="n">
-        <v>170.66</v>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>62.6</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -953,15 +955,15 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>7046000</v>
+        <v>6700000</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K4" t="b">
         <v>1</v>
@@ -970,70 +972,70 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>6847000</v>
+        <v>5808000</v>
       </c>
       <c r="N4" t="n">
-        <v>199000</v>
+        <v>892000</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02906382357236746</v>
+        <v>0.1535812672176309</v>
       </c>
       <c r="P4" t="n">
-        <v>1625</v>
+        <v>1245</v>
       </c>
       <c r="Q4" t="n">
-        <v>1625</v>
+        <v>1245</v>
       </c>
       <c r="R4" t="n">
-        <v>14219284</v>
+        <v>15727206</v>
       </c>
       <c r="S4" t="n">
-        <v>1698</v>
+        <v>1220</v>
       </c>
       <c r="T4" t="n">
-        <v>1560.5</v>
+        <v>1141.85</v>
       </c>
       <c r="U4" t="n">
-        <v>1549.75</v>
+        <v>1128.2</v>
       </c>
       <c r="V4" t="n">
-        <v>1453.416666666667</v>
+        <v>1040.966666666667</v>
       </c>
       <c r="W4" t="n">
-        <v>57.73155631103646</v>
+        <v>38.14472539795747</v>
       </c>
       <c r="X4" t="n">
-        <v>63.35963080173483</v>
+        <v>38.55835926692416</v>
       </c>
       <c r="Y4" t="n">
-        <v>-5.628074490698374</v>
+        <v>-0.4136338689666914</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.677347067840913</v>
+        <v>-0.5591652991634533</v>
       </c>
       <c r="AA4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1524822695035462</v>
+        <v>0.2808641975308641</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.2704081632653061</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.1283372470796154</v>
+        <v>0.2457132170220795</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.3379614314151449</v>
+        <v>0.2053345979771892</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.2096241843355295</v>
+        <v>0.04037861904489026</v>
       </c>
       <c r="AG4" t="n">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="AH4" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AI4" t="b">
         <v>1</v>
@@ -1048,13 +1050,13 @@
         <v>0</v>
       </c>
       <c r="AM4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN4" t="b">
         <v>1</v>
       </c>
       <c r="AO4" t="n">
-        <v>1690</v>
+        <v>1249.98</v>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
@@ -1065,118 +1067,118 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>61.6</v>
+        <v>48</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>18938000</v>
+        <v>1000</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="K5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="b">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>18721000</v>
+        <v>1000</v>
       </c>
       <c r="N5" t="n">
-        <v>217000</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01159126115057956</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1075</v>
+        <v>557</v>
       </c>
       <c r="Q5" t="n">
-        <v>1075</v>
+        <v>557</v>
       </c>
       <c r="R5" t="n">
-        <v>29104625</v>
+        <v>28104300</v>
       </c>
       <c r="S5" t="n">
-        <v>1193</v>
+        <v>555.2</v>
       </c>
       <c r="T5" t="n">
-        <v>1154.15</v>
+        <v>526.975</v>
       </c>
       <c r="U5" t="n">
-        <v>1148.9</v>
+        <v>523</v>
       </c>
       <c r="V5" t="n">
-        <v>1031.466666666667</v>
+        <v>490.7916666666667</v>
       </c>
       <c r="W5" t="n">
-        <v>17.60147184379503</v>
+        <v>13.0298655157427</v>
       </c>
       <c r="X5" t="n">
-        <v>47.22825782463612</v>
+        <v>17.33104492404922</v>
       </c>
       <c r="Y5" t="n">
-        <v>-29.6267859808411</v>
+        <v>-4.301179408306524</v>
       </c>
       <c r="Z5" t="n">
-        <v>-16.08969647293449</v>
+        <v>-4.317652886009135</v>
       </c>
       <c r="AA5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.1082474226804124</v>
+        <v>0.1664921465968587</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.4333333333333333</v>
+        <v>0.09430255402750487</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.08410240025648164</v>
+        <v>0.1313411660880741</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.3268503203040338</v>
+        <v>0.02922898873938795</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.2427479200475522</v>
+        <v>0.1021121773486862</v>
       </c>
       <c r="AG5" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH5" t="n">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="AI5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ5" t="b">
         <v>1</v>
@@ -1188,12 +1190,14 @@
         <v>0</v>
       </c>
       <c r="AM5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO5" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>606.02</v>
+      </c>
       <c r="AP5" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -1203,26 +1207,26 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>55.6</v>
+        <v>47.40000000000001</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1231,24 +1235,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>8937000</v>
+        <v>501000</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="K6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="b">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>8937000</v>
+        <v>501000</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1257,61 +1261,61 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1345</v>
+        <v>248</v>
       </c>
       <c r="Q6" t="n">
-        <v>1345</v>
+        <v>248</v>
       </c>
       <c r="R6" t="n">
-        <v>10513585</v>
+        <v>50253773</v>
       </c>
       <c r="S6" t="n">
-        <v>1426</v>
+        <v>244.4</v>
       </c>
       <c r="T6" t="n">
-        <v>1306.5</v>
+        <v>234.1</v>
       </c>
       <c r="U6" t="n">
-        <v>1292</v>
+        <v>232.625</v>
       </c>
       <c r="V6" t="n">
-        <v>1186.666666666667</v>
+        <v>221.55</v>
       </c>
       <c r="W6" t="n">
-        <v>53.28766341803134</v>
+        <v>3.972947556634949</v>
       </c>
       <c r="X6" t="n">
-        <v>69.21207353577972</v>
+        <v>4.107292513375468</v>
       </c>
       <c r="Y6" t="n">
-        <v>-15.92441011774838</v>
+        <v>-0.1343449567405184</v>
       </c>
       <c r="Z6" t="n">
-        <v>-2.863371057998521</v>
+        <v>-0.5706998436825916</v>
       </c>
       <c r="AA6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.2748815165876777</v>
+        <v>0.1350114416475972</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.2171945701357465</v>
+        <v>0.180952380952381</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.2507364941637469</v>
+        <v>0.09986046113881253</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.110711557106447</v>
+        <v>0.1158788156642641</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.1400249370572999</v>
+        <v>-0.01601835452545153</v>
       </c>
       <c r="AG6" t="n">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AH6" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="AI6" t="b">
         <v>1</v>
@@ -1326,13 +1330,13 @@
         <v>0</v>
       </c>
       <c r="AM6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN6" t="b">
         <v>1</v>
       </c>
       <c r="AO6" t="n">
-        <v>1525.23</v>
+        <v>249.98</v>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
@@ -1343,17 +1347,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1362,7 +1366,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>54</v>
+        <v>62.2</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1371,87 +1375,87 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>5808000</v>
+        <v>7224000</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="b">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>5423000</v>
+        <v>7046000</v>
       </c>
       <c r="N7" t="n">
-        <v>385000</v>
+        <v>178000</v>
       </c>
       <c r="O7" t="n">
-        <v>0.07099391480730223</v>
+        <v>0.02526256031791087</v>
       </c>
       <c r="P7" t="n">
-        <v>1190</v>
+        <v>1615</v>
       </c>
       <c r="Q7" t="n">
-        <v>1190</v>
+        <v>1615</v>
       </c>
       <c r="R7" t="n">
-        <v>13734387</v>
+        <v>10975718</v>
       </c>
       <c r="S7" t="n">
-        <v>1228</v>
+        <v>1673</v>
       </c>
       <c r="T7" t="n">
-        <v>1128.2</v>
+        <v>1572.75</v>
       </c>
       <c r="U7" t="n">
-        <v>1119.7</v>
+        <v>1560.5</v>
       </c>
       <c r="V7" t="n">
-        <v>1036.55</v>
+        <v>1459.75</v>
       </c>
       <c r="W7" t="n">
-        <v>38.10260243500238</v>
+        <v>45.02341109165354</v>
       </c>
       <c r="X7" t="n">
-        <v>38.66176773416586</v>
+        <v>59.69238685971857</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.5591652991634817</v>
+        <v>-14.66897576806503</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.718594003378385</v>
+        <v>-5.628074490698374</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1788321167883211</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.2837108953613807</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.1425216442427359</v>
+        <v>0.1436811362795365</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.1772278823320812</v>
+        <v>0.2426187424041908</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.03470623808934525</v>
+        <v>-0.0989376061246543</v>
       </c>
       <c r="AG7" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AH7" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AI7" t="b">
         <v>1</v>
@@ -1472,7 +1476,7 @@
         <v>1</v>
       </c>
       <c r="AO7" t="n">
-        <v>1197.14</v>
+        <v>1782.96</v>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
@@ -1483,17 +1487,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1502,24 +1506,24 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>47.6</v>
+        <v>60.8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>8348000</v>
+        <v>19386000</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K8" t="b">
         <v>1</v>
@@ -1528,70 +1532,70 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>8348000</v>
+        <v>18938000</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>448000</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.02365614109198437</v>
       </c>
       <c r="P8" t="n">
-        <v>673</v>
+        <v>1090</v>
       </c>
       <c r="Q8" t="n">
-        <v>673</v>
+        <v>1090</v>
       </c>
       <c r="R8" t="n">
-        <v>38892294</v>
+        <v>14914936</v>
       </c>
       <c r="S8" t="n">
-        <v>733.2</v>
+        <v>1157</v>
       </c>
       <c r="T8" t="n">
-        <v>694.7</v>
+        <v>1161.1</v>
       </c>
       <c r="U8" t="n">
-        <v>691.65</v>
+        <v>1154.15</v>
       </c>
       <c r="V8" t="n">
-        <v>632.5833333333334</v>
+        <v>1035.883333333333</v>
       </c>
       <c r="W8" t="n">
-        <v>16.2207547112946</v>
+        <v>4.353879746731536</v>
       </c>
       <c r="X8" t="n">
-        <v>24.2395656431005</v>
+        <v>38.65338220905522</v>
       </c>
       <c r="Y8" t="n">
-        <v>-8.018810931805895</v>
+        <v>-34.29950246232368</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0.1113463356609614</v>
+        <v>-29.62678598084111</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.09967320261437917</v>
+        <v>0.1461619348054679</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.1273031825795645</v>
+        <v>0.3212121212121213</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.07552818019044838</v>
+        <v>0.1110109542966833</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.020820169550265</v>
+        <v>0.2561385559240044</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.05470801064018338</v>
+        <v>-0.1451276016273211</v>
       </c>
       <c r="AG8" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="AH8" t="n">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
@@ -1609,11 +1613,9 @@
         <v>0</v>
       </c>
       <c r="AN8" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>764.53</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -1623,7 +1625,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1642,24 +1644,24 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>47.2</v>
+        <v>57.2</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>696000</v>
+        <v>981000</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="K9" t="b">
         <v>0</v>
@@ -1671,70 +1673,70 @@
         <v>696000</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>285000</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>0.4094827586206897</v>
       </c>
       <c r="P9" t="n">
-        <v>1520</v>
+        <v>1570</v>
       </c>
       <c r="Q9" t="n">
-        <v>1520</v>
+        <v>1570</v>
       </c>
       <c r="R9" t="n">
-        <v>4663196</v>
+        <v>6008077</v>
       </c>
       <c r="S9" t="n">
-        <v>1670</v>
+        <v>1642</v>
       </c>
       <c r="T9" t="n">
+        <v>1564.25</v>
+      </c>
+      <c r="U9" t="n">
         <v>1546.75</v>
       </c>
-      <c r="U9" t="n">
-        <v>1532.5</v>
-      </c>
       <c r="V9" t="n">
-        <v>1269.766666666667</v>
+        <v>1279.55</v>
       </c>
       <c r="W9" t="n">
-        <v>56.77879251635659</v>
+        <v>44.2140083672773</v>
       </c>
       <c r="X9" t="n">
-        <v>75.81528451744614</v>
+        <v>69.49502928741238</v>
       </c>
       <c r="Y9" t="n">
+        <v>-25.28102092013508</v>
+      </c>
+      <c r="Z9" t="n">
         <v>-19.03649200108956</v>
       </c>
-      <c r="Z9" t="n">
-        <v>0.3863480529721812</v>
-      </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.2307692307692308</v>
+        <v>0.2868852459016393</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.5653964984552009</v>
+        <v>0.5971515768056967</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.2066242083453</v>
+        <v>0.2517342653928547</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.4589134854259014</v>
+        <v>0.5320780115175798</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.2522892770806013</v>
+        <v>-0.2803437461247251</v>
       </c>
       <c r="AG9" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AH9" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AI9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ9" t="b">
         <v>1</v>
@@ -1749,10 +1751,10 @@
         <v>0</v>
       </c>
       <c r="AN9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>1735.84</v>
+        <v>1855.74</v>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
@@ -1763,17 +1765,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1782,96 +1784,96 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>47</v>
+        <v>54.6</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>751000</v>
+        <v>6303000</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="K10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="b">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>751000</v>
+        <v>6147000</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>156000</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>0.02537823328452904</v>
       </c>
       <c r="P10" t="n">
-        <v>7670</v>
+        <v>3315</v>
       </c>
       <c r="Q10" t="n">
-        <v>7670</v>
+        <v>3315</v>
       </c>
       <c r="R10" t="n">
-        <v>2351062</v>
+        <v>3730261</v>
       </c>
       <c r="S10" t="n">
-        <v>8094</v>
+        <v>3276</v>
       </c>
       <c r="T10" t="n">
-        <v>7821.25</v>
+        <v>3402</v>
       </c>
       <c r="U10" t="n">
-        <v>7757.75</v>
+        <v>3392</v>
       </c>
       <c r="V10" t="n">
-        <v>6034.416666666667</v>
+        <v>3093.299527994792</v>
       </c>
       <c r="W10" t="n">
-        <v>231.2510412784031</v>
+        <v>-35.3894972052758</v>
       </c>
       <c r="X10" t="n">
-        <v>393.6329477446294</v>
+        <v>13.16323473578665</v>
       </c>
       <c r="Y10" t="n">
-        <v>-162.3819064662263</v>
+        <v>-48.55273194106245</v>
       </c>
       <c r="Z10" t="n">
-        <v>-110.2352865917775</v>
+        <v>-62.50287942092719</v>
       </c>
       <c r="AA10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.1984375</v>
+        <v>0.0642054574638844</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.048064085447263</v>
+        <v>0.437355921588952</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.1742924775760692</v>
+        <v>0.02905447695509977</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.9415810724179636</v>
+        <v>0.3722823563008351</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.7672885948418944</v>
+        <v>-0.3432278793457353</v>
       </c>
       <c r="AG10" t="n">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="AH10" t="n">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="AI10" t="b">
         <v>0</v>
@@ -1886,12 +1888,14 @@
         <v>0</v>
       </c>
       <c r="AM10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO10" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>3865.29</v>
+      </c>
       <c r="AP10" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -1901,17 +1905,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1920,24 +1924,24 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>45.4</v>
+        <v>52.2</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2502000</v>
+        <v>1857000</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K11" t="b">
         <v>0</v>
@@ -1946,70 +1950,70 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2502000</v>
+        <v>1257000</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>600000</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>0.477326968973747</v>
       </c>
       <c r="P11" t="n">
-        <v>6765</v>
+        <v>258.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>6765</v>
+        <v>258.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1725555</v>
+        <v>24088759</v>
       </c>
       <c r="S11" t="n">
-        <v>7030</v>
+        <v>269.1</v>
       </c>
       <c r="T11" t="n">
-        <v>6499.5</v>
+        <v>255.45</v>
       </c>
       <c r="U11" t="n">
-        <v>6452.25</v>
+        <v>253.575</v>
       </c>
       <c r="V11" t="n">
-        <v>5368.221321614584</v>
+        <v>227.675</v>
       </c>
       <c r="W11" t="n">
-        <v>238.1808050766131</v>
+        <v>6.416139638692187</v>
       </c>
       <c r="X11" t="n">
-        <v>304.7328259863507</v>
+        <v>6.022033229720711</v>
       </c>
       <c r="Y11" t="n">
-        <v>-66.55202090973768</v>
+        <v>0.3941064089714752</v>
       </c>
       <c r="Z11" t="n">
-        <v>-27.25489173255033</v>
+        <v>1.892489559765102</v>
       </c>
       <c r="AA11" t="b">
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.1623711340206186</v>
+        <v>0.1696832579185521</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.127188645757205</v>
+        <v>0.230952380952381</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.1382261115966879</v>
+        <v>0.1345322774097675</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.020705632727906</v>
+        <v>0.1658788156642641</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.882479521131218</v>
+        <v>-0.03134653825449663</v>
       </c>
       <c r="AG11" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AH11" t="n">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="AI11" t="b">
         <v>1</v>
@@ -2018,19 +2022,21 @@
         <v>1</v>
       </c>
       <c r="AK11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM11" t="b">
         <v>0</v>
       </c>
       <c r="AN11" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>7522.68</v>
+        <v>0</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
@@ -2041,17 +2047,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2060,7 +2066,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>44.4</v>
+        <v>51.2</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2069,24 +2075,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1257000</v>
+        <v>8937000</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="K12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="b">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1257000</v>
+        <v>8937000</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -2095,61 +2101,61 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>268</v>
+        <v>1355</v>
       </c>
       <c r="Q12" t="n">
-        <v>268</v>
+        <v>1355</v>
       </c>
       <c r="R12" t="n">
-        <v>22397989</v>
+        <v>9127777</v>
       </c>
       <c r="S12" t="n">
-        <v>268.6</v>
+        <v>1402</v>
       </c>
       <c r="T12" t="n">
-        <v>253.575</v>
+        <v>1320</v>
       </c>
       <c r="U12" t="n">
-        <v>251.55</v>
+        <v>1306.5</v>
       </c>
       <c r="V12" t="n">
-        <v>226.8666666666667</v>
+        <v>1189.416666666667</v>
       </c>
       <c r="W12" t="n">
-        <v>7.815996187242945</v>
+        <v>41.30080840777782</v>
       </c>
       <c r="X12" t="n">
-        <v>5.923506627477843</v>
+        <v>63.62982051017935</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.892489559765102</v>
+        <v>-22.32901210240153</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.584476022172923</v>
+        <v>-15.92441011774838</v>
       </c>
       <c r="AA12" t="b">
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.1780219780219781</v>
+        <v>0.2488479262672811</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.3569620253164556</v>
+        <v>0.1386554621848739</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.1538769555980473</v>
+        <v>0.2136969457584965</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.2504790122871561</v>
+        <v>0.07358189689675698</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.09660205668910882</v>
+        <v>0.1401150488617395</v>
       </c>
       <c r="AG12" t="n">
         <v>90</v>
       </c>
       <c r="AH12" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="AI12" t="b">
         <v>1</v>
@@ -2158,10 +2164,10 @@
         <v>1</v>
       </c>
       <c r="AK12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="b">
         <v>0</v>
@@ -2169,10 +2175,8 @@
       <c r="AN12" t="b">
         <v>0</v>
       </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+      <c r="AO12" t="n">
+        <v>1607.03</v>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
@@ -2183,17 +2187,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2202,24 +2206,24 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>42.8</v>
+        <v>47.8</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>121000</v>
+        <v>649000</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="K13" t="b">
         <v>0</v>
@@ -2228,94 +2232,90 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>121000</v>
+        <v>499000</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>0.3006012024048096</v>
       </c>
       <c r="P13" t="n">
-        <v>1390</v>
+        <v>2250</v>
       </c>
       <c r="Q13" t="n">
-        <v>1390</v>
+        <v>2250</v>
       </c>
       <c r="R13" t="n">
-        <v>3407870</v>
+        <v>1783307</v>
       </c>
       <c r="S13" t="n">
-        <v>1546</v>
+        <v>2208</v>
       </c>
       <c r="T13" t="n">
-        <v>1364.25</v>
+        <v>2343.75</v>
       </c>
       <c r="U13" t="n">
-        <v>1356</v>
+        <v>2332.5</v>
       </c>
       <c r="V13" t="n">
-        <v>1244.200631713867</v>
+        <v>2005.600705973307</v>
       </c>
       <c r="W13" t="n">
-        <v>60.63853146731913</v>
+        <v>-27.82926529920223</v>
       </c>
       <c r="X13" t="n">
-        <v>60.42184308991468</v>
+        <v>16.09219857541557</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.216688377404445</v>
+        <v>-43.9214638746178</v>
       </c>
       <c r="Z13" t="n">
-        <v>24.02794551791079</v>
+        <v>-56.51359028373258</v>
       </c>
       <c r="AA13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.1346938775510205</v>
+        <v>0.1111111111111112</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.5055280513162139</v>
+        <v>0.6012255213039355</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.1105488551270897</v>
+        <v>0.07596013060232654</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.3990450382869144</v>
+        <v>0.5361519560158186</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.2884961831598247</v>
+        <v>-0.460191825413492</v>
       </c>
       <c r="AG13" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="AH13" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="AI13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="b">
         <v>1</v>
       </c>
       <c r="AK13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN13" t="b">
         <v>0</v>
       </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
+      <c r="AO13" t="inlineStr"/>
       <c r="AP13" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -2325,17 +2325,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>42.4</v>
+        <v>47.8</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K14" t="b">
         <v>0</v>
@@ -2379,61 +2379,61 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>6605</v>
+        <v>298.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>6605</v>
+        <v>298.5</v>
       </c>
       <c r="R14" t="n">
-        <v>3317049</v>
+        <v>39973694</v>
       </c>
       <c r="S14" t="n">
-        <v>6949</v>
+        <v>285.6</v>
       </c>
       <c r="T14" t="n">
-        <v>6480.25</v>
+        <v>232</v>
       </c>
       <c r="U14" t="n">
-        <v>6449.75</v>
+        <v>226.1</v>
       </c>
       <c r="V14" t="n">
-        <v>5741.891507975261</v>
+        <v>194.0583333333333</v>
       </c>
       <c r="W14" t="n">
-        <v>149.9785618622345</v>
+        <v>24.41714981393159</v>
       </c>
       <c r="X14" t="n">
-        <v>127.2206041127149</v>
+        <v>17.18132826767882</v>
       </c>
       <c r="Y14" t="n">
-        <v>22.75795774951962</v>
+        <v>7.235821546252765</v>
       </c>
       <c r="Z14" t="n">
-        <v>78.81847565582092</v>
+        <v>7.992130067756996</v>
       </c>
       <c r="AA14" t="b">
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.1017514595496247</v>
+        <v>0.6537396121883656</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.7200851100732957</v>
+        <v>0.7874251497005988</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.07760643712569393</v>
+        <v>0.618588631679581</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.6136020970439962</v>
+        <v>0.7223515844124819</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.5359956599183022</v>
+        <v>-0.1037629527329009</v>
       </c>
       <c r="AG14" t="n">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AH14" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AI14" t="b">
         <v>1</v>
@@ -2467,17 +2467,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>41.6</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2495,24 +2495,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>23519000</v>
+        <v>2502000</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="K15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="b">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>23519000</v>
+        <v>2502000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2521,64 +2521,64 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>573</v>
+        <v>6730</v>
       </c>
       <c r="Q15" t="n">
-        <v>573</v>
+        <v>6730</v>
       </c>
       <c r="R15" t="n">
-        <v>55840314</v>
+        <v>1131578</v>
       </c>
       <c r="S15" t="n">
-        <v>614</v>
+        <v>6943</v>
       </c>
       <c r="T15" t="n">
-        <v>586.25</v>
+        <v>6570.5</v>
       </c>
       <c r="U15" t="n">
-        <v>584.85</v>
+        <v>6499.5</v>
       </c>
       <c r="V15" t="n">
-        <v>578.9916666666667</v>
+        <v>5422.083333333333</v>
       </c>
       <c r="W15" t="n">
-        <v>9.119528519109963</v>
+        <v>189.7397046221449</v>
       </c>
       <c r="X15" t="n">
-        <v>13.22992947122095</v>
+        <v>281.7342017135096</v>
       </c>
       <c r="Y15" t="n">
-        <v>-4.110400952110991</v>
+        <v>-91.99449709136468</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.572349389277775</v>
+        <v>-66.55202090973768</v>
       </c>
       <c r="AA15" t="b">
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.05137614678899083</v>
+        <v>0.2674199623352165</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.09047619047619049</v>
+        <v>0.9238029410664506</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.02723112436506003</v>
+        <v>0.2322689818264319</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0.19695920350549</v>
+        <v>0.8587293757783336</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.22419032787055</v>
+        <v>-0.6264603939519018</v>
       </c>
       <c r="AG15" t="n">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="AH15" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="AI15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ15" t="b">
         <v>1</v>
@@ -2596,7 +2596,7 @@
         <v>1</v>
       </c>
       <c r="AO15" t="n">
-        <v>619.99</v>
+        <v>7766.42</v>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
@@ -2607,17 +2607,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2626,7 +2626,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>40.6</v>
+        <v>44.40000000000001</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2635,15 +2635,15 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1000</v>
+        <v>751000</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="K16" t="b">
         <v>0</v>
@@ -2652,7 +2652,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1000</v>
+        <v>751000</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2661,61 +2661,61 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>105.5</v>
+        <v>7480</v>
       </c>
       <c r="Q16" t="n">
-        <v>105.5</v>
+        <v>7480</v>
       </c>
       <c r="R16" t="n">
-        <v>29963917</v>
+        <v>1890956</v>
       </c>
       <c r="S16" t="n">
-        <v>117.9</v>
+        <v>7918</v>
       </c>
       <c r="T16" t="n">
-        <v>110.5349998474121</v>
+        <v>7893.5</v>
       </c>
       <c r="U16" t="n">
-        <v>109.5899997711182</v>
+        <v>7821.25</v>
       </c>
       <c r="V16" t="n">
-        <v>95.88999989827474</v>
+        <v>6090.5</v>
       </c>
       <c r="W16" t="n">
-        <v>3.315660036079052</v>
+        <v>140.3120352777469</v>
       </c>
       <c r="X16" t="n">
-        <v>6.159377143649936</v>
+        <v>342.9687652512529</v>
       </c>
       <c r="Y16" t="n">
-        <v>-2.843717107570884</v>
+        <v>-202.6567299735061</v>
       </c>
       <c r="Z16" t="n">
-        <v>-1.356631719348664</v>
+        <v>-162.3819064662263</v>
       </c>
       <c r="AA16" t="b">
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.2182448251604396</v>
+        <v>0.2394366197183098</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.02427184466019416</v>
+        <v>0.8177399756986634</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.1940998027365088</v>
+        <v>0.2042856392095251</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0.08221116836910536</v>
+        <v>0.7526664104105465</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.2763109711056142</v>
+        <v>-0.5483807712010214</v>
       </c>
       <c r="AG16" t="n">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="AH16" t="n">
-        <v>28</v>
+        <v>98</v>
       </c>
       <c r="AI16" t="b">
         <v>0</v>
@@ -2745,17 +2745,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2764,7 +2764,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>39.40000000000001</v>
+        <v>44.2</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2773,15 +2773,15 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>12188000</v>
+        <v>8348000</v>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K17" t="b">
         <v>1</v>
@@ -2790,7 +2790,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>12188000</v>
+        <v>8348000</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2799,61 +2799,61 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2440</v>
+        <v>671</v>
       </c>
       <c r="Q17" t="n">
-        <v>2440</v>
+        <v>671</v>
       </c>
       <c r="R17" t="n">
-        <v>57820478</v>
+        <v>19182798</v>
       </c>
       <c r="S17" t="n">
-        <v>2502</v>
+        <v>718.6</v>
       </c>
       <c r="T17" t="n">
-        <v>2488.9</v>
+        <v>698.65</v>
       </c>
       <c r="U17" t="n">
-        <v>2485.550732421875</v>
+        <v>694.7</v>
       </c>
       <c r="V17" t="n">
-        <v>2416.213037109375</v>
+        <v>633.2166666666667</v>
       </c>
       <c r="W17" t="n">
-        <v>6.539743496080519</v>
+        <v>8.745163602010734</v>
       </c>
       <c r="X17" t="n">
-        <v>22.45524442090876</v>
+        <v>21.14068523488255</v>
       </c>
       <c r="Y17" t="n">
-        <v>-15.91550092482824</v>
+        <v>-12.39552163287181</v>
       </c>
       <c r="Z17" t="n">
-        <v>-9.164258495517888</v>
+        <v>-8.018810931805895</v>
       </c>
       <c r="AA17" t="b">
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.02822795535906453</v>
+        <v>0.1334459459459461</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.054819980938972</v>
+        <v>0.0600315955766193</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.004082932935133732</v>
+        <v>0.09829496543716143</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0.05166303209032752</v>
+        <v>-0.005041969711497618</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.05574596502546125</v>
+        <v>0.103336935148659</v>
       </c>
       <c r="AG17" t="n">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="AH17" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AI17" t="b">
         <v>0</v>
@@ -2871,11 +2871,9 @@
         <v>0</v>
       </c>
       <c r="AN17" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>2620.56</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO17" t="inlineStr"/>
       <c r="AP17" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -2885,17 +2883,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2904,7 +2902,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>39.4</v>
+        <v>40.6</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2913,24 +2911,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>6264000</v>
+        <v>121000</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="K18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="b">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>6264000</v>
+        <v>121000</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2939,61 +2937,61 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1950</v>
+        <v>1410</v>
       </c>
       <c r="Q18" t="n">
-        <v>1950</v>
+        <v>1410</v>
       </c>
       <c r="R18" t="n">
-        <v>4607746</v>
+        <v>2929194</v>
       </c>
       <c r="S18" t="n">
-        <v>2048</v>
+        <v>1523</v>
       </c>
       <c r="T18" t="n">
-        <v>1935.25</v>
+        <v>1374</v>
       </c>
       <c r="U18" t="n">
-        <v>1931.5</v>
+        <v>1364.25</v>
       </c>
       <c r="V18" t="n">
-        <v>2069.171905517578</v>
+        <v>1251.276076253255</v>
       </c>
       <c r="W18" t="n">
-        <v>22.5393164659597</v>
+        <v>44.93885460905562</v>
       </c>
       <c r="X18" t="n">
-        <v>14.55305818500008</v>
+        <v>57.32524539374288</v>
       </c>
       <c r="Y18" t="n">
-        <v>7.986258280959616</v>
+        <v>-12.38639078468725</v>
       </c>
       <c r="Z18" t="n">
-        <v>22.9108081901605</v>
+        <v>0.216688377404445</v>
       </c>
       <c r="AA18" t="b">
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.04000000000000004</v>
+        <v>0.1604938271604939</v>
       </c>
       <c r="AC18" t="n">
-        <v>-0.05960032542877358</v>
+        <v>0.430784538209011</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.01585497757606924</v>
+        <v>0.1253428466517092</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0.1660833384580731</v>
+        <v>0.3657109729208941</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.1819383160341423</v>
+        <v>-0.2403681262691848</v>
       </c>
       <c r="AG18" t="n">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="AH18" t="n">
-        <v>12</v>
+        <v>84</v>
       </c>
       <c r="AI18" t="b">
         <v>1</v>
@@ -3002,21 +3000,19 @@
         <v>1</v>
       </c>
       <c r="AK18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="b">
         <v>0</v>
       </c>
       <c r="AN18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1551</v>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
@@ -3027,17 +3023,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3046,7 +3042,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>35.6</v>
+        <v>39.4</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3055,15 +3051,15 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2185000</v>
+        <v>1000</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="K19" t="b">
         <v>0</v>
@@ -3072,7 +3068,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2185000</v>
+        <v>1000</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -3081,61 +3077,61 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>229</v>
+        <v>105.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>229</v>
+        <v>105.5</v>
       </c>
       <c r="R19" t="n">
-        <v>2458715</v>
+        <v>19183974</v>
       </c>
       <c r="S19" t="n">
-        <v>240.8</v>
+        <v>113.4</v>
       </c>
       <c r="T19" t="n">
-        <v>233</v>
+        <v>111.5899997711182</v>
       </c>
       <c r="U19" t="n">
-        <v>232.55</v>
+        <v>110.5349998474121</v>
       </c>
       <c r="V19" t="n">
-        <v>210.575</v>
+        <v>95.91499989827474</v>
       </c>
       <c r="W19" t="n">
-        <v>3.198866842150721</v>
+        <v>1.714176809923529</v>
       </c>
       <c r="X19" t="n">
-        <v>4.465841089938604</v>
+        <v>5.27033707690464</v>
       </c>
       <c r="Y19" t="n">
-        <v>-1.266974247787883</v>
+        <v>-3.55616026698111</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.2099306232097398</v>
+        <v>-2.843717107570892</v>
       </c>
       <c r="AA19" t="b">
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.04090909090909101</v>
+        <v>0.249999977401083</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.1896103896103896</v>
+        <v>0.01442307692307687</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.01676406848516021</v>
+        <v>0.2148489968922984</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.08312737658109004</v>
+        <v>-0.05065048836504005</v>
       </c>
       <c r="AF19" t="n">
-        <v>-0.06636330809592983</v>
+        <v>0.2654994852573385</v>
       </c>
       <c r="AG19" t="n">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="AH19" t="n">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="AI19" t="b">
         <v>0</v>
@@ -3153,11 +3149,9 @@
         <v>0</v>
       </c>
       <c r="AN19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>243.66</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO19" t="inlineStr"/>
       <c r="AP19" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -3167,17 +3161,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3186,102 +3180,102 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>35.4</v>
+        <v>36.4</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1000</v>
+        <v>7507000</v>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="K20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="b">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1000</v>
+        <v>7389000</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>118000</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>0.015969684666396</v>
       </c>
       <c r="P20" t="n">
-        <v>519</v>
+        <v>1635</v>
       </c>
       <c r="Q20" t="n">
-        <v>519</v>
+        <v>1635</v>
       </c>
       <c r="R20" t="n">
-        <v>24674635</v>
+        <v>8576514</v>
       </c>
       <c r="S20" t="n">
-        <v>562.2</v>
+        <v>1745</v>
       </c>
       <c r="T20" t="n">
-        <v>523</v>
+        <v>1848.25</v>
       </c>
       <c r="U20" t="n">
-        <v>521.525</v>
+        <v>1850</v>
       </c>
       <c r="V20" t="n">
-        <v>489.9916666666667</v>
+        <v>1778.083333333333</v>
       </c>
       <c r="W20" t="n">
-        <v>14.08868689011672</v>
+        <v>-39.69044453345396</v>
       </c>
       <c r="X20" t="n">
-        <v>18.40633977612585</v>
+        <v>9.736984121348616</v>
       </c>
       <c r="Y20" t="n">
-        <v>-4.317652886009135</v>
+        <v>-49.42742865480257</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.738418848632652</v>
+        <v>-43.51850691221316</v>
       </c>
       <c r="AA20" t="b">
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.06026557711950975</v>
+        <v>-0.02095808383233533</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.08463949843260199</v>
+        <v>-0.1089918256130791</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.03612055469557895</v>
+        <v>-0.05610906434111995</v>
       </c>
       <c r="AE20" t="n">
-        <v>-0.02184351459669753</v>
+        <v>-0.174065390901196</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.05796406929227649</v>
+        <v>0.117956326560076</v>
       </c>
       <c r="AG20" t="n">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="AH20" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="AI20" t="b">
         <v>0</v>
       </c>
       <c r="AJ20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="b">
         <v>0</v>
@@ -3293,31 +3287,27 @@
         <v>0</v>
       </c>
       <c r="AN20" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>567.79</v>
-      </c>
-      <c r="AP20" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="AO20" t="inlineStr"/>
+      <c r="AP20" t="n">
+        <v>1934.47</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3326,7 +3316,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>34.8</v>
+        <v>35.2</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3335,15 +3325,15 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>7389000</v>
+        <v>23519000</v>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K21" t="b">
         <v>1</v>
@@ -3352,7 +3342,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>7389000</v>
+        <v>23519000</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -3361,61 +3351,61 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1630</v>
+        <v>567</v>
       </c>
       <c r="Q21" t="n">
-        <v>1630</v>
+        <v>567</v>
       </c>
       <c r="R21" t="n">
-        <v>25165431</v>
+        <v>36099734</v>
       </c>
       <c r="S21" t="n">
-        <v>1811</v>
+        <v>600.4</v>
       </c>
       <c r="T21" t="n">
-        <v>1850</v>
+        <v>587.75</v>
       </c>
       <c r="U21" t="n">
-        <v>1849.5</v>
+        <v>586.25</v>
       </c>
       <c r="V21" t="n">
-        <v>1781.416666666667</v>
+        <v>577.275</v>
       </c>
       <c r="W21" t="n">
-        <v>-21.4246656271639</v>
+        <v>3.588433587189684</v>
       </c>
       <c r="X21" t="n">
-        <v>22.09384128504931</v>
+        <v>11.3016302944147</v>
       </c>
       <c r="Y21" t="n">
-        <v>-43.51850691221321</v>
+        <v>-7.713196707225018</v>
       </c>
       <c r="Z21" t="n">
-        <v>-26.40925109269831</v>
+        <v>-4.110400952110991</v>
       </c>
       <c r="AA21" t="b">
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.006172839506172867</v>
+        <v>0.05586592178770955</v>
       </c>
       <c r="AC21" t="n">
-        <v>-0.04398826979472137</v>
+        <v>-0.1537313432835821</v>
       </c>
       <c r="AD21" t="n">
-        <v>-0.01797218291775793</v>
+        <v>0.02071494127892493</v>
       </c>
       <c r="AE21" t="n">
-        <v>-0.1504712828240209</v>
+        <v>-0.218804908571699</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.132499099906263</v>
+        <v>0.2395198498506239</v>
       </c>
       <c r="AG21" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="AH21" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AI21" t="b">
         <v>0</v>
@@ -3433,9 +3423,11 @@
         <v>0</v>
       </c>
       <c r="AN21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO21" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>654.3200000000001</v>
+      </c>
       <c r="AP21" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -3445,7 +3437,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3464,7 +3456,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>34</v>
+        <v>34.8</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3473,7 +3465,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -3499,61 +3491,61 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>90</v>
+        <v>92.30000305175781</v>
       </c>
       <c r="Q22" t="n">
-        <v>90</v>
+        <v>92.30000305175781</v>
       </c>
       <c r="R22" t="n">
-        <v>6093412</v>
+        <v>5955803</v>
       </c>
       <c r="S22" t="n">
-        <v>92.64000091552734</v>
+        <v>93.52000122070312</v>
       </c>
       <c r="T22" t="n">
+        <v>86.62500038146973</v>
+      </c>
+      <c r="U22" t="n">
         <v>86.06000022888183</v>
       </c>
-      <c r="U22" t="n">
-        <v>85.66000022888184</v>
-      </c>
       <c r="V22" t="n">
-        <v>84.71500015258789</v>
+        <v>84.74500020345052</v>
       </c>
       <c r="W22" t="n">
-        <v>2.580452518079056</v>
+        <v>2.474931803364896</v>
       </c>
       <c r="X22" t="n">
-        <v>1.765648662409141</v>
+        <v>1.907505290600312</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.8148038556699149</v>
+        <v>0.5674265127645846</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.448617325328615</v>
+        <v>0.8148038556698909</v>
       </c>
       <c r="AA22" t="b">
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.09756097560975618</v>
+        <v>0.1395062105155285</v>
       </c>
       <c r="AC22" t="n">
-        <v>-0.005524861878453025</v>
+        <v>0.01988953648351166</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.07341595318582539</v>
+        <v>0.1043552300067438</v>
       </c>
       <c r="AE22" t="n">
-        <v>-0.1120078749077525</v>
+        <v>-0.04518402880460526</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.1854238280935779</v>
+        <v>0.1495392588113491</v>
       </c>
       <c r="AG22" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH22" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="AI22" t="b">
         <v>1</v>
@@ -3587,17 +3579,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3606,7 +3598,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>33.40000000000001</v>
+        <v>34.40000000000001</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3615,24 +3607,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>6147000</v>
+        <v>1000</v>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="K23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="b">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>6147000</v>
+        <v>1000</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -3641,67 +3633,67 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>3085</v>
+        <v>6400</v>
       </c>
       <c r="Q23" t="n">
-        <v>3085</v>
+        <v>6400</v>
       </c>
       <c r="R23" t="n">
-        <v>4117102</v>
+        <v>4806266</v>
       </c>
       <c r="S23" t="n">
-        <v>3301</v>
+        <v>6897</v>
       </c>
       <c r="T23" t="n">
-        <v>3392</v>
+        <v>6497.5</v>
       </c>
       <c r="U23" t="n">
-        <v>3403.25</v>
+        <v>6480.25</v>
       </c>
       <c r="V23" t="n">
-        <v>3076.488163248698</v>
+        <v>5782.742663574219</v>
       </c>
       <c r="W23" t="n">
-        <v>-37.20146169987493</v>
+        <v>88.6731949735431</v>
       </c>
       <c r="X23" t="n">
-        <v>25.30141772105226</v>
+        <v>119.5111222848806</v>
       </c>
       <c r="Y23" t="n">
-        <v>-62.50287942092719</v>
+        <v>-30.83792731133747</v>
       </c>
       <c r="Z23" t="n">
-        <v>-42.45656714513813</v>
+        <v>22.75795774951959</v>
       </c>
       <c r="AA23" t="b">
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>-0.06797583081571001</v>
+        <v>0.05697770437654825</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.4535368719307133</v>
+        <v>0.6206919149641232</v>
       </c>
       <c r="AD23" t="n">
-        <v>-0.09212085323964081</v>
+        <v>0.02182672386776363</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.3470538589014138</v>
+        <v>0.5556183496760063</v>
       </c>
       <c r="AF23" t="n">
-        <v>-0.4391747121410546</v>
+        <v>-0.5337916258082427</v>
       </c>
       <c r="AG23" t="n">
-        <v>18</v>
+        <v>56.00000000000001</v>
       </c>
       <c r="AH23" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="AI23" t="b">
         <v>0</v>
       </c>
       <c r="AJ23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK23" t="b">
         <v>0</v>
@@ -3713,27 +3705,31 @@
         <v>0</v>
       </c>
       <c r="AN23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO23" t="inlineStr"/>
-      <c r="AP23" t="n">
-        <v>3438.16</v>
+        <v>1</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>6758.4</v>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>美律</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3751,7 +3747,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -3759,7 +3755,7 @@
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="K24" t="b">
         <v>0</v>
@@ -3777,84 +3773,82 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>80.90000152587891</v>
+        <v>3685</v>
       </c>
       <c r="Q24" t="n">
-        <v>80.90000152587891</v>
+        <v>3685</v>
       </c>
       <c r="R24" t="n">
-        <v>2756912</v>
+        <v>1717320</v>
       </c>
       <c r="S24" t="n">
-        <v>81.11999969482422</v>
+        <v>3956</v>
       </c>
       <c r="T24" t="n">
-        <v>78.3699993133545</v>
+        <v>3826.75</v>
       </c>
       <c r="U24" t="n">
-        <v>78.18999938964843</v>
+        <v>3810.25</v>
       </c>
       <c r="V24" t="n">
-        <v>77.81253980000814</v>
+        <v>3750.121183268229</v>
       </c>
       <c r="W24" t="n">
-        <v>1.022513155601047</v>
+        <v>9.753653540336018</v>
       </c>
       <c r="X24" t="n">
-        <v>0.4734498472867613</v>
+        <v>60.77968998631973</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.5490633083142854</v>
+        <v>-51.02603644598371</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.6624512411172711</v>
+        <v>-25.21574529991113</v>
       </c>
       <c r="AA24" t="b">
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.04657177661054734</v>
+        <v>0.09836065573770503</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.0357084496915796</v>
+        <v>0.06412674688517317</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.02242675418661655</v>
+        <v>0.0632096752289204</v>
       </c>
       <c r="AE24" t="n">
-        <v>-0.07077456333771992</v>
+        <v>-0.0009468184029437499</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.09320131752433647</v>
+        <v>0.06415649363186415</v>
       </c>
       <c r="AG24" t="n">
         <v>68</v>
       </c>
       <c r="AH24" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="AI24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="b">
         <v>1</v>
       </c>
       <c r="AK24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="b">
         <v>0</v>
       </c>
       <c r="AN24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>4259.86</v>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
@@ -3865,17 +3859,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3884,7 +3878,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>32.8</v>
+        <v>33</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3893,15 +3887,15 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>4143450</v>
+        <v>1000</v>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="K25" t="b">
         <v>0</v>
@@ -3910,7 +3904,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>4143450</v>
+        <v>1000</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3919,61 +3913,61 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>272</v>
+        <v>167.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>272</v>
+        <v>167.5</v>
       </c>
       <c r="R25" t="n">
-        <v>45882595</v>
+        <v>9654317</v>
       </c>
       <c r="S25" t="n">
-        <v>295.6</v>
+        <v>172.2</v>
       </c>
       <c r="T25" t="n">
-        <v>292.925</v>
+        <v>176.375</v>
       </c>
       <c r="U25" t="n">
-        <v>292.4</v>
+        <v>175.65</v>
       </c>
       <c r="V25" t="n">
-        <v>265.0567036946615</v>
+        <v>161.4333333333333</v>
       </c>
       <c r="W25" t="n">
-        <v>1.59777248717279</v>
+        <v>-0.2991385622451048</v>
       </c>
       <c r="X25" t="n">
-        <v>5.819726435740899</v>
+        <v>3.505857435229374</v>
       </c>
       <c r="Y25" t="n">
-        <v>-4.221953948568109</v>
+        <v>-3.804995997474479</v>
       </c>
       <c r="Z25" t="n">
-        <v>-1.674281199515953</v>
+        <v>-3.704980493044535</v>
       </c>
       <c r="AA25" t="b">
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.04015296367112819</v>
+        <v>0.09477124183006547</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.05985459857167075</v>
+        <v>0.07717041800643076</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.0160079412471974</v>
+        <v>0.05962026132128084</v>
       </c>
       <c r="AE25" t="n">
-        <v>-0.04662841445762878</v>
+        <v>0.01209685271831384</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.06263635570482617</v>
+        <v>0.047523408602967</v>
       </c>
       <c r="AG25" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="AH25" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AI25" t="b">
         <v>0</v>
@@ -3993,9 +3987,7 @@
       <c r="AN25" t="b">
         <v>0</v>
       </c>
-      <c r="AO25" t="n">
-        <v>319.87</v>
-      </c>
+      <c r="AO25" t="inlineStr"/>
       <c r="AP25" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -4005,17 +3997,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4033,24 +4025,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>501000</v>
+        <v>12188000</v>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="K26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="b">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>501000</v>
+        <v>12188000</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -4059,61 +4051,61 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>228</v>
+        <v>2420</v>
       </c>
       <c r="Q26" t="n">
-        <v>228</v>
+        <v>2420</v>
       </c>
       <c r="R26" t="n">
-        <v>29280281</v>
+        <v>40787765</v>
       </c>
       <c r="S26" t="n">
-        <v>244.4</v>
+        <v>2476</v>
       </c>
       <c r="T26" t="n">
-        <v>232.625</v>
+        <v>2491</v>
       </c>
       <c r="U26" t="n">
-        <v>232.275</v>
+        <v>2488.9</v>
       </c>
       <c r="V26" t="n">
-        <v>220.9166666666667</v>
+        <v>2416.497591145833</v>
       </c>
       <c r="W26" t="n">
-        <v>3.570178908878006</v>
+        <v>-3.262306824247389</v>
       </c>
       <c r="X26" t="n">
-        <v>4.140878752560598</v>
+        <v>17.31173417264522</v>
       </c>
       <c r="Y26" t="n">
-        <v>-0.5706998436825916</v>
+        <v>-20.57404099689261</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.790828440288431</v>
+        <v>-15.91550092530764</v>
       </c>
       <c r="AA26" t="b">
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.03167420814479649</v>
+        <v>0.01766190075693852</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.1457286432160805</v>
+        <v>0.007105186261707974</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.007529185720865694</v>
+        <v>-0.0174890797518461</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.03924563018678096</v>
+        <v>-0.05796837902640894</v>
       </c>
       <c r="AF26" t="n">
-        <v>-0.03171644446591526</v>
+        <v>0.04047929927456284</v>
       </c>
       <c r="AG26" t="n">
-        <v>57.99999999999999</v>
+        <v>38</v>
       </c>
       <c r="AH26" t="n">
-        <v>56.00000000000001</v>
+        <v>30</v>
       </c>
       <c r="AI26" t="b">
         <v>0</v>
@@ -4134,7 +4126,7 @@
         <v>1</v>
       </c>
       <c r="AO26" t="n">
-        <v>234.84</v>
+        <v>2652.32</v>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
@@ -4145,17 +4137,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>慧洋-KY</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4164,7 +4156,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>32.40000000000001</v>
+        <v>30.8</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4173,7 +4165,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -4181,7 +4173,7 @@
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="K27" t="b">
         <v>0</v>
@@ -4199,82 +4191,84 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>3705</v>
+        <v>101.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>3705</v>
+        <v>101.5</v>
       </c>
       <c r="R27" t="n">
-        <v>2288438</v>
+        <v>1884892</v>
       </c>
       <c r="S27" t="n">
-        <v>4088</v>
+        <v>102.2</v>
       </c>
       <c r="T27" t="n">
-        <v>3810.25</v>
+        <v>99.99500045776367</v>
       </c>
       <c r="U27" t="n">
-        <v>3804.5</v>
+        <v>99.76500053405762</v>
       </c>
       <c r="V27" t="n">
-        <v>3746.420072428386</v>
+        <v>93.78500022888184</v>
       </c>
       <c r="W27" t="n">
-        <v>48.32045379790452</v>
+        <v>0.936456649952774</v>
       </c>
       <c r="X27" t="n">
-        <v>73.53619909781604</v>
+        <v>0.6580228346008048</v>
       </c>
       <c r="Y27" t="n">
-        <v>-25.21574529991152</v>
+        <v>0.2784338153519692</v>
       </c>
       <c r="Z27" t="n">
-        <v>19.32442396916858</v>
+        <v>0.3747123579904621</v>
       </c>
       <c r="AA27" t="b">
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.03203342618384397</v>
+        <v>0.0474716037325611</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.1096459485004035</v>
+        <v>0.2515413305758387</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.007888403759913176</v>
+        <v>0.01232062322377647</v>
       </c>
       <c r="AE27" t="n">
-        <v>0.003162935471104023</v>
+        <v>0.1864677652877218</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.004725468288809154</v>
+        <v>-0.1741471420639453</v>
       </c>
       <c r="AG27" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH27" t="n">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="AI27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ27" t="b">
         <v>1</v>
       </c>
       <c r="AK27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM27" t="b">
         <v>0</v>
       </c>
       <c r="AN27" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>3993.99</v>
+        <v>0</v>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
@@ -4285,17 +4279,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4304,7 +4298,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>31</v>
+        <v>30.8</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4313,15 +4307,15 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2887848</v>
+        <v>4143450</v>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K28" t="b">
         <v>0</v>
@@ -4330,7 +4324,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>2887848</v>
+        <v>4143450</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -4339,61 +4333,61 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2015</v>
+        <v>275</v>
       </c>
       <c r="Q28" t="n">
-        <v>2015</v>
+        <v>275</v>
       </c>
       <c r="R28" t="n">
-        <v>3266361</v>
+        <v>17453696</v>
       </c>
       <c r="S28" t="n">
-        <v>2245</v>
+        <v>289.7</v>
       </c>
       <c r="T28" t="n">
-        <v>2295.25</v>
+        <v>293.825</v>
       </c>
       <c r="U28" t="n">
-        <v>2292.25</v>
+        <v>292.925</v>
       </c>
       <c r="V28" t="n">
-        <v>2190.5</v>
+        <v>265.2283131917318</v>
       </c>
       <c r="W28" t="n">
-        <v>-20.5337082438773</v>
+        <v>-0.5994197869163145</v>
       </c>
       <c r="X28" t="n">
-        <v>39.11282467810747</v>
+        <v>4.535897191209456</v>
       </c>
       <c r="Y28" t="n">
-        <v>-59.64653292198476</v>
+        <v>-5.13531697812577</v>
       </c>
       <c r="Z28" t="n">
-        <v>-38.37366887015406</v>
+        <v>-4.221953948568109</v>
       </c>
       <c r="AA28" t="b">
         <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.03069053708439906</v>
+        <v>0.07003891050583655</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.1071428571428572</v>
+        <v>0.03889851301655267</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.006545514660468266</v>
+        <v>0.03488792999705193</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.0006598441135576838</v>
+        <v>-0.02617505227156425</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.005885670546910582</v>
+        <v>0.06106298226861617</v>
       </c>
       <c r="AG28" t="n">
-        <v>56.00000000000001</v>
+        <v>62</v>
       </c>
       <c r="AH28" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AI28" t="b">
         <v>0</v>
@@ -4423,7 +4417,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -4442,7 +4436,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>30.6</v>
+        <v>29.6</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4451,7 +4445,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -4459,7 +4453,7 @@
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K29" t="b">
         <v>0</v>
@@ -4477,67 +4471,67 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>542</v>
+        <v>520</v>
       </c>
       <c r="Q29" t="n">
-        <v>542</v>
+        <v>520</v>
       </c>
       <c r="R29" t="n">
-        <v>9211718</v>
+        <v>9753012</v>
       </c>
       <c r="S29" t="n">
-        <v>562.4</v>
+        <v>553.4</v>
       </c>
       <c r="T29" t="n">
+        <v>572.25</v>
+      </c>
+      <c r="U29" t="n">
         <v>571.7</v>
       </c>
-      <c r="U29" t="n">
-        <v>571.95</v>
-      </c>
       <c r="V29" t="n">
-        <v>536.7666666666667</v>
+        <v>539.4833333333333</v>
       </c>
       <c r="W29" t="n">
-        <v>-4.524911816179042</v>
+        <v>-9.044624543949112</v>
       </c>
       <c r="X29" t="n">
-        <v>-0.9976479507050332</v>
+        <v>-2.607043269353864</v>
       </c>
       <c r="Y29" t="n">
-        <v>-3.527263865474009</v>
+        <v>-6.437581274595249</v>
       </c>
       <c r="Z29" t="n">
-        <v>-1.24574850002579</v>
+        <v>-3.527263865473991</v>
       </c>
       <c r="AA29" t="b">
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>-0.009140767824497242</v>
+        <v>0.0216110019646365</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.5941176470588236</v>
+        <v>0.4565826330532212</v>
       </c>
       <c r="AD29" t="n">
-        <v>-0.03328579024842804</v>
+        <v>-0.01353997854414812</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.4876346340295241</v>
+        <v>0.3915090677651043</v>
       </c>
       <c r="AF29" t="n">
-        <v>-0.5209204242779522</v>
+        <v>-0.4050490463092524</v>
       </c>
       <c r="AG29" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AH29" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AI29" t="b">
         <v>0</v>
       </c>
       <c r="AJ29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK29" t="b">
         <v>0</v>
@@ -4552,26 +4546,28 @@
         <v>1</v>
       </c>
       <c r="AO29" t="n">
-        <v>582.11</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>540.26</v>
+        <v>592.8</v>
+      </c>
+      <c r="AP29" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4580,7 +4576,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>29.6</v>
+        <v>29</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4589,15 +4585,15 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>499000</v>
+        <v>6264000</v>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="K30" t="b">
         <v>0</v>
@@ -4606,7 +4602,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>499000</v>
+        <v>6264000</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -4615,73 +4611,73 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2115</v>
+        <v>1980</v>
       </c>
       <c r="Q30" t="n">
-        <v>2115</v>
+        <v>1980</v>
       </c>
       <c r="R30" t="n">
-        <v>977025</v>
+        <v>3530427</v>
       </c>
       <c r="S30" t="n">
-        <v>2232</v>
+        <v>2030</v>
       </c>
       <c r="T30" t="n">
-        <v>2332.5</v>
+        <v>1942.25</v>
       </c>
       <c r="U30" t="n">
-        <v>2335</v>
+        <v>1935.25</v>
       </c>
       <c r="V30" t="n">
-        <v>1991.520267740885</v>
+        <v>2065.462481689453</v>
       </c>
       <c r="W30" t="n">
-        <v>-29.44102573966256</v>
+        <v>16.37825705961723</v>
       </c>
       <c r="X30" t="n">
-        <v>27.07256454407002</v>
+        <v>14.91809795992351</v>
       </c>
       <c r="Y30" t="n">
-        <v>-56.51359028373258</v>
+        <v>1.460159099693712</v>
       </c>
       <c r="Z30" t="n">
-        <v>-50.22539042962939</v>
+        <v>7.986258280959616</v>
       </c>
       <c r="AA30" t="b">
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>-0.02309468822170901</v>
+        <v>0.07608695652173902</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.6320231492645285</v>
+        <v>-0.1010482715689757</v>
       </c>
       <c r="AD30" t="n">
-        <v>-0.04723971064563981</v>
+        <v>0.0409359760129544</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.525540136235229</v>
+        <v>-0.1661218368570926</v>
       </c>
       <c r="AF30" t="n">
-        <v>-0.5727798468808688</v>
+        <v>0.207057812870047</v>
       </c>
       <c r="AG30" t="n">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="AH30" t="n">
-        <v>92</v>
+        <v>16</v>
       </c>
       <c r="AI30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM30" t="b">
         <v>0</v>
@@ -4689,25 +4685,31 @@
       <c r="AN30" t="b">
         <v>0</v>
       </c>
-      <c r="AO30" t="inlineStr"/>
-      <c r="AP30" t="n">
-        <v>2253.95</v>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
+      </c>
+      <c r="AP30" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>美律</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4716,7 +4718,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>29.6</v>
+        <v>29</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4725,7 +4727,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -4733,7 +4735,7 @@
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="K31" t="b">
         <v>0</v>
@@ -4751,67 +4753,67 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>101</v>
+        <v>81.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>101</v>
+        <v>81.5</v>
       </c>
       <c r="R31" t="n">
-        <v>1980561</v>
+        <v>1313913</v>
       </c>
       <c r="S31" t="n">
-        <v>101.5800003051758</v>
+        <v>81.3</v>
       </c>
       <c r="T31" t="n">
-        <v>99.76500053405762</v>
+        <v>78.61499938964843</v>
       </c>
       <c r="U31" t="n">
-        <v>99.76500053405762</v>
+        <v>78.3699993133545</v>
       </c>
       <c r="V31" t="n">
-        <v>93.44500020345052</v>
+        <v>77.82943280537923</v>
       </c>
       <c r="W31" t="n">
-        <v>0.9631267387532745</v>
+        <v>1.080440588135886</v>
       </c>
       <c r="X31" t="n">
-        <v>0.5884143807628124</v>
+        <v>0.5948479954566041</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.3747123579904621</v>
+        <v>0.485592592679282</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.5529265852619162</v>
+        <v>0.5490633083142774</v>
       </c>
       <c r="AA31" t="b">
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>0.06396868960166291</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.2768647528235271</v>
+        <v>0.01259318436978529</v>
       </c>
       <c r="AD31" t="n">
-        <v>-0.0241450224239308</v>
+        <v>0.02881770909287829</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.1703817397942275</v>
+        <v>-0.05248038091833163</v>
       </c>
       <c r="AF31" t="n">
-        <v>-0.1945267622181583</v>
+        <v>0.08129809001120991</v>
       </c>
       <c r="AG31" t="n">
-        <v>42</v>
+        <v>57.99999999999999</v>
       </c>
       <c r="AH31" t="n">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="AI31" t="b">
         <v>1</v>
       </c>
       <c r="AJ31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK31" t="b">
         <v>1</v>
@@ -4830,24 +4832,26 @@
           <t>Already &gt; 0</t>
         </is>
       </c>
-      <c r="AP31" t="n">
-        <v>95.59999999999999</v>
+      <c r="AP31" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>6271</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4856,7 +4860,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>28.6</v>
+        <v>28.8</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4865,24 +4869,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>79618000</v>
+        <v>2185000</v>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="K32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" t="b">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>79618000</v>
+        <v>2185000</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -4891,67 +4895,67 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>133.5</v>
+        <v>229</v>
       </c>
       <c r="Q32" t="n">
-        <v>133.5</v>
+        <v>229</v>
       </c>
       <c r="R32" t="n">
-        <v>214575784</v>
+        <v>2285882</v>
       </c>
       <c r="S32" t="n">
-        <v>142</v>
+        <v>237.5</v>
       </c>
       <c r="T32" t="n">
-        <v>150.225</v>
+        <v>233.4</v>
       </c>
       <c r="U32" t="n">
-        <v>150.675</v>
+        <v>233</v>
       </c>
       <c r="V32" t="n">
-        <v>133.7666666666667</v>
+        <v>211.05</v>
       </c>
       <c r="W32" t="n">
-        <v>-2.257982444045922</v>
+        <v>1.879829238086529</v>
       </c>
       <c r="X32" t="n">
-        <v>1.183775827998165</v>
+        <v>3.948638719568172</v>
       </c>
       <c r="Y32" t="n">
-        <v>-3.441758272044087</v>
+        <v>-2.068809481481643</v>
       </c>
       <c r="Z32" t="n">
-        <v>-2.916571305106211</v>
+        <v>-1.266974247787861</v>
       </c>
       <c r="AA32" t="b">
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>-0.06315789473684208</v>
+        <v>0.03619909502262453</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.02692307692307683</v>
+        <v>0.1421446384039899</v>
       </c>
       <c r="AD32" t="n">
-        <v>-0.08730291716077287</v>
+        <v>0.001048114513839904</v>
       </c>
       <c r="AE32" t="n">
-        <v>-0.0795599361062227</v>
+        <v>0.07707107311587302</v>
       </c>
       <c r="AF32" t="n">
-        <v>-0.00774298105455018</v>
+        <v>-0.07602295860203312</v>
       </c>
       <c r="AG32" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="AH32" t="n">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="AI32" t="b">
         <v>0</v>
       </c>
       <c r="AJ32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK32" t="b">
         <v>0</v>
@@ -4963,27 +4967,31 @@
         <v>0</v>
       </c>
       <c r="AN32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO32" t="inlineStr"/>
-      <c r="AP32" t="n">
-        <v>156.11</v>
+        <v>1</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>252.36</v>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4996,20 +5004,20 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>5163000</v>
+        <v>5143000</v>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K33" t="b">
         <v>0</v>
@@ -5018,114 +5026,108 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>5163000</v>
+        <v>5086000</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>57000</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>0.01120723554856469</v>
       </c>
       <c r="P33" t="n">
-        <v>19.25</v>
+        <v>4250</v>
       </c>
       <c r="Q33" t="n">
-        <v>19.25</v>
+        <v>4250</v>
       </c>
       <c r="R33" t="n">
-        <v>46513793</v>
+        <v>8594719</v>
       </c>
       <c r="S33" t="n">
-        <v>19.21000022888184</v>
+        <v>4408</v>
       </c>
       <c r="T33" t="n">
-        <v>18.90750007629395</v>
+        <v>4790.5</v>
       </c>
       <c r="U33" t="n">
-        <v>18.88500003814697</v>
+        <v>4799.5</v>
       </c>
       <c r="V33" t="n">
-        <v>19.02257207234701</v>
+        <v>4274.5</v>
       </c>
       <c r="W33" t="n">
-        <v>0.1090578800445208</v>
+        <v>-122.8760504218917</v>
       </c>
       <c r="X33" t="n">
-        <v>0.04730777682413234</v>
+        <v>-0.09212629721524124</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.06175010322038843</v>
+        <v>-122.7839241246765</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.07553552354631526</v>
+        <v>-127.5067884662056</v>
       </c>
       <c r="AA33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.02393621176602845</v>
+        <v>-0.04063205417607219</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.04595009474395906</v>
+        <v>0.1580381471389645</v>
       </c>
       <c r="AD33" t="n">
-        <v>-0.0002088106579023474</v>
+        <v>-0.07578303468485681</v>
       </c>
       <c r="AE33" t="n">
-        <v>-0.06053291828534046</v>
+        <v>0.09296458185084755</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.06032410762743812</v>
+        <v>-0.1687476165357044</v>
       </c>
       <c r="AG33" t="n">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="AH33" t="n">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="AI33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN33" t="b">
         <v>0</v>
       </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
-      <c r="AP33" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+      <c r="AO33" t="inlineStr"/>
+      <c r="AP33" t="n">
+        <v>5098.95</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5134,7 +5136,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>27.8</v>
+        <v>27.6</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5143,15 +5145,15 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="K34" t="b">
         <v>0</v>
@@ -5160,7 +5162,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -5169,61 +5171,61 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>161.5</v>
+        <v>158.5</v>
       </c>
       <c r="Q34" t="n">
-        <v>161.5</v>
+        <v>158.5</v>
       </c>
       <c r="R34" t="n">
-        <v>19553094</v>
+        <v>13277885</v>
       </c>
       <c r="S34" t="n">
-        <v>176</v>
+        <v>162.6</v>
       </c>
       <c r="T34" t="n">
-        <v>175.65</v>
+        <v>170.325</v>
       </c>
       <c r="U34" t="n">
-        <v>175.55</v>
+        <v>170.075</v>
       </c>
       <c r="V34" t="n">
-        <v>161.2333333333333</v>
+        <v>151.2083333333333</v>
       </c>
       <c r="W34" t="n">
-        <v>0.7521259415534587</v>
+        <v>-1.609375708961352</v>
       </c>
       <c r="X34" t="n">
-        <v>4.457106434597994</v>
+        <v>1.875328055753662</v>
       </c>
       <c r="Y34" t="n">
-        <v>-3.704980493044535</v>
+        <v>-3.484703764715014</v>
       </c>
       <c r="Z34" t="n">
-        <v>-2.173222528366749</v>
+        <v>-3.510037546493362</v>
       </c>
       <c r="AA34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.01253918495297812</v>
+        <v>0.03257328990228014</v>
       </c>
       <c r="AC34" t="n">
-        <v>0.05901639344262288</v>
+        <v>0.1045296167247387</v>
       </c>
       <c r="AD34" t="n">
-        <v>-0.01160583747095267</v>
+        <v>-0.002577690606504479</v>
       </c>
       <c r="AE34" t="n">
-        <v>-0.04746661958667664</v>
+        <v>0.03945605143662179</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.03586078211572397</v>
+        <v>-0.04203374204312627</v>
       </c>
       <c r="AG34" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AH34" t="n">
-        <v>38</v>
+        <v>56.00000000000001</v>
       </c>
       <c r="AI34" t="b">
         <v>0</v>
@@ -5238,7 +5240,7 @@
         <v>0</v>
       </c>
       <c r="AM34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN34" t="b">
         <v>0</v>
@@ -5253,17 +5255,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5272,7 +5274,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>26</v>
+        <v>25.8</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5281,24 +5283,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>5000</v>
+        <v>79618000</v>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="K35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" t="b">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>5000</v>
+        <v>79618000</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -5307,61 +5309,61 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>155.5</v>
+        <v>133</v>
       </c>
       <c r="Q35" t="n">
-        <v>155.5</v>
+        <v>133</v>
       </c>
       <c r="R35" t="n">
-        <v>15414533</v>
+        <v>92001831</v>
       </c>
       <c r="S35" t="n">
-        <v>165.4</v>
+        <v>139.1</v>
       </c>
       <c r="T35" t="n">
-        <v>170.075</v>
+        <v>149.95</v>
       </c>
       <c r="U35" t="n">
-        <v>170.25</v>
+        <v>150.225</v>
       </c>
       <c r="V35" t="n">
-        <v>150.9583333333333</v>
+        <v>133.7416666666667</v>
       </c>
       <c r="W35" t="n">
-        <v>-0.7635335495609468</v>
+        <v>-3.215749370824284</v>
       </c>
       <c r="X35" t="n">
-        <v>2.746503996932415</v>
+        <v>0.3038707882336754</v>
       </c>
       <c r="Y35" t="n">
-        <v>-3.510037546493362</v>
+        <v>-3.519620159057959</v>
       </c>
       <c r="Z35" t="n">
-        <v>-2.654684754356815</v>
+        <v>-3.441758272044087</v>
       </c>
       <c r="AA35" t="b">
         <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>-0.0220125786163522</v>
+        <v>-0.03971119133574008</v>
       </c>
       <c r="AC35" t="n">
-        <v>0.1146953405017921</v>
+        <v>-0.01115241635687736</v>
       </c>
       <c r="AD35" t="n">
-        <v>-0.04615760104028299</v>
+        <v>-0.07486217184452471</v>
       </c>
       <c r="AE35" t="n">
-        <v>0.008212327472492564</v>
+        <v>-0.07622598164499428</v>
       </c>
       <c r="AF35" t="n">
-        <v>-0.05436992851277556</v>
+        <v>0.001363809800469573</v>
       </c>
       <c r="AG35" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="AH35" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="AI35" t="b">
         <v>0</v>
@@ -5383,23 +5385,23 @@
       </c>
       <c r="AO35" t="inlineStr"/>
       <c r="AP35" t="n">
-        <v>168.84</v>
+        <v>159.84</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5412,20 +5414,20 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1000</v>
+        <v>201900</v>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="n">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="K36" t="b">
         <v>0</v>
@@ -5434,76 +5436,76 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1000</v>
+        <v>186900</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>0.08025682182985554</v>
       </c>
       <c r="P36" t="n">
-        <v>923</v>
+        <v>16480</v>
       </c>
       <c r="Q36" t="n">
-        <v>923</v>
+        <v>16480</v>
       </c>
       <c r="R36" t="n">
-        <v>18824519</v>
+        <v>310762</v>
       </c>
       <c r="S36" t="n">
-        <v>1040.6</v>
+        <v>16994</v>
       </c>
       <c r="T36" t="n">
-        <v>1028.25</v>
+        <v>18569.5</v>
       </c>
       <c r="U36" t="n">
-        <v>1027.1</v>
+        <v>18621.5</v>
       </c>
       <c r="V36" t="n">
-        <v>983.8833333333333</v>
+        <v>17089.25</v>
       </c>
       <c r="W36" t="n">
-        <v>2.828710826272527</v>
+        <v>-560.0191406263875</v>
       </c>
       <c r="X36" t="n">
-        <v>31.09670029254504</v>
+        <v>-175.275731059236</v>
       </c>
       <c r="Y36" t="n">
-        <v>-28.26798946627251</v>
+        <v>-384.7434095671516</v>
       </c>
       <c r="Z36" t="n">
-        <v>-15.17878487514748</v>
+        <v>-418.1097860404951</v>
       </c>
       <c r="AA36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.02555555555555555</v>
+        <v>-0.05936073059360736</v>
       </c>
       <c r="AC36" t="n">
-        <v>-0.2703557312252964</v>
+        <v>0.1687943262411347</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.001410533131624758</v>
+        <v>-0.09451171110239198</v>
       </c>
       <c r="AE36" t="n">
-        <v>-0.376838744254596</v>
+        <v>0.1037207609530177</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.3782492773862207</v>
+        <v>-0.1982324720554097</v>
       </c>
       <c r="AG36" t="n">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="AH36" t="n">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="AI36" t="b">
         <v>0</v>
       </c>
       <c r="AJ36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="b">
         <v>0</v>
@@ -5512,32 +5514,30 @@
         <v>0</v>
       </c>
       <c r="AM36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN36" t="b">
         <v>0</v>
       </c>
       <c r="AO36" t="inlineStr"/>
-      <c r="AP36" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+      <c r="AP36" t="n">
+        <v>20449.47</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5546,7 +5546,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>24.6</v>
+        <v>23.8</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5555,15 +5555,15 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>4328000</v>
+        <v>1000</v>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="n">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="K37" t="b">
         <v>0</v>
@@ -5572,7 +5572,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>4328000</v>
+        <v>1000</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -5581,61 +5581,61 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>5120</v>
+        <v>472</v>
       </c>
       <c r="Q37" t="n">
-        <v>5120</v>
+        <v>472</v>
       </c>
       <c r="R37" t="n">
-        <v>5890083</v>
+        <v>15781676</v>
       </c>
       <c r="S37" t="n">
-        <v>5667</v>
+        <v>490.1</v>
       </c>
       <c r="T37" t="n">
-        <v>5280.25</v>
+        <v>507.575</v>
       </c>
       <c r="U37" t="n">
-        <v>5291.5</v>
+        <v>508.075</v>
       </c>
       <c r="V37" t="n">
-        <v>5316.959847005209</v>
+        <v>453.25</v>
       </c>
       <c r="W37" t="n">
-        <v>74.35940143287371</v>
+        <v>-6.440507620384722</v>
       </c>
       <c r="X37" t="n">
-        <v>101.2213302666985</v>
+        <v>3.912199831102986</v>
       </c>
       <c r="Y37" t="n">
-        <v>-26.86192883382478</v>
+        <v>-10.35270745148771</v>
       </c>
       <c r="Z37" t="n">
-        <v>41.7261634333907</v>
+        <v>-9.644600973429901</v>
       </c>
       <c r="AA37" t="b">
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>-0.04209541627689428</v>
+        <v>-0.02074688796680502</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.1702795755424051</v>
+        <v>0.1964512040557669</v>
       </c>
       <c r="AD37" t="n">
-        <v>-0.06624043870082508</v>
+        <v>-0.05589786847558964</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.06379656251310561</v>
+        <v>0.13137763876765</v>
       </c>
       <c r="AF37" t="n">
-        <v>-0.1300370012139307</v>
+        <v>-0.1872755072432396</v>
       </c>
       <c r="AG37" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AH37" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="AI37" t="b">
         <v>0</v>
@@ -5653,29 +5653,27 @@
         <v>0</v>
       </c>
       <c r="AN37" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>5427.2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO37" t="inlineStr"/>
       <c r="AP37" t="n">
-        <v>5283.68</v>
+        <v>547.45</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5684,7 +5682,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>24.4</v>
+        <v>23.4</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5693,15 +5691,15 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1000</v>
+        <v>2887848</v>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="n">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="K38" t="b">
         <v>0</v>
@@ -5710,7 +5708,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1000</v>
+        <v>2887848</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -5719,61 +5717,61 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>538</v>
+        <v>2015</v>
       </c>
       <c r="Q38" t="n">
-        <v>538</v>
+        <v>2015</v>
       </c>
       <c r="R38" t="n">
-        <v>944422</v>
+        <v>2221187</v>
       </c>
       <c r="S38" t="n">
-        <v>551.4</v>
+        <v>2176</v>
       </c>
       <c r="T38" t="n">
-        <v>561.05</v>
+        <v>2297</v>
       </c>
       <c r="U38" t="n">
-        <v>561</v>
+        <v>2295.25</v>
       </c>
       <c r="V38" t="n">
-        <v>567.5520161946614</v>
+        <v>2190.75</v>
       </c>
       <c r="W38" t="n">
-        <v>-4.077612311283474</v>
+        <v>-45.04314566761286</v>
       </c>
       <c r="X38" t="n">
-        <v>-0.7025682295655331</v>
+        <v>22.28163060896342</v>
       </c>
       <c r="Y38" t="n">
-        <v>-3.375044081717941</v>
+        <v>-67.32477627657627</v>
       </c>
       <c r="Z38" t="n">
-        <v>-1.993522866647877</v>
+        <v>-59.64653292198479</v>
       </c>
       <c r="AA38" t="b">
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.001862197392923592</v>
+        <v>0.01767676767676774</v>
       </c>
       <c r="AC38" t="n">
-        <v>-0.03644178592822878</v>
+        <v>0.007500000000000062</v>
       </c>
       <c r="AD38" t="n">
-        <v>-0.0222828250310072</v>
+        <v>-0.01747421283201689</v>
       </c>
       <c r="AE38" t="n">
-        <v>-0.1429247989575283</v>
+        <v>-0.05757356528811686</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.1206419739265211</v>
+        <v>0.04009935245609997</v>
       </c>
       <c r="AG38" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AH38" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="AI38" t="b">
         <v>0</v>
@@ -5791,11 +5789,9 @@
         <v>0</v>
       </c>
       <c r="AN38" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>576.74</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO38" t="inlineStr"/>
       <c r="AP38" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -5805,17 +5801,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5824,7 +5820,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>21.8</v>
+        <v>23.2</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5833,15 +5829,15 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1000</v>
+        <v>4328000</v>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="n">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="K39" t="b">
         <v>0</v>
@@ -5850,7 +5846,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>1000</v>
+        <v>4328000</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -5859,67 +5855,67 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>239.5</v>
+        <v>5165</v>
       </c>
       <c r="Q39" t="n">
-        <v>239.5</v>
+        <v>5165</v>
       </c>
       <c r="R39" t="n">
-        <v>48438668</v>
+        <v>2761868</v>
       </c>
       <c r="S39" t="n">
-        <v>243.2</v>
+        <v>5500</v>
       </c>
       <c r="T39" t="n">
-        <v>249.5</v>
+        <v>5282.75</v>
       </c>
       <c r="U39" t="n">
-        <v>249.95</v>
+        <v>5280.25</v>
       </c>
       <c r="V39" t="n">
-        <v>250.95</v>
+        <v>5322.909090169271</v>
       </c>
       <c r="W39" t="n">
-        <v>-2.679263462451758</v>
+        <v>25.46163632789376</v>
       </c>
       <c r="X39" t="n">
-        <v>-0.9903492723649286</v>
+        <v>86.06939147893755</v>
       </c>
       <c r="Y39" t="n">
-        <v>-1.688914190086829</v>
+        <v>-60.60775515104379</v>
       </c>
       <c r="Z39" t="n">
-        <v>-1.520546764007297</v>
+        <v>-26.86192883382478</v>
       </c>
       <c r="AA39" t="b">
         <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>-0.03621730382293764</v>
+        <v>0.009775171065493637</v>
       </c>
       <c r="AC39" t="n">
-        <v>0.02132196162046918</v>
+        <v>0.07424110202656142</v>
       </c>
       <c r="AD39" t="n">
-        <v>-0.06036232624686844</v>
+        <v>-0.02537580944329099</v>
       </c>
       <c r="AE39" t="n">
-        <v>-0.08516105140883035</v>
+        <v>0.009167536738444504</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.02479872516196191</v>
+        <v>-0.03454334618173549</v>
       </c>
       <c r="AG39" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AH39" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="AI39" t="b">
         <v>0</v>
       </c>
       <c r="AJ39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK39" t="b">
         <v>0</v>
@@ -5934,26 +5930,28 @@
         <v>1</v>
       </c>
       <c r="AO39" t="n">
-        <v>258.66</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>257.03</v>
+        <v>5857.11</v>
+      </c>
+      <c r="AP39" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5962,7 +5960,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>21.2</v>
+        <v>23.2</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5971,7 +5969,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -5979,7 +5977,7 @@
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="K40" t="b">
         <v>0</v>
@@ -5997,67 +5995,67 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2025</v>
+        <v>540</v>
       </c>
       <c r="Q40" t="n">
-        <v>2025</v>
+        <v>540</v>
       </c>
       <c r="R40" t="n">
-        <v>4025397</v>
+        <v>525680</v>
       </c>
       <c r="S40" t="n">
-        <v>2234</v>
+        <v>547.8</v>
       </c>
       <c r="T40" t="n">
-        <v>2240.75</v>
+        <v>561.9</v>
       </c>
       <c r="U40" t="n">
-        <v>2246.5</v>
+        <v>561.05</v>
       </c>
       <c r="V40" t="n">
-        <v>2135.25</v>
+        <v>566.9836334228515</v>
       </c>
       <c r="W40" t="n">
-        <v>-8.532542899430155</v>
+        <v>-5.293175034313435</v>
       </c>
       <c r="X40" t="n">
-        <v>23.79912208840344</v>
+        <v>-1.620689590515267</v>
       </c>
       <c r="Y40" t="n">
-        <v>-32.33166498783359</v>
+        <v>-3.672485443798168</v>
       </c>
       <c r="Z40" t="n">
-        <v>-9.861646968649456</v>
+        <v>-3.375044081717863</v>
       </c>
       <c r="AA40" t="b">
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>-0.05373831775700932</v>
+        <v>0.03250478011472269</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.103542234332425</v>
+        <v>-0.05940217750113941</v>
       </c>
       <c r="AD40" t="n">
-        <v>-0.07788334018094012</v>
+        <v>-0.002646200394061937</v>
       </c>
       <c r="AE40" t="n">
-        <v>-0.00294077869687448</v>
+        <v>-0.1244757427892563</v>
       </c>
       <c r="AF40" t="n">
-        <v>-0.07494256148406564</v>
+        <v>0.1218295423951944</v>
       </c>
       <c r="AG40" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="AH40" t="n">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="AI40" t="b">
         <v>0</v>
       </c>
       <c r="AJ40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK40" t="b">
         <v>0</v>
@@ -6069,29 +6067,31 @@
         <v>0</v>
       </c>
       <c r="AN40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO40" t="n">
-        <v>2389.5</v>
-      </c>
-      <c r="AP40" t="n">
-        <v>2307.11</v>
+        <v>582.12</v>
+      </c>
+      <c r="AP40" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6100,7 +6100,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>21</v>
+        <v>20.2</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -6109,15 +6109,15 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>5086000</v>
+        <v>1000</v>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="n">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="K41" t="b">
         <v>0</v>
@@ -6126,7 +6126,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>5086000</v>
+        <v>1000</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -6135,61 +6135,61 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>4165</v>
+        <v>244</v>
       </c>
       <c r="Q41" t="n">
-        <v>4165</v>
+        <v>244</v>
       </c>
       <c r="R41" t="n">
-        <v>18514362</v>
+        <v>50072297</v>
       </c>
       <c r="S41" t="n">
-        <v>4496</v>
+        <v>242.2</v>
       </c>
       <c r="T41" t="n">
-        <v>4799.5</v>
+        <v>249.375</v>
       </c>
       <c r="U41" t="n">
-        <v>4819.25</v>
+        <v>249.5</v>
       </c>
       <c r="V41" t="n">
-        <v>4264.833333333333</v>
+        <v>250.9166666666667</v>
       </c>
       <c r="W41" t="n">
-        <v>-96.90293373225177</v>
+        <v>-2.52142207475751</v>
       </c>
       <c r="X41" t="n">
-        <v>30.60385473395387</v>
+        <v>-1.296563832843444</v>
       </c>
       <c r="Y41" t="n">
-        <v>-127.5067884662056</v>
+        <v>-1.224858241914066</v>
       </c>
       <c r="Z41" t="n">
-        <v>-104.6936941662323</v>
+        <v>-1.688914190086831</v>
       </c>
       <c r="AA41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB41" t="n">
-        <v>-0.08662280701754388</v>
+        <v>-0.01014198782961462</v>
       </c>
       <c r="AC41" t="n">
-        <v>0.2470059880239521</v>
+        <v>-0.008130081300813052</v>
       </c>
       <c r="AD41" t="n">
-        <v>-0.1107678294414747</v>
+        <v>-0.04529296833839924</v>
       </c>
       <c r="AE41" t="n">
-        <v>0.1405229749946526</v>
+        <v>-0.07320364658892997</v>
       </c>
       <c r="AF41" t="n">
-        <v>-0.2512908044361273</v>
+        <v>0.02791067825053073</v>
       </c>
       <c r="AG41" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="AH41" t="n">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="AI41" t="b">
         <v>0</v>
@@ -6204,30 +6204,32 @@
         <v>0</v>
       </c>
       <c r="AM41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO41" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>258.15</v>
+      </c>
       <c r="AP41" t="n">
-        <v>5097.89</v>
+        <v>253.66</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6236,7 +6238,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>20.4</v>
+        <v>20</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6245,7 +6247,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -6253,7 +6255,7 @@
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K42" t="b">
         <v>0</v>
@@ -6271,61 +6273,61 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>316.5</v>
+        <v>447.5</v>
       </c>
       <c r="Q42" t="n">
-        <v>316.5</v>
+        <v>447.5</v>
       </c>
       <c r="R42" t="n">
-        <v>15421586</v>
+        <v>46975365</v>
       </c>
       <c r="S42" t="n">
-        <v>322</v>
+        <v>476.5</v>
       </c>
       <c r="T42" t="n">
-        <v>333.625</v>
+        <v>504.5</v>
       </c>
       <c r="U42" t="n">
-        <v>334.425</v>
+        <v>505.4</v>
       </c>
       <c r="V42" t="n">
-        <v>327.0833333333333</v>
+        <v>486.1666666666667</v>
       </c>
       <c r="W42" t="n">
-        <v>-4.426038179004934</v>
+        <v>-13.58907882775202</v>
       </c>
       <c r="X42" t="n">
-        <v>-2.324717114287667</v>
+        <v>-2.506816021675073</v>
       </c>
       <c r="Y42" t="n">
-        <v>-2.101321064717267</v>
+        <v>-11.08226280607695</v>
       </c>
       <c r="Z42" t="n">
-        <v>-1.815482466906621</v>
+        <v>-9.97394763226195</v>
       </c>
       <c r="AA42" t="b">
         <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>-0.04812030075187967</v>
+        <v>-0.03866809881847477</v>
       </c>
       <c r="AC42" t="n">
-        <v>0.001582278481012667</v>
+        <v>0.1049382716049383</v>
       </c>
       <c r="AD42" t="n">
-        <v>-0.07226532317581047</v>
+        <v>-0.0738190793272594</v>
       </c>
       <c r="AE42" t="n">
-        <v>-0.1049007345482869</v>
+        <v>0.03986470631682137</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.03263541137247639</v>
+        <v>-0.1136837856440808</v>
       </c>
       <c r="AG42" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="AH42" t="n">
-        <v>24</v>
+        <v>57.99999999999999</v>
       </c>
       <c r="AI42" t="b">
         <v>0</v>
@@ -6343,29 +6345,27 @@
         <v>0</v>
       </c>
       <c r="AN42" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO42" t="n">
-        <v>340.55</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO42" t="inlineStr"/>
       <c r="AP42" t="n">
-        <v>351.03</v>
+        <v>552.5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6374,7 +6374,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>20.2</v>
+        <v>19.2</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6383,15 +6383,15 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1000</v>
+        <v>470000</v>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="K43" t="b">
         <v>0</v>
@@ -6400,7 +6400,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>1000</v>
+        <v>470000</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -6409,61 +6409,61 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>439.5</v>
+        <v>3120</v>
       </c>
       <c r="Q43" t="n">
-        <v>439.5</v>
+        <v>3120</v>
       </c>
       <c r="R43" t="n">
-        <v>78339384</v>
+        <v>1103993</v>
       </c>
       <c r="S43" t="n">
-        <v>493.4</v>
+        <v>3189</v>
       </c>
       <c r="T43" t="n">
-        <v>505.4</v>
+        <v>3232</v>
       </c>
       <c r="U43" t="n">
-        <v>507.075</v>
+        <v>3238.75</v>
       </c>
       <c r="V43" t="n">
-        <v>485.4583333333333</v>
+        <v>3011</v>
       </c>
       <c r="W43" t="n">
-        <v>-9.710197952417786</v>
+        <v>-36.18505579455723</v>
       </c>
       <c r="X43" t="n">
-        <v>0.263749679844183</v>
+        <v>-18.69783317724341</v>
       </c>
       <c r="Y43" t="n">
-        <v>-9.97394763226197</v>
+        <v>-17.48722261731382</v>
       </c>
       <c r="Z43" t="n">
-        <v>-5.22440334734698</v>
+        <v>-21.52010150547813</v>
       </c>
       <c r="AA43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB43" t="n">
-        <v>-0.07082452431289643</v>
+        <v>-0.04147465437788023</v>
       </c>
       <c r="AC43" t="n">
-        <v>0.1535433070866141</v>
+        <v>0.1795841209829867</v>
       </c>
       <c r="AD43" t="n">
-        <v>-0.09496954673682723</v>
+        <v>-0.07662563488666485</v>
       </c>
       <c r="AE43" t="n">
-        <v>0.0470602940573146</v>
+        <v>0.1145105556948698</v>
       </c>
       <c r="AF43" t="n">
-        <v>-0.1420298407941418</v>
+        <v>-0.1911361905815346</v>
       </c>
       <c r="AG43" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AH43" t="n">
-        <v>57.99999999999999</v>
+        <v>68</v>
       </c>
       <c r="AI43" t="b">
         <v>0</v>
@@ -6478,30 +6478,32 @@
         <v>0</v>
       </c>
       <c r="AM43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO43" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>3319.68</v>
+      </c>
       <c r="AP43" t="n">
-        <v>534.87</v>
+        <v>3347.89</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6510,7 +6512,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>19.6</v>
+        <v>18.2</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6519,7 +6521,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -6527,7 +6529,7 @@
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="K44" t="b">
         <v>0</v>
@@ -6545,61 +6547,61 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>461.5</v>
+        <v>322</v>
       </c>
       <c r="Q44" t="n">
-        <v>461.5</v>
+        <v>322</v>
       </c>
       <c r="R44" t="n">
-        <v>3844049</v>
+        <v>9667065</v>
       </c>
       <c r="S44" t="n">
-        <v>502.7</v>
+        <v>321.3</v>
       </c>
       <c r="T44" t="n">
-        <v>508.075</v>
+        <v>333.075</v>
       </c>
       <c r="U44" t="n">
-        <v>510.9</v>
+        <v>333.625</v>
       </c>
       <c r="V44" t="n">
-        <v>451.9583333333333</v>
+        <v>327.05</v>
       </c>
       <c r="W44" t="n">
-        <v>-3.144224279454988</v>
+        <v>-4.266450278084278</v>
       </c>
       <c r="X44" t="n">
-        <v>6.50037669397498</v>
+        <v>-2.71306374704698</v>
       </c>
       <c r="Y44" t="n">
-        <v>-9.644600973429968</v>
+        <v>-1.553386531037298</v>
       </c>
       <c r="Z44" t="n">
-        <v>-5.488119088676374</v>
+        <v>-2.101321064717278</v>
       </c>
       <c r="AA44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB44" t="n">
-        <v>-0.109073359073359</v>
+        <v>-0.03303303303303307</v>
       </c>
       <c r="AC44" t="n">
-        <v>0.2439353099730459</v>
+        <v>-0.006172839506172867</v>
       </c>
       <c r="AD44" t="n">
-        <v>-0.1332183814972898</v>
+        <v>-0.06818401354181769</v>
       </c>
       <c r="AE44" t="n">
-        <v>0.1374522969437464</v>
+        <v>-0.07124640479428979</v>
       </c>
       <c r="AF44" t="n">
-        <v>-0.2706706784410362</v>
+        <v>0.003062391252472096</v>
       </c>
       <c r="AG44" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="AH44" t="n">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="AI44" t="b">
         <v>0</v>
@@ -6614,30 +6616,32 @@
         <v>0</v>
       </c>
       <c r="AM44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO44" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>340.03</v>
+      </c>
       <c r="AP44" t="n">
-        <v>531.03</v>
+        <v>352.16</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6646,7 +6650,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>19.4</v>
+        <v>17.6</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6655,15 +6659,15 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>2504000</v>
+        <v>1000</v>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="n">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="K45" t="b">
         <v>0</v>
@@ -6672,7 +6676,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>2504000</v>
+        <v>1000</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
@@ -6681,61 +6685,61 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>5300</v>
+        <v>902</v>
       </c>
       <c r="Q45" t="n">
-        <v>5300</v>
+        <v>902</v>
       </c>
       <c r="R45" t="n">
-        <v>1186784</v>
+        <v>16344010</v>
       </c>
       <c r="S45" t="n">
-        <v>5766</v>
+        <v>995</v>
       </c>
       <c r="T45" t="n">
-        <v>5520.75</v>
+        <v>1027.65</v>
       </c>
       <c r="U45" t="n">
-        <v>5535.5</v>
+        <v>1028.25</v>
       </c>
       <c r="V45" t="n">
-        <v>5599.25</v>
+        <v>978.8333333333334</v>
       </c>
       <c r="W45" t="n">
-        <v>60.76939428348669</v>
+        <v>-13.50961918957125</v>
       </c>
       <c r="X45" t="n">
-        <v>45.91084964429631</v>
+        <v>22.17543639612178</v>
       </c>
       <c r="Y45" t="n">
-        <v>14.85854463919038</v>
+        <v>-35.68505558569304</v>
       </c>
       <c r="Z45" t="n">
-        <v>80.35245945445624</v>
+        <v>-28.26798946627251</v>
       </c>
       <c r="AA45" t="b">
         <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>-0.05272564789991063</v>
+        <v>-0.01312910284463897</v>
       </c>
       <c r="AC45" t="n">
-        <v>-0.0284142988084326</v>
+        <v>-0.2514522821576763</v>
       </c>
       <c r="AD45" t="n">
-        <v>-0.07687067032384143</v>
+        <v>-0.0482800833534236</v>
       </c>
       <c r="AE45" t="n">
-        <v>-0.1348973118377321</v>
+        <v>-0.3165258474457933</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.0580266415138907</v>
+        <v>0.2682457640923697</v>
       </c>
       <c r="AG45" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AH45" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="AI45" t="b">
         <v>0</v>
@@ -6744,10 +6748,10 @@
         <v>0</v>
       </c>
       <c r="AK45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM45" t="b">
         <v>0</v>
@@ -6755,29 +6759,25 @@
       <c r="AN45" t="b">
         <v>0</v>
       </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
+      <c r="AO45" t="inlineStr"/>
       <c r="AP45" t="n">
-        <v>5672.37</v>
+        <v>1069.26</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6786,7 +6786,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6795,15 +6795,15 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>186900</v>
+        <v>1000</v>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="K46" t="b">
         <v>0</v>
@@ -6812,7 +6812,7 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>186900</v>
+        <v>1000</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
@@ -6821,61 +6821,61 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>15945</v>
+        <v>2000</v>
       </c>
       <c r="Q46" t="n">
-        <v>15945</v>
+        <v>2000</v>
       </c>
       <c r="R46" t="n">
-        <v>725983</v>
+        <v>3575004</v>
       </c>
       <c r="S46" t="n">
-        <v>17195</v>
+        <v>2168</v>
       </c>
       <c r="T46" t="n">
-        <v>18621.5</v>
+        <v>2236.75</v>
       </c>
       <c r="U46" t="n">
-        <v>18723.25</v>
+        <v>2240.75</v>
       </c>
       <c r="V46" t="n">
-        <v>17049.58333333333</v>
+        <v>2135</v>
       </c>
       <c r="W46" t="n">
-        <v>-497.1996647079432</v>
+        <v>-32.22265688838252</v>
       </c>
       <c r="X46" t="n">
-        <v>-79.08987866744792</v>
+        <v>12.59476629304625</v>
       </c>
       <c r="Y46" t="n">
-        <v>-418.1097860404952</v>
+        <v>-44.81742318142877</v>
       </c>
       <c r="Z46" t="n">
-        <v>-328.0340740004422</v>
+        <v>-32.3316649878336</v>
       </c>
       <c r="AA46" t="b">
         <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>-0.1131813125695217</v>
+        <v>-0.03846153846153844</v>
       </c>
       <c r="AC46" t="n">
-        <v>0.2346109175377469</v>
+        <v>-0.007444168734491274</v>
       </c>
       <c r="AD46" t="n">
-        <v>-0.1373263349934525</v>
+        <v>-0.07361251897032306</v>
       </c>
       <c r="AE46" t="n">
-        <v>0.1281279045084474</v>
+        <v>-0.07251773402260819</v>
       </c>
       <c r="AF46" t="n">
-        <v>-0.2654542395018998</v>
+        <v>-0.001094784947714866</v>
       </c>
       <c r="AG46" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="AH46" t="n">
-        <v>68</v>
+        <v>26</v>
       </c>
       <c r="AI46" t="b">
         <v>0</v>
@@ -6897,13 +6897,13 @@
       </c>
       <c r="AO46" t="inlineStr"/>
       <c r="AP46" t="n">
-        <v>20337.37</v>
+        <v>2339.21</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6922,7 +6922,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>17.2</v>
+        <v>14.2</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="H47" t="n">
@@ -6957,61 +6957,61 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>1905</v>
+        <v>1845</v>
       </c>
       <c r="Q47" t="n">
-        <v>1905</v>
+        <v>1845</v>
       </c>
       <c r="R47" t="n">
-        <v>10159270</v>
+        <v>13372287</v>
       </c>
       <c r="S47" t="n">
-        <v>2146</v>
+        <v>2067</v>
       </c>
       <c r="T47" t="n">
+        <v>2128.25</v>
+      </c>
+      <c r="U47" t="n">
         <v>2151.75</v>
       </c>
-      <c r="U47" t="n">
-        <v>2170</v>
-      </c>
       <c r="V47" t="n">
-        <v>2139.580183919271</v>
+        <v>2142.392177327474</v>
       </c>
       <c r="W47" t="n">
-        <v>-35.69547770504778</v>
+        <v>-62.78250070016929</v>
       </c>
       <c r="X47" t="n">
-        <v>-15.84564882429594</v>
+        <v>-25.23301919947082</v>
       </c>
       <c r="Y47" t="n">
-        <v>-19.84982888075184</v>
+        <v>-37.54948150069847</v>
       </c>
       <c r="Z47" t="n">
-        <v>5.999139220754717</v>
+        <v>-19.84982888075157</v>
       </c>
       <c r="AA47" t="b">
         <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>-0.1607929515418502</v>
+        <v>-0.203023758099352</v>
       </c>
       <c r="AC47" t="n">
-        <v>0.2128545911402431</v>
+        <v>0.1006511827879939</v>
       </c>
       <c r="AD47" t="n">
-        <v>-0.184937973965781</v>
+        <v>-0.2381747386081366</v>
       </c>
       <c r="AE47" t="n">
-        <v>0.1063715781109436</v>
+        <v>0.03557761749987698</v>
       </c>
       <c r="AF47" t="n">
-        <v>-0.2913095520767246</v>
+        <v>-0.2737523561080136</v>
       </c>
       <c r="AG47" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AH47" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="AI47" t="b">
         <v>0</v>
@@ -7029,29 +7029,27 @@
         <v>0</v>
       </c>
       <c r="AN47" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO47" t="n">
-        <v>2129.79</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO47" t="inlineStr"/>
       <c r="AP47" t="n">
-        <v>2574.74</v>
+        <v>2463.16</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7060,7 +7058,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>16.8</v>
+        <v>13</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -7069,15 +7067,15 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>470000</v>
+        <v>2504000</v>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="K48" t="b">
         <v>0</v>
@@ -7086,7 +7084,7 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>470000</v>
+        <v>2504000</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
@@ -7095,61 +7093,61 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>2905</v>
+        <v>5205</v>
       </c>
       <c r="Q48" t="n">
-        <v>2905</v>
+        <v>5205</v>
       </c>
       <c r="R48" t="n">
-        <v>795268</v>
+        <v>1540825</v>
       </c>
       <c r="S48" t="n">
-        <v>3229</v>
+        <v>5692</v>
       </c>
       <c r="T48" t="n">
-        <v>3238.75</v>
+        <v>5509</v>
       </c>
       <c r="U48" t="n">
-        <v>3262.25</v>
+        <v>5520.75</v>
       </c>
       <c r="V48" t="n">
-        <v>3003.083333333333</v>
+        <v>5588.083333333333</v>
       </c>
       <c r="W48" t="n">
-        <v>-35.84612902839308</v>
+        <v>6.001759798634339</v>
       </c>
       <c r="X48" t="n">
-        <v>-14.32602752291495</v>
+        <v>37.92903167516392</v>
       </c>
       <c r="Y48" t="n">
-        <v>-21.52010150547813</v>
+        <v>-31.92727187652958</v>
       </c>
       <c r="Z48" t="n">
-        <v>9.423896798796923</v>
+        <v>14.85854463919038</v>
       </c>
       <c r="AA48" t="b">
         <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>-0.1392592592592593</v>
+        <v>-0.04319852941176472</v>
       </c>
       <c r="AC48" t="n">
-        <v>0.1325536062378168</v>
+        <v>-0.1140425531914894</v>
       </c>
       <c r="AD48" t="n">
-        <v>-0.1634042816831901</v>
+        <v>-0.07834950992054934</v>
       </c>
       <c r="AE48" t="n">
-        <v>0.02607059320851723</v>
+        <v>-0.1791161184796063</v>
       </c>
       <c r="AF48" t="n">
-        <v>-0.1894748748917073</v>
+        <v>0.1007666085590569</v>
       </c>
       <c r="AG48" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AH48" t="n">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="AI48" t="b">
         <v>0</v>
@@ -7170,16 +7168,16 @@
         <v>1</v>
       </c>
       <c r="AO48" t="n">
-        <v>3149.02</v>
+        <v>5569.35</v>
       </c>
       <c r="AP48" t="n">
-        <v>3606.32</v>
+        <v>5920</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -7198,7 +7196,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>16.6</v>
+        <v>11.4</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -7207,7 +7205,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="H49" t="n">
@@ -7233,61 +7231,61 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="Q49" t="n">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="R49" t="n">
-        <v>1786411</v>
+        <v>639403</v>
       </c>
       <c r="S49" t="n">
-        <v>851.8</v>
+        <v>843.8</v>
       </c>
       <c r="T49" t="n">
+        <v>870.1</v>
+      </c>
+      <c r="U49" t="n">
         <v>872.1</v>
       </c>
-      <c r="U49" t="n">
-        <v>874.75</v>
-      </c>
       <c r="V49" t="n">
-        <v>968.3333333333334</v>
+        <v>962.8166666666667</v>
       </c>
       <c r="W49" t="n">
-        <v>-15.69055561026494</v>
+        <v>-16.27706785386522</v>
       </c>
       <c r="X49" t="n">
-        <v>-15.7557322792823</v>
+        <v>-15.85999939419889</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.06517666901736163</v>
+        <v>-0.4170684596663303</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.650910174703082</v>
+        <v>0.06517666901736874</v>
       </c>
       <c r="AA49" t="b">
         <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>-0.05981941309255079</v>
+        <v>-0.04576659038901598</v>
       </c>
       <c r="AC49" t="n">
-        <v>-0.2287037037037037</v>
+        <v>-0.2841201716738198</v>
       </c>
       <c r="AD49" t="n">
-        <v>-0.08396443551648158</v>
+        <v>-0.08091757089780061</v>
       </c>
       <c r="AE49" t="n">
-        <v>-0.3351867167330033</v>
+        <v>-0.3491937369619367</v>
       </c>
       <c r="AF49" t="n">
-        <v>0.2512222812165217</v>
+        <v>0.2682761660641361</v>
       </c>
       <c r="AG49" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="AH49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI49" t="b">
         <v>0</v>
@@ -7296,30 +7294,28 @@
         <v>0</v>
       </c>
       <c r="AK49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM49" t="b">
         <v>0</v>
       </c>
       <c r="AN49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>839</v>
       </c>
       <c r="AP49" t="n">
-        <v>915.16</v>
+        <v>921</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -7338,7 +7334,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7347,7 +7343,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="H50" t="n">
@@ -7379,55 +7375,55 @@
         <v>1155</v>
       </c>
       <c r="R50" t="n">
-        <v>854729</v>
+        <v>533893</v>
       </c>
       <c r="S50" t="n">
-        <v>1185</v>
+        <v>1175</v>
       </c>
       <c r="T50" t="n">
+        <v>1205.25</v>
+      </c>
+      <c r="U50" t="n">
         <v>1211.5</v>
       </c>
-      <c r="U50" t="n">
-        <v>1217.25</v>
-      </c>
       <c r="V50" t="n">
-        <v>1352.357442220052</v>
+        <v>1349.416479492188</v>
       </c>
       <c r="W50" t="n">
-        <v>-25.9242692595235</v>
+        <v>-26.61889905514317</v>
       </c>
       <c r="X50" t="n">
-        <v>-29.42821261421521</v>
+        <v>-28.8663499024008</v>
       </c>
       <c r="Y50" t="n">
+        <v>2.247450847257628</v>
+      </c>
+      <c r="Z50" t="n">
         <v>3.503943354691707</v>
       </c>
-      <c r="Z50" t="n">
-        <v>6.31052833558303</v>
-      </c>
       <c r="AA50" t="b">
         <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>-0.09055118110236215</v>
+        <v>-0.09765625</v>
       </c>
       <c r="AC50" t="n">
-        <v>-0.1162849777711361</v>
+        <v>-0.1325297493367288</v>
       </c>
       <c r="AD50" t="n">
-        <v>-0.114696203526293</v>
+        <v>-0.1328072305087846</v>
       </c>
       <c r="AE50" t="n">
-        <v>-0.2227679908004356</v>
+        <v>-0.1976033146248457</v>
       </c>
       <c r="AF50" t="n">
-        <v>0.1080717872741427</v>
+        <v>0.06479608411606108</v>
       </c>
       <c r="AG50" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="AH50" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AI50" t="b">
         <v>0</v>
@@ -7453,13 +7449,13 @@
         </is>
       </c>
       <c r="AP50" t="n">
-        <v>1339.47</v>
+        <v>1292.89</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -7478,7 +7474,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>10.8</v>
+        <v>10</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7487,7 +7483,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -7513,58 +7509,58 @@
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>5055</v>
+        <v>5160</v>
       </c>
       <c r="Q51" t="n">
-        <v>5055</v>
+        <v>5160</v>
       </c>
       <c r="R51" t="n">
-        <v>879953</v>
+        <v>790793</v>
       </c>
       <c r="S51" t="n">
-        <v>5602</v>
+        <v>5511</v>
       </c>
       <c r="T51" t="n">
+        <v>5832</v>
+      </c>
+      <c r="U51" t="n">
         <v>5889.5</v>
       </c>
-      <c r="U51" t="n">
-        <v>5966.75</v>
-      </c>
       <c r="V51" t="n">
-        <v>6336.666666666667</v>
+        <v>6311.75</v>
       </c>
       <c r="W51" t="n">
-        <v>-223.5106797362596</v>
+        <v>-251.3873140364049</v>
       </c>
       <c r="X51" t="n">
-        <v>-172.4805049870362</v>
+        <v>-188.2618667969099</v>
       </c>
       <c r="Y51" t="n">
+        <v>-63.12544723949495</v>
+      </c>
+      <c r="Z51" t="n">
         <v>-51.03017474922342</v>
       </c>
-      <c r="Z51" t="n">
-        <v>1.39136616676069</v>
-      </c>
       <c r="AA51" t="b">
         <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>-0.2340909090909091</v>
+        <v>-0.1822503961965135</v>
       </c>
       <c r="AC51" t="n">
-        <v>-0.1644628099173554</v>
+        <v>-0.2246431254695718</v>
       </c>
       <c r="AD51" t="n">
-        <v>-0.2582359315148399</v>
+        <v>-0.2174013767052981</v>
       </c>
       <c r="AE51" t="n">
-        <v>-0.2709458229466549</v>
+        <v>-0.2897166907576887</v>
       </c>
       <c r="AF51" t="n">
-        <v>0.012709891431815</v>
+        <v>0.07231531405239056</v>
       </c>
       <c r="AG51" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AH51" t="n">
         <v>6</v>
@@ -7588,10 +7584,10 @@
         <v>1</v>
       </c>
       <c r="AO51" t="n">
-        <v>5631.27</v>
+        <v>5872.08</v>
       </c>
       <c r="AP51" t="n">
-        <v>7188.42</v>
+        <v>6917.37</v>
       </c>
     </row>
   </sheetData>

--- a/output/daily_screen_latest.xlsx
+++ b/output/daily_screen_latest.xlsx
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>68</v>
+        <v>68.2</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -703,7 +703,7 @@
         <v>19.54999923706055</v>
       </c>
       <c r="R2" t="n">
-        <v>65846976</v>
+        <v>65670302</v>
       </c>
       <c r="S2" t="n">
         <v>19.32999992370605</v>
@@ -718,16 +718,16 @@
         <v>19.03753280639648</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1408405378258699</v>
+        <v>0.1408405378258664</v>
       </c>
       <c r="X2" t="n">
-        <v>0.06601432902447982</v>
+        <v>0.06601432902447313</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0748262088013901</v>
+        <v>0.07482620880139323</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.06175010322038849</v>
+        <v>0.06175010322038885</v>
       </c>
       <c r="AA2" t="b">
         <v>1</v>
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>61</v>
+        <v>61.2</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -845,7 +845,7 @@
         <v>176</v>
       </c>
       <c r="R3" t="n">
-        <v>1711116</v>
+        <v>1689482</v>
       </c>
       <c r="S3" t="n">
         <v>174.8</v>
@@ -860,16 +860,16 @@
         <v>184.3876274108887</v>
       </c>
       <c r="W3" t="n">
-        <v>-1.427535160659488</v>
+        <v>-1.427535160659517</v>
       </c>
       <c r="X3" t="n">
-        <v>-3.096546092956168</v>
+        <v>-3.096546092956211</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.66901093229668</v>
+        <v>1.669010932296694</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.660792931061975</v>
+        <v>1.660792931061994</v>
       </c>
       <c r="AA3" t="b">
         <v>1</v>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>76.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,11 +955,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>6700000</v>
+        <v>6899000</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
@@ -972,13 +972,13 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>5808000</v>
+        <v>6700000</v>
       </c>
       <c r="N4" t="n">
-        <v>892000</v>
+        <v>199000</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1535812672176309</v>
+        <v>0.02970149253731343</v>
       </c>
       <c r="P4" t="n">
         <v>1245</v>
@@ -987,7 +987,7 @@
         <v>1245</v>
       </c>
       <c r="R4" t="n">
-        <v>15727206</v>
+        <v>15215404</v>
       </c>
       <c r="S4" t="n">
         <v>1220</v>
@@ -1005,13 +1005,13 @@
         <v>38.14472539795747</v>
       </c>
       <c r="X4" t="n">
-        <v>38.55835926692416</v>
+        <v>38.55835926692415</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.4136338689666914</v>
+        <v>-0.4136338689666772</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.5591652991634533</v>
+        <v>-0.559165299163439</v>
       </c>
       <c r="AA4" t="b">
         <v>1</v>
@@ -1086,7 +1086,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>48</v>
+        <v>48.2</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1127,7 +1127,7 @@
         <v>557</v>
       </c>
       <c r="R5" t="n">
-        <v>28104300</v>
+        <v>27282900</v>
       </c>
       <c r="S5" t="n">
         <v>555.2</v>
@@ -1145,13 +1145,13 @@
         <v>13.0298655157427</v>
       </c>
       <c r="X5" t="n">
-        <v>17.33104492404922</v>
+        <v>17.33104492404919</v>
       </c>
       <c r="Y5" t="n">
-        <v>-4.301179408306524</v>
+        <v>-4.301179408306488</v>
       </c>
       <c r="Z5" t="n">
-        <v>-4.317652886009135</v>
+        <v>-4.317652886009089</v>
       </c>
       <c r="AA5" t="b">
         <v>1</v>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>47.40000000000001</v>
+        <v>47.6</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K6" t="b">
         <v>0</v>
@@ -1267,7 +1267,7 @@
         <v>248</v>
       </c>
       <c r="R6" t="n">
-        <v>50253773</v>
+        <v>49130197</v>
       </c>
       <c r="S6" t="n">
         <v>244.4</v>
@@ -1285,13 +1285,13 @@
         <v>3.972947556634949</v>
       </c>
       <c r="X6" t="n">
-        <v>4.107292513375468</v>
+        <v>4.107292513375461</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.1343449567405184</v>
+        <v>-0.1343449567405113</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.5706998436825916</v>
+        <v>-0.5706998436825819</v>
       </c>
       <c r="AA6" t="b">
         <v>1</v>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>62.2</v>
+        <v>59.2</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1375,15 +1375,15 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>7224000</v>
+        <v>19499000</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K7" t="b">
         <v>1</v>
@@ -1392,73 +1392,73 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>7046000</v>
+        <v>19386000</v>
       </c>
       <c r="N7" t="n">
-        <v>178000</v>
+        <v>113000</v>
       </c>
       <c r="O7" t="n">
-        <v>0.02526256031791087</v>
+        <v>0.005828948725884659</v>
       </c>
       <c r="P7" t="n">
-        <v>1615</v>
+        <v>1090</v>
       </c>
       <c r="Q7" t="n">
-        <v>1615</v>
+        <v>1090</v>
       </c>
       <c r="R7" t="n">
-        <v>10975718</v>
+        <v>14516214</v>
       </c>
       <c r="S7" t="n">
-        <v>1673</v>
+        <v>1157</v>
       </c>
       <c r="T7" t="n">
-        <v>1572.75</v>
+        <v>1161.1</v>
       </c>
       <c r="U7" t="n">
-        <v>1560.5</v>
+        <v>1154.15</v>
       </c>
       <c r="V7" t="n">
-        <v>1459.75</v>
+        <v>1035.883333333333</v>
       </c>
       <c r="W7" t="n">
-        <v>45.02341109165354</v>
+        <v>4.353879746731536</v>
       </c>
       <c r="X7" t="n">
-        <v>59.69238685971857</v>
+        <v>38.65338220905522</v>
       </c>
       <c r="Y7" t="n">
-        <v>-14.66897576806503</v>
+        <v>-34.29950246232368</v>
       </c>
       <c r="Z7" t="n">
-        <v>-5.628074490698374</v>
+        <v>-29.62678598084111</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.1788321167883211</v>
+        <v>0.1461619348054679</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.3212121212121213</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.1436811362795365</v>
+        <v>0.1110109542966833</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.2426187424041908</v>
+        <v>0.2561385559240044</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.0989376061246543</v>
+        <v>-0.1451276016273211</v>
       </c>
       <c r="AG7" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AH7" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="b">
         <v>1</v>
@@ -1473,11 +1473,9 @@
         <v>0</v>
       </c>
       <c r="AN7" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>1782.96</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -1492,12 +1490,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1506,7 +1504,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>60.8</v>
+        <v>53.40000000000001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1515,87 +1513,87 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>19386000</v>
+        <v>852000</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="K8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="b">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>18938000</v>
+        <v>751000</v>
       </c>
       <c r="N8" t="n">
-        <v>448000</v>
+        <v>101000</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02365614109198437</v>
+        <v>0.1344873501997337</v>
       </c>
       <c r="P8" t="n">
-        <v>1090</v>
+        <v>7480</v>
       </c>
       <c r="Q8" t="n">
-        <v>1090</v>
+        <v>7480</v>
       </c>
       <c r="R8" t="n">
-        <v>14914936</v>
+        <v>1804746</v>
       </c>
       <c r="S8" t="n">
-        <v>1157</v>
+        <v>7918</v>
       </c>
       <c r="T8" t="n">
-        <v>1161.1</v>
+        <v>7893.5</v>
       </c>
       <c r="U8" t="n">
-        <v>1154.15</v>
+        <v>7821.25</v>
       </c>
       <c r="V8" t="n">
-        <v>1035.883333333333</v>
+        <v>6090.5</v>
       </c>
       <c r="W8" t="n">
-        <v>4.353879746731536</v>
+        <v>140.3120352777469</v>
       </c>
       <c r="X8" t="n">
-        <v>38.65338220905522</v>
+        <v>342.9687652512529</v>
       </c>
       <c r="Y8" t="n">
-        <v>-34.29950246232368</v>
+        <v>-202.6567299735061</v>
       </c>
       <c r="Z8" t="n">
-        <v>-29.62678598084111</v>
+        <v>-162.3819064662263</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.1461619348054679</v>
+        <v>0.2394366197183098</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.3212121212121213</v>
+        <v>0.8177399756986634</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.1110109542966833</v>
+        <v>0.2042856392095251</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.2561385559240044</v>
+        <v>0.7526664104105465</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.1451276016273211</v>
+        <v>-0.5483807712010214</v>
       </c>
       <c r="AG8" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH8" t="n">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
@@ -1630,12 +1628,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1644,7 +1642,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>57.2</v>
+        <v>52.2</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1653,15 +1651,15 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>981000</v>
+        <v>2657000</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K9" t="b">
         <v>0</v>
@@ -1670,70 +1668,70 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>696000</v>
+        <v>1857000</v>
       </c>
       <c r="N9" t="n">
-        <v>285000</v>
+        <v>800000</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4094827586206897</v>
+        <v>0.4308023694130318</v>
       </c>
       <c r="P9" t="n">
-        <v>1570</v>
+        <v>258.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>1570</v>
+        <v>258.5</v>
       </c>
       <c r="R9" t="n">
-        <v>6008077</v>
+        <v>23753240</v>
       </c>
       <c r="S9" t="n">
-        <v>1642</v>
+        <v>269.1</v>
       </c>
       <c r="T9" t="n">
-        <v>1564.25</v>
+        <v>255.45</v>
       </c>
       <c r="U9" t="n">
-        <v>1546.75</v>
+        <v>253.575</v>
       </c>
       <c r="V9" t="n">
-        <v>1279.55</v>
+        <v>227.675</v>
       </c>
       <c r="W9" t="n">
-        <v>44.2140083672773</v>
+        <v>6.416139638692187</v>
       </c>
       <c r="X9" t="n">
-        <v>69.49502928741238</v>
+        <v>6.022033229720711</v>
       </c>
       <c r="Y9" t="n">
-        <v>-25.28102092013508</v>
+        <v>0.3941064089714752</v>
       </c>
       <c r="Z9" t="n">
-        <v>-19.03649200108956</v>
+        <v>1.892489559765102</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.2868852459016393</v>
+        <v>0.1696832579185521</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.5971515768056967</v>
+        <v>0.230952380952381</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.2517342653928547</v>
+        <v>0.1345322774097675</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.5320780115175798</v>
+        <v>0.1658788156642641</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.2803437461247251</v>
+        <v>-0.03134653825449663</v>
       </c>
       <c r="AG9" t="n">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="AH9" t="n">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="AI9" t="b">
         <v>1</v>
@@ -1742,10 +1740,10 @@
         <v>1</v>
       </c>
       <c r="AK9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM9" t="b">
         <v>0</v>
@@ -1753,8 +1751,10 @@
       <c r="AN9" t="b">
         <v>0</v>
       </c>
-      <c r="AO9" t="n">
-        <v>1855.74</v>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
@@ -1770,12 +1770,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1784,24 +1784,24 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>54.6</v>
+        <v>52.2</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>6303000</v>
+        <v>7224000</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K10" t="b">
         <v>1</v>
@@ -1810,73 +1810,73 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>6147000</v>
+        <v>7224000</v>
       </c>
       <c r="N10" t="n">
-        <v>156000</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0.02537823328452904</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>3315</v>
+        <v>1615</v>
       </c>
       <c r="Q10" t="n">
-        <v>3315</v>
+        <v>1615</v>
       </c>
       <c r="R10" t="n">
-        <v>3730261</v>
+        <v>10612264</v>
       </c>
       <c r="S10" t="n">
-        <v>3276</v>
+        <v>1673</v>
       </c>
       <c r="T10" t="n">
-        <v>3402</v>
+        <v>1572.75</v>
       </c>
       <c r="U10" t="n">
-        <v>3392</v>
+        <v>1560.5</v>
       </c>
       <c r="V10" t="n">
-        <v>3093.299527994792</v>
+        <v>1459.75</v>
       </c>
       <c r="W10" t="n">
-        <v>-35.3894972052758</v>
+        <v>45.02341109165354</v>
       </c>
       <c r="X10" t="n">
-        <v>13.16323473578665</v>
+        <v>59.69238685971835</v>
       </c>
       <c r="Y10" t="n">
-        <v>-48.55273194106245</v>
+        <v>-14.6689757680648</v>
       </c>
       <c r="Z10" t="n">
-        <v>-62.50287942092719</v>
+        <v>-5.62807449069809</v>
       </c>
       <c r="AA10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.0642054574638844</v>
+        <v>0.1788321167883211</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.437355921588952</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.02905447695509977</v>
+        <v>0.1436811362795365</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.3722823563008351</v>
+        <v>0.2426187424041908</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.3432278793457353</v>
+        <v>-0.0989376061246543</v>
       </c>
       <c r="AG10" t="n">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="AH10" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="AI10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ10" t="b">
         <v>1</v>
@@ -1888,13 +1888,13 @@
         <v>0</v>
       </c>
       <c r="AM10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="b">
         <v>1</v>
       </c>
       <c r="AO10" t="n">
-        <v>3865.29</v>
+        <v>1782.96</v>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
@@ -1910,12 +1910,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1924,96 +1924,96 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>52.2</v>
+        <v>51.4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1857000</v>
+        <v>8937000</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="K11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="b">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1257000</v>
+        <v>8937000</v>
       </c>
       <c r="N11" t="n">
-        <v>600000</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.477326968973747</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>258.5</v>
+        <v>1355</v>
       </c>
       <c r="Q11" t="n">
-        <v>258.5</v>
+        <v>1355</v>
       </c>
       <c r="R11" t="n">
-        <v>24088759</v>
+        <v>8990416</v>
       </c>
       <c r="S11" t="n">
-        <v>269.1</v>
+        <v>1402</v>
       </c>
       <c r="T11" t="n">
-        <v>255.45</v>
+        <v>1320</v>
       </c>
       <c r="U11" t="n">
-        <v>253.575</v>
+        <v>1306.5</v>
       </c>
       <c r="V11" t="n">
-        <v>227.675</v>
+        <v>1189.416666666667</v>
       </c>
       <c r="W11" t="n">
-        <v>6.416139638692187</v>
+        <v>41.30080840777782</v>
       </c>
       <c r="X11" t="n">
-        <v>6.022033229720711</v>
+        <v>63.62982051017949</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.3941064089714752</v>
+        <v>-22.32901210240167</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.892489559765102</v>
+        <v>-15.92441011774856</v>
       </c>
       <c r="AA11" t="b">
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.1696832579185521</v>
+        <v>0.2488479262672811</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.230952380952381</v>
+        <v>0.1386554621848739</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.1345322774097675</v>
+        <v>0.2136969457584965</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.1658788156642641</v>
+        <v>0.07358189689675698</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.03134653825449663</v>
+        <v>0.1401150488617395</v>
       </c>
       <c r="AG11" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="AH11" t="n">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="AI11" t="b">
         <v>1</v>
@@ -2022,10 +2022,10 @@
         <v>1</v>
       </c>
       <c r="AK11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="b">
         <v>0</v>
@@ -2033,10 +2033,8 @@
       <c r="AN11" t="b">
         <v>0</v>
       </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+      <c r="AO11" t="n">
+        <v>1607.03</v>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
@@ -2052,12 +2050,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2066,99 +2064,99 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>51.2</v>
+        <v>48.2</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>8937000</v>
+        <v>769000</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="K12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="b">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>8937000</v>
+        <v>649000</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>120000</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>0.1848998459167951</v>
       </c>
       <c r="P12" t="n">
-        <v>1355</v>
+        <v>2250</v>
       </c>
       <c r="Q12" t="n">
-        <v>1355</v>
+        <v>2250</v>
       </c>
       <c r="R12" t="n">
-        <v>9127777</v>
+        <v>1747205</v>
       </c>
       <c r="S12" t="n">
-        <v>1402</v>
+        <v>2208</v>
       </c>
       <c r="T12" t="n">
-        <v>1320</v>
+        <v>2343.75</v>
       </c>
       <c r="U12" t="n">
-        <v>1306.5</v>
+        <v>2332.5</v>
       </c>
       <c r="V12" t="n">
-        <v>1189.416666666667</v>
+        <v>2005.600705973307</v>
       </c>
       <c r="W12" t="n">
-        <v>41.30080840777782</v>
+        <v>-27.82926529920223</v>
       </c>
       <c r="X12" t="n">
-        <v>63.62982051017935</v>
+        <v>16.09219857541557</v>
       </c>
       <c r="Y12" t="n">
-        <v>-22.32901210240153</v>
+        <v>-43.9214638746178</v>
       </c>
       <c r="Z12" t="n">
-        <v>-15.92441011774838</v>
+        <v>-56.51359028373258</v>
       </c>
       <c r="AA12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.2488479262672811</v>
+        <v>0.1111111111111112</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.1386554621848739</v>
+        <v>0.6012255213039355</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.2136969457584965</v>
+        <v>0.07596013060232654</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.07358189689675698</v>
+        <v>0.5361519560158186</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.1401150488617395</v>
+        <v>-0.460191825413492</v>
       </c>
       <c r="AG12" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="AH12" t="n">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="AI12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="b">
         <v>1</v>
@@ -2170,14 +2168,12 @@
         <v>0</v>
       </c>
       <c r="AM12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN12" t="b">
         <v>0</v>
       </c>
-      <c r="AO12" t="n">
-        <v>1607.03</v>
-      </c>
+      <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -2192,12 +2188,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2206,24 +2202,24 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>47.8</v>
+        <v>48</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>649000</v>
+        <v>1000</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="K13" t="b">
         <v>0</v>
@@ -2232,90 +2228,94 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>499000</v>
+        <v>1000</v>
       </c>
       <c r="N13" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3006012024048096</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2250</v>
+        <v>298.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>2250</v>
+        <v>298.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1783307</v>
+        <v>39659568</v>
       </c>
       <c r="S13" t="n">
-        <v>2208</v>
+        <v>285.6</v>
       </c>
       <c r="T13" t="n">
-        <v>2343.75</v>
+        <v>232</v>
       </c>
       <c r="U13" t="n">
-        <v>2332.5</v>
+        <v>226.1</v>
       </c>
       <c r="V13" t="n">
-        <v>2005.600705973307</v>
+        <v>194.0583333333333</v>
       </c>
       <c r="W13" t="n">
-        <v>-27.82926529920223</v>
+        <v>24.41714981393159</v>
       </c>
       <c r="X13" t="n">
-        <v>16.09219857541557</v>
+        <v>17.18132826767883</v>
       </c>
       <c r="Y13" t="n">
-        <v>-43.9214638746178</v>
+        <v>7.235821546252758</v>
       </c>
       <c r="Z13" t="n">
-        <v>-56.51359028373258</v>
+        <v>7.992130067756985</v>
       </c>
       <c r="AA13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.1111111111111112</v>
+        <v>0.6537396121883656</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.6012255213039355</v>
+        <v>0.7874251497005988</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.07596013060232654</v>
+        <v>0.618588631679581</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.5361519560158186</v>
+        <v>0.7223515844124819</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.460191825413492</v>
+        <v>-0.1037629527329009</v>
       </c>
       <c r="AG13" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="AH13" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="AI13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ13" t="b">
         <v>1</v>
       </c>
       <c r="AK13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="b">
         <v>0</v>
       </c>
-      <c r="AO13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
+      </c>
       <c r="AP13" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -2330,12 +2330,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>47.8</v>
+        <v>46.8</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2353,15 +2353,15 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1000</v>
+        <v>981000</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="K14" t="b">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1000</v>
+        <v>981000</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2379,61 +2379,61 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>298.5</v>
+        <v>1570</v>
       </c>
       <c r="Q14" t="n">
-        <v>298.5</v>
+        <v>1570</v>
       </c>
       <c r="R14" t="n">
-        <v>39973694</v>
+        <v>5916466</v>
       </c>
       <c r="S14" t="n">
-        <v>285.6</v>
+        <v>1642</v>
       </c>
       <c r="T14" t="n">
-        <v>232</v>
+        <v>1564.25</v>
       </c>
       <c r="U14" t="n">
-        <v>226.1</v>
+        <v>1546.75</v>
       </c>
       <c r="V14" t="n">
-        <v>194.0583333333333</v>
+        <v>1279.55</v>
       </c>
       <c r="W14" t="n">
-        <v>24.41714981393159</v>
+        <v>44.2140083672773</v>
       </c>
       <c r="X14" t="n">
-        <v>17.18132826767882</v>
+        <v>69.49502928741234</v>
       </c>
       <c r="Y14" t="n">
-        <v>7.235821546252765</v>
+        <v>-25.28102092013503</v>
       </c>
       <c r="Z14" t="n">
-        <v>7.992130067756996</v>
+        <v>-19.03649200108951</v>
       </c>
       <c r="AA14" t="b">
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.6537396121883656</v>
+        <v>0.2868852459016393</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.7874251497005988</v>
+        <v>0.5971515768056967</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.618588631679581</v>
+        <v>0.2517342653928547</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.7223515844124819</v>
+        <v>0.5320780115175798</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.1037629527329009</v>
+        <v>-0.2803437461247251</v>
       </c>
       <c r="AG14" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AH14" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="AI14" t="b">
         <v>1</v>
@@ -2442,10 +2442,10 @@
         <v>1</v>
       </c>
       <c r="AK14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="b">
         <v>0</v>
@@ -2453,10 +2453,8 @@
       <c r="AN14" t="b">
         <v>0</v>
       </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+      <c r="AO14" t="n">
+        <v>1855.74</v>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
@@ -2486,7 +2484,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>46.40000000000001</v>
+        <v>46.6</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2495,7 +2493,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -2503,7 +2501,7 @@
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K15" t="b">
         <v>0</v>
@@ -2527,7 +2525,7 @@
         <v>6730</v>
       </c>
       <c r="R15" t="n">
-        <v>1131578</v>
+        <v>1099414</v>
       </c>
       <c r="S15" t="n">
         <v>6943</v>
@@ -2545,13 +2543,13 @@
         <v>189.7397046221449</v>
       </c>
       <c r="X15" t="n">
-        <v>281.7342017135096</v>
+        <v>281.7342017135097</v>
       </c>
       <c r="Y15" t="n">
-        <v>-91.99449709136468</v>
+        <v>-91.99449709136474</v>
       </c>
       <c r="Z15" t="n">
-        <v>-66.55202090973768</v>
+        <v>-66.55202090973779</v>
       </c>
       <c r="AA15" t="b">
         <v>0</v>
@@ -2612,12 +2610,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2626,7 +2624,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>44.40000000000001</v>
+        <v>45</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2635,24 +2633,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>751000</v>
+        <v>6303000</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="K16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="b">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>751000</v>
+        <v>6303000</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2661,61 +2659,61 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>7480</v>
+        <v>3315</v>
       </c>
       <c r="Q16" t="n">
-        <v>7480</v>
+        <v>3315</v>
       </c>
       <c r="R16" t="n">
-        <v>1890956</v>
+        <v>3569214</v>
       </c>
       <c r="S16" t="n">
-        <v>7918</v>
+        <v>3276</v>
       </c>
       <c r="T16" t="n">
-        <v>7893.5</v>
+        <v>3402</v>
       </c>
       <c r="U16" t="n">
-        <v>7821.25</v>
+        <v>3392</v>
       </c>
       <c r="V16" t="n">
-        <v>6090.5</v>
+        <v>3093.299527994792</v>
       </c>
       <c r="W16" t="n">
-        <v>140.3120352777469</v>
+        <v>-35.3894972052758</v>
       </c>
       <c r="X16" t="n">
-        <v>342.9687652512529</v>
+        <v>13.16323473578665</v>
       </c>
       <c r="Y16" t="n">
-        <v>-202.6567299735061</v>
+        <v>-48.55273194106245</v>
       </c>
       <c r="Z16" t="n">
-        <v>-162.3819064662263</v>
+        <v>-62.50287942092719</v>
       </c>
       <c r="AA16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.2394366197183098</v>
+        <v>0.0642054574638844</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.8177399756986634</v>
+        <v>0.437355921588952</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.2042856392095251</v>
+        <v>0.02905447695509977</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.7526664104105465</v>
+        <v>0.3722823563008351</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.5483807712010214</v>
+        <v>-0.3432278793457353</v>
       </c>
       <c r="AG16" t="n">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="AH16" t="n">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="AI16" t="b">
         <v>0</v>
@@ -2730,12 +2728,14 @@
         <v>0</v>
       </c>
       <c r="AM16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO16" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>3865.29</v>
+      </c>
       <c r="AP16" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -2764,7 +2764,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>44.2</v>
+        <v>44.4</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -2805,7 +2805,7 @@
         <v>671</v>
       </c>
       <c r="R17" t="n">
-        <v>19182798</v>
+        <v>18315373</v>
       </c>
       <c r="S17" t="n">
         <v>718.6</v>
@@ -2888,12 +2888,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2902,99 +2902,99 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>40.6</v>
+        <v>43.2</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>121000</v>
+        <v>12392000</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="K18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="b">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>121000</v>
+        <v>12188000</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>204000</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>0.01673777486051854</v>
       </c>
       <c r="P18" t="n">
-        <v>1410</v>
+        <v>2420</v>
       </c>
       <c r="Q18" t="n">
-        <v>1410</v>
+        <v>2420</v>
       </c>
       <c r="R18" t="n">
-        <v>2929194</v>
+        <v>33490270</v>
       </c>
       <c r="S18" t="n">
-        <v>1523</v>
+        <v>2476</v>
       </c>
       <c r="T18" t="n">
-        <v>1374</v>
+        <v>2491</v>
       </c>
       <c r="U18" t="n">
-        <v>1364.25</v>
+        <v>2488.9</v>
       </c>
       <c r="V18" t="n">
-        <v>1251.276076253255</v>
+        <v>2416.497591145833</v>
       </c>
       <c r="W18" t="n">
-        <v>44.93885460905562</v>
+        <v>-3.262306824247389</v>
       </c>
       <c r="X18" t="n">
-        <v>57.32524539374288</v>
+        <v>17.31173417264522</v>
       </c>
       <c r="Y18" t="n">
-        <v>-12.38639078468725</v>
+        <v>-20.57404099689261</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.216688377404445</v>
+        <v>-15.91550092530764</v>
       </c>
       <c r="AA18" t="b">
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.1604938271604939</v>
+        <v>0.01766190075693852</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.430784538209011</v>
+        <v>0.007105186261707974</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.1253428466517092</v>
+        <v>-0.0174890797518461</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.3657109729208941</v>
+        <v>-0.05796837902640894</v>
       </c>
       <c r="AF18" t="n">
-        <v>-0.2403681262691848</v>
+        <v>0.04047929927456284</v>
       </c>
       <c r="AG18" t="n">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="AH18" t="n">
-        <v>84</v>
+        <v>30</v>
       </c>
       <c r="AI18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="b">
         <v>1</v>
@@ -3012,7 +3012,7 @@
         <v>1</v>
       </c>
       <c r="AO18" t="n">
-        <v>1551</v>
+        <v>2652.32</v>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
@@ -3028,12 +3028,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3042,24 +3042,24 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>39.4</v>
+        <v>42.59999999999999</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1000</v>
+        <v>5151450</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="K19" t="b">
         <v>0</v>
@@ -3068,70 +3068,70 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1000</v>
+        <v>4143450</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1008000</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>0.2432755312601817</v>
       </c>
       <c r="P19" t="n">
-        <v>105.5</v>
+        <v>275</v>
       </c>
       <c r="Q19" t="n">
-        <v>105.5</v>
+        <v>275</v>
       </c>
       <c r="R19" t="n">
-        <v>19183974</v>
+        <v>16768982</v>
       </c>
       <c r="S19" t="n">
-        <v>113.4</v>
+        <v>289.7</v>
       </c>
       <c r="T19" t="n">
-        <v>111.5899997711182</v>
+        <v>293.825</v>
       </c>
       <c r="U19" t="n">
-        <v>110.5349998474121</v>
+        <v>292.925</v>
       </c>
       <c r="V19" t="n">
-        <v>95.91499989827474</v>
+        <v>265.2283131917318</v>
       </c>
       <c r="W19" t="n">
-        <v>1.714176809923529</v>
+        <v>-0.5994197869163145</v>
       </c>
       <c r="X19" t="n">
-        <v>5.27033707690464</v>
+        <v>4.535897191209457</v>
       </c>
       <c r="Y19" t="n">
-        <v>-3.55616026698111</v>
+        <v>-5.135316978125772</v>
       </c>
       <c r="Z19" t="n">
-        <v>-2.843717107570892</v>
+        <v>-4.22195394856811</v>
       </c>
       <c r="AA19" t="b">
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.249999977401083</v>
+        <v>0.07003891050583655</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.01442307692307687</v>
+        <v>0.03889851301655267</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.2148489968922984</v>
+        <v>0.03488792999705193</v>
       </c>
       <c r="AE19" t="n">
-        <v>-0.05065048836504005</v>
+        <v>-0.02617505227156425</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.2654994852573385</v>
+        <v>0.06106298226861617</v>
       </c>
       <c r="AG19" t="n">
-        <v>92</v>
+        <v>62</v>
       </c>
       <c r="AH19" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AI19" t="b">
         <v>0</v>
@@ -3166,12 +3166,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3180,102 +3180,102 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>36.4</v>
+        <v>40.8</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>7507000</v>
+        <v>121000</v>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="K20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="b">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>7389000</v>
+        <v>121000</v>
       </c>
       <c r="N20" t="n">
-        <v>118000</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0.015969684666396</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1635</v>
+        <v>1410</v>
       </c>
       <c r="Q20" t="n">
-        <v>1635</v>
+        <v>1410</v>
       </c>
       <c r="R20" t="n">
-        <v>8576514</v>
+        <v>2852725</v>
       </c>
       <c r="S20" t="n">
-        <v>1745</v>
+        <v>1523</v>
       </c>
       <c r="T20" t="n">
-        <v>1848.25</v>
+        <v>1374</v>
       </c>
       <c r="U20" t="n">
-        <v>1850</v>
+        <v>1364.25</v>
       </c>
       <c r="V20" t="n">
-        <v>1778.083333333333</v>
+        <v>1251.276076253255</v>
       </c>
       <c r="W20" t="n">
-        <v>-39.69044453345396</v>
+        <v>44.93885460905562</v>
       </c>
       <c r="X20" t="n">
-        <v>9.736984121348616</v>
+        <v>57.32524539374285</v>
       </c>
       <c r="Y20" t="n">
-        <v>-49.42742865480257</v>
+        <v>-12.38639078468723</v>
       </c>
       <c r="Z20" t="n">
-        <v>-43.51850691221316</v>
+        <v>0.2166883774044663</v>
       </c>
       <c r="AA20" t="b">
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>-0.02095808383233533</v>
+        <v>0.1604938271604939</v>
       </c>
       <c r="AC20" t="n">
-        <v>-0.1089918256130791</v>
+        <v>0.430784538209011</v>
       </c>
       <c r="AD20" t="n">
-        <v>-0.05610906434111995</v>
+        <v>0.1253428466517092</v>
       </c>
       <c r="AE20" t="n">
-        <v>-0.174065390901196</v>
+        <v>0.3657109729208941</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.117956326560076</v>
+        <v>-0.2403681262691848</v>
       </c>
       <c r="AG20" t="n">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="AH20" t="n">
-        <v>14</v>
+        <v>84</v>
       </c>
       <c r="AI20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK20" t="b">
         <v>0</v>
@@ -3287,11 +3287,15 @@
         <v>0</v>
       </c>
       <c r="AN20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO20" t="inlineStr"/>
-      <c r="AP20" t="n">
-        <v>1934.47</v>
+        <v>1</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1551</v>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -3302,12 +3306,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3316,7 +3320,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>35.2</v>
+        <v>39.6</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3325,24 +3329,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>23519000</v>
+        <v>1000</v>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="K21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="b">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>23519000</v>
+        <v>1000</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -3351,61 +3355,61 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>567</v>
+        <v>105.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>567</v>
+        <v>105.5</v>
       </c>
       <c r="R21" t="n">
-        <v>36099734</v>
+        <v>19016531</v>
       </c>
       <c r="S21" t="n">
-        <v>600.4</v>
+        <v>113.4</v>
       </c>
       <c r="T21" t="n">
-        <v>587.75</v>
+        <v>111.5899997711182</v>
       </c>
       <c r="U21" t="n">
-        <v>586.25</v>
+        <v>110.5349998474121</v>
       </c>
       <c r="V21" t="n">
-        <v>577.275</v>
+        <v>95.91499989827474</v>
       </c>
       <c r="W21" t="n">
-        <v>3.588433587189684</v>
+        <v>1.714176809923558</v>
       </c>
       <c r="X21" t="n">
-        <v>11.3016302944147</v>
+        <v>5.270337076904664</v>
       </c>
       <c r="Y21" t="n">
-        <v>-7.713196707225018</v>
+        <v>-3.556160266981106</v>
       </c>
       <c r="Z21" t="n">
-        <v>-4.110400952110991</v>
+        <v>-2.843717107570888</v>
       </c>
       <c r="AA21" t="b">
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.05586592178770955</v>
+        <v>0.249999977401083</v>
       </c>
       <c r="AC21" t="n">
-        <v>-0.1537313432835821</v>
+        <v>0.01442307692307687</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.02071494127892493</v>
+        <v>0.2148489968922984</v>
       </c>
       <c r="AE21" t="n">
-        <v>-0.218804908571699</v>
+        <v>-0.05065048836504005</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.2395198498506239</v>
+        <v>0.2654994852573385</v>
       </c>
       <c r="AG21" t="n">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="AH21" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="AI21" t="b">
         <v>0</v>
@@ -3423,11 +3427,9 @@
         <v>0</v>
       </c>
       <c r="AN21" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>654.3200000000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO21" t="inlineStr"/>
       <c r="AP21" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -3442,12 +3444,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3456,108 +3458,108 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>34.8</v>
+        <v>36</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>3921000</v>
+        <v>7582000</v>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="K22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" t="b">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3921000</v>
+        <v>7507000</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>0.009990675369654988</v>
       </c>
       <c r="P22" t="n">
-        <v>92.30000305175781</v>
+        <v>1635</v>
       </c>
       <c r="Q22" t="n">
-        <v>92.30000305175781</v>
+        <v>1635</v>
       </c>
       <c r="R22" t="n">
-        <v>5955803</v>
+        <v>7401193</v>
       </c>
       <c r="S22" t="n">
-        <v>93.52000122070312</v>
+        <v>1745</v>
       </c>
       <c r="T22" t="n">
-        <v>86.62500038146973</v>
+        <v>1848.25</v>
       </c>
       <c r="U22" t="n">
-        <v>86.06000022888183</v>
+        <v>1850</v>
       </c>
       <c r="V22" t="n">
-        <v>84.74500020345052</v>
+        <v>1778.083333333333</v>
       </c>
       <c r="W22" t="n">
-        <v>2.474931803364896</v>
+        <v>-39.69044453345396</v>
       </c>
       <c r="X22" t="n">
-        <v>1.907505290600312</v>
+        <v>9.73698412134852</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.5674265127645846</v>
+        <v>-49.42742865480248</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.8148038556698909</v>
+        <v>-43.51850691221304</v>
       </c>
       <c r="AA22" t="b">
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.1395062105155285</v>
+        <v>-0.02095808383233533</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.01988953648351166</v>
+        <v>-0.1089918256130791</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.1043552300067438</v>
+        <v>-0.05610906434111995</v>
       </c>
       <c r="AE22" t="n">
-        <v>-0.04518402880460526</v>
+        <v>-0.174065390901196</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.1495392588113491</v>
+        <v>0.117956326560076</v>
       </c>
       <c r="AG22" t="n">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="AH22" t="n">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="AI22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="b">
         <v>0</v>
@@ -3565,15 +3567,9 @@
       <c r="AN22" t="b">
         <v>0</v>
       </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
-      <c r="AP22" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+      <c r="AO22" t="inlineStr"/>
+      <c r="AP22" t="n">
+        <v>1934.47</v>
       </c>
     </row>
     <row r="23">
@@ -3584,12 +3580,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3598,7 +3594,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>34.40000000000001</v>
+        <v>35.4</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3607,24 +3603,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1000</v>
+        <v>23519000</v>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="K23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="b">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1000</v>
+        <v>23519000</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -3633,61 +3629,61 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>6400</v>
+        <v>567</v>
       </c>
       <c r="Q23" t="n">
-        <v>6400</v>
+        <v>567</v>
       </c>
       <c r="R23" t="n">
-        <v>4806266</v>
+        <v>35134462</v>
       </c>
       <c r="S23" t="n">
-        <v>6897</v>
+        <v>600.4</v>
       </c>
       <c r="T23" t="n">
-        <v>6497.5</v>
+        <v>587.75</v>
       </c>
       <c r="U23" t="n">
-        <v>6480.25</v>
+        <v>586.25</v>
       </c>
       <c r="V23" t="n">
-        <v>5782.742663574219</v>
+        <v>577.275</v>
       </c>
       <c r="W23" t="n">
-        <v>88.6731949735431</v>
+        <v>3.588433587189684</v>
       </c>
       <c r="X23" t="n">
-        <v>119.5111222848806</v>
+        <v>11.30163029441461</v>
       </c>
       <c r="Y23" t="n">
-        <v>-30.83792731133747</v>
+        <v>-7.713196707224926</v>
       </c>
       <c r="Z23" t="n">
-        <v>22.75795774951959</v>
+        <v>-4.110400952110989</v>
       </c>
       <c r="AA23" t="b">
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.05697770437654825</v>
+        <v>0.05586592178770955</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.6206919149641232</v>
+        <v>-0.1537313432835821</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.02182672386776363</v>
+        <v>0.02071494127892493</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.5556183496760063</v>
+        <v>-0.218804908571699</v>
       </c>
       <c r="AF23" t="n">
-        <v>-0.5337916258082427</v>
+        <v>0.2395198498506239</v>
       </c>
       <c r="AG23" t="n">
-        <v>56.00000000000001</v>
+        <v>54</v>
       </c>
       <c r="AH23" t="n">
-        <v>94</v>
+        <v>8</v>
       </c>
       <c r="AI23" t="b">
         <v>0</v>
@@ -3708,7 +3704,7 @@
         <v>1</v>
       </c>
       <c r="AO23" t="n">
-        <v>6758.4</v>
+        <v>654.3200000000001</v>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
@@ -3724,12 +3720,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3738,7 +3734,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>33.2</v>
+        <v>35</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3747,15 +3743,15 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1000</v>
+        <v>3921000</v>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="K24" t="b">
         <v>0</v>
@@ -3764,7 +3760,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1000</v>
+        <v>3921000</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3773,82 +3769,84 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>3685</v>
+        <v>92.30000305175781</v>
       </c>
       <c r="Q24" t="n">
-        <v>3685</v>
+        <v>92.30000305175781</v>
       </c>
       <c r="R24" t="n">
-        <v>1717320</v>
+        <v>5900291</v>
       </c>
       <c r="S24" t="n">
-        <v>3956</v>
+        <v>93.52000122070312</v>
       </c>
       <c r="T24" t="n">
-        <v>3826.75</v>
+        <v>86.62500038146973</v>
       </c>
       <c r="U24" t="n">
-        <v>3810.25</v>
+        <v>86.06000022888183</v>
       </c>
       <c r="V24" t="n">
-        <v>3750.121183268229</v>
+        <v>84.74500020345052</v>
       </c>
       <c r="W24" t="n">
-        <v>9.753653540336018</v>
+        <v>2.474931803364896</v>
       </c>
       <c r="X24" t="n">
-        <v>60.77968998631973</v>
+        <v>1.907505290600308</v>
       </c>
       <c r="Y24" t="n">
-        <v>-51.02603644598371</v>
+        <v>0.5674265127645881</v>
       </c>
       <c r="Z24" t="n">
-        <v>-25.21574529991113</v>
+        <v>0.8148038556698953</v>
       </c>
       <c r="AA24" t="b">
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.09836065573770503</v>
+        <v>0.1395062105155285</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.06412674688517317</v>
+        <v>0.01988953648351166</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.0632096752289204</v>
+        <v>0.1043552300067438</v>
       </c>
       <c r="AE24" t="n">
-        <v>-0.0009468184029437499</v>
+        <v>-0.04518402880460526</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.06415649363186415</v>
+        <v>0.1495392588113491</v>
       </c>
       <c r="AG24" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="AH24" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AI24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ24" t="b">
         <v>1</v>
       </c>
       <c r="AK24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM24" t="b">
         <v>0</v>
       </c>
       <c r="AN24" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>4259.86</v>
+        <v>0</v>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
@@ -3864,12 +3862,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3878,24 +3876,24 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>33</v>
+        <v>34.8</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1000</v>
+        <v>654000</v>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="K25" t="b">
         <v>0</v>
@@ -3907,73 +3905,73 @@
         <v>1000</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>653000</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>653</v>
       </c>
       <c r="P25" t="n">
-        <v>167.5</v>
+        <v>472</v>
       </c>
       <c r="Q25" t="n">
-        <v>167.5</v>
+        <v>472</v>
       </c>
       <c r="R25" t="n">
-        <v>9654317</v>
+        <v>15256059</v>
       </c>
       <c r="S25" t="n">
-        <v>172.2</v>
+        <v>490.1</v>
       </c>
       <c r="T25" t="n">
-        <v>176.375</v>
+        <v>507.575</v>
       </c>
       <c r="U25" t="n">
-        <v>175.65</v>
+        <v>508.075</v>
       </c>
       <c r="V25" t="n">
-        <v>161.4333333333333</v>
+        <v>453.25</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.2991385622451048</v>
+        <v>-6.440507620384835</v>
       </c>
       <c r="X25" t="n">
-        <v>3.505857435229374</v>
+        <v>3.912199831102828</v>
       </c>
       <c r="Y25" t="n">
-        <v>-3.804995997474479</v>
+        <v>-10.35270745148766</v>
       </c>
       <c r="Z25" t="n">
-        <v>-3.704980493044535</v>
+        <v>-9.644600973429846</v>
       </c>
       <c r="AA25" t="b">
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.09477124183006547</v>
+        <v>-0.02074688796680502</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.07717041800643076</v>
+        <v>0.1964512040557669</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.05962026132128084</v>
+        <v>-0.05589786847558964</v>
       </c>
       <c r="AE25" t="n">
-        <v>0.01209685271831384</v>
+        <v>0.13137763876765</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.047523408602967</v>
+        <v>-0.1872755072432396</v>
       </c>
       <c r="AG25" t="n">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="AH25" t="n">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="AI25" t="b">
         <v>0</v>
       </c>
       <c r="AJ25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="b">
         <v>0</v>
@@ -3988,10 +3986,8 @@
         <v>0</v>
       </c>
       <c r="AO25" t="inlineStr"/>
-      <c r="AP25" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+      <c r="AP25" t="n">
+        <v>547.45</v>
       </c>
     </row>
     <row r="26">
@@ -4002,12 +3998,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4016,7 +4012,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>32.6</v>
+        <v>34.6</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4025,24 +4021,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>12188000</v>
+        <v>1000</v>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="K26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" t="b">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>12188000</v>
+        <v>1000</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -4051,61 +4047,61 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2420</v>
+        <v>6400</v>
       </c>
       <c r="Q26" t="n">
-        <v>2420</v>
+        <v>6400</v>
       </c>
       <c r="R26" t="n">
-        <v>40787765</v>
+        <v>4442616</v>
       </c>
       <c r="S26" t="n">
-        <v>2476</v>
+        <v>6897</v>
       </c>
       <c r="T26" t="n">
-        <v>2491</v>
+        <v>6497.5</v>
       </c>
       <c r="U26" t="n">
-        <v>2488.9</v>
+        <v>6480.25</v>
       </c>
       <c r="V26" t="n">
-        <v>2416.497591145833</v>
+        <v>5782.742663574219</v>
       </c>
       <c r="W26" t="n">
-        <v>-3.262306824247389</v>
+        <v>88.6731949735431</v>
       </c>
       <c r="X26" t="n">
-        <v>17.31173417264522</v>
+        <v>119.5111222848806</v>
       </c>
       <c r="Y26" t="n">
-        <v>-20.57404099689261</v>
+        <v>-30.83792731133747</v>
       </c>
       <c r="Z26" t="n">
-        <v>-15.91550092530764</v>
+        <v>22.75795774951959</v>
       </c>
       <c r="AA26" t="b">
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.01766190075693852</v>
+        <v>0.05697770437654825</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.007105186261707974</v>
+        <v>0.6206919149641232</v>
       </c>
       <c r="AD26" t="n">
-        <v>-0.0174890797518461</v>
+        <v>0.02182672386776363</v>
       </c>
       <c r="AE26" t="n">
-        <v>-0.05796837902640894</v>
+        <v>0.5556183496760063</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.04047929927456284</v>
+        <v>-0.5337916258082427</v>
       </c>
       <c r="AG26" t="n">
-        <v>38</v>
+        <v>56.00000000000001</v>
       </c>
       <c r="AH26" t="n">
-        <v>30</v>
+        <v>94</v>
       </c>
       <c r="AI26" t="b">
         <v>0</v>
@@ -4126,7 +4122,7 @@
         <v>1</v>
       </c>
       <c r="AO26" t="n">
-        <v>2652.32</v>
+        <v>6758.4</v>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
@@ -4142,12 +4138,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4156,7 +4152,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>30.8</v>
+        <v>33.4</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4165,7 +4161,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -4173,7 +4169,7 @@
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="K27" t="b">
         <v>0</v>
@@ -4191,84 +4187,82 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>101.5</v>
+        <v>3685</v>
       </c>
       <c r="Q27" t="n">
-        <v>101.5</v>
+        <v>3685</v>
       </c>
       <c r="R27" t="n">
-        <v>1884892</v>
+        <v>1554727</v>
       </c>
       <c r="S27" t="n">
-        <v>102.2</v>
+        <v>3956</v>
       </c>
       <c r="T27" t="n">
-        <v>99.99500045776367</v>
+        <v>3826.75</v>
       </c>
       <c r="U27" t="n">
-        <v>99.76500053405762</v>
+        <v>3810.25</v>
       </c>
       <c r="V27" t="n">
-        <v>93.78500022888184</v>
+        <v>3750.121183268229</v>
       </c>
       <c r="W27" t="n">
-        <v>0.936456649952774</v>
+        <v>9.753653540335563</v>
       </c>
       <c r="X27" t="n">
-        <v>0.6580228346008048</v>
+        <v>60.77968998631829</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.2784338153519692</v>
+        <v>-51.02603644598273</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.3747123579904621</v>
+        <v>-25.21574529991035</v>
       </c>
       <c r="AA27" t="b">
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.0474716037325611</v>
+        <v>0.09836065573770503</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.2515413305758387</v>
+        <v>0.06412674688517317</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.01232062322377647</v>
+        <v>0.0632096752289204</v>
       </c>
       <c r="AE27" t="n">
-        <v>0.1864677652877218</v>
+        <v>-0.0009468184029437499</v>
       </c>
       <c r="AF27" t="n">
-        <v>-0.1741471420639453</v>
+        <v>0.06415649363186415</v>
       </c>
       <c r="AG27" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="AH27" t="n">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="AI27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="b">
         <v>1</v>
       </c>
       <c r="AK27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM27" t="b">
         <v>0</v>
       </c>
       <c r="AN27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>4259.86</v>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
@@ -4284,12 +4278,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4298,7 +4292,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>30.8</v>
+        <v>33.2</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4307,15 +4301,15 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>4143450</v>
+        <v>1000</v>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="K28" t="b">
         <v>0</v>
@@ -4324,7 +4318,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>4143450</v>
+        <v>1000</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -4333,61 +4327,61 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>275</v>
+        <v>167.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>275</v>
+        <v>167.5</v>
       </c>
       <c r="R28" t="n">
-        <v>17453696</v>
+        <v>9553134</v>
       </c>
       <c r="S28" t="n">
-        <v>289.7</v>
+        <v>172.2</v>
       </c>
       <c r="T28" t="n">
-        <v>293.825</v>
+        <v>176.375</v>
       </c>
       <c r="U28" t="n">
-        <v>292.925</v>
+        <v>175.65</v>
       </c>
       <c r="V28" t="n">
-        <v>265.2283131917318</v>
+        <v>161.4333333333333</v>
       </c>
       <c r="W28" t="n">
-        <v>-0.5994197869163145</v>
+        <v>-0.2991385622451048</v>
       </c>
       <c r="X28" t="n">
-        <v>4.535897191209456</v>
+        <v>3.505857435229376</v>
       </c>
       <c r="Y28" t="n">
-        <v>-5.13531697812577</v>
+        <v>-3.804995997474481</v>
       </c>
       <c r="Z28" t="n">
-        <v>-4.221953948568109</v>
+        <v>-3.704980493044538</v>
       </c>
       <c r="AA28" t="b">
         <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.07003891050583655</v>
+        <v>0.09477124183006547</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.03889851301655267</v>
+        <v>0.07717041800643076</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.03488792999705193</v>
+        <v>0.05962026132128084</v>
       </c>
       <c r="AE28" t="n">
-        <v>-0.02617505227156425</v>
+        <v>0.01209685271831384</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.06106298226861617</v>
+        <v>0.047523408602967</v>
       </c>
       <c r="AG28" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="AH28" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AI28" t="b">
         <v>0</v>
@@ -4422,12 +4416,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>慧洋-KY</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4436,7 +4430,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>29.6</v>
+        <v>31</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4445,15 +4439,15 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>957000</v>
+        <v>1000</v>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="K29" t="b">
         <v>0</v>
@@ -4462,7 +4456,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>957000</v>
+        <v>1000</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -4471,82 +4465,84 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>520</v>
+        <v>101.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>520</v>
+        <v>101.5</v>
       </c>
       <c r="R29" t="n">
-        <v>9753012</v>
+        <v>1874677</v>
       </c>
       <c r="S29" t="n">
-        <v>553.4</v>
+        <v>102.2</v>
       </c>
       <c r="T29" t="n">
-        <v>572.25</v>
+        <v>99.99500045776367</v>
       </c>
       <c r="U29" t="n">
-        <v>571.7</v>
+        <v>99.76500053405762</v>
       </c>
       <c r="V29" t="n">
-        <v>539.4833333333333</v>
+        <v>93.78500022888184</v>
       </c>
       <c r="W29" t="n">
-        <v>-9.044624543949112</v>
+        <v>0.936456649952774</v>
       </c>
       <c r="X29" t="n">
-        <v>-2.607043269353864</v>
+        <v>0.6580228346008017</v>
       </c>
       <c r="Y29" t="n">
-        <v>-6.437581274595249</v>
+        <v>0.2784338153519723</v>
       </c>
       <c r="Z29" t="n">
-        <v>-3.527263865473991</v>
+        <v>0.374712357990466</v>
       </c>
       <c r="AA29" t="b">
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.0216110019646365</v>
+        <v>0.0474716037325611</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.4565826330532212</v>
+        <v>0.2515413305758387</v>
       </c>
       <c r="AD29" t="n">
-        <v>-0.01353997854414812</v>
+        <v>0.01232062322377647</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.3915090677651043</v>
+        <v>0.1864677652877218</v>
       </c>
       <c r="AF29" t="n">
-        <v>-0.4050490463092524</v>
+        <v>-0.1741471420639453</v>
       </c>
       <c r="AG29" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AH29" t="n">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="AI29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ29" t="b">
         <v>1</v>
       </c>
       <c r="AK29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM29" t="b">
         <v>0</v>
       </c>
       <c r="AN29" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>592.8</v>
+        <v>0</v>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
@@ -4562,12 +4558,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4576,7 +4572,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>29</v>
+        <v>29.8</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4585,15 +4581,15 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>6264000</v>
+        <v>957000</v>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="K30" t="b">
         <v>0</v>
@@ -4602,7 +4598,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>6264000</v>
+        <v>957000</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -4611,84 +4607,82 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1980</v>
+        <v>520</v>
       </c>
       <c r="Q30" t="n">
-        <v>1980</v>
+        <v>520</v>
       </c>
       <c r="R30" t="n">
-        <v>3530427</v>
+        <v>9436955</v>
       </c>
       <c r="S30" t="n">
-        <v>2030</v>
+        <v>553.4</v>
       </c>
       <c r="T30" t="n">
-        <v>1942.25</v>
+        <v>572.25</v>
       </c>
       <c r="U30" t="n">
-        <v>1935.25</v>
+        <v>571.7</v>
       </c>
       <c r="V30" t="n">
-        <v>2065.462481689453</v>
+        <v>539.4833333333333</v>
       </c>
       <c r="W30" t="n">
-        <v>16.37825705961723</v>
+        <v>-9.044624543949112</v>
       </c>
       <c r="X30" t="n">
-        <v>14.91809795992351</v>
+        <v>-2.607043269353877</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.460159099693712</v>
+        <v>-6.437581274595235</v>
       </c>
       <c r="Z30" t="n">
-        <v>7.986258280959616</v>
+        <v>-3.527263865473973</v>
       </c>
       <c r="AA30" t="b">
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.07608695652173902</v>
+        <v>0.0216110019646365</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.1010482715689757</v>
+        <v>0.4565826330532212</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.0409359760129544</v>
+        <v>-0.01353997854414812</v>
       </c>
       <c r="AE30" t="n">
-        <v>-0.1661218368570926</v>
+        <v>0.3915090677651043</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.207057812870047</v>
+        <v>-0.4050490463092524</v>
       </c>
       <c r="AG30" t="n">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="AH30" t="n">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c r="AI30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="b">
         <v>1</v>
       </c>
       <c r="AK30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="b">
         <v>0</v>
       </c>
       <c r="AN30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>592.8</v>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
@@ -4704,12 +4698,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>美律</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4718,7 +4712,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>29</v>
+        <v>29.2</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4727,15 +4721,15 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1000</v>
+        <v>6264000</v>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="K31" t="b">
         <v>0</v>
@@ -4744,7 +4738,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1000</v>
+        <v>6264000</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -4753,61 +4747,61 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>81.5</v>
+        <v>1980</v>
       </c>
       <c r="Q31" t="n">
-        <v>81.5</v>
+        <v>1980</v>
       </c>
       <c r="R31" t="n">
-        <v>1313913</v>
+        <v>3397911</v>
       </c>
       <c r="S31" t="n">
-        <v>81.3</v>
+        <v>2030</v>
       </c>
       <c r="T31" t="n">
-        <v>78.61499938964843</v>
+        <v>1942.25</v>
       </c>
       <c r="U31" t="n">
-        <v>78.3699993133545</v>
+        <v>1935.25</v>
       </c>
       <c r="V31" t="n">
-        <v>77.82943280537923</v>
+        <v>2065.462481689453</v>
       </c>
       <c r="W31" t="n">
-        <v>1.080440588135886</v>
+        <v>16.37825705961723</v>
       </c>
       <c r="X31" t="n">
-        <v>0.5948479954566041</v>
+        <v>14.9180979599235</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.485592592679282</v>
+        <v>1.460159099693723</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.5490633083142774</v>
+        <v>7.986258280959628</v>
       </c>
       <c r="AA31" t="b">
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.06396868960166291</v>
+        <v>0.07608695652173902</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.01259318436978529</v>
+        <v>-0.1010482715689757</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.02881770909287829</v>
+        <v>0.0409359760129544</v>
       </c>
       <c r="AE31" t="n">
-        <v>-0.05248038091833163</v>
+        <v>-0.1661218368570926</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.08129809001120991</v>
+        <v>0.207057812870047</v>
       </c>
       <c r="AG31" t="n">
-        <v>57.99999999999999</v>
+        <v>64</v>
       </c>
       <c r="AH31" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="AI31" t="b">
         <v>1</v>
@@ -4846,12 +4840,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>美律</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4860,7 +4854,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>28.8</v>
+        <v>29.2</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4869,15 +4863,15 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>2185000</v>
+        <v>1000</v>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="K32" t="b">
         <v>0</v>
@@ -4886,7 +4880,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>2185000</v>
+        <v>1000</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -4895,82 +4889,84 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>229</v>
+        <v>81.5</v>
       </c>
       <c r="Q32" t="n">
-        <v>229</v>
+        <v>81.5</v>
       </c>
       <c r="R32" t="n">
-        <v>2285882</v>
+        <v>1304419</v>
       </c>
       <c r="S32" t="n">
-        <v>237.5</v>
+        <v>81.3</v>
       </c>
       <c r="T32" t="n">
-        <v>233.4</v>
+        <v>78.61499938964843</v>
       </c>
       <c r="U32" t="n">
-        <v>233</v>
+        <v>78.3699993133545</v>
       </c>
       <c r="V32" t="n">
-        <v>211.05</v>
+        <v>77.82943280537923</v>
       </c>
       <c r="W32" t="n">
-        <v>1.879829238086529</v>
+        <v>1.080440588135872</v>
       </c>
       <c r="X32" t="n">
-        <v>3.948638719568172</v>
+        <v>0.5948479954565822</v>
       </c>
       <c r="Y32" t="n">
-        <v>-2.068809481481643</v>
+        <v>0.4855925926792897</v>
       </c>
       <c r="Z32" t="n">
-        <v>-1.266974247787861</v>
+        <v>0.549063308314287</v>
       </c>
       <c r="AA32" t="b">
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.03619909502262453</v>
+        <v>0.06396868960166291</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.1421446384039899</v>
+        <v>0.01259318436978529</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.001048114513839904</v>
+        <v>0.02881770909287829</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.07707107311587302</v>
+        <v>-0.05248038091833163</v>
       </c>
       <c r="AF32" t="n">
-        <v>-0.07602295860203312</v>
+        <v>0.08129809001120991</v>
       </c>
       <c r="AG32" t="n">
-        <v>48</v>
+        <v>57.99999999999999</v>
       </c>
       <c r="AH32" t="n">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="AI32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ32" t="b">
         <v>1</v>
       </c>
       <c r="AK32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM32" t="b">
         <v>0</v>
       </c>
       <c r="AN32" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>252.36</v>
+        <v>0</v>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
@@ -4986,12 +4982,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>6271</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5000,24 +4996,24 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>5143000</v>
+        <v>2185000</v>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K33" t="b">
         <v>0</v>
@@ -5026,76 +5022,76 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>5086000</v>
+        <v>2185000</v>
       </c>
       <c r="N33" t="n">
-        <v>57000</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>0.01120723554856469</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>4250</v>
+        <v>229</v>
       </c>
       <c r="Q33" t="n">
-        <v>4250</v>
+        <v>229</v>
       </c>
       <c r="R33" t="n">
-        <v>8594719</v>
+        <v>2240743</v>
       </c>
       <c r="S33" t="n">
-        <v>4408</v>
+        <v>237.5</v>
       </c>
       <c r="T33" t="n">
-        <v>4790.5</v>
+        <v>233.4</v>
       </c>
       <c r="U33" t="n">
-        <v>4799.5</v>
+        <v>233</v>
       </c>
       <c r="V33" t="n">
-        <v>4274.5</v>
+        <v>211.05</v>
       </c>
       <c r="W33" t="n">
-        <v>-122.8760504218917</v>
+        <v>1.879829238086529</v>
       </c>
       <c r="X33" t="n">
-        <v>-0.09212629721524124</v>
+        <v>3.948638719568165</v>
       </c>
       <c r="Y33" t="n">
-        <v>-122.7839241246765</v>
+        <v>-2.068809481481636</v>
       </c>
       <c r="Z33" t="n">
-        <v>-127.5067884662056</v>
+        <v>-1.266974247787852</v>
       </c>
       <c r="AA33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>-0.04063205417607219</v>
+        <v>0.03619909502262453</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.1580381471389645</v>
+        <v>0.1421446384039899</v>
       </c>
       <c r="AD33" t="n">
-        <v>-0.07578303468485681</v>
+        <v>0.001048114513839904</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.09296458185084755</v>
+        <v>0.07707107311587302</v>
       </c>
       <c r="AF33" t="n">
-        <v>-0.1687476165357044</v>
+        <v>-0.07602295860203312</v>
       </c>
       <c r="AG33" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="AH33" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="AI33" t="b">
         <v>0</v>
       </c>
       <c r="AJ33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK33" t="b">
         <v>0</v>
@@ -5104,14 +5100,18 @@
         <v>0</v>
       </c>
       <c r="AM33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO33" t="inlineStr"/>
-      <c r="AP33" t="n">
-        <v>5098.95</v>
+        <v>1</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>252.36</v>
+      </c>
+      <c r="AP33" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -5136,7 +5136,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>27.6</v>
+        <v>27.8</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K34" t="b">
         <v>0</v>
@@ -5177,7 +5177,7 @@
         <v>158.5</v>
       </c>
       <c r="R34" t="n">
-        <v>13277885</v>
+        <v>13169977</v>
       </c>
       <c r="S34" t="n">
         <v>162.6</v>
@@ -5192,10 +5192,10 @@
         <v>151.2083333333333</v>
       </c>
       <c r="W34" t="n">
-        <v>-1.609375708961352</v>
+        <v>-1.609375708961409</v>
       </c>
       <c r="X34" t="n">
-        <v>1.875328055753662</v>
+        <v>1.875328055753605</v>
       </c>
       <c r="Y34" t="n">
         <v>-3.484703764715014</v>
@@ -5274,7 +5274,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>25.8</v>
+        <v>26</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -5315,7 +5315,7 @@
         <v>133</v>
       </c>
       <c r="R35" t="n">
-        <v>92001831</v>
+        <v>90187620</v>
       </c>
       <c r="S35" t="n">
         <v>139.1</v>
@@ -5333,13 +5333,13 @@
         <v>-3.215749370824284</v>
       </c>
       <c r="X35" t="n">
-        <v>0.3038707882336754</v>
+        <v>0.3038707882336746</v>
       </c>
       <c r="Y35" t="n">
         <v>-3.519620159057959</v>
       </c>
       <c r="Z35" t="n">
-        <v>-3.441758272044087</v>
+        <v>-3.441758272044086</v>
       </c>
       <c r="AA35" t="b">
         <v>0</v>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5410,24 +5410,24 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>25.4</v>
+        <v>23.6</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>201900</v>
+        <v>2887848</v>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K36" t="b">
         <v>0</v>
@@ -5436,76 +5436,76 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>186900</v>
+        <v>2887848</v>
       </c>
       <c r="N36" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>0.08025682182985554</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>16480</v>
+        <v>2015</v>
       </c>
       <c r="Q36" t="n">
-        <v>16480</v>
+        <v>2015</v>
       </c>
       <c r="R36" t="n">
-        <v>310762</v>
+        <v>2095587</v>
       </c>
       <c r="S36" t="n">
-        <v>16994</v>
+        <v>2176</v>
       </c>
       <c r="T36" t="n">
-        <v>18569.5</v>
+        <v>2297</v>
       </c>
       <c r="U36" t="n">
-        <v>18621.5</v>
+        <v>2295.25</v>
       </c>
       <c r="V36" t="n">
-        <v>17089.25</v>
+        <v>2190.75</v>
       </c>
       <c r="W36" t="n">
-        <v>-560.0191406263875</v>
+        <v>-45.04314566761286</v>
       </c>
       <c r="X36" t="n">
-        <v>-175.275731059236</v>
+        <v>22.2816306089634</v>
       </c>
       <c r="Y36" t="n">
-        <v>-384.7434095671516</v>
+        <v>-67.32477627657626</v>
       </c>
       <c r="Z36" t="n">
-        <v>-418.1097860404951</v>
+        <v>-59.64653292198476</v>
       </c>
       <c r="AA36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>-0.05936073059360736</v>
+        <v>0.01767676767676774</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.1687943262411347</v>
+        <v>0.007500000000000062</v>
       </c>
       <c r="AD36" t="n">
-        <v>-0.09451171110239198</v>
+        <v>-0.01747421283201689</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.1037207609530177</v>
+        <v>-0.05757356528811686</v>
       </c>
       <c r="AF36" t="n">
-        <v>-0.1982324720554097</v>
+        <v>0.04009935245609997</v>
       </c>
       <c r="AG36" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="AH36" t="n">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="AI36" t="b">
         <v>0</v>
       </c>
       <c r="AJ36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK36" t="b">
         <v>0</v>
@@ -5514,14 +5514,16 @@
         <v>0</v>
       </c>
       <c r="AM36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN36" t="b">
         <v>0</v>
       </c>
       <c r="AO36" t="inlineStr"/>
-      <c r="AP36" t="n">
-        <v>20449.47</v>
+      <c r="AP36" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -5532,12 +5534,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5546,7 +5548,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>23.8</v>
+        <v>23.4</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5555,15 +5557,15 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1000</v>
+        <v>4328000</v>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="K37" t="b">
         <v>0</v>
@@ -5572,7 +5574,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1000</v>
+        <v>4328000</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -5581,67 +5583,67 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>472</v>
+        <v>5165</v>
       </c>
       <c r="Q37" t="n">
-        <v>472</v>
+        <v>5165</v>
       </c>
       <c r="R37" t="n">
-        <v>15781676</v>
+        <v>2553270</v>
       </c>
       <c r="S37" t="n">
-        <v>490.1</v>
+        <v>5500</v>
       </c>
       <c r="T37" t="n">
-        <v>507.575</v>
+        <v>5282.75</v>
       </c>
       <c r="U37" t="n">
-        <v>508.075</v>
+        <v>5280.25</v>
       </c>
       <c r="V37" t="n">
-        <v>453.25</v>
+        <v>5322.909090169271</v>
       </c>
       <c r="W37" t="n">
-        <v>-6.440507620384722</v>
+        <v>25.46163632789285</v>
       </c>
       <c r="X37" t="n">
-        <v>3.912199831102986</v>
+        <v>86.06939147893658</v>
       </c>
       <c r="Y37" t="n">
-        <v>-10.35270745148771</v>
+        <v>-60.60775515104373</v>
       </c>
       <c r="Z37" t="n">
-        <v>-9.644600973429901</v>
+        <v>-26.86192883382469</v>
       </c>
       <c r="AA37" t="b">
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>-0.02074688796680502</v>
+        <v>0.009775171065493637</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.1964512040557669</v>
+        <v>0.07424110202656142</v>
       </c>
       <c r="AD37" t="n">
-        <v>-0.05589786847558964</v>
+        <v>-0.02537580944329099</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.13137763876765</v>
+        <v>0.009167536738444504</v>
       </c>
       <c r="AF37" t="n">
-        <v>-0.1872755072432396</v>
+        <v>-0.03454334618173549</v>
       </c>
       <c r="AG37" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AH37" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="AI37" t="b">
         <v>0</v>
       </c>
       <c r="AJ37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK37" t="b">
         <v>0</v>
@@ -5653,11 +5655,15 @@
         <v>0</v>
       </c>
       <c r="AN37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO37" t="inlineStr"/>
-      <c r="AP37" t="n">
-        <v>547.45</v>
+        <v>1</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>5857.11</v>
+      </c>
+      <c r="AP37" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -5668,12 +5674,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5691,88 +5697,88 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>2887848</v>
+        <v>1000</v>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="n">
+        <v>44</v>
+      </c>
+      <c r="K38" t="b">
+        <v>0</v>
+      </c>
+      <c r="L38" t="b">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>540</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>540</v>
+      </c>
+      <c r="R38" t="n">
+        <v>503564</v>
+      </c>
+      <c r="S38" t="n">
+        <v>547.8</v>
+      </c>
+      <c r="T38" t="n">
+        <v>561.9</v>
+      </c>
+      <c r="U38" t="n">
+        <v>561.05</v>
+      </c>
+      <c r="V38" t="n">
+        <v>566.9836334228515</v>
+      </c>
+      <c r="W38" t="n">
+        <v>-5.293175034313435</v>
+      </c>
+      <c r="X38" t="n">
+        <v>-1.620689590515565</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>-3.67248544379787</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-3.375044081717603</v>
+      </c>
+      <c r="AA38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0.03250478011472269</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>-0.05940217750113941</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>-0.002646200394061937</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>-0.1244757427892563</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0.1218295423951944</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>44</v>
+      </c>
+      <c r="AH38" t="n">
         <v>18</v>
       </c>
-      <c r="K38" t="b">
-        <v>0</v>
-      </c>
-      <c r="L38" t="b">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
-        <v>2887848</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>2015</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>2015</v>
-      </c>
-      <c r="R38" t="n">
-        <v>2221187</v>
-      </c>
-      <c r="S38" t="n">
-        <v>2176</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2297</v>
-      </c>
-      <c r="U38" t="n">
-        <v>2295.25</v>
-      </c>
-      <c r="V38" t="n">
-        <v>2190.75</v>
-      </c>
-      <c r="W38" t="n">
-        <v>-45.04314566761286</v>
-      </c>
-      <c r="X38" t="n">
-        <v>22.28163060896342</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>-67.32477627657627</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>-59.64653292198479</v>
-      </c>
-      <c r="AA38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>0.01767676767676774</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>0.007500000000000062</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>-0.01747421283201689</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>-0.05757356528811686</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>0.04009935245609997</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>40</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>32</v>
-      </c>
       <c r="AI38" t="b">
         <v>0</v>
       </c>
@@ -5789,9 +5795,11 @@
         <v>0</v>
       </c>
       <c r="AN38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO38" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>582.12</v>
+      </c>
       <c r="AP38" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -5806,12 +5814,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5820,7 +5828,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>23.2</v>
+        <v>20.4</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5829,15 +5837,15 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>4328000</v>
+        <v>1000</v>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="n">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="K39" t="b">
         <v>0</v>
@@ -5846,7 +5854,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>4328000</v>
+        <v>1000</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -5855,67 +5863,67 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>5165</v>
+        <v>244</v>
       </c>
       <c r="Q39" t="n">
-        <v>5165</v>
+        <v>244</v>
       </c>
       <c r="R39" t="n">
-        <v>2761868</v>
+        <v>49281775</v>
       </c>
       <c r="S39" t="n">
-        <v>5500</v>
+        <v>242.2</v>
       </c>
       <c r="T39" t="n">
-        <v>5282.75</v>
+        <v>249.375</v>
       </c>
       <c r="U39" t="n">
-        <v>5280.25</v>
+        <v>249.5</v>
       </c>
       <c r="V39" t="n">
-        <v>5322.909090169271</v>
+        <v>250.9166666666667</v>
       </c>
       <c r="W39" t="n">
-        <v>25.46163632789376</v>
+        <v>-2.52142207475751</v>
       </c>
       <c r="X39" t="n">
-        <v>86.06939147893755</v>
+        <v>-1.296563832843463</v>
       </c>
       <c r="Y39" t="n">
-        <v>-60.60775515104379</v>
+        <v>-1.224858241914047</v>
       </c>
       <c r="Z39" t="n">
-        <v>-26.86192883382478</v>
+        <v>-1.688914190086806</v>
       </c>
       <c r="AA39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.009775171065493637</v>
+        <v>-0.01014198782961462</v>
       </c>
       <c r="AC39" t="n">
-        <v>0.07424110202656142</v>
+        <v>-0.008130081300813052</v>
       </c>
       <c r="AD39" t="n">
-        <v>-0.02537580944329099</v>
+        <v>-0.04529296833839924</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.009167536738444504</v>
+        <v>-0.07320364658892997</v>
       </c>
       <c r="AF39" t="n">
-        <v>-0.03454334618173549</v>
+        <v>0.02791067825053073</v>
       </c>
       <c r="AG39" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AH39" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="AI39" t="b">
         <v>0</v>
       </c>
       <c r="AJ39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="b">
         <v>0</v>
@@ -5924,18 +5932,16 @@
         <v>0</v>
       </c>
       <c r="AM39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN39" t="b">
         <v>1</v>
       </c>
       <c r="AO39" t="n">
-        <v>5857.11</v>
-      </c>
-      <c r="AP39" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>258.15</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>253.66</v>
       </c>
     </row>
     <row r="40">
@@ -5946,12 +5952,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5960,7 +5966,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>23.2</v>
+        <v>20.2</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5969,7 +5975,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -5977,7 +5983,7 @@
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="K40" t="b">
         <v>0</v>
@@ -5995,67 +6001,67 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>540</v>
+        <v>447.5</v>
       </c>
       <c r="Q40" t="n">
-        <v>540</v>
+        <v>447.5</v>
       </c>
       <c r="R40" t="n">
-        <v>525680</v>
+        <v>45967146</v>
       </c>
       <c r="S40" t="n">
-        <v>547.8</v>
+        <v>476.5</v>
       </c>
       <c r="T40" t="n">
-        <v>561.9</v>
+        <v>504.5</v>
       </c>
       <c r="U40" t="n">
-        <v>561.05</v>
+        <v>505.4</v>
       </c>
       <c r="V40" t="n">
-        <v>566.9836334228515</v>
+        <v>486.1666666666667</v>
       </c>
       <c r="W40" t="n">
-        <v>-5.293175034313435</v>
+        <v>-13.58907882775202</v>
       </c>
       <c r="X40" t="n">
-        <v>-1.620689590515267</v>
+        <v>-2.506816021675073</v>
       </c>
       <c r="Y40" t="n">
-        <v>-3.672485443798168</v>
+        <v>-11.08226280607695</v>
       </c>
       <c r="Z40" t="n">
-        <v>-3.375044081717863</v>
+        <v>-9.97394763226195</v>
       </c>
       <c r="AA40" t="b">
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.03250478011472269</v>
+        <v>-0.03866809881847477</v>
       </c>
       <c r="AC40" t="n">
-        <v>-0.05940217750113941</v>
+        <v>0.1049382716049383</v>
       </c>
       <c r="AD40" t="n">
-        <v>-0.002646200394061937</v>
+        <v>-0.0738190793272594</v>
       </c>
       <c r="AE40" t="n">
-        <v>-0.1244757427892563</v>
+        <v>0.03986470631682137</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.1218295423951944</v>
+        <v>-0.1136837856440808</v>
       </c>
       <c r="AG40" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="AH40" t="n">
-        <v>18</v>
+        <v>57.99999999999999</v>
       </c>
       <c r="AI40" t="b">
         <v>0</v>
       </c>
       <c r="AJ40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="b">
         <v>0</v>
@@ -6067,15 +6073,11 @@
         <v>0</v>
       </c>
       <c r="AN40" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO40" t="n">
-        <v>582.12</v>
-      </c>
-      <c r="AP40" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="AO40" t="inlineStr"/>
+      <c r="AP40" t="n">
+        <v>552.5</v>
       </c>
     </row>
     <row r="41">
@@ -6086,12 +6088,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6100,7 +6102,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>20.2</v>
+        <v>19.6</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -6109,15 +6111,15 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1000</v>
+        <v>5143000</v>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="n">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="K41" t="b">
         <v>0</v>
@@ -6126,7 +6128,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1000</v>
+        <v>5143000</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -6135,61 +6137,61 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>244</v>
+        <v>4250</v>
       </c>
       <c r="Q41" t="n">
-        <v>244</v>
+        <v>4250</v>
       </c>
       <c r="R41" t="n">
-        <v>50072297</v>
+        <v>7757617</v>
       </c>
       <c r="S41" t="n">
-        <v>242.2</v>
+        <v>4408</v>
       </c>
       <c r="T41" t="n">
-        <v>249.375</v>
+        <v>4790.5</v>
       </c>
       <c r="U41" t="n">
-        <v>249.5</v>
+        <v>4799.5</v>
       </c>
       <c r="V41" t="n">
-        <v>250.9166666666667</v>
+        <v>4274.5</v>
       </c>
       <c r="W41" t="n">
-        <v>-2.52142207475751</v>
+        <v>-122.8760504218917</v>
       </c>
       <c r="X41" t="n">
-        <v>-1.296563832843444</v>
+        <v>-0.09212629721524124</v>
       </c>
       <c r="Y41" t="n">
-        <v>-1.224858241914066</v>
+        <v>-122.7839241246765</v>
       </c>
       <c r="Z41" t="n">
-        <v>-1.688914190086831</v>
+        <v>-127.5067884662056</v>
       </c>
       <c r="AA41" t="b">
         <v>1</v>
       </c>
       <c r="AB41" t="n">
-        <v>-0.01014198782961462</v>
+        <v>-0.04063205417607219</v>
       </c>
       <c r="AC41" t="n">
-        <v>-0.008130081300813052</v>
+        <v>0.1580381471389645</v>
       </c>
       <c r="AD41" t="n">
-        <v>-0.04529296833839924</v>
+        <v>-0.07578303468485681</v>
       </c>
       <c r="AE41" t="n">
-        <v>-0.07320364658892997</v>
+        <v>0.09296458185084755</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.02791067825053073</v>
+        <v>-0.1687476165357044</v>
       </c>
       <c r="AG41" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="AH41" t="n">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="AI41" t="b">
         <v>0</v>
@@ -6207,13 +6209,11 @@
         <v>1</v>
       </c>
       <c r="AN41" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO41" t="n">
-        <v>258.15</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO41" t="inlineStr"/>
       <c r="AP41" t="n">
-        <v>253.66</v>
+        <v>5098.95</v>
       </c>
     </row>
     <row r="42">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6238,7 +6238,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>20</v>
+        <v>19.4</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6247,15 +6247,15 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1000</v>
+        <v>470000</v>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="K42" t="b">
         <v>0</v>
@@ -6264,7 +6264,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1000</v>
+        <v>470000</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
@@ -6273,61 +6273,61 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>447.5</v>
+        <v>3120</v>
       </c>
       <c r="Q42" t="n">
-        <v>447.5</v>
+        <v>3120</v>
       </c>
       <c r="R42" t="n">
-        <v>46975365</v>
+        <v>1049185</v>
       </c>
       <c r="S42" t="n">
-        <v>476.5</v>
+        <v>3189</v>
       </c>
       <c r="T42" t="n">
-        <v>504.5</v>
+        <v>3232</v>
       </c>
       <c r="U42" t="n">
-        <v>505.4</v>
+        <v>3238.75</v>
       </c>
       <c r="V42" t="n">
-        <v>486.1666666666667</v>
+        <v>3011</v>
       </c>
       <c r="W42" t="n">
-        <v>-13.58907882775202</v>
+        <v>-36.18505579455723</v>
       </c>
       <c r="X42" t="n">
-        <v>-2.506816021675073</v>
+        <v>-18.69783317724361</v>
       </c>
       <c r="Y42" t="n">
-        <v>-11.08226280607695</v>
+        <v>-17.48722261731362</v>
       </c>
       <c r="Z42" t="n">
-        <v>-9.97394763226195</v>
+        <v>-21.52010150547788</v>
       </c>
       <c r="AA42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB42" t="n">
-        <v>-0.03866809881847477</v>
+        <v>-0.04147465437788023</v>
       </c>
       <c r="AC42" t="n">
-        <v>0.1049382716049383</v>
+        <v>0.1795841209829867</v>
       </c>
       <c r="AD42" t="n">
-        <v>-0.0738190793272594</v>
+        <v>-0.07662563488666485</v>
       </c>
       <c r="AE42" t="n">
-        <v>0.03986470631682137</v>
+        <v>0.1145105556948698</v>
       </c>
       <c r="AF42" t="n">
-        <v>-0.1136837856440808</v>
+        <v>-0.1911361905815346</v>
       </c>
       <c r="AG42" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AH42" t="n">
-        <v>57.99999999999999</v>
+        <v>68</v>
       </c>
       <c r="AI42" t="b">
         <v>0</v>
@@ -6342,14 +6342,16 @@
         <v>0</v>
       </c>
       <c r="AM42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO42" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>3319.68</v>
+      </c>
       <c r="AP42" t="n">
-        <v>552.5</v>
+        <v>3347.89</v>
       </c>
     </row>
     <row r="43">
@@ -6360,12 +6362,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6374,7 +6376,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>19.2</v>
+        <v>18.4</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6383,15 +6385,15 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>470000</v>
+        <v>1000</v>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="K43" t="b">
         <v>0</v>
@@ -6400,7 +6402,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>470000</v>
+        <v>1000</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -6409,61 +6411,61 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>3120</v>
+        <v>322</v>
       </c>
       <c r="Q43" t="n">
-        <v>3120</v>
+        <v>322</v>
       </c>
       <c r="R43" t="n">
-        <v>1103993</v>
+        <v>9511272</v>
       </c>
       <c r="S43" t="n">
-        <v>3189</v>
+        <v>321.3</v>
       </c>
       <c r="T43" t="n">
-        <v>3232</v>
+        <v>333.075</v>
       </c>
       <c r="U43" t="n">
-        <v>3238.75</v>
+        <v>333.625</v>
       </c>
       <c r="V43" t="n">
-        <v>3011</v>
+        <v>327.05</v>
       </c>
       <c r="W43" t="n">
-        <v>-36.18505579455723</v>
+        <v>-4.266450278084278</v>
       </c>
       <c r="X43" t="n">
-        <v>-18.69783317724341</v>
+        <v>-2.713063747046953</v>
       </c>
       <c r="Y43" t="n">
-        <v>-17.48722261731382</v>
+        <v>-1.553386531037325</v>
       </c>
       <c r="Z43" t="n">
-        <v>-21.52010150547813</v>
+        <v>-2.101321064717312</v>
       </c>
       <c r="AA43" t="b">
         <v>1</v>
       </c>
       <c r="AB43" t="n">
-        <v>-0.04147465437788023</v>
+        <v>-0.03303303303303307</v>
       </c>
       <c r="AC43" t="n">
-        <v>0.1795841209829867</v>
+        <v>-0.006172839506172867</v>
       </c>
       <c r="AD43" t="n">
-        <v>-0.07662563488666485</v>
+        <v>-0.06818401354181769</v>
       </c>
       <c r="AE43" t="n">
-        <v>0.1145105556948698</v>
+        <v>-0.07124640479428979</v>
       </c>
       <c r="AF43" t="n">
-        <v>-0.1911361905815346</v>
+        <v>0.003062391252472096</v>
       </c>
       <c r="AG43" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="AH43" t="n">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="AI43" t="b">
         <v>0</v>
@@ -6484,10 +6486,10 @@
         <v>1</v>
       </c>
       <c r="AO43" t="n">
-        <v>3319.68</v>
+        <v>340.03</v>
       </c>
       <c r="AP43" t="n">
-        <v>3347.89</v>
+        <v>352.16</v>
       </c>
     </row>
     <row r="44">
@@ -6498,12 +6500,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6512,7 +6514,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>18.2</v>
+        <v>17.8</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6521,7 +6523,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -6529,7 +6531,7 @@
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="K44" t="b">
         <v>0</v>
@@ -6547,61 +6549,61 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>322</v>
+        <v>902</v>
       </c>
       <c r="Q44" t="n">
-        <v>322</v>
+        <v>902</v>
       </c>
       <c r="R44" t="n">
-        <v>9667065</v>
+        <v>14865775</v>
       </c>
       <c r="S44" t="n">
-        <v>321.3</v>
+        <v>995</v>
       </c>
       <c r="T44" t="n">
-        <v>333.075</v>
+        <v>1027.65</v>
       </c>
       <c r="U44" t="n">
-        <v>333.625</v>
+        <v>1028.25</v>
       </c>
       <c r="V44" t="n">
-        <v>327.05</v>
+        <v>978.8333333333334</v>
       </c>
       <c r="W44" t="n">
-        <v>-4.266450278084278</v>
+        <v>-13.50961918957125</v>
       </c>
       <c r="X44" t="n">
-        <v>-2.71306374704698</v>
+        <v>22.17543639612178</v>
       </c>
       <c r="Y44" t="n">
-        <v>-1.553386531037298</v>
+        <v>-35.68505558569304</v>
       </c>
       <c r="Z44" t="n">
-        <v>-2.101321064717278</v>
+        <v>-28.26798946627251</v>
       </c>
       <c r="AA44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>-0.03303303303303307</v>
+        <v>-0.01312910284463897</v>
       </c>
       <c r="AC44" t="n">
-        <v>-0.006172839506172867</v>
+        <v>-0.2514522821576763</v>
       </c>
       <c r="AD44" t="n">
-        <v>-0.06818401354181769</v>
+        <v>-0.0482800833534236</v>
       </c>
       <c r="AE44" t="n">
-        <v>-0.07124640479428979</v>
+        <v>-0.3165258474457933</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.003062391252472096</v>
+        <v>0.2682457640923697</v>
       </c>
       <c r="AG44" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AH44" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="AI44" t="b">
         <v>0</v>
@@ -6616,16 +6618,14 @@
         <v>0</v>
       </c>
       <c r="AM44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN44" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO44" t="n">
-        <v>340.03</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO44" t="inlineStr"/>
       <c r="AP44" t="n">
-        <v>352.16</v>
+        <v>1069.26</v>
       </c>
     </row>
     <row r="45">
@@ -6636,12 +6636,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6659,7 +6659,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -6667,7 +6667,7 @@
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="K45" t="b">
         <v>0</v>
@@ -6685,61 +6685,61 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>902</v>
+        <v>2000</v>
       </c>
       <c r="Q45" t="n">
-        <v>902</v>
+        <v>2000</v>
       </c>
       <c r="R45" t="n">
-        <v>16344010</v>
+        <v>3436716</v>
       </c>
       <c r="S45" t="n">
-        <v>995</v>
+        <v>2168</v>
       </c>
       <c r="T45" t="n">
-        <v>1027.65</v>
+        <v>2236.75</v>
       </c>
       <c r="U45" t="n">
-        <v>1028.25</v>
+        <v>2240.75</v>
       </c>
       <c r="V45" t="n">
-        <v>978.8333333333334</v>
+        <v>2135</v>
       </c>
       <c r="W45" t="n">
-        <v>-13.50961918957125</v>
+        <v>-32.22265688838252</v>
       </c>
       <c r="X45" t="n">
-        <v>22.17543639612178</v>
+        <v>12.59476629304624</v>
       </c>
       <c r="Y45" t="n">
-        <v>-35.68505558569304</v>
+        <v>-44.81742318142877</v>
       </c>
       <c r="Z45" t="n">
-        <v>-28.26798946627251</v>
+        <v>-32.33166498783359</v>
       </c>
       <c r="AA45" t="b">
         <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>-0.01312910284463897</v>
+        <v>-0.03846153846153844</v>
       </c>
       <c r="AC45" t="n">
-        <v>-0.2514522821576763</v>
+        <v>-0.007444168734491274</v>
       </c>
       <c r="AD45" t="n">
-        <v>-0.0482800833534236</v>
+        <v>-0.07361251897032306</v>
       </c>
       <c r="AE45" t="n">
-        <v>-0.3165258474457933</v>
+        <v>-0.07251773402260819</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.2682457640923697</v>
+        <v>-0.001094784947714866</v>
       </c>
       <c r="AG45" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AH45" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="AI45" t="b">
         <v>0</v>
@@ -6761,7 +6761,7 @@
       </c>
       <c r="AO45" t="inlineStr"/>
       <c r="AP45" t="n">
-        <v>1069.26</v>
+        <v>2339.21</v>
       </c>
     </row>
     <row r="46">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6795,15 +6795,15 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1000</v>
+        <v>201900</v>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="K46" t="b">
         <v>0</v>
@@ -6812,7 +6812,7 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>1000</v>
+        <v>201900</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
@@ -6821,61 +6821,61 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>2000</v>
+        <v>16480</v>
       </c>
       <c r="Q46" t="n">
-        <v>2000</v>
+        <v>16480</v>
       </c>
       <c r="R46" t="n">
-        <v>3575004</v>
+        <v>284297</v>
       </c>
       <c r="S46" t="n">
-        <v>2168</v>
+        <v>16994</v>
       </c>
       <c r="T46" t="n">
-        <v>2236.75</v>
+        <v>18569.5</v>
       </c>
       <c r="U46" t="n">
-        <v>2240.75</v>
+        <v>18621.5</v>
       </c>
       <c r="V46" t="n">
-        <v>2135</v>
+        <v>17089.25</v>
       </c>
       <c r="W46" t="n">
-        <v>-32.22265688838252</v>
+        <v>-560.0191406263875</v>
       </c>
       <c r="X46" t="n">
-        <v>12.59476629304625</v>
+        <v>-175.2757310592362</v>
       </c>
       <c r="Y46" t="n">
-        <v>-44.81742318142877</v>
+        <v>-384.7434095671514</v>
       </c>
       <c r="Z46" t="n">
-        <v>-32.3316649878336</v>
+        <v>-418.1097860404948</v>
       </c>
       <c r="AA46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB46" t="n">
-        <v>-0.03846153846153844</v>
+        <v>-0.05936073059360736</v>
       </c>
       <c r="AC46" t="n">
-        <v>-0.007444168734491274</v>
+        <v>0.1687943262411347</v>
       </c>
       <c r="AD46" t="n">
-        <v>-0.07361251897032306</v>
+        <v>-0.09451171110239198</v>
       </c>
       <c r="AE46" t="n">
-        <v>-0.07251773402260819</v>
+        <v>0.1037207609530177</v>
       </c>
       <c r="AF46" t="n">
-        <v>-0.001094784947714866</v>
+        <v>-0.1982324720554097</v>
       </c>
       <c r="AG46" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="AH46" t="n">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="AI46" t="b">
         <v>0</v>
@@ -6890,14 +6890,14 @@
         <v>0</v>
       </c>
       <c r="AM46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN46" t="b">
         <v>0</v>
       </c>
       <c r="AO46" t="inlineStr"/>
       <c r="AP46" t="n">
-        <v>2339.21</v>
+        <v>20449.47</v>
       </c>
     </row>
     <row r="47">
@@ -6922,7 +6922,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>14.2</v>
+        <v>14.4</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H47" t="n">
@@ -6963,7 +6963,7 @@
         <v>1845</v>
       </c>
       <c r="R47" t="n">
-        <v>13372287</v>
+        <v>12287772</v>
       </c>
       <c r="S47" t="n">
         <v>2067</v>
@@ -6981,13 +6981,13 @@
         <v>-62.78250070016929</v>
       </c>
       <c r="X47" t="n">
-        <v>-25.23301919947082</v>
+        <v>-25.233019199471</v>
       </c>
       <c r="Y47" t="n">
-        <v>-37.54948150069847</v>
+        <v>-37.54948150069829</v>
       </c>
       <c r="Z47" t="n">
-        <v>-19.84982888075157</v>
+        <v>-19.84982888075135</v>
       </c>
       <c r="AA47" t="b">
         <v>0</v>
@@ -7058,7 +7058,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>13</v>
+        <v>13.2</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H48" t="n">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K48" t="b">
         <v>0</v>
@@ -7099,7 +7099,7 @@
         <v>5205</v>
       </c>
       <c r="R48" t="n">
-        <v>1540825</v>
+        <v>1463336</v>
       </c>
       <c r="S48" t="n">
         <v>5692</v>
@@ -7114,16 +7114,16 @@
         <v>5588.083333333333</v>
       </c>
       <c r="W48" t="n">
-        <v>6.001759798634339</v>
+        <v>6.001759798633429</v>
       </c>
       <c r="X48" t="n">
-        <v>37.92903167516392</v>
+        <v>37.92903167516284</v>
       </c>
       <c r="Y48" t="n">
-        <v>-31.92727187652958</v>
+        <v>-31.92727187652941</v>
       </c>
       <c r="Z48" t="n">
-        <v>14.85854463919038</v>
+        <v>14.8585446391906</v>
       </c>
       <c r="AA48" t="b">
         <v>0</v>
@@ -7196,7 +7196,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>11.4</v>
+        <v>11.6</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H49" t="n">
@@ -7213,7 +7213,7 @@
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K49" t="b">
         <v>0</v>
@@ -7237,7 +7237,7 @@
         <v>834</v>
       </c>
       <c r="R49" t="n">
-        <v>639403</v>
+        <v>585807</v>
       </c>
       <c r="S49" t="n">
         <v>843.8</v>
@@ -7255,13 +7255,13 @@
         <v>-16.27706785386522</v>
       </c>
       <c r="X49" t="n">
-        <v>-15.85999939419889</v>
+        <v>-15.85999939419888</v>
       </c>
       <c r="Y49" t="n">
-        <v>-0.4170684596663303</v>
+        <v>-0.4170684596663357</v>
       </c>
       <c r="Z49" t="n">
-        <v>0.06517666901736874</v>
+        <v>0.06517666901736163</v>
       </c>
       <c r="AA49" t="b">
         <v>0</v>
@@ -7334,7 +7334,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>11</v>
+        <v>11.2</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H50" t="n">
@@ -7375,7 +7375,7 @@
         <v>1155</v>
       </c>
       <c r="R50" t="n">
-        <v>533893</v>
+        <v>504166</v>
       </c>
       <c r="S50" t="n">
         <v>1175</v>
@@ -7393,13 +7393,13 @@
         <v>-26.61889905514317</v>
       </c>
       <c r="X50" t="n">
-        <v>-28.8663499024008</v>
+        <v>-28.86634990240082</v>
       </c>
       <c r="Y50" t="n">
-        <v>2.247450847257628</v>
+        <v>2.247450847257646</v>
       </c>
       <c r="Z50" t="n">
-        <v>3.503943354691707</v>
+        <v>3.503943354691728</v>
       </c>
       <c r="AA50" t="b">
         <v>0</v>
@@ -7474,7 +7474,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K51" t="b">
         <v>0</v>
@@ -7515,7 +7515,7 @@
         <v>5160</v>
       </c>
       <c r="R51" t="n">
-        <v>790793</v>
+        <v>735494</v>
       </c>
       <c r="S51" t="n">
         <v>5511</v>
@@ -7533,13 +7533,13 @@
         <v>-251.3873140364049</v>
       </c>
       <c r="X51" t="n">
-        <v>-188.2618667969099</v>
+        <v>-188.2618667969104</v>
       </c>
       <c r="Y51" t="n">
-        <v>-63.12544723949495</v>
+        <v>-63.12544723949443</v>
       </c>
       <c r="Z51" t="n">
-        <v>-51.03017474922342</v>
+        <v>-51.03017474922279</v>
       </c>
       <c r="AA51" t="b">
         <v>0</v>

--- a/output/daily_screen_latest.xlsx
+++ b/output/daily_screen_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP51"/>
+  <dimension ref="A1:AP52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,17 +643,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>3376</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>新日興</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>68.2</v>
+        <v>70.19607843137254</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -671,15 +671,15 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>5163000</v>
+        <v>1740000</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="K2" t="b">
         <v>0</v>
@@ -688,7 +688,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>5163000</v>
+        <v>1740000</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -697,61 +697,61 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>19.54999923706055</v>
+        <v>178.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>19.54999923706055</v>
+        <v>178.5</v>
       </c>
       <c r="R2" t="n">
-        <v>65670302</v>
+        <v>3394821</v>
       </c>
       <c r="S2" t="n">
-        <v>19.32999992370605</v>
+        <v>176.6</v>
       </c>
       <c r="T2" t="n">
-        <v>18.95250005722046</v>
+        <v>174.4</v>
       </c>
       <c r="U2" t="n">
-        <v>18.90750007629395</v>
+        <v>174.25</v>
       </c>
       <c r="V2" t="n">
-        <v>19.03753280639648</v>
+        <v>184.0006340026856</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1408405378258664</v>
+        <v>-0.7877311763919295</v>
       </c>
       <c r="X2" t="n">
-        <v>0.06601432902447313</v>
+        <v>-2.36837063170035</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.07482620880139323</v>
+        <v>1.58063945530842</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.06175010322038885</v>
+        <v>1.332062389715027</v>
       </c>
       <c r="AA2" t="b">
         <v>1</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.04825735318707736</v>
+        <v>0.01709401709401703</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.04812497047306286</v>
+        <v>-0.04728763662152335</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.01310637267829273</v>
+        <v>0.01698751675915711</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.01694859481505406</v>
+        <v>-0.07944137339832169</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.0300549674933468</v>
+        <v>0.0964288901574788</v>
       </c>
       <c r="AG2" t="n">
-        <v>52</v>
+        <v>60.78431372549019</v>
       </c>
       <c r="AH2" t="n">
-        <v>42</v>
+        <v>29.41176470588236</v>
       </c>
       <c r="AI2" t="b">
         <v>1</v>
@@ -785,115 +785,113 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>新日興</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>61.2</v>
+        <v>62.11764705882353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>New Entry</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1740000</v>
+        <v>4703000</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="K3" t="b">
         <v>0</v>
       </c>
       <c r="L3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>1740000</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
+        <v>4703000</v>
+      </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="Q3" t="n">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="R3" t="n">
-        <v>1689482</v>
+        <v>83332939</v>
       </c>
       <c r="S3" t="n">
-        <v>174.8</v>
+        <v>182.9</v>
       </c>
       <c r="T3" t="n">
-        <v>174.425</v>
+        <v>185.425</v>
       </c>
       <c r="U3" t="n">
-        <v>174.275</v>
+        <v>185.3</v>
       </c>
       <c r="V3" t="n">
-        <v>184.3876274108887</v>
+        <v>184.3666666666667</v>
       </c>
       <c r="W3" t="n">
-        <v>-1.427535160659517</v>
+        <v>-0.4580398142185516</v>
       </c>
       <c r="X3" t="n">
-        <v>-3.096546092956211</v>
+        <v>-0.150035242042377</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.669010932296694</v>
+        <v>-0.3080045721761746</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.660792931061994</v>
+        <v>-1.145018467419051</v>
       </c>
       <c r="AA3" t="b">
         <v>1</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01734104046242768</v>
+        <v>0.01340482573726542</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.05071678095207688</v>
+        <v>0.08933717579250722</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.01780994004635694</v>
+        <v>0.0132983254024055</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.1157903462401938</v>
+        <v>0.05718343901570888</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.09798040619383686</v>
+        <v>-0.04388511361330338</v>
       </c>
       <c r="AG3" t="n">
-        <v>36</v>
+        <v>58.82352941176471</v>
       </c>
       <c r="AH3" t="n">
-        <v>20</v>
+        <v>64.70588235294117</v>
       </c>
       <c r="AI3" t="b">
         <v>1</v>
@@ -902,21 +900,19 @@
         <v>1</v>
       </c>
       <c r="AK3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="b">
         <v>1</v>
       </c>
       <c r="AN3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>192.78</v>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
@@ -927,7 +923,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -942,20 +938,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>75</v>
+        <v>56.86274509803921</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -972,70 +968,70 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>6700000</v>
+        <v>6899000</v>
       </c>
       <c r="N4" t="n">
-        <v>199000</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02970149253731343</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1245</v>
+        <v>1185</v>
       </c>
       <c r="Q4" t="n">
-        <v>1245</v>
+        <v>1185</v>
       </c>
       <c r="R4" t="n">
-        <v>15215404</v>
+        <v>11097132</v>
       </c>
       <c r="S4" t="n">
-        <v>1220</v>
+        <v>1226</v>
       </c>
       <c r="T4" t="n">
-        <v>1141.85</v>
+        <v>1166.5</v>
       </c>
       <c r="U4" t="n">
-        <v>1128.2</v>
+        <v>1154.75</v>
       </c>
       <c r="V4" t="n">
-        <v>1040.966666666667</v>
+        <v>1050.2</v>
       </c>
       <c r="W4" t="n">
-        <v>38.14472539795747</v>
+        <v>29.38537899162043</v>
       </c>
       <c r="X4" t="n">
-        <v>38.55835926692415</v>
+        <v>36.60043499802292</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.4136338689666772</v>
+        <v>-7.215056006402492</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.559165299163439</v>
+        <v>-0.6166410692021671</v>
       </c>
       <c r="AA4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.2808641975308641</v>
+        <v>0.2473684210526317</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.2704081632653061</v>
+        <v>0.2592986184909671</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.2457132170220795</v>
+        <v>0.2472619207177718</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.2053345979771892</v>
+        <v>0.2271448817141688</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.04037861904489026</v>
+        <v>0.02011703900360295</v>
       </c>
       <c r="AG4" t="n">
-        <v>96</v>
+        <v>98.0392156862745</v>
       </c>
       <c r="AH4" t="n">
-        <v>78</v>
+        <v>84.31372549019608</v>
       </c>
       <c r="AI4" t="b">
         <v>1</v>
@@ -1050,13 +1046,13 @@
         <v>0</v>
       </c>
       <c r="AM4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="b">
         <v>1</v>
       </c>
       <c r="AO4" t="n">
-        <v>1249.98</v>
+        <v>1267.95</v>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
@@ -1067,43 +1063,43 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>48.2</v>
+        <v>56.86274509803921</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1000</v>
+        <v>2512000</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="K5" t="b">
         <v>0</v>
@@ -1112,73 +1108,73 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1000</v>
+        <v>2502000</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>0.003996802557953637</v>
       </c>
       <c r="P5" t="n">
-        <v>557</v>
+        <v>6650</v>
       </c>
       <c r="Q5" t="n">
-        <v>557</v>
+        <v>6650</v>
       </c>
       <c r="R5" t="n">
-        <v>27282900</v>
+        <v>898505</v>
       </c>
       <c r="S5" t="n">
-        <v>555.2</v>
+        <v>6755</v>
       </c>
       <c r="T5" t="n">
-        <v>526.975</v>
+        <v>6701.25</v>
       </c>
       <c r="U5" t="n">
-        <v>523</v>
+        <v>6636.5</v>
       </c>
       <c r="V5" t="n">
-        <v>490.7916666666667</v>
+        <v>5522.083333333333</v>
       </c>
       <c r="W5" t="n">
-        <v>13.0298655157427</v>
+        <v>99.94816799166802</v>
       </c>
       <c r="X5" t="n">
-        <v>17.33104492404919</v>
+        <v>221.5276412919161</v>
       </c>
       <c r="Y5" t="n">
-        <v>-4.301179408306488</v>
+        <v>-121.5794733002481</v>
       </c>
       <c r="Z5" t="n">
-        <v>-4.317652886009089</v>
+        <v>-119.2467683861247</v>
       </c>
       <c r="AA5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.1664921465968587</v>
+        <v>0.2418300653594772</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.09430255402750487</v>
+        <v>0.7924528301886793</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.1313411660880741</v>
+        <v>0.2417235650246172</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.02922898873938795</v>
+        <v>0.760299093411881</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.1021121773486862</v>
+        <v>-0.5185755283872637</v>
       </c>
       <c r="AG5" t="n">
-        <v>82</v>
+        <v>96.07843137254902</v>
       </c>
       <c r="AH5" t="n">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="AI5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="b">
         <v>1</v>
@@ -1190,14 +1186,12 @@
         <v>0</v>
       </c>
       <c r="AM5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>606.02</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -1207,26 +1201,26 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>47.6</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1235,24 +1229,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>501000</v>
+        <v>7224000</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="K6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="b">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>501000</v>
+        <v>7224000</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1261,64 +1255,64 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>248</v>
+        <v>1550</v>
       </c>
       <c r="Q6" t="n">
-        <v>248</v>
+        <v>1550</v>
       </c>
       <c r="R6" t="n">
-        <v>49130197</v>
+        <v>9261663</v>
       </c>
       <c r="S6" t="n">
-        <v>244.4</v>
+        <v>1631</v>
       </c>
       <c r="T6" t="n">
-        <v>234.1</v>
+        <v>1595</v>
       </c>
       <c r="U6" t="n">
-        <v>232.625</v>
+        <v>1583.5</v>
       </c>
       <c r="V6" t="n">
-        <v>221.55</v>
+        <v>1467.916666666667</v>
       </c>
       <c r="W6" t="n">
-        <v>3.972947556634949</v>
+        <v>21.30466525258475</v>
       </c>
       <c r="X6" t="n">
-        <v>4.107292513375461</v>
+        <v>48.35086230780859</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.1343449567405113</v>
+        <v>-27.04619705522384</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.5706998436825819</v>
+        <v>-18.3199011524148</v>
       </c>
       <c r="AA6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.1350114416475972</v>
+        <v>0.1742424242424243</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.180952380952381</v>
+        <v>0.1610486891385767</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.09986046113881253</v>
+        <v>0.1741359239075644</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.1158788156642641</v>
+        <v>0.1288949523617784</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.01601835452545153</v>
+        <v>0.04524097154578599</v>
       </c>
       <c r="AG6" t="n">
-        <v>74</v>
+        <v>88.23529411764706</v>
       </c>
       <c r="AH6" t="n">
-        <v>70</v>
+        <v>78.43137254901961</v>
       </c>
       <c r="AI6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="b">
         <v>1</v>
@@ -1330,13 +1324,13 @@
         <v>0</v>
       </c>
       <c r="AM6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>249.98</v>
+        <v>1856.9</v>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
@@ -1347,17 +1341,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1366,24 +1360,24 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>59.2</v>
+        <v>52.94117647058823</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>19499000</v>
+        <v>8937000</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K7" t="b">
         <v>1</v>
@@ -1392,70 +1386,70 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>19386000</v>
+        <v>8937000</v>
       </c>
       <c r="N7" t="n">
-        <v>113000</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.005828948725884659</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1090</v>
+        <v>1305</v>
       </c>
       <c r="Q7" t="n">
-        <v>1090</v>
+        <v>1305</v>
       </c>
       <c r="R7" t="n">
-        <v>14516214</v>
+        <v>8831230</v>
       </c>
       <c r="S7" t="n">
-        <v>1157</v>
+        <v>1363</v>
       </c>
       <c r="T7" t="n">
-        <v>1161.1</v>
+        <v>1345.75</v>
       </c>
       <c r="U7" t="n">
-        <v>1154.15</v>
+        <v>1333.75</v>
       </c>
       <c r="V7" t="n">
-        <v>1035.883333333333</v>
+        <v>1191.916666666667</v>
       </c>
       <c r="W7" t="n">
-        <v>4.353879746731536</v>
+        <v>21.065695908208</v>
       </c>
       <c r="X7" t="n">
-        <v>38.65338220905522</v>
+        <v>50.49968106596425</v>
       </c>
       <c r="Y7" t="n">
-        <v>-34.29950246232368</v>
+        <v>-29.43398515775625</v>
       </c>
       <c r="Z7" t="n">
-        <v>-29.62678598084111</v>
+        <v>-23.0865726191041</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.1461619348054679</v>
+        <v>0.2253521126760563</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.3212121212121213</v>
+        <v>0.06097560975609762</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.1110109542966833</v>
+        <v>0.2252456123411963</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.2561385559240044</v>
+        <v>0.02882187297929928</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.1451276016273211</v>
+        <v>0.1964237393618971</v>
       </c>
       <c r="AG7" t="n">
-        <v>78</v>
+        <v>94.11764705882352</v>
       </c>
       <c r="AH7" t="n">
-        <v>82</v>
+        <v>56.86274509803921</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -1485,17 +1479,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1504,96 +1498,96 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53.40000000000001</v>
+        <v>51.76470588235294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>852000</v>
+        <v>19499000</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="K8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="b">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>751000</v>
+        <v>19499000</v>
       </c>
       <c r="N8" t="n">
-        <v>101000</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1344873501997337</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>7480</v>
+        <v>1055</v>
       </c>
       <c r="Q8" t="n">
-        <v>7480</v>
+        <v>1055</v>
       </c>
       <c r="R8" t="n">
-        <v>1804746</v>
+        <v>13971291</v>
       </c>
       <c r="S8" t="n">
-        <v>7918</v>
+        <v>1105</v>
       </c>
       <c r="T8" t="n">
-        <v>7893.5</v>
+        <v>1174.8</v>
       </c>
       <c r="U8" t="n">
-        <v>7821.25</v>
+        <v>1169.05</v>
       </c>
       <c r="V8" t="n">
-        <v>6090.5</v>
+        <v>1042.083333333333</v>
       </c>
       <c r="W8" t="n">
-        <v>140.3120352777469</v>
+        <v>-12.86417730316748</v>
       </c>
       <c r="X8" t="n">
-        <v>342.9687652512529</v>
+        <v>21.91267007672974</v>
       </c>
       <c r="Y8" t="n">
-        <v>-202.6567299735061</v>
+        <v>-34.77684737989722</v>
       </c>
       <c r="Z8" t="n">
-        <v>-162.3819064662263</v>
+        <v>-32.18600114940467</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.2394366197183098</v>
+        <v>0.1223404255319149</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.8177399756986634</v>
+        <v>0.1774553571428572</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.2042856392095251</v>
+        <v>0.122233925197055</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.7526664104105465</v>
+        <v>0.1453016203660589</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.5483807712010214</v>
+        <v>-0.02306769516900387</v>
       </c>
       <c r="AG8" t="n">
-        <v>88</v>
+        <v>82.35294117647058</v>
       </c>
       <c r="AH8" t="n">
-        <v>98</v>
+        <v>80.3921568627451</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
@@ -1623,17 +1617,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1642,7 +1636,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>52.2</v>
+        <v>50.58823529411765</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1651,15 +1645,15 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2657000</v>
+        <v>819000</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="K9" t="b">
         <v>0</v>
@@ -1668,93 +1662,91 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1857000</v>
+        <v>769000</v>
       </c>
       <c r="N9" t="n">
-        <v>800000</v>
+        <v>50000</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4308023694130318</v>
+        <v>0.06501950585175553</v>
       </c>
       <c r="P9" t="n">
-        <v>258.5</v>
+        <v>2290</v>
       </c>
       <c r="Q9" t="n">
-        <v>258.5</v>
+        <v>2290</v>
       </c>
       <c r="R9" t="n">
-        <v>23753240</v>
+        <v>1436269</v>
       </c>
       <c r="S9" t="n">
-        <v>269.1</v>
+        <v>2237</v>
       </c>
       <c r="T9" t="n">
-        <v>255.45</v>
+        <v>2368.25</v>
       </c>
       <c r="U9" t="n">
-        <v>253.575</v>
+        <v>2358.25</v>
       </c>
       <c r="V9" t="n">
-        <v>227.675</v>
+        <v>2035.513899739583</v>
       </c>
       <c r="W9" t="n">
-        <v>6.416139638692187</v>
+        <v>-13.3989724262965</v>
       </c>
       <c r="X9" t="n">
-        <v>6.022033229720711</v>
+        <v>4.965872605038653</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.3941064089714752</v>
+        <v>-18.36484503133515</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.892489559765102</v>
+        <v>-26.14045885017151</v>
       </c>
       <c r="AA9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.1696832579185521</v>
+        <v>0.09569377990430628</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.230952380952381</v>
+        <v>0.5848892928341591</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.1345322774097675</v>
+        <v>0.09558727956944635</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.1658788156642641</v>
+        <v>0.5527355560573608</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.03134653825449663</v>
+        <v>-0.4571482764879145</v>
       </c>
       <c r="AG9" t="n">
-        <v>84</v>
+        <v>74.50980392156863</v>
       </c>
       <c r="AH9" t="n">
-        <v>74</v>
+        <v>94.11764705882352</v>
       </c>
       <c r="AI9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="b">
         <v>1</v>
       </c>
       <c r="AK9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>2500.68</v>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
@@ -1765,17 +1757,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1784,7 +1776,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>52.2</v>
+        <v>48.62745098039216</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1793,24 +1785,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>7224000</v>
+        <v>1000</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="K10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="b">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>7224000</v>
+        <v>1000</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1819,61 +1811,61 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1615</v>
+        <v>288</v>
       </c>
       <c r="Q10" t="n">
-        <v>1615</v>
+        <v>288</v>
       </c>
       <c r="R10" t="n">
-        <v>10612264</v>
+        <v>20130541</v>
       </c>
       <c r="S10" t="n">
-        <v>1673</v>
+        <v>293.8</v>
       </c>
       <c r="T10" t="n">
-        <v>1572.75</v>
+        <v>242.525</v>
       </c>
       <c r="U10" t="n">
-        <v>1560.5</v>
+        <v>237.325</v>
       </c>
       <c r="V10" t="n">
-        <v>1459.75</v>
+        <v>198.1333333333333</v>
       </c>
       <c r="W10" t="n">
-        <v>45.02341109165354</v>
+        <v>22.18902934147718</v>
       </c>
       <c r="X10" t="n">
-        <v>59.69238685971835</v>
+        <v>19.20057805293116</v>
       </c>
       <c r="Y10" t="n">
-        <v>-14.6689757680648</v>
+        <v>2.988451288546017</v>
       </c>
       <c r="Z10" t="n">
-        <v>-5.62807449069809</v>
+        <v>5.0885478524633</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.1788321167883211</v>
+        <v>0.5652173913043479</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.7349397590361446</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.1436811362795365</v>
+        <v>0.565110890969488</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.2426187424041908</v>
+        <v>0.7027860222593463</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.0989376061246543</v>
+        <v>-0.1376751312898583</v>
       </c>
       <c r="AG10" t="n">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="AH10" t="n">
-        <v>80</v>
+        <v>96.07843137254902</v>
       </c>
       <c r="AI10" t="b">
         <v>1</v>
@@ -1882,19 +1874,21 @@
         <v>1</v>
       </c>
       <c r="AK10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM10" t="b">
         <v>0</v>
       </c>
       <c r="AN10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>1782.96</v>
+        <v>0</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
@@ -1905,17 +1899,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1924,24 +1918,24 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>51.4</v>
+        <v>48.62745098039215</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>8937000</v>
+        <v>12671000</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K11" t="b">
         <v>1</v>
@@ -1950,76 +1944,76 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>8937000</v>
+        <v>12392000</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>279000</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>0.02251452550032279</v>
       </c>
       <c r="P11" t="n">
-        <v>1355</v>
+        <v>2405</v>
       </c>
       <c r="Q11" t="n">
-        <v>1355</v>
+        <v>2405</v>
       </c>
       <c r="R11" t="n">
-        <v>8990416</v>
+        <v>21297866</v>
       </c>
       <c r="S11" t="n">
-        <v>1402</v>
+        <v>2435</v>
       </c>
       <c r="T11" t="n">
-        <v>1320</v>
+        <v>2492</v>
       </c>
       <c r="U11" t="n">
-        <v>1306.5</v>
+        <v>2493</v>
       </c>
       <c r="V11" t="n">
-        <v>1189.416666666667</v>
+        <v>2417.065966796875</v>
       </c>
       <c r="W11" t="n">
-        <v>41.30080840777782</v>
+        <v>-16.008714975359</v>
       </c>
       <c r="X11" t="n">
-        <v>63.62982051017949</v>
+        <v>6.284409725025386</v>
       </c>
       <c r="Y11" t="n">
-        <v>-22.32901210240167</v>
+        <v>-22.29312470038438</v>
       </c>
       <c r="Z11" t="n">
-        <v>-15.92441011774856</v>
+        <v>-21.81617308668295</v>
       </c>
       <c r="AA11" t="b">
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.2488479262672811</v>
+        <v>-0.008247422680412342</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.1386554621848739</v>
+        <v>0.002943605599203813</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.2136969457584965</v>
+        <v>-0.008353923015272269</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.07358189689675698</v>
+        <v>-0.02921013117759452</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.1401150488617395</v>
+        <v>0.02085620816232225</v>
       </c>
       <c r="AG11" t="n">
-        <v>90</v>
+        <v>50.98039215686274</v>
       </c>
       <c r="AH11" t="n">
-        <v>60</v>
+        <v>41.17647058823529</v>
       </c>
       <c r="AI11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="b">
         <v>0</v>
@@ -2031,31 +2025,29 @@
         <v>0</v>
       </c>
       <c r="AN11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO11" t="n">
-        <v>1607.03</v>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>2659.93</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>2551.58</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2064,20 +2056,20 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>48.2</v>
+        <v>46.47058823529412</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>769000</v>
+        <v>852000</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
@@ -2090,70 +2082,70 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>649000</v>
+        <v>852000</v>
       </c>
       <c r="N12" t="n">
-        <v>120000</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1848998459167951</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2250</v>
+        <v>7745</v>
       </c>
       <c r="Q12" t="n">
-        <v>2250</v>
+        <v>7745</v>
       </c>
       <c r="R12" t="n">
-        <v>1747205</v>
+        <v>1404603</v>
       </c>
       <c r="S12" t="n">
-        <v>2208</v>
+        <v>7794</v>
       </c>
       <c r="T12" t="n">
-        <v>2343.75</v>
+        <v>8038.75</v>
       </c>
       <c r="U12" t="n">
-        <v>2332.5</v>
+        <v>7976.5</v>
       </c>
       <c r="V12" t="n">
-        <v>2005.600705973307</v>
+        <v>6204.25</v>
       </c>
       <c r="W12" t="n">
-        <v>-27.82926529920223</v>
+        <v>81.65806719286047</v>
       </c>
       <c r="X12" t="n">
-        <v>16.09219857541557</v>
+        <v>253.8900260653598</v>
       </c>
       <c r="Y12" t="n">
-        <v>-43.9214638746178</v>
+        <v>-172.2319588724994</v>
       </c>
       <c r="Z12" t="n">
-        <v>-56.51359028373258</v>
+        <v>-184.0829978710731</v>
       </c>
       <c r="AA12" t="b">
         <v>1</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.1111111111111112</v>
+        <v>0.1915384615384614</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.6012255213039355</v>
+        <v>0.7682648401826484</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.07596013060232654</v>
+        <v>0.1914319612036015</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.5361519560158186</v>
+        <v>0.7361111034058501</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.460191825413492</v>
+        <v>-0.5446791422022486</v>
       </c>
       <c r="AG12" t="n">
-        <v>70</v>
+        <v>92.15686274509804</v>
       </c>
       <c r="AH12" t="n">
-        <v>92</v>
+        <v>98.0392156862745</v>
       </c>
       <c r="AI12" t="b">
         <v>0</v>
@@ -2183,17 +2175,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2202,108 +2194,108 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>48</v>
+        <v>46.47058823529412</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1000</v>
+        <v>6351450</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="K13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="b">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1000</v>
+        <v>5151450</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1200000</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>0.2329441225286084</v>
       </c>
       <c r="P13" t="n">
-        <v>298.5</v>
+        <v>259.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>298.5</v>
+        <v>259.5</v>
       </c>
       <c r="R13" t="n">
-        <v>39659568</v>
+        <v>14912383</v>
       </c>
       <c r="S13" t="n">
-        <v>285.6</v>
+        <v>273.3</v>
       </c>
       <c r="T13" t="n">
-        <v>232</v>
+        <v>293.65</v>
       </c>
       <c r="U13" t="n">
-        <v>226.1</v>
+        <v>293.925</v>
       </c>
       <c r="V13" t="n">
-        <v>194.0583333333333</v>
+        <v>264.7578420003255</v>
       </c>
       <c r="W13" t="n">
-        <v>24.41714981393159</v>
+        <v>-5.665770075617104</v>
       </c>
       <c r="X13" t="n">
-        <v>17.18132826767883</v>
+        <v>1.22878921339309</v>
       </c>
       <c r="Y13" t="n">
-        <v>7.235821546252758</v>
+        <v>-6.894559289010194</v>
       </c>
       <c r="Z13" t="n">
-        <v>7.992130067756985</v>
+        <v>-6.333872622255273</v>
       </c>
       <c r="AA13" t="b">
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.6537396121883656</v>
+        <v>-0.02075471698113207</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.7874251497005988</v>
+        <v>-0.04365195046372772</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.618588631679581</v>
+        <v>-0.020861217315992</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.7223515844124819</v>
+        <v>-0.07580568724052605</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.1037629527329009</v>
+        <v>0.05494446992453406</v>
       </c>
       <c r="AG13" t="n">
-        <v>100</v>
+        <v>45.09803921568628</v>
       </c>
       <c r="AH13" t="n">
-        <v>96</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="AI13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="b">
         <v>0</v>
@@ -2311,31 +2303,25 @@
       <c r="AN13" t="b">
         <v>0</v>
       </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="n">
+        <v>327.45</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2344,24 +2330,24 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>46.8</v>
+        <v>46.07843137254902</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>981000</v>
+        <v>6343000</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="K14" t="b">
         <v>0</v>
@@ -2370,73 +2356,73 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>981000</v>
+        <v>6303000</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>0.00634618435665556</v>
       </c>
       <c r="P14" t="n">
-        <v>1570</v>
+        <v>3325</v>
       </c>
       <c r="Q14" t="n">
-        <v>1570</v>
+        <v>3325</v>
       </c>
       <c r="R14" t="n">
-        <v>5916466</v>
+        <v>2738048</v>
       </c>
       <c r="S14" t="n">
-        <v>1642</v>
+        <v>3272</v>
       </c>
       <c r="T14" t="n">
-        <v>1564.25</v>
+        <v>3416.25</v>
       </c>
       <c r="U14" t="n">
-        <v>1546.75</v>
+        <v>3409.25</v>
       </c>
       <c r="V14" t="n">
-        <v>1279.55</v>
+        <v>3126.095308430989</v>
       </c>
       <c r="W14" t="n">
-        <v>44.2140083672773</v>
+        <v>-29.48998274530686</v>
       </c>
       <c r="X14" t="n">
-        <v>69.49502928741234</v>
+        <v>-2.706712031776206</v>
       </c>
       <c r="Y14" t="n">
-        <v>-25.28102092013503</v>
+        <v>-26.78327071353065</v>
       </c>
       <c r="Z14" t="n">
-        <v>-19.03649200108951</v>
+        <v>-36.6965163567199</v>
       </c>
       <c r="AA14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.2868852459016393</v>
+        <v>0.04395604395604402</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.5971515768056967</v>
+        <v>0.3707888668898909</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.2517342653928547</v>
+        <v>0.04384954362118409</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.5320780115175798</v>
+        <v>0.3386351301130925</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.2803437461247251</v>
+        <v>-0.2947855864919084</v>
       </c>
       <c r="AG14" t="n">
-        <v>98</v>
+        <v>62.74509803921568</v>
       </c>
       <c r="AH14" t="n">
-        <v>90</v>
+        <v>88.23529411764706</v>
       </c>
       <c r="AI14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="b">
         <v>1</v>
@@ -2448,13 +2434,13 @@
         <v>0</v>
       </c>
       <c r="AM14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO14" t="n">
-        <v>1855.74</v>
+        <v>3630.9</v>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
@@ -2465,17 +2451,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2484,7 +2470,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>46.6</v>
+        <v>45.09803921568628</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2493,15 +2479,15 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2502000</v>
+        <v>981000</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K15" t="b">
         <v>0</v>
@@ -2510,7 +2496,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2502000</v>
+        <v>981000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2519,64 +2505,64 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>6730</v>
+        <v>1545</v>
       </c>
       <c r="Q15" t="n">
-        <v>6730</v>
+        <v>1545</v>
       </c>
       <c r="R15" t="n">
-        <v>1099414</v>
+        <v>3669863</v>
       </c>
       <c r="S15" t="n">
-        <v>6943</v>
+        <v>1569</v>
       </c>
       <c r="T15" t="n">
-        <v>6570.5</v>
+        <v>1587.75</v>
       </c>
       <c r="U15" t="n">
-        <v>6499.5</v>
+        <v>1575.5</v>
       </c>
       <c r="V15" t="n">
-        <v>5422.083333333333</v>
+        <v>1294.8</v>
       </c>
       <c r="W15" t="n">
-        <v>189.7397046221449</v>
+        <v>20.71374624538976</v>
       </c>
       <c r="X15" t="n">
-        <v>281.7342017135097</v>
+        <v>53.32925441014079</v>
       </c>
       <c r="Y15" t="n">
-        <v>-91.99449709136474</v>
+        <v>-32.61550816475103</v>
       </c>
       <c r="Z15" t="n">
-        <v>-66.55202090973779</v>
+        <v>-32.04759134433519</v>
       </c>
       <c r="AA15" t="b">
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.2674199623352165</v>
+        <v>0.1884615384615385</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.9238029410664506</v>
+        <v>0.4372093023255814</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.2322689818264319</v>
+        <v>0.1883550381266785</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.8587293757783336</v>
+        <v>0.4050555655487831</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.6264603939519018</v>
+        <v>-0.2167005274221045</v>
       </c>
       <c r="AG15" t="n">
-        <v>94</v>
+        <v>90.19607843137256</v>
       </c>
       <c r="AH15" t="n">
-        <v>100</v>
+        <v>90.19607843137256</v>
       </c>
       <c r="AI15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="b">
         <v>1</v>
@@ -2591,11 +2577,9 @@
         <v>0</v>
       </c>
       <c r="AN15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>7766.42</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO15" t="inlineStr"/>
       <c r="AP15" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -2605,17 +2589,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2624,7 +2608,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>45</v>
+        <v>44.31372549019608</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2633,15 +2617,15 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>6303000</v>
+        <v>8348000</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K16" t="b">
         <v>1</v>
@@ -2650,7 +2634,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>6303000</v>
+        <v>8348000</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2659,61 +2643,61 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>3315</v>
+        <v>660</v>
       </c>
       <c r="Q16" t="n">
-        <v>3315</v>
+        <v>660</v>
       </c>
       <c r="R16" t="n">
-        <v>3569214</v>
+        <v>12369824</v>
       </c>
       <c r="S16" t="n">
-        <v>3276</v>
+        <v>684.2</v>
       </c>
       <c r="T16" t="n">
-        <v>3402</v>
+        <v>704.2</v>
       </c>
       <c r="U16" t="n">
-        <v>3392</v>
+        <v>701.9</v>
       </c>
       <c r="V16" t="n">
-        <v>3093.299527994792</v>
+        <v>633.6333333333333</v>
       </c>
       <c r="W16" t="n">
-        <v>-35.3894972052758</v>
+        <v>-1.74079577342809</v>
       </c>
       <c r="X16" t="n">
-        <v>13.16323473578665</v>
+        <v>13.70184941527172</v>
       </c>
       <c r="Y16" t="n">
-        <v>-48.55273194106245</v>
+        <v>-15.44264518869981</v>
       </c>
       <c r="Z16" t="n">
-        <v>-62.50287942092719</v>
+        <v>-14.31269808974348</v>
       </c>
       <c r="AA16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.0642054574638844</v>
+        <v>0.07491856677524433</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.437355921588952</v>
+        <v>0.01694915254237284</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.02905447695509977</v>
+        <v>0.07481206644038441</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.3722823563008351</v>
+        <v>-0.0152045842344255</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.3432278793457353</v>
+        <v>0.09001665067480991</v>
       </c>
       <c r="AG16" t="n">
-        <v>60</v>
+        <v>68.62745098039215</v>
       </c>
       <c r="AH16" t="n">
-        <v>86</v>
+        <v>47.05882352941176</v>
       </c>
       <c r="AI16" t="b">
         <v>0</v>
@@ -2728,14 +2712,12 @@
         <v>0</v>
       </c>
       <c r="AM16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>3865.29</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO16" t="inlineStr"/>
       <c r="AP16" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -2745,17 +2727,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2764,7 +2746,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>44.4</v>
+        <v>41.1764705882353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2773,24 +2755,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>8348000</v>
+        <v>1000</v>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="n">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="K17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="b">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>8348000</v>
+        <v>1000</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2799,64 +2781,64 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>671</v>
+        <v>547</v>
       </c>
       <c r="Q17" t="n">
-        <v>671</v>
+        <v>547</v>
       </c>
       <c r="R17" t="n">
-        <v>18315373</v>
+        <v>29732029</v>
       </c>
       <c r="S17" t="n">
-        <v>718.6</v>
+        <v>547.4</v>
       </c>
       <c r="T17" t="n">
-        <v>698.65</v>
+        <v>533.2</v>
       </c>
       <c r="U17" t="n">
-        <v>694.7</v>
+        <v>529.65</v>
       </c>
       <c r="V17" t="n">
-        <v>633.2166666666667</v>
+        <v>491.275</v>
       </c>
       <c r="W17" t="n">
-        <v>8.745163602010734</v>
+        <v>9.100039042176491</v>
       </c>
       <c r="X17" t="n">
-        <v>21.14068523488255</v>
+        <v>14.65027730803168</v>
       </c>
       <c r="Y17" t="n">
-        <v>-12.39552163287181</v>
+        <v>-5.550238265855194</v>
       </c>
       <c r="Z17" t="n">
-        <v>-8.018810931805895</v>
+        <v>-5.172832198214778</v>
       </c>
       <c r="AA17" t="b">
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.1334459459459461</v>
+        <v>0.1491596638655461</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.0600315955766193</v>
+        <v>0.0810276679841897</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.09829496543716143</v>
+        <v>0.1490531635306862</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0.005041969711497618</v>
+        <v>0.04887393120739136</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.103336935148659</v>
+        <v>0.1001792323232948</v>
       </c>
       <c r="AG17" t="n">
-        <v>72</v>
+        <v>86.27450980392157</v>
       </c>
       <c r="AH17" t="n">
-        <v>44</v>
+        <v>62.74509803921568</v>
       </c>
       <c r="AI17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ17" t="b">
         <v>1</v>
@@ -2871,9 +2853,11 @@
         <v>0</v>
       </c>
       <c r="AN17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>610.45</v>
+      </c>
       <c r="AP17" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -2883,17 +2867,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2902,99 +2886,99 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>43.2</v>
+        <v>40.3921568627451</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>12392000</v>
+        <v>501000</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="K18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="b">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>12188000</v>
+        <v>501000</v>
       </c>
       <c r="N18" t="n">
-        <v>204000</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0.01673777486051854</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2420</v>
+        <v>243.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>2420</v>
+        <v>243.5</v>
       </c>
       <c r="R18" t="n">
-        <v>33490270</v>
+        <v>30958244</v>
       </c>
       <c r="S18" t="n">
-        <v>2476</v>
+        <v>243.6</v>
       </c>
       <c r="T18" t="n">
-        <v>2491</v>
+        <v>236.5</v>
       </c>
       <c r="U18" t="n">
-        <v>2488.9</v>
+        <v>235.25</v>
       </c>
       <c r="V18" t="n">
-        <v>2416.497591145833</v>
+        <v>222.7083333333333</v>
       </c>
       <c r="W18" t="n">
-        <v>-3.262306824247389</v>
+        <v>3.675449863078512</v>
       </c>
       <c r="X18" t="n">
-        <v>17.31173417264522</v>
+        <v>4.028286368827454</v>
       </c>
       <c r="Y18" t="n">
-        <v>-20.57404099689261</v>
+        <v>-0.3528365057489413</v>
       </c>
       <c r="Z18" t="n">
-        <v>-15.91550092530764</v>
+        <v>0.03681192755690965</v>
       </c>
       <c r="AA18" t="b">
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.01766190075693852</v>
+        <v>0.1144164759725401</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.007105186261707974</v>
+        <v>0.1378504672897196</v>
       </c>
       <c r="AD18" t="n">
-        <v>-0.0174890797518461</v>
+        <v>0.1143099756376802</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0.05796837902640894</v>
+        <v>0.1056967305129213</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.04047929927456284</v>
+        <v>0.008613245124758917</v>
       </c>
       <c r="AG18" t="n">
-        <v>38</v>
+        <v>80.3921568627451</v>
       </c>
       <c r="AH18" t="n">
-        <v>30</v>
+        <v>72.54901960784314</v>
       </c>
       <c r="AI18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ18" t="b">
         <v>1</v>
@@ -3012,7 +2996,7 @@
         <v>1</v>
       </c>
       <c r="AO18" t="n">
-        <v>2652.32</v>
+        <v>247.88</v>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
@@ -3023,17 +3007,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3042,24 +3026,24 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>42.59999999999999</v>
+        <v>38.82352941176471</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5151450</v>
+        <v>121000</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="K19" t="b">
         <v>0</v>
@@ -3068,70 +3052,70 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>4143450</v>
+        <v>121000</v>
       </c>
       <c r="N19" t="n">
-        <v>1008000</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2432755312601817</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>275</v>
+        <v>1320</v>
       </c>
       <c r="Q19" t="n">
-        <v>275</v>
+        <v>1320</v>
       </c>
       <c r="R19" t="n">
-        <v>16768982</v>
+        <v>2504403</v>
       </c>
       <c r="S19" t="n">
-        <v>289.7</v>
+        <v>1413</v>
       </c>
       <c r="T19" t="n">
-        <v>293.825</v>
+        <v>1388.75</v>
       </c>
       <c r="U19" t="n">
-        <v>292.925</v>
+        <v>1383.25</v>
       </c>
       <c r="V19" t="n">
-        <v>265.2283131917318</v>
+        <v>1262.461206054687</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.5994197869163145</v>
+        <v>13.51938467465766</v>
       </c>
       <c r="X19" t="n">
-        <v>4.535897191209457</v>
+        <v>44.57917000678403</v>
       </c>
       <c r="Y19" t="n">
-        <v>-5.135316978125772</v>
+        <v>-31.05978533212637</v>
       </c>
       <c r="Z19" t="n">
-        <v>-4.22195394856811</v>
+        <v>-19.92451621570898</v>
       </c>
       <c r="AA19" t="b">
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.07003891050583655</v>
+        <v>0.09090909090909083</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.03889851301655267</v>
+        <v>0.3041746242042211</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.03488792999705193</v>
+        <v>0.0908025905742309</v>
       </c>
       <c r="AE19" t="n">
-        <v>-0.02617505227156425</v>
+        <v>0.2720208874274228</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.06106298226861617</v>
+        <v>-0.1812182968531919</v>
       </c>
       <c r="AG19" t="n">
-        <v>62</v>
+        <v>70.58823529411765</v>
       </c>
       <c r="AH19" t="n">
-        <v>40</v>
+        <v>86.27450980392157</v>
       </c>
       <c r="AI19" t="b">
         <v>0</v>
@@ -3161,17 +3145,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3180,7 +3164,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>40.8</v>
+        <v>38.82352941176471</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3189,15 +3173,15 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>121000</v>
+        <v>1000</v>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="K20" t="b">
         <v>0</v>
@@ -3206,7 +3190,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>121000</v>
+        <v>1000</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -3215,64 +3199,64 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1410</v>
+        <v>99.09999847412109</v>
       </c>
       <c r="Q20" t="n">
-        <v>1410</v>
+        <v>99.09999847412109</v>
       </c>
       <c r="R20" t="n">
-        <v>2852725</v>
+        <v>12418893</v>
       </c>
       <c r="S20" t="n">
-        <v>1523</v>
+        <v>105.9199996948242</v>
       </c>
       <c r="T20" t="n">
-        <v>1374</v>
+        <v>112.9799999237061</v>
       </c>
       <c r="U20" t="n">
-        <v>1364.25</v>
+        <v>112.3599998474121</v>
       </c>
       <c r="V20" t="n">
-        <v>1251.276076253255</v>
+        <v>95.97166659037272</v>
       </c>
       <c r="W20" t="n">
-        <v>44.93885460905562</v>
+        <v>-1.177354768187755</v>
       </c>
       <c r="X20" t="n">
-        <v>57.32524539374285</v>
+        <v>3.174555950533045</v>
       </c>
       <c r="Y20" t="n">
-        <v>-12.38639078468723</v>
+        <v>-4.351910718720799</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.2166883774044663</v>
+        <v>-4.031213786765679</v>
       </c>
       <c r="AA20" t="b">
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.1604938271604939</v>
+        <v>0.1430219372819748</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.430784538209011</v>
+        <v>0.009164985273403481</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.1253428466517092</v>
+        <v>0.1429154369471148</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.3657109729208941</v>
+        <v>-0.02298875150339486</v>
       </c>
       <c r="AF20" t="n">
-        <v>-0.2403681262691848</v>
+        <v>0.1659041884505097</v>
       </c>
       <c r="AG20" t="n">
-        <v>80</v>
+        <v>84.31372549019608</v>
       </c>
       <c r="AH20" t="n">
-        <v>84</v>
+        <v>45.09803921568628</v>
       </c>
       <c r="AI20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="b">
         <v>1</v>
@@ -3287,11 +3271,9 @@
         <v>0</v>
       </c>
       <c r="AN20" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>1551</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO20" t="inlineStr"/>
       <c r="AP20" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -3301,17 +3283,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3320,7 +3302,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>39.6</v>
+        <v>37.84313725490197</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3329,7 +3311,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -3337,7 +3319,7 @@
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="K21" t="b">
         <v>0</v>
@@ -3355,61 +3337,61 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>105.5</v>
+        <v>3640</v>
       </c>
       <c r="Q21" t="n">
-        <v>105.5</v>
+        <v>3640</v>
       </c>
       <c r="R21" t="n">
-        <v>19016531</v>
+        <v>1172944</v>
       </c>
       <c r="S21" t="n">
-        <v>113.4</v>
+        <v>3737</v>
       </c>
       <c r="T21" t="n">
-        <v>111.5899997711182</v>
+        <v>3862.5</v>
       </c>
       <c r="U21" t="n">
-        <v>110.5349998474121</v>
+        <v>3845.25</v>
       </c>
       <c r="V21" t="n">
-        <v>95.91499989827474</v>
+        <v>3755.288911946614</v>
       </c>
       <c r="W21" t="n">
-        <v>1.714176809923558</v>
+        <v>-38.10545151630822</v>
       </c>
       <c r="X21" t="n">
-        <v>5.270337076904664</v>
+        <v>29.06714154035313</v>
       </c>
       <c r="Y21" t="n">
-        <v>-3.556160266981106</v>
+        <v>-67.17259305666136</v>
       </c>
       <c r="Z21" t="n">
-        <v>-2.843717107570888</v>
+        <v>-59.6776007272012</v>
       </c>
       <c r="AA21" t="b">
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.249999977401083</v>
+        <v>0.1047040971168438</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.01442307692307687</v>
+        <v>0.04514260318279262</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.2148489968922984</v>
+        <v>0.1045975967819839</v>
       </c>
       <c r="AE21" t="n">
-        <v>-0.05065048836504005</v>
+        <v>0.01298886640599428</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.2654994852573385</v>
+        <v>0.0916087303759896</v>
       </c>
       <c r="AG21" t="n">
-        <v>92</v>
+        <v>78.43137254901961</v>
       </c>
       <c r="AH21" t="n">
-        <v>36</v>
+        <v>52.94117647058824</v>
       </c>
       <c r="AI21" t="b">
         <v>0</v>
@@ -3439,17 +3421,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3458,102 +3440,102 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>36</v>
+        <v>36.27450980392157</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>7582000</v>
+        <v>3921000</v>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="K22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" t="b">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>7507000</v>
+        <v>3921000</v>
       </c>
       <c r="N22" t="n">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>0.009990675369654988</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1635</v>
+        <v>90.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>1635</v>
+        <v>90.5</v>
       </c>
       <c r="R22" t="n">
-        <v>7401193</v>
+        <v>4910073</v>
       </c>
       <c r="S22" t="n">
-        <v>1745</v>
+        <v>91.84000091552734</v>
       </c>
       <c r="T22" t="n">
-        <v>1848.25</v>
+        <v>87.4550006866455</v>
       </c>
       <c r="U22" t="n">
-        <v>1850</v>
+        <v>87.04000053405761</v>
       </c>
       <c r="V22" t="n">
-        <v>1778.083333333333</v>
+        <v>84.75666681925456</v>
       </c>
       <c r="W22" t="n">
-        <v>-39.69044453345396</v>
+        <v>1.89408881446407</v>
       </c>
       <c r="X22" t="n">
-        <v>9.73698412134852</v>
+        <v>1.951049148829624</v>
       </c>
       <c r="Y22" t="n">
-        <v>-49.42742865480248</v>
+        <v>-0.05696033436555425</v>
       </c>
       <c r="Z22" t="n">
-        <v>-43.51850691221304</v>
+        <v>0.2311357672828671</v>
       </c>
       <c r="AA22" t="b">
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>-0.02095808383233533</v>
+        <v>0.1009732768844744</v>
       </c>
       <c r="AC22" t="n">
-        <v>-0.1089918256130791</v>
+        <v>0.007795065973870141</v>
       </c>
       <c r="AD22" t="n">
-        <v>-0.05610906434111995</v>
+        <v>0.1008667765496145</v>
       </c>
       <c r="AE22" t="n">
-        <v>-0.174065390901196</v>
+        <v>-0.0243586708029282</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.117956326560076</v>
+        <v>0.1252254473525427</v>
       </c>
       <c r="AG22" t="n">
-        <v>26</v>
+        <v>76.47058823529412</v>
       </c>
       <c r="AH22" t="n">
-        <v>14</v>
+        <v>43.13725490196079</v>
       </c>
       <c r="AI22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK22" t="b">
         <v>0</v>
@@ -3565,17 +3547,21 @@
         <v>0</v>
       </c>
       <c r="AN22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO22" t="inlineStr"/>
-      <c r="AP22" t="n">
-        <v>1934.47</v>
+        <v>1</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>91.22</v>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3594,7 +3580,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>35.4</v>
+        <v>34.31372549019608</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3603,7 +3589,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -3629,67 +3615,67 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>567</v>
+        <v>523</v>
       </c>
       <c r="Q23" t="n">
-        <v>567</v>
+        <v>523</v>
       </c>
       <c r="R23" t="n">
-        <v>35134462</v>
+        <v>42890540</v>
       </c>
       <c r="S23" t="n">
-        <v>600.4</v>
+        <v>564.8</v>
       </c>
       <c r="T23" t="n">
-        <v>587.75</v>
+        <v>587.35</v>
       </c>
       <c r="U23" t="n">
-        <v>586.25</v>
+        <v>587.65</v>
       </c>
       <c r="V23" t="n">
-        <v>577.275</v>
+        <v>571.575</v>
       </c>
       <c r="W23" t="n">
-        <v>3.588433587189684</v>
+        <v>-10.3544533195294</v>
       </c>
       <c r="X23" t="n">
-        <v>11.30163029441461</v>
+        <v>4.523624205409231</v>
       </c>
       <c r="Y23" t="n">
-        <v>-7.713196707224926</v>
+        <v>-14.87807752493863</v>
       </c>
       <c r="Z23" t="n">
-        <v>-4.110400952110989</v>
+        <v>-12.23394683108289</v>
       </c>
       <c r="AA23" t="b">
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.05586592178770955</v>
+        <v>-0.01134215500945179</v>
       </c>
       <c r="AC23" t="n">
-        <v>-0.1537313432835821</v>
+        <v>-0.2485632183908046</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.02071494127892493</v>
+        <v>-0.01144865534431172</v>
       </c>
       <c r="AE23" t="n">
-        <v>-0.218804908571699</v>
+        <v>-0.280716955167603</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.2395198498506239</v>
+        <v>0.2692682998232913</v>
       </c>
       <c r="AG23" t="n">
-        <v>54</v>
+        <v>49.01960784313725</v>
       </c>
       <c r="AH23" t="n">
-        <v>8</v>
+        <v>5.88235294117647</v>
       </c>
       <c r="AI23" t="b">
         <v>0</v>
       </c>
       <c r="AJ23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="b">
         <v>0</v>
@@ -3701,31 +3687,27 @@
         <v>0</v>
       </c>
       <c r="AN23" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>654.3200000000001</v>
-      </c>
-      <c r="AP23" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="AO23" t="inlineStr"/>
+      <c r="AP23" t="n">
+        <v>617.74</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3734,7 +3716,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>35</v>
+        <v>34.11764705882354</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3743,15 +3725,15 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>3921000</v>
+        <v>1000</v>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="K24" t="b">
         <v>0</v>
@@ -3760,7 +3742,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3921000</v>
+        <v>1000</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3769,73 +3751,73 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>92.30000305175781</v>
+        <v>5975</v>
       </c>
       <c r="Q24" t="n">
-        <v>92.30000305175781</v>
+        <v>5975</v>
       </c>
       <c r="R24" t="n">
-        <v>5900291</v>
+        <v>3147937</v>
       </c>
       <c r="S24" t="n">
-        <v>93.52000122070312</v>
+        <v>6421</v>
       </c>
       <c r="T24" t="n">
-        <v>86.62500038146973</v>
+        <v>6496.25</v>
       </c>
       <c r="U24" t="n">
-        <v>86.06000022888183</v>
+        <v>6498.5</v>
       </c>
       <c r="V24" t="n">
-        <v>84.74500020345052</v>
+        <v>5851.970617675781</v>
       </c>
       <c r="W24" t="n">
-        <v>2.474931803364896</v>
+        <v>-46.50900193349571</v>
       </c>
       <c r="X24" t="n">
-        <v>1.907505290600308</v>
+        <v>71.48572648232718</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.5674265127645881</v>
+        <v>-117.9947284158229</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.8148038556698953</v>
+        <v>-74.10685479439196</v>
       </c>
       <c r="AA24" t="b">
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.1395062105155285</v>
+        <v>-0.007475083056478371</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.01988953648351166</v>
+        <v>0.4564191261175792</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.1043552300067438</v>
+        <v>-0.007581583391338298</v>
       </c>
       <c r="AE24" t="n">
-        <v>-0.04518402880460526</v>
+        <v>0.4242653893407808</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.1495392588113491</v>
+        <v>-0.4318469727321191</v>
       </c>
       <c r="AG24" t="n">
-        <v>76</v>
+        <v>52.94117647058824</v>
       </c>
       <c r="AH24" t="n">
-        <v>38</v>
+        <v>92.15686274509804</v>
       </c>
       <c r="AI24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="b">
         <v>0</v>
@@ -3843,31 +3825,25 @@
       <c r="AN24" t="b">
         <v>0</v>
       </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
-      <c r="AP24" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+      <c r="AO24" t="inlineStr"/>
+      <c r="AP24" t="n">
+        <v>6978.68</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3876,24 +3852,24 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>34.8</v>
+        <v>33.52941176470588</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>654000</v>
+        <v>5163000</v>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="K25" t="b">
         <v>0</v>
@@ -3902,82 +3878,82 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1000</v>
+        <v>5163000</v>
       </c>
       <c r="N25" t="n">
-        <v>653000</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>653</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>472</v>
+        <v>19.60000038146973</v>
       </c>
       <c r="Q25" t="n">
-        <v>472</v>
+        <v>19.60000038146973</v>
       </c>
       <c r="R25" t="n">
-        <v>15256059</v>
+        <v>44575418</v>
       </c>
       <c r="S25" t="n">
-        <v>490.1</v>
+        <v>19.47999992370605</v>
       </c>
       <c r="T25" t="n">
-        <v>507.575</v>
+        <v>19.04000005722046</v>
       </c>
       <c r="U25" t="n">
-        <v>508.075</v>
+        <v>18.99500007629394</v>
       </c>
       <c r="V25" t="n">
-        <v>453.25</v>
+        <v>19.06166674296061</v>
       </c>
       <c r="W25" t="n">
-        <v>-6.440507620384835</v>
+        <v>0.1700411148033254</v>
       </c>
       <c r="X25" t="n">
-        <v>3.912199831102828</v>
+        <v>0.1008623084804349</v>
       </c>
       <c r="Y25" t="n">
-        <v>-10.35270745148766</v>
+        <v>0.06917880632289054</v>
       </c>
       <c r="Z25" t="n">
-        <v>-9.644600973429846</v>
+        <v>0.07021311150095588</v>
       </c>
       <c r="AA25" t="b">
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>-0.02074688796680502</v>
+        <v>0.04812831988295607</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.1964512040557669</v>
+        <v>0.03430077004542809</v>
       </c>
       <c r="AD25" t="n">
-        <v>-0.05589786847558964</v>
+        <v>0.04802181954809615</v>
       </c>
       <c r="AE25" t="n">
-        <v>0.13137763876765</v>
+        <v>0.00214703326862975</v>
       </c>
       <c r="AF25" t="n">
-        <v>-0.1872755072432396</v>
+        <v>0.0458747862794664</v>
       </c>
       <c r="AG25" t="n">
-        <v>28</v>
+        <v>64.70588235294117</v>
       </c>
       <c r="AH25" t="n">
-        <v>72</v>
+        <v>50.98039215686274</v>
       </c>
       <c r="AI25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM25" t="b">
         <v>0</v>
@@ -3985,25 +3961,31 @@
       <c r="AN25" t="b">
         <v>0</v>
       </c>
-      <c r="AO25" t="inlineStr"/>
-      <c r="AP25" t="n">
-        <v>547.45</v>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
+      </c>
+      <c r="AP25" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4012,7 +3994,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>34.6</v>
+        <v>33.13725490196079</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4021,15 +4003,15 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1000</v>
+        <v>2657000</v>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="K26" t="b">
         <v>0</v>
@@ -4038,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1000</v>
+        <v>2657000</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -4047,61 +4029,61 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>6400</v>
+        <v>247</v>
       </c>
       <c r="Q26" t="n">
-        <v>6400</v>
+        <v>247</v>
       </c>
       <c r="R26" t="n">
-        <v>4442616</v>
+        <v>16920521</v>
       </c>
       <c r="S26" t="n">
-        <v>6897</v>
+        <v>261.9</v>
       </c>
       <c r="T26" t="n">
-        <v>6497.5</v>
+        <v>257.325</v>
       </c>
       <c r="U26" t="n">
-        <v>6480.25</v>
+        <v>257.2</v>
       </c>
       <c r="V26" t="n">
-        <v>5782.742663574219</v>
+        <v>228.8416666666667</v>
       </c>
       <c r="W26" t="n">
-        <v>88.6731949735431</v>
+        <v>3.065859524234213</v>
       </c>
       <c r="X26" t="n">
-        <v>119.5111222848806</v>
+        <v>5.30477058369592</v>
       </c>
       <c r="Y26" t="n">
-        <v>-30.83792731133747</v>
+        <v>-2.238911059461707</v>
       </c>
       <c r="Z26" t="n">
-        <v>22.75795774951959</v>
+        <v>-0.6301395246374328</v>
       </c>
       <c r="AA26" t="b">
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.05697770437654825</v>
+        <v>0.01022494887525571</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.6206919149641232</v>
+        <v>0.1330275229357798</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.02182672386776363</v>
+        <v>0.01011844854039579</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.5556183496760063</v>
+        <v>0.1008737861589815</v>
       </c>
       <c r="AF26" t="n">
-        <v>-0.5337916258082427</v>
+        <v>-0.09075533761858567</v>
       </c>
       <c r="AG26" t="n">
-        <v>56.00000000000001</v>
+        <v>56.86274509803921</v>
       </c>
       <c r="AH26" t="n">
-        <v>94</v>
+        <v>70.58823529411765</v>
       </c>
       <c r="AI26" t="b">
         <v>0</v>
@@ -4122,7 +4104,7 @@
         <v>1</v>
       </c>
       <c r="AO26" t="n">
-        <v>6758.4</v>
+        <v>272.19</v>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
@@ -4133,17 +4115,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4152,7 +4134,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>33.4</v>
+        <v>32.54901960784314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4161,15 +4143,15 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1000</v>
+        <v>6264000</v>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="K27" t="b">
         <v>0</v>
@@ -4178,7 +4160,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1000</v>
+        <v>6264000</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -4187,64 +4169,64 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>3685</v>
+        <v>1970</v>
       </c>
       <c r="Q27" t="n">
-        <v>3685</v>
+        <v>1970</v>
       </c>
       <c r="R27" t="n">
-        <v>1554727</v>
+        <v>3909794</v>
       </c>
       <c r="S27" t="n">
-        <v>3956</v>
+        <v>1991</v>
       </c>
       <c r="T27" t="n">
-        <v>3826.75</v>
+        <v>1959</v>
       </c>
       <c r="U27" t="n">
-        <v>3810.25</v>
+        <v>1950.5</v>
       </c>
       <c r="V27" t="n">
-        <v>3750.121183268229</v>
+        <v>2055.482550048828</v>
       </c>
       <c r="W27" t="n">
-        <v>9.753653540335563</v>
+        <v>8.941430941387807</v>
       </c>
       <c r="X27" t="n">
-        <v>60.77968998631829</v>
+        <v>13.65461057340279</v>
       </c>
       <c r="Y27" t="n">
-        <v>-51.02603644598273</v>
+        <v>-4.713179632014981</v>
       </c>
       <c r="Z27" t="n">
-        <v>-25.21574529991035</v>
+        <v>-0.3407699140660494</v>
       </c>
       <c r="AA27" t="b">
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.09836065573770503</v>
+        <v>0.09444444444444455</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.06412674688517317</v>
+        <v>-0.1459812660562713</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.0632096752289204</v>
+        <v>0.09433794410958463</v>
       </c>
       <c r="AE27" t="n">
-        <v>-0.0009468184029437499</v>
+        <v>-0.1781350028330696</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.06415649363186415</v>
+        <v>0.2724729469426542</v>
       </c>
       <c r="AG27" t="n">
-        <v>68</v>
+        <v>72.54901960784314</v>
       </c>
       <c r="AH27" t="n">
-        <v>46</v>
+        <v>17.64705882352941</v>
       </c>
       <c r="AI27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ27" t="b">
         <v>1</v>
@@ -4262,7 +4244,7 @@
         <v>1</v>
       </c>
       <c r="AO27" t="n">
-        <v>4259.86</v>
+        <v>2025.16</v>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
@@ -4273,17 +4255,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4292,7 +4274,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>33.2</v>
+        <v>32.54901960784314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4301,15 +4283,15 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1000</v>
+        <v>4328000</v>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="K28" t="b">
         <v>0</v>
@@ -4318,7 +4300,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1000</v>
+        <v>4328000</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -4327,61 +4309,61 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>167.5</v>
+        <v>4945</v>
       </c>
       <c r="Q28" t="n">
-        <v>167.5</v>
+        <v>4945</v>
       </c>
       <c r="R28" t="n">
-        <v>9553134</v>
+        <v>1797434</v>
       </c>
       <c r="S28" t="n">
-        <v>172.2</v>
+        <v>5175</v>
       </c>
       <c r="T28" t="n">
-        <v>176.375</v>
+        <v>5297.25</v>
       </c>
       <c r="U28" t="n">
-        <v>175.65</v>
+        <v>5284.75</v>
       </c>
       <c r="V28" t="n">
-        <v>161.4333333333333</v>
+        <v>5321.183333333333</v>
       </c>
       <c r="W28" t="n">
-        <v>-0.2991385622451048</v>
+        <v>-59.96536124676004</v>
       </c>
       <c r="X28" t="n">
-        <v>3.505857435229376</v>
+        <v>40.94456185079647</v>
       </c>
       <c r="Y28" t="n">
-        <v>-3.804995997474481</v>
+        <v>-100.9099230975565</v>
       </c>
       <c r="Z28" t="n">
-        <v>-3.704980493044538</v>
+        <v>-79.58939541500392</v>
       </c>
       <c r="AA28" t="b">
         <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.09477124183006547</v>
+        <v>0.05324813631522907</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.07717041800643076</v>
+        <v>-0.02500883304627943</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.05962026132128084</v>
+        <v>0.05314163598036914</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.01209685271831384</v>
+        <v>-0.05716256982307777</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.047523408602967</v>
+        <v>0.1103042058034469</v>
       </c>
       <c r="AG28" t="n">
-        <v>66</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="AH28" t="n">
-        <v>50</v>
+        <v>35.29411764705883</v>
       </c>
       <c r="AI28" t="b">
         <v>0</v>
@@ -4411,17 +4393,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4430,7 +4412,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>31</v>
+        <v>30.78431372549019</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4439,15 +4421,15 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1000</v>
+        <v>654000</v>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="K29" t="b">
         <v>0</v>
@@ -4456,7 +4438,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1000</v>
+        <v>654000</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -4465,105 +4447,99 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>101.5</v>
+        <v>469.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>101.5</v>
+        <v>469.5</v>
       </c>
       <c r="R29" t="n">
-        <v>1874677</v>
+        <v>16981651</v>
       </c>
       <c r="S29" t="n">
-        <v>102.2</v>
+        <v>477.8</v>
       </c>
       <c r="T29" t="n">
-        <v>99.99500045776367</v>
+        <v>505.825</v>
       </c>
       <c r="U29" t="n">
-        <v>99.76500053405762</v>
+        <v>506.275</v>
       </c>
       <c r="V29" t="n">
-        <v>93.78500022888184</v>
+        <v>455.4916666666667</v>
       </c>
       <c r="W29" t="n">
-        <v>0.936456649952774</v>
+        <v>-9.203516729578951</v>
       </c>
       <c r="X29" t="n">
-        <v>0.6580228346008017</v>
+        <v>-0.4932252695210619</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.2784338153519723</v>
+        <v>-8.710291460057888</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.374712357990466</v>
+        <v>-8.911408942437436</v>
       </c>
       <c r="AA29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.0474716037325611</v>
+        <v>-0.01880877742946707</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.2515413305758387</v>
+        <v>0.1549815498154981</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.01232062322377647</v>
+        <v>-0.018915277764327</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.1864677652877218</v>
+        <v>0.1228278130386997</v>
       </c>
       <c r="AF29" t="n">
-        <v>-0.1741471420639453</v>
+        <v>-0.1417430908030267</v>
       </c>
       <c r="AG29" t="n">
-        <v>50</v>
+        <v>47.05882352941176</v>
       </c>
       <c r="AH29" t="n">
-        <v>76</v>
+        <v>76.47058823529412</v>
       </c>
       <c r="AI29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN29" t="b">
         <v>0</v>
       </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
-      <c r="AP29" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+      <c r="AO29" t="inlineStr"/>
+      <c r="AP29" t="n">
+        <v>537.74</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>慧洋-KY</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4572,7 +4548,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>29.8</v>
+        <v>29.6078431372549</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4581,15 +4557,15 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>957000</v>
+        <v>1000</v>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="K30" t="b">
         <v>0</v>
@@ -4598,7 +4574,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>957000</v>
+        <v>1000</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -4607,67 +4583,67 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>520</v>
+        <v>99.09999847412109</v>
       </c>
       <c r="Q30" t="n">
-        <v>520</v>
+        <v>99.09999847412109</v>
       </c>
       <c r="R30" t="n">
-        <v>9436955</v>
+        <v>1361326</v>
       </c>
       <c r="S30" t="n">
-        <v>553.4</v>
+        <v>101.0199996948242</v>
       </c>
       <c r="T30" t="n">
-        <v>572.25</v>
+        <v>99.72500038146973</v>
       </c>
       <c r="U30" t="n">
-        <v>571.7</v>
+        <v>99.87000045776367</v>
       </c>
       <c r="V30" t="n">
-        <v>539.4833333333333</v>
+        <v>94.35500017801921</v>
       </c>
       <c r="W30" t="n">
-        <v>-9.044624543949112</v>
+        <v>0.466288038997547</v>
       </c>
       <c r="X30" t="n">
-        <v>-2.607043269353877</v>
+        <v>0.6309088646569888</v>
       </c>
       <c r="Y30" t="n">
-        <v>-6.437581274595235</v>
+        <v>-0.1646208256594418</v>
       </c>
       <c r="Z30" t="n">
-        <v>-3.527263865473973</v>
+        <v>0.05616494588420051</v>
       </c>
       <c r="AA30" t="b">
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.0216110019646365</v>
+        <v>-0.02843138750861673</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.4565826330532212</v>
+        <v>0.2189421248979697</v>
       </c>
       <c r="AD30" t="n">
-        <v>-0.01353997854414812</v>
+        <v>-0.02853788784347666</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.3915090677651043</v>
+        <v>0.1867883881211714</v>
       </c>
       <c r="AF30" t="n">
-        <v>-0.4050490463092524</v>
+        <v>-0.215326275964648</v>
       </c>
       <c r="AG30" t="n">
-        <v>42</v>
+        <v>41.17647058823529</v>
       </c>
       <c r="AH30" t="n">
-        <v>88</v>
+        <v>82.35294117647058</v>
       </c>
       <c r="AI30" t="b">
         <v>0</v>
       </c>
       <c r="AJ30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="b">
         <v>0</v>
@@ -4682,28 +4658,26 @@
         <v>1</v>
       </c>
       <c r="AO30" t="n">
-        <v>592.8</v>
-      </c>
-      <c r="AP30" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>101.08</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>102.66</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4712,7 +4686,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>29.2</v>
+        <v>29.41176470588236</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4721,24 +4695,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>6264000</v>
+        <v>7582000</v>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="K31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" t="b">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>6264000</v>
+        <v>7582000</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -4747,95 +4721,89 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1980</v>
+        <v>1605</v>
       </c>
       <c r="Q31" t="n">
-        <v>1980</v>
+        <v>1605</v>
       </c>
       <c r="R31" t="n">
-        <v>3397911</v>
+        <v>9204085</v>
       </c>
       <c r="S31" t="n">
-        <v>2030</v>
+        <v>1659</v>
       </c>
       <c r="T31" t="n">
-        <v>1942.25</v>
+        <v>1840.75</v>
       </c>
       <c r="U31" t="n">
-        <v>1935.25</v>
+        <v>1844.75</v>
       </c>
       <c r="V31" t="n">
-        <v>2065.462481689453</v>
+        <v>1769.5</v>
       </c>
       <c r="W31" t="n">
-        <v>16.37825705961723</v>
+        <v>-61.08703293356007</v>
       </c>
       <c r="X31" t="n">
-        <v>14.9180979599235</v>
+        <v>-14.1110280811874</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.460159099693723</v>
+        <v>-46.97600485237267</v>
       </c>
       <c r="Z31" t="n">
-        <v>7.986258280959628</v>
+        <v>-48.41604395777102</v>
       </c>
       <c r="AA31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.07608695652173902</v>
+        <v>-0.04747774480712164</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0.1010482715689757</v>
+        <v>-0.1462765957446809</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.0409359760129544</v>
+        <v>-0.04758424514198156</v>
       </c>
       <c r="AE31" t="n">
-        <v>-0.1661218368570926</v>
+        <v>-0.1784303325214792</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.207057812870047</v>
+        <v>0.1308460873794977</v>
       </c>
       <c r="AG31" t="n">
-        <v>64</v>
+        <v>29.41176470588236</v>
       </c>
       <c r="AH31" t="n">
-        <v>16</v>
+        <v>15.68627450980392</v>
       </c>
       <c r="AI31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN31" t="b">
         <v>0</v>
       </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
-      <c r="AP31" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+      <c r="AO31" t="inlineStr"/>
+      <c r="AP31" t="n">
+        <v>1983.16</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4854,7 +4822,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>29.2</v>
+        <v>29.41176470588236</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4863,7 +4831,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -4871,7 +4839,7 @@
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="K32" t="b">
         <v>0</v>
@@ -4889,61 +4857,61 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>81.5</v>
+        <v>79.59999847412109</v>
       </c>
       <c r="Q32" t="n">
-        <v>81.5</v>
+        <v>79.59999847412109</v>
       </c>
       <c r="R32" t="n">
-        <v>1304419</v>
+        <v>1055568</v>
       </c>
       <c r="S32" t="n">
-        <v>81.3</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="T32" t="n">
-        <v>78.61499938964843</v>
+        <v>78.69499931335449</v>
       </c>
       <c r="U32" t="n">
-        <v>78.3699993133545</v>
+        <v>78.67999954223633</v>
       </c>
       <c r="V32" t="n">
-        <v>77.82943280537923</v>
+        <v>77.81705805460612</v>
       </c>
       <c r="W32" t="n">
-        <v>1.080440588135872</v>
+        <v>0.701974108434186</v>
       </c>
       <c r="X32" t="n">
-        <v>0.5948479954565822</v>
+        <v>0.6569963440146152</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.4855925926792897</v>
+        <v>0.0449777644195708</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.549063308314287</v>
+        <v>0.2036156298125609</v>
       </c>
       <c r="AA32" t="b">
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.06396868960166291</v>
+        <v>0.003783044272614777</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.01259318436978529</v>
+        <v>0.00199971015631295</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.02881770909287829</v>
+        <v>0.00367654393775485</v>
       </c>
       <c r="AE32" t="n">
-        <v>-0.05248038091833163</v>
+        <v>-0.03015402662048539</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.08129809001120991</v>
+        <v>0.03383057055824024</v>
       </c>
       <c r="AG32" t="n">
-        <v>57.99999999999999</v>
+        <v>54.90196078431373</v>
       </c>
       <c r="AH32" t="n">
-        <v>34</v>
+        <v>39.21568627450981</v>
       </c>
       <c r="AI32" t="b">
         <v>1</v>
@@ -4977,7 +4945,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4996,7 +4964,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>29</v>
+        <v>28.62745098039216</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5005,7 +4973,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -5013,7 +4981,7 @@
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K33" t="b">
         <v>0</v>
@@ -5031,67 +4999,67 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="Q33" t="n">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="R33" t="n">
-        <v>2240743</v>
+        <v>1433670</v>
       </c>
       <c r="S33" t="n">
-        <v>237.5</v>
+        <v>228.9</v>
       </c>
       <c r="T33" t="n">
-        <v>233.4</v>
+        <v>232.975</v>
       </c>
       <c r="U33" t="n">
-        <v>233</v>
+        <v>233.275</v>
       </c>
       <c r="V33" t="n">
-        <v>211.05</v>
+        <v>211.7416666666667</v>
       </c>
       <c r="W33" t="n">
-        <v>1.879829238086529</v>
+        <v>-1.134194617663923</v>
       </c>
       <c r="X33" t="n">
-        <v>3.948638719568165</v>
+        <v>2.385505469793294</v>
       </c>
       <c r="Y33" t="n">
-        <v>-2.068809481481636</v>
+        <v>-3.519700087457216</v>
       </c>
       <c r="Z33" t="n">
-        <v>-1.266974247787852</v>
+        <v>-2.732832911642263</v>
       </c>
       <c r="AA33" t="b">
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.03619909502262453</v>
+        <v>-0.02666666666666662</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.1421446384039899</v>
+        <v>0.09499999999999997</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.001048114513839904</v>
+        <v>-0.02677316700152654</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.07707107311587302</v>
+        <v>0.06284626322320164</v>
       </c>
       <c r="AF33" t="n">
-        <v>-0.07602295860203312</v>
+        <v>-0.08961943022472818</v>
       </c>
       <c r="AG33" t="n">
-        <v>48</v>
+        <v>43.13725490196079</v>
       </c>
       <c r="AH33" t="n">
-        <v>62</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="AI33" t="b">
         <v>0</v>
       </c>
       <c r="AJ33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="b">
         <v>0</v>
@@ -5103,31 +5071,29 @@
         <v>0</v>
       </c>
       <c r="AN33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO33" t="n">
-        <v>252.36</v>
-      </c>
-      <c r="AP33" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>258.86</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>244.21</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5136,7 +5102,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>27.8</v>
+        <v>27.64705882352941</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5145,15 +5111,15 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>5000</v>
+        <v>470000</v>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="K34" t="b">
         <v>0</v>
@@ -5162,7 +5128,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>5000</v>
+        <v>470000</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -5171,67 +5137,67 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>158.5</v>
+        <v>3095</v>
       </c>
       <c r="Q34" t="n">
-        <v>158.5</v>
+        <v>3095</v>
       </c>
       <c r="R34" t="n">
-        <v>13169977</v>
+        <v>1030333</v>
       </c>
       <c r="S34" t="n">
-        <v>162.6</v>
+        <v>3104</v>
       </c>
       <c r="T34" t="n">
-        <v>170.325</v>
+        <v>3224</v>
       </c>
       <c r="U34" t="n">
-        <v>170.075</v>
+        <v>3229.25</v>
       </c>
       <c r="V34" t="n">
-        <v>151.2083333333333</v>
+        <v>3024.333333333333</v>
       </c>
       <c r="W34" t="n">
-        <v>-1.609375708961409</v>
+        <v>-32.89673728350044</v>
       </c>
       <c r="X34" t="n">
-        <v>1.875328055753605</v>
+        <v>-23.25232969097646</v>
       </c>
       <c r="Y34" t="n">
-        <v>-3.484703764715014</v>
+        <v>-9.644407592523979</v>
       </c>
       <c r="Z34" t="n">
-        <v>-3.510037546493362</v>
+        <v>-8.5735784624049</v>
       </c>
       <c r="AA34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.03257328990228014</v>
+        <v>-0.03281250000000002</v>
       </c>
       <c r="AC34" t="n">
-        <v>0.1045296167247387</v>
+        <v>0.1213768115942029</v>
       </c>
       <c r="AD34" t="n">
-        <v>-0.002577690606504479</v>
+        <v>-0.03291900033485995</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.03945605143662179</v>
+        <v>0.08922307481740455</v>
       </c>
       <c r="AF34" t="n">
-        <v>-0.04203374204312627</v>
+        <v>-0.1221420751522645</v>
       </c>
       <c r="AG34" t="n">
-        <v>46</v>
+        <v>39.21568627450981</v>
       </c>
       <c r="AH34" t="n">
-        <v>56.00000000000001</v>
+        <v>68.62745098039215</v>
       </c>
       <c r="AI34" t="b">
         <v>0</v>
       </c>
       <c r="AJ34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="b">
         <v>0</v>
@@ -5240,22 +5206,22 @@
         <v>0</v>
       </c>
       <c r="AM34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO34" t="inlineStr"/>
-      <c r="AP34" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>3206.42</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>3655.79</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5274,7 +5240,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>26</v>
+        <v>22.94117647058824</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5283,7 +5249,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -5309,61 +5275,61 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="Q35" t="n">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="R35" t="n">
-        <v>90187620</v>
+        <v>98805968</v>
       </c>
       <c r="S35" t="n">
-        <v>139.1</v>
+        <v>133.4</v>
       </c>
       <c r="T35" t="n">
-        <v>149.95</v>
+        <v>148.4</v>
       </c>
       <c r="U35" t="n">
-        <v>150.225</v>
+        <v>149.425</v>
       </c>
       <c r="V35" t="n">
-        <v>133.7416666666667</v>
+        <v>133.425</v>
       </c>
       <c r="W35" t="n">
-        <v>-3.215749370824284</v>
+        <v>-4.885390315535176</v>
       </c>
       <c r="X35" t="n">
-        <v>0.3038707882336746</v>
+        <v>-1.417028705688755</v>
       </c>
       <c r="Y35" t="n">
-        <v>-3.519620159057959</v>
+        <v>-3.468361609846421</v>
       </c>
       <c r="Z35" t="n">
-        <v>-3.441758272044086</v>
+        <v>-3.4152363658433</v>
       </c>
       <c r="AA35" t="b">
         <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>-0.03971119133574008</v>
+        <v>-0.1389830508474577</v>
       </c>
       <c r="AC35" t="n">
-        <v>-0.01115241635687736</v>
+        <v>-0.0830324909747292</v>
       </c>
       <c r="AD35" t="n">
-        <v>-0.07486217184452471</v>
+        <v>-0.1390895511823176</v>
       </c>
       <c r="AE35" t="n">
-        <v>-0.07622598164499428</v>
+        <v>-0.1151862277515275</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.001363809800469573</v>
+        <v>-0.02390332343079005</v>
       </c>
       <c r="AG35" t="n">
-        <v>18</v>
+        <v>5.88235294117647</v>
       </c>
       <c r="AH35" t="n">
-        <v>22</v>
+        <v>21.56862745098039</v>
       </c>
       <c r="AI35" t="b">
         <v>0</v>
@@ -5385,23 +5351,23 @@
       </c>
       <c r="AO35" t="inlineStr"/>
       <c r="AP35" t="n">
-        <v>159.84</v>
+        <v>178.53</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5410,7 +5376,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>23.6</v>
+        <v>22.94117647058824</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5419,15 +5385,15 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>2887848</v>
+        <v>1000</v>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="n">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="K36" t="b">
         <v>0</v>
@@ -5436,7 +5402,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>2887848</v>
+        <v>1000</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -5445,67 +5411,67 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2015</v>
+        <v>160</v>
       </c>
       <c r="Q36" t="n">
-        <v>2015</v>
+        <v>160</v>
       </c>
       <c r="R36" t="n">
-        <v>2095587</v>
+        <v>9653817</v>
       </c>
       <c r="S36" t="n">
-        <v>2176</v>
+        <v>165.7</v>
       </c>
       <c r="T36" t="n">
-        <v>2297</v>
+        <v>176.375</v>
       </c>
       <c r="U36" t="n">
-        <v>2295.25</v>
+        <v>176.65</v>
       </c>
       <c r="V36" t="n">
-        <v>2190.75</v>
+        <v>161.1666666666667</v>
       </c>
       <c r="W36" t="n">
-        <v>-45.04314566761286</v>
+        <v>-2.620405410260162</v>
       </c>
       <c r="X36" t="n">
-        <v>22.2816306089634</v>
+        <v>1.485588153274897</v>
       </c>
       <c r="Y36" t="n">
-        <v>-67.32477627657626</v>
+        <v>-4.105993563535058</v>
       </c>
       <c r="Z36" t="n">
-        <v>-59.64653292198476</v>
+        <v>-3.97508356428308</v>
       </c>
       <c r="AA36" t="b">
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.01767676767676774</v>
+        <v>-0.03323262839879149</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.007500000000000062</v>
+        <v>-0.05044510385756673</v>
       </c>
       <c r="AD36" t="n">
-        <v>-0.01747421283201689</v>
+        <v>-0.03333912873365141</v>
       </c>
       <c r="AE36" t="n">
-        <v>-0.05757356528811686</v>
+        <v>-0.08259884063436507</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.04009935245609997</v>
+        <v>0.04925971190071365</v>
       </c>
       <c r="AG36" t="n">
-        <v>40</v>
+        <v>37.25490196078432</v>
       </c>
       <c r="AH36" t="n">
-        <v>32</v>
+        <v>27.45098039215686</v>
       </c>
       <c r="AI36" t="b">
         <v>0</v>
       </c>
       <c r="AJ36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="b">
         <v>0</v>
@@ -5520,26 +5486,24 @@
         <v>0</v>
       </c>
       <c r="AO36" t="inlineStr"/>
-      <c r="AP36" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+      <c r="AP36" t="n">
+        <v>189.24</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5548,7 +5512,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>23.4</v>
+        <v>22.54901960784314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5557,15 +5521,15 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>4328000</v>
+        <v>5000</v>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="K37" t="b">
         <v>0</v>
@@ -5574,7 +5538,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>4328000</v>
+        <v>5000</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -5583,67 +5547,67 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>5165</v>
+        <v>153.5</v>
       </c>
       <c r="Q37" t="n">
-        <v>5165</v>
+        <v>153.5</v>
       </c>
       <c r="R37" t="n">
-        <v>2553270</v>
+        <v>7897014</v>
       </c>
       <c r="S37" t="n">
-        <v>5500</v>
+        <v>158.2</v>
       </c>
       <c r="T37" t="n">
-        <v>5282.75</v>
+        <v>169.3</v>
       </c>
       <c r="U37" t="n">
-        <v>5280.25</v>
+        <v>169.775</v>
       </c>
       <c r="V37" t="n">
-        <v>5322.909090169271</v>
+        <v>151.3583333333333</v>
       </c>
       <c r="W37" t="n">
-        <v>25.46163632789285</v>
+        <v>-3.107671154594044</v>
       </c>
       <c r="X37" t="n">
-        <v>86.06939147893658</v>
+        <v>0.2161910987202716</v>
       </c>
       <c r="Y37" t="n">
-        <v>-60.60775515104373</v>
+        <v>-3.323862253314316</v>
       </c>
       <c r="Z37" t="n">
-        <v>-26.86192883382469</v>
+        <v>-3.312685574818888</v>
       </c>
       <c r="AA37" t="b">
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.009775171065493637</v>
+        <v>-0.05828220858895705</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.07424110202656142</v>
+        <v>0.06228373702422152</v>
       </c>
       <c r="AD37" t="n">
-        <v>-0.02537580944329099</v>
+        <v>-0.05838870892381698</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.009167536738444504</v>
+        <v>0.03013000024742318</v>
       </c>
       <c r="AF37" t="n">
-        <v>-0.03454334618173549</v>
+        <v>-0.08851870917124016</v>
       </c>
       <c r="AG37" t="n">
-        <v>34</v>
+        <v>25.49019607843137</v>
       </c>
       <c r="AH37" t="n">
-        <v>48</v>
+        <v>58.82352941176471</v>
       </c>
       <c r="AI37" t="b">
         <v>0</v>
       </c>
       <c r="AJ37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="b">
         <v>0</v>
@@ -5655,31 +5619,27 @@
         <v>0</v>
       </c>
       <c r="AN37" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>5857.11</v>
-      </c>
-      <c r="AP37" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="AO37" t="inlineStr"/>
+      <c r="AP37" t="n">
+        <v>185.13</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5688,7 +5648,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>23.4</v>
+        <v>22.15686274509804</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5697,7 +5657,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -5705,7 +5665,7 @@
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="K38" t="b">
         <v>0</v>
@@ -5723,67 +5683,67 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>540</v>
+        <v>241.5</v>
       </c>
       <c r="Q38" t="n">
-        <v>540</v>
+        <v>241.5</v>
       </c>
       <c r="R38" t="n">
-        <v>503564</v>
+        <v>26839387</v>
       </c>
       <c r="S38" t="n">
-        <v>547.8</v>
+        <v>241.5</v>
       </c>
       <c r="T38" t="n">
-        <v>561.9</v>
+        <v>248.5</v>
       </c>
       <c r="U38" t="n">
-        <v>561.05</v>
+        <v>248.95</v>
       </c>
       <c r="V38" t="n">
-        <v>566.9836334228515</v>
+        <v>250.45</v>
       </c>
       <c r="W38" t="n">
-        <v>-5.293175034313435</v>
+        <v>-2.784638775372684</v>
       </c>
       <c r="X38" t="n">
-        <v>-1.620689590515565</v>
+        <v>-1.842734980825168</v>
       </c>
       <c r="Y38" t="n">
-        <v>-3.67248544379787</v>
+        <v>-0.9419037945475166</v>
       </c>
       <c r="Z38" t="n">
-        <v>-3.375044081717603</v>
+        <v>-1.242780797379176</v>
       </c>
       <c r="AA38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.03250478011472269</v>
+        <v>-0.0359281437125748</v>
       </c>
       <c r="AC38" t="n">
-        <v>-0.05940217750113941</v>
+        <v>-0.06213592233009713</v>
       </c>
       <c r="AD38" t="n">
-        <v>-0.002646200394061937</v>
+        <v>-0.03603464404743473</v>
       </c>
       <c r="AE38" t="n">
-        <v>-0.1244757427892563</v>
+        <v>-0.09428965910689546</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.1218295423951944</v>
+        <v>0.05825501505946074</v>
       </c>
       <c r="AG38" t="n">
-        <v>44</v>
+        <v>35.29411764705883</v>
       </c>
       <c r="AH38" t="n">
-        <v>18</v>
+        <v>25.49019607843137</v>
       </c>
       <c r="AI38" t="b">
         <v>0</v>
       </c>
       <c r="AJ38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="b">
         <v>0</v>
@@ -5792,34 +5752,32 @@
         <v>0</v>
       </c>
       <c r="AM38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN38" t="b">
         <v>1</v>
       </c>
       <c r="AO38" t="n">
-        <v>582.12</v>
-      </c>
-      <c r="AP38" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>252.13</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>257.87</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5828,7 +5786,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>20.4</v>
+        <v>21.37254901960785</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5837,7 +5795,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -5845,7 +5803,7 @@
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K39" t="b">
         <v>0</v>
@@ -5863,61 +5821,61 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>244</v>
+        <v>2000</v>
       </c>
       <c r="Q39" t="n">
-        <v>244</v>
+        <v>2000</v>
       </c>
       <c r="R39" t="n">
-        <v>49281775</v>
+        <v>1794629</v>
       </c>
       <c r="S39" t="n">
-        <v>242.2</v>
+        <v>2056</v>
       </c>
       <c r="T39" t="n">
-        <v>249.375</v>
+        <v>2228.25</v>
       </c>
       <c r="U39" t="n">
-        <v>249.5</v>
+        <v>2232.5</v>
       </c>
       <c r="V39" t="n">
-        <v>250.9166666666667</v>
+        <v>2130.416666666667</v>
       </c>
       <c r="W39" t="n">
-        <v>-2.52142207475751</v>
+        <v>-57.02788078423646</v>
       </c>
       <c r="X39" t="n">
-        <v>-1.296563832843463</v>
+        <v>-10.90489862325036</v>
       </c>
       <c r="Y39" t="n">
-        <v>-1.224858241914047</v>
+        <v>-46.1229821609861</v>
       </c>
       <c r="Z39" t="n">
-        <v>-1.688914190086806</v>
+        <v>-47.87567750420025</v>
       </c>
       <c r="AA39" t="b">
         <v>1</v>
       </c>
       <c r="AB39" t="n">
-        <v>-0.01014198782961462</v>
+        <v>-0.04076738609112707</v>
       </c>
       <c r="AC39" t="n">
-        <v>-0.008130081300813052</v>
+        <v>-0.07192575406032486</v>
       </c>
       <c r="AD39" t="n">
-        <v>-0.04529296833839924</v>
+        <v>-0.04087388642598699</v>
       </c>
       <c r="AE39" t="n">
-        <v>-0.07320364658892997</v>
+        <v>-0.1040794908371232</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.02791067825053073</v>
+        <v>0.06320560441113621</v>
       </c>
       <c r="AG39" t="n">
-        <v>32</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="AH39" t="n">
-        <v>24</v>
+        <v>23.52941176470588</v>
       </c>
       <c r="AI39" t="b">
         <v>0</v>
@@ -5935,29 +5893,27 @@
         <v>1</v>
       </c>
       <c r="AN39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>258.15</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO39" t="inlineStr"/>
       <c r="AP39" t="n">
-        <v>253.66</v>
+        <v>2530.26</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5966,7 +5922,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>20.2</v>
+        <v>20.98039215686275</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5975,15 +5931,15 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1000</v>
+        <v>5143000</v>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="K40" t="b">
         <v>0</v>
@@ -5992,7 +5948,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1000</v>
+        <v>5143000</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -6001,61 +5957,61 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>447.5</v>
+        <v>4150</v>
       </c>
       <c r="Q40" t="n">
-        <v>447.5</v>
+        <v>4150</v>
       </c>
       <c r="R40" t="n">
-        <v>45967146</v>
+        <v>6616927</v>
       </c>
       <c r="S40" t="n">
-        <v>476.5</v>
+        <v>4249</v>
       </c>
       <c r="T40" t="n">
-        <v>504.5</v>
+        <v>4756.75</v>
       </c>
       <c r="U40" t="n">
-        <v>505.4</v>
+        <v>4774.25</v>
       </c>
       <c r="V40" t="n">
-        <v>486.1666666666667</v>
+        <v>4285</v>
       </c>
       <c r="W40" t="n">
-        <v>-13.58907882775202</v>
+        <v>-159.1577618060437</v>
       </c>
       <c r="X40" t="n">
-        <v>-2.506816021675073</v>
+        <v>-54.73832063428937</v>
       </c>
       <c r="Y40" t="n">
-        <v>-11.08226280607695</v>
+        <v>-104.4194411717543</v>
       </c>
       <c r="Z40" t="n">
-        <v>-9.97394763226195</v>
+        <v>-114.1653361765419</v>
       </c>
       <c r="AA40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB40" t="n">
-        <v>-0.03866809881847477</v>
+        <v>-0.07777777777777772</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.1049382716049383</v>
+        <v>0.07096774193548394</v>
       </c>
       <c r="AD40" t="n">
-        <v>-0.0738190793272594</v>
+        <v>-0.07788427811263765</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.03986470631682137</v>
+        <v>0.0388140051586856</v>
       </c>
       <c r="AF40" t="n">
-        <v>-0.1136837856440808</v>
+        <v>-0.1166982832713233</v>
       </c>
       <c r="AG40" t="n">
-        <v>20</v>
+        <v>19.6078431372549</v>
       </c>
       <c r="AH40" t="n">
-        <v>57.99999999999999</v>
+        <v>60.78431372549019</v>
       </c>
       <c r="AI40" t="b">
         <v>0</v>
@@ -6070,30 +6026,30 @@
         <v>0</v>
       </c>
       <c r="AM40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN40" t="b">
         <v>0</v>
       </c>
       <c r="AO40" t="inlineStr"/>
       <c r="AP40" t="n">
-        <v>552.5</v>
+        <v>5348.68</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6102,7 +6058,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>19.6</v>
+        <v>19.80392156862745</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -6111,15 +6067,15 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>5143000</v>
+        <v>3281561</v>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K41" t="b">
         <v>0</v>
@@ -6128,7 +6084,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>5143000</v>
+        <v>3281561</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -6137,61 +6093,61 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>4250</v>
+        <v>1925</v>
       </c>
       <c r="Q41" t="n">
-        <v>4250</v>
+        <v>1925</v>
       </c>
       <c r="R41" t="n">
-        <v>7757617</v>
+        <v>4847292</v>
       </c>
       <c r="S41" t="n">
-        <v>4408</v>
+        <v>1935</v>
       </c>
       <c r="T41" t="n">
-        <v>4790.5</v>
+        <v>2103.75</v>
       </c>
       <c r="U41" t="n">
-        <v>4799.5</v>
+        <v>2114.25</v>
       </c>
       <c r="V41" t="n">
-        <v>4274.5</v>
+        <v>2144.59619140625</v>
       </c>
       <c r="W41" t="n">
-        <v>-122.8760504218917</v>
+        <v>-78.00820616284841</v>
       </c>
       <c r="X41" t="n">
-        <v>-0.09212629721524124</v>
+        <v>-43.83312580277956</v>
       </c>
       <c r="Y41" t="n">
-        <v>-122.7839241246765</v>
+        <v>-34.17508036006885</v>
       </c>
       <c r="Z41" t="n">
-        <v>-127.5067884662056</v>
+        <v>-40.22534605316526</v>
       </c>
       <c r="AA41" t="b">
         <v>1</v>
       </c>
       <c r="AB41" t="n">
-        <v>-0.04063205417607219</v>
+        <v>-0.09836065573770492</v>
       </c>
       <c r="AC41" t="n">
-        <v>0.1580381471389645</v>
+        <v>0.04970376901138618</v>
       </c>
       <c r="AD41" t="n">
-        <v>-0.07578303468485681</v>
+        <v>-0.09846715607256484</v>
       </c>
       <c r="AE41" t="n">
-        <v>0.09296458185084755</v>
+        <v>0.01755003223458784</v>
       </c>
       <c r="AF41" t="n">
-        <v>-0.1687476165357044</v>
+        <v>-0.1160171883071527</v>
       </c>
       <c r="AG41" t="n">
-        <v>16</v>
+        <v>17.64705882352941</v>
       </c>
       <c r="AH41" t="n">
-        <v>64</v>
+        <v>54.90196078431373</v>
       </c>
       <c r="AI41" t="b">
         <v>0</v>
@@ -6211,25 +6167,27 @@
       <c r="AN41" t="b">
         <v>0</v>
       </c>
-      <c r="AO41" t="inlineStr"/>
+      <c r="AO41" t="n">
+        <v>2310</v>
+      </c>
       <c r="AP41" t="n">
-        <v>5098.95</v>
+        <v>2328.16</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6238,7 +6196,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>19.4</v>
+        <v>19.80392156862745</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6247,15 +6205,15 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>470000</v>
+        <v>2887848</v>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="K42" t="b">
         <v>0</v>
@@ -6264,7 +6222,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>470000</v>
+        <v>2887848</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
@@ -6273,61 +6231,61 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>3120</v>
+        <v>1925</v>
       </c>
       <c r="Q42" t="n">
-        <v>3120</v>
+        <v>1925</v>
       </c>
       <c r="R42" t="n">
-        <v>1049185</v>
+        <v>1653523</v>
       </c>
       <c r="S42" t="n">
-        <v>3189</v>
+        <v>2033</v>
       </c>
       <c r="T42" t="n">
-        <v>3232</v>
+        <v>2291.75</v>
       </c>
       <c r="U42" t="n">
-        <v>3238.75</v>
+        <v>2296</v>
       </c>
       <c r="V42" t="n">
-        <v>3011</v>
+        <v>2182.416666666667</v>
       </c>
       <c r="W42" t="n">
-        <v>-36.18505579455723</v>
+        <v>-83.28163187322662</v>
       </c>
       <c r="X42" t="n">
-        <v>-18.69783317724361</v>
+        <v>-12.84731637201121</v>
       </c>
       <c r="Y42" t="n">
-        <v>-17.48722261731362</v>
+        <v>-70.43431550121541</v>
       </c>
       <c r="Z42" t="n">
-        <v>-21.52010150547788</v>
+        <v>-70.08147242268308</v>
       </c>
       <c r="AA42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>-0.04147465437788023</v>
+        <v>-0.04228855721393032</v>
       </c>
       <c r="AC42" t="n">
-        <v>0.1795841209829867</v>
+        <v>-0.1575492341356673</v>
       </c>
       <c r="AD42" t="n">
-        <v>-0.07662563488666485</v>
+        <v>-0.04239505754879025</v>
       </c>
       <c r="AE42" t="n">
-        <v>0.1145105556948698</v>
+        <v>-0.1897029709124657</v>
       </c>
       <c r="AF42" t="n">
-        <v>-0.1911361905815346</v>
+        <v>0.1473079133636754</v>
       </c>
       <c r="AG42" t="n">
-        <v>14</v>
+        <v>31.37254901960784</v>
       </c>
       <c r="AH42" t="n">
-        <v>68</v>
+        <v>13.72549019607843</v>
       </c>
       <c r="AI42" t="b">
         <v>0</v>
@@ -6342,22 +6300,20 @@
         <v>0</v>
       </c>
       <c r="AM42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN42" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO42" t="n">
-        <v>3319.68</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO42" t="inlineStr"/>
       <c r="AP42" t="n">
-        <v>3347.89</v>
+        <v>2596.05</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -6376,7 +6332,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>18.4</v>
+        <v>19.21568627450981</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6385,7 +6341,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -6393,7 +6349,7 @@
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K43" t="b">
         <v>0</v>
@@ -6411,61 +6367,61 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>322</v>
+        <v>320.5</v>
       </c>
       <c r="Q43" t="n">
-        <v>322</v>
+        <v>320.5</v>
       </c>
       <c r="R43" t="n">
-        <v>9511272</v>
+        <v>8492298</v>
       </c>
       <c r="S43" t="n">
-        <v>321.3</v>
+        <v>319.3</v>
       </c>
       <c r="T43" t="n">
-        <v>333.075</v>
+        <v>330.6</v>
       </c>
       <c r="U43" t="n">
-        <v>333.625</v>
+        <v>331.775</v>
       </c>
       <c r="V43" t="n">
-        <v>327.05</v>
+        <v>326.55</v>
       </c>
       <c r="W43" t="n">
-        <v>-4.266450278084278</v>
+        <v>-4.523866670236032</v>
       </c>
       <c r="X43" t="n">
-        <v>-2.713063747046953</v>
+        <v>-3.422591217623121</v>
       </c>
       <c r="Y43" t="n">
-        <v>-1.553386531037325</v>
+        <v>-1.101275452612911</v>
       </c>
       <c r="Z43" t="n">
-        <v>-2.101321064717312</v>
+        <v>-1.736834429691923</v>
       </c>
       <c r="AA43" t="b">
         <v>1</v>
       </c>
       <c r="AB43" t="n">
-        <v>-0.03303303303303307</v>
+        <v>-0.0683139534883721</v>
       </c>
       <c r="AC43" t="n">
-        <v>-0.006172839506172867</v>
+        <v>-0.04613095238095233</v>
       </c>
       <c r="AD43" t="n">
-        <v>-0.06818401354181769</v>
+        <v>-0.06842045382323203</v>
       </c>
       <c r="AE43" t="n">
-        <v>-0.07124640479428979</v>
+        <v>-0.07828468915775066</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.003062391252472096</v>
+        <v>0.009864235334518634</v>
       </c>
       <c r="AG43" t="n">
-        <v>24</v>
+        <v>23.52941176470588</v>
       </c>
       <c r="AH43" t="n">
-        <v>28</v>
+        <v>31.37254901960784</v>
       </c>
       <c r="AI43" t="b">
         <v>0</v>
@@ -6486,26 +6442,26 @@
         <v>1</v>
       </c>
       <c r="AO43" t="n">
-        <v>340.03</v>
+        <v>333.32</v>
       </c>
       <c r="AP43" t="n">
-        <v>352.16</v>
+        <v>353.63</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6514,7 +6470,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>17.8</v>
+        <v>19.21568627450981</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6523,7 +6479,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -6531,7 +6487,7 @@
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="K44" t="b">
         <v>0</v>
@@ -6549,61 +6505,61 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>902</v>
+        <v>524</v>
       </c>
       <c r="Q44" t="n">
-        <v>902</v>
+        <v>524</v>
       </c>
       <c r="R44" t="n">
-        <v>14865775</v>
+        <v>233848</v>
       </c>
       <c r="S44" t="n">
-        <v>995</v>
+        <v>538</v>
       </c>
       <c r="T44" t="n">
-        <v>1027.65</v>
+        <v>559.6</v>
       </c>
       <c r="U44" t="n">
-        <v>1028.25</v>
+        <v>561.2</v>
       </c>
       <c r="V44" t="n">
-        <v>978.8333333333334</v>
+        <v>564.4116200764973</v>
       </c>
       <c r="W44" t="n">
-        <v>-13.50961918957125</v>
+        <v>-9.086042367232153</v>
       </c>
       <c r="X44" t="n">
-        <v>22.17543639612178</v>
+        <v>-4.046019866092821</v>
       </c>
       <c r="Y44" t="n">
-        <v>-35.68505558569304</v>
+        <v>-5.040022501139332</v>
       </c>
       <c r="Z44" t="n">
-        <v>-28.26798946627251</v>
+        <v>-4.661298601172318</v>
       </c>
       <c r="AA44" t="b">
         <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>-0.01312910284463897</v>
+        <v>-0.05755395683453235</v>
       </c>
       <c r="AC44" t="n">
-        <v>-0.2514522821576763</v>
+        <v>-0.1305219329818914</v>
       </c>
       <c r="AD44" t="n">
-        <v>-0.0482800833534236</v>
+        <v>-0.05766045716939228</v>
       </c>
       <c r="AE44" t="n">
-        <v>-0.3165258474457933</v>
+        <v>-0.1626756697586897</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.2682457640923697</v>
+        <v>0.1050152125892975</v>
       </c>
       <c r="AG44" t="n">
-        <v>30</v>
+        <v>27.45098039215686</v>
       </c>
       <c r="AH44" t="n">
-        <v>4</v>
+        <v>19.6078431372549</v>
       </c>
       <c r="AI44" t="b">
         <v>0</v>
@@ -6621,27 +6577,29 @@
         <v>0</v>
       </c>
       <c r="AN44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO44" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>581.64</v>
+      </c>
       <c r="AP44" t="n">
-        <v>1069.26</v>
+        <v>605.47</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6650,7 +6608,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>17.6</v>
+        <v>17.64705882352941</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6659,15 +6617,15 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1000</v>
+        <v>957000</v>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="K45" t="b">
         <v>0</v>
@@ -6676,7 +6634,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>1000</v>
+        <v>957000</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
@@ -6685,61 +6643,61 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2000</v>
+        <v>470</v>
       </c>
       <c r="Q45" t="n">
-        <v>2000</v>
+        <v>470</v>
       </c>
       <c r="R45" t="n">
-        <v>3436716</v>
+        <v>1483863</v>
       </c>
       <c r="S45" t="n">
-        <v>2168</v>
+        <v>520</v>
       </c>
       <c r="T45" t="n">
-        <v>2236.75</v>
+        <v>564.6</v>
       </c>
       <c r="U45" t="n">
-        <v>2240.75</v>
+        <v>568.9</v>
       </c>
       <c r="V45" t="n">
-        <v>2135</v>
+        <v>542.2083333333334</v>
       </c>
       <c r="W45" t="n">
-        <v>-32.22265688838252</v>
+        <v>-22.17551166770397</v>
       </c>
       <c r="X45" t="n">
-        <v>12.59476629304624</v>
+        <v>-8.726087560203045</v>
       </c>
       <c r="Y45" t="n">
-        <v>-44.81742318142877</v>
+        <v>-13.44942410750093</v>
       </c>
       <c r="Z45" t="n">
-        <v>-32.33166498783359</v>
+        <v>-11.02675305589574</v>
       </c>
       <c r="AA45" t="b">
         <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>-0.03846153846153844</v>
+        <v>-0.1546762589928058</v>
       </c>
       <c r="AC45" t="n">
-        <v>-0.007444168734491274</v>
+        <v>0.1533742331288344</v>
       </c>
       <c r="AD45" t="n">
-        <v>-0.07361251897032306</v>
+        <v>-0.1547827593276657</v>
       </c>
       <c r="AE45" t="n">
-        <v>-0.07251773402260819</v>
+        <v>0.121220496352036</v>
       </c>
       <c r="AF45" t="n">
-        <v>-0.001094784947714866</v>
+        <v>-0.2760032556797017</v>
       </c>
       <c r="AG45" t="n">
-        <v>22</v>
+        <v>3.92156862745098</v>
       </c>
       <c r="AH45" t="n">
-        <v>26</v>
+        <v>74.50980392156863</v>
       </c>
       <c r="AI45" t="b">
         <v>0</v>
@@ -6761,13 +6719,13 @@
       </c>
       <c r="AO45" t="inlineStr"/>
       <c r="AP45" t="n">
-        <v>2339.21</v>
+        <v>710.58</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6786,7 +6744,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>17.4</v>
+        <v>16.86274509803922</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6795,7 +6753,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="H46" t="n">
@@ -6803,7 +6761,7 @@
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K46" t="b">
         <v>0</v>
@@ -6821,61 +6779,61 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>16480</v>
+        <v>15900</v>
       </c>
       <c r="Q46" t="n">
-        <v>16480</v>
+        <v>15900</v>
       </c>
       <c r="R46" t="n">
-        <v>284297</v>
+        <v>168347</v>
       </c>
       <c r="S46" t="n">
-        <v>16994</v>
+        <v>16361</v>
       </c>
       <c r="T46" t="n">
-        <v>18569.5</v>
+        <v>18337.25</v>
       </c>
       <c r="U46" t="n">
-        <v>18621.5</v>
+        <v>18456</v>
       </c>
       <c r="V46" t="n">
-        <v>17089.25</v>
+        <v>17103.08333333333</v>
       </c>
       <c r="W46" t="n">
-        <v>-560.0191406263875</v>
+        <v>-697.0115151413738</v>
       </c>
       <c r="X46" t="n">
-        <v>-175.2757310592362</v>
+        <v>-354.8072208042943</v>
       </c>
       <c r="Y46" t="n">
-        <v>-384.7434095671514</v>
+        <v>-342.2042943370795</v>
       </c>
       <c r="Z46" t="n">
-        <v>-418.1097860404948</v>
+        <v>-375.921664643153</v>
       </c>
       <c r="AA46" t="b">
         <v>1</v>
       </c>
       <c r="AB46" t="n">
-        <v>-0.05936073059360736</v>
+        <v>-0.1299589603283173</v>
       </c>
       <c r="AC46" t="n">
-        <v>0.1687943262411347</v>
+        <v>0.02316602316602312</v>
       </c>
       <c r="AD46" t="n">
-        <v>-0.09451171110239198</v>
+        <v>-0.1300654606631773</v>
       </c>
       <c r="AE46" t="n">
-        <v>0.1037207609530177</v>
+        <v>-0.008987713610775216</v>
       </c>
       <c r="AF46" t="n">
-        <v>-0.1982324720554097</v>
+        <v>-0.121077747052402</v>
       </c>
       <c r="AG46" t="n">
-        <v>8</v>
+        <v>9.803921568627452</v>
       </c>
       <c r="AH46" t="n">
-        <v>66</v>
+        <v>49.01960784313725</v>
       </c>
       <c r="AI46" t="b">
         <v>0</v>
@@ -6897,23 +6855,23 @@
       </c>
       <c r="AO46" t="inlineStr"/>
       <c r="AP46" t="n">
-        <v>20449.47</v>
+        <v>21855.53</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6922,7 +6880,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>14.4</v>
+        <v>16.27450980392157</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6931,15 +6889,15 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>3281561</v>
+        <v>1000</v>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="n">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="K47" t="b">
         <v>0</v>
@@ -6948,7 +6906,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3281561</v>
+        <v>1000</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
@@ -6957,61 +6915,61 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>1845</v>
+        <v>844</v>
       </c>
       <c r="Q47" t="n">
-        <v>1845</v>
+        <v>844</v>
       </c>
       <c r="R47" t="n">
-        <v>12287772</v>
+        <v>11741197</v>
       </c>
       <c r="S47" t="n">
-        <v>2067</v>
+        <v>914.2</v>
       </c>
       <c r="T47" t="n">
-        <v>2128.25</v>
+        <v>1021.5</v>
       </c>
       <c r="U47" t="n">
-        <v>2151.75</v>
+        <v>1024.9</v>
       </c>
       <c r="V47" t="n">
-        <v>2142.392177327474</v>
+        <v>968.2666666666667</v>
       </c>
       <c r="W47" t="n">
-        <v>-62.78250070016929</v>
+        <v>-39.37208214184761</v>
       </c>
       <c r="X47" t="n">
-        <v>-25.233019199471</v>
+        <v>2.046837883689879</v>
       </c>
       <c r="Y47" t="n">
-        <v>-37.54948150069829</v>
+        <v>-41.41892002553749</v>
       </c>
       <c r="Z47" t="n">
-        <v>-19.84982888075135</v>
+        <v>-39.09547402419012</v>
       </c>
       <c r="AA47" t="b">
         <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>-0.203023758099352</v>
+        <v>-0.07456140350877194</v>
       </c>
       <c r="AC47" t="n">
-        <v>0.1006511827879939</v>
+        <v>-0.2464285714285714</v>
       </c>
       <c r="AD47" t="n">
-        <v>-0.2381747386081366</v>
+        <v>-0.07466790384363187</v>
       </c>
       <c r="AE47" t="n">
-        <v>0.03557761749987698</v>
+        <v>-0.2785823082053698</v>
       </c>
       <c r="AF47" t="n">
-        <v>-0.2737523561080136</v>
+        <v>0.2039144043617379</v>
       </c>
       <c r="AG47" t="n">
-        <v>2</v>
+        <v>21.56862745098039</v>
       </c>
       <c r="AH47" t="n">
-        <v>54</v>
+        <v>7.84313725490196</v>
       </c>
       <c r="AI47" t="b">
         <v>0</v>
@@ -7033,23 +6991,23 @@
       </c>
       <c r="AO47" t="inlineStr"/>
       <c r="AP47" t="n">
-        <v>2463.16</v>
+        <v>1130.84</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7058,7 +7016,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>13.2</v>
+        <v>15.09803921568628</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -7067,15 +7025,15 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>2504000</v>
+        <v>1000</v>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="K48" t="b">
         <v>0</v>
@@ -7084,7 +7042,7 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>2504000</v>
+        <v>1000</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
@@ -7093,61 +7051,61 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>5205</v>
+        <v>422</v>
       </c>
       <c r="Q48" t="n">
-        <v>5205</v>
+        <v>422</v>
       </c>
       <c r="R48" t="n">
-        <v>1463336</v>
+        <v>38690697</v>
       </c>
       <c r="S48" t="n">
-        <v>5692</v>
+        <v>445.1</v>
       </c>
       <c r="T48" t="n">
-        <v>5509</v>
+        <v>498.375</v>
       </c>
       <c r="U48" t="n">
-        <v>5520.75</v>
+        <v>501.675</v>
       </c>
       <c r="V48" t="n">
-        <v>5588.083333333333</v>
+        <v>485.9416666666667</v>
       </c>
       <c r="W48" t="n">
-        <v>6.001759798633429</v>
+        <v>-20.84900221807942</v>
       </c>
       <c r="X48" t="n">
-        <v>37.92903167516284</v>
+        <v>-8.528245771880288</v>
       </c>
       <c r="Y48" t="n">
-        <v>-31.92727187652941</v>
+        <v>-12.32075644619913</v>
       </c>
       <c r="Z48" t="n">
-        <v>14.8585446391906</v>
+        <v>-11.76496255462172</v>
       </c>
       <c r="AA48" t="b">
         <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>-0.04319852941176472</v>
+        <v>-0.1352459016393442</v>
       </c>
       <c r="AC48" t="n">
-        <v>-0.1140425531914894</v>
+        <v>-0.009389671361502372</v>
       </c>
       <c r="AD48" t="n">
-        <v>-0.07834950992054934</v>
+        <v>-0.1353524019742042</v>
       </c>
       <c r="AE48" t="n">
-        <v>-0.1791161184796063</v>
+        <v>-0.04154340813830071</v>
       </c>
       <c r="AF48" t="n">
-        <v>0.1007666085590569</v>
+        <v>-0.09380899383590346</v>
       </c>
       <c r="AG48" t="n">
-        <v>12</v>
+        <v>7.84313725490196</v>
       </c>
       <c r="AH48" t="n">
-        <v>12</v>
+        <v>37.25490196078432</v>
       </c>
       <c r="AI48" t="b">
         <v>0</v>
@@ -7165,29 +7123,27 @@
         <v>0</v>
       </c>
       <c r="AN48" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO48" t="n">
-        <v>5569.35</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO48" t="inlineStr"/>
       <c r="AP48" t="n">
-        <v>5920</v>
+        <v>605.39</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -7196,7 +7152,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>11.6</v>
+        <v>14.31372549019608</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -7205,15 +7161,15 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>478000</v>
+        <v>1000</v>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="K49" t="b">
         <v>0</v>
@@ -7222,7 +7178,7 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>478000</v>
+        <v>1000</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
@@ -7231,61 +7187,61 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>834</v>
+        <v>1110</v>
       </c>
       <c r="Q49" t="n">
-        <v>834</v>
+        <v>1110</v>
       </c>
       <c r="R49" t="n">
-        <v>585807</v>
+        <v>1530982</v>
       </c>
       <c r="S49" t="n">
-        <v>843.8</v>
+        <v>1154</v>
       </c>
       <c r="T49" t="n">
-        <v>870.1</v>
+        <v>1194.75</v>
       </c>
       <c r="U49" t="n">
-        <v>872.1</v>
+        <v>1201.5</v>
       </c>
       <c r="V49" t="n">
-        <v>962.8166666666667</v>
+        <v>1340.583333333333</v>
       </c>
       <c r="W49" t="n">
-        <v>-16.27706785386522</v>
+        <v>-29.9258700752714</v>
       </c>
       <c r="X49" t="n">
-        <v>-15.85999939419888</v>
+        <v>-28.51256100229154</v>
       </c>
       <c r="Y49" t="n">
-        <v>-0.4170684596663357</v>
+        <v>-1.413309072979864</v>
       </c>
       <c r="Z49" t="n">
-        <v>0.06517666901736163</v>
+        <v>2.82846467341701</v>
       </c>
       <c r="AA49" t="b">
         <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>-0.04576659038901598</v>
+        <v>-0.1084337349397591</v>
       </c>
       <c r="AC49" t="n">
-        <v>-0.2841201716738198</v>
+        <v>-0.2099644128113879</v>
       </c>
       <c r="AD49" t="n">
-        <v>-0.08091757089780061</v>
+        <v>-0.108540235274619</v>
       </c>
       <c r="AE49" t="n">
-        <v>-0.3491937369619367</v>
+        <v>-0.2421181495881862</v>
       </c>
       <c r="AF49" t="n">
-        <v>0.2682761660641361</v>
+        <v>0.1335779143135672</v>
       </c>
       <c r="AG49" t="n">
-        <v>10</v>
+        <v>13.72549019607843</v>
       </c>
       <c r="AH49" t="n">
-        <v>2</v>
+        <v>11.76470588235294</v>
       </c>
       <c r="AI49" t="b">
         <v>0</v>
@@ -7306,26 +7262,26 @@
         <v>1</v>
       </c>
       <c r="AO49" t="n">
-        <v>839</v>
+        <v>1127.76</v>
       </c>
       <c r="AP49" t="n">
-        <v>921</v>
+        <v>1309.21</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7334,7 +7290,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>11.2</v>
+        <v>13.92156862745098</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7343,15 +7299,15 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1000</v>
+        <v>478000</v>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="K50" t="b">
         <v>0</v>
@@ -7360,7 +7316,7 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>1000</v>
+        <v>478000</v>
       </c>
       <c r="N50" t="n">
         <v>0</v>
@@ -7369,61 +7325,61 @@
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>1155</v>
+        <v>801</v>
       </c>
       <c r="Q50" t="n">
-        <v>1155</v>
+        <v>801</v>
       </c>
       <c r="R50" t="n">
-        <v>504166</v>
+        <v>583410</v>
       </c>
       <c r="S50" t="n">
-        <v>1175</v>
+        <v>826.8</v>
       </c>
       <c r="T50" t="n">
-        <v>1205.25</v>
+        <v>862.1</v>
       </c>
       <c r="U50" t="n">
-        <v>1211.5</v>
+        <v>866.6</v>
       </c>
       <c r="V50" t="n">
-        <v>1349.416479492188</v>
+        <v>950.8833333333333</v>
       </c>
       <c r="W50" t="n">
-        <v>-26.61889905514317</v>
+        <v>-21.10336555981689</v>
       </c>
       <c r="X50" t="n">
-        <v>-28.86634990240082</v>
+        <v>-17.34931083999784</v>
       </c>
       <c r="Y50" t="n">
-        <v>2.247450847257646</v>
+        <v>-3.754054719819052</v>
       </c>
       <c r="Z50" t="n">
-        <v>3.503943354691728</v>
+        <v>-2.203191063376405</v>
       </c>
       <c r="AA50" t="b">
         <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>-0.09765625</v>
+        <v>-0.101010101010101</v>
       </c>
       <c r="AC50" t="n">
-        <v>-0.1325297493367288</v>
+        <v>-0.3211864406779661</v>
       </c>
       <c r="AD50" t="n">
-        <v>-0.1328072305087846</v>
+        <v>-0.1011166013449609</v>
       </c>
       <c r="AE50" t="n">
-        <v>-0.1976033146248457</v>
+        <v>-0.3533401774547644</v>
       </c>
       <c r="AF50" t="n">
-        <v>0.06479608411606108</v>
+        <v>0.2522235761098035</v>
       </c>
       <c r="AG50" t="n">
-        <v>6</v>
+        <v>15.68627450980392</v>
       </c>
       <c r="AH50" t="n">
-        <v>10</v>
+        <v>1.96078431372549</v>
       </c>
       <c r="AI50" t="b">
         <v>0</v>
@@ -7432,40 +7388,38 @@
         <v>0</v>
       </c>
       <c r="AK50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM50" t="b">
         <v>0</v>
       </c>
       <c r="AN50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>844.25</v>
       </c>
       <c r="AP50" t="n">
-        <v>1292.89</v>
+        <v>966.3200000000001</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7474,7 +7428,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>10.2</v>
+        <v>13.52941176470588</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7483,15 +7437,15 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>93000</v>
+        <v>2504000</v>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="K51" t="b">
         <v>0</v>
@@ -7500,94 +7454,230 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
+        <v>2504000</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>4900</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>4900</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1723762</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5305</v>
+      </c>
+      <c r="T51" t="n">
+        <v>5460.75</v>
+      </c>
+      <c r="U51" t="n">
+        <v>5490.75</v>
+      </c>
+      <c r="V51" t="n">
+        <v>5552.833333333333</v>
+      </c>
+      <c r="W51" t="n">
+        <v>-89.16682379205486</v>
+      </c>
+      <c r="X51" t="n">
+        <v>1.852872783698629</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>-91.01969657575349</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>-53.28493899010337</v>
+      </c>
+      <c r="AA51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>-0.1090909090909091</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>-0.216</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>-0.1091974094257691</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>-0.2481537367767983</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>0.1389563273510293</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>11.76470588235294</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>9.803921568627452</v>
+      </c>
+      <c r="AI51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO51" t="inlineStr"/>
+      <c r="AP51" t="n">
+        <v>6390.26</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>10</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
         <v>93000</v>
       </c>
-      <c r="N51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>5160</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>5160</v>
-      </c>
-      <c r="R51" t="n">
-        <v>735494</v>
-      </c>
-      <c r="S51" t="n">
-        <v>5511</v>
-      </c>
-      <c r="T51" t="n">
-        <v>5832</v>
-      </c>
-      <c r="U51" t="n">
-        <v>5889.5</v>
-      </c>
-      <c r="V51" t="n">
-        <v>6311.75</v>
-      </c>
-      <c r="W51" t="n">
-        <v>-251.3873140364049</v>
-      </c>
-      <c r="X51" t="n">
-        <v>-188.2618667969104</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>-63.12544723949443</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>-51.03017474922279</v>
-      </c>
-      <c r="AA51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>-0.1822503961965135</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>-0.2246431254695718</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>-0.2174013767052981</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>-0.2897166907576887</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>0.07231531405239056</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>6</v>
-      </c>
-      <c r="AI51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AL51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AM51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN51" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO51" t="n">
-        <v>5872.08</v>
-      </c>
-      <c r="AP51" t="n">
-        <v>6917.37</v>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="n">
+        <v>35</v>
+      </c>
+      <c r="K52" t="b">
+        <v>0</v>
+      </c>
+      <c r="L52" t="b">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>93000</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>4960</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>4960</v>
+      </c>
+      <c r="R52" t="n">
+        <v>425716</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5190</v>
+      </c>
+      <c r="T52" t="n">
+        <v>5721.5</v>
+      </c>
+      <c r="U52" t="n">
+        <v>5779.5</v>
+      </c>
+      <c r="V52" t="n">
+        <v>6261.916666666667</v>
+      </c>
+      <c r="W52" t="n">
+        <v>-289.1785098366445</v>
+      </c>
+      <c r="X52" t="n">
+        <v>-220.6357694673449</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>-68.54274036929957</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>-60.95287031243825</v>
+      </c>
+      <c r="AA52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>-0.1895424836601307</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>-0.2496217851739788</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>-0.1896489839949906</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>-0.2817755219507772</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>0.09212653795578651</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>1.96078431372549</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>3.92156862745098</v>
+      </c>
+      <c r="AI52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN52" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>5733.76</v>
+      </c>
+      <c r="AP52" t="n">
+        <v>7236.58</v>
       </c>
     </row>
   </sheetData>

--- a/output/daily_screen_latest.xlsx
+++ b/output/daily_screen_latest.xlsx
@@ -643,17 +643,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>新日興</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>70.19607843137254</v>
+        <v>88.82352941176471</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -671,15 +671,15 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1740000</v>
+        <v>1000</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="K2" t="b">
         <v>0</v>
@@ -688,7 +688,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1740000</v>
+        <v>1000</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -697,61 +697,61 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>178.5</v>
+        <v>316.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>178.5</v>
+        <v>316.5</v>
       </c>
       <c r="R2" t="n">
-        <v>3394821</v>
+        <v>18734510</v>
       </c>
       <c r="S2" t="n">
-        <v>176.6</v>
+        <v>299.1</v>
       </c>
       <c r="T2" t="n">
-        <v>174.4</v>
+        <v>248.55</v>
       </c>
       <c r="U2" t="n">
-        <v>174.25</v>
+        <v>242.525</v>
       </c>
       <c r="V2" t="n">
-        <v>184.0006340026856</v>
+        <v>200.75</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7877311763919295</v>
+        <v>23.87242257329603</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.36837063170035</v>
+        <v>20.13494695700414</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.58063945530842</v>
+        <v>3.737475616291896</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.332062389715027</v>
+        <v>2.988451288546017</v>
       </c>
       <c r="AA2" t="b">
         <v>1</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.01709401709401703</v>
+        <v>0.614795918367347</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.04728763662152335</v>
+        <v>0.9843260188087775</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.01698751675915711</v>
+        <v>0.6210056642647734</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.07944137339832169</v>
+        <v>0.9102694033436574</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.0964288901574788</v>
+        <v>-0.2892637390788839</v>
       </c>
       <c r="AG2" t="n">
-        <v>60.78431372549019</v>
+        <v>100</v>
       </c>
       <c r="AH2" t="n">
-        <v>29.41176470588236</v>
+        <v>100</v>
       </c>
       <c r="AI2" t="b">
         <v>1</v>
@@ -785,7 +785,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -800,98 +800,100 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>62.11764705882353</v>
+        <v>85.68627450980392</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>New Entry</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4703000</v>
+        <v>6003000</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K3" t="b">
         <v>0</v>
       </c>
       <c r="L3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>4703000</v>
       </c>
       <c r="N3" t="n">
-        <v>4703000</v>
-      </c>
-      <c r="O3" t="inlineStr"/>
+        <v>1300000</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.2764193068254306</v>
+      </c>
       <c r="P3" t="n">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="Q3" t="n">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="R3" t="n">
-        <v>83332939</v>
+        <v>80059631</v>
       </c>
       <c r="S3" t="n">
-        <v>182.9</v>
+        <v>184.5</v>
       </c>
       <c r="T3" t="n">
+        <v>185.85</v>
+      </c>
+      <c r="U3" t="n">
         <v>185.425</v>
       </c>
-      <c r="U3" t="n">
-        <v>185.3</v>
-      </c>
       <c r="V3" t="n">
-        <v>184.3666666666667</v>
+        <v>184.6333333333333</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.4580398142185516</v>
+        <v>0.7453773925909388</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.150035242042377</v>
+        <v>0.02904728488428618</v>
       </c>
       <c r="Y3" t="n">
+        <v>0.7163301077066526</v>
+      </c>
+      <c r="Z3" t="n">
         <v>-0.3080045721761746</v>
       </c>
-      <c r="Z3" t="n">
-        <v>-1.145018467419051</v>
-      </c>
       <c r="AA3" t="b">
         <v>1</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01340482573726542</v>
+        <v>0.04557640750670244</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.08933717579250722</v>
+        <v>0.0893854748603351</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.0132983254024055</v>
+        <v>0.05178615340412884</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.05718343901570888</v>
+        <v>0.015328859395215</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.04388511361330338</v>
+        <v>0.03645729400891384</v>
       </c>
       <c r="AG3" t="n">
-        <v>58.82352941176471</v>
+        <v>70.58823529411765</v>
       </c>
       <c r="AH3" t="n">
-        <v>64.70588235294117</v>
+        <v>49.01960784313725</v>
       </c>
       <c r="AI3" t="b">
         <v>1</v>
@@ -900,19 +902,21 @@
         <v>1</v>
       </c>
       <c r="AK3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM3" t="b">
         <v>1</v>
       </c>
       <c r="AN3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>192.78</v>
+        <v>0</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
@@ -923,26 +927,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>美律</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>56.86274509803921</v>
+        <v>71.96078431372548</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,24 +955,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>6899000</v>
+        <v>1000</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="K4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="b">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>6899000</v>
+        <v>1000</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -977,61 +981,61 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1185</v>
+        <v>81.59999847412109</v>
       </c>
       <c r="Q4" t="n">
-        <v>1185</v>
+        <v>81.59999847412109</v>
       </c>
       <c r="R4" t="n">
-        <v>11097132</v>
+        <v>1776191</v>
       </c>
       <c r="S4" t="n">
-        <v>1226</v>
+        <v>80.58000030517579</v>
       </c>
       <c r="T4" t="n">
-        <v>1166.5</v>
+        <v>78.86499938964843</v>
       </c>
       <c r="U4" t="n">
-        <v>1154.75</v>
+        <v>78.69499931335449</v>
       </c>
       <c r="V4" t="n">
-        <v>1050.2</v>
+        <v>77.8641253153483</v>
       </c>
       <c r="W4" t="n">
-        <v>29.38537899162043</v>
+        <v>0.8049620099526749</v>
       </c>
       <c r="X4" t="n">
-        <v>36.60043499802292</v>
+        <v>0.6865894772022272</v>
       </c>
       <c r="Y4" t="n">
-        <v>-7.215056006402492</v>
+        <v>0.1183725327504477</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.6166410692021671</v>
+        <v>0.0449777644195708</v>
       </c>
       <c r="AA4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.2473684210526317</v>
+        <v>0.04347828207882465</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.2592986184909671</v>
+        <v>0.03584895116598297</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.2472619207177718</v>
+        <v>0.04968802797625105</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.2271448817141688</v>
+        <v>-0.03820766429913713</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.02011703900360295</v>
+        <v>0.08789569227538818</v>
       </c>
       <c r="AG4" t="n">
-        <v>98.0392156862745</v>
+        <v>64.70588235294117</v>
       </c>
       <c r="AH4" t="n">
-        <v>84.31372549019608</v>
+        <v>37.25490196078432</v>
       </c>
       <c r="AI4" t="b">
         <v>1</v>
@@ -1040,19 +1044,21 @@
         <v>1</v>
       </c>
       <c r="AK4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN4" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>1267.95</v>
+        <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
@@ -1063,43 +1069,43 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3376</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>新日興</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>56.86274509803921</v>
+        <v>70.19607843137256</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2512000</v>
+        <v>1740000</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K5" t="b">
         <v>0</v>
@@ -1108,90 +1114,94 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2502000</v>
+        <v>1740000</v>
       </c>
       <c r="N5" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.003996802557953637</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>6650</v>
+        <v>182.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>6650</v>
+        <v>182.5</v>
       </c>
       <c r="R5" t="n">
-        <v>898505</v>
+        <v>3877276</v>
       </c>
       <c r="S5" t="n">
-        <v>6755</v>
+        <v>177.3</v>
       </c>
       <c r="T5" t="n">
-        <v>6701.25</v>
+        <v>174.575</v>
       </c>
       <c r="U5" t="n">
-        <v>6636.5</v>
+        <v>174.4</v>
       </c>
       <c r="V5" t="n">
-        <v>5522.083333333333</v>
+        <v>184.0174751281738</v>
       </c>
       <c r="W5" t="n">
-        <v>99.94816799166802</v>
+        <v>0.121216112501088</v>
       </c>
       <c r="X5" t="n">
-        <v>221.5276412919161</v>
+        <v>-1.870453282860062</v>
       </c>
       <c r="Y5" t="n">
-        <v>-121.5794733002481</v>
+        <v>1.99166939536115</v>
       </c>
       <c r="Z5" t="n">
-        <v>-119.2467683861247</v>
+        <v>1.58063945530842</v>
       </c>
       <c r="AA5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.2418300653594772</v>
+        <v>0.01955307262569828</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.7924528301886793</v>
+        <v>0.00556763530954596</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.2417235650246172</v>
+        <v>0.02576281852312468</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.760299093411881</v>
+        <v>-0.06848898015557414</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.5185755283872637</v>
+        <v>0.09425179867869882</v>
       </c>
       <c r="AG5" t="n">
-        <v>96.07843137254902</v>
+        <v>60.78431372549019</v>
       </c>
       <c r="AH5" t="n">
-        <v>100</v>
+        <v>31.37254901960784</v>
       </c>
       <c r="AI5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ5" t="b">
         <v>1</v>
       </c>
       <c r="AK5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN5" t="b">
         <v>0</v>
       </c>
-      <c r="AO5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
+      </c>
       <c r="AP5" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -1201,118 +1211,118 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53.33333333333334</v>
+        <v>57.45098039215686</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>7224000</v>
+        <v>919000</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="K6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="b">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>7224000</v>
+        <v>819000</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.1221001221001221</v>
       </c>
       <c r="P6" t="n">
-        <v>1550</v>
+        <v>2395</v>
       </c>
       <c r="Q6" t="n">
-        <v>1550</v>
+        <v>2395</v>
       </c>
       <c r="R6" t="n">
-        <v>9261663</v>
+        <v>1872137</v>
       </c>
       <c r="S6" t="n">
-        <v>1631</v>
+        <v>2277</v>
       </c>
       <c r="T6" t="n">
-        <v>1595</v>
+        <v>2373.25</v>
       </c>
       <c r="U6" t="n">
-        <v>1583.5</v>
+        <v>2368.25</v>
       </c>
       <c r="V6" t="n">
-        <v>1467.916666666667</v>
+        <v>2052.093760172526</v>
       </c>
       <c r="W6" t="n">
-        <v>21.30466525258475</v>
+        <v>0.8000953301075242</v>
       </c>
       <c r="X6" t="n">
-        <v>48.35086230780859</v>
+        <v>4.132717150052427</v>
       </c>
       <c r="Y6" t="n">
-        <v>-27.04619705522384</v>
+        <v>-3.332621819944903</v>
       </c>
       <c r="Z6" t="n">
-        <v>-18.3199011524148</v>
+        <v>-18.36484503133515</v>
       </c>
       <c r="AA6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.1742424242424243</v>
+        <v>0.04357298474945526</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.1610486891385767</v>
+        <v>0.7104597033069244</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.1741359239075644</v>
+        <v>0.04978273064688166</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.1288949523617784</v>
+        <v>0.6364030878418043</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.04524097154578599</v>
+        <v>-0.5866203571949227</v>
       </c>
       <c r="AG6" t="n">
-        <v>88.23529411764706</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="AH6" t="n">
-        <v>78.43137254901961</v>
+        <v>94.11764705882352</v>
       </c>
       <c r="AI6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ6" t="b">
         <v>1</v>
@@ -1324,13 +1334,13 @@
         <v>0</v>
       </c>
       <c r="AM6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO6" t="n">
-        <v>1856.9</v>
+        <v>2433.32</v>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
@@ -1341,26 +1351,26 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>52.94117647058823</v>
+        <v>55.09803921568628</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1369,24 +1379,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>8937000</v>
+        <v>981000</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="K7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="b">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>8937000</v>
+        <v>981000</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1395,64 +1405,64 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1305</v>
+        <v>1660</v>
       </c>
       <c r="Q7" t="n">
-        <v>1305</v>
+        <v>1660</v>
       </c>
       <c r="R7" t="n">
-        <v>8831230</v>
+        <v>6228551</v>
       </c>
       <c r="S7" t="n">
-        <v>1363</v>
+        <v>1564</v>
       </c>
       <c r="T7" t="n">
-        <v>1345.75</v>
+        <v>1599.25</v>
       </c>
       <c r="U7" t="n">
-        <v>1333.75</v>
+        <v>1587.75</v>
       </c>
       <c r="V7" t="n">
-        <v>1191.916666666667</v>
+        <v>1305.716666666667</v>
       </c>
       <c r="W7" t="n">
-        <v>21.065695908208</v>
+        <v>26.9501913226668</v>
       </c>
       <c r="X7" t="n">
-        <v>50.49968106596425</v>
+        <v>48.053441792646</v>
       </c>
       <c r="Y7" t="n">
-        <v>-29.43398515775625</v>
+        <v>-21.1032504699792</v>
       </c>
       <c r="Z7" t="n">
-        <v>-23.0865726191041</v>
+        <v>-32.61550816475103</v>
       </c>
       <c r="AA7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.2253521126760563</v>
+        <v>0.1608391608391608</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.06097560975609762</v>
+        <v>0.6517412935323383</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.2252456123411963</v>
+        <v>0.1670489067365872</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.02882187297929928</v>
+        <v>0.5776846780672182</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.1964237393618971</v>
+        <v>-0.410635771330631</v>
       </c>
       <c r="AG7" t="n">
-        <v>94.11764705882352</v>
+        <v>90.19607843137256</v>
       </c>
       <c r="AH7" t="n">
-        <v>56.86274509803921</v>
+        <v>92.15686274509804</v>
       </c>
       <c r="AI7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ7" t="b">
         <v>1</v>
@@ -1464,12 +1474,14 @@
         <v>0</v>
       </c>
       <c r="AM7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO7" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1899.04</v>
+      </c>
       <c r="AP7" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -1479,26 +1491,26 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>51.76470588235294</v>
+        <v>54.90196078431372</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1507,24 +1519,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>19499000</v>
+        <v>1000</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="K8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="b">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>19499000</v>
+        <v>1000</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1533,64 +1545,64 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1055</v>
+        <v>578</v>
       </c>
       <c r="Q8" t="n">
-        <v>1055</v>
+        <v>578</v>
       </c>
       <c r="R8" t="n">
-        <v>13971291</v>
+        <v>34078662</v>
       </c>
       <c r="S8" t="n">
-        <v>1105</v>
+        <v>549.6</v>
       </c>
       <c r="T8" t="n">
-        <v>1174.8</v>
+        <v>538.45</v>
       </c>
       <c r="U8" t="n">
-        <v>1169.05</v>
+        <v>533.2</v>
       </c>
       <c r="V8" t="n">
-        <v>1042.083333333333</v>
+        <v>492.875</v>
       </c>
       <c r="W8" t="n">
-        <v>-12.86417730316748</v>
+        <v>11.09956801014948</v>
       </c>
       <c r="X8" t="n">
-        <v>21.91267007672974</v>
+        <v>13.94013544845524</v>
       </c>
       <c r="Y8" t="n">
-        <v>-34.77684737989722</v>
+        <v>-2.840567438305762</v>
       </c>
       <c r="Z8" t="n">
-        <v>-32.18600114940467</v>
+        <v>-5.550238265855194</v>
       </c>
       <c r="AA8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.1223404255319149</v>
+        <v>0.2219873150105709</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.1774553571428572</v>
+        <v>0.1991701244813278</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.122233925197055</v>
+        <v>0.2281970609079973</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.1453016203660589</v>
+        <v>0.1251135090162077</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.02306769516900387</v>
+        <v>0.1030835518917896</v>
       </c>
       <c r="AG8" t="n">
-        <v>82.35294117647058</v>
+        <v>98.0392156862745</v>
       </c>
       <c r="AH8" t="n">
-        <v>80.3921568627451</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="AI8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ8" t="b">
         <v>1</v>
@@ -1602,12 +1614,14 @@
         <v>0</v>
       </c>
       <c r="AM8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO8" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>610.37</v>
+      </c>
       <c r="AP8" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -1617,26 +1631,26 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>50.58823529411765</v>
+        <v>54.31372549019608</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1645,15 +1659,15 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>819000</v>
+        <v>4827000</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="K9" t="b">
         <v>0</v>
@@ -1662,76 +1676,76 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>769000</v>
+        <v>2657000</v>
       </c>
       <c r="N9" t="n">
-        <v>50000</v>
+        <v>2170000</v>
       </c>
       <c r="O9" t="n">
-        <v>0.06501950585175553</v>
+        <v>0.8167105758374106</v>
       </c>
       <c r="P9" t="n">
-        <v>2290</v>
+        <v>265</v>
       </c>
       <c r="Q9" t="n">
-        <v>2290</v>
+        <v>265</v>
       </c>
       <c r="R9" t="n">
-        <v>1436269</v>
+        <v>20810434</v>
       </c>
       <c r="S9" t="n">
-        <v>2237</v>
+        <v>259.3</v>
       </c>
       <c r="T9" t="n">
-        <v>2368.25</v>
+        <v>257.15</v>
       </c>
       <c r="U9" t="n">
-        <v>2358.25</v>
+        <v>257.325</v>
       </c>
       <c r="V9" t="n">
-        <v>2035.513899739583</v>
+        <v>229.7666666666667</v>
       </c>
       <c r="W9" t="n">
-        <v>-13.3989724262965</v>
+        <v>3.490949896689813</v>
       </c>
       <c r="X9" t="n">
-        <v>4.965872605038653</v>
+        <v>4.942006446294699</v>
       </c>
       <c r="Y9" t="n">
-        <v>-18.36484503133515</v>
+        <v>-1.451056549604886</v>
       </c>
       <c r="Z9" t="n">
-        <v>-26.14045885017151</v>
+        <v>-2.238911059461707</v>
       </c>
       <c r="AA9" t="b">
         <v>1</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.09569377990430628</v>
+        <v>-0.01303538175046559</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.5848892928341591</v>
+        <v>0.2649164677804297</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.09558727956944635</v>
+        <v>-0.006825635853039191</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.5527355560573608</v>
+        <v>0.1908598523153096</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.4571482764879145</v>
+        <v>-0.1976854881683487</v>
       </c>
       <c r="AG9" t="n">
-        <v>74.50980392156863</v>
+        <v>54.90196078431373</v>
       </c>
       <c r="AH9" t="n">
-        <v>94.11764705882352</v>
+        <v>78.43137254901961</v>
       </c>
       <c r="AI9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="b">
         <v>0</v>
@@ -1746,37 +1760,35 @@
         <v>1</v>
       </c>
       <c r="AO9" t="n">
-        <v>2500.68</v>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>281.43</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>275.74</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>慧洋-KY</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>48.62745098039216</v>
+        <v>40.98039215686275</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1785,7 +1797,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1793,7 +1805,7 @@
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="K10" t="b">
         <v>0</v>
@@ -1811,252 +1823,250 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>288</v>
+        <v>100.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>288</v>
+        <v>100.5</v>
       </c>
       <c r="R10" t="n">
-        <v>20130541</v>
+        <v>1156541</v>
       </c>
       <c r="S10" t="n">
-        <v>293.8</v>
+        <v>100.4199996948242</v>
       </c>
       <c r="T10" t="n">
-        <v>242.525</v>
+        <v>99.65000038146972</v>
       </c>
       <c r="U10" t="n">
-        <v>237.325</v>
+        <v>99.72500038146973</v>
       </c>
       <c r="V10" t="n">
-        <v>198.1333333333333</v>
+        <v>94.63333346048991</v>
       </c>
       <c r="W10" t="n">
-        <v>22.18902934147718</v>
+        <v>0.4292354820745743</v>
       </c>
       <c r="X10" t="n">
-        <v>19.20057805293116</v>
+        <v>0.5905741881405059</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.988451288546017</v>
+        <v>-0.1613387060659316</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.0885478524633</v>
+        <v>-0.1646208256594418</v>
       </c>
       <c r="AA10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.5652173913043479</v>
+        <v>-0.01470588235294112</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.7349397590361446</v>
+        <v>0.199283965872026</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.565110890969488</v>
+        <v>-0.008496136455514725</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.7027860222593463</v>
+        <v>0.1252273504069059</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.1376751312898583</v>
+        <v>-0.1337234868624206</v>
       </c>
       <c r="AG10" t="n">
-        <v>100</v>
+        <v>50.98039215686274</v>
       </c>
       <c r="AH10" t="n">
-        <v>96.07843137254902</v>
+        <v>68.62745098039215</v>
       </c>
       <c r="AI10" t="b">
         <v>1</v>
       </c>
       <c r="AJ10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>102.51</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>101.61</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>48.62745098039215</v>
+        <v>38.43137254901961</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>12671000</v>
+        <v>1000</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="K11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="b">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>12392000</v>
+        <v>1000</v>
       </c>
       <c r="N11" t="n">
-        <v>279000</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.02251452550032279</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2405</v>
+        <v>250</v>
       </c>
       <c r="Q11" t="n">
-        <v>2405</v>
+        <v>250</v>
       </c>
       <c r="R11" t="n">
-        <v>21297866</v>
+        <v>54319165</v>
       </c>
       <c r="S11" t="n">
-        <v>2435</v>
+        <v>242.9</v>
       </c>
       <c r="T11" t="n">
-        <v>2492</v>
+        <v>248.475</v>
       </c>
       <c r="U11" t="n">
-        <v>2493</v>
+        <v>248.5</v>
       </c>
       <c r="V11" t="n">
-        <v>2417.065966796875</v>
+        <v>250.4083333333333</v>
       </c>
       <c r="W11" t="n">
-        <v>-16.008714975359</v>
+        <v>-1.726222274315262</v>
       </c>
       <c r="X11" t="n">
-        <v>6.284409725025386</v>
+        <v>-1.819432439523187</v>
       </c>
       <c r="Y11" t="n">
-        <v>-22.29312470038438</v>
+        <v>0.09321016520792491</v>
       </c>
       <c r="Z11" t="n">
-        <v>-21.81617308668295</v>
+        <v>-0.9419037945475166</v>
       </c>
       <c r="AA11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0.008247422680412342</v>
+        <v>-0.001996007984031989</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.002943605599203813</v>
+        <v>-0.00990099009900991</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0.008353923015272269</v>
+        <v>0.004213737913394411</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.02921013117759452</v>
+        <v>-0.08395760556413001</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.02085620816232225</v>
+        <v>0.08817134347752442</v>
       </c>
       <c r="AG11" t="n">
-        <v>50.98039215686274</v>
+        <v>56.86274509803921</v>
       </c>
       <c r="AH11" t="n">
-        <v>41.17647058823529</v>
+        <v>25.49019607843137</v>
       </c>
       <c r="AI11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ11" t="b">
         <v>0</v>
       </c>
       <c r="AK11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN11" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>2659.93</v>
+        <v>0</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP11" t="n">
-        <v>2551.58</v>
+        <v>248.39</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>46.47058823529412</v>
+        <v>33.52941176470588</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2065,15 +2075,15 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>852000</v>
+        <v>470000</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="K12" t="b">
         <v>0</v>
@@ -2082,7 +2092,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>852000</v>
+        <v>470000</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -2091,73 +2101,73 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>7745</v>
+        <v>3230</v>
       </c>
       <c r="Q12" t="n">
-        <v>7745</v>
+        <v>3230</v>
       </c>
       <c r="R12" t="n">
-        <v>1404603</v>
+        <v>820966</v>
       </c>
       <c r="S12" t="n">
-        <v>7794</v>
+        <v>3105</v>
       </c>
       <c r="T12" t="n">
-        <v>8038.75</v>
+        <v>3209.5</v>
       </c>
       <c r="U12" t="n">
-        <v>7976.5</v>
+        <v>3224</v>
       </c>
       <c r="V12" t="n">
-        <v>6204.25</v>
+        <v>3035</v>
       </c>
       <c r="W12" t="n">
-        <v>81.65806719286047</v>
+        <v>-19.49173312319181</v>
       </c>
       <c r="X12" t="n">
-        <v>253.8900260653598</v>
+        <v>-22.50021037741953</v>
       </c>
       <c r="Y12" t="n">
-        <v>-172.2319588724994</v>
+        <v>3.008477254227724</v>
       </c>
       <c r="Z12" t="n">
-        <v>-184.0829978710731</v>
+        <v>-9.644407592523979</v>
       </c>
       <c r="AA12" t="b">
         <v>1</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.1915384615384614</v>
+        <v>-0.08238636363636365</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.7682648401826484</v>
+        <v>0.2471042471042471</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.1914319612036015</v>
+        <v>-0.07617661773893725</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.7361111034058501</v>
+        <v>0.173047631639127</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.5446791422022486</v>
+        <v>-0.2492242493780642</v>
       </c>
       <c r="AG12" t="n">
-        <v>92.15686274509804</v>
+        <v>23.52941176470588</v>
       </c>
       <c r="AH12" t="n">
-        <v>98.0392156862745</v>
+        <v>76.47058823529412</v>
       </c>
       <c r="AI12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM12" t="b">
         <v>1</v>
@@ -2165,27 +2175,29 @@
       <c r="AN12" t="b">
         <v>0</v>
       </c>
-      <c r="AO12" t="inlineStr"/>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
+      </c>
+      <c r="AP12" t="n">
+        <v>3463.42</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2194,7 +2206,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>46.47058823529412</v>
+        <v>63.33333333333333</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2203,15 +2215,15 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>6351450</v>
+        <v>19689000</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K13" t="b">
         <v>1</v>
@@ -2220,76 +2232,76 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>5151450</v>
+        <v>19499000</v>
       </c>
       <c r="N13" t="n">
-        <v>1200000</v>
+        <v>190000</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2329441225286084</v>
+        <v>0.009744089440484128</v>
       </c>
       <c r="P13" t="n">
-        <v>259.5</v>
+        <v>1100</v>
       </c>
       <c r="Q13" t="n">
-        <v>259.5</v>
+        <v>1100</v>
       </c>
       <c r="R13" t="n">
-        <v>14912383</v>
+        <v>19004375</v>
       </c>
       <c r="S13" t="n">
-        <v>273.3</v>
+        <v>1088</v>
       </c>
       <c r="T13" t="n">
-        <v>293.65</v>
+        <v>1180.75</v>
       </c>
       <c r="U13" t="n">
-        <v>293.925</v>
+        <v>1174.8</v>
       </c>
       <c r="V13" t="n">
-        <v>264.7578420003255</v>
+        <v>1046.433333333333</v>
       </c>
       <c r="W13" t="n">
-        <v>-5.665770075617104</v>
+        <v>-15.34855875526387</v>
       </c>
       <c r="X13" t="n">
-        <v>1.22878921339309</v>
+        <v>14.46042431033102</v>
       </c>
       <c r="Y13" t="n">
-        <v>-6.894559289010194</v>
+        <v>-29.80898306559489</v>
       </c>
       <c r="Z13" t="n">
-        <v>-6.333872622255273</v>
+        <v>-34.77684737989722</v>
       </c>
       <c r="AA13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0.02075471698113207</v>
+        <v>0.1213047910295617</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.04365195046372772</v>
+        <v>0.3110846245530394</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0.020861217315992</v>
+        <v>0.1275145369269881</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0.07580568724052605</v>
+        <v>0.2370280090879193</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.05494446992453406</v>
+        <v>-0.1095134721609312</v>
       </c>
       <c r="AG13" t="n">
-        <v>45.09803921568628</v>
+        <v>88.23529411764706</v>
       </c>
       <c r="AH13" t="n">
-        <v>33.33333333333333</v>
+        <v>80.3921568627451</v>
       </c>
       <c r="AI13" t="b">
         <v>0</v>
       </c>
       <c r="AJ13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK13" t="b">
         <v>0</v>
@@ -2298,30 +2310,32 @@
         <v>0</v>
       </c>
       <c r="AM13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN13" t="b">
         <v>0</v>
       </c>
       <c r="AO13" t="inlineStr"/>
-      <c r="AP13" t="n">
-        <v>327.45</v>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2330,96 +2344,96 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>46.07843137254902</v>
+        <v>54.90196078431373</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>6343000</v>
+        <v>8937000</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="b">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>6303000</v>
+        <v>8937000</v>
       </c>
       <c r="N14" t="n">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.00634618435665556</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>3325</v>
+        <v>1340</v>
       </c>
       <c r="Q14" t="n">
-        <v>3325</v>
+        <v>1340</v>
       </c>
       <c r="R14" t="n">
-        <v>2738048</v>
+        <v>7305114</v>
       </c>
       <c r="S14" t="n">
-        <v>3272</v>
+        <v>1345</v>
       </c>
       <c r="T14" t="n">
-        <v>3416.25</v>
+        <v>1357.75</v>
       </c>
       <c r="U14" t="n">
-        <v>3409.25</v>
+        <v>1345.75</v>
       </c>
       <c r="V14" t="n">
-        <v>3126.095308430989</v>
+        <v>1195.75</v>
       </c>
       <c r="W14" t="n">
-        <v>-29.48998274530686</v>
+        <v>14.95875410339909</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.706712031776206</v>
+        <v>43.39149567345122</v>
       </c>
       <c r="Y14" t="n">
-        <v>-26.78327071353065</v>
+        <v>-28.43274157005213</v>
       </c>
       <c r="Z14" t="n">
-        <v>-36.6965163567199</v>
+        <v>-29.43398515775625</v>
       </c>
       <c r="AA14" t="b">
         <v>1</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.04395604395604402</v>
+        <v>0.2181818181818183</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.3707888668898909</v>
+        <v>0.2072072072072073</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.04384954362118409</v>
+        <v>0.2243915640792447</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.3386351301130925</v>
+        <v>0.1331505917420872</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.2947855864919084</v>
+        <v>0.09124097233715744</v>
       </c>
       <c r="AG14" t="n">
-        <v>62.74509803921568</v>
+        <v>96.07843137254902</v>
       </c>
       <c r="AH14" t="n">
-        <v>88.23529411764706</v>
+        <v>72.54901960784314</v>
       </c>
       <c r="AI14" t="b">
         <v>0</v>
@@ -2437,11 +2451,9 @@
         <v>1</v>
       </c>
       <c r="AN14" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>3630.9</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO14" t="inlineStr"/>
       <c r="AP14" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -2451,17 +2463,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2470,7 +2482,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>45.09803921568628</v>
+        <v>54.90196078431373</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2479,24 +2491,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>981000</v>
+        <v>6899000</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="K15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="b">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>981000</v>
+        <v>6899000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2505,64 +2517,64 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1545</v>
+        <v>1195</v>
       </c>
       <c r="Q15" t="n">
-        <v>1545</v>
+        <v>1195</v>
       </c>
       <c r="R15" t="n">
-        <v>3669863</v>
+        <v>8380399</v>
       </c>
       <c r="S15" t="n">
-        <v>1569</v>
+        <v>1213</v>
       </c>
       <c r="T15" t="n">
-        <v>1587.75</v>
+        <v>1175.25</v>
       </c>
       <c r="U15" t="n">
-        <v>1575.5</v>
+        <v>1166.5</v>
       </c>
       <c r="V15" t="n">
-        <v>1294.8</v>
+        <v>1055.1</v>
       </c>
       <c r="W15" t="n">
-        <v>20.71374624538976</v>
+        <v>23.96201135512547</v>
       </c>
       <c r="X15" t="n">
-        <v>53.32925441014079</v>
+        <v>34.07275026944343</v>
       </c>
       <c r="Y15" t="n">
-        <v>-32.61550816475103</v>
+        <v>-10.11073891431796</v>
       </c>
       <c r="Z15" t="n">
-        <v>-32.04759134433519</v>
+        <v>-7.215056006402492</v>
       </c>
       <c r="AA15" t="b">
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.1884615384615385</v>
+        <v>0.1715686274509804</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.4372093023255814</v>
+        <v>0.3263041065482797</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.1883550381266785</v>
+        <v>0.1777783733484068</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.4050555655487831</v>
+        <v>0.2522474910831596</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.2167005274221045</v>
+        <v>-0.07446911773475273</v>
       </c>
       <c r="AG15" t="n">
-        <v>90.19607843137256</v>
+        <v>92.15686274509804</v>
       </c>
       <c r="AH15" t="n">
-        <v>90.19607843137256</v>
+        <v>84.31372549019608</v>
       </c>
       <c r="AI15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ15" t="b">
         <v>1</v>
@@ -2577,9 +2589,11 @@
         <v>0</v>
       </c>
       <c r="AN15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO15" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1309.72</v>
+      </c>
       <c r="AP15" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -2589,17 +2603,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2608,7 +2622,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>44.31372549019608</v>
+        <v>50.58823529411764</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2617,15 +2631,15 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>8348000</v>
+        <v>7224000</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K16" t="b">
         <v>1</v>
@@ -2634,7 +2648,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>8348000</v>
+        <v>7224000</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2643,61 +2657,61 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>660</v>
+        <v>1500</v>
       </c>
       <c r="Q16" t="n">
-        <v>660</v>
+        <v>1500</v>
       </c>
       <c r="R16" t="n">
-        <v>12369824</v>
+        <v>20799640</v>
       </c>
       <c r="S16" t="n">
-        <v>684.2</v>
+        <v>1584</v>
       </c>
       <c r="T16" t="n">
-        <v>704.2</v>
+        <v>1601.5</v>
       </c>
       <c r="U16" t="n">
-        <v>701.9</v>
+        <v>1595</v>
       </c>
       <c r="V16" t="n">
-        <v>633.6333333333333</v>
+        <v>1472.083333333333</v>
       </c>
       <c r="W16" t="n">
-        <v>-1.74079577342809</v>
+        <v>4.515422538564735</v>
       </c>
       <c r="X16" t="n">
-        <v>13.70184941527172</v>
+        <v>39.58377435395983</v>
       </c>
       <c r="Y16" t="n">
-        <v>-15.44264518869981</v>
+        <v>-35.06835181539509</v>
       </c>
       <c r="Z16" t="n">
-        <v>-14.31269808974348</v>
+        <v>-27.04619705522384</v>
       </c>
       <c r="AA16" t="b">
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.07491856677524433</v>
+        <v>0.0948905109489051</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.01694915254237284</v>
+        <v>0.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.07481206644038441</v>
+        <v>0.1011002568463315</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0.0152045842344255</v>
+        <v>0.1259433845348799</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.09001665067480991</v>
+        <v>-0.02484312768854835</v>
       </c>
       <c r="AG16" t="n">
-        <v>68.62745098039215</v>
+        <v>82.35294117647058</v>
       </c>
       <c r="AH16" t="n">
-        <v>47.05882352941176</v>
+        <v>70.58823529411765</v>
       </c>
       <c r="AI16" t="b">
         <v>0</v>
@@ -2727,17 +2741,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2746,7 +2760,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>41.1764705882353</v>
+        <v>47.84313725490196</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2755,24 +2769,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1000</v>
+        <v>8348000</v>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="n">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="K17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="b">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1000</v>
+        <v>8348000</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2781,64 +2795,64 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>547</v>
+        <v>684</v>
       </c>
       <c r="Q17" t="n">
-        <v>547</v>
+        <v>684</v>
       </c>
       <c r="R17" t="n">
-        <v>29732029</v>
+        <v>10778211</v>
       </c>
       <c r="S17" t="n">
-        <v>547.4</v>
+        <v>671.6</v>
       </c>
       <c r="T17" t="n">
-        <v>533.2</v>
+        <v>706.5</v>
       </c>
       <c r="U17" t="n">
-        <v>529.65</v>
+        <v>704.2</v>
       </c>
       <c r="V17" t="n">
-        <v>491.275</v>
+        <v>634.8166666666667</v>
       </c>
       <c r="W17" t="n">
-        <v>9.100039042176491</v>
+        <v>-2.481443657829232</v>
       </c>
       <c r="X17" t="n">
-        <v>14.65027730803168</v>
+        <v>10.46519080065153</v>
       </c>
       <c r="Y17" t="n">
-        <v>-5.550238265855194</v>
+        <v>-12.94663445848076</v>
       </c>
       <c r="Z17" t="n">
-        <v>-5.172832198214778</v>
+        <v>-15.44264518869981</v>
       </c>
       <c r="AA17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.1491596638655461</v>
+        <v>0.07210031347962387</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.0810276679841897</v>
+        <v>0.1158238172920065</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.1490531635306862</v>
+        <v>0.07831005937705027</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.04887393120739136</v>
+        <v>0.04176720182688642</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.1001792323232948</v>
+        <v>0.03654285755016384</v>
       </c>
       <c r="AG17" t="n">
-        <v>86.27450980392157</v>
+        <v>78.43137254901961</v>
       </c>
       <c r="AH17" t="n">
-        <v>62.74509803921568</v>
+        <v>54.90196078431373</v>
       </c>
       <c r="AI17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="b">
         <v>1</v>
@@ -2850,14 +2864,12 @@
         <v>0</v>
       </c>
       <c r="AM17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN17" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>610.45</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO17" t="inlineStr"/>
       <c r="AP17" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -2867,17 +2879,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2886,7 +2898,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>40.3921568627451</v>
+        <v>46.66666666666667</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2895,15 +2907,15 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>501000</v>
+        <v>2512000</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="K18" t="b">
         <v>0</v>
@@ -2912,7 +2924,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>501000</v>
+        <v>2512000</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2921,64 +2933,64 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>243.5</v>
+        <v>6535</v>
       </c>
       <c r="Q18" t="n">
-        <v>243.5</v>
+        <v>6535</v>
       </c>
       <c r="R18" t="n">
-        <v>30958244</v>
+        <v>1306728</v>
       </c>
       <c r="S18" t="n">
-        <v>243.6</v>
+        <v>6648</v>
       </c>
       <c r="T18" t="n">
-        <v>236.5</v>
+        <v>6751.75</v>
       </c>
       <c r="U18" t="n">
-        <v>235.25</v>
+        <v>6701.25</v>
       </c>
       <c r="V18" t="n">
-        <v>222.7083333333333</v>
+        <v>5573.833333333333</v>
       </c>
       <c r="W18" t="n">
-        <v>3.675449863078512</v>
+        <v>62.07606382651102</v>
       </c>
       <c r="X18" t="n">
-        <v>4.028286368827454</v>
+        <v>189.6373257988351</v>
       </c>
       <c r="Y18" t="n">
-        <v>-0.3528365057489413</v>
+        <v>-127.5612619723241</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.03681192755690965</v>
+        <v>-121.5794733002481</v>
       </c>
       <c r="AA18" t="b">
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.1144164759725401</v>
+        <v>0.1828054298642534</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.1378504672897196</v>
+        <v>0.9052478134110786</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.1143099756376802</v>
+        <v>0.1890151757616798</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.1056967305129213</v>
+        <v>0.8311911979459585</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.008613245124758917</v>
+        <v>-0.6421760221842787</v>
       </c>
       <c r="AG18" t="n">
-        <v>80.3921568627451</v>
+        <v>94.11764705882352</v>
       </c>
       <c r="AH18" t="n">
-        <v>72.54901960784314</v>
+        <v>96.07843137254902</v>
       </c>
       <c r="AI18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="b">
         <v>1</v>
@@ -2993,11 +3005,9 @@
         <v>0</v>
       </c>
       <c r="AN18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>247.88</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO18" t="inlineStr"/>
       <c r="AP18" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -3007,17 +3017,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3026,102 +3036,102 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>38.82352941176471</v>
+        <v>44.90196078431373</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>121000</v>
+        <v>6587450</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="b">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>121000</v>
+        <v>6351450</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>236000</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>0.03715686969117288</v>
       </c>
       <c r="P19" t="n">
-        <v>1320</v>
+        <v>278</v>
       </c>
       <c r="Q19" t="n">
-        <v>1320</v>
+        <v>278</v>
       </c>
       <c r="R19" t="n">
-        <v>2504403</v>
+        <v>23007725</v>
       </c>
       <c r="S19" t="n">
-        <v>1413</v>
+        <v>269.6</v>
       </c>
       <c r="T19" t="n">
-        <v>1388.75</v>
+        <v>292.975</v>
       </c>
       <c r="U19" t="n">
-        <v>1383.25</v>
+        <v>293.65</v>
       </c>
       <c r="V19" t="n">
-        <v>1262.461206054687</v>
+        <v>265.1059524536133</v>
       </c>
       <c r="W19" t="n">
-        <v>13.51938467465766</v>
+        <v>-5.049606411829302</v>
       </c>
       <c r="X19" t="n">
-        <v>44.57917000678403</v>
+        <v>-0.02688991165138888</v>
       </c>
       <c r="Y19" t="n">
-        <v>-31.05978533212637</v>
+        <v>-5.022716500177913</v>
       </c>
       <c r="Z19" t="n">
-        <v>-19.92451621570898</v>
+        <v>-6.894559289010194</v>
       </c>
       <c r="AA19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.09090909090909083</v>
+        <v>-0.04631217838765012</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.3041746242042211</v>
+        <v>0.08123508695633075</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.0908025905742309</v>
+        <v>-0.04010243249022372</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.2720208874274228</v>
+        <v>0.007178471491210647</v>
       </c>
       <c r="AF19" t="n">
-        <v>-0.1812182968531919</v>
+        <v>-0.04728090398143436</v>
       </c>
       <c r="AG19" t="n">
-        <v>70.58823529411765</v>
+        <v>37.25490196078432</v>
       </c>
       <c r="AH19" t="n">
-        <v>86.27450980392157</v>
+        <v>45.09803921568628</v>
       </c>
       <c r="AI19" t="b">
         <v>0</v>
       </c>
       <c r="AJ19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="b">
         <v>0</v>
@@ -3130,32 +3140,30 @@
         <v>0</v>
       </c>
       <c r="AM19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN19" t="b">
         <v>0</v>
       </c>
       <c r="AO19" t="inlineStr"/>
-      <c r="AP19" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+      <c r="AP19" t="n">
+        <v>317.26</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3164,7 +3172,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>38.82352941176471</v>
+        <v>44.50980392156863</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3173,15 +3181,15 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1000</v>
+        <v>852000</v>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="K20" t="b">
         <v>0</v>
@@ -3190,7 +3198,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1000</v>
+        <v>852000</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -3199,61 +3207,61 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>99.09999847412109</v>
+        <v>8000</v>
       </c>
       <c r="Q20" t="n">
-        <v>99.09999847412109</v>
+        <v>8000</v>
       </c>
       <c r="R20" t="n">
-        <v>12418893</v>
+        <v>1994023</v>
       </c>
       <c r="S20" t="n">
-        <v>105.9199996948242</v>
+        <v>7745</v>
       </c>
       <c r="T20" t="n">
-        <v>112.9799999237061</v>
+        <v>8081.25</v>
       </c>
       <c r="U20" t="n">
-        <v>112.3599998474121</v>
+        <v>8038.75</v>
       </c>
       <c r="V20" t="n">
-        <v>95.97166659037272</v>
+        <v>6269.75</v>
       </c>
       <c r="W20" t="n">
-        <v>-1.177354768187755</v>
+        <v>86.39997614742151</v>
       </c>
       <c r="X20" t="n">
-        <v>3.174555950533045</v>
+        <v>220.3920160817722</v>
       </c>
       <c r="Y20" t="n">
-        <v>-4.351910718720799</v>
+        <v>-133.9920399343507</v>
       </c>
       <c r="Z20" t="n">
-        <v>-4.031213786765679</v>
+        <v>-172.2319588724994</v>
       </c>
       <c r="AA20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.1430219372819748</v>
+        <v>0.118881118881119</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.009164985273403481</v>
+        <v>0.9656019656019657</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.1429154369471148</v>
+        <v>0.1250908647785454</v>
       </c>
       <c r="AE20" t="n">
-        <v>-0.02298875150339486</v>
+        <v>0.8915453501368455</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.1659041884505097</v>
+        <v>-0.7664544853583002</v>
       </c>
       <c r="AG20" t="n">
-        <v>84.31372549019608</v>
+        <v>86.27450980392157</v>
       </c>
       <c r="AH20" t="n">
-        <v>45.09803921568628</v>
+        <v>98.0392156862745</v>
       </c>
       <c r="AI20" t="b">
         <v>0</v>
@@ -3268,12 +3276,14 @@
         <v>0</v>
       </c>
       <c r="AM20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN20" t="b">
         <v>0</v>
       </c>
-      <c r="AO20" t="inlineStr"/>
+      <c r="AO20" t="n">
+        <v>9520</v>
+      </c>
       <c r="AP20" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -3283,17 +3293,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3302,7 +3312,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>37.84313725490197</v>
+        <v>40.58823529411765</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3311,15 +3321,15 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1000</v>
+        <v>121000</v>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="K21" t="b">
         <v>0</v>
@@ -3328,7 +3338,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1000</v>
+        <v>121000</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -3337,61 +3347,61 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>3640</v>
+        <v>1330</v>
       </c>
       <c r="Q21" t="n">
-        <v>3640</v>
+        <v>1330</v>
       </c>
       <c r="R21" t="n">
-        <v>1172944</v>
+        <v>1726741</v>
       </c>
       <c r="S21" t="n">
-        <v>3737</v>
+        <v>1371</v>
       </c>
       <c r="T21" t="n">
-        <v>3862.5</v>
+        <v>1392.75</v>
       </c>
       <c r="U21" t="n">
-        <v>3845.25</v>
+        <v>1388.75</v>
       </c>
       <c r="V21" t="n">
-        <v>3755.288911946614</v>
+        <v>1269.124935913086</v>
       </c>
       <c r="W21" t="n">
-        <v>-38.10545151630822</v>
+        <v>1.229868199121256</v>
       </c>
       <c r="X21" t="n">
-        <v>29.06714154035313</v>
+        <v>35.90930964525147</v>
       </c>
       <c r="Y21" t="n">
-        <v>-67.17259305666136</v>
+        <v>-34.67944144613021</v>
       </c>
       <c r="Z21" t="n">
-        <v>-59.6776007272012</v>
+        <v>-31.05978533212637</v>
       </c>
       <c r="AA21" t="b">
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.1047040971168438</v>
+        <v>0.06400000000000006</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.04514260318279262</v>
+        <v>0.4298366135921066</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.1045975967819839</v>
+        <v>0.07020974589742646</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.01298886640599428</v>
+        <v>0.3557799981269865</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.0916087303759896</v>
+        <v>-0.28557025222956</v>
       </c>
       <c r="AG21" t="n">
-        <v>78.43137254901961</v>
+        <v>76.47058823529412</v>
       </c>
       <c r="AH21" t="n">
-        <v>52.94117647058824</v>
+        <v>88.23529411764706</v>
       </c>
       <c r="AI21" t="b">
         <v>0</v>
@@ -3421,17 +3431,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3440,7 +3450,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>36.27450980392157</v>
+        <v>38.82352941176471</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3449,15 +3459,15 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>3921000</v>
+        <v>1000</v>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="K22" t="b">
         <v>0</v>
@@ -3466,7 +3476,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3921000</v>
+        <v>1000</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -3475,64 +3485,64 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>90.5</v>
+        <v>102.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>90.5</v>
+        <v>102.5</v>
       </c>
       <c r="R22" t="n">
-        <v>4910073</v>
+        <v>12862742</v>
       </c>
       <c r="S22" t="n">
-        <v>91.84000091552734</v>
+        <v>103.0199996948242</v>
       </c>
       <c r="T22" t="n">
-        <v>87.4550006866455</v>
+        <v>113.4049999237061</v>
       </c>
       <c r="U22" t="n">
-        <v>87.04000053405761</v>
+        <v>112.9799999237061</v>
       </c>
       <c r="V22" t="n">
-        <v>84.75666681925456</v>
+        <v>96.16666653951009</v>
       </c>
       <c r="W22" t="n">
-        <v>1.89408881446407</v>
+        <v>-1.74440482969753</v>
       </c>
       <c r="X22" t="n">
-        <v>1.951049148829624</v>
+        <v>2.19076379448693</v>
       </c>
       <c r="Y22" t="n">
-        <v>-0.05696033436555425</v>
+        <v>-3.93516862418446</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.2311357672828671</v>
+        <v>-4.351910718720799</v>
       </c>
       <c r="AA22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.1009732768844744</v>
+        <v>0.09042553191489366</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.007795065973870141</v>
+        <v>0.1288545876102334</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.1008667765496145</v>
+        <v>0.09663527781232006</v>
       </c>
       <c r="AE22" t="n">
-        <v>-0.0243586708029282</v>
+        <v>0.05479797214511328</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.1252254473525427</v>
+        <v>0.04183730566720678</v>
       </c>
       <c r="AG22" t="n">
-        <v>76.47058823529412</v>
+        <v>80.3921568627451</v>
       </c>
       <c r="AH22" t="n">
-        <v>43.13725490196079</v>
+        <v>58.82352941176471</v>
       </c>
       <c r="AI22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="b">
         <v>1</v>
@@ -3544,14 +3554,12 @@
         <v>0</v>
       </c>
       <c r="AM22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN22" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>91.22</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO22" t="inlineStr"/>
       <c r="AP22" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -3561,17 +3569,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3580,7 +3588,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>34.31372549019608</v>
+        <v>38.03921568627451</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3589,24 +3597,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>23519000</v>
+        <v>3921000</v>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="K23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="b">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>23519000</v>
+        <v>3921000</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -3615,67 +3623,67 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>523</v>
+        <v>92.19999694824219</v>
       </c>
       <c r="Q23" t="n">
-        <v>523</v>
+        <v>92.19999694824219</v>
       </c>
       <c r="R23" t="n">
-        <v>42890540</v>
+        <v>2571552</v>
       </c>
       <c r="S23" t="n">
-        <v>564.8</v>
+        <v>91.2</v>
       </c>
       <c r="T23" t="n">
-        <v>587.35</v>
+        <v>87.90500068664551</v>
       </c>
       <c r="U23" t="n">
-        <v>587.65</v>
+        <v>87.4550006866455</v>
       </c>
       <c r="V23" t="n">
-        <v>571.575</v>
+        <v>84.81166674296061</v>
       </c>
       <c r="W23" t="n">
-        <v>-10.3544533195294</v>
+        <v>1.827187191400142</v>
       </c>
       <c r="X23" t="n">
-        <v>4.523624205409231</v>
+        <v>1.926276757343728</v>
       </c>
       <c r="Y23" t="n">
-        <v>-14.87807752493863</v>
+        <v>-0.09908956594358531</v>
       </c>
       <c r="Z23" t="n">
-        <v>-12.23394683108289</v>
+        <v>-0.05696033436555425</v>
       </c>
       <c r="AA23" t="b">
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>-0.01134215500945179</v>
+        <v>0.1081730808908419</v>
       </c>
       <c r="AC23" t="n">
-        <v>-0.2485632183908046</v>
+        <v>0.03712030782589637</v>
       </c>
       <c r="AD23" t="n">
-        <v>-0.01144865534431172</v>
+        <v>0.1143828267882683</v>
       </c>
       <c r="AE23" t="n">
-        <v>-0.280716955167603</v>
+        <v>-0.03693630763922373</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.2692682998232913</v>
+        <v>0.151319134427492</v>
       </c>
       <c r="AG23" t="n">
-        <v>49.01960784313725</v>
+        <v>84.31372549019608</v>
       </c>
       <c r="AH23" t="n">
-        <v>5.88235294117647</v>
+        <v>39.21568627450981</v>
       </c>
       <c r="AI23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK23" t="b">
         <v>0</v>
@@ -3687,27 +3695,31 @@
         <v>0</v>
       </c>
       <c r="AN23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO23" t="inlineStr"/>
-      <c r="AP23" t="n">
-        <v>617.74</v>
+        <v>1</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>93.48999999999999</v>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3716,7 +3728,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>34.11764705882354</v>
+        <v>37.64705882352942</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3725,15 +3737,15 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1000</v>
+        <v>501000</v>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="K24" t="b">
         <v>0</v>
@@ -3742,7 +3754,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1000</v>
+        <v>501000</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3751,67 +3763,67 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>5975</v>
+        <v>240.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>5975</v>
+        <v>240.5</v>
       </c>
       <c r="R24" t="n">
-        <v>3147937</v>
+        <v>62505022</v>
       </c>
       <c r="S24" t="n">
-        <v>6421</v>
+        <v>241.6</v>
       </c>
       <c r="T24" t="n">
-        <v>6496.25</v>
+        <v>237.1</v>
       </c>
       <c r="U24" t="n">
-        <v>6498.5</v>
+        <v>236.5</v>
       </c>
       <c r="V24" t="n">
-        <v>5851.970617675781</v>
+        <v>223.3583333333333</v>
       </c>
       <c r="W24" t="n">
-        <v>-46.50900193349571</v>
+        <v>2.920994022686273</v>
       </c>
       <c r="X24" t="n">
-        <v>71.48572648232718</v>
+        <v>3.806827899599218</v>
       </c>
       <c r="Y24" t="n">
-        <v>-117.9947284158229</v>
+        <v>-0.8858338769129448</v>
       </c>
       <c r="Z24" t="n">
-        <v>-74.10685479439196</v>
+        <v>-0.3528365057489413</v>
       </c>
       <c r="AA24" t="b">
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>-0.007475083056478371</v>
+        <v>0.05251641137855589</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.4564191261175792</v>
+        <v>0.1935483870967742</v>
       </c>
       <c r="AD24" t="n">
-        <v>-0.007581583391338298</v>
+        <v>0.05872615727598229</v>
       </c>
       <c r="AE24" t="n">
-        <v>0.4242653893407808</v>
+        <v>0.1194917716316541</v>
       </c>
       <c r="AF24" t="n">
-        <v>-0.4318469727321191</v>
+        <v>-0.06076561435567185</v>
       </c>
       <c r="AG24" t="n">
-        <v>52.94117647058824</v>
+        <v>74.50980392156863</v>
       </c>
       <c r="AH24" t="n">
-        <v>92.15686274509804</v>
+        <v>64.70588235294117</v>
       </c>
       <c r="AI24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK24" t="b">
         <v>0</v>
@@ -3823,27 +3835,31 @@
         <v>0</v>
       </c>
       <c r="AN24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO24" t="inlineStr"/>
-      <c r="AP24" t="n">
-        <v>6978.68</v>
+        <v>1</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>250.6</v>
+      </c>
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3852,7 +3868,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>33.52941176470588</v>
+        <v>37.05882352941177</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3861,24 +3877,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>5163000</v>
+        <v>12671000</v>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="K25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" t="b">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>5163000</v>
+        <v>12671000</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3887,105 +3903,101 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>19.60000038146973</v>
+        <v>2420</v>
       </c>
       <c r="Q25" t="n">
-        <v>19.60000038146973</v>
+        <v>2420</v>
       </c>
       <c r="R25" t="n">
-        <v>44575418</v>
+        <v>23935196</v>
       </c>
       <c r="S25" t="n">
-        <v>19.47999992370605</v>
+        <v>2421</v>
       </c>
       <c r="T25" t="n">
-        <v>19.04000005722046</v>
+        <v>2490</v>
       </c>
       <c r="U25" t="n">
-        <v>18.99500007629394</v>
+        <v>2492</v>
       </c>
       <c r="V25" t="n">
-        <v>19.06166674296061</v>
+        <v>2418.347587076823</v>
       </c>
       <c r="W25" t="n">
-        <v>0.1700411148033254</v>
+        <v>-18.1296483855067</v>
       </c>
       <c r="X25" t="n">
-        <v>0.1008623084804349</v>
+        <v>1.401598102918036</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.06917880632289054</v>
+        <v>-19.53124648842473</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.07021311150095588</v>
+        <v>-22.29312470038367</v>
       </c>
       <c r="AA25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.04812831988295607</v>
+        <v>-0.01626016260162599</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.03430077004542809</v>
+        <v>0.03281854187026023</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.04802181954809615</v>
+        <v>-0.01005041670419959</v>
       </c>
       <c r="AE25" t="n">
-        <v>0.00214703326862975</v>
+        <v>-0.04123807359485987</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.0458747862794664</v>
+        <v>0.03118765689066028</v>
       </c>
       <c r="AG25" t="n">
-        <v>64.70588235294117</v>
+        <v>49.01960784313725</v>
       </c>
       <c r="AH25" t="n">
-        <v>50.98039215686274</v>
+        <v>35.29411764705883</v>
       </c>
       <c r="AI25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
-      <c r="AP25" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>2642.64</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>2553.68</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3994,24 +4006,24 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>33.13725490196079</v>
+        <v>37.05882352941177</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>2657000</v>
+        <v>6457000</v>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="K26" t="b">
         <v>0</v>
@@ -4020,76 +4032,76 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>2657000</v>
+        <v>6343000</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>114000</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>0.01797256818540123</v>
       </c>
       <c r="P26" t="n">
-        <v>247</v>
+        <v>3235</v>
       </c>
       <c r="Q26" t="n">
-        <v>247</v>
+        <v>3235</v>
       </c>
       <c r="R26" t="n">
-        <v>16920521</v>
+        <v>3941653</v>
       </c>
       <c r="S26" t="n">
-        <v>261.9</v>
+        <v>3256</v>
       </c>
       <c r="T26" t="n">
-        <v>257.325</v>
+        <v>3406.5</v>
       </c>
       <c r="U26" t="n">
-        <v>257.2</v>
+        <v>3416.25</v>
       </c>
       <c r="V26" t="n">
-        <v>228.8416666666667</v>
+        <v>3140.579235839844</v>
       </c>
       <c r="W26" t="n">
-        <v>3.065859524234213</v>
+        <v>-36.53744038086506</v>
       </c>
       <c r="X26" t="n">
-        <v>5.30477058369592</v>
+        <v>-9.472857701593977</v>
       </c>
       <c r="Y26" t="n">
-        <v>-2.238911059461707</v>
+        <v>-27.06458267927109</v>
       </c>
       <c r="Z26" t="n">
-        <v>-0.6301395246374328</v>
+        <v>-26.78327071353065</v>
       </c>
       <c r="AA26" t="b">
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.01022494887525571</v>
+        <v>-0.0568513119533528</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.1330275229357798</v>
+        <v>0.3673071585049619</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.01011844854039579</v>
+        <v>-0.0506415660559264</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.1008737861589815</v>
+        <v>0.2932505430398418</v>
       </c>
       <c r="AF26" t="n">
-        <v>-0.09075533761858567</v>
+        <v>-0.3438921090957682</v>
       </c>
       <c r="AG26" t="n">
-        <v>56.86274509803921</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="AH26" t="n">
-        <v>70.58823529411765</v>
+        <v>86.27450980392157</v>
       </c>
       <c r="AI26" t="b">
         <v>0</v>
       </c>
       <c r="AJ26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="b">
         <v>0</v>
@@ -4104,28 +4116,26 @@
         <v>1</v>
       </c>
       <c r="AO26" t="n">
-        <v>272.19</v>
-      </c>
-      <c r="AP26" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>3545.56</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>3595.53</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4134,7 +4144,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>32.54901960784314</v>
+        <v>35.68627450980392</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4143,24 +4153,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>6264000</v>
+        <v>23519000</v>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="K27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="b">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>6264000</v>
+        <v>23519000</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -4169,67 +4179,67 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1970</v>
+        <v>542</v>
       </c>
       <c r="Q27" t="n">
-        <v>1970</v>
+        <v>542</v>
       </c>
       <c r="R27" t="n">
-        <v>3909794</v>
+        <v>34027010</v>
       </c>
       <c r="S27" t="n">
-        <v>1991</v>
+        <v>547.8</v>
       </c>
       <c r="T27" t="n">
-        <v>1959</v>
+        <v>586.95</v>
       </c>
       <c r="U27" t="n">
-        <v>1950.5</v>
+        <v>587.35</v>
       </c>
       <c r="V27" t="n">
-        <v>2055.482550048828</v>
+        <v>569.9083333333333</v>
       </c>
       <c r="W27" t="n">
-        <v>8.941430941387807</v>
+        <v>-12.38723724009731</v>
       </c>
       <c r="X27" t="n">
-        <v>13.65461057340279</v>
+        <v>1.141451916307924</v>
       </c>
       <c r="Y27" t="n">
-        <v>-4.713179632014981</v>
+        <v>-13.52868915640523</v>
       </c>
       <c r="Z27" t="n">
-        <v>-0.3407699140660494</v>
+        <v>-14.87807752493863</v>
       </c>
       <c r="AA27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.09444444444444455</v>
+        <v>-0.01454545454545453</v>
       </c>
       <c r="AC27" t="n">
-        <v>-0.1459812660562713</v>
+        <v>-0.1557632398753894</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.09433794410958463</v>
+        <v>-0.008335708648028128</v>
       </c>
       <c r="AE27" t="n">
-        <v>-0.1781350028330696</v>
+        <v>-0.2298198553405095</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.2724729469426542</v>
+        <v>0.2214841466924814</v>
       </c>
       <c r="AG27" t="n">
-        <v>72.54901960784314</v>
+        <v>52.94117647058824</v>
       </c>
       <c r="AH27" t="n">
-        <v>17.64705882352941</v>
+        <v>9.803921568627452</v>
       </c>
       <c r="AI27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="b">
         <v>0</v>
@@ -4238,34 +4248,30 @@
         <v>0</v>
       </c>
       <c r="AM27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN27" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>2025.16</v>
-      </c>
-      <c r="AP27" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="AO27" t="inlineStr"/>
+      <c r="AP27" t="n">
+        <v>604.3200000000001</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4274,7 +4280,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>32.54901960784314</v>
+        <v>35.68627450980392</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4283,15 +4289,15 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>4328000</v>
+        <v>1000</v>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="K28" t="b">
         <v>0</v>
@@ -4300,7 +4306,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>4328000</v>
+        <v>1000</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -4309,61 +4315,61 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>4945</v>
+        <v>3710</v>
       </c>
       <c r="Q28" t="n">
-        <v>4945</v>
+        <v>3710</v>
       </c>
       <c r="R28" t="n">
-        <v>1797434</v>
+        <v>1277241</v>
       </c>
       <c r="S28" t="n">
-        <v>5175</v>
+        <v>3691</v>
       </c>
       <c r="T28" t="n">
-        <v>5297.25</v>
+        <v>3871</v>
       </c>
       <c r="U28" t="n">
-        <v>5284.75</v>
+        <v>3862.5</v>
       </c>
       <c r="V28" t="n">
-        <v>5321.183333333333</v>
+        <v>3760.812365722656</v>
       </c>
       <c r="W28" t="n">
-        <v>-59.96536124676004</v>
+        <v>-46.17859929668339</v>
       </c>
       <c r="X28" t="n">
-        <v>40.94456185079647</v>
+        <v>14.01799337294583</v>
       </c>
       <c r="Y28" t="n">
-        <v>-100.9099230975565</v>
+        <v>-60.19659266962921</v>
       </c>
       <c r="Z28" t="n">
-        <v>-79.58939541500392</v>
+        <v>-67.17259305666136</v>
       </c>
       <c r="AA28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.05324813631522907</v>
+        <v>0.04802259887005644</v>
       </c>
       <c r="AC28" t="n">
-        <v>-0.02500883304627943</v>
+        <v>0.09809031415920377</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.05314163598036914</v>
+        <v>0.05423234476748284</v>
       </c>
       <c r="AE28" t="n">
-        <v>-0.05716256982307777</v>
+        <v>0.02403369869408367</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.1103042058034469</v>
+        <v>0.03019864607339917</v>
       </c>
       <c r="AG28" t="n">
-        <v>66.66666666666666</v>
+        <v>72.54901960784314</v>
       </c>
       <c r="AH28" t="n">
-        <v>35.29411764705883</v>
+        <v>50.98039215686274</v>
       </c>
       <c r="AI28" t="b">
         <v>0</v>
@@ -4378,12 +4384,14 @@
         <v>0</v>
       </c>
       <c r="AM28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN28" t="b">
         <v>0</v>
       </c>
-      <c r="AO28" t="inlineStr"/>
+      <c r="AO28" t="n">
+        <v>4392.64</v>
+      </c>
       <c r="AP28" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -4393,17 +4401,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>6271</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4412,7 +4420,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>30.78431372549019</v>
+        <v>33.92156862745098</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4421,15 +4429,15 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>654000</v>
+        <v>2185000</v>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="K29" t="b">
         <v>0</v>
@@ -4438,7 +4446,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>654000</v>
+        <v>2185000</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -4447,67 +4455,67 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>469.5</v>
+        <v>232</v>
       </c>
       <c r="Q29" t="n">
-        <v>469.5</v>
+        <v>232</v>
       </c>
       <c r="R29" t="n">
-        <v>16981651</v>
+        <v>3476575</v>
       </c>
       <c r="S29" t="n">
-        <v>477.8</v>
+        <v>226.9</v>
       </c>
       <c r="T29" t="n">
-        <v>505.825</v>
+        <v>233.1</v>
       </c>
       <c r="U29" t="n">
-        <v>506.275</v>
+        <v>232.975</v>
       </c>
       <c r="V29" t="n">
-        <v>455.4916666666667</v>
+        <v>212.4583333333333</v>
       </c>
       <c r="W29" t="n">
-        <v>-9.203516729578951</v>
+        <v>-0.8140955292035414</v>
       </c>
       <c r="X29" t="n">
-        <v>-0.4932252695210619</v>
+        <v>1.745585269993927</v>
       </c>
       <c r="Y29" t="n">
-        <v>-8.710291460057888</v>
+        <v>-2.559680799197468</v>
       </c>
       <c r="Z29" t="n">
-        <v>-8.911408942437436</v>
+        <v>-3.519700087457216</v>
       </c>
       <c r="AA29" t="b">
         <v>1</v>
       </c>
       <c r="AB29" t="n">
-        <v>-0.01880877742946707</v>
+        <v>0.01089324618736387</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.1549815498154981</v>
+        <v>0.2275132275132274</v>
       </c>
       <c r="AD29" t="n">
-        <v>-0.018915277764327</v>
+        <v>0.01710299208479027</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.1228278130386997</v>
+        <v>0.1534566120481073</v>
       </c>
       <c r="AF29" t="n">
-        <v>-0.1417430908030267</v>
+        <v>-0.1363536199633171</v>
       </c>
       <c r="AG29" t="n">
-        <v>47.05882352941176</v>
+        <v>58.82352941176471</v>
       </c>
       <c r="AH29" t="n">
-        <v>76.47058823529412</v>
+        <v>74.50980392156863</v>
       </c>
       <c r="AI29" t="b">
         <v>0</v>
       </c>
       <c r="AJ29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK29" t="b">
         <v>0</v>
@@ -4519,27 +4527,31 @@
         <v>1</v>
       </c>
       <c r="AN29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO29" t="inlineStr"/>
-      <c r="AP29" t="n">
-        <v>537.74</v>
+        <v>1</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>261.23</v>
+      </c>
+      <c r="AP29" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4548,7 +4560,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>29.6078431372549</v>
+        <v>32.74509803921568</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4557,15 +4569,15 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1000</v>
+        <v>5163000</v>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="K30" t="b">
         <v>0</v>
@@ -4574,7 +4586,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1000</v>
+        <v>5163000</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -4583,101 +4595,105 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>99.09999847412109</v>
+        <v>19.60000038146973</v>
       </c>
       <c r="Q30" t="n">
-        <v>99.09999847412109</v>
+        <v>19.60000038146973</v>
       </c>
       <c r="R30" t="n">
-        <v>1361326</v>
+        <v>40203403</v>
       </c>
       <c r="S30" t="n">
-        <v>101.0199996948242</v>
+        <v>19.5</v>
       </c>
       <c r="T30" t="n">
-        <v>99.72500038146973</v>
+        <v>19.08250007629395</v>
       </c>
       <c r="U30" t="n">
-        <v>99.87000045776367</v>
+        <v>19.04000005722046</v>
       </c>
       <c r="V30" t="n">
-        <v>94.35500017801921</v>
+        <v>19.06916675567627</v>
       </c>
       <c r="W30" t="n">
-        <v>0.466288038997547</v>
+        <v>0.1770843242964411</v>
       </c>
       <c r="X30" t="n">
-        <v>0.6309088646569888</v>
+        <v>0.1161067116436361</v>
       </c>
       <c r="Y30" t="n">
-        <v>-0.1646208256594418</v>
+        <v>0.06097761265280496</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.05616494588420051</v>
+        <v>0.06917880632289054</v>
       </c>
       <c r="AA30" t="b">
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>-0.02843138750861673</v>
+        <v>0.04533335367838531</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.2189421248979697</v>
+        <v>0.02349873482524845</v>
       </c>
       <c r="AD30" t="n">
-        <v>-0.02853788784347666</v>
+        <v>0.05154309957581171</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.1867883881211714</v>
+        <v>-0.05055788063987166</v>
       </c>
       <c r="AF30" t="n">
-        <v>-0.215326275964648</v>
+        <v>0.1021009802156834</v>
       </c>
       <c r="AG30" t="n">
-        <v>41.17647058823529</v>
+        <v>68.62745098039215</v>
       </c>
       <c r="AH30" t="n">
-        <v>82.35294117647058</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="AI30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM30" t="b">
         <v>0</v>
       </c>
       <c r="AN30" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>101.08</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>102.66</v>
+        <v>0</v>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
+      </c>
+      <c r="AP30" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4686,96 +4702,96 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>29.41176470588236</v>
+        <v>32.54901960784314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>7582000</v>
+        <v>6331000</v>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" t="b">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>7582000</v>
+        <v>6264000</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>67000</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>0.01069604086845466</v>
       </c>
       <c r="P31" t="n">
-        <v>1605</v>
+        <v>1815</v>
       </c>
       <c r="Q31" t="n">
-        <v>1605</v>
+        <v>1815</v>
       </c>
       <c r="R31" t="n">
-        <v>9204085</v>
+        <v>7762173</v>
       </c>
       <c r="S31" t="n">
-        <v>1659</v>
+        <v>1944</v>
       </c>
       <c r="T31" t="n">
-        <v>1840.75</v>
+        <v>1957</v>
       </c>
       <c r="U31" t="n">
-        <v>1844.75</v>
+        <v>1959</v>
       </c>
       <c r="V31" t="n">
-        <v>1769.5</v>
+        <v>2049.023126220703</v>
       </c>
       <c r="W31" t="n">
-        <v>-61.08703293356007</v>
+        <v>-12.33909153930517</v>
       </c>
       <c r="X31" t="n">
-        <v>-14.1110280811874</v>
+        <v>8.455870150861198</v>
       </c>
       <c r="Y31" t="n">
-        <v>-46.97600485237267</v>
+        <v>-20.79496169016637</v>
       </c>
       <c r="Z31" t="n">
-        <v>-48.41604395777102</v>
+        <v>-4.713179632014981</v>
       </c>
       <c r="AA31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>-0.04747774480712164</v>
+        <v>-0.02156334231805934</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0.1462765957446809</v>
+        <v>-0.1759609156048944</v>
       </c>
       <c r="AD31" t="n">
-        <v>-0.04758424514198156</v>
+        <v>-0.01535359642063294</v>
       </c>
       <c r="AE31" t="n">
-        <v>-0.1784303325214792</v>
+        <v>-0.2500175310700145</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.1308460873794977</v>
+        <v>0.2346639346493815</v>
       </c>
       <c r="AG31" t="n">
-        <v>29.41176470588236</v>
+        <v>47.05882352941176</v>
       </c>
       <c r="AH31" t="n">
-        <v>15.68627450980392</v>
+        <v>7.84313725490196</v>
       </c>
       <c r="AI31" t="b">
         <v>0</v>
@@ -4790,30 +4806,32 @@
         <v>0</v>
       </c>
       <c r="AM31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO31" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>2050.95</v>
+      </c>
       <c r="AP31" t="n">
-        <v>1983.16</v>
+        <v>1989.47</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>美律</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4822,7 +4840,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>29.41176470588236</v>
+        <v>31.76470588235294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4831,15 +4849,15 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1000</v>
+        <v>4328000</v>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="n">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="K32" t="b">
         <v>0</v>
@@ -4848,7 +4866,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1000</v>
+        <v>4328000</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -4857,73 +4875,73 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>79.59999847412109</v>
+        <v>4990</v>
       </c>
       <c r="Q32" t="n">
-        <v>79.59999847412109</v>
+        <v>4990</v>
       </c>
       <c r="R32" t="n">
-        <v>1055568</v>
+        <v>2719797</v>
       </c>
       <c r="S32" t="n">
-        <v>80.59999999999999</v>
+        <v>5069</v>
       </c>
       <c r="T32" t="n">
-        <v>78.69499931335449</v>
+        <v>5302.25</v>
       </c>
       <c r="U32" t="n">
-        <v>78.67999954223633</v>
+        <v>5297.25</v>
       </c>
       <c r="V32" t="n">
-        <v>77.81705805460612</v>
+        <v>5325.460229492188</v>
       </c>
       <c r="W32" t="n">
-        <v>0.701974108434186</v>
+        <v>-85.66607422324341</v>
       </c>
       <c r="X32" t="n">
-        <v>0.6569963440146152</v>
+        <v>15.62243463598849</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.0449777644195708</v>
+        <v>-101.2885088592319</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.2036156298125609</v>
+        <v>-100.9099230975565</v>
       </c>
       <c r="AA32" t="b">
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.003783044272614777</v>
+        <v>0.0204498977505112</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.00199971015631295</v>
+        <v>0.05421357080041989</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.00367654393775485</v>
+        <v>0.0266596436479376</v>
       </c>
       <c r="AE32" t="n">
-        <v>-0.03015402662048539</v>
+        <v>-0.01984304466470022</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.03383057055824024</v>
+        <v>0.04650268831263782</v>
       </c>
       <c r="AG32" t="n">
-        <v>54.90196078431373</v>
+        <v>62.74509803921568</v>
       </c>
       <c r="AH32" t="n">
-        <v>39.21568627450981</v>
+        <v>41.17647058823529</v>
       </c>
       <c r="AI32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="b">
         <v>1</v>
       </c>
       <c r="AK32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM32" t="b">
         <v>0</v>
@@ -4931,11 +4949,7 @@
       <c r="AN32" t="b">
         <v>0</v>
       </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
+      <c r="AO32" t="inlineStr"/>
       <c r="AP32" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -4945,17 +4959,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4964,7 +4978,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>28.62745098039216</v>
+        <v>30.19607843137255</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4973,15 +4987,15 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>2185000</v>
+        <v>1000</v>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="K33" t="b">
         <v>0</v>
@@ -4990,7 +5004,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>2185000</v>
+        <v>1000</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
@@ -4999,61 +5013,61 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>219</v>
+        <v>6170</v>
       </c>
       <c r="Q33" t="n">
-        <v>219</v>
+        <v>6170</v>
       </c>
       <c r="R33" t="n">
-        <v>1433670</v>
+        <v>2653180</v>
       </c>
       <c r="S33" t="n">
-        <v>228.9</v>
+        <v>6279</v>
       </c>
       <c r="T33" t="n">
-        <v>232.975</v>
+        <v>6483.25</v>
       </c>
       <c r="U33" t="n">
-        <v>233.275</v>
+        <v>6496.25</v>
       </c>
       <c r="V33" t="n">
-        <v>211.7416666666667</v>
+        <v>5890.061966959635</v>
       </c>
       <c r="W33" t="n">
-        <v>-1.134194617663923</v>
+        <v>-74.43034905392324</v>
       </c>
       <c r="X33" t="n">
-        <v>2.385505469793294</v>
+        <v>42.30251137507694</v>
       </c>
       <c r="Y33" t="n">
-        <v>-3.519700087457216</v>
+        <v>-116.7328604290002</v>
       </c>
       <c r="Z33" t="n">
-        <v>-2.732832911642263</v>
+        <v>-117.9947284158227</v>
       </c>
       <c r="AA33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB33" t="n">
-        <v>-0.02666666666666662</v>
+        <v>-0.04043545878693622</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.09499999999999997</v>
+        <v>0.5883562242198632</v>
       </c>
       <c r="AD33" t="n">
-        <v>-0.02677316700152654</v>
+        <v>-0.03422571288950982</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.06284626322320164</v>
+        <v>0.5142996087547431</v>
       </c>
       <c r="AF33" t="n">
-        <v>-0.08961943022472818</v>
+        <v>-0.5485253216442529</v>
       </c>
       <c r="AG33" t="n">
-        <v>43.13725490196079</v>
+        <v>41.17647058823529</v>
       </c>
       <c r="AH33" t="n">
-        <v>66.66666666666666</v>
+        <v>90.19607843137256</v>
       </c>
       <c r="AI33" t="b">
         <v>0</v>
@@ -5068,32 +5082,30 @@
         <v>0</v>
       </c>
       <c r="AM33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN33" t="b">
         <v>0</v>
       </c>
-      <c r="AO33" t="n">
-        <v>258.86</v>
-      </c>
+      <c r="AO33" t="inlineStr"/>
       <c r="AP33" t="n">
-        <v>244.21</v>
+        <v>6729.74</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5102,7 +5114,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>27.64705882352941</v>
+        <v>30.19607843137255</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5111,24 +5123,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>470000</v>
+        <v>7582000</v>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="K34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" t="b">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>470000</v>
+        <v>7582000</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -5137,61 +5149,61 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>3095</v>
+        <v>1625</v>
       </c>
       <c r="Q34" t="n">
-        <v>3095</v>
+        <v>1625</v>
       </c>
       <c r="R34" t="n">
-        <v>1030333</v>
+        <v>11289452</v>
       </c>
       <c r="S34" t="n">
-        <v>3104</v>
+        <v>1627</v>
       </c>
       <c r="T34" t="n">
-        <v>3224</v>
+        <v>1835.25</v>
       </c>
       <c r="U34" t="n">
-        <v>3229.25</v>
+        <v>1840.75</v>
       </c>
       <c r="V34" t="n">
-        <v>3024.333333333333</v>
+        <v>1766.833333333333</v>
       </c>
       <c r="W34" t="n">
-        <v>-32.89673728350044</v>
+        <v>-64.48021579978013</v>
       </c>
       <c r="X34" t="n">
-        <v>-23.25232969097646</v>
+        <v>-24.18486562490595</v>
       </c>
       <c r="Y34" t="n">
-        <v>-9.644407592523979</v>
+        <v>-40.29535017487417</v>
       </c>
       <c r="Z34" t="n">
-        <v>-8.5735784624049</v>
+        <v>-46.97600485237267</v>
       </c>
       <c r="AA34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB34" t="n">
-        <v>-0.03281250000000002</v>
+        <v>-0.06340057636887608</v>
       </c>
       <c r="AC34" t="n">
-        <v>0.1213768115942029</v>
+        <v>-0.08963585434173671</v>
       </c>
       <c r="AD34" t="n">
-        <v>-0.03291900033485995</v>
+        <v>-0.05719083047144968</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.08922307481740455</v>
+        <v>-0.1636924698068568</v>
       </c>
       <c r="AF34" t="n">
-        <v>-0.1221420751522645</v>
+        <v>0.1065016393354071</v>
       </c>
       <c r="AG34" t="n">
-        <v>39.21568627450981</v>
+        <v>31.37254901960784</v>
       </c>
       <c r="AH34" t="n">
-        <v>68.62745098039215</v>
+        <v>19.6078431372549</v>
       </c>
       <c r="AI34" t="b">
         <v>0</v>
@@ -5206,32 +5218,30 @@
         <v>0</v>
       </c>
       <c r="AM34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN34" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>3206.42</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO34" t="inlineStr"/>
       <c r="AP34" t="n">
-        <v>3655.79</v>
+        <v>2096.32</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5240,7 +5250,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>22.94117647058824</v>
+        <v>30</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5249,24 +5259,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>79618000</v>
+        <v>654000</v>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="K35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" t="b">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>79618000</v>
+        <v>654000</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -5275,61 +5285,61 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>127</v>
+        <v>482</v>
       </c>
       <c r="Q35" t="n">
-        <v>127</v>
+        <v>482</v>
       </c>
       <c r="R35" t="n">
-        <v>98805968</v>
+        <v>15872872</v>
       </c>
       <c r="S35" t="n">
-        <v>133.4</v>
+        <v>473.8</v>
       </c>
       <c r="T35" t="n">
-        <v>148.4</v>
+        <v>504.95</v>
       </c>
       <c r="U35" t="n">
-        <v>149.425</v>
+        <v>505.825</v>
       </c>
       <c r="V35" t="n">
-        <v>133.425</v>
+        <v>457.4083333333334</v>
       </c>
       <c r="W35" t="n">
-        <v>-4.885390315535176</v>
+        <v>-8.953818803262834</v>
       </c>
       <c r="X35" t="n">
-        <v>-1.417028705688755</v>
+        <v>-2.185343976269416</v>
       </c>
       <c r="Y35" t="n">
-        <v>-3.468361609846421</v>
+        <v>-6.768474826993417</v>
       </c>
       <c r="Z35" t="n">
-        <v>-3.4152363658433</v>
+        <v>-8.710291460057888</v>
       </c>
       <c r="AA35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB35" t="n">
-        <v>-0.1389830508474577</v>
+        <v>-0.03503503503503502</v>
       </c>
       <c r="AC35" t="n">
-        <v>-0.0830324909747292</v>
+        <v>0.3133514986376023</v>
       </c>
       <c r="AD35" t="n">
-        <v>-0.1390895511823176</v>
+        <v>-0.02882528913760862</v>
       </c>
       <c r="AE35" t="n">
-        <v>-0.1151862277515275</v>
+        <v>0.2392948831724822</v>
       </c>
       <c r="AF35" t="n">
-        <v>-0.02390332343079005</v>
+        <v>-0.2681201723100908</v>
       </c>
       <c r="AG35" t="n">
-        <v>5.88235294117647</v>
+        <v>43.13725490196079</v>
       </c>
       <c r="AH35" t="n">
-        <v>21.56862745098039</v>
+        <v>82.35294117647058</v>
       </c>
       <c r="AI35" t="b">
         <v>0</v>
@@ -5344,20 +5354,22 @@
         <v>0</v>
       </c>
       <c r="AM35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO35" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>558.16</v>
+      </c>
       <c r="AP35" t="n">
-        <v>178.53</v>
+        <v>515.66</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5376,7 +5388,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>22.94117647058824</v>
+        <v>26.66666666666667</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5385,7 +5397,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -5411,61 +5423,61 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>160</v>
+        <v>166.5</v>
       </c>
       <c r="Q36" t="n">
-        <v>160</v>
+        <v>166.5</v>
       </c>
       <c r="R36" t="n">
-        <v>9653817</v>
+        <v>8984913</v>
       </c>
       <c r="S36" t="n">
-        <v>165.7</v>
+        <v>163.8</v>
       </c>
       <c r="T36" t="n">
+        <v>176.1</v>
+      </c>
+      <c r="U36" t="n">
         <v>176.375</v>
       </c>
-      <c r="U36" t="n">
-        <v>176.65</v>
-      </c>
       <c r="V36" t="n">
-        <v>161.1666666666667</v>
+        <v>161.325</v>
       </c>
       <c r="W36" t="n">
-        <v>-2.620405410260162</v>
+        <v>-2.633665398248837</v>
       </c>
       <c r="X36" t="n">
-        <v>1.485588153274897</v>
+        <v>0.66173744297015</v>
       </c>
       <c r="Y36" t="n">
+        <v>-3.295402841218987</v>
+      </c>
+      <c r="Z36" t="n">
         <v>-4.105993563535058</v>
       </c>
-      <c r="Z36" t="n">
-        <v>-3.97508356428308</v>
-      </c>
       <c r="AA36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB36" t="n">
-        <v>-0.03323262839879149</v>
+        <v>-0.03197674418604646</v>
       </c>
       <c r="AC36" t="n">
-        <v>-0.05044510385756673</v>
+        <v>0.06050955414012749</v>
       </c>
       <c r="AD36" t="n">
-        <v>-0.03333912873365141</v>
+        <v>-0.02576699828862006</v>
       </c>
       <c r="AE36" t="n">
-        <v>-0.08259884063436507</v>
+        <v>-0.01354706132499262</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.04925971190071365</v>
+        <v>-0.01221993696362744</v>
       </c>
       <c r="AG36" t="n">
-        <v>37.25490196078432</v>
+        <v>45.09803921568628</v>
       </c>
       <c r="AH36" t="n">
-        <v>27.45098039215686</v>
+        <v>43.13725490196079</v>
       </c>
       <c r="AI36" t="b">
         <v>0</v>
@@ -5480,20 +5492,20 @@
         <v>0</v>
       </c>
       <c r="AM36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN36" t="b">
         <v>0</v>
       </c>
       <c r="AO36" t="inlineStr"/>
       <c r="AP36" t="n">
-        <v>189.24</v>
+        <v>182.11</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5512,7 +5524,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>22.54901960784314</v>
+        <v>25.49019607843137</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5521,7 +5533,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -5547,61 +5559,61 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>153.5</v>
+        <v>159</v>
       </c>
       <c r="Q37" t="n">
-        <v>153.5</v>
+        <v>159</v>
       </c>
       <c r="R37" t="n">
-        <v>7897014</v>
+        <v>7682625</v>
       </c>
       <c r="S37" t="n">
-        <v>158.2</v>
+        <v>156.8</v>
       </c>
       <c r="T37" t="n">
+        <v>168.825</v>
+      </c>
+      <c r="U37" t="n">
         <v>169.3</v>
       </c>
-      <c r="U37" t="n">
-        <v>169.775</v>
-      </c>
       <c r="V37" t="n">
-        <v>151.3583333333333</v>
+        <v>151.675</v>
       </c>
       <c r="W37" t="n">
-        <v>-3.107671154594044</v>
+        <v>-3.002049219198454</v>
       </c>
       <c r="X37" t="n">
-        <v>0.2161910987202716</v>
+        <v>-0.4274569648634736</v>
       </c>
       <c r="Y37" t="n">
+        <v>-2.574592254334981</v>
+      </c>
+      <c r="Z37" t="n">
         <v>-3.323862253314316</v>
       </c>
-      <c r="Z37" t="n">
-        <v>-3.312685574818888</v>
-      </c>
       <c r="AA37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB37" t="n">
-        <v>-0.05828220858895705</v>
+        <v>-0.05637982195845692</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.06228373702422152</v>
+        <v>0.1357142857142857</v>
       </c>
       <c r="AD37" t="n">
-        <v>-0.05838870892381698</v>
+        <v>-0.05017007606103052</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.03013000024742318</v>
+        <v>0.06165767024916557</v>
       </c>
       <c r="AF37" t="n">
-        <v>-0.08851870917124016</v>
+        <v>-0.1118277463101961</v>
       </c>
       <c r="AG37" t="n">
-        <v>25.49019607843137</v>
+        <v>35.29411764705883</v>
       </c>
       <c r="AH37" t="n">
-        <v>58.82352941176471</v>
+        <v>60.78431372549019</v>
       </c>
       <c r="AI37" t="b">
         <v>0</v>
@@ -5616,30 +5628,32 @@
         <v>0</v>
       </c>
       <c r="AM37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN37" t="b">
         <v>0</v>
       </c>
-      <c r="AO37" t="inlineStr"/>
+      <c r="AO37" t="n">
+        <v>188.26</v>
+      </c>
       <c r="AP37" t="n">
-        <v>185.13</v>
+        <v>178.34</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5648,7 +5662,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>22.15686274509804</v>
+        <v>23.52941176470588</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5657,7 +5671,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -5665,7 +5679,7 @@
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K38" t="b">
         <v>0</v>
@@ -5683,61 +5697,61 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>241.5</v>
+        <v>328.5</v>
       </c>
       <c r="Q38" t="n">
-        <v>241.5</v>
+        <v>328.5</v>
       </c>
       <c r="R38" t="n">
-        <v>26839387</v>
+        <v>10332339</v>
       </c>
       <c r="S38" t="n">
-        <v>241.5</v>
+        <v>320.4</v>
       </c>
       <c r="T38" t="n">
-        <v>248.5</v>
+        <v>329.875</v>
       </c>
       <c r="U38" t="n">
-        <v>248.95</v>
+        <v>330.6</v>
       </c>
       <c r="V38" t="n">
-        <v>250.45</v>
+        <v>326.5583333333333</v>
       </c>
       <c r="W38" t="n">
-        <v>-2.784638775372684</v>
+        <v>-3.274222476158116</v>
       </c>
       <c r="X38" t="n">
-        <v>-1.842734980825168</v>
+        <v>-3.39291746933012</v>
       </c>
       <c r="Y38" t="n">
-        <v>-0.9419037945475166</v>
+        <v>0.1186949931720043</v>
       </c>
       <c r="Z38" t="n">
-        <v>-1.242780797379176</v>
+        <v>-1.101275452612911</v>
       </c>
       <c r="AA38" t="b">
         <v>1</v>
       </c>
       <c r="AB38" t="n">
-        <v>-0.0359281437125748</v>
+        <v>-0.04227405247813409</v>
       </c>
       <c r="AC38" t="n">
-        <v>-0.06213592233009713</v>
+        <v>0.001524390243902385</v>
       </c>
       <c r="AD38" t="n">
-        <v>-0.03603464404743473</v>
+        <v>-0.03606430658070769</v>
       </c>
       <c r="AE38" t="n">
-        <v>-0.09428965910689546</v>
+        <v>-0.07253222522121772</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.05825501505946074</v>
+        <v>0.03646791864051002</v>
       </c>
       <c r="AG38" t="n">
-        <v>35.29411764705883</v>
+        <v>39.21568627450981</v>
       </c>
       <c r="AH38" t="n">
-        <v>25.49019607843137</v>
+        <v>29.41176470588236</v>
       </c>
       <c r="AI38" t="b">
         <v>0</v>
@@ -5746,38 +5760,40 @@
         <v>0</v>
       </c>
       <c r="AK38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM38" t="b">
         <v>1</v>
       </c>
       <c r="AN38" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>252.13</v>
+        <v>0</v>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP38" t="n">
-        <v>257.87</v>
+        <v>345.95</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5786,7 +5802,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>21.37254901960785</v>
+        <v>23.33333333333334</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5795,24 +5811,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1000</v>
+        <v>79618000</v>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="K39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" t="b">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>1000</v>
+        <v>79618000</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -5821,61 +5837,61 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2000</v>
+        <v>128</v>
       </c>
       <c r="Q39" t="n">
-        <v>2000</v>
+        <v>128</v>
       </c>
       <c r="R39" t="n">
-        <v>1794629</v>
+        <v>73759992</v>
       </c>
       <c r="S39" t="n">
-        <v>2056</v>
+        <v>130.6</v>
       </c>
       <c r="T39" t="n">
-        <v>2228.25</v>
+        <v>147</v>
       </c>
       <c r="U39" t="n">
-        <v>2232.5</v>
+        <v>148.4</v>
       </c>
       <c r="V39" t="n">
-        <v>2130.416666666667</v>
+        <v>133.425</v>
       </c>
       <c r="W39" t="n">
-        <v>-57.02788078423646</v>
+        <v>-5.28985075468276</v>
       </c>
       <c r="X39" t="n">
-        <v>-10.90489862325036</v>
+        <v>-2.191593115487556</v>
       </c>
       <c r="Y39" t="n">
-        <v>-46.1229821609861</v>
+        <v>-3.098257639195204</v>
       </c>
       <c r="Z39" t="n">
-        <v>-47.87567750420025</v>
+        <v>-3.468361609846421</v>
       </c>
       <c r="AA39" t="b">
         <v>1</v>
       </c>
       <c r="AB39" t="n">
-        <v>-0.04076738609112707</v>
+        <v>-0.1794871794871795</v>
       </c>
       <c r="AC39" t="n">
-        <v>-0.07192575406032486</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>-0.04087388642598699</v>
+        <v>-0.1732774335897531</v>
       </c>
       <c r="AE39" t="n">
-        <v>-0.1040794908371232</v>
+        <v>-0.0740566154651201</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.06320560441113621</v>
+        <v>-0.09922081812463301</v>
       </c>
       <c r="AG39" t="n">
-        <v>33.33333333333333</v>
+        <v>5.88235294117647</v>
       </c>
       <c r="AH39" t="n">
-        <v>23.52941176470588</v>
+        <v>27.45098039215686</v>
       </c>
       <c r="AI39" t="b">
         <v>0</v>
@@ -5897,13 +5913,13 @@
       </c>
       <c r="AO39" t="inlineStr"/>
       <c r="AP39" t="n">
-        <v>2530.26</v>
+        <v>177</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5922,7 +5938,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>20.98039215686275</v>
+        <v>19.41176470588236</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5931,7 +5947,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -5939,7 +5955,7 @@
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K40" t="b">
         <v>0</v>
@@ -5957,61 +5973,61 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>4150</v>
+        <v>4140</v>
       </c>
       <c r="Q40" t="n">
-        <v>4150</v>
+        <v>4140</v>
       </c>
       <c r="R40" t="n">
-        <v>6616927</v>
+        <v>9026097</v>
       </c>
       <c r="S40" t="n">
-        <v>4249</v>
+        <v>4182</v>
       </c>
       <c r="T40" t="n">
+        <v>4728.25</v>
+      </c>
+      <c r="U40" t="n">
         <v>4756.75</v>
       </c>
-      <c r="U40" t="n">
-        <v>4774.25</v>
-      </c>
       <c r="V40" t="n">
-        <v>4285</v>
+        <v>4291.5</v>
       </c>
       <c r="W40" t="n">
-        <v>-159.1577618060437</v>
+        <v>-167.6489535656037</v>
       </c>
       <c r="X40" t="n">
-        <v>-54.73832063428937</v>
+        <v>-77.32044722055224</v>
       </c>
       <c r="Y40" t="n">
+        <v>-90.32850634505149</v>
+      </c>
+      <c r="Z40" t="n">
         <v>-104.4194411717543</v>
       </c>
-      <c r="Z40" t="n">
-        <v>-114.1653361765419</v>
-      </c>
       <c r="AA40" t="b">
         <v>1</v>
       </c>
       <c r="AB40" t="n">
-        <v>-0.07777777777777772</v>
+        <v>-0.1210191082802548</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.07096774193548394</v>
+        <v>0.1040000000000001</v>
       </c>
       <c r="AD40" t="n">
-        <v>-0.07788427811263765</v>
+        <v>-0.1148093623828284</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.0388140051586856</v>
+        <v>0.02994338453487999</v>
       </c>
       <c r="AF40" t="n">
-        <v>-0.1166982832713233</v>
+        <v>-0.1447527469177083</v>
       </c>
       <c r="AG40" t="n">
-        <v>19.6078431372549</v>
+        <v>17.64705882352941</v>
       </c>
       <c r="AH40" t="n">
-        <v>60.78431372549019</v>
+        <v>52.94117647058824</v>
       </c>
       <c r="AI40" t="b">
         <v>0</v>
@@ -6033,23 +6049,23 @@
       </c>
       <c r="AO40" t="inlineStr"/>
       <c r="AP40" t="n">
-        <v>5348.68</v>
+        <v>5629.21</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6058,7 +6074,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>19.80392156862745</v>
+        <v>18.82352941176471</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -6067,15 +6083,15 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>3281561</v>
+        <v>1000</v>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="n">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="K41" t="b">
         <v>0</v>
@@ -6084,7 +6100,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3281561</v>
+        <v>1000</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -6093,61 +6109,61 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>1925</v>
+        <v>880</v>
       </c>
       <c r="Q41" t="n">
-        <v>1925</v>
+        <v>880</v>
       </c>
       <c r="R41" t="n">
-        <v>4847292</v>
+        <v>8859917</v>
       </c>
       <c r="S41" t="n">
-        <v>1935</v>
+        <v>886.2</v>
       </c>
       <c r="T41" t="n">
-        <v>2103.75</v>
+        <v>1018.3</v>
       </c>
       <c r="U41" t="n">
-        <v>2114.25</v>
+        <v>1021.5</v>
       </c>
       <c r="V41" t="n">
-        <v>2144.59619140625</v>
+        <v>965.7666666666667</v>
       </c>
       <c r="W41" t="n">
-        <v>-78.00820616284841</v>
+        <v>-43.16509068690038</v>
       </c>
       <c r="X41" t="n">
-        <v>-43.83312580277956</v>
+        <v>-6.995547830428174</v>
       </c>
       <c r="Y41" t="n">
-        <v>-34.17508036006885</v>
+        <v>-36.16954285647221</v>
       </c>
       <c r="Z41" t="n">
-        <v>-40.22534605316526</v>
+        <v>-41.41892002553749</v>
       </c>
       <c r="AA41" t="b">
         <v>1</v>
       </c>
       <c r="AB41" t="n">
-        <v>-0.09836065573770492</v>
+        <v>-0.06779661016949157</v>
       </c>
       <c r="AC41" t="n">
-        <v>0.04970376901138618</v>
+        <v>-0.1456310679611651</v>
       </c>
       <c r="AD41" t="n">
-        <v>-0.09846715607256484</v>
+        <v>-0.06158686427206517</v>
       </c>
       <c r="AE41" t="n">
-        <v>0.01755003223458784</v>
+        <v>-0.2196876834262852</v>
       </c>
       <c r="AF41" t="n">
-        <v>-0.1160171883071527</v>
+        <v>0.15810081915422</v>
       </c>
       <c r="AG41" t="n">
-        <v>17.64705882352941</v>
+        <v>29.41176470588236</v>
       </c>
       <c r="AH41" t="n">
-        <v>54.90196078431373</v>
+        <v>11.76470588235294</v>
       </c>
       <c r="AI41" t="b">
         <v>0</v>
@@ -6167,27 +6183,25 @@
       <c r="AN41" t="b">
         <v>0</v>
       </c>
-      <c r="AO41" t="n">
-        <v>2310</v>
-      </c>
+      <c r="AO41" t="inlineStr"/>
       <c r="AP41" t="n">
-        <v>2328.16</v>
+        <v>1076.58</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6196,7 +6210,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>19.80392156862745</v>
+        <v>18.43137254901961</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6205,15 +6219,15 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>2887848</v>
+        <v>1000</v>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="n">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="K42" t="b">
         <v>0</v>
@@ -6222,7 +6236,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>2887848</v>
+        <v>1000</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
@@ -6231,58 +6245,58 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>1925</v>
+        <v>527</v>
       </c>
       <c r="Q42" t="n">
-        <v>1925</v>
+        <v>527</v>
       </c>
       <c r="R42" t="n">
-        <v>1653523</v>
+        <v>213323</v>
       </c>
       <c r="S42" t="n">
-        <v>2033</v>
+        <v>531.2</v>
       </c>
       <c r="T42" t="n">
-        <v>2291.75</v>
+        <v>557.55</v>
       </c>
       <c r="U42" t="n">
-        <v>2296</v>
+        <v>559.6</v>
       </c>
       <c r="V42" t="n">
-        <v>2182.416666666667</v>
+        <v>563.167025756836</v>
       </c>
       <c r="W42" t="n">
-        <v>-83.28163187322662</v>
+        <v>-9.661311116363549</v>
       </c>
       <c r="X42" t="n">
-        <v>-12.84731637201121</v>
+        <v>-5.16907811614728</v>
       </c>
       <c r="Y42" t="n">
-        <v>-70.43431550121541</v>
+        <v>-4.492233000216269</v>
       </c>
       <c r="Z42" t="n">
-        <v>-70.08147242268308</v>
+        <v>-5.040022501139054</v>
       </c>
       <c r="AA42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB42" t="n">
-        <v>-0.04228855721393032</v>
+        <v>-0.07218309859154926</v>
       </c>
       <c r="AC42" t="n">
-        <v>-0.1575492341356673</v>
+        <v>-0.1241128140059693</v>
       </c>
       <c r="AD42" t="n">
-        <v>-0.04239505754879025</v>
+        <v>-0.06597335269412286</v>
       </c>
       <c r="AE42" t="n">
-        <v>-0.1897029709124657</v>
+        <v>-0.1981694294710894</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.1473079133636754</v>
+        <v>0.1321960767769665</v>
       </c>
       <c r="AG42" t="n">
-        <v>31.37254901960784</v>
+        <v>27.45098039215686</v>
       </c>
       <c r="AH42" t="n">
         <v>13.72549019607843</v>
@@ -6300,30 +6314,32 @@
         <v>0</v>
       </c>
       <c r="AM42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO42" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>577.59</v>
+      </c>
       <c r="AP42" t="n">
-        <v>2596.05</v>
+        <v>599.16</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6332,7 +6348,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>19.21568627450981</v>
+        <v>17.45098039215686</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6341,15 +6357,15 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1000</v>
+        <v>201900</v>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="K43" t="b">
         <v>0</v>
@@ -6358,7 +6374,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>1000</v>
+        <v>201900</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -6367,61 +6383,61 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>320.5</v>
+        <v>16515</v>
       </c>
       <c r="Q43" t="n">
-        <v>320.5</v>
+        <v>16515</v>
       </c>
       <c r="R43" t="n">
-        <v>8492298</v>
+        <v>276775</v>
       </c>
       <c r="S43" t="n">
-        <v>319.3</v>
+        <v>16164</v>
       </c>
       <c r="T43" t="n">
-        <v>330.6</v>
+        <v>18198.5</v>
       </c>
       <c r="U43" t="n">
-        <v>331.775</v>
+        <v>18337.25</v>
       </c>
       <c r="V43" t="n">
-        <v>326.55</v>
+        <v>17132.83333333333</v>
       </c>
       <c r="W43" t="n">
-        <v>-4.523866670236032</v>
+        <v>-647.3036676512056</v>
       </c>
       <c r="X43" t="n">
-        <v>-3.422591217623121</v>
+        <v>-413.3065101736765</v>
       </c>
       <c r="Y43" t="n">
-        <v>-1.101275452612911</v>
+        <v>-233.9971574775291</v>
       </c>
       <c r="Z43" t="n">
-        <v>-1.736834429691923</v>
+        <v>-342.2042943370795</v>
       </c>
       <c r="AA43" t="b">
         <v>1</v>
       </c>
       <c r="AB43" t="n">
-        <v>-0.0683139534883721</v>
+        <v>-0.1438569206842923</v>
       </c>
       <c r="AC43" t="n">
-        <v>-0.04613095238095233</v>
+        <v>0.1211812627291242</v>
       </c>
       <c r="AD43" t="n">
-        <v>-0.06842045382323203</v>
+        <v>-0.1376471747868659</v>
       </c>
       <c r="AE43" t="n">
-        <v>-0.07828468915775066</v>
+        <v>0.04712464726400412</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.009864235334518634</v>
+        <v>-0.1847718220508701</v>
       </c>
       <c r="AG43" t="n">
-        <v>23.52941176470588</v>
+        <v>9.803921568627452</v>
       </c>
       <c r="AH43" t="n">
-        <v>31.37254901960784</v>
+        <v>56.86274509803921</v>
       </c>
       <c r="AI43" t="b">
         <v>0</v>
@@ -6442,26 +6458,26 @@
         <v>1</v>
       </c>
       <c r="AO43" t="n">
-        <v>333.32</v>
+        <v>19157.4</v>
       </c>
       <c r="AP43" t="n">
-        <v>353.63</v>
+        <v>21592.11</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6470,7 +6486,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>19.21568627450981</v>
+        <v>16.86274509803922</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6479,7 +6495,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -6487,7 +6503,7 @@
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="K44" t="b">
         <v>0</v>
@@ -6505,61 +6521,61 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>524</v>
+        <v>1120</v>
       </c>
       <c r="Q44" t="n">
-        <v>524</v>
+        <v>1120</v>
       </c>
       <c r="R44" t="n">
-        <v>233848</v>
+        <v>1094055</v>
       </c>
       <c r="S44" t="n">
-        <v>538</v>
+        <v>1141</v>
       </c>
       <c r="T44" t="n">
-        <v>559.6</v>
+        <v>1189.75</v>
       </c>
       <c r="U44" t="n">
-        <v>561.2</v>
+        <v>1194.75</v>
       </c>
       <c r="V44" t="n">
-        <v>564.4116200764973</v>
+        <v>1335.5</v>
       </c>
       <c r="W44" t="n">
-        <v>-9.086042367232153</v>
+        <v>-31.25270855267127</v>
       </c>
       <c r="X44" t="n">
-        <v>-4.046019866092821</v>
+        <v>-29.06059051236749</v>
       </c>
       <c r="Y44" t="n">
-        <v>-5.040022501139332</v>
+        <v>-2.192118040303779</v>
       </c>
       <c r="Z44" t="n">
-        <v>-4.661298601172318</v>
+        <v>-1.413309072979864</v>
       </c>
       <c r="AA44" t="b">
         <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>-0.05755395683453235</v>
+        <v>-0.08196721311475408</v>
       </c>
       <c r="AC44" t="n">
-        <v>-0.1305219329818914</v>
+        <v>-0.2140350877192982</v>
       </c>
       <c r="AD44" t="n">
-        <v>-0.05766045716939228</v>
+        <v>-0.07575746721732768</v>
       </c>
       <c r="AE44" t="n">
-        <v>-0.1626756697586897</v>
+        <v>-0.2880917031844183</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.1050152125892975</v>
+        <v>0.2123342359670907</v>
       </c>
       <c r="AG44" t="n">
-        <v>27.45098039215686</v>
+        <v>25.49019607843137</v>
       </c>
       <c r="AH44" t="n">
-        <v>19.6078431372549</v>
+        <v>3.92156862745098</v>
       </c>
       <c r="AI44" t="b">
         <v>0</v>
@@ -6580,26 +6596,26 @@
         <v>1</v>
       </c>
       <c r="AO44" t="n">
-        <v>581.64</v>
+        <v>1146.88</v>
       </c>
       <c r="AP44" t="n">
-        <v>605.47</v>
+        <v>1313.42</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6608,7 +6624,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>17.64705882352941</v>
+        <v>16.47058823529412</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6617,15 +6633,15 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>957000</v>
+        <v>2887848</v>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K45" t="b">
         <v>0</v>
@@ -6634,7 +6650,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>957000</v>
+        <v>2887848</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
@@ -6643,61 +6659,61 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>470</v>
+        <v>1950</v>
       </c>
       <c r="Q45" t="n">
-        <v>470</v>
+        <v>1950</v>
       </c>
       <c r="R45" t="n">
-        <v>1483863</v>
+        <v>2688491</v>
       </c>
       <c r="S45" t="n">
-        <v>520</v>
+        <v>1976</v>
       </c>
       <c r="T45" t="n">
-        <v>564.6</v>
+        <v>2278.75</v>
       </c>
       <c r="U45" t="n">
-        <v>568.9</v>
+        <v>2291.75</v>
       </c>
       <c r="V45" t="n">
-        <v>542.2083333333334</v>
+        <v>2178.166666666667</v>
       </c>
       <c r="W45" t="n">
-        <v>-22.17551166770397</v>
+        <v>-90.86529070863844</v>
       </c>
       <c r="X45" t="n">
-        <v>-8.726087560203045</v>
+        <v>-28.45091123933666</v>
       </c>
       <c r="Y45" t="n">
-        <v>-13.44942410750093</v>
+        <v>-62.41437946930179</v>
       </c>
       <c r="Z45" t="n">
-        <v>-11.02675305589574</v>
+        <v>-70.43431550121541</v>
       </c>
       <c r="AA45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB45" t="n">
-        <v>-0.1546762589928058</v>
+        <v>-0.1176470588235294</v>
       </c>
       <c r="AC45" t="n">
-        <v>0.1533742331288344</v>
+        <v>-0.1156462585034014</v>
       </c>
       <c r="AD45" t="n">
-        <v>-0.1547827593276657</v>
+        <v>-0.111437312926103</v>
       </c>
       <c r="AE45" t="n">
-        <v>0.121220496352036</v>
+        <v>-0.1897028739685215</v>
       </c>
       <c r="AF45" t="n">
-        <v>-0.2760032556797017</v>
+        <v>0.07826556104241844</v>
       </c>
       <c r="AG45" t="n">
-        <v>3.92156862745098</v>
+        <v>19.6078431372549</v>
       </c>
       <c r="AH45" t="n">
-        <v>74.50980392156863</v>
+        <v>17.64705882352941</v>
       </c>
       <c r="AI45" t="b">
         <v>0</v>
@@ -6712,30 +6728,30 @@
         <v>0</v>
       </c>
       <c r="AM45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN45" t="b">
         <v>0</v>
       </c>
       <c r="AO45" t="inlineStr"/>
       <c r="AP45" t="n">
-        <v>710.58</v>
+        <v>2646.05</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6744,7 +6760,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>16.86274509803922</v>
+        <v>16.27450980392157</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6753,15 +6769,15 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>201900</v>
+        <v>957000</v>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="K46" t="b">
         <v>0</v>
@@ -6770,7 +6786,7 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>201900</v>
+        <v>957000</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
@@ -6779,61 +6795,61 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>15900</v>
+        <v>488</v>
       </c>
       <c r="Q46" t="n">
-        <v>15900</v>
+        <v>488</v>
       </c>
       <c r="R46" t="n">
-        <v>168347</v>
+        <v>1025366</v>
       </c>
       <c r="S46" t="n">
-        <v>16361</v>
+        <v>500</v>
       </c>
       <c r="T46" t="n">
-        <v>18337.25</v>
+        <v>558.45</v>
       </c>
       <c r="U46" t="n">
-        <v>18456</v>
+        <v>564.6</v>
       </c>
       <c r="V46" t="n">
-        <v>17103.08333333333</v>
+        <v>543.2333333333333</v>
       </c>
       <c r="W46" t="n">
-        <v>-697.0115151413738</v>
+        <v>-23.62749306350031</v>
       </c>
       <c r="X46" t="n">
-        <v>-354.8072208042943</v>
+        <v>-11.7063686608625</v>
       </c>
       <c r="Y46" t="n">
-        <v>-342.2042943370795</v>
+        <v>-11.92112440263781</v>
       </c>
       <c r="Z46" t="n">
-        <v>-375.921664643153</v>
+        <v>-13.44942410750093</v>
       </c>
       <c r="AA46" t="b">
         <v>1</v>
       </c>
       <c r="AB46" t="n">
-        <v>-0.1299589603283173</v>
+        <v>-0.2013093289689034</v>
       </c>
       <c r="AC46" t="n">
-        <v>0.02316602316602312</v>
+        <v>0.1441969519343493</v>
       </c>
       <c r="AD46" t="n">
-        <v>-0.1300654606631773</v>
+        <v>-0.195099583071477</v>
       </c>
       <c r="AE46" t="n">
-        <v>-0.008987713610775216</v>
+        <v>0.07014033646922924</v>
       </c>
       <c r="AF46" t="n">
-        <v>-0.121077747052402</v>
+        <v>-0.2652399195407062</v>
       </c>
       <c r="AG46" t="n">
-        <v>9.803921568627452</v>
+        <v>3.92156862745098</v>
       </c>
       <c r="AH46" t="n">
-        <v>49.01960784313725</v>
+        <v>62.74509803921568</v>
       </c>
       <c r="AI46" t="b">
         <v>0</v>
@@ -6855,23 +6871,23 @@
       </c>
       <c r="AO46" t="inlineStr"/>
       <c r="AP46" t="n">
-        <v>21855.53</v>
+        <v>692.16</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6880,7 +6896,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>16.27450980392157</v>
+        <v>15.88235294117647</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6889,15 +6905,15 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>1000</v>
+        <v>3281561</v>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="n">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="K47" t="b">
         <v>0</v>
@@ -6906,7 +6922,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>1000</v>
+        <v>3281561</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
@@ -6915,61 +6931,61 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>844</v>
+        <v>1880</v>
       </c>
       <c r="Q47" t="n">
-        <v>844</v>
+        <v>1880</v>
       </c>
       <c r="R47" t="n">
-        <v>11741197</v>
+        <v>6022146</v>
       </c>
       <c r="S47" t="n">
-        <v>914.2</v>
+        <v>1888</v>
       </c>
       <c r="T47" t="n">
-        <v>1021.5</v>
+        <v>2090.75</v>
       </c>
       <c r="U47" t="n">
-        <v>1024.9</v>
+        <v>2103.75</v>
       </c>
       <c r="V47" t="n">
-        <v>968.2666666666667</v>
+        <v>2143.912569173177</v>
       </c>
       <c r="W47" t="n">
-        <v>-39.37208214184761</v>
+        <v>-82.80598189003217</v>
       </c>
       <c r="X47" t="n">
-        <v>2.046837883689879</v>
+        <v>-51.62769702023009</v>
       </c>
       <c r="Y47" t="n">
-        <v>-41.41892002553749</v>
+        <v>-31.17828486980208</v>
       </c>
       <c r="Z47" t="n">
-        <v>-39.09547402419012</v>
+        <v>-34.17508036006885</v>
       </c>
       <c r="AA47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB47" t="n">
-        <v>-0.07456140350877194</v>
+        <v>-0.1214953271028038</v>
       </c>
       <c r="AC47" t="n">
-        <v>-0.2464285714285714</v>
+        <v>-0.02135188124476795</v>
       </c>
       <c r="AD47" t="n">
-        <v>-0.07466790384363187</v>
+        <v>-0.1152855812053774</v>
       </c>
       <c r="AE47" t="n">
-        <v>-0.2785823082053698</v>
+        <v>-0.09540849670988805</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.2039144043617379</v>
+        <v>-0.01987708449548931</v>
       </c>
       <c r="AG47" t="n">
-        <v>21.56862745098039</v>
+        <v>15.68627450980392</v>
       </c>
       <c r="AH47" t="n">
-        <v>7.84313725490196</v>
+        <v>23.52941176470588</v>
       </c>
       <c r="AI47" t="b">
         <v>0</v>
@@ -6984,20 +7000,22 @@
         <v>0</v>
       </c>
       <c r="AM47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN47" t="b">
         <v>0</v>
       </c>
-      <c r="AO47" t="inlineStr"/>
+      <c r="AO47" t="n">
+        <v>2233.44</v>
+      </c>
       <c r="AP47" t="n">
-        <v>1130.84</v>
+        <v>2371.84</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -7016,7 +7034,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>15.09803921568628</v>
+        <v>15.88235294117647</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -7025,7 +7043,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="H48" t="n">
@@ -7051,61 +7069,61 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>422</v>
+        <v>436.5</v>
       </c>
       <c r="Q48" t="n">
-        <v>422</v>
+        <v>436.5</v>
       </c>
       <c r="R48" t="n">
-        <v>38690697</v>
+        <v>31780106</v>
       </c>
       <c r="S48" t="n">
-        <v>445.1</v>
+        <v>436.3</v>
       </c>
       <c r="T48" t="n">
+        <v>493.95</v>
+      </c>
+      <c r="U48" t="n">
         <v>498.375</v>
       </c>
-      <c r="U48" t="n">
-        <v>501.675</v>
-      </c>
       <c r="V48" t="n">
-        <v>485.9416666666667</v>
+        <v>486.5333333333334</v>
       </c>
       <c r="W48" t="n">
-        <v>-20.84900221807942</v>
+        <v>-21.23686695559746</v>
       </c>
       <c r="X48" t="n">
-        <v>-8.528245771880288</v>
+        <v>-11.06997000862372</v>
       </c>
       <c r="Y48" t="n">
+        <v>-10.16689694697374</v>
+      </c>
+      <c r="Z48" t="n">
         <v>-12.32075644619913</v>
       </c>
-      <c r="Z48" t="n">
-        <v>-11.76496255462172</v>
-      </c>
       <c r="AA48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB48" t="n">
-        <v>-0.1352459016393442</v>
+        <v>-0.1685714285714286</v>
       </c>
       <c r="AC48" t="n">
-        <v>-0.009389671361502372</v>
+        <v>0.08852867830423938</v>
       </c>
       <c r="AD48" t="n">
-        <v>-0.1353524019742042</v>
+        <v>-0.1623616826740022</v>
       </c>
       <c r="AE48" t="n">
-        <v>-0.04154340813830071</v>
+        <v>0.01447206283911928</v>
       </c>
       <c r="AF48" t="n">
-        <v>-0.09380899383590346</v>
+        <v>-0.1768337455131215</v>
       </c>
       <c r="AG48" t="n">
         <v>7.84313725490196</v>
       </c>
       <c r="AH48" t="n">
-        <v>37.25490196078432</v>
+        <v>47.05882352941176</v>
       </c>
       <c r="AI48" t="b">
         <v>0</v>
@@ -7120,30 +7138,30 @@
         <v>0</v>
       </c>
       <c r="AM48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN48" t="b">
         <v>0</v>
       </c>
       <c r="AO48" t="inlineStr"/>
       <c r="AP48" t="n">
-        <v>605.39</v>
+        <v>576.47</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -7152,7 +7170,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>14.31372549019608</v>
+        <v>15.49019607843137</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -7161,15 +7179,15 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1000</v>
+        <v>478000</v>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="K49" t="b">
         <v>0</v>
@@ -7178,7 +7196,7 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>1000</v>
+        <v>478000</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
@@ -7187,61 +7205,61 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>1110</v>
+        <v>802</v>
       </c>
       <c r="Q49" t="n">
-        <v>1110</v>
+        <v>802</v>
       </c>
       <c r="R49" t="n">
-        <v>1530982</v>
+        <v>1133338</v>
       </c>
       <c r="S49" t="n">
-        <v>1154</v>
+        <v>816.6</v>
       </c>
       <c r="T49" t="n">
-        <v>1194.75</v>
+        <v>857.1</v>
       </c>
       <c r="U49" t="n">
-        <v>1201.5</v>
+        <v>862.1</v>
       </c>
       <c r="V49" t="n">
-        <v>1340.583333333333</v>
+        <v>946</v>
       </c>
       <c r="W49" t="n">
-        <v>-29.9258700752714</v>
+        <v>-22.19223469214558</v>
       </c>
       <c r="X49" t="n">
-        <v>-28.51256100229154</v>
+        <v>-18.31789561042739</v>
       </c>
       <c r="Y49" t="n">
-        <v>-1.413309072979864</v>
+        <v>-3.874339081718187</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.82846467341701</v>
+        <v>-3.754054719819052</v>
       </c>
       <c r="AA49" t="b">
         <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>-0.1084337349397591</v>
+        <v>-0.1108647450110865</v>
       </c>
       <c r="AC49" t="n">
-        <v>-0.2099644128113879</v>
+        <v>-0.2675799086757991</v>
       </c>
       <c r="AD49" t="n">
-        <v>-0.108540235274619</v>
+        <v>-0.1046549991136601</v>
       </c>
       <c r="AE49" t="n">
-        <v>-0.2421181495881862</v>
+        <v>-0.3416365241409192</v>
       </c>
       <c r="AF49" t="n">
-        <v>0.1335779143135672</v>
+        <v>0.2369815250272591</v>
       </c>
       <c r="AG49" t="n">
-        <v>13.72549019607843</v>
+        <v>21.56862745098039</v>
       </c>
       <c r="AH49" t="n">
-        <v>11.76470588235294</v>
+        <v>1.96078431372549</v>
       </c>
       <c r="AI49" t="b">
         <v>0</v>
@@ -7262,26 +7280,26 @@
         <v>1</v>
       </c>
       <c r="AO49" t="n">
-        <v>1127.76</v>
+        <v>846.91</v>
       </c>
       <c r="AP49" t="n">
-        <v>1309.21</v>
+        <v>958</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7290,7 +7308,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>13.92156862745098</v>
+        <v>15.09803921568628</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7299,15 +7317,15 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>478000</v>
+        <v>1000</v>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="K50" t="b">
         <v>0</v>
@@ -7316,7 +7334,7 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>478000</v>
+        <v>1000</v>
       </c>
       <c r="N50" t="n">
         <v>0</v>
@@ -7325,61 +7343,61 @@
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>801</v>
+        <v>2010</v>
       </c>
       <c r="Q50" t="n">
-        <v>801</v>
+        <v>2010</v>
       </c>
       <c r="R50" t="n">
-        <v>583410</v>
+        <v>2645879</v>
       </c>
       <c r="S50" t="n">
-        <v>826.8</v>
+        <v>2008</v>
       </c>
       <c r="T50" t="n">
-        <v>862.1</v>
+        <v>2214.25</v>
       </c>
       <c r="U50" t="n">
-        <v>866.6</v>
+        <v>2228.25</v>
       </c>
       <c r="V50" t="n">
-        <v>950.8833333333333</v>
+        <v>2129.25</v>
       </c>
       <c r="W50" t="n">
-        <v>-21.10336555981689</v>
+        <v>-61.26880732084555</v>
       </c>
       <c r="X50" t="n">
-        <v>-17.34931083999784</v>
+        <v>-20.9776803627694</v>
       </c>
       <c r="Y50" t="n">
-        <v>-3.754054719819052</v>
+        <v>-40.29112695807616</v>
       </c>
       <c r="Z50" t="n">
-        <v>-2.203191063376405</v>
+        <v>-46.1229821609861</v>
       </c>
       <c r="AA50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB50" t="n">
-        <v>-0.101010101010101</v>
+        <v>-0.1222707423580786</v>
       </c>
       <c r="AC50" t="n">
-        <v>-0.3211864406779661</v>
+        <v>-0.03365384615384615</v>
       </c>
       <c r="AD50" t="n">
-        <v>-0.1011166013449609</v>
+        <v>-0.1160609964606522</v>
       </c>
       <c r="AE50" t="n">
-        <v>-0.3533401774547644</v>
+        <v>-0.1077104616189662</v>
       </c>
       <c r="AF50" t="n">
-        <v>0.2522235761098035</v>
+        <v>-0.008350534841685908</v>
       </c>
       <c r="AG50" t="n">
-        <v>15.68627450980392</v>
+        <v>13.72549019607843</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.96078431372549</v>
+        <v>21.56862745098039</v>
       </c>
       <c r="AI50" t="b">
         <v>0</v>
@@ -7394,22 +7412,20 @@
         <v>0</v>
       </c>
       <c r="AM50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN50" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO50" t="n">
-        <v>844.25</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO50" t="inlineStr"/>
       <c r="AP50" t="n">
-        <v>966.3200000000001</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -7428,7 +7444,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>13.52941176470588</v>
+        <v>13.92156862745098</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7437,7 +7453,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -7463,61 +7479,61 @@
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>4900</v>
+        <v>5005</v>
       </c>
       <c r="Q51" t="n">
-        <v>4900</v>
+        <v>5005</v>
       </c>
       <c r="R51" t="n">
-        <v>1723762</v>
+        <v>616279</v>
       </c>
       <c r="S51" t="n">
-        <v>5305</v>
+        <v>5129</v>
       </c>
       <c r="T51" t="n">
+        <v>5421</v>
+      </c>
+      <c r="U51" t="n">
         <v>5460.75</v>
       </c>
-      <c r="U51" t="n">
-        <v>5490.75</v>
-      </c>
       <c r="V51" t="n">
-        <v>5552.833333333333</v>
+        <v>5541.166666666667</v>
       </c>
       <c r="W51" t="n">
-        <v>-89.16682379205486</v>
+        <v>-117.1185340299917</v>
       </c>
       <c r="X51" t="n">
-        <v>1.852872783698629</v>
+        <v>-21.94140857903943</v>
       </c>
       <c r="Y51" t="n">
+        <v>-95.17712545095225</v>
+      </c>
+      <c r="Z51" t="n">
         <v>-91.01969657575349</v>
       </c>
-      <c r="Z51" t="n">
-        <v>-53.28493899010337</v>
-      </c>
       <c r="AA51" t="b">
         <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>-0.1090909090909091</v>
+        <v>-0.1370689655172413</v>
       </c>
       <c r="AC51" t="n">
-        <v>-0.216</v>
+        <v>-0.1226993865030674</v>
       </c>
       <c r="AD51" t="n">
-        <v>-0.1091974094257691</v>
+        <v>-0.1308592196198149</v>
       </c>
       <c r="AE51" t="n">
-        <v>-0.2481537367767983</v>
+        <v>-0.1967560019681875</v>
       </c>
       <c r="AF51" t="n">
-        <v>0.1389563273510293</v>
+        <v>0.0658967823483726</v>
       </c>
       <c r="AG51" t="n">
         <v>11.76470588235294</v>
       </c>
       <c r="AH51" t="n">
-        <v>9.803921568627452</v>
+        <v>15.68627450980392</v>
       </c>
       <c r="AI51" t="b">
         <v>0</v>
@@ -7539,13 +7555,13 @@
       </c>
       <c r="AO51" t="inlineStr"/>
       <c r="AP51" t="n">
-        <v>6390.26</v>
+        <v>5932.89</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -7573,7 +7589,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="H52" t="n">
@@ -7599,61 +7615,61 @@
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>4960</v>
+        <v>4970</v>
       </c>
       <c r="Q52" t="n">
-        <v>4960</v>
+        <v>4970</v>
       </c>
       <c r="R52" t="n">
-        <v>425716</v>
+        <v>430025</v>
       </c>
       <c r="S52" t="n">
-        <v>5190</v>
+        <v>5061</v>
       </c>
       <c r="T52" t="n">
+        <v>5648.25</v>
+      </c>
+      <c r="U52" t="n">
         <v>5721.5</v>
       </c>
-      <c r="U52" t="n">
-        <v>5779.5</v>
-      </c>
       <c r="V52" t="n">
-        <v>6261.916666666667</v>
+        <v>6239.833333333333</v>
       </c>
       <c r="W52" t="n">
-        <v>-289.1785098366445</v>
+        <v>-298.0213995734484</v>
       </c>
       <c r="X52" t="n">
-        <v>-220.6357694673449</v>
+        <v>-236.1128954885656</v>
       </c>
       <c r="Y52" t="n">
+        <v>-61.90850408488279</v>
+      </c>
+      <c r="Z52" t="n">
         <v>-68.54274036929957</v>
       </c>
-      <c r="Z52" t="n">
-        <v>-60.95287031243825</v>
-      </c>
       <c r="AA52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB52" t="n">
-        <v>-0.1895424836601307</v>
+        <v>-0.2276612276612276</v>
       </c>
       <c r="AC52" t="n">
-        <v>-0.2496217851739788</v>
+        <v>-0.210484511517077</v>
       </c>
       <c r="AD52" t="n">
-        <v>-0.1896489839949906</v>
+        <v>-0.2214514817638013</v>
       </c>
       <c r="AE52" t="n">
-        <v>-0.2817755219507772</v>
+        <v>-0.2845411269821971</v>
       </c>
       <c r="AF52" t="n">
-        <v>0.09212653795578651</v>
+        <v>0.06308964521839588</v>
       </c>
       <c r="AG52" t="n">
         <v>1.96078431372549</v>
       </c>
       <c r="AH52" t="n">
-        <v>3.92156862745098</v>
+        <v>5.88235294117647</v>
       </c>
       <c r="AI52" t="b">
         <v>0</v>
@@ -7668,16 +7684,16 @@
         <v>0</v>
       </c>
       <c r="AM52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN52" t="b">
         <v>1</v>
       </c>
       <c r="AO52" t="n">
-        <v>5733.76</v>
+        <v>5675.74</v>
       </c>
       <c r="AP52" t="n">
-        <v>7236.58</v>
+        <v>6508.95</v>
       </c>
     </row>
   </sheetData>

--- a/output/daily_screen_latest.xlsx
+++ b/output/daily_screen_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP52"/>
+  <dimension ref="A1:AP51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,17 +643,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>88.82352941176471</v>
+        <v>78.8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -671,15 +671,15 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1000</v>
+        <v>6003000</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="K2" t="b">
         <v>0</v>
@@ -688,7 +688,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1000</v>
+        <v>6003000</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -697,61 +697,61 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>316.5</v>
+        <v>190</v>
       </c>
       <c r="Q2" t="n">
-        <v>316.5</v>
+        <v>190</v>
       </c>
       <c r="R2" t="n">
-        <v>18734510</v>
+        <v>36509667</v>
       </c>
       <c r="S2" t="n">
-        <v>299.1</v>
+        <v>187.3</v>
       </c>
       <c r="T2" t="n">
-        <v>248.55</v>
+        <v>186.025</v>
       </c>
       <c r="U2" t="n">
-        <v>242.525</v>
+        <v>185.85</v>
       </c>
       <c r="V2" t="n">
-        <v>200.75</v>
+        <v>184.85</v>
       </c>
       <c r="W2" t="n">
-        <v>23.87242257329603</v>
+        <v>1.003409599950857</v>
       </c>
       <c r="X2" t="n">
-        <v>20.13494695700414</v>
+        <v>0.2239197478976003</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.737475616291896</v>
+        <v>0.7794898520532563</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.988451288546017</v>
+        <v>0.7163301077066526</v>
       </c>
       <c r="AA2" t="b">
         <v>1</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.614795918367347</v>
+        <v>0.01876675603217159</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.9843260188087775</v>
+        <v>0.07344632768361592</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.6210056642647734</v>
+        <v>0.05391870360135997</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.9102694033436574</v>
+        <v>0.01827770409580265</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.2892637390788839</v>
+        <v>0.03564099950555732</v>
       </c>
       <c r="AG2" t="n">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AH2" t="n">
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="AI2" t="b">
         <v>1</v>
@@ -785,43 +785,43 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>85.68627450980392</v>
+        <v>57.2</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>6003000</v>
+        <v>1000</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="K3" t="b">
         <v>0</v>
@@ -830,70 +830,70 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>4703000</v>
+        <v>1000</v>
       </c>
       <c r="N3" t="n">
-        <v>1300000</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2764193068254306</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>195</v>
+        <v>567</v>
       </c>
       <c r="Q3" t="n">
-        <v>195</v>
+        <v>567</v>
       </c>
       <c r="R3" t="n">
-        <v>80059631</v>
+        <v>45785250</v>
       </c>
       <c r="S3" t="n">
-        <v>184.5</v>
+        <v>559.2</v>
       </c>
       <c r="T3" t="n">
-        <v>185.85</v>
+        <v>543.3</v>
       </c>
       <c r="U3" t="n">
-        <v>185.425</v>
+        <v>538.45</v>
       </c>
       <c r="V3" t="n">
-        <v>184.6333333333333</v>
+        <v>494.4833333333333</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7453773925909388</v>
+        <v>10.98567277788015</v>
       </c>
       <c r="X3" t="n">
-        <v>0.02904728488428618</v>
+        <v>13.34924291434023</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.7163301077066526</v>
+        <v>-2.363570136460073</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.3080045721761746</v>
+        <v>-2.840567438305762</v>
       </c>
       <c r="AA3" t="b">
         <v>1</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.04557640750670244</v>
+        <v>0.2063829787234042</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.0893854748603351</v>
+        <v>0.2051009564293305</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.05178615340412884</v>
+        <v>0.2415349262925925</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.015328859395215</v>
+        <v>0.1499323328415172</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.03645729400891384</v>
+        <v>0.09160259345107535</v>
       </c>
       <c r="AG3" t="n">
-        <v>70.58823529411765</v>
+        <v>98</v>
       </c>
       <c r="AH3" t="n">
-        <v>49.01960784313725</v>
+        <v>78</v>
       </c>
       <c r="AI3" t="b">
         <v>1</v>
@@ -902,21 +902,19 @@
         <v>1</v>
       </c>
       <c r="AK3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="b">
         <v>1</v>
       </c>
       <c r="AN3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>594.22</v>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
@@ -927,26 +925,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>美律</t>
+          <t>慧洋-KY</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>71.96078431372548</v>
+        <v>47.8</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +953,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -963,7 +961,7 @@
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="K4" t="b">
         <v>0</v>
@@ -981,114 +979,110 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>81.59999847412109</v>
+        <v>100.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>81.59999847412109</v>
+        <v>100.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1776191</v>
+        <v>1548142</v>
       </c>
       <c r="S4" t="n">
-        <v>80.58000030517579</v>
+        <v>100.3199996948242</v>
       </c>
       <c r="T4" t="n">
-        <v>78.86499938964843</v>
+        <v>99.55000038146973</v>
       </c>
       <c r="U4" t="n">
-        <v>78.69499931335449</v>
+        <v>99.65000038146972</v>
       </c>
       <c r="V4" t="n">
-        <v>77.8641253153483</v>
+        <v>94.93666674296061</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8049620099526749</v>
+        <v>0.3930204925457446</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6865894772022272</v>
+        <v>0.5510634490215537</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1183725327504477</v>
+        <v>-0.1580429564758091</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0449777644195708</v>
+        <v>-0.1613387060659316</v>
       </c>
       <c r="AA4" t="b">
         <v>1</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.04347828207882465</v>
+        <v>-0.01951219512195124</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.03584895116598297</v>
+        <v>0.22114211753791</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.04968802797625105</v>
+        <v>0.01563975244723714</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.03820766429913713</v>
+        <v>0.1659734939500968</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.08789569227538818</v>
+        <v>-0.1503337415028596</v>
       </c>
       <c r="AG4" t="n">
-        <v>64.70588235294117</v>
+        <v>66</v>
       </c>
       <c r="AH4" t="n">
-        <v>37.25490196078432</v>
+        <v>80</v>
       </c>
       <c r="AI4" t="b">
         <v>1</v>
       </c>
       <c r="AJ4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="b">
         <v>1</v>
       </c>
       <c r="AN4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>102.31</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>99.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>新日興</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>70.19607843137256</v>
+        <v>56</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1097,24 +1091,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1740000</v>
+        <v>8937000</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="K5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="b">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1740000</v>
+        <v>8937000</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -1123,85 +1117,81 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>182.5</v>
+        <v>1265</v>
       </c>
       <c r="Q5" t="n">
-        <v>182.5</v>
+        <v>1265</v>
       </c>
       <c r="R5" t="n">
-        <v>3877276</v>
+        <v>7943255</v>
       </c>
       <c r="S5" t="n">
-        <v>177.3</v>
+        <v>1329</v>
       </c>
       <c r="T5" t="n">
-        <v>174.575</v>
+        <v>1368</v>
       </c>
       <c r="U5" t="n">
-        <v>174.4</v>
+        <v>1357.75</v>
       </c>
       <c r="V5" t="n">
-        <v>184.0174751281738</v>
+        <v>1198.916666666667</v>
       </c>
       <c r="W5" t="n">
-        <v>0.121216112501088</v>
+        <v>2.033985593817533</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.870453282860062</v>
+        <v>35.11999365752448</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.99166939536115</v>
+        <v>-33.08600806370695</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.58063945530842</v>
+        <v>-28.43274157005213</v>
       </c>
       <c r="AA5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.01955307262569828</v>
+        <v>0.1933962264150944</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.00556763530954596</v>
+        <v>0.1767441860465115</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.02576281852312468</v>
+        <v>0.2285481739842827</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.06848898015557414</v>
+        <v>0.1215755624586983</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.09425179867869882</v>
+        <v>0.1069726115255845</v>
       </c>
       <c r="AG5" t="n">
-        <v>60.78431372549019</v>
+        <v>96</v>
       </c>
       <c r="AH5" t="n">
-        <v>31.37254901960784</v>
+        <v>72</v>
       </c>
       <c r="AI5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="b">
         <v>1</v>
       </c>
       <c r="AK5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="b">
         <v>0</v>
       </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
+      <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -1211,26 +1201,26 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>57.45098039215686</v>
+        <v>56</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1239,93 +1229,93 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>919000</v>
+        <v>8895000</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="K6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="b">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>819000</v>
+        <v>8348000</v>
       </c>
       <c r="N6" t="n">
-        <v>100000</v>
+        <v>547000</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1221001221001221</v>
+        <v>0.06552467656923815</v>
       </c>
       <c r="P6" t="n">
-        <v>2395</v>
+        <v>654</v>
       </c>
       <c r="Q6" t="n">
-        <v>2395</v>
+        <v>654</v>
       </c>
       <c r="R6" t="n">
-        <v>1872137</v>
+        <v>17897421</v>
       </c>
       <c r="S6" t="n">
-        <v>2277</v>
+        <v>667.8</v>
       </c>
       <c r="T6" t="n">
-        <v>2373.25</v>
+        <v>706.05</v>
       </c>
       <c r="U6" t="n">
-        <v>2368.25</v>
+        <v>706.5</v>
       </c>
       <c r="V6" t="n">
-        <v>2052.093760172526</v>
+        <v>635.5833333333334</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8000953301075242</v>
+        <v>-6.265559635740374</v>
       </c>
       <c r="X6" t="n">
-        <v>4.132717150052427</v>
+        <v>7.119040713373153</v>
       </c>
       <c r="Y6" t="n">
-        <v>-3.332621819944903</v>
+        <v>-13.38460034911353</v>
       </c>
       <c r="Z6" t="n">
-        <v>-18.36484503133515</v>
+        <v>-12.94663445848076</v>
       </c>
       <c r="AA6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.04357298474945526</v>
+        <v>-0.01357466063348411</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.7104597033069244</v>
+        <v>0.07565789473684204</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.04978273064688166</v>
+        <v>0.02157728693570427</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.6364030878418043</v>
+        <v>0.02048927114902876</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.5866203571949227</v>
+        <v>0.0010880157866755</v>
       </c>
       <c r="AG6" t="n">
-        <v>66.66666666666666</v>
+        <v>68</v>
       </c>
       <c r="AH6" t="n">
-        <v>94.11764705882352</v>
+        <v>56.00000000000001</v>
       </c>
       <c r="AI6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="b">
         <v>0</v>
@@ -1334,43 +1324,39 @@
         <v>0</v>
       </c>
       <c r="AM6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>2433.32</v>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="n">
+        <v>747.79</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>55.09803921568628</v>
+        <v>56</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1379,24 +1365,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>981000</v>
+        <v>6899000</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="K7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="b">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>981000</v>
+        <v>6899000</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1405,64 +1391,64 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1660</v>
+        <v>1115</v>
       </c>
       <c r="Q7" t="n">
-        <v>1660</v>
+        <v>1115</v>
       </c>
       <c r="R7" t="n">
-        <v>6228551</v>
+        <v>9411771</v>
       </c>
       <c r="S7" t="n">
-        <v>1564</v>
+        <v>1198</v>
       </c>
       <c r="T7" t="n">
-        <v>1599.25</v>
+        <v>1178.75</v>
       </c>
       <c r="U7" t="n">
-        <v>1587.75</v>
+        <v>1175.25</v>
       </c>
       <c r="V7" t="n">
-        <v>1305.716666666667</v>
+        <v>1058.766666666667</v>
       </c>
       <c r="W7" t="n">
-        <v>26.9501913226668</v>
+        <v>10.73197912853334</v>
       </c>
       <c r="X7" t="n">
-        <v>48.053441792646</v>
+        <v>29.40459604126142</v>
       </c>
       <c r="Y7" t="n">
-        <v>-21.1032504699792</v>
+        <v>-18.67261691272808</v>
       </c>
       <c r="Z7" t="n">
-        <v>-32.61550816475103</v>
+        <v>-10.11073891431796</v>
       </c>
       <c r="AA7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.1608391608391608</v>
+        <v>0.06698564593301426</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.6517412935323383</v>
+        <v>0.2458100558659218</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.1670489067365872</v>
+        <v>0.1021375935022026</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.5776846780672182</v>
+        <v>0.1906414322781085</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.410635771330631</v>
+        <v>-0.08850383877590584</v>
       </c>
       <c r="AG7" t="n">
-        <v>90.19607843137256</v>
+        <v>92</v>
       </c>
       <c r="AH7" t="n">
-        <v>92.15686274509804</v>
+        <v>84</v>
       </c>
       <c r="AI7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="b">
         <v>1</v>
@@ -1474,13 +1460,13 @@
         <v>0</v>
       </c>
       <c r="AM7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>1899.04</v>
+        <v>1326.85</v>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
@@ -1491,26 +1477,26 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>54.90196078431372</v>
+        <v>55.6</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1519,24 +1505,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1000</v>
+        <v>19689000</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="K8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="b">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1000</v>
+        <v>19689000</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1545,64 +1531,64 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>578</v>
+        <v>1085</v>
       </c>
       <c r="Q8" t="n">
-        <v>578</v>
+        <v>1085</v>
       </c>
       <c r="R8" t="n">
-        <v>34078662</v>
+        <v>21227071</v>
       </c>
       <c r="S8" t="n">
-        <v>549.6</v>
+        <v>1090</v>
       </c>
       <c r="T8" t="n">
-        <v>538.45</v>
+        <v>1184</v>
       </c>
       <c r="U8" t="n">
-        <v>533.2</v>
+        <v>1180.75</v>
       </c>
       <c r="V8" t="n">
-        <v>492.875</v>
+        <v>1050.383333333333</v>
       </c>
       <c r="W8" t="n">
-        <v>11.09956801014948</v>
+        <v>-18.35384571584245</v>
       </c>
       <c r="X8" t="n">
-        <v>13.94013544845524</v>
+        <v>7.897570305096325</v>
       </c>
       <c r="Y8" t="n">
-        <v>-2.840567438305762</v>
+        <v>-26.25141602093878</v>
       </c>
       <c r="Z8" t="n">
-        <v>-5.550238265855194</v>
+        <v>-29.80898306559489</v>
       </c>
       <c r="AA8" t="b">
         <v>1</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.2219873150105709</v>
+        <v>0.06372549019607843</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.1991701244813278</v>
+        <v>0.2794811320754718</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.2281970609079973</v>
+        <v>0.09887743776526681</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.1251135090162077</v>
+        <v>0.2243125084876585</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.1030835518917896</v>
+        <v>-0.1254350707223917</v>
       </c>
       <c r="AG8" t="n">
-        <v>98.0392156862745</v>
+        <v>90</v>
       </c>
       <c r="AH8" t="n">
-        <v>66.66666666666666</v>
+        <v>86</v>
       </c>
       <c r="AI8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="b">
         <v>1</v>
@@ -1617,11 +1603,9 @@
         <v>1</v>
       </c>
       <c r="AN8" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>610.37</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -1631,43 +1615,43 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>54.31372549019608</v>
+        <v>49.8</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>4827000</v>
+        <v>1000</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="K9" t="b">
         <v>0</v>
@@ -1676,119 +1660,123 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2657000</v>
+        <v>1000</v>
       </c>
       <c r="N9" t="n">
-        <v>2170000</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8167105758374106</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>265</v>
+        <v>290.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>265</v>
+        <v>290.5</v>
       </c>
       <c r="R9" t="n">
-        <v>20810434</v>
+        <v>24850413</v>
       </c>
       <c r="S9" t="n">
-        <v>259.3</v>
+        <v>296.6</v>
       </c>
       <c r="T9" t="n">
-        <v>257.15</v>
+        <v>253.35</v>
       </c>
       <c r="U9" t="n">
-        <v>257.325</v>
+        <v>248.55</v>
       </c>
       <c r="V9" t="n">
-        <v>229.7666666666667</v>
+        <v>202.975</v>
       </c>
       <c r="W9" t="n">
-        <v>3.490949896689813</v>
+        <v>21.55791857126223</v>
       </c>
       <c r="X9" t="n">
-        <v>4.942006446294699</v>
+        <v>20.41954127985576</v>
       </c>
       <c r="Y9" t="n">
-        <v>-1.451056549604886</v>
+        <v>1.138377291406478</v>
       </c>
       <c r="Z9" t="n">
-        <v>-2.238911059461707</v>
+        <v>3.737475616291896</v>
       </c>
       <c r="AA9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0.01303538175046559</v>
+        <v>0.493573264781491</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.2649164677804297</v>
+        <v>0.8503184713375795</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0.006825635853039191</v>
+        <v>0.5287252123506794</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.1908598523153096</v>
+        <v>0.7951498477497663</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.1976854881683487</v>
+        <v>-0.2664246353990869</v>
       </c>
       <c r="AG9" t="n">
-        <v>54.90196078431373</v>
+        <v>100</v>
       </c>
       <c r="AH9" t="n">
-        <v>78.43137254901961</v>
+        <v>98</v>
       </c>
       <c r="AI9" t="b">
         <v>1</v>
       </c>
       <c r="AJ9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>281.43</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>275.74</v>
+        <v>0</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>40.98039215686275</v>
+        <v>47.6</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1797,24 +1785,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1000</v>
+        <v>7224000</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="K10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="b">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1000</v>
+        <v>7224000</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1823,64 +1811,64 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>100.5</v>
+        <v>1420</v>
       </c>
       <c r="Q10" t="n">
-        <v>100.5</v>
+        <v>1420</v>
       </c>
       <c r="R10" t="n">
-        <v>1156541</v>
+        <v>18706845</v>
       </c>
       <c r="S10" t="n">
-        <v>100.4199996948242</v>
+        <v>1543</v>
       </c>
       <c r="T10" t="n">
-        <v>99.65000038146972</v>
+        <v>1600.75</v>
       </c>
       <c r="U10" t="n">
-        <v>99.72500038146973</v>
+        <v>1601.5</v>
       </c>
       <c r="V10" t="n">
-        <v>94.63333346048991</v>
+        <v>1474.833333333333</v>
       </c>
       <c r="W10" t="n">
-        <v>0.4292354820745743</v>
+        <v>-16.09233594368516</v>
       </c>
       <c r="X10" t="n">
-        <v>0.5905741881405059</v>
+        <v>28.44855229443083</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.1613387060659316</v>
+        <v>-44.54088823811599</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.1646208256594418</v>
+        <v>-35.06835181539509</v>
       </c>
       <c r="AA10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.01470588235294112</v>
+        <v>-0.01045296167247389</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.199283965872026</v>
+        <v>0.1314741035856575</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0.008496136455514725</v>
+        <v>0.02469898589671449</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.1252273504069059</v>
+        <v>0.07630547999784421</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.1337234868624206</v>
+        <v>-0.05160649410112972</v>
       </c>
       <c r="AG10" t="n">
-        <v>50.98039215686274</v>
+        <v>70</v>
       </c>
       <c r="AH10" t="n">
-        <v>68.62745098039215</v>
+        <v>66</v>
       </c>
       <c r="AI10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="b">
         <v>0</v>
@@ -1892,41 +1880,39 @@
         <v>0</v>
       </c>
       <c r="AM10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>102.51</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="n">
-        <v>101.61</v>
+        <v>1630.26</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>38.43137254901961</v>
+        <v>46</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1935,15 +1921,15 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1000</v>
+        <v>2512000</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="K11" t="b">
         <v>0</v>
@@ -1952,7 +1938,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1000</v>
+        <v>2512000</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1961,112 +1947,110 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>250</v>
+        <v>6070</v>
       </c>
       <c r="Q11" t="n">
-        <v>250</v>
+        <v>6070</v>
       </c>
       <c r="R11" t="n">
-        <v>54319165</v>
+        <v>1719419</v>
       </c>
       <c r="S11" t="n">
-        <v>242.9</v>
+        <v>6509</v>
       </c>
       <c r="T11" t="n">
-        <v>248.475</v>
+        <v>6765.75</v>
       </c>
       <c r="U11" t="n">
-        <v>248.5</v>
+        <v>6751.75</v>
       </c>
       <c r="V11" t="n">
-        <v>250.4083333333333</v>
+        <v>5616.25</v>
       </c>
       <c r="W11" t="n">
-        <v>-1.726222274315262</v>
+        <v>-17.30652828338771</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.819432439523187</v>
+        <v>148.2485549823905</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.09321016520792491</v>
+        <v>-165.5550832657782</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.9419037945475166</v>
+        <v>-127.5612619723241</v>
       </c>
       <c r="AA11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0.001996007984031989</v>
+        <v>0.04835924006908465</v>
       </c>
       <c r="AC11" t="n">
-        <v>-0.00990099009900991</v>
+        <v>0.7219858156028369</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.004213737913394411</v>
+        <v>0.08351118763827303</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.08395760556413001</v>
+        <v>0.6668171920150237</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.08817134347752442</v>
+        <v>-0.5833060043767506</v>
       </c>
       <c r="AG11" t="n">
-        <v>56.86274509803921</v>
+        <v>88</v>
       </c>
       <c r="AH11" t="n">
-        <v>25.49019607843137</v>
+        <v>96</v>
       </c>
       <c r="AI11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="b">
         <v>0</v>
       </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
-      <c r="AP11" t="n">
-        <v>248.39</v>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>33.52941176470588</v>
+        <v>44.4</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2075,15 +2059,15 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>470000</v>
+        <v>981000</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="K12" t="b">
         <v>0</v>
@@ -2092,7 +2076,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>470000</v>
+        <v>981000</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -2101,103 +2085,103 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>3230</v>
+        <v>1560</v>
       </c>
       <c r="Q12" t="n">
-        <v>3230</v>
+        <v>1560</v>
       </c>
       <c r="R12" t="n">
-        <v>820966</v>
+        <v>5705283</v>
       </c>
       <c r="S12" t="n">
-        <v>3105</v>
+        <v>1572</v>
       </c>
       <c r="T12" t="n">
-        <v>3209.5</v>
+        <v>1602</v>
       </c>
       <c r="U12" t="n">
-        <v>3224</v>
+        <v>1599.25</v>
       </c>
       <c r="V12" t="n">
-        <v>3035</v>
+        <v>1315.133333333333</v>
       </c>
       <c r="W12" t="n">
-        <v>-19.49173312319181</v>
+        <v>19.48525973849632</v>
       </c>
       <c r="X12" t="n">
-        <v>-22.50021037741953</v>
+        <v>42.33980538181607</v>
       </c>
       <c r="Y12" t="n">
-        <v>3.008477254227724</v>
+        <v>-22.85454564331975</v>
       </c>
       <c r="Z12" t="n">
-        <v>-9.644407592523979</v>
+        <v>-21.1032504699792</v>
       </c>
       <c r="AA12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0.08238636363636365</v>
+        <v>0.03654485049833878</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.2471042471042471</v>
+        <v>0.5678391959798994</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0.07617661773893725</v>
+        <v>0.07169679806752716</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.173047631639127</v>
+        <v>0.5126705723920861</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.2492242493780642</v>
+        <v>-0.440973774324559</v>
       </c>
       <c r="AG12" t="n">
-        <v>23.52941176470588</v>
+        <v>84</v>
       </c>
       <c r="AH12" t="n">
-        <v>76.47058823529412</v>
+        <v>92</v>
       </c>
       <c r="AI12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
-      <c r="AP12" t="n">
-        <v>3463.42</v>
+        <v>1</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1818.96</v>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2206,99 +2190,99 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>63.33333333333333</v>
+        <v>42.4</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>19689000</v>
+        <v>3921000</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="K13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="b">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>19499000</v>
+        <v>3921000</v>
       </c>
       <c r="N13" t="n">
-        <v>190000</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0.009744089440484128</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1100</v>
+        <v>89.80000305175781</v>
       </c>
       <c r="Q13" t="n">
-        <v>1100</v>
+        <v>89.80000305175781</v>
       </c>
       <c r="R13" t="n">
-        <v>19004375</v>
+        <v>2745757</v>
       </c>
       <c r="S13" t="n">
-        <v>1088</v>
+        <v>91.16000061035156</v>
       </c>
       <c r="T13" t="n">
-        <v>1180.75</v>
+        <v>88.23500099182129</v>
       </c>
       <c r="U13" t="n">
-        <v>1174.8</v>
+        <v>87.90500068664551</v>
       </c>
       <c r="V13" t="n">
-        <v>1046.433333333333</v>
+        <v>84.83500010172526</v>
       </c>
       <c r="W13" t="n">
-        <v>-15.34855875526387</v>
+        <v>1.469152495810761</v>
       </c>
       <c r="X13" t="n">
-        <v>14.46042431033102</v>
+        <v>1.834851905037134</v>
       </c>
       <c r="Y13" t="n">
-        <v>-29.80898306559489</v>
+        <v>-0.3656994092263737</v>
       </c>
       <c r="Z13" t="n">
-        <v>-34.77684737989722</v>
+        <v>-0.09908956594358531</v>
       </c>
       <c r="AA13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.1213047910295617</v>
+        <v>0.07932699934618292</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.3110846245530394</v>
+        <v>0.01583712106010604</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.1275145369269881</v>
+        <v>0.1144789469153713</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.2370280090879193</v>
+        <v>-0.03933150252770723</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.1095134721609312</v>
+        <v>0.1538104494430785</v>
       </c>
       <c r="AG13" t="n">
-        <v>88.23529411764706</v>
+        <v>94</v>
       </c>
       <c r="AH13" t="n">
-        <v>80.3921568627451</v>
+        <v>42</v>
       </c>
       <c r="AI13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ13" t="b">
         <v>1</v>
@@ -2310,12 +2294,14 @@
         <v>0</v>
       </c>
       <c r="AM13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO13" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>93.93000000000001</v>
+      </c>
       <c r="AP13" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -2325,17 +2311,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2344,7 +2330,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>54.90196078431373</v>
+        <v>42.2</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2353,24 +2339,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>8937000</v>
+        <v>121000</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="K14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="b">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>8937000</v>
+        <v>121000</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2379,61 +2365,61 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1340</v>
+        <v>1260</v>
       </c>
       <c r="Q14" t="n">
-        <v>1340</v>
+        <v>1260</v>
       </c>
       <c r="R14" t="n">
-        <v>7305114</v>
+        <v>2017503</v>
       </c>
       <c r="S14" t="n">
         <v>1345</v>
       </c>
       <c r="T14" t="n">
-        <v>1357.75</v>
+        <v>1394</v>
       </c>
       <c r="U14" t="n">
-        <v>1345.75</v>
+        <v>1392.75</v>
       </c>
       <c r="V14" t="n">
-        <v>1195.75</v>
+        <v>1273.091454060872</v>
       </c>
       <c r="W14" t="n">
-        <v>14.95875410339909</v>
+        <v>-15.07473252962268</v>
       </c>
       <c r="X14" t="n">
-        <v>43.39149567345122</v>
+        <v>25.71250121027664</v>
       </c>
       <c r="Y14" t="n">
-        <v>-28.43274157005213</v>
+        <v>-40.78723373989932</v>
       </c>
       <c r="Z14" t="n">
-        <v>-29.43398515775625</v>
+        <v>-34.67944144613021</v>
       </c>
       <c r="AA14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.2181818181818183</v>
+        <v>0.02024291497975717</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.2072072072072073</v>
+        <v>0.2328659625906726</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.2243915640792447</v>
+        <v>0.05539486254894554</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.1331505917420872</v>
+        <v>0.1776973390028593</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.09124097233715744</v>
+        <v>-0.1223024764539138</v>
       </c>
       <c r="AG14" t="n">
-        <v>96.07843137254902</v>
+        <v>80</v>
       </c>
       <c r="AH14" t="n">
-        <v>72.54901960784314</v>
+        <v>82</v>
       </c>
       <c r="AI14" t="b">
         <v>0</v>
@@ -2448,7 +2434,7 @@
         <v>0</v>
       </c>
       <c r="AM14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="b">
         <v>0</v>
@@ -2463,17 +2449,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2482,7 +2468,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>54.90196078431373</v>
+        <v>41.59999999999999</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2491,24 +2477,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>6899000</v>
+        <v>852000</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="K15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="b">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>6899000</v>
+        <v>852000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2517,67 +2503,67 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1195</v>
+        <v>7585</v>
       </c>
       <c r="Q15" t="n">
-        <v>1195</v>
+        <v>7585</v>
       </c>
       <c r="R15" t="n">
-        <v>8380399</v>
+        <v>1507339</v>
       </c>
       <c r="S15" t="n">
-        <v>1213</v>
+        <v>7728</v>
       </c>
       <c r="T15" t="n">
-        <v>1175.25</v>
+        <v>8079.75</v>
       </c>
       <c r="U15" t="n">
-        <v>1166.5</v>
+        <v>8081.25</v>
       </c>
       <c r="V15" t="n">
-        <v>1055.1</v>
+        <v>6328.666666666667</v>
       </c>
       <c r="W15" t="n">
-        <v>23.96201135512547</v>
+        <v>41.43388910002159</v>
       </c>
       <c r="X15" t="n">
-        <v>34.07275026944343</v>
+        <v>184.6003906854221</v>
       </c>
       <c r="Y15" t="n">
-        <v>-10.11073891431796</v>
+        <v>-143.1665015854005</v>
       </c>
       <c r="Z15" t="n">
-        <v>-7.215056006402492</v>
+        <v>-133.9920399343507</v>
       </c>
       <c r="AA15" t="b">
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.1715686274509804</v>
+        <v>-0.003939592908732803</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.3263041065482797</v>
+        <v>0.8728395061728396</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.1777783733484068</v>
+        <v>0.03121235466045558</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.2522474910831596</v>
+        <v>0.8176708825850263</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.07446911773475273</v>
+        <v>-0.7864585279245707</v>
       </c>
       <c r="AG15" t="n">
-        <v>92.15686274509804</v>
+        <v>72</v>
       </c>
       <c r="AH15" t="n">
-        <v>84.31372549019608</v>
+        <v>100</v>
       </c>
       <c r="AI15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="b">
         <v>0</v>
@@ -2589,31 +2575,27 @@
         <v>0</v>
       </c>
       <c r="AN15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>1309.72</v>
-      </c>
-      <c r="AP15" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="n">
+        <v>8895.790000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2622,7 +2604,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>50.58823529411764</v>
+        <v>40.6</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2631,15 +2613,15 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>7224000</v>
+        <v>12671000</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K16" t="b">
         <v>1</v>
@@ -2648,7 +2630,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>7224000</v>
+        <v>12671000</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2657,67 +2639,67 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1500</v>
+        <v>2385</v>
       </c>
       <c r="Q16" t="n">
-        <v>1500</v>
+        <v>2385</v>
       </c>
       <c r="R16" t="n">
-        <v>20799640</v>
+        <v>27360404</v>
       </c>
       <c r="S16" t="n">
-        <v>1584</v>
+        <v>2410</v>
       </c>
       <c r="T16" t="n">
-        <v>1601.5</v>
+        <v>2485.25</v>
       </c>
       <c r="U16" t="n">
-        <v>1595</v>
+        <v>2490</v>
       </c>
       <c r="V16" t="n">
-        <v>1472.083333333333</v>
+        <v>2419.045874023438</v>
       </c>
       <c r="W16" t="n">
-        <v>4.515422538564735</v>
+        <v>-23.03721596792138</v>
       </c>
       <c r="X16" t="n">
-        <v>39.58377435395983</v>
+        <v>-3.486164710769593</v>
       </c>
       <c r="Y16" t="n">
-        <v>-35.06835181539509</v>
+        <v>-19.55105125715179</v>
       </c>
       <c r="Z16" t="n">
-        <v>-27.04619705522384</v>
+        <v>-19.53124648872446</v>
       </c>
       <c r="AA16" t="b">
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.0948905109489051</v>
+        <v>-0.03830645161290325</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.2</v>
+        <v>0.01788108362007046</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.1011002568463315</v>
+        <v>-0.003154504043714867</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.1259433845348799</v>
+        <v>-0.03728753996774281</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.02484312768854835</v>
+        <v>0.03413303592402794</v>
       </c>
       <c r="AG16" t="n">
-        <v>82.35294117647058</v>
+        <v>54</v>
       </c>
       <c r="AH16" t="n">
-        <v>70.58823529411765</v>
+        <v>44</v>
       </c>
       <c r="AI16" t="b">
         <v>0</v>
       </c>
       <c r="AJ16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="b">
         <v>0</v>
@@ -2729,29 +2711,29 @@
         <v>0</v>
       </c>
       <c r="AN16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO16" t="inlineStr"/>
-      <c r="AP16" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>2609.19</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>2565.53</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2760,7 +2742,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>47.84313725490196</v>
+        <v>39.8</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2769,24 +2751,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>8348000</v>
+        <v>5163000</v>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="K17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="b">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>8348000</v>
+        <v>5163000</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2795,81 +2777,85 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>684</v>
+        <v>19.54999923706055</v>
       </c>
       <c r="Q17" t="n">
-        <v>684</v>
+        <v>19.54999923706055</v>
       </c>
       <c r="R17" t="n">
-        <v>10778211</v>
+        <v>48162401</v>
       </c>
       <c r="S17" t="n">
-        <v>671.6</v>
+        <v>19.55999984741211</v>
       </c>
       <c r="T17" t="n">
-        <v>706.5</v>
+        <v>19.12750005722046</v>
       </c>
       <c r="U17" t="n">
-        <v>704.2</v>
+        <v>19.08250007629395</v>
       </c>
       <c r="V17" t="n">
-        <v>634.8166666666667</v>
+        <v>19.07416674296061</v>
       </c>
       <c r="W17" t="n">
-        <v>-2.481443657829232</v>
+        <v>0.1720255685351937</v>
       </c>
       <c r="X17" t="n">
-        <v>10.46519080065153</v>
+        <v>0.1272904830219476</v>
       </c>
       <c r="Y17" t="n">
-        <v>-12.94663445848076</v>
+        <v>0.04473508551324606</v>
       </c>
       <c r="Z17" t="n">
-        <v>-15.44264518869981</v>
+        <v>0.06097761265280496</v>
       </c>
       <c r="AA17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.07210031347962387</v>
+        <v>0.04825735318707736</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.1158238172920065</v>
+        <v>0.01558437595119733</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.07831005937705027</v>
+        <v>0.08340930075626574</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.04176720182688642</v>
+        <v>-0.03958424763661594</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.03654285755016384</v>
+        <v>0.1229935483928817</v>
       </c>
       <c r="AG17" t="n">
-        <v>78.43137254901961</v>
+        <v>86</v>
       </c>
       <c r="AH17" t="n">
-        <v>54.90196078431373</v>
+        <v>40</v>
       </c>
       <c r="AI17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ17" t="b">
         <v>1</v>
       </c>
       <c r="AK17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="b">
         <v>0</v>
       </c>
-      <c r="AO17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
+      </c>
       <c r="AP17" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -2879,17 +2865,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2898,7 +2884,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>46.66666666666667</v>
+        <v>39.59999999999999</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2907,15 +2893,15 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2512000</v>
+        <v>4328000</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K18" t="b">
         <v>0</v>
@@ -2924,7 +2910,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2512000</v>
+        <v>4328000</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2933,61 +2919,61 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>6535</v>
+        <v>5070</v>
       </c>
       <c r="Q18" t="n">
-        <v>6535</v>
+        <v>5070</v>
       </c>
       <c r="R18" t="n">
-        <v>1306728</v>
+        <v>4742168</v>
       </c>
       <c r="S18" t="n">
-        <v>6648</v>
+        <v>5059</v>
       </c>
       <c r="T18" t="n">
-        <v>6751.75</v>
+        <v>5311</v>
       </c>
       <c r="U18" t="n">
-        <v>6701.25</v>
+        <v>5302.25</v>
       </c>
       <c r="V18" t="n">
-        <v>5573.833333333333</v>
+        <v>5330.075</v>
       </c>
       <c r="W18" t="n">
-        <v>62.07606382651102</v>
+        <v>-92.43036778172063</v>
       </c>
       <c r="X18" t="n">
-        <v>189.6373257988351</v>
+        <v>-5.988125847553334</v>
       </c>
       <c r="Y18" t="n">
-        <v>-127.5612619723241</v>
+        <v>-86.4422419341673</v>
       </c>
       <c r="Z18" t="n">
-        <v>-121.5794733002481</v>
+        <v>-101.2885088592319</v>
       </c>
       <c r="AA18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.1828054298642534</v>
+        <v>0.03575076608784467</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.9052478134110786</v>
+        <v>0.05776750642324702</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.1890151757616798</v>
+        <v>0.07090271365703305</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.8311911979459585</v>
+        <v>0.002598882835433747</v>
       </c>
       <c r="AF18" t="n">
-        <v>-0.6421760221842787</v>
+        <v>0.0683038308215993</v>
       </c>
       <c r="AG18" t="n">
-        <v>94.11764705882352</v>
+        <v>82</v>
       </c>
       <c r="AH18" t="n">
-        <v>96.07843137254902</v>
+        <v>50</v>
       </c>
       <c r="AI18" t="b">
         <v>0</v>
@@ -3002,12 +2988,14 @@
         <v>0</v>
       </c>
       <c r="AM18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN18" t="b">
         <v>0</v>
       </c>
-      <c r="AO18" t="inlineStr"/>
+      <c r="AO18" t="n">
+        <v>6043.44</v>
+      </c>
       <c r="AP18" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -3017,17 +3005,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3036,102 +3024,102 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>44.90196078431373</v>
+        <v>39.2</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>6587450</v>
+        <v>501000</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="K19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="b">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>6351450</v>
+        <v>501000</v>
       </c>
       <c r="N19" t="n">
-        <v>236000</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0.03715686969117288</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>278</v>
+        <v>224.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>278</v>
+        <v>224.5</v>
       </c>
       <c r="R19" t="n">
-        <v>23007725</v>
+        <v>40806726</v>
       </c>
       <c r="S19" t="n">
-        <v>269.6</v>
+        <v>240.9</v>
       </c>
       <c r="T19" t="n">
-        <v>292.975</v>
+        <v>237.225</v>
       </c>
       <c r="U19" t="n">
-        <v>293.65</v>
+        <v>237.1</v>
       </c>
       <c r="V19" t="n">
-        <v>265.1059524536133</v>
+        <v>223.775</v>
       </c>
       <c r="W19" t="n">
-        <v>-5.049606411829302</v>
+        <v>0.5494938361759409</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.02688991165138888</v>
+        <v>3.155361086914562</v>
       </c>
       <c r="Y19" t="n">
-        <v>-5.022716500177913</v>
+        <v>-2.605867250738621</v>
       </c>
       <c r="Z19" t="n">
-        <v>-6.894559289010194</v>
+        <v>-0.8858338769129448</v>
       </c>
       <c r="AA19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>-0.04631217838765012</v>
+        <v>0.01126126126126126</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.08123508695633075</v>
+        <v>0.1253132832080202</v>
       </c>
       <c r="AD19" t="n">
-        <v>-0.04010243249022372</v>
+        <v>0.04641320883044964</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.007178471491210647</v>
+        <v>0.07014465962020688</v>
       </c>
       <c r="AF19" t="n">
-        <v>-0.04728090398143436</v>
+        <v>-0.02373145078975725</v>
       </c>
       <c r="AG19" t="n">
-        <v>37.25490196078432</v>
+        <v>76</v>
       </c>
       <c r="AH19" t="n">
-        <v>45.09803921568628</v>
+        <v>64</v>
       </c>
       <c r="AI19" t="b">
         <v>0</v>
       </c>
       <c r="AJ19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK19" t="b">
         <v>0</v>
@@ -3140,30 +3128,34 @@
         <v>0</v>
       </c>
       <c r="AM19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO19" t="inlineStr"/>
-      <c r="AP19" t="n">
-        <v>317.26</v>
+        <v>1</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>254.13</v>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3172,7 +3164,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>44.50980392156863</v>
+        <v>37.4</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3181,15 +3173,15 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>852000</v>
+        <v>919000</v>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K20" t="b">
         <v>0</v>
@@ -3198,7 +3190,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>852000</v>
+        <v>919000</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -3207,67 +3199,67 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>8000</v>
+        <v>2335</v>
       </c>
       <c r="Q20" t="n">
-        <v>8000</v>
+        <v>2335</v>
       </c>
       <c r="R20" t="n">
-        <v>1994023</v>
+        <v>1263039</v>
       </c>
       <c r="S20" t="n">
-        <v>7745</v>
+        <v>2321</v>
       </c>
       <c r="T20" t="n">
-        <v>8081.25</v>
+        <v>2369.25</v>
       </c>
       <c r="U20" t="n">
-        <v>8038.75</v>
+        <v>2373.25</v>
       </c>
       <c r="V20" t="n">
-        <v>6269.75</v>
+        <v>2066.928828938802</v>
       </c>
       <c r="W20" t="n">
-        <v>86.39997614742151</v>
+        <v>3.930312659717401</v>
       </c>
       <c r="X20" t="n">
-        <v>220.3920160817722</v>
+        <v>4.092236251985423</v>
       </c>
       <c r="Y20" t="n">
-        <v>-133.9920399343507</v>
+        <v>-0.1619235922680211</v>
       </c>
       <c r="Z20" t="n">
-        <v>-172.2319588724994</v>
+        <v>-3.332621819944903</v>
       </c>
       <c r="AA20" t="b">
         <v>1</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.118881118881119</v>
+        <v>-0.0331262939958592</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.9656019656019657</v>
+        <v>0.6160334055754417</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.1250908647785454</v>
+        <v>0.002025653573329178</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.8915453501368455</v>
+        <v>0.5608647819876285</v>
       </c>
       <c r="AF20" t="n">
-        <v>-0.7664544853583002</v>
+        <v>-0.5588391284142993</v>
       </c>
       <c r="AG20" t="n">
-        <v>86.27450980392157</v>
+        <v>60</v>
       </c>
       <c r="AH20" t="n">
-        <v>98.0392156862745</v>
+        <v>94</v>
       </c>
       <c r="AI20" t="b">
         <v>0</v>
       </c>
       <c r="AJ20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="b">
         <v>0</v>
@@ -3279,31 +3271,29 @@
         <v>1</v>
       </c>
       <c r="AN20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO20" t="n">
-        <v>9520</v>
-      </c>
-      <c r="AP20" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>2339.67</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>2536.05</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3312,7 +3302,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>40.58823529411765</v>
+        <v>36.4</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3321,15 +3311,15 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>121000</v>
+        <v>1000</v>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="K21" t="b">
         <v>0</v>
@@ -3338,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>121000</v>
+        <v>1000</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -3347,67 +3337,67 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1330</v>
+        <v>6175</v>
       </c>
       <c r="Q21" t="n">
-        <v>1330</v>
+        <v>6175</v>
       </c>
       <c r="R21" t="n">
-        <v>1726741</v>
+        <v>1825937</v>
       </c>
       <c r="S21" t="n">
-        <v>1371</v>
+        <v>6193</v>
       </c>
       <c r="T21" t="n">
-        <v>1392.75</v>
+        <v>6472</v>
       </c>
       <c r="U21" t="n">
-        <v>1388.75</v>
+        <v>6483.25</v>
       </c>
       <c r="V21" t="n">
-        <v>1269.124935913086</v>
+        <v>5925.428963216146</v>
       </c>
       <c r="W21" t="n">
-        <v>1.229868199121256</v>
+        <v>-91.34065449387526</v>
       </c>
       <c r="X21" t="n">
-        <v>35.90930964525147</v>
+        <v>15.5738782012865</v>
       </c>
       <c r="Y21" t="n">
-        <v>-34.67944144613021</v>
+        <v>-106.9145326951618</v>
       </c>
       <c r="Z21" t="n">
-        <v>-31.05978533212637</v>
+        <v>-116.7328604290002</v>
       </c>
       <c r="AA21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.06400000000000006</v>
+        <v>-0.03515625</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.4298366135921066</v>
+        <v>0.5235702267940734</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.07020974589742646</v>
+        <v>-4.302430811620184e-06</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.3557799981269865</v>
+        <v>0.4684016032062601</v>
       </c>
       <c r="AF21" t="n">
-        <v>-0.28557025222956</v>
+        <v>-0.4684059056370717</v>
       </c>
       <c r="AG21" t="n">
-        <v>76.47058823529412</v>
+        <v>57.99999999999999</v>
       </c>
       <c r="AH21" t="n">
-        <v>88.23529411764706</v>
+        <v>90</v>
       </c>
       <c r="AI21" t="b">
         <v>0</v>
       </c>
       <c r="AJ21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="b">
         <v>0</v>
@@ -3416,32 +3406,32 @@
         <v>0</v>
       </c>
       <c r="AM21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN21" t="b">
         <v>0</v>
       </c>
-      <c r="AO21" t="inlineStr"/>
-      <c r="AP21" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+      <c r="AO21" t="n">
+        <v>7385.3</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>6717.63</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>美律</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3450,7 +3440,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>38.82352941176471</v>
+        <v>35.2</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3459,7 +3449,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -3467,7 +3457,7 @@
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="K22" t="b">
         <v>0</v>
@@ -3485,64 +3475,64 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>102.5</v>
+        <v>79.40000152587891</v>
       </c>
       <c r="Q22" t="n">
-        <v>102.5</v>
+        <v>79.40000152587891</v>
       </c>
       <c r="R22" t="n">
-        <v>12862742</v>
+        <v>1417071</v>
       </c>
       <c r="S22" t="n">
-        <v>103.0199996948242</v>
+        <v>80.28000030517578</v>
       </c>
       <c r="T22" t="n">
-        <v>113.4049999237061</v>
+        <v>78.90499954223633</v>
       </c>
       <c r="U22" t="n">
-        <v>112.9799999237061</v>
+        <v>78.86499938964843</v>
       </c>
       <c r="V22" t="n">
-        <v>96.16666653951009</v>
+        <v>77.85868835449219</v>
       </c>
       <c r="W22" t="n">
-        <v>-1.74440482969753</v>
+        <v>0.6118438115693436</v>
       </c>
       <c r="X22" t="n">
-        <v>2.19076379448693</v>
+        <v>0.6716403440756505</v>
       </c>
       <c r="Y22" t="n">
-        <v>-3.93516862418446</v>
+        <v>-0.0597965325063069</v>
       </c>
       <c r="Z22" t="n">
-        <v>-4.351910718720799</v>
+        <v>0.1183725327504477</v>
       </c>
       <c r="AA22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.09042553191489366</v>
+        <v>0.01017815607237216</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.1288545876102334</v>
+        <v>-0.004091723585210372</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.09663527781232006</v>
+        <v>0.04533010364156054</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.05479797214511328</v>
+        <v>-0.05926034717302364</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.04183730566720678</v>
+        <v>0.1045904508145842</v>
       </c>
       <c r="AG22" t="n">
-        <v>80.3921568627451</v>
+        <v>74</v>
       </c>
       <c r="AH22" t="n">
-        <v>58.82352941176471</v>
+        <v>30</v>
       </c>
       <c r="AI22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ22" t="b">
         <v>1</v>
@@ -3554,12 +3544,14 @@
         <v>0</v>
       </c>
       <c r="AM22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO22" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>80.19</v>
+      </c>
       <c r="AP22" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -3569,17 +3561,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3588,7 +3580,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>38.03921568627451</v>
+        <v>32.6</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3597,24 +3589,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>3921000</v>
+        <v>23519000</v>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="K23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="b">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3921000</v>
+        <v>23519000</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -3623,67 +3615,67 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>92.19999694824219</v>
+        <v>507</v>
       </c>
       <c r="Q23" t="n">
-        <v>92.19999694824219</v>
+        <v>507</v>
       </c>
       <c r="R23" t="n">
-        <v>2571552</v>
+        <v>45898163</v>
       </c>
       <c r="S23" t="n">
-        <v>91.2</v>
+        <v>534.6</v>
       </c>
       <c r="T23" t="n">
-        <v>87.90500068664551</v>
+        <v>584.45</v>
       </c>
       <c r="U23" t="n">
-        <v>87.4550006866455</v>
+        <v>586.95</v>
       </c>
       <c r="V23" t="n">
-        <v>84.81166674296061</v>
+        <v>567.9416666666667</v>
       </c>
       <c r="W23" t="n">
-        <v>1.827187191400142</v>
+        <v>-17.37564989530244</v>
       </c>
       <c r="X23" t="n">
-        <v>1.926276757343728</v>
+        <v>-2.56196844601415</v>
       </c>
       <c r="Y23" t="n">
-        <v>-0.09908956594358531</v>
+        <v>-14.81368144928829</v>
       </c>
       <c r="Z23" t="n">
-        <v>-0.05696033436555425</v>
+        <v>-13.52868915640523</v>
       </c>
       <c r="AA23" t="b">
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.1081730808908419</v>
+        <v>-0.08976660682226212</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.03712030782589637</v>
+        <v>-0.1888</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.1143828267882683</v>
+        <v>-0.05461465925307374</v>
       </c>
       <c r="AE23" t="n">
-        <v>-0.03693630763922373</v>
+        <v>-0.2439686235878132</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.151319134427492</v>
+        <v>0.1893539643347395</v>
       </c>
       <c r="AG23" t="n">
-        <v>84.31372549019608</v>
+        <v>38</v>
       </c>
       <c r="AH23" t="n">
-        <v>39.21568627450981</v>
+        <v>12</v>
       </c>
       <c r="AI23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="b">
         <v>0</v>
@@ -3695,31 +3687,27 @@
         <v>0</v>
       </c>
       <c r="AN23" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>93.48999999999999</v>
-      </c>
-      <c r="AP23" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="AO23" t="inlineStr"/>
+      <c r="AP23" t="n">
+        <v>652.53</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3728,7 +3716,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>37.64705882352942</v>
+        <v>32</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3737,15 +3725,15 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>501000</v>
+        <v>1000</v>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="K24" t="b">
         <v>0</v>
@@ -3754,7 +3742,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>501000</v>
+        <v>1000</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3763,103 +3751,103 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>240.5</v>
+        <v>245</v>
       </c>
       <c r="Q24" t="n">
-        <v>240.5</v>
+        <v>245</v>
       </c>
       <c r="R24" t="n">
-        <v>62505022</v>
+        <v>26532180</v>
       </c>
       <c r="S24" t="n">
-        <v>241.6</v>
+        <v>244</v>
       </c>
       <c r="T24" t="n">
-        <v>237.1</v>
+        <v>248.225</v>
       </c>
       <c r="U24" t="n">
-        <v>236.5</v>
+        <v>248.475</v>
       </c>
       <c r="V24" t="n">
-        <v>223.3583333333333</v>
+        <v>250.275</v>
       </c>
       <c r="W24" t="n">
-        <v>2.920994022686273</v>
+        <v>-1.507410316193699</v>
       </c>
       <c r="X24" t="n">
-        <v>3.806827899599218</v>
+        <v>-1.757028014857289</v>
       </c>
       <c r="Y24" t="n">
-        <v>-0.8858338769129448</v>
+        <v>0.2496176986635905</v>
       </c>
       <c r="Z24" t="n">
-        <v>-0.3528365057489413</v>
+        <v>0.09321016520792491</v>
       </c>
       <c r="AA24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.05251641137855589</v>
+        <v>-0.02000000000000002</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.1935483870967742</v>
+        <v>-0.03162055335968383</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.05872615727598229</v>
+        <v>0.01515194756918836</v>
       </c>
       <c r="AE24" t="n">
-        <v>0.1194917716316541</v>
+        <v>-0.0867891769474971</v>
       </c>
       <c r="AF24" t="n">
-        <v>-0.06076561435567185</v>
+        <v>0.1019411245166855</v>
       </c>
       <c r="AG24" t="n">
-        <v>74.50980392156863</v>
+        <v>64</v>
       </c>
       <c r="AH24" t="n">
-        <v>64.70588235294117</v>
+        <v>28</v>
       </c>
       <c r="AI24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN24" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>250.6</v>
-      </c>
-      <c r="AP24" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
+      </c>
+      <c r="AP24" t="n">
+        <v>256.39</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3868,7 +3856,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>37.05882352941177</v>
+        <v>31.4</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3877,15 +3865,15 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>12671000</v>
+        <v>6587450</v>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K25" t="b">
         <v>1</v>
@@ -3894,7 +3882,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>12671000</v>
+        <v>6587450</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3903,61 +3891,61 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2420</v>
+        <v>262.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>2420</v>
+        <v>262.5</v>
       </c>
       <c r="R25" t="n">
-        <v>23935196</v>
+        <v>33661928</v>
       </c>
       <c r="S25" t="n">
-        <v>2421</v>
+        <v>267.7</v>
       </c>
       <c r="T25" t="n">
-        <v>2490</v>
+        <v>291.025</v>
       </c>
       <c r="U25" t="n">
-        <v>2492</v>
+        <v>292.975</v>
       </c>
       <c r="V25" t="n">
-        <v>2418.347587076823</v>
+        <v>265.1166666666667</v>
       </c>
       <c r="W25" t="n">
-        <v>-18.1296483855067</v>
+        <v>-6.221157300770301</v>
       </c>
       <c r="X25" t="n">
-        <v>1.401598102918036</v>
+        <v>-1.265743389475171</v>
       </c>
       <c r="Y25" t="n">
-        <v>-19.53124648842473</v>
+        <v>-4.95541391129513</v>
       </c>
       <c r="Z25" t="n">
-        <v>-22.29312470038367</v>
+        <v>-5.022716500177913</v>
       </c>
       <c r="AA25" t="b">
         <v>1</v>
       </c>
       <c r="AB25" t="n">
-        <v>-0.01626016260162599</v>
+        <v>-0.1293532338308457</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.03281854187026023</v>
+        <v>0.00245497512684234</v>
       </c>
       <c r="AD25" t="n">
-        <v>-0.01005041670419959</v>
+        <v>-0.09420128626165736</v>
       </c>
       <c r="AE25" t="n">
-        <v>-0.04123807359485987</v>
+        <v>-0.05271364846097093</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.03118765689066028</v>
+        <v>-0.04148763780068643</v>
       </c>
       <c r="AG25" t="n">
-        <v>49.01960784313725</v>
+        <v>26</v>
       </c>
       <c r="AH25" t="n">
-        <v>35.29411764705883</v>
+        <v>36</v>
       </c>
       <c r="AI25" t="b">
         <v>0</v>
@@ -3975,19 +3963,17 @@
         <v>1</v>
       </c>
       <c r="AN25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>2642.64</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO25" t="inlineStr"/>
       <c r="AP25" t="n">
-        <v>2553.68</v>
+        <v>347.03</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -4006,16 +3992,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>37.05882352941177</v>
+        <v>31.4</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -4032,70 +4018,70 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>6343000</v>
+        <v>6457000</v>
       </c>
       <c r="N26" t="n">
-        <v>114000</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>0.01797256818540123</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>3235</v>
+        <v>3145</v>
       </c>
       <c r="Q26" t="n">
-        <v>3235</v>
+        <v>3145</v>
       </c>
       <c r="R26" t="n">
-        <v>3941653</v>
+        <v>2509829</v>
       </c>
       <c r="S26" t="n">
-        <v>3256</v>
+        <v>3268</v>
       </c>
       <c r="T26" t="n">
+        <v>3393</v>
+      </c>
+      <c r="U26" t="n">
         <v>3406.5</v>
       </c>
-      <c r="U26" t="n">
-        <v>3416.25</v>
-      </c>
       <c r="V26" t="n">
-        <v>3140.579235839844</v>
+        <v>3153.231795247396</v>
       </c>
       <c r="W26" t="n">
-        <v>-36.53744038086506</v>
+        <v>-50.50759774913104</v>
       </c>
       <c r="X26" t="n">
-        <v>-9.472857701593977</v>
+        <v>-17.67980571110139</v>
       </c>
       <c r="Y26" t="n">
+        <v>-32.82779203802965</v>
+      </c>
+      <c r="Z26" t="n">
         <v>-27.06458267927109</v>
       </c>
-      <c r="Z26" t="n">
-        <v>-26.78327071353065</v>
-      </c>
       <c r="AA26" t="b">
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>-0.0568513119533528</v>
+        <v>-0.07906295754026349</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.3673071585049619</v>
+        <v>0.3181904556565121</v>
       </c>
       <c r="AD26" t="n">
-        <v>-0.0506415660559264</v>
+        <v>-0.04391100997107511</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.2932505430398418</v>
+        <v>0.2630218320686988</v>
       </c>
       <c r="AF26" t="n">
-        <v>-0.3438921090957682</v>
+        <v>-0.3069328420397739</v>
       </c>
       <c r="AG26" t="n">
-        <v>33.33333333333333</v>
+        <v>42</v>
       </c>
       <c r="AH26" t="n">
-        <v>86.27450980392157</v>
+        <v>88</v>
       </c>
       <c r="AI26" t="b">
         <v>0</v>
@@ -4116,26 +4102,26 @@
         <v>1</v>
       </c>
       <c r="AO26" t="n">
-        <v>3545.56</v>
+        <v>3516.11</v>
       </c>
       <c r="AP26" t="n">
-        <v>3595.53</v>
+        <v>3651.05</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>6271</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4144,7 +4130,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>35.68627450980392</v>
+        <v>31.4</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4153,24 +4139,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>23519000</v>
+        <v>2185000</v>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="K27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" t="b">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>23519000</v>
+        <v>2185000</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -4179,61 +4165,61 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>542</v>
+        <v>215</v>
       </c>
       <c r="Q27" t="n">
-        <v>542</v>
+        <v>215</v>
       </c>
       <c r="R27" t="n">
-        <v>34027010</v>
+        <v>2499080</v>
       </c>
       <c r="S27" t="n">
-        <v>547.8</v>
+        <v>224.1</v>
       </c>
       <c r="T27" t="n">
-        <v>586.95</v>
+        <v>232.35</v>
       </c>
       <c r="U27" t="n">
-        <v>587.35</v>
+        <v>233.1</v>
       </c>
       <c r="V27" t="n">
-        <v>569.9083333333333</v>
+        <v>212.9833333333333</v>
       </c>
       <c r="W27" t="n">
-        <v>-12.38723724009731</v>
+        <v>-2.461580220411093</v>
       </c>
       <c r="X27" t="n">
-        <v>1.141451916307924</v>
+        <v>0.9041521719129229</v>
       </c>
       <c r="Y27" t="n">
-        <v>-13.52868915640523</v>
+        <v>-3.365732392324016</v>
       </c>
       <c r="Z27" t="n">
-        <v>-14.87807752493863</v>
+        <v>-2.559680799197468</v>
       </c>
       <c r="AA27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>-0.01454545454545453</v>
+        <v>-0.06521739130434778</v>
       </c>
       <c r="AC27" t="n">
-        <v>-0.1557632398753894</v>
+        <v>0.1716621253405994</v>
       </c>
       <c r="AD27" t="n">
-        <v>-0.008335708648028128</v>
+        <v>-0.0300654437351594</v>
       </c>
       <c r="AE27" t="n">
-        <v>-0.2298198553405095</v>
+        <v>0.1164935017527862</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.2214841466924814</v>
+        <v>-0.1465589454879456</v>
       </c>
       <c r="AG27" t="n">
-        <v>52.94117647058824</v>
+        <v>48</v>
       </c>
       <c r="AH27" t="n">
-        <v>9.803921568627452</v>
+        <v>70</v>
       </c>
       <c r="AI27" t="b">
         <v>0</v>
@@ -4248,30 +4234,32 @@
         <v>0</v>
       </c>
       <c r="AM27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN27" t="b">
         <v>0</v>
       </c>
-      <c r="AO27" t="inlineStr"/>
+      <c r="AO27" t="n">
+        <v>253.27</v>
+      </c>
       <c r="AP27" t="n">
-        <v>604.3200000000001</v>
+        <v>246.26</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3376</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>新日興</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4280,7 +4268,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>35.68627450980392</v>
+        <v>31.2</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4289,15 +4277,15 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1000</v>
+        <v>1740000</v>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="K28" t="b">
         <v>0</v>
@@ -4306,7 +4294,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1000</v>
+        <v>1740000</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -4315,103 +4303,103 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>3710</v>
+        <v>172.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>3710</v>
+        <v>172.5</v>
       </c>
       <c r="R28" t="n">
-        <v>1277241</v>
+        <v>2336685</v>
       </c>
       <c r="S28" t="n">
-        <v>3691</v>
+        <v>176.5</v>
       </c>
       <c r="T28" t="n">
-        <v>3871</v>
+        <v>174.35</v>
       </c>
       <c r="U28" t="n">
-        <v>3862.5</v>
+        <v>174.575</v>
       </c>
       <c r="V28" t="n">
-        <v>3760.812365722656</v>
+        <v>183.8839558919271</v>
       </c>
       <c r="W28" t="n">
-        <v>-46.17859929668339</v>
+        <v>-0.3644799868444863</v>
       </c>
       <c r="X28" t="n">
-        <v>14.01799337294583</v>
+        <v>-1.569258623656947</v>
       </c>
       <c r="Y28" t="n">
-        <v>-60.19659266962921</v>
+        <v>1.204778636812461</v>
       </c>
       <c r="Z28" t="n">
-        <v>-67.17259305666136</v>
+        <v>1.99166939536115</v>
       </c>
       <c r="AA28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.04802259887005644</v>
+        <v>-0.02542372881355937</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.09809031415920377</v>
+        <v>-0.04438038309281866</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.05423234476748284</v>
+        <v>0.009728218755629015</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.02403369869408367</v>
+        <v>-0.09954900668063194</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.03019864607339917</v>
+        <v>0.1092772254362609</v>
       </c>
       <c r="AG28" t="n">
-        <v>72.54901960784314</v>
+        <v>62</v>
       </c>
       <c r="AH28" t="n">
-        <v>50.98039215686274</v>
+        <v>26</v>
       </c>
       <c r="AI28" t="b">
         <v>0</v>
       </c>
       <c r="AJ28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN28" t="b">
         <v>0</v>
       </c>
-      <c r="AO28" t="n">
-        <v>4392.64</v>
-      </c>
-      <c r="AP28" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
+      </c>
+      <c r="AP28" t="n">
+        <v>182.45</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4420,7 +4408,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>33.92156862745098</v>
+        <v>30.2</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4429,15 +4417,15 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2185000</v>
+        <v>1000</v>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="K29" t="b">
         <v>0</v>
@@ -4446,7 +4434,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>2185000</v>
+        <v>1000</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -4455,67 +4443,67 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>232</v>
+        <v>3495</v>
       </c>
       <c r="Q29" t="n">
-        <v>232</v>
+        <v>3495</v>
       </c>
       <c r="R29" t="n">
-        <v>3476575</v>
+        <v>1517390</v>
       </c>
       <c r="S29" t="n">
-        <v>226.9</v>
+        <v>3649</v>
       </c>
       <c r="T29" t="n">
-        <v>233.1</v>
+        <v>3862.5</v>
       </c>
       <c r="U29" t="n">
-        <v>232.975</v>
+        <v>3871</v>
       </c>
       <c r="V29" t="n">
-        <v>212.4583333333333</v>
+        <v>3761.842932128906</v>
       </c>
       <c r="W29" t="n">
-        <v>-0.8140955292035414</v>
+        <v>-74.50871135974103</v>
       </c>
       <c r="X29" t="n">
-        <v>1.745585269993927</v>
+        <v>-3.687347573591545</v>
       </c>
       <c r="Y29" t="n">
-        <v>-2.559680799197468</v>
+        <v>-70.82136378614948</v>
       </c>
       <c r="Z29" t="n">
-        <v>-3.519700087457216</v>
+        <v>-60.19659266962921</v>
       </c>
       <c r="AA29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.01089324618736387</v>
+        <v>-0.04638472032742158</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.2275132275132274</v>
+        <v>0.01801077608644075</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.01710299208479027</v>
+        <v>-0.0112327727582332</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.1534566120481073</v>
+        <v>-0.03715784750137252</v>
       </c>
       <c r="AF29" t="n">
-        <v>-0.1363536199633171</v>
+        <v>0.02592507474313932</v>
       </c>
       <c r="AG29" t="n">
-        <v>58.82352941176471</v>
+        <v>52</v>
       </c>
       <c r="AH29" t="n">
-        <v>74.50980392156863</v>
+        <v>46</v>
       </c>
       <c r="AI29" t="b">
         <v>0</v>
       </c>
       <c r="AJ29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="b">
         <v>0</v>
@@ -4524,34 +4512,30 @@
         <v>0</v>
       </c>
       <c r="AM29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN29" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>261.23</v>
-      </c>
-      <c r="AP29" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="AO29" t="inlineStr"/>
+      <c r="AP29" t="n">
+        <v>4101.84</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4560,7 +4544,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>32.74509803921568</v>
+        <v>29.8</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4569,15 +4553,15 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>5163000</v>
+        <v>1000</v>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="K30" t="b">
         <v>0</v>
@@ -4586,7 +4570,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>5163000</v>
+        <v>1000</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -4595,105 +4579,99 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>19.60000038146973</v>
+        <v>161</v>
       </c>
       <c r="Q30" t="n">
-        <v>19.60000038146973</v>
+        <v>161</v>
       </c>
       <c r="R30" t="n">
-        <v>40203403</v>
+        <v>6205059</v>
       </c>
       <c r="S30" t="n">
-        <v>19.5</v>
+        <v>163.7</v>
       </c>
       <c r="T30" t="n">
-        <v>19.08250007629395</v>
+        <v>175.55</v>
       </c>
       <c r="U30" t="n">
-        <v>19.04000005722046</v>
+        <v>176.1</v>
       </c>
       <c r="V30" t="n">
-        <v>19.06916675567627</v>
+        <v>161.3916666666667</v>
       </c>
       <c r="W30" t="n">
-        <v>0.1770843242964411</v>
+        <v>-3.188915133197838</v>
       </c>
       <c r="X30" t="n">
-        <v>0.1161067116436361</v>
+        <v>-0.1083930722634476</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.06097761265280496</v>
+        <v>-3.080522060934391</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.06917880632289054</v>
+        <v>-3.295402841218987</v>
       </c>
       <c r="AA30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.04533335367838531</v>
+        <v>-0.06395348837209303</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.02349873482524845</v>
+        <v>0.02547770700636942</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.05154309957581171</v>
+        <v>-0.02880154080290465</v>
       </c>
       <c r="AE30" t="n">
-        <v>-0.05055788063987166</v>
+        <v>-0.02969091658144385</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.1021009802156834</v>
+        <v>0.0008893757785392031</v>
       </c>
       <c r="AG30" t="n">
-        <v>68.62745098039215</v>
+        <v>50</v>
       </c>
       <c r="AH30" t="n">
-        <v>33.33333333333333</v>
+        <v>48</v>
       </c>
       <c r="AI30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN30" t="b">
         <v>0</v>
       </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
-      <c r="AP30" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+      <c r="AO30" t="inlineStr"/>
+      <c r="AP30" t="n">
+        <v>188.32</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4702,24 +4680,24 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>32.54901960784314</v>
+        <v>28.4</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>6331000</v>
+        <v>1000</v>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="K31" t="b">
         <v>0</v>
@@ -4728,70 +4706,70 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>6264000</v>
+        <v>1000</v>
       </c>
       <c r="N31" t="n">
-        <v>67000</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>0.01069604086845466</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1815</v>
+        <v>95.90000152587891</v>
       </c>
       <c r="Q31" t="n">
-        <v>1815</v>
+        <v>95.90000152587891</v>
       </c>
       <c r="R31" t="n">
-        <v>7762173</v>
+        <v>19257495</v>
       </c>
       <c r="S31" t="n">
-        <v>1944</v>
+        <v>101.1</v>
       </c>
       <c r="T31" t="n">
-        <v>1957</v>
+        <v>113.05</v>
       </c>
       <c r="U31" t="n">
-        <v>1959</v>
+        <v>113.4049999237061</v>
       </c>
       <c r="V31" t="n">
-        <v>2049.023126220703</v>
+        <v>96.2666665395101</v>
       </c>
       <c r="W31" t="n">
-        <v>-12.33909153930517</v>
+        <v>-2.826700879725209</v>
       </c>
       <c r="X31" t="n">
-        <v>8.455870150861198</v>
+        <v>1.187270859644502</v>
       </c>
       <c r="Y31" t="n">
-        <v>-20.79496169016637</v>
+        <v>-4.013971739369711</v>
       </c>
       <c r="Z31" t="n">
-        <v>-4.713179632014981</v>
+        <v>-3.93516862418446</v>
       </c>
       <c r="AA31" t="b">
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>-0.02156334231805934</v>
+        <v>-0.06893202402059317</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0.1759609156048944</v>
+        <v>0.0667408220040222</v>
       </c>
       <c r="AD31" t="n">
-        <v>-0.01535359642063294</v>
+        <v>-0.03378007645140479</v>
       </c>
       <c r="AE31" t="n">
-        <v>-0.2500175310700145</v>
+        <v>0.01157219841620893</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.2346639346493815</v>
+        <v>-0.04535227486761373</v>
       </c>
       <c r="AG31" t="n">
-        <v>47.05882352941176</v>
+        <v>44</v>
       </c>
       <c r="AH31" t="n">
-        <v>7.84313725490196</v>
+        <v>52</v>
       </c>
       <c r="AI31" t="b">
         <v>0</v>
@@ -4809,29 +4787,27 @@
         <v>0</v>
       </c>
       <c r="AN31" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>2050.95</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO31" t="inlineStr"/>
       <c r="AP31" t="n">
-        <v>1989.47</v>
+        <v>123.55</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4840,7 +4816,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>31.76470588235294</v>
+        <v>28.2</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4849,15 +4825,15 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>4328000</v>
+        <v>654000</v>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="K32" t="b">
         <v>0</v>
@@ -4866,7 +4842,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>4328000</v>
+        <v>654000</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -4875,67 +4851,67 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>4990</v>
+        <v>438.5</v>
       </c>
       <c r="Q32" t="n">
-        <v>4990</v>
+        <v>438.5</v>
       </c>
       <c r="R32" t="n">
-        <v>2719797</v>
+        <v>17463211</v>
       </c>
       <c r="S32" t="n">
-        <v>5069</v>
+        <v>469.2</v>
       </c>
       <c r="T32" t="n">
-        <v>5302.25</v>
+        <v>502.3</v>
       </c>
       <c r="U32" t="n">
-        <v>5297.25</v>
+        <v>504.95</v>
       </c>
       <c r="V32" t="n">
-        <v>5325.460229492188</v>
+        <v>458.5333333333334</v>
       </c>
       <c r="W32" t="n">
-        <v>-85.66607422324341</v>
+        <v>-13.39343952572915</v>
       </c>
       <c r="X32" t="n">
-        <v>15.62243463598849</v>
+        <v>-4.426963086161363</v>
       </c>
       <c r="Y32" t="n">
-        <v>-101.2885088592319</v>
+        <v>-8.966476439567787</v>
       </c>
       <c r="Z32" t="n">
-        <v>-100.9099230975565</v>
+        <v>-6.768474826993417</v>
       </c>
       <c r="AA32" t="b">
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.0204498977505112</v>
+        <v>-0.1078331637843337</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.05421357080041989</v>
+        <v>0.1819407008086253</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.0266596436479376</v>
+        <v>-0.07268121621514534</v>
       </c>
       <c r="AE32" t="n">
-        <v>-0.01984304466470022</v>
+        <v>0.1267720772208121</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.04650268831263782</v>
+        <v>-0.1994532934359574</v>
       </c>
       <c r="AG32" t="n">
-        <v>62.74509803921568</v>
+        <v>36</v>
       </c>
       <c r="AH32" t="n">
-        <v>41.17647058823529</v>
+        <v>74</v>
       </c>
       <c r="AI32" t="b">
         <v>0</v>
       </c>
       <c r="AJ32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="b">
         <v>0</v>
@@ -4950,26 +4926,24 @@
         <v>0</v>
       </c>
       <c r="AO32" t="inlineStr"/>
-      <c r="AP32" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+      <c r="AP32" t="n">
+        <v>558.66</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4978,7 +4952,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>30.19607843137255</v>
+        <v>28.2</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4987,15 +4961,15 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="K33" t="b">
         <v>0</v>
@@ -5004,7 +4978,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
@@ -5013,61 +4987,61 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>6170</v>
+        <v>153.5</v>
       </c>
       <c r="Q33" t="n">
-        <v>6170</v>
+        <v>153.5</v>
       </c>
       <c r="R33" t="n">
-        <v>2653180</v>
+        <v>15925848</v>
       </c>
       <c r="S33" t="n">
-        <v>6279</v>
+        <v>156.4</v>
       </c>
       <c r="T33" t="n">
-        <v>6483.25</v>
+        <v>168.1</v>
       </c>
       <c r="U33" t="n">
-        <v>6496.25</v>
+        <v>168.825</v>
       </c>
       <c r="V33" t="n">
-        <v>5890.061966959635</v>
+        <v>151.95</v>
       </c>
       <c r="W33" t="n">
-        <v>-74.43034905392324</v>
+        <v>-3.466013085611394</v>
       </c>
       <c r="X33" t="n">
-        <v>42.30251137507694</v>
+        <v>-1.035168189013058</v>
       </c>
       <c r="Y33" t="n">
-        <v>-116.7328604290002</v>
+        <v>-2.430844896598336</v>
       </c>
       <c r="Z33" t="n">
-        <v>-117.9947284158227</v>
+        <v>-2.574592254334981</v>
       </c>
       <c r="AA33" t="b">
         <v>1</v>
       </c>
       <c r="AB33" t="n">
-        <v>-0.04043545878693622</v>
+        <v>-0.08630952380952384</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.5883562242198632</v>
+        <v>0.1204379562043796</v>
       </c>
       <c r="AD33" t="n">
-        <v>-0.03422571288950982</v>
+        <v>-0.05115757624033546</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.5142996087547431</v>
+        <v>0.06526933261656631</v>
       </c>
       <c r="AF33" t="n">
-        <v>-0.5485253216442529</v>
+        <v>-0.1164269088569018</v>
       </c>
       <c r="AG33" t="n">
-        <v>41.17647058823529</v>
+        <v>40</v>
       </c>
       <c r="AH33" t="n">
-        <v>90.19607843137256</v>
+        <v>62</v>
       </c>
       <c r="AI33" t="b">
         <v>0</v>
@@ -5087,25 +5061,27 @@
       <c r="AN33" t="b">
         <v>0</v>
       </c>
-      <c r="AO33" t="inlineStr"/>
+      <c r="AO33" t="n">
+        <v>181.13</v>
+      </c>
       <c r="AP33" t="n">
-        <v>6729.74</v>
+        <v>186.37</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5114,7 +5090,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>30.19607843137255</v>
+        <v>27.8</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5123,24 +5099,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>7582000</v>
+        <v>6331000</v>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34" t="b">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>7582000</v>
+        <v>6331000</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -5149,61 +5125,61 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1625</v>
+        <v>1775</v>
       </c>
       <c r="Q34" t="n">
-        <v>1625</v>
+        <v>1775</v>
       </c>
       <c r="R34" t="n">
-        <v>11289452</v>
+        <v>3474156</v>
       </c>
       <c r="S34" t="n">
-        <v>1627</v>
+        <v>1909</v>
       </c>
       <c r="T34" t="n">
-        <v>1835.25</v>
+        <v>1953.75</v>
       </c>
       <c r="U34" t="n">
-        <v>1840.75</v>
+        <v>1957</v>
       </c>
       <c r="V34" t="n">
-        <v>1766.833333333333</v>
+        <v>2041.566318766276</v>
       </c>
       <c r="W34" t="n">
-        <v>-64.48021579978013</v>
+        <v>-31.191327043505</v>
       </c>
       <c r="X34" t="n">
-        <v>-24.18486562490595</v>
+        <v>0.5264307119879588</v>
       </c>
       <c r="Y34" t="n">
-        <v>-40.29535017487417</v>
+        <v>-31.71775775549296</v>
       </c>
       <c r="Z34" t="n">
-        <v>-46.97600485237267</v>
+        <v>-20.79496169016637</v>
       </c>
       <c r="AA34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>-0.06340057636887608</v>
+        <v>-0.03532608695652173</v>
       </c>
       <c r="AC34" t="n">
-        <v>-0.08963585434173671</v>
+        <v>-0.2013169306551642</v>
       </c>
       <c r="AD34" t="n">
-        <v>-0.05719083047144968</v>
+        <v>-0.0001741393873333497</v>
       </c>
       <c r="AE34" t="n">
-        <v>-0.1636924698068568</v>
+        <v>-0.2564855542429775</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.1065016393354071</v>
+        <v>0.2563114148556441</v>
       </c>
       <c r="AG34" t="n">
-        <v>31.37254901960784</v>
+        <v>56.00000000000001</v>
       </c>
       <c r="AH34" t="n">
-        <v>19.6078431372549</v>
+        <v>10</v>
       </c>
       <c r="AI34" t="b">
         <v>0</v>
@@ -5218,30 +5194,30 @@
         <v>0</v>
       </c>
       <c r="AM34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="b">
         <v>0</v>
       </c>
       <c r="AO34" t="inlineStr"/>
       <c r="AP34" t="n">
-        <v>2096.32</v>
+        <v>2103.16</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5250,7 +5226,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>30</v>
+        <v>27.2</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5259,15 +5235,15 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>654000</v>
+        <v>1000</v>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="K35" t="b">
         <v>0</v>
@@ -5276,7 +5252,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>654000</v>
+        <v>1000</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -5285,61 +5261,61 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>482</v>
+        <v>322</v>
       </c>
       <c r="Q35" t="n">
-        <v>482</v>
+        <v>322</v>
       </c>
       <c r="R35" t="n">
-        <v>15872872</v>
+        <v>8624935</v>
       </c>
       <c r="S35" t="n">
-        <v>473.8</v>
+        <v>321.5</v>
       </c>
       <c r="T35" t="n">
-        <v>504.95</v>
+        <v>328.75</v>
       </c>
       <c r="U35" t="n">
-        <v>505.825</v>
+        <v>329.875</v>
       </c>
       <c r="V35" t="n">
-        <v>457.4083333333334</v>
+        <v>326.5583333333333</v>
       </c>
       <c r="W35" t="n">
-        <v>-8.953818803262834</v>
+        <v>-3.05164815738425</v>
       </c>
       <c r="X35" t="n">
-        <v>-2.185343976269416</v>
+        <v>-3.324663606940946</v>
       </c>
       <c r="Y35" t="n">
-        <v>-6.768474826993417</v>
+        <v>0.2730154495566963</v>
       </c>
       <c r="Z35" t="n">
-        <v>-8.710291460057888</v>
+        <v>0.1186949931720043</v>
       </c>
       <c r="AA35" t="b">
         <v>1</v>
       </c>
       <c r="AB35" t="n">
-        <v>-0.03503503503503502</v>
+        <v>-0.06531204644412192</v>
       </c>
       <c r="AC35" t="n">
-        <v>0.3133514986376023</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>-0.02882528913760862</v>
+        <v>-0.03016009887493354</v>
       </c>
       <c r="AE35" t="n">
-        <v>0.2392948831724822</v>
+        <v>-0.05516862358781327</v>
       </c>
       <c r="AF35" t="n">
-        <v>-0.2681201723100908</v>
+        <v>0.02500852471287973</v>
       </c>
       <c r="AG35" t="n">
-        <v>43.13725490196079</v>
+        <v>46</v>
       </c>
       <c r="AH35" t="n">
-        <v>82.35294117647058</v>
+        <v>34</v>
       </c>
       <c r="AI35" t="b">
         <v>0</v>
@@ -5348,38 +5324,40 @@
         <v>0</v>
       </c>
       <c r="AK35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM35" t="b">
         <v>1</v>
       </c>
       <c r="AN35" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>558.16</v>
+        <v>0</v>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP35" t="n">
-        <v>515.66</v>
+        <v>349.11</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5388,7 +5366,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>26.66666666666667</v>
+        <v>26.6</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5397,24 +5375,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1000</v>
+        <v>7582000</v>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="K36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" t="b">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1000</v>
+        <v>7582000</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -5423,61 +5401,61 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>166.5</v>
+        <v>1560</v>
       </c>
       <c r="Q36" t="n">
-        <v>166.5</v>
+        <v>1560</v>
       </c>
       <c r="R36" t="n">
-        <v>8984913</v>
+        <v>10096638</v>
       </c>
       <c r="S36" t="n">
-        <v>163.8</v>
+        <v>1613</v>
       </c>
       <c r="T36" t="n">
-        <v>176.1</v>
+        <v>1819.5</v>
       </c>
       <c r="U36" t="n">
-        <v>176.375</v>
+        <v>1835.25</v>
       </c>
       <c r="V36" t="n">
-        <v>161.325</v>
+        <v>1763.583333333333</v>
       </c>
       <c r="W36" t="n">
-        <v>-2.633665398248837</v>
+        <v>-72.45623813198699</v>
       </c>
       <c r="X36" t="n">
-        <v>0.66173744297015</v>
+        <v>-33.83914012632216</v>
       </c>
       <c r="Y36" t="n">
-        <v>-3.295402841218987</v>
+        <v>-38.61709800566483</v>
       </c>
       <c r="Z36" t="n">
-        <v>-4.105993563535058</v>
+        <v>-40.29535017487417</v>
       </c>
       <c r="AA36" t="b">
         <v>1</v>
       </c>
       <c r="AB36" t="n">
-        <v>-0.03197674418604646</v>
+        <v>-0.168</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.06050955414012749</v>
+        <v>-0.1111111111111112</v>
       </c>
       <c r="AD36" t="n">
-        <v>-0.02576699828862006</v>
+        <v>-0.1328480524308117</v>
       </c>
       <c r="AE36" t="n">
-        <v>-0.01354706132499262</v>
+        <v>-0.1662797346989244</v>
       </c>
       <c r="AF36" t="n">
-        <v>-0.01221993696362744</v>
+        <v>0.03343168226811277</v>
       </c>
       <c r="AG36" t="n">
-        <v>45.09803921568628</v>
+        <v>16</v>
       </c>
       <c r="AH36" t="n">
-        <v>43.13725490196079</v>
+        <v>18</v>
       </c>
       <c r="AI36" t="b">
         <v>0</v>
@@ -5499,23 +5477,23 @@
       </c>
       <c r="AO36" t="inlineStr"/>
       <c r="AP36" t="n">
-        <v>182.11</v>
+        <v>2173.16</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5524,7 +5502,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>25.49019607843137</v>
+        <v>25.2</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5533,15 +5511,15 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>5000</v>
+        <v>470000</v>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K37" t="b">
         <v>0</v>
@@ -5550,7 +5528,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>5000</v>
+        <v>470000</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -5559,61 +5537,61 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>159</v>
+        <v>3065</v>
       </c>
       <c r="Q37" t="n">
-        <v>159</v>
+        <v>3065</v>
       </c>
       <c r="R37" t="n">
-        <v>7682625</v>
+        <v>730172</v>
       </c>
       <c r="S37" t="n">
-        <v>156.8</v>
+        <v>3137</v>
       </c>
       <c r="T37" t="n">
-        <v>168.825</v>
+        <v>3188.5</v>
       </c>
       <c r="U37" t="n">
-        <v>169.3</v>
+        <v>3209.5</v>
       </c>
       <c r="V37" t="n">
-        <v>151.675</v>
+        <v>3041.75</v>
       </c>
       <c r="W37" t="n">
-        <v>-3.002049219198454</v>
+        <v>-28.07613189820859</v>
       </c>
       <c r="X37" t="n">
-        <v>-0.4274569648634736</v>
+        <v>-23.61539468157735</v>
       </c>
       <c r="Y37" t="n">
-        <v>-2.574592254334981</v>
+        <v>-4.460737216631241</v>
       </c>
       <c r="Z37" t="n">
-        <v>-3.323862253314316</v>
+        <v>3.008477254227724</v>
       </c>
       <c r="AA37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>-0.05637982195845692</v>
+        <v>-0.1205164992826399</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.1357142857142857</v>
+        <v>0.1522556390977443</v>
       </c>
       <c r="AD37" t="n">
-        <v>-0.05017007606103052</v>
+        <v>-0.08536455171345148</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.06165767024916557</v>
+        <v>0.09708701550993104</v>
       </c>
       <c r="AF37" t="n">
-        <v>-0.1118277463101961</v>
+        <v>-0.1824515672233825</v>
       </c>
       <c r="AG37" t="n">
-        <v>35.29411764705883</v>
+        <v>28</v>
       </c>
       <c r="AH37" t="n">
-        <v>60.78431372549019</v>
+        <v>68</v>
       </c>
       <c r="AI37" t="b">
         <v>0</v>
@@ -5628,32 +5606,32 @@
         <v>0</v>
       </c>
       <c r="AM37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO37" t="n">
-        <v>188.26</v>
+        <v>3120.17</v>
       </c>
       <c r="AP37" t="n">
-        <v>178.34</v>
+        <v>3830</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5662,7 +5640,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>23.52941176470588</v>
+        <v>24.8</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5671,15 +5649,15 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1000</v>
+        <v>4827000</v>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="n">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="K38" t="b">
         <v>0</v>
@@ -5688,7 +5666,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1000</v>
+        <v>4827000</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -5697,61 +5675,61 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>328.5</v>
+        <v>246.5</v>
       </c>
       <c r="Q38" t="n">
-        <v>328.5</v>
+        <v>246.5</v>
       </c>
       <c r="R38" t="n">
-        <v>10332339</v>
+        <v>23017388</v>
       </c>
       <c r="S38" t="n">
-        <v>320.4</v>
+        <v>255</v>
       </c>
       <c r="T38" t="n">
-        <v>329.875</v>
+        <v>255.275</v>
       </c>
       <c r="U38" t="n">
-        <v>330.6</v>
+        <v>257.15</v>
       </c>
       <c r="V38" t="n">
-        <v>326.5583333333333</v>
+        <v>230.4416666666667</v>
       </c>
       <c r="W38" t="n">
-        <v>-3.274222476158116</v>
+        <v>1.643087687605117</v>
       </c>
       <c r="X38" t="n">
-        <v>-3.39291746933012</v>
+        <v>4.282222694556783</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.1186949931720043</v>
+        <v>-2.639135006951665</v>
       </c>
       <c r="Z38" t="n">
-        <v>-1.101275452612911</v>
+        <v>-1.451056549604886</v>
       </c>
       <c r="AA38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>-0.04227405247813409</v>
+        <v>-0.1320422535211268</v>
       </c>
       <c r="AC38" t="n">
-        <v>0.001524390243902385</v>
+        <v>0.1966019417475728</v>
       </c>
       <c r="AD38" t="n">
-        <v>-0.03606430658070769</v>
+        <v>-0.09689030595193837</v>
       </c>
       <c r="AE38" t="n">
-        <v>-0.07253222522121772</v>
+        <v>0.1414333181597596</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.03646791864051002</v>
+        <v>-0.2383236241116979</v>
       </c>
       <c r="AG38" t="n">
-        <v>39.21568627450981</v>
+        <v>24</v>
       </c>
       <c r="AH38" t="n">
-        <v>29.41176470588236</v>
+        <v>76</v>
       </c>
       <c r="AI38" t="b">
         <v>0</v>
@@ -5760,30 +5738,28 @@
         <v>0</v>
       </c>
       <c r="AK38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>276.57</v>
       </c>
       <c r="AP38" t="n">
-        <v>345.95</v>
+        <v>285.74</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5802,7 +5778,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>23.33333333333334</v>
+        <v>24.4</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5811,7 +5787,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -5837,61 +5813,61 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>128</v>
+        <v>125.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>128</v>
+        <v>125.5</v>
       </c>
       <c r="R39" t="n">
-        <v>73759992</v>
+        <v>88183899</v>
       </c>
       <c r="S39" t="n">
-        <v>130.6</v>
+        <v>129</v>
       </c>
       <c r="T39" t="n">
+        <v>145.425</v>
+      </c>
+      <c r="U39" t="n">
         <v>147</v>
       </c>
-      <c r="U39" t="n">
-        <v>148.4</v>
-      </c>
       <c r="V39" t="n">
-        <v>133.425</v>
+        <v>133.4166666666667</v>
       </c>
       <c r="W39" t="n">
-        <v>-5.28985075468276</v>
+        <v>-5.716641903854367</v>
       </c>
       <c r="X39" t="n">
-        <v>-2.191593115487556</v>
+        <v>-2.896602873160918</v>
       </c>
       <c r="Y39" t="n">
+        <v>-2.820039030693448</v>
+      </c>
+      <c r="Z39" t="n">
         <v>-3.098257639195204</v>
       </c>
-      <c r="Z39" t="n">
-        <v>-3.468361609846421</v>
-      </c>
       <c r="AA39" t="b">
         <v>1</v>
       </c>
       <c r="AB39" t="n">
-        <v>-0.1794871794871795</v>
+        <v>-0.2006369426751592</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>-0.003968253968253954</v>
       </c>
       <c r="AD39" t="n">
-        <v>-0.1732774335897531</v>
+        <v>-0.1654849951059708</v>
       </c>
       <c r="AE39" t="n">
-        <v>-0.0740566154651201</v>
+        <v>-0.05913687755606722</v>
       </c>
       <c r="AF39" t="n">
-        <v>-0.09922081812463301</v>
+        <v>-0.1063481175499036</v>
       </c>
       <c r="AG39" t="n">
-        <v>5.88235294117647</v>
+        <v>4</v>
       </c>
       <c r="AH39" t="n">
-        <v>27.45098039215686</v>
+        <v>32</v>
       </c>
       <c r="AI39" t="b">
         <v>0</v>
@@ -5913,23 +5889,23 @@
       </c>
       <c r="AO39" t="inlineStr"/>
       <c r="AP39" t="n">
-        <v>177</v>
+        <v>180.97</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5938,7 +5914,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>19.41176470588236</v>
+        <v>21.6</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5947,15 +5923,15 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>5143000</v>
+        <v>2504000</v>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="K40" t="b">
         <v>0</v>
@@ -5964,7 +5940,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>5143000</v>
+        <v>2504000</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -5973,61 +5949,61 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>4140</v>
+        <v>4890</v>
       </c>
       <c r="Q40" t="n">
-        <v>4140</v>
+        <v>4890</v>
       </c>
       <c r="R40" t="n">
-        <v>9026097</v>
+        <v>818727</v>
       </c>
       <c r="S40" t="n">
-        <v>4182</v>
+        <v>5047</v>
       </c>
       <c r="T40" t="n">
-        <v>4728.25</v>
+        <v>5390.75</v>
       </c>
       <c r="U40" t="n">
-        <v>4756.75</v>
+        <v>5421</v>
       </c>
       <c r="V40" t="n">
-        <v>4291.5</v>
+        <v>5527.333333333333</v>
       </c>
       <c r="W40" t="n">
-        <v>-167.6489535656037</v>
+        <v>-146.3291353295526</v>
       </c>
       <c r="X40" t="n">
-        <v>-77.32044722055224</v>
+        <v>-46.81895392914208</v>
       </c>
       <c r="Y40" t="n">
-        <v>-90.32850634505149</v>
+        <v>-99.51018140041054</v>
       </c>
       <c r="Z40" t="n">
-        <v>-104.4194411717543</v>
+        <v>-95.17712545095225</v>
       </c>
       <c r="AA40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>-0.1210191082802548</v>
+        <v>-0.1101000909918107</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.1040000000000001</v>
+        <v>-0.1451048951048951</v>
       </c>
       <c r="AD40" t="n">
-        <v>-0.1148093623828284</v>
+        <v>-0.07494814342262235</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.02994338453487999</v>
+        <v>-0.2002735186927084</v>
       </c>
       <c r="AF40" t="n">
-        <v>-0.1447527469177083</v>
+        <v>0.125325375270086</v>
       </c>
       <c r="AG40" t="n">
-        <v>17.64705882352941</v>
+        <v>34</v>
       </c>
       <c r="AH40" t="n">
-        <v>52.94117647058824</v>
+        <v>14</v>
       </c>
       <c r="AI40" t="b">
         <v>0</v>
@@ -6042,20 +6018,20 @@
         <v>0</v>
       </c>
       <c r="AM40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN40" t="b">
         <v>0</v>
       </c>
       <c r="AO40" t="inlineStr"/>
       <c r="AP40" t="n">
-        <v>5629.21</v>
+        <v>5872.11</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6074,7 +6050,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>18.82352941176471</v>
+        <v>20.4</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -6083,7 +6059,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -6091,7 +6067,7 @@
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K41" t="b">
         <v>0</v>
@@ -6109,61 +6085,61 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>880</v>
+        <v>826</v>
       </c>
       <c r="Q41" t="n">
-        <v>880</v>
+        <v>826</v>
       </c>
       <c r="R41" t="n">
-        <v>8859917</v>
+        <v>10475522</v>
       </c>
       <c r="S41" t="n">
-        <v>886.2</v>
+        <v>866.8</v>
       </c>
       <c r="T41" t="n">
+        <v>1013.05</v>
+      </c>
+      <c r="U41" t="n">
         <v>1018.3</v>
       </c>
-      <c r="U41" t="n">
-        <v>1021.5</v>
-      </c>
       <c r="V41" t="n">
-        <v>965.7666666666667</v>
+        <v>961.7833333333333</v>
       </c>
       <c r="W41" t="n">
-        <v>-43.16509068690038</v>
+        <v>-50.72161287392692</v>
       </c>
       <c r="X41" t="n">
-        <v>-6.995547830428174</v>
+        <v>-15.74076083912792</v>
       </c>
       <c r="Y41" t="n">
+        <v>-34.98085203479899</v>
+      </c>
+      <c r="Z41" t="n">
         <v>-36.16954285647221</v>
       </c>
-      <c r="Z41" t="n">
-        <v>-41.41892002553749</v>
-      </c>
       <c r="AA41" t="b">
         <v>1</v>
       </c>
       <c r="AB41" t="n">
-        <v>-0.06779661016949157</v>
+        <v>-0.1127819548872181</v>
       </c>
       <c r="AC41" t="n">
-        <v>-0.1456310679611651</v>
+        <v>-0.2244131455399061</v>
       </c>
       <c r="AD41" t="n">
-        <v>-0.06158686427206517</v>
+        <v>-0.07763000731802971</v>
       </c>
       <c r="AE41" t="n">
-        <v>-0.2196876834262852</v>
+        <v>-0.2795817691277194</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.15810081915422</v>
+        <v>0.2019517618096897</v>
       </c>
       <c r="AG41" t="n">
-        <v>29.41176470588236</v>
+        <v>32</v>
       </c>
       <c r="AH41" t="n">
-        <v>11.76470588235294</v>
+        <v>8</v>
       </c>
       <c r="AI41" t="b">
         <v>0</v>
@@ -6185,23 +6161,23 @@
       </c>
       <c r="AO41" t="inlineStr"/>
       <c r="AP41" t="n">
-        <v>1076.58</v>
+        <v>1167.89</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6210,7 +6186,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>18.43137254901961</v>
+        <v>19.6</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6219,7 +6195,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -6227,7 +6203,7 @@
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="K42" t="b">
         <v>0</v>
@@ -6245,61 +6221,61 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>527</v>
+        <v>1100</v>
       </c>
       <c r="Q42" t="n">
-        <v>527</v>
+        <v>1100</v>
       </c>
       <c r="R42" t="n">
-        <v>213323</v>
+        <v>604282</v>
       </c>
       <c r="S42" t="n">
-        <v>531.2</v>
+        <v>1130</v>
       </c>
       <c r="T42" t="n">
-        <v>557.55</v>
+        <v>1182.75</v>
       </c>
       <c r="U42" t="n">
-        <v>559.6</v>
+        <v>1189.75</v>
       </c>
       <c r="V42" t="n">
-        <v>563.167025756836</v>
+        <v>1329.833333333333</v>
       </c>
       <c r="W42" t="n">
-        <v>-9.661311116363549</v>
+        <v>-33.6205793875979</v>
       </c>
       <c r="X42" t="n">
-        <v>-5.16907811614728</v>
+        <v>-29.97258828741357</v>
       </c>
       <c r="Y42" t="n">
-        <v>-4.492233000216269</v>
+        <v>-3.647991100184328</v>
       </c>
       <c r="Z42" t="n">
-        <v>-5.040022501139054</v>
+        <v>-2.192118040303779</v>
       </c>
       <c r="AA42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>-0.07218309859154926</v>
+        <v>-0.1129032258064516</v>
       </c>
       <c r="AC42" t="n">
-        <v>-0.1241128140059693</v>
+        <v>-0.2361111111111112</v>
       </c>
       <c r="AD42" t="n">
-        <v>-0.06597335269412286</v>
+        <v>-0.07775127823726324</v>
       </c>
       <c r="AE42" t="n">
-        <v>-0.1981694294710894</v>
+        <v>-0.2912797346989244</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.1321960767769665</v>
+        <v>0.2135284564616612</v>
       </c>
       <c r="AG42" t="n">
-        <v>27.45098039215686</v>
+        <v>30</v>
       </c>
       <c r="AH42" t="n">
-        <v>13.72549019607843</v>
+        <v>6</v>
       </c>
       <c r="AI42" t="b">
         <v>0</v>
@@ -6314,32 +6290,32 @@
         <v>0</v>
       </c>
       <c r="AM42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN42" t="b">
         <v>1</v>
       </c>
       <c r="AO42" t="n">
-        <v>577.59</v>
+        <v>1141.8</v>
       </c>
       <c r="AP42" t="n">
-        <v>599.16</v>
+        <v>1347.11</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6348,7 +6324,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>17.45098039215686</v>
+        <v>19</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6357,15 +6333,15 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>201900</v>
+        <v>3281561</v>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="K43" t="b">
         <v>0</v>
@@ -6374,7 +6350,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>201900</v>
+        <v>3281561</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -6383,61 +6359,61 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>16515</v>
+        <v>1840</v>
       </c>
       <c r="Q43" t="n">
-        <v>16515</v>
+        <v>1840</v>
       </c>
       <c r="R43" t="n">
-        <v>276775</v>
+        <v>4704079</v>
       </c>
       <c r="S43" t="n">
-        <v>16164</v>
+        <v>1875</v>
       </c>
       <c r="T43" t="n">
-        <v>18198.5</v>
+        <v>2075.25</v>
       </c>
       <c r="U43" t="n">
-        <v>18337.25</v>
+        <v>2090.75</v>
       </c>
       <c r="V43" t="n">
-        <v>17132.83333333333</v>
+        <v>2142.478466796875</v>
       </c>
       <c r="W43" t="n">
-        <v>-647.3036676512056</v>
+        <v>-88.52281493870146</v>
       </c>
       <c r="X43" t="n">
-        <v>-413.3065101736765</v>
+        <v>-59.00672060392436</v>
       </c>
       <c r="Y43" t="n">
-        <v>-233.9971574775291</v>
+        <v>-29.51609433477709</v>
       </c>
       <c r="Z43" t="n">
-        <v>-342.2042943370795</v>
+        <v>-31.17828486980208</v>
       </c>
       <c r="AA43" t="b">
         <v>1</v>
       </c>
       <c r="AB43" t="n">
-        <v>-0.1438569206842923</v>
+        <v>-0.1441860465116279</v>
       </c>
       <c r="AC43" t="n">
-        <v>0.1211812627291242</v>
+        <v>-0.04467501617741476</v>
       </c>
       <c r="AD43" t="n">
-        <v>-0.1376471747868659</v>
+        <v>-0.1090340989424395</v>
       </c>
       <c r="AE43" t="n">
-        <v>0.04712464726400412</v>
+        <v>-0.09984363976522803</v>
       </c>
       <c r="AF43" t="n">
-        <v>-0.1847718220508701</v>
+        <v>-0.009190459177211507</v>
       </c>
       <c r="AG43" t="n">
-        <v>9.803921568627452</v>
+        <v>22</v>
       </c>
       <c r="AH43" t="n">
-        <v>56.86274509803921</v>
+        <v>24</v>
       </c>
       <c r="AI43" t="b">
         <v>0</v>
@@ -6455,29 +6431,29 @@
         <v>1</v>
       </c>
       <c r="AN43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO43" t="n">
-        <v>19157.4</v>
+        <v>2174.88</v>
       </c>
       <c r="AP43" t="n">
-        <v>21592.11</v>
+        <v>2362.63</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6486,7 +6462,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>16.86274509803922</v>
+        <v>18.8</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6495,15 +6471,15 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>1000</v>
+        <v>201900</v>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="K44" t="b">
         <v>0</v>
@@ -6512,7 +6488,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>1000</v>
+        <v>201900</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
@@ -6521,61 +6497,61 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>1120</v>
+        <v>16010</v>
       </c>
       <c r="Q44" t="n">
-        <v>1120</v>
+        <v>16010</v>
       </c>
       <c r="R44" t="n">
-        <v>1094055</v>
+        <v>257879</v>
       </c>
       <c r="S44" t="n">
-        <v>1141</v>
+        <v>16177</v>
       </c>
       <c r="T44" t="n">
-        <v>1189.75</v>
+        <v>18008</v>
       </c>
       <c r="U44" t="n">
-        <v>1194.75</v>
+        <v>18198.5</v>
       </c>
       <c r="V44" t="n">
-        <v>1335.5</v>
+        <v>17154.75</v>
       </c>
       <c r="W44" t="n">
-        <v>-31.25270855267127</v>
+        <v>-653.0660529011802</v>
       </c>
       <c r="X44" t="n">
-        <v>-29.06059051236749</v>
+        <v>-461.2584187191773</v>
       </c>
       <c r="Y44" t="n">
-        <v>-2.192118040303779</v>
+        <v>-191.8076341820029</v>
       </c>
       <c r="Z44" t="n">
-        <v>-1.413309072979864</v>
+        <v>-233.9971574775291</v>
       </c>
       <c r="AA44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB44" t="n">
-        <v>-0.08196721311475408</v>
+        <v>-0.1922300706357215</v>
       </c>
       <c r="AC44" t="n">
-        <v>-0.2140350877192982</v>
+        <v>0.08948621980265403</v>
       </c>
       <c r="AD44" t="n">
-        <v>-0.07575746721732768</v>
+        <v>-0.1570781230665331</v>
       </c>
       <c r="AE44" t="n">
-        <v>-0.2880917031844183</v>
+        <v>0.03431759621484076</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.2123342359670907</v>
+        <v>-0.1913957192813739</v>
       </c>
       <c r="AG44" t="n">
-        <v>25.49019607843137</v>
+        <v>10</v>
       </c>
       <c r="AH44" t="n">
-        <v>3.92156862745098</v>
+        <v>57.99999999999999</v>
       </c>
       <c r="AI44" t="b">
         <v>0</v>
@@ -6590,32 +6566,32 @@
         <v>0</v>
       </c>
       <c r="AM44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN44" t="b">
         <v>1</v>
       </c>
       <c r="AO44" t="n">
-        <v>1146.88</v>
+        <v>18187.36</v>
       </c>
       <c r="AP44" t="n">
-        <v>1313.42</v>
+        <v>23008.16</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6624,7 +6600,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>16.47058823529412</v>
+        <v>17.8</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6633,15 +6609,15 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>2887848</v>
+        <v>5143000</v>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K45" t="b">
         <v>0</v>
@@ -6650,7 +6626,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>2887848</v>
+        <v>5143000</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
@@ -6659,61 +6635,61 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>1950</v>
+        <v>4010</v>
       </c>
       <c r="Q45" t="n">
-        <v>1950</v>
+        <v>4010</v>
       </c>
       <c r="R45" t="n">
-        <v>2688491</v>
+        <v>6932946</v>
       </c>
       <c r="S45" t="n">
-        <v>1976</v>
+        <v>4151</v>
       </c>
       <c r="T45" t="n">
-        <v>2278.75</v>
+        <v>4678.25</v>
       </c>
       <c r="U45" t="n">
-        <v>2291.75</v>
+        <v>4728.25</v>
       </c>
       <c r="V45" t="n">
-        <v>2178.166666666667</v>
+        <v>4297</v>
       </c>
       <c r="W45" t="n">
-        <v>-90.86529070863844</v>
+        <v>-183.8243712372605</v>
       </c>
       <c r="X45" t="n">
-        <v>-28.45091123933666</v>
+        <v>-98.6212320238939</v>
       </c>
       <c r="Y45" t="n">
-        <v>-62.41437946930179</v>
+        <v>-85.2031392133666</v>
       </c>
       <c r="Z45" t="n">
-        <v>-70.43431550121541</v>
+        <v>-90.32850634505149</v>
       </c>
       <c r="AA45" t="b">
         <v>1</v>
       </c>
       <c r="AB45" t="n">
-        <v>-0.1176470588235294</v>
+        <v>-0.1996007984031936</v>
       </c>
       <c r="AC45" t="n">
-        <v>-0.1156462585034014</v>
+        <v>0.08967391304347827</v>
       </c>
       <c r="AD45" t="n">
-        <v>-0.111437312926103</v>
+        <v>-0.1644488508340052</v>
       </c>
       <c r="AE45" t="n">
-        <v>-0.1897028739685215</v>
+        <v>0.034505289455665</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.07826556104241844</v>
+        <v>-0.1989541402896702</v>
       </c>
       <c r="AG45" t="n">
-        <v>19.6078431372549</v>
+        <v>6</v>
       </c>
       <c r="AH45" t="n">
-        <v>17.64705882352941</v>
+        <v>60</v>
       </c>
       <c r="AI45" t="b">
         <v>0</v>
@@ -6735,23 +6711,23 @@
       </c>
       <c r="AO45" t="inlineStr"/>
       <c r="AP45" t="n">
-        <v>2646.05</v>
+        <v>5883.42</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6760,7 +6736,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>16.27450980392157</v>
+        <v>17.4</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6769,15 +6745,15 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>957000</v>
+        <v>1000</v>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="K46" t="b">
         <v>0</v>
@@ -6786,7 +6762,7 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>957000</v>
+        <v>1000</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
@@ -6795,61 +6771,61 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>488</v>
+        <v>1980</v>
       </c>
       <c r="Q46" t="n">
-        <v>488</v>
+        <v>1980</v>
       </c>
       <c r="R46" t="n">
-        <v>1025366</v>
+        <v>2228594</v>
       </c>
       <c r="S46" t="n">
-        <v>500</v>
+        <v>1999</v>
       </c>
       <c r="T46" t="n">
-        <v>558.45</v>
+        <v>2194.5</v>
       </c>
       <c r="U46" t="n">
-        <v>564.6</v>
+        <v>2214.25</v>
       </c>
       <c r="V46" t="n">
-        <v>543.2333333333333</v>
+        <v>2127.25</v>
       </c>
       <c r="W46" t="n">
-        <v>-23.62749306350031</v>
+        <v>-66.02132919008454</v>
       </c>
       <c r="X46" t="n">
-        <v>-11.7063686608625</v>
+        <v>-29.98641012823243</v>
       </c>
       <c r="Y46" t="n">
-        <v>-11.92112440263781</v>
+        <v>-36.03491906185211</v>
       </c>
       <c r="Z46" t="n">
-        <v>-13.44942410750093</v>
+        <v>-40.29112695807616</v>
       </c>
       <c r="AA46" t="b">
         <v>1</v>
       </c>
       <c r="AB46" t="n">
-        <v>-0.2013093289689034</v>
+        <v>-0.1663157894736842</v>
       </c>
       <c r="AC46" t="n">
-        <v>0.1441969519343493</v>
+        <v>-0.05714285714285716</v>
       </c>
       <c r="AD46" t="n">
-        <v>-0.195099583071477</v>
+        <v>-0.1311638419044958</v>
       </c>
       <c r="AE46" t="n">
-        <v>0.07014033646922924</v>
+        <v>-0.1123114807306704</v>
       </c>
       <c r="AF46" t="n">
-        <v>-0.2652399195407062</v>
+        <v>-0.01885236117382538</v>
       </c>
       <c r="AG46" t="n">
-        <v>3.92156862745098</v>
+        <v>18</v>
       </c>
       <c r="AH46" t="n">
-        <v>62.74509803921568</v>
+        <v>20</v>
       </c>
       <c r="AI46" t="b">
         <v>0</v>
@@ -6871,23 +6847,23 @@
       </c>
       <c r="AO46" t="inlineStr"/>
       <c r="AP46" t="n">
-        <v>692.16</v>
+        <v>2665.79</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6896,7 +6872,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>15.88235294117647</v>
+        <v>16.2</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6905,15 +6881,15 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>3281561</v>
+        <v>478000</v>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="K47" t="b">
         <v>0</v>
@@ -6922,7 +6898,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3281561</v>
+        <v>478000</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
@@ -6931,61 +6907,61 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>1880</v>
+        <v>764</v>
       </c>
       <c r="Q47" t="n">
-        <v>1880</v>
+        <v>764</v>
       </c>
       <c r="R47" t="n">
-        <v>6022146</v>
+        <v>1925674</v>
       </c>
       <c r="S47" t="n">
-        <v>1888</v>
+        <v>802.8</v>
       </c>
       <c r="T47" t="n">
-        <v>2090.75</v>
+        <v>850.3</v>
       </c>
       <c r="U47" t="n">
-        <v>2103.75</v>
+        <v>857.1</v>
       </c>
       <c r="V47" t="n">
-        <v>2143.912569173177</v>
+        <v>940.0666666666667</v>
       </c>
       <c r="W47" t="n">
-        <v>-82.80598189003217</v>
+        <v>-26.61929891469026</v>
       </c>
       <c r="X47" t="n">
-        <v>-51.62769702023009</v>
+        <v>-19.97817627127996</v>
       </c>
       <c r="Y47" t="n">
-        <v>-31.17828486980208</v>
+        <v>-6.641122643410299</v>
       </c>
       <c r="Z47" t="n">
-        <v>-34.17508036006885</v>
+        <v>-3.874339081718187</v>
       </c>
       <c r="AA47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>-0.1214953271028038</v>
+        <v>-0.1511111111111111</v>
       </c>
       <c r="AC47" t="n">
-        <v>-0.02135188124476795</v>
+        <v>-0.3178571428571428</v>
       </c>
       <c r="AD47" t="n">
-        <v>-0.1152855812053774</v>
+        <v>-0.1159591635419227</v>
       </c>
       <c r="AE47" t="n">
-        <v>-0.09540849670988805</v>
+        <v>-0.3730257664449561</v>
       </c>
       <c r="AF47" t="n">
-        <v>-0.01987708449548931</v>
+        <v>0.2570666029030334</v>
       </c>
       <c r="AG47" t="n">
-        <v>15.68627450980392</v>
+        <v>20</v>
       </c>
       <c r="AH47" t="n">
-        <v>23.52941176470588</v>
+        <v>2</v>
       </c>
       <c r="AI47" t="b">
         <v>0</v>
@@ -7000,32 +6976,32 @@
         <v>0</v>
       </c>
       <c r="AM47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO47" t="n">
-        <v>2233.44</v>
+        <v>838.87</v>
       </c>
       <c r="AP47" t="n">
-        <v>2371.84</v>
+        <v>988.84</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7034,7 +7010,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>15.88235294117647</v>
+        <v>15.2</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -7043,15 +7019,15 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1000</v>
+        <v>2887848</v>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="K48" t="b">
         <v>0</v>
@@ -7060,7 +7036,7 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>1000</v>
+        <v>2887848</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
@@ -7069,61 +7045,61 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>436.5</v>
+        <v>1875</v>
       </c>
       <c r="Q48" t="n">
-        <v>436.5</v>
+        <v>1875</v>
       </c>
       <c r="R48" t="n">
-        <v>31780106</v>
+        <v>2078527</v>
       </c>
       <c r="S48" t="n">
-        <v>436.3</v>
+        <v>1948</v>
       </c>
       <c r="T48" t="n">
-        <v>493.95</v>
+        <v>2257.5</v>
       </c>
       <c r="U48" t="n">
-        <v>498.375</v>
+        <v>2278.75</v>
       </c>
       <c r="V48" t="n">
-        <v>486.5333333333334</v>
+        <v>2173.583333333333</v>
       </c>
       <c r="W48" t="n">
-        <v>-21.23686695559746</v>
+        <v>-102.1980600094507</v>
       </c>
       <c r="X48" t="n">
-        <v>-11.06997000862372</v>
+        <v>-43.20034099335948</v>
       </c>
       <c r="Y48" t="n">
-        <v>-10.16689694697374</v>
+        <v>-58.99771901609125</v>
       </c>
       <c r="Z48" t="n">
-        <v>-12.32075644619913</v>
+        <v>-62.41437946930179</v>
       </c>
       <c r="AA48" t="b">
         <v>1</v>
       </c>
       <c r="AB48" t="n">
-        <v>-0.1685714285714286</v>
+        <v>-0.1847826086956522</v>
       </c>
       <c r="AC48" t="n">
-        <v>0.08852867830423938</v>
+        <v>-0.1279069767441861</v>
       </c>
       <c r="AD48" t="n">
-        <v>-0.1623616826740022</v>
+        <v>-0.1496306611264638</v>
       </c>
       <c r="AE48" t="n">
-        <v>0.01447206283911928</v>
+        <v>-0.1830756003319993</v>
       </c>
       <c r="AF48" t="n">
-        <v>-0.1768337455131215</v>
+        <v>0.03344493920553548</v>
       </c>
       <c r="AG48" t="n">
-        <v>7.84313725490196</v>
+        <v>12</v>
       </c>
       <c r="AH48" t="n">
-        <v>47.05882352941176</v>
+        <v>16</v>
       </c>
       <c r="AI48" t="b">
         <v>0</v>
@@ -7145,23 +7121,23 @@
       </c>
       <c r="AO48" t="inlineStr"/>
       <c r="AP48" t="n">
-        <v>576.47</v>
+        <v>2647.63</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -7170,7 +7146,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>15.49019607843137</v>
+        <v>14.6</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -7179,15 +7155,15 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>478000</v>
+        <v>93000</v>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K49" t="b">
         <v>0</v>
@@ -7196,7 +7172,7 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>478000</v>
+        <v>93000</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
@@ -7205,61 +7181,61 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>802</v>
+        <v>4795</v>
       </c>
       <c r="Q49" t="n">
-        <v>802</v>
+        <v>4795</v>
       </c>
       <c r="R49" t="n">
-        <v>1133338</v>
+        <v>475249</v>
       </c>
       <c r="S49" t="n">
-        <v>816.6</v>
+        <v>5009</v>
       </c>
       <c r="T49" t="n">
-        <v>857.1</v>
+        <v>5598.25</v>
       </c>
       <c r="U49" t="n">
-        <v>862.1</v>
+        <v>5648.25</v>
       </c>
       <c r="V49" t="n">
-        <v>946</v>
+        <v>6213.166666666667</v>
       </c>
       <c r="W49" t="n">
-        <v>-22.19223469214558</v>
+        <v>-316.2208937230052</v>
       </c>
       <c r="X49" t="n">
-        <v>-18.31789561042739</v>
+        <v>-252.1344951354536</v>
       </c>
       <c r="Y49" t="n">
-        <v>-3.874339081718187</v>
+        <v>-64.08639858755168</v>
       </c>
       <c r="Z49" t="n">
-        <v>-3.754054719819052</v>
+        <v>-61.90850408488279</v>
       </c>
       <c r="AA49" t="b">
         <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>-0.1108647450110865</v>
+        <v>-0.1725625539257981</v>
       </c>
       <c r="AC49" t="n">
-        <v>-0.2675799086757991</v>
+        <v>-0.2501954652071932</v>
       </c>
       <c r="AD49" t="n">
-        <v>-0.1046549991136601</v>
+        <v>-0.1374106063566097</v>
       </c>
       <c r="AE49" t="n">
-        <v>-0.3416365241409192</v>
+        <v>-0.3053640887950064</v>
       </c>
       <c r="AF49" t="n">
-        <v>0.2369815250272591</v>
+        <v>0.1679534824383967</v>
       </c>
       <c r="AG49" t="n">
-        <v>21.56862745098039</v>
+        <v>14</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.96078431372549</v>
+        <v>4</v>
       </c>
       <c r="AI49" t="b">
         <v>0</v>
@@ -7280,26 +7256,26 @@
         <v>1</v>
       </c>
       <c r="AO49" t="n">
-        <v>846.91</v>
+        <v>5523.84</v>
       </c>
       <c r="AP49" t="n">
-        <v>958</v>
+        <v>6610.53</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7308,7 +7284,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>15.09803921568628</v>
+        <v>14.6</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7317,7 +7293,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="H50" t="n">
@@ -7325,7 +7301,7 @@
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="K50" t="b">
         <v>0</v>
@@ -7343,61 +7319,61 @@
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>2010</v>
+        <v>414</v>
       </c>
       <c r="Q50" t="n">
-        <v>2010</v>
+        <v>414</v>
       </c>
       <c r="R50" t="n">
-        <v>2645879</v>
+        <v>32213621</v>
       </c>
       <c r="S50" t="n">
-        <v>2008</v>
+        <v>431.2</v>
       </c>
       <c r="T50" t="n">
-        <v>2214.25</v>
+        <v>488.85</v>
       </c>
       <c r="U50" t="n">
-        <v>2228.25</v>
+        <v>493.95</v>
       </c>
       <c r="V50" t="n">
-        <v>2129.25</v>
+        <v>486.1666666666667</v>
       </c>
       <c r="W50" t="n">
-        <v>-61.26880732084555</v>
+        <v>-23.48065326905203</v>
       </c>
       <c r="X50" t="n">
-        <v>-20.9776803627694</v>
+        <v>-13.55210666070938</v>
       </c>
       <c r="Y50" t="n">
-        <v>-40.29112695807616</v>
+        <v>-9.928546608342643</v>
       </c>
       <c r="Z50" t="n">
-        <v>-46.1229821609861</v>
+        <v>-10.16689694697374</v>
       </c>
       <c r="AA50" t="b">
         <v>1</v>
       </c>
       <c r="AB50" t="n">
-        <v>-0.1222707423580786</v>
+        <v>-0.1976744186046512</v>
       </c>
       <c r="AC50" t="n">
-        <v>-0.03365384615384615</v>
+        <v>-0.05045871559633031</v>
       </c>
       <c r="AD50" t="n">
-        <v>-0.1160609964606522</v>
+        <v>-0.1625224710354628</v>
       </c>
       <c r="AE50" t="n">
-        <v>-0.1077104616189662</v>
+        <v>-0.1056273391841436</v>
       </c>
       <c r="AF50" t="n">
-        <v>-0.008350534841685908</v>
+        <v>-0.05689513185131923</v>
       </c>
       <c r="AG50" t="n">
-        <v>13.72549019607843</v>
+        <v>8</v>
       </c>
       <c r="AH50" t="n">
-        <v>21.56862745098039</v>
+        <v>22</v>
       </c>
       <c r="AI50" t="b">
         <v>0</v>
@@ -7419,23 +7395,23 @@
       </c>
       <c r="AO50" t="inlineStr"/>
       <c r="AP50" t="n">
-        <v>2590</v>
+        <v>575.79</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7444,7 +7420,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>13.92156862745098</v>
+        <v>14.4</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7453,15 +7429,15 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>2504000</v>
+        <v>957000</v>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K51" t="b">
         <v>0</v>
@@ -7470,7 +7446,7 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>2504000</v>
+        <v>957000</v>
       </c>
       <c r="N51" t="n">
         <v>0</v>
@@ -7479,61 +7455,61 @@
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>5005</v>
+        <v>450</v>
       </c>
       <c r="Q51" t="n">
-        <v>5005</v>
+        <v>450</v>
       </c>
       <c r="R51" t="n">
-        <v>616279</v>
+        <v>1225780</v>
       </c>
       <c r="S51" t="n">
-        <v>5129</v>
+        <v>481.6</v>
       </c>
       <c r="T51" t="n">
-        <v>5421</v>
+        <v>550.05</v>
       </c>
       <c r="U51" t="n">
-        <v>5460.75</v>
+        <v>558.45</v>
       </c>
       <c r="V51" t="n">
-        <v>5541.166666666667</v>
+        <v>543.2583333333333</v>
       </c>
       <c r="W51" t="n">
-        <v>-117.1185340299917</v>
+        <v>-28.27015938495214</v>
       </c>
       <c r="X51" t="n">
-        <v>-21.94140857903943</v>
+        <v>-15.01912680568043</v>
       </c>
       <c r="Y51" t="n">
-        <v>-95.17712545095225</v>
+        <v>-13.25103257927171</v>
       </c>
       <c r="Z51" t="n">
-        <v>-91.01969657575349</v>
+        <v>-11.92112440263781</v>
       </c>
       <c r="AA51" t="b">
         <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>-0.1370689655172413</v>
+        <v>-0.2718446601941747</v>
       </c>
       <c r="AC51" t="n">
-        <v>-0.1226993865030674</v>
+        <v>0.003344481605351168</v>
       </c>
       <c r="AD51" t="n">
-        <v>-0.1308592196198149</v>
+        <v>-0.2366927126249864</v>
       </c>
       <c r="AE51" t="n">
-        <v>-0.1967560019681875</v>
+        <v>-0.0518241419824621</v>
       </c>
       <c r="AF51" t="n">
-        <v>0.0658967823483726</v>
+        <v>-0.1848685706425243</v>
       </c>
       <c r="AG51" t="n">
-        <v>11.76470588235294</v>
+        <v>2</v>
       </c>
       <c r="AH51" t="n">
-        <v>15.68627450980392</v>
+        <v>38</v>
       </c>
       <c r="AI51" t="b">
         <v>0</v>
@@ -7555,145 +7531,7 @@
       </c>
       <c r="AO51" t="inlineStr"/>
       <c r="AP51" t="n">
-        <v>5932.89</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>6515</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>10</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>20261021</t>
-        </is>
-      </c>
-      <c r="H52" t="n">
-        <v>93000</v>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="n">
-        <v>35</v>
-      </c>
-      <c r="K52" t="b">
-        <v>0</v>
-      </c>
-      <c r="L52" t="b">
-        <v>0</v>
-      </c>
-      <c r="M52" t="n">
-        <v>93000</v>
-      </c>
-      <c r="N52" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" t="n">
-        <v>4970</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>4970</v>
-      </c>
-      <c r="R52" t="n">
-        <v>430025</v>
-      </c>
-      <c r="S52" t="n">
-        <v>5061</v>
-      </c>
-      <c r="T52" t="n">
-        <v>5648.25</v>
-      </c>
-      <c r="U52" t="n">
-        <v>5721.5</v>
-      </c>
-      <c r="V52" t="n">
-        <v>6239.833333333333</v>
-      </c>
-      <c r="W52" t="n">
-        <v>-298.0213995734484</v>
-      </c>
-      <c r="X52" t="n">
-        <v>-236.1128954885656</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>-61.90850408488279</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>-68.54274036929957</v>
-      </c>
-      <c r="AA52" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>-0.2276612276612276</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>-0.210484511517077</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>-0.2214514817638013</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>-0.2845411269821971</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>0.06308964521839588</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>1.96078431372549</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>5.88235294117647</v>
-      </c>
-      <c r="AI52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AL52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AM52" t="b">
-        <v>1</v>
-      </c>
-      <c r="AN52" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO52" t="n">
-        <v>5675.74</v>
-      </c>
-      <c r="AP52" t="n">
-        <v>6508.95</v>
+        <v>710.3200000000001</v>
       </c>
     </row>
   </sheetData>

--- a/output/daily_screen_latest.xlsx
+++ b/output/daily_screen_latest.xlsx
@@ -643,26 +643,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>78.8</v>
+        <v>57.2</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -675,11 +675,11 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>6003000</v>
+        <v>1000</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="K2" t="b">
         <v>0</v>
@@ -688,7 +688,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>6003000</v>
+        <v>1000</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -697,62 +697,62 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>190</v>
+        <v>567</v>
       </c>
       <c r="Q2" t="n">
-        <v>190</v>
+        <v>567</v>
       </c>
       <c r="R2" t="n">
-        <v>36509667</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>187.3</v>
+        <v>561.2</v>
       </c>
       <c r="T2" t="n">
-        <v>186.025</v>
+        <v>547.2</v>
       </c>
       <c r="U2" t="n">
-        <v>185.85</v>
+        <v>543.3</v>
       </c>
       <c r="V2" t="n">
-        <v>184.85</v>
+        <v>496.8083333333333</v>
       </c>
       <c r="W2" t="n">
-        <v>1.003409599950857</v>
+        <v>10.63567921537594</v>
       </c>
       <c r="X2" t="n">
-        <v>0.2239197478976003</v>
+        <v>12.80653017454735</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.7794898520532563</v>
+        <v>-2.170850959171409</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.7163301077066526</v>
+        <v>-2.36357013646005</v>
       </c>
       <c r="AA2" t="b">
         <v>1</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.01876675603217159</v>
+        <v>0.1595092024539877</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.07344632768361592</v>
+        <v>0.3263157894736841</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.05391870360135997</v>
+        <v>0.1946611500231761</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.01827770409580265</v>
+        <v>0.2711471658858708</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.03564099950555732</v>
+        <v>-0.07648601586269477</v>
       </c>
       <c r="AG2" t="n">
+        <v>98</v>
+      </c>
+      <c r="AH2" t="n">
         <v>78</v>
       </c>
-      <c r="AH2" t="n">
-        <v>54</v>
-      </c>
       <c r="AI2" t="b">
         <v>1</v>
       </c>
@@ -760,21 +760,19 @@
         <v>1</v>
       </c>
       <c r="AK2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="b">
         <v>1</v>
       </c>
       <c r="AN2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>591.95</v>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
@@ -785,17 +783,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>慧洋-KY</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -804,7 +802,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>57.2</v>
+        <v>49</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -821,7 +819,7 @@
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K3" t="b">
         <v>0</v>
@@ -839,67 +837,67 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>567</v>
+        <v>100.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>567</v>
+        <v>100.5</v>
       </c>
       <c r="R3" t="n">
-        <v>45785250</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>559.2</v>
+        <v>100.1199996948242</v>
       </c>
       <c r="T3" t="n">
-        <v>543.3</v>
+        <v>99.55000038146973</v>
       </c>
       <c r="U3" t="n">
-        <v>538.45</v>
+        <v>99.55000038146973</v>
       </c>
       <c r="V3" t="n">
-        <v>494.4833333333333</v>
+        <v>95.24666671752929</v>
       </c>
       <c r="W3" t="n">
-        <v>10.98567277788015</v>
+        <v>0.3582787592283694</v>
       </c>
       <c r="X3" t="n">
-        <v>13.34924291434023</v>
+        <v>0.5125065110629193</v>
       </c>
       <c r="Y3" t="n">
-        <v>-2.363570136460073</v>
+        <v>-0.15422775183455</v>
       </c>
       <c r="Z3" t="n">
-        <v>-2.840567438305762</v>
+        <v>-0.1580429564758122</v>
       </c>
       <c r="AA3" t="b">
         <v>1</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.2063829787234042</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.2051009564293305</v>
+        <v>0.2271062042440113</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.2415349262925925</v>
+        <v>0.03515194756918838</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.1499323328415172</v>
+        <v>0.171937580656198</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.09160259345107535</v>
+        <v>-0.1367856330870096</v>
       </c>
       <c r="AG3" t="n">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="AH3" t="n">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="AI3" t="b">
         <v>1</v>
       </c>
       <c r="AJ3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="b">
         <v>0</v>
@@ -914,37 +912,35 @@
         <v>1</v>
       </c>
       <c r="AO3" t="n">
-        <v>594.22</v>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>102.31</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>99.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>47.8</v>
+        <v>56.6</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,20 +953,20 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1000</v>
+        <v>6899000</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="K4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="b">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1000</v>
+        <v>6899000</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -979,67 +975,67 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>100.5</v>
+        <v>1115</v>
       </c>
       <c r="Q4" t="n">
-        <v>100.5</v>
+        <v>1115</v>
       </c>
       <c r="R4" t="n">
-        <v>1548142</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>100.3199996948242</v>
+        <v>1172</v>
       </c>
       <c r="T4" t="n">
-        <v>99.55000038146973</v>
+        <v>1182.5</v>
       </c>
       <c r="U4" t="n">
-        <v>99.65000038146972</v>
+        <v>1178.75</v>
       </c>
       <c r="V4" t="n">
-        <v>94.93666674296061</v>
+        <v>1063.866666666667</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3930204925457446</v>
+        <v>1.320303042777368</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5510634490215537</v>
+        <v>23.78773744156464</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.1580429564758091</v>
+        <v>-22.46743439878727</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.1613387060659316</v>
+        <v>-18.67261691272811</v>
       </c>
       <c r="AA4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0.01951219512195124</v>
+        <v>0.07211538461538458</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.22114211753791</v>
+        <v>0.3782447466007417</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.01563975244723714</v>
+        <v>0.107267332184573</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.1659734939500968</v>
+        <v>0.3230761230129284</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.1503337415028596</v>
+        <v>-0.2158087908283555</v>
       </c>
       <c r="AG4" t="n">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="AH4" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="AI4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK4" t="b">
         <v>0</v>
@@ -1048,22 +1044,22 @@
         <v>0</v>
       </c>
       <c r="AM4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>102.31</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>99.5</v>
+        <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1123,49 +1119,49 @@
         <v>1265</v>
       </c>
       <c r="R5" t="n">
-        <v>7943255</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1329</v>
+        <v>1311</v>
       </c>
       <c r="T5" t="n">
+        <v>1373</v>
+      </c>
+      <c r="U5" t="n">
         <v>1368</v>
       </c>
-      <c r="U5" t="n">
-        <v>1357.75</v>
-      </c>
       <c r="V5" t="n">
-        <v>1198.916666666667</v>
+        <v>1203.733333333333</v>
       </c>
       <c r="W5" t="n">
-        <v>2.033985593817533</v>
+        <v>-6.951878699073632</v>
       </c>
       <c r="X5" t="n">
-        <v>35.11999365752448</v>
+        <v>26.70561918620492</v>
       </c>
       <c r="Y5" t="n">
-        <v>-33.08600806370695</v>
+        <v>-33.65749788527854</v>
       </c>
       <c r="Z5" t="n">
-        <v>-28.43274157005213</v>
+        <v>-33.08600806370702</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.1933962264150944</v>
+        <v>0.08583690987124459</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.1767441860465115</v>
+        <v>0.2961065573770492</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.2285481739842827</v>
+        <v>0.120988857440433</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.1215755624586983</v>
+        <v>0.2409379337892359</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.1069726115255845</v>
+        <v>-0.1199490763488029</v>
       </c>
       <c r="AG5" t="n">
         <v>96</v>
@@ -1201,7 +1197,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1220,7 +1216,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1261,55 +1257,55 @@
         <v>654</v>
       </c>
       <c r="R6" t="n">
-        <v>17897421</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>667.8</v>
+        <v>664.4</v>
       </c>
       <c r="T6" t="n">
+        <v>704.1</v>
+      </c>
+      <c r="U6" t="n">
         <v>706.05</v>
       </c>
-      <c r="U6" t="n">
-        <v>706.5</v>
-      </c>
       <c r="V6" t="n">
-        <v>635.5833333333334</v>
+        <v>637.25</v>
       </c>
       <c r="W6" t="n">
-        <v>-6.265559635740374</v>
+        <v>-8.727033407240924</v>
       </c>
       <c r="X6" t="n">
-        <v>7.119040713373153</v>
+        <v>3.949825889250339</v>
       </c>
       <c r="Y6" t="n">
+        <v>-12.67685929649126</v>
+      </c>
+      <c r="Z6" t="n">
         <v>-13.38460034911353</v>
       </c>
-      <c r="Z6" t="n">
-        <v>-12.94663445848076</v>
-      </c>
       <c r="AA6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.01357466063348411</v>
+        <v>-0.05627705627705626</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.07565789473684204</v>
+        <v>0.1805054151624548</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.02157728693570427</v>
+        <v>-0.02112510870786788</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.02048927114902876</v>
+        <v>0.1253367915746415</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.0010880157866755</v>
+        <v>-0.1464619002825094</v>
       </c>
       <c r="AG6" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="AH6" t="n">
-        <v>56.00000000000001</v>
+        <v>54</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
@@ -1324,30 +1320,30 @@
         <v>0</v>
       </c>
       <c r="AM6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN6" t="b">
         <v>0</v>
       </c>
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="n">
-        <v>747.79</v>
+        <v>745.74</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1356,7 +1352,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>56</v>
+        <v>49.8</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1369,11 +1365,11 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>6899000</v>
+        <v>19689000</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K7" t="b">
         <v>1</v>
@@ -1382,7 +1378,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>6899000</v>
+        <v>19689000</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1391,67 +1387,67 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1115</v>
+        <v>1085</v>
       </c>
       <c r="Q7" t="n">
-        <v>1115</v>
+        <v>1085</v>
       </c>
       <c r="R7" t="n">
-        <v>9411771</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1198</v>
+        <v>1089</v>
       </c>
       <c r="T7" t="n">
-        <v>1178.75</v>
+        <v>1182.25</v>
       </c>
       <c r="U7" t="n">
-        <v>1175.25</v>
+        <v>1184</v>
       </c>
       <c r="V7" t="n">
-        <v>1058.766666666667</v>
+        <v>1055.733333333333</v>
       </c>
       <c r="W7" t="n">
-        <v>10.73197912853334</v>
+        <v>-19.97839359683894</v>
       </c>
       <c r="X7" t="n">
-        <v>29.40459604126142</v>
+        <v>2.322377524709275</v>
       </c>
       <c r="Y7" t="n">
-        <v>-18.67261691272808</v>
+        <v>-22.30077112154822</v>
       </c>
       <c r="Z7" t="n">
-        <v>-10.11073891431796</v>
+        <v>-26.25141602093878</v>
       </c>
       <c r="AA7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.06698564593301426</v>
+        <v>-0.03125</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.2458100558659218</v>
+        <v>0.4201570680628273</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.1021375935022026</v>
+        <v>0.00390194756918838</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.1906414322781085</v>
+        <v>0.364988444475014</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.08850383877590584</v>
+        <v>-0.3610864969058256</v>
       </c>
       <c r="AG7" t="n">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="AH7" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
       </c>
       <c r="AJ7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="b">
         <v>0</v>
@@ -1460,34 +1456,30 @@
         <v>0</v>
       </c>
       <c r="AM7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN7" t="b">
         <v>0</v>
       </c>
-      <c r="AO7" t="n">
-        <v>1326.85</v>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="n">
+        <v>1262.37</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1496,7 +1488,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>55.6</v>
+        <v>49.8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1509,20 +1501,20 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>19689000</v>
+        <v>1000</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="K8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="b">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>19689000</v>
+        <v>1000</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1531,64 +1523,64 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1085</v>
+        <v>290.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>1085</v>
+        <v>290.5</v>
       </c>
       <c r="R8" t="n">
-        <v>21227071</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1090</v>
+        <v>295</v>
       </c>
       <c r="T8" t="n">
-        <v>1184</v>
+        <v>257.2</v>
       </c>
       <c r="U8" t="n">
-        <v>1180.75</v>
+        <v>253.35</v>
       </c>
       <c r="V8" t="n">
-        <v>1050.383333333333</v>
+        <v>205.425</v>
       </c>
       <c r="W8" t="n">
-        <v>-18.35384571584245</v>
+        <v>19.42547337056578</v>
       </c>
       <c r="X8" t="n">
-        <v>7.897570305096325</v>
+        <v>20.2207276979978</v>
       </c>
       <c r="Y8" t="n">
-        <v>-26.25141602093878</v>
+        <v>-0.7952543274320192</v>
       </c>
       <c r="Z8" t="n">
-        <v>-29.80898306559489</v>
+        <v>1.138377291406485</v>
       </c>
       <c r="AA8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.06372549019607843</v>
+        <v>0.360655737704918</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.2794811320754718</v>
+        <v>1.024390243902439</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.09887743776526681</v>
+        <v>0.3958076852741064</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.2243125084876585</v>
+        <v>0.9692216203146258</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.1254350707223917</v>
+        <v>-0.5734139350405194</v>
       </c>
       <c r="AG8" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AH8" t="n">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="AI8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ8" t="b">
         <v>1</v>
@@ -1600,12 +1592,14 @@
         <v>0</v>
       </c>
       <c r="AM8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO8" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>299.8</v>
+      </c>
       <c r="AP8" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -1615,17 +1609,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1634,7 +1628,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>49.8</v>
+        <v>49.2</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1647,20 +1641,20 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1000</v>
+        <v>7224000</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="K9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="b">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1000</v>
+        <v>7224000</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1669,73 +1663,73 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>290.5</v>
+        <v>1420</v>
       </c>
       <c r="Q9" t="n">
-        <v>290.5</v>
+        <v>1420</v>
       </c>
       <c r="R9" t="n">
-        <v>24850413</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>296.6</v>
+        <v>1504</v>
       </c>
       <c r="T9" t="n">
-        <v>253.35</v>
+        <v>1599.75</v>
       </c>
       <c r="U9" t="n">
-        <v>248.55</v>
+        <v>1600.75</v>
       </c>
       <c r="V9" t="n">
-        <v>202.975</v>
+        <v>1479.666666666667</v>
       </c>
       <c r="W9" t="n">
-        <v>21.55791857126223</v>
+        <v>-29.94233351305093</v>
       </c>
       <c r="X9" t="n">
-        <v>20.41954127985576</v>
+        <v>16.77037513293451</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.138377291406478</v>
+        <v>-46.71270864598544</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.737475616291896</v>
+        <v>-44.54088823811603</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.493573264781491</v>
+        <v>-0.01388888888888884</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.8503184713375795</v>
+        <v>0.2566371681415929</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.5287252123506794</v>
+        <v>0.02126305868029954</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.7951498477497663</v>
+        <v>0.2014685445537796</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.2664246353990869</v>
+        <v>-0.1802054858734801</v>
       </c>
       <c r="AG9" t="n">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="AH9" t="n">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="AI9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="b">
         <v>0</v>
@@ -1743,31 +1737,25 @@
       <c r="AN9" t="b">
         <v>0</v>
       </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="n">
+        <v>1649.21</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1776,7 +1764,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>47.6</v>
+        <v>45</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1789,11 +1777,11 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>7224000</v>
+        <v>12671000</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K10" t="b">
         <v>1</v>
@@ -1802,7 +1790,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>7224000</v>
+        <v>12671000</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1811,61 +1799,61 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1420</v>
+        <v>2385</v>
       </c>
       <c r="Q10" t="n">
-        <v>1420</v>
+        <v>2385</v>
       </c>
       <c r="R10" t="n">
-        <v>18706845</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1543</v>
+        <v>2403</v>
       </c>
       <c r="T10" t="n">
-        <v>1600.75</v>
+        <v>2481.5</v>
       </c>
       <c r="U10" t="n">
-        <v>1601.5</v>
+        <v>2485.25</v>
       </c>
       <c r="V10" t="n">
-        <v>1474.833333333333</v>
+        <v>2420.907405598958</v>
       </c>
       <c r="W10" t="n">
-        <v>-16.09233594368516</v>
+        <v>-25.86128205082832</v>
       </c>
       <c r="X10" t="n">
-        <v>28.44855229443083</v>
+        <v>-7.961188179207749</v>
       </c>
       <c r="Y10" t="n">
-        <v>-44.54088823811599</v>
+        <v>-17.90009387162057</v>
       </c>
       <c r="Z10" t="n">
-        <v>-35.06835181539509</v>
+        <v>-19.55105125688571</v>
       </c>
       <c r="AA10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.01045296167247389</v>
+        <v>-0.03048780487804881</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.1314741035856575</v>
+        <v>0.04913187713647793</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.02469898589671449</v>
+        <v>0.004664142691139572</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.07630547999784421</v>
+        <v>-0.00603674645133534</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.05160649410112972</v>
+        <v>0.01070088914247491</v>
       </c>
       <c r="AG10" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="AH10" t="n">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="AI10" t="b">
         <v>0</v>
@@ -1880,20 +1868,22 @@
         <v>0</v>
       </c>
       <c r="AM10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO10" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>2590.11</v>
+      </c>
       <c r="AP10" t="n">
-        <v>1630.26</v>
+        <v>2601.58</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1912,7 +1902,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>46</v>
+        <v>44.8</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1953,52 +1943,52 @@
         <v>6070</v>
       </c>
       <c r="R11" t="n">
-        <v>1719419</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>6509</v>
+        <v>6377</v>
       </c>
       <c r="T11" t="n">
+        <v>6777.75</v>
+      </c>
+      <c r="U11" t="n">
         <v>6765.75</v>
       </c>
-      <c r="U11" t="n">
-        <v>6751.75</v>
-      </c>
       <c r="V11" t="n">
-        <v>5616.25</v>
+        <v>5661.25</v>
       </c>
       <c r="W11" t="n">
-        <v>-17.30652828338771</v>
+        <v>-71.76099867335688</v>
       </c>
       <c r="X11" t="n">
-        <v>148.2485549823905</v>
+        <v>104.2466442512411</v>
       </c>
       <c r="Y11" t="n">
+        <v>-176.0076429245979</v>
+      </c>
+      <c r="Z11" t="n">
         <v>-165.5550832657782</v>
       </c>
-      <c r="Z11" t="n">
-        <v>-127.5612619723241</v>
-      </c>
       <c r="AA11" t="b">
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.04835924006908465</v>
+        <v>0.04116638078902235</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.7219858156028369</v>
+        <v>0.8011869436201779</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.08351118763827303</v>
+        <v>0.07631832835821073</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.6668171920150237</v>
+        <v>0.7460183200323647</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.5833060043767506</v>
+        <v>-0.6696999916741539</v>
       </c>
       <c r="AG11" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="AH11" t="n">
         <v>96</v>
@@ -2031,17 +2021,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2050,7 +2040,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>44.4</v>
+        <v>42.59999999999999</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2063,11 +2053,11 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>981000</v>
+        <v>121000</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="K12" t="b">
         <v>0</v>
@@ -2076,7 +2066,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>981000</v>
+        <v>121000</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -2085,61 +2075,61 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1560</v>
+        <v>1260</v>
       </c>
       <c r="Q12" t="n">
-        <v>1560</v>
+        <v>1260</v>
       </c>
       <c r="R12" t="n">
-        <v>5705283</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1572</v>
+        <v>1315</v>
       </c>
       <c r="T12" t="n">
-        <v>1602</v>
+        <v>1396.25</v>
       </c>
       <c r="U12" t="n">
-        <v>1599.25</v>
+        <v>1394</v>
       </c>
       <c r="V12" t="n">
-        <v>1315.133333333333</v>
+        <v>1278.259367879232</v>
       </c>
       <c r="W12" t="n">
-        <v>19.48525973849632</v>
+        <v>-25.97483346481295</v>
       </c>
       <c r="X12" t="n">
-        <v>42.33980538181607</v>
+        <v>15.37503427525873</v>
       </c>
       <c r="Y12" t="n">
-        <v>-22.85454564331975</v>
+        <v>-41.34986774007168</v>
       </c>
       <c r="Z12" t="n">
-        <v>-21.1032504699792</v>
+        <v>-40.78723373989933</v>
       </c>
       <c r="AA12" t="b">
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.03654485049833878</v>
+        <v>0.03703703703703698</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.5678391959798994</v>
+        <v>0.3264202682494393</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.07169679806752716</v>
+        <v>0.07218898460622536</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.5126705723920861</v>
+        <v>0.271251644661626</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.440973774324559</v>
+        <v>-0.1990626600554006</v>
       </c>
       <c r="AG12" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="AH12" t="n">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="AI12" t="b">
         <v>0</v>
@@ -2157,11 +2147,9 @@
         <v>0</v>
       </c>
       <c r="AN12" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>1818.96</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -2171,17 +2159,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2190,7 +2178,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>42.4</v>
+        <v>41.8</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2203,11 +2191,11 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>3921000</v>
+        <v>6003000</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K13" t="b">
         <v>0</v>
@@ -2216,7 +2204,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3921000</v>
+        <v>6003000</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -2225,61 +2213,61 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>89.80000305175781</v>
+        <v>190</v>
       </c>
       <c r="Q13" t="n">
-        <v>89.80000305175781</v>
+        <v>190</v>
       </c>
       <c r="R13" t="n">
-        <v>2745757</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>91.16000061035156</v>
+        <v>188.8</v>
       </c>
       <c r="T13" t="n">
-        <v>88.23500099182129</v>
+        <v>186.5</v>
       </c>
       <c r="U13" t="n">
-        <v>87.90500068664551</v>
+        <v>186.025</v>
       </c>
       <c r="V13" t="n">
-        <v>84.83500010172526</v>
+        <v>185.1833333333333</v>
       </c>
       <c r="W13" t="n">
-        <v>1.469152495810761</v>
+        <v>1.157026691460175</v>
       </c>
       <c r="X13" t="n">
-        <v>1.834851905037134</v>
+        <v>0.4105411366101419</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0.3656994092263737</v>
+        <v>0.7464855548500327</v>
       </c>
       <c r="Z13" t="n">
-        <v>-0.09908956594358531</v>
+        <v>0.7794898520532512</v>
       </c>
       <c r="AA13" t="b">
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.07932699934618292</v>
+        <v>0.05263157894736836</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.01583712106010604</v>
+        <v>0.1176470588235294</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.1144789469153713</v>
+        <v>0.08778352651655674</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0.03933150252770723</v>
+        <v>0.06247843523571617</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.1538104494430785</v>
+        <v>0.02530509128084057</v>
       </c>
       <c r="AG13" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="AH13" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AI13" t="b">
         <v>1</v>
@@ -2288,19 +2276,21 @@
         <v>1</v>
       </c>
       <c r="AK13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM13" t="b">
         <v>0</v>
       </c>
       <c r="AN13" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>93.93000000000001</v>
+        <v>0</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
@@ -2311,17 +2301,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2330,7 +2320,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>42.2</v>
+        <v>41.59999999999999</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2343,11 +2333,11 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>121000</v>
+        <v>3921000</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="K14" t="b">
         <v>0</v>
@@ -2356,7 +2346,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>121000</v>
+        <v>3921000</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2365,64 +2355,64 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1260</v>
+        <v>89.80000305175781</v>
       </c>
       <c r="Q14" t="n">
-        <v>1260</v>
+        <v>89.80000305175781</v>
       </c>
       <c r="R14" t="n">
-        <v>2017503</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1345</v>
+        <v>90.66000061035156</v>
       </c>
       <c r="T14" t="n">
-        <v>1394</v>
+        <v>88.51000099182129</v>
       </c>
       <c r="U14" t="n">
-        <v>1392.75</v>
+        <v>88.23500099182129</v>
       </c>
       <c r="V14" t="n">
-        <v>1273.091454060872</v>
+        <v>84.93166681925456</v>
       </c>
       <c r="W14" t="n">
-        <v>-15.07473252962268</v>
+        <v>1.185346965630188</v>
       </c>
       <c r="X14" t="n">
-        <v>25.71250121027664</v>
+        <v>1.704950917155769</v>
       </c>
       <c r="Y14" t="n">
-        <v>-40.78723373989932</v>
+        <v>-0.5196039515255806</v>
       </c>
       <c r="Z14" t="n">
-        <v>-34.67944144613021</v>
+        <v>-0.365699409226389</v>
       </c>
       <c r="AA14" t="b">
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.02024291497975717</v>
+        <v>0.06524317676030389</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.2328659625906726</v>
+        <v>0.06904765537806923</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.05539486254894554</v>
+        <v>0.1003951243294923</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.1776973390028593</v>
+        <v>0.01387903179025596</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.1223024764539138</v>
+        <v>0.08651609253923631</v>
       </c>
       <c r="AG14" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="AH14" t="n">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="AI14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ14" t="b">
         <v>1</v>
@@ -2437,9 +2427,11 @@
         <v>0</v>
       </c>
       <c r="AN14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>95.73</v>
+      </c>
       <c r="AP14" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -2449,17 +2441,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2468,7 +2460,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>41.59999999999999</v>
+        <v>41</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2481,11 +2473,11 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>852000</v>
+        <v>4328000</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="K15" t="b">
         <v>0</v>
@@ -2494,7 +2486,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>852000</v>
+        <v>4328000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2503,67 +2495,67 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>7585</v>
+        <v>5070</v>
       </c>
       <c r="Q15" t="n">
-        <v>7585</v>
+        <v>5070</v>
       </c>
       <c r="R15" t="n">
-        <v>1507339</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>7728</v>
+        <v>5040</v>
       </c>
       <c r="T15" t="n">
-        <v>8079.75</v>
+        <v>5321.5</v>
       </c>
       <c r="U15" t="n">
-        <v>8081.25</v>
+        <v>5311</v>
       </c>
       <c r="V15" t="n">
-        <v>6328.666666666667</v>
+        <v>5341.409090169271</v>
       </c>
       <c r="W15" t="n">
-        <v>41.43388910002159</v>
+        <v>-94.82468511148818</v>
       </c>
       <c r="X15" t="n">
-        <v>184.6003906854221</v>
+        <v>-23.75543770033998</v>
       </c>
       <c r="Y15" t="n">
-        <v>-143.1665015854005</v>
+        <v>-71.0692474111482</v>
       </c>
       <c r="Z15" t="n">
-        <v>-133.9920399343507</v>
+        <v>-86.4422419341677</v>
       </c>
       <c r="AA15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0.003939592908732803</v>
+        <v>0.04320987654320985</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.8728395061728396</v>
+        <v>0.1549094406875071</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.03121235466045558</v>
+        <v>0.07836182411239823</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.8176708825850263</v>
+        <v>0.09974081709969385</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.7864585279245707</v>
+        <v>-0.02137899298729562</v>
       </c>
       <c r="AG15" t="n">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="AH15" t="n">
-        <v>100</v>
+        <v>52</v>
       </c>
       <c r="AI15" t="b">
         <v>0</v>
       </c>
       <c r="AJ15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK15" t="b">
         <v>0</v>
@@ -2572,30 +2564,34 @@
         <v>0</v>
       </c>
       <c r="AM15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO15" t="inlineStr"/>
-      <c r="AP15" t="n">
-        <v>8895.790000000001</v>
+        <v>1</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>5871.06</v>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2604,7 +2600,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>40.6</v>
+        <v>40</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2617,20 +2613,20 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>12671000</v>
+        <v>501000</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="K16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="b">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>12671000</v>
+        <v>501000</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2639,67 +2635,67 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2385</v>
+        <v>224.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>2385</v>
+        <v>224.5</v>
       </c>
       <c r="R16" t="n">
-        <v>27360404</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2410</v>
+        <v>236.2</v>
       </c>
       <c r="T16" t="n">
-        <v>2485.25</v>
+        <v>237.35</v>
       </c>
       <c r="U16" t="n">
-        <v>2490</v>
+        <v>237.225</v>
       </c>
       <c r="V16" t="n">
-        <v>2419.045874023438</v>
+        <v>224.4833333333333</v>
       </c>
       <c r="W16" t="n">
-        <v>-23.03721596792138</v>
+        <v>-1.103629597366393</v>
       </c>
       <c r="X16" t="n">
-        <v>-3.486164710769593</v>
+        <v>2.303562950058372</v>
       </c>
       <c r="Y16" t="n">
-        <v>-19.55105125715179</v>
+        <v>-3.407192547424765</v>
       </c>
       <c r="Z16" t="n">
-        <v>-19.53124648872446</v>
+        <v>-2.605867250738623</v>
       </c>
       <c r="AA16" t="b">
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>-0.03830645161290325</v>
+        <v>0.01126126126126126</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.01788108362007046</v>
+        <v>0.2335164835164836</v>
       </c>
       <c r="AD16" t="n">
-        <v>-0.003154504043714867</v>
+        <v>0.04641320883044964</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0.03728753996774281</v>
+        <v>0.1783478599286703</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.03413303592402794</v>
+        <v>-0.1319346510982207</v>
       </c>
       <c r="AG16" t="n">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="AH16" t="n">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="AI16" t="b">
         <v>0</v>
       </c>
       <c r="AJ16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK16" t="b">
         <v>0</v>
@@ -2711,19 +2707,21 @@
         <v>0</v>
       </c>
       <c r="AN16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>2609.19</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>2565.53</v>
+        <v>263.11</v>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2742,7 +2740,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>39.8</v>
+        <v>39.2</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2783,31 +2781,31 @@
         <v>19.54999923706055</v>
       </c>
       <c r="R17" t="n">
-        <v>48162401</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>19.55999984741211</v>
       </c>
       <c r="T17" t="n">
+        <v>19.17250003814697</v>
+      </c>
+      <c r="U17" t="n">
         <v>19.12750005722046</v>
       </c>
-      <c r="U17" t="n">
-        <v>19.08250007629395</v>
-      </c>
       <c r="V17" t="n">
-        <v>19.07416674296061</v>
+        <v>19.08333339691162</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1720255685351937</v>
+        <v>0.1642806122425959</v>
       </c>
       <c r="X17" t="n">
-        <v>0.1272904830219476</v>
+        <v>0.1346885088660775</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.04473508551324606</v>
+        <v>0.02959210337651844</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.06097761265280496</v>
+        <v>0.04473508551324581</v>
       </c>
       <c r="AA17" t="b">
         <v>0</v>
@@ -2816,22 +2814,22 @@
         <v>0.04825735318707736</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.01558437595119733</v>
+        <v>0.02894732826634461</v>
       </c>
       <c r="AD17" t="n">
         <v>0.08340930075626574</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0.03958424763661594</v>
+        <v>-0.02622129532146866</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.1229935483928817</v>
+        <v>0.1096305960777344</v>
       </c>
       <c r="AG17" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AH17" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AI17" t="b">
         <v>1</v>
@@ -2865,17 +2863,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2884,7 +2882,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>39.59999999999999</v>
+        <v>38.8</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2897,11 +2895,11 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>4328000</v>
+        <v>1000</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="K18" t="b">
         <v>0</v>
@@ -2910,7 +2908,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>4328000</v>
+        <v>1000</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2919,67 +2917,67 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>5070</v>
+        <v>6175</v>
       </c>
       <c r="Q18" t="n">
-        <v>5070</v>
+        <v>6175</v>
       </c>
       <c r="R18" t="n">
-        <v>4742168</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>5059</v>
+        <v>6148</v>
       </c>
       <c r="T18" t="n">
-        <v>5311</v>
+        <v>6460.5</v>
       </c>
       <c r="U18" t="n">
-        <v>5302.25</v>
+        <v>6472</v>
       </c>
       <c r="V18" t="n">
-        <v>5330.075</v>
+        <v>5963.933964029948</v>
       </c>
       <c r="W18" t="n">
-        <v>-92.43036778172063</v>
+        <v>-100.7764050574497</v>
       </c>
       <c r="X18" t="n">
-        <v>-5.988125847553334</v>
+        <v>-7.696178450460646</v>
       </c>
       <c r="Y18" t="n">
-        <v>-86.4422419341673</v>
+        <v>-93.08022660698902</v>
       </c>
       <c r="Z18" t="n">
-        <v>-101.2885088592319</v>
+        <v>-106.9145326951619</v>
       </c>
       <c r="AA18" t="b">
         <v>1</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.03575076608784467</v>
+        <v>-0.03590944574551136</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.05776750642324702</v>
+        <v>0.5977954506216152</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.07090271365703305</v>
+        <v>-0.0007574981763229793</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.002598882835433747</v>
+        <v>0.5426268270338019</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.0683038308215993</v>
+        <v>-0.5433843252101249</v>
       </c>
       <c r="AG18" t="n">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="AH18" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="AI18" t="b">
         <v>0</v>
       </c>
       <c r="AJ18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="b">
         <v>0</v>
@@ -2994,28 +2992,26 @@
         <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>6043.44</v>
-      </c>
-      <c r="AP18" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>7224.75</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>6490.53</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3024,7 +3020,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>39.2</v>
+        <v>36.6</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3037,11 +3033,11 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>501000</v>
+        <v>981000</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K19" t="b">
         <v>0</v>
@@ -3050,7 +3046,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>501000</v>
+        <v>981000</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -3059,67 +3055,67 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>224.5</v>
+        <v>1560</v>
       </c>
       <c r="Q19" t="n">
-        <v>224.5</v>
+        <v>1560</v>
       </c>
       <c r="R19" t="n">
-        <v>40806726</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>240.9</v>
+        <v>1570</v>
       </c>
       <c r="T19" t="n">
-        <v>237.225</v>
+        <v>1597.25</v>
       </c>
       <c r="U19" t="n">
-        <v>237.1</v>
+        <v>1602</v>
       </c>
       <c r="V19" t="n">
-        <v>223.775</v>
+        <v>1326.033333333333</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5494938361759409</v>
+        <v>13.84320185960064</v>
       </c>
       <c r="X19" t="n">
-        <v>3.155361086914562</v>
+        <v>36.6404846773729</v>
       </c>
       <c r="Y19" t="n">
-        <v>-2.605867250738621</v>
+        <v>-22.79728281777226</v>
       </c>
       <c r="Z19" t="n">
-        <v>-0.8858338769129448</v>
+        <v>-22.85454564331965</v>
       </c>
       <c r="AA19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.01126126126126126</v>
+        <v>-0.05740181268882172</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.1253132832080202</v>
+        <v>0.7218543046357615</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.04641320883044964</v>
+        <v>-0.02224986511963334</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.07014465962020688</v>
+        <v>0.6666856810479482</v>
       </c>
       <c r="AF19" t="n">
-        <v>-0.02373145078975725</v>
+        <v>-0.6889355461675816</v>
       </c>
       <c r="AG19" t="n">
-        <v>76</v>
+        <v>57.99999999999999</v>
       </c>
       <c r="AH19" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="AI19" t="b">
         <v>0</v>
       </c>
       <c r="AJ19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="b">
         <v>0</v>
@@ -3128,34 +3124,32 @@
         <v>0</v>
       </c>
       <c r="AM19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN19" t="b">
         <v>1</v>
       </c>
       <c r="AO19" t="n">
-        <v>254.13</v>
-      </c>
-      <c r="AP19" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>1818.96</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1579.21</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>美律</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3164,7 +3158,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>37.4</v>
+        <v>36.2</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3177,11 +3171,11 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>919000</v>
+        <v>1000</v>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="K20" t="b">
         <v>0</v>
@@ -3190,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>919000</v>
+        <v>1000</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -3199,67 +3193,67 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2335</v>
+        <v>79.40000152587891</v>
       </c>
       <c r="Q20" t="n">
-        <v>2335</v>
+        <v>79.40000152587891</v>
       </c>
       <c r="R20" t="n">
-        <v>1263039</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2321</v>
+        <v>79.86000061035156</v>
       </c>
       <c r="T20" t="n">
-        <v>2369.25</v>
+        <v>78.96999969482422</v>
       </c>
       <c r="U20" t="n">
-        <v>2373.25</v>
+        <v>78.90499954223633</v>
       </c>
       <c r="V20" t="n">
-        <v>2066.928828938802</v>
+        <v>77.88492647806804</v>
       </c>
       <c r="W20" t="n">
-        <v>3.930312659717401</v>
+        <v>0.4632227407964393</v>
       </c>
       <c r="X20" t="n">
-        <v>4.092236251985423</v>
+        <v>0.6299568234198029</v>
       </c>
       <c r="Y20" t="n">
-        <v>-0.1619235922680211</v>
+        <v>-0.1667340826233635</v>
       </c>
       <c r="Z20" t="n">
-        <v>-3.332621819944903</v>
+        <v>-0.05979653250630002</v>
       </c>
       <c r="AA20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>-0.0331262939958592</v>
+        <v>0.01664536590469434</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.6160334055754417</v>
+        <v>0.02022837095074759</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.002025653573329178</v>
+        <v>0.05179731347388272</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.5608647819876285</v>
+        <v>-0.03494025263706568</v>
       </c>
       <c r="AF20" t="n">
-        <v>-0.5588391284142993</v>
+        <v>0.08673756611094841</v>
       </c>
       <c r="AG20" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AH20" t="n">
-        <v>94</v>
+        <v>22</v>
       </c>
       <c r="AI20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK20" t="b">
         <v>0</v>
@@ -3268,32 +3262,34 @@
         <v>0</v>
       </c>
       <c r="AM20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="b">
         <v>1</v>
       </c>
       <c r="AO20" t="n">
-        <v>2339.67</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>2536.05</v>
+        <v>81.31</v>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>6271</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3302,7 +3298,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>36.4</v>
+        <v>35.4</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3315,11 +3311,11 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1000</v>
+        <v>2185000</v>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="K21" t="b">
         <v>0</v>
@@ -3328,7 +3324,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1000</v>
+        <v>2185000</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -3337,61 +3333,61 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>6175</v>
+        <v>215</v>
       </c>
       <c r="Q21" t="n">
-        <v>6175</v>
+        <v>215</v>
       </c>
       <c r="R21" t="n">
-        <v>1825937</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>6193</v>
+        <v>221.3</v>
       </c>
       <c r="T21" t="n">
-        <v>6472</v>
+        <v>231.7</v>
       </c>
       <c r="U21" t="n">
-        <v>6483.25</v>
+        <v>232.35</v>
       </c>
       <c r="V21" t="n">
-        <v>5925.428963216146</v>
+        <v>213.8083333333333</v>
       </c>
       <c r="W21" t="n">
-        <v>-91.34065449387526</v>
+        <v>-3.539802223704925</v>
       </c>
       <c r="X21" t="n">
-        <v>15.5738782012865</v>
+        <v>0.01536129278935316</v>
       </c>
       <c r="Y21" t="n">
-        <v>-106.9145326951618</v>
+        <v>-3.555163516494278</v>
       </c>
       <c r="Z21" t="n">
-        <v>-116.7328604290002</v>
+        <v>-3.365732392324016</v>
       </c>
       <c r="AA21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>-0.03515625</v>
+        <v>-0.05701754385964908</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.5235702267940734</v>
+        <v>0.2990936555891239</v>
       </c>
       <c r="AD21" t="n">
-        <v>-4.302430811620184e-06</v>
+        <v>-0.0218655962904607</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.4684016032062601</v>
+        <v>0.2439250320013107</v>
       </c>
       <c r="AF21" t="n">
-        <v>-0.4684059056370717</v>
+        <v>-0.2657906282917714</v>
       </c>
       <c r="AG21" t="n">
-        <v>57.99999999999999</v>
+        <v>60</v>
       </c>
       <c r="AH21" t="n">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="AI21" t="b">
         <v>0</v>
@@ -3406,32 +3402,32 @@
         <v>0</v>
       </c>
       <c r="AM21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="b">
         <v>0</v>
       </c>
       <c r="AO21" t="n">
-        <v>7385.3</v>
+        <v>255.42</v>
       </c>
       <c r="AP21" t="n">
-        <v>6717.63</v>
+        <v>246.08</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>美律</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3440,7 +3436,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>35.2</v>
+        <v>35</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3453,11 +3449,11 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1000</v>
+        <v>919000</v>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="K22" t="b">
         <v>0</v>
@@ -3466,7 +3462,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1000</v>
+        <v>919000</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -3475,103 +3471,103 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>79.40000152587891</v>
+        <v>2335</v>
       </c>
       <c r="Q22" t="n">
-        <v>79.40000152587891</v>
+        <v>2335</v>
       </c>
       <c r="R22" t="n">
-        <v>1417071</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>80.28000030517578</v>
+        <v>2338</v>
       </c>
       <c r="T22" t="n">
-        <v>78.90499954223633</v>
+        <v>2361</v>
       </c>
       <c r="U22" t="n">
-        <v>78.86499938964843</v>
+        <v>2369.25</v>
       </c>
       <c r="V22" t="n">
-        <v>77.85868835449219</v>
+        <v>2083.667254638672</v>
       </c>
       <c r="W22" t="n">
-        <v>0.6118438115693436</v>
+        <v>5.997368772541449</v>
       </c>
       <c r="X22" t="n">
-        <v>0.6716403440756505</v>
+        <v>4.473262756096712</v>
       </c>
       <c r="Y22" t="n">
-        <v>-0.0597965325063069</v>
+        <v>1.524106016444737</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.1183725327504477</v>
+        <v>-0.1619235922681259</v>
       </c>
       <c r="AA22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.01017815607237216</v>
+        <v>-0.06599999999999995</v>
       </c>
       <c r="AC22" t="n">
-        <v>-0.004091723585210372</v>
+        <v>0.7547228711658851</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.04533010364156054</v>
+        <v>-0.03084805243081157</v>
       </c>
       <c r="AE22" t="n">
-        <v>-0.05926034717302364</v>
+        <v>0.6995542475780718</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.1045904508145842</v>
+        <v>-0.7304023000088834</v>
       </c>
       <c r="AG22" t="n">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="AH22" t="n">
-        <v>30</v>
+        <v>94</v>
       </c>
       <c r="AI22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN22" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>80.19</v>
-      </c>
-      <c r="AP22" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
+      </c>
+      <c r="AP22" t="n">
+        <v>2627.37</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3580,7 +3576,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>32.6</v>
+        <v>33.4</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3593,20 +3589,20 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>23519000</v>
+        <v>1000</v>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="K23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="b">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>23519000</v>
+        <v>1000</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -3615,61 +3611,61 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>507</v>
+        <v>245</v>
       </c>
       <c r="Q23" t="n">
-        <v>507</v>
+        <v>245</v>
       </c>
       <c r="R23" t="n">
-        <v>45898163</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>534.6</v>
+        <v>244.2</v>
       </c>
       <c r="T23" t="n">
-        <v>584.45</v>
+        <v>247.825</v>
       </c>
       <c r="U23" t="n">
-        <v>586.95</v>
+        <v>248.225</v>
       </c>
       <c r="V23" t="n">
-        <v>567.9416666666667</v>
+        <v>250.3916666666667</v>
       </c>
       <c r="W23" t="n">
-        <v>-17.37564989530244</v>
+        <v>-1.318912905240666</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.56196844601415</v>
+        <v>-1.669404992933951</v>
       </c>
       <c r="Y23" t="n">
-        <v>-14.81368144928829</v>
+        <v>0.3504920876932855</v>
       </c>
       <c r="Z23" t="n">
-        <v>-13.52868915640523</v>
+        <v>0.2496176986635734</v>
       </c>
       <c r="AA23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB23" t="n">
-        <v>-0.08976660682226212</v>
+        <v>-0.03162055335968383</v>
       </c>
       <c r="AC23" t="n">
-        <v>-0.1888</v>
+        <v>0.02941176470588225</v>
       </c>
       <c r="AD23" t="n">
-        <v>-0.05461465925307374</v>
+        <v>0.003531394209504546</v>
       </c>
       <c r="AE23" t="n">
-        <v>-0.2439686235878132</v>
+        <v>-0.02575685888193102</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.1893539643347395</v>
+        <v>0.02928825309143557</v>
       </c>
       <c r="AG23" t="n">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="AH23" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="AI23" t="b">
         <v>0</v>
@@ -3678,36 +3674,40 @@
         <v>0</v>
       </c>
       <c r="AK23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN23" t="b">
         <v>0</v>
       </c>
-      <c r="AO23" t="inlineStr"/>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
+      </c>
       <c r="AP23" t="n">
-        <v>652.53</v>
+        <v>258.97</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3716,7 +3716,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3729,11 +3729,11 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1000</v>
+        <v>6457000</v>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="K24" t="b">
         <v>0</v>
@@ -3742,7 +3742,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1000</v>
+        <v>6457000</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3751,61 +3751,61 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>245</v>
+        <v>3145</v>
       </c>
       <c r="Q24" t="n">
-        <v>245</v>
+        <v>3145</v>
       </c>
       <c r="R24" t="n">
-        <v>26532180</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>244</v>
+        <v>3234</v>
       </c>
       <c r="T24" t="n">
-        <v>248.225</v>
+        <v>3380.75</v>
       </c>
       <c r="U24" t="n">
-        <v>248.475</v>
+        <v>3393</v>
       </c>
       <c r="V24" t="n">
-        <v>250.275</v>
+        <v>3168.535294596354</v>
       </c>
       <c r="W24" t="n">
-        <v>-1.507410316193699</v>
+        <v>-58.91887697289167</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.757028014857289</v>
+        <v>-25.92761996345932</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.2496176986635905</v>
+        <v>-32.99125700943235</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.09321016520792491</v>
+        <v>-32.82779203802981</v>
       </c>
       <c r="AA24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>-0.02000000000000002</v>
+        <v>-0.07227138643067843</v>
       </c>
       <c r="AC24" t="n">
-        <v>-0.03162055335968383</v>
+        <v>0.4123468961285974</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.01515194756918836</v>
+        <v>-0.03711943886149005</v>
       </c>
       <c r="AE24" t="n">
-        <v>-0.0867891769474971</v>
+        <v>0.3571782725407842</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.1019411245166855</v>
+        <v>-0.3942977114022742</v>
       </c>
       <c r="AG24" t="n">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="AH24" t="n">
-        <v>28</v>
+        <v>86</v>
       </c>
       <c r="AI24" t="b">
         <v>0</v>
@@ -3814,40 +3814,38 @@
         <v>0</v>
       </c>
       <c r="AK24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>3522.4</v>
       </c>
       <c r="AP24" t="n">
-        <v>256.39</v>
+        <v>3718.16</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3856,7 +3854,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>31.4</v>
+        <v>32</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3869,20 +3867,20 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>6587450</v>
+        <v>852000</v>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="K25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" t="b">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>6587450</v>
+        <v>852000</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3891,61 +3889,61 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>262.5</v>
+        <v>7585</v>
       </c>
       <c r="Q25" t="n">
-        <v>262.5</v>
+        <v>7585</v>
       </c>
       <c r="R25" t="n">
-        <v>33661928</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>267.7</v>
+        <v>7749</v>
       </c>
       <c r="T25" t="n">
-        <v>291.025</v>
+        <v>8040.25</v>
       </c>
       <c r="U25" t="n">
-        <v>292.975</v>
+        <v>8079.75</v>
       </c>
       <c r="V25" t="n">
-        <v>265.1166666666667</v>
+        <v>6394.083333333333</v>
       </c>
       <c r="W25" t="n">
-        <v>-6.221157300770301</v>
+        <v>9.323164990708392</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.265743389475171</v>
+        <v>149.5449455464794</v>
       </c>
       <c r="Y25" t="n">
-        <v>-4.95541391129513</v>
+        <v>-140.221780555771</v>
       </c>
       <c r="Z25" t="n">
-        <v>-5.022716500177913</v>
+        <v>-143.1665015854005</v>
       </c>
       <c r="AA25" t="b">
         <v>1</v>
       </c>
       <c r="AB25" t="n">
-        <v>-0.1293532338308457</v>
+        <v>-0.09432835820895524</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.00245497512684234</v>
+        <v>1.0724043715847</v>
       </c>
       <c r="AD25" t="n">
-        <v>-0.09420128626165736</v>
+        <v>-0.05917641063976686</v>
       </c>
       <c r="AE25" t="n">
-        <v>-0.05271364846097093</v>
+        <v>1.017235747996886</v>
       </c>
       <c r="AF25" t="n">
-        <v>-0.04148763780068643</v>
+        <v>-1.076412158636653</v>
       </c>
       <c r="AG25" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="AH25" t="n">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="AI25" t="b">
         <v>0</v>
@@ -3967,23 +3965,23 @@
       </c>
       <c r="AO25" t="inlineStr"/>
       <c r="AP25" t="n">
-        <v>347.03</v>
+        <v>8864.209999999999</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3992,7 +3990,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>31.4</v>
+        <v>31.2</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4005,11 +4003,11 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>6457000</v>
+        <v>1000</v>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="K26" t="b">
         <v>0</v>
@@ -4018,7 +4016,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>6457000</v>
+        <v>1000</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -4027,61 +4025,61 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>3145</v>
+        <v>3495</v>
       </c>
       <c r="Q26" t="n">
-        <v>3145</v>
+        <v>3495</v>
       </c>
       <c r="R26" t="n">
-        <v>2509829</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>3268</v>
+        <v>3611</v>
       </c>
       <c r="T26" t="n">
-        <v>3393</v>
+        <v>3851.5</v>
       </c>
       <c r="U26" t="n">
-        <v>3406.5</v>
+        <v>3862.5</v>
       </c>
       <c r="V26" t="n">
-        <v>3153.231795247396</v>
+        <v>3768.57890218099</v>
       </c>
       <c r="W26" t="n">
-        <v>-50.50759774913104</v>
+        <v>-92.25524040679875</v>
       </c>
       <c r="X26" t="n">
-        <v>-17.67980571110139</v>
+        <v>-21.40092614023082</v>
       </c>
       <c r="Y26" t="n">
-        <v>-32.82779203802965</v>
+        <v>-70.85431426656794</v>
       </c>
       <c r="Z26" t="n">
-        <v>-27.06458267927109</v>
+        <v>-70.82136378615128</v>
       </c>
       <c r="AA26" t="b">
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>-0.07906295754026349</v>
+        <v>-0.05921938088829071</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.3181904556565121</v>
+        <v>0.1307599125693282</v>
       </c>
       <c r="AD26" t="n">
-        <v>-0.04391100997107511</v>
+        <v>-0.02406743331910233</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.2630218320686988</v>
+        <v>0.0755912889815149</v>
       </c>
       <c r="AF26" t="n">
-        <v>-0.3069328420397739</v>
+        <v>-0.09965872230061723</v>
       </c>
       <c r="AG26" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="AH26" t="n">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="AI26" t="b">
         <v>0</v>
@@ -4099,29 +4097,27 @@
         <v>0</v>
       </c>
       <c r="AN26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>3516.11</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO26" t="inlineStr"/>
       <c r="AP26" t="n">
-        <v>3651.05</v>
+        <v>4135.26</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4130,7 +4126,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>31.4</v>
+        <v>31</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4143,20 +4139,20 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>2185000</v>
+        <v>23519000</v>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="K27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="b">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>2185000</v>
+        <v>23519000</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -4165,61 +4161,61 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>215</v>
+        <v>507</v>
       </c>
       <c r="Q27" t="n">
-        <v>215</v>
+        <v>507</v>
       </c>
       <c r="R27" t="n">
-        <v>2499080</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>224.1</v>
+        <v>522.6</v>
       </c>
       <c r="T27" t="n">
-        <v>232.35</v>
+        <v>581.25</v>
       </c>
       <c r="U27" t="n">
-        <v>233.1</v>
+        <v>584.45</v>
       </c>
       <c r="V27" t="n">
-        <v>212.9833333333333</v>
+        <v>567.0083333333333</v>
       </c>
       <c r="W27" t="n">
-        <v>-2.461580220411093</v>
+        <v>-20.39540062247374</v>
       </c>
       <c r="X27" t="n">
-        <v>0.9041521719129229</v>
+        <v>-6.128654881306069</v>
       </c>
       <c r="Y27" t="n">
-        <v>-3.365732392324016</v>
+        <v>-14.26674574116768</v>
       </c>
       <c r="Z27" t="n">
-        <v>-2.559680799197468</v>
+        <v>-14.81368144928829</v>
       </c>
       <c r="AA27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB27" t="n">
-        <v>-0.06521739130434778</v>
+        <v>-0.1120840630472855</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.1716621253405994</v>
+        <v>-0.09946714031971582</v>
       </c>
       <c r="AD27" t="n">
-        <v>-0.0300654437351594</v>
+        <v>-0.07693211547809709</v>
       </c>
       <c r="AE27" t="n">
-        <v>0.1164935017527862</v>
+        <v>-0.1546357639075291</v>
       </c>
       <c r="AF27" t="n">
-        <v>-0.1465589454879456</v>
+        <v>0.077703648429432</v>
       </c>
       <c r="AG27" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="AH27" t="n">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="AI27" t="b">
         <v>0</v>
@@ -4234,22 +4230,20 @@
         <v>0</v>
       </c>
       <c r="AM27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN27" t="b">
         <v>0</v>
       </c>
-      <c r="AO27" t="n">
-        <v>253.27</v>
-      </c>
+      <c r="AO27" t="inlineStr"/>
       <c r="AP27" t="n">
-        <v>246.26</v>
+        <v>651.16</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -4268,7 +4262,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>31.2</v>
+        <v>31</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4309,55 +4303,55 @@
         <v>172.5</v>
       </c>
       <c r="R28" t="n">
-        <v>2336685</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>176.5</v>
+        <v>175.8</v>
       </c>
       <c r="T28" t="n">
+        <v>173.95</v>
+      </c>
+      <c r="U28" t="n">
         <v>174.35</v>
       </c>
-      <c r="U28" t="n">
-        <v>174.575</v>
-      </c>
       <c r="V28" t="n">
-        <v>183.8839558919271</v>
+        <v>183.8319684346517</v>
       </c>
       <c r="W28" t="n">
-        <v>-0.3644799868444863</v>
+        <v>-0.6912703768403219</v>
       </c>
       <c r="X28" t="n">
-        <v>-1.569258623656947</v>
+        <v>-1.393660974293531</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.204778636812461</v>
+        <v>0.7023905974532094</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.99166939536115</v>
+        <v>1.204778636812404</v>
       </c>
       <c r="AA28" t="b">
         <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>-0.02542372881355937</v>
+        <v>-0.04432132963988922</v>
       </c>
       <c r="AC28" t="n">
-        <v>-0.04438038309281866</v>
+        <v>-0.0177614212681948</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.009728218755629015</v>
+        <v>-0.009169382070700838</v>
       </c>
       <c r="AE28" t="n">
-        <v>-0.09954900668063194</v>
+        <v>-0.07293004485600807</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.1092772254362609</v>
+        <v>0.06376066278530723</v>
       </c>
       <c r="AG28" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="AH28" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="AI28" t="b">
         <v>0</v>
@@ -4383,23 +4377,23 @@
         </is>
       </c>
       <c r="AP28" t="n">
-        <v>182.45</v>
+        <v>178.03</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4408,7 +4402,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>30.2</v>
+        <v>29.4</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4425,7 +4419,7 @@
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="K29" t="b">
         <v>0</v>
@@ -4443,61 +4437,61 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>3495</v>
+        <v>322</v>
       </c>
       <c r="Q29" t="n">
-        <v>3495</v>
+        <v>322</v>
       </c>
       <c r="R29" t="n">
-        <v>1517390</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>3649</v>
+        <v>321.5</v>
       </c>
       <c r="T29" t="n">
-        <v>3862.5</v>
+        <v>327.75</v>
       </c>
       <c r="U29" t="n">
-        <v>3871</v>
+        <v>328.75</v>
       </c>
       <c r="V29" t="n">
-        <v>3761.842932128906</v>
+        <v>326.7</v>
       </c>
       <c r="W29" t="n">
-        <v>-74.50871135974103</v>
+        <v>-2.822420278790332</v>
       </c>
       <c r="X29" t="n">
-        <v>-3.687347573591545</v>
+        <v>-3.224214941310815</v>
       </c>
       <c r="Y29" t="n">
-        <v>-70.82136378614948</v>
+        <v>0.4017946625204831</v>
       </c>
       <c r="Z29" t="n">
-        <v>-60.19659266962921</v>
+        <v>0.2730154495566866</v>
       </c>
       <c r="AA29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB29" t="n">
-        <v>-0.04638472032742158</v>
+        <v>-0.05847953216374269</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.01801077608644075</v>
+        <v>0.02711323763955353</v>
       </c>
       <c r="AD29" t="n">
-        <v>-0.0112327727582332</v>
+        <v>-0.02332758459455431</v>
       </c>
       <c r="AE29" t="n">
-        <v>-0.03715784750137252</v>
+        <v>-0.02805538594825974</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.02592507474313932</v>
+        <v>0.00472780135370543</v>
       </c>
       <c r="AG29" t="n">
-        <v>52</v>
+        <v>56.00000000000001</v>
       </c>
       <c r="AH29" t="n">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="AI29" t="b">
         <v>0</v>
@@ -4506,26 +4500,30 @@
         <v>0</v>
       </c>
       <c r="AK29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN29" t="b">
         <v>0</v>
       </c>
-      <c r="AO29" t="inlineStr"/>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
+      </c>
       <c r="AP29" t="n">
-        <v>4101.84</v>
+        <v>347.55</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4544,7 +4542,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>29.8</v>
+        <v>29.2</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4585,55 +4583,55 @@
         <v>161</v>
       </c>
       <c r="R30" t="n">
-        <v>6205059</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>163.7</v>
+        <v>162.4</v>
       </c>
       <c r="T30" t="n">
+        <v>174.95</v>
+      </c>
+      <c r="U30" t="n">
         <v>175.55</v>
       </c>
-      <c r="U30" t="n">
-        <v>176.1</v>
-      </c>
       <c r="V30" t="n">
-        <v>161.3916666666667</v>
+        <v>161.6166666666667</v>
       </c>
       <c r="W30" t="n">
-        <v>-3.188915133197838</v>
+        <v>-3.494052847898416</v>
       </c>
       <c r="X30" t="n">
-        <v>-0.1083930722634476</v>
+        <v>-0.7855250273904424</v>
       </c>
       <c r="Y30" t="n">
-        <v>-3.080522060934391</v>
+        <v>-2.708527820507974</v>
       </c>
       <c r="Z30" t="n">
-        <v>-3.295402841218987</v>
+        <v>-3.080522060934389</v>
       </c>
       <c r="AA30" t="b">
         <v>1</v>
       </c>
       <c r="AB30" t="n">
-        <v>-0.06395348837209303</v>
+        <v>-0.06936416184971095</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.02547770700636942</v>
+        <v>0.09152542372881345</v>
       </c>
       <c r="AD30" t="n">
-        <v>-0.02880154080290465</v>
+        <v>-0.03421221428052257</v>
       </c>
       <c r="AE30" t="n">
-        <v>-0.02969091658144385</v>
+        <v>0.03635680014100018</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.0008893757785392031</v>
+        <v>-0.07056901442152275</v>
       </c>
       <c r="AG30" t="n">
         <v>50</v>
       </c>
       <c r="AH30" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AI30" t="b">
         <v>0</v>
@@ -4653,25 +4651,27 @@
       <c r="AN30" t="b">
         <v>0</v>
       </c>
-      <c r="AO30" t="inlineStr"/>
+      <c r="AO30" t="n">
+        <v>191.59</v>
+      </c>
       <c r="AP30" t="n">
-        <v>188.32</v>
+        <v>187.68</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4680,7 +4680,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>28.4</v>
+        <v>28.8</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4693,20 +4693,20 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1000</v>
+        <v>6587450</v>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="K31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" t="b">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1000</v>
+        <v>6587450</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -4715,61 +4715,61 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>95.90000152587891</v>
+        <v>262.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>95.90000152587891</v>
+        <v>262.5</v>
       </c>
       <c r="R31" t="n">
-        <v>19257495</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>101.1</v>
+        <v>265.2</v>
       </c>
       <c r="T31" t="n">
-        <v>113.05</v>
+        <v>288.3</v>
       </c>
       <c r="U31" t="n">
-        <v>113.4049999237061</v>
+        <v>291.025</v>
       </c>
       <c r="V31" t="n">
-        <v>96.2666665395101</v>
+        <v>265.5583333333333</v>
       </c>
       <c r="W31" t="n">
-        <v>-2.826700879725209</v>
+        <v>-6.877509586932717</v>
       </c>
       <c r="X31" t="n">
-        <v>1.187270859644502</v>
+        <v>-2.388096628966672</v>
       </c>
       <c r="Y31" t="n">
-        <v>-4.013971739369711</v>
+        <v>-4.489412957966046</v>
       </c>
       <c r="Z31" t="n">
-        <v>-3.93516862418446</v>
+        <v>-4.955413911295141</v>
       </c>
       <c r="AA31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB31" t="n">
-        <v>-0.06893202402059317</v>
+        <v>-0.1719242902208202</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.0667408220040222</v>
+        <v>0.1122881355932204</v>
       </c>
       <c r="AD31" t="n">
-        <v>-0.03378007645140479</v>
+        <v>-0.1367723426516319</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.01157219841620893</v>
+        <v>0.0571195120054071</v>
       </c>
       <c r="AF31" t="n">
-        <v>-0.04535227486761373</v>
+        <v>-0.193891854657039</v>
       </c>
       <c r="AG31" t="n">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="AH31" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="AI31" t="b">
         <v>0</v>
@@ -4784,30 +4784,32 @@
         <v>0</v>
       </c>
       <c r="AM31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN31" t="b">
         <v>0</v>
       </c>
-      <c r="AO31" t="inlineStr"/>
+      <c r="AO31" t="n">
+        <v>313.43</v>
+      </c>
       <c r="AP31" t="n">
-        <v>123.55</v>
+        <v>331.16</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4816,7 +4818,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>28.2</v>
+        <v>28.4</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4829,11 +4831,11 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>654000</v>
+        <v>4827000</v>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="K32" t="b">
         <v>0</v>
@@ -4842,7 +4844,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>654000</v>
+        <v>4827000</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -4851,61 +4853,61 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>438.5</v>
+        <v>246.5</v>
       </c>
       <c r="Q32" t="n">
-        <v>438.5</v>
+        <v>246.5</v>
       </c>
       <c r="R32" t="n">
-        <v>17463211</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>469.2</v>
+        <v>252.6</v>
       </c>
       <c r="T32" t="n">
-        <v>502.3</v>
+        <v>253.775</v>
       </c>
       <c r="U32" t="n">
-        <v>504.95</v>
+        <v>255.275</v>
       </c>
       <c r="V32" t="n">
-        <v>458.5333333333334</v>
+        <v>231.4583333333333</v>
       </c>
       <c r="W32" t="n">
-        <v>-13.39343952572915</v>
+        <v>0.3249832544698563</v>
       </c>
       <c r="X32" t="n">
-        <v>-4.426963086161363</v>
+        <v>3.490774806539403</v>
       </c>
       <c r="Y32" t="n">
-        <v>-8.966476439567787</v>
+        <v>-3.165791552069547</v>
       </c>
       <c r="Z32" t="n">
-        <v>-6.768474826993417</v>
+        <v>-2.639135006951672</v>
       </c>
       <c r="AA32" t="b">
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>-0.1078331637843337</v>
+        <v>-0.108499095840868</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.1819407008086253</v>
+        <v>0.3288409703504043</v>
       </c>
       <c r="AD32" t="n">
-        <v>-0.07268121621514534</v>
+        <v>-0.07334714827167965</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.1267720772208121</v>
+        <v>0.273672346762591</v>
       </c>
       <c r="AF32" t="n">
-        <v>-0.1994532934359574</v>
+        <v>-0.3470194950342707</v>
       </c>
       <c r="AG32" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AH32" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="AI32" t="b">
         <v>0</v>
@@ -4923,27 +4925,29 @@
         <v>0</v>
       </c>
       <c r="AN32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO32" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>282.49</v>
+      </c>
       <c r="AP32" t="n">
-        <v>558.66</v>
+        <v>259.66</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4952,7 +4956,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>28.2</v>
+        <v>28.4</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4965,83 +4969,83 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>5000</v>
+        <v>654000</v>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="n">
+        <v>29</v>
+      </c>
+      <c r="K33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33" t="b">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>654000</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>438.5</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>438.5</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>462.5</v>
+      </c>
+      <c r="T33" t="n">
+        <v>499.65</v>
+      </c>
+      <c r="U33" t="n">
+        <v>502.3</v>
+      </c>
+      <c r="V33" t="n">
+        <v>460.275</v>
+      </c>
+      <c r="W33" t="n">
+        <v>-16.13210472828047</v>
+      </c>
+      <c r="X33" t="n">
+        <v>-6.76799141458519</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>-9.364113313695277</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-8.966476439567781</v>
+      </c>
+      <c r="AA33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>-0.1078331637843337</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0.312874251497006</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>-0.07268121621514534</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0.2577056279091927</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>-0.3303868441243381</v>
+      </c>
+      <c r="AG33" t="n">
         <v>36</v>
       </c>
-      <c r="K33" t="b">
-        <v>0</v>
-      </c>
-      <c r="L33" t="b">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>5000</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>153.5</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>153.5</v>
-      </c>
-      <c r="R33" t="n">
-        <v>15925848</v>
-      </c>
-      <c r="S33" t="n">
-        <v>156.4</v>
-      </c>
-      <c r="T33" t="n">
-        <v>168.1</v>
-      </c>
-      <c r="U33" t="n">
-        <v>168.825</v>
-      </c>
-      <c r="V33" t="n">
-        <v>151.95</v>
-      </c>
-      <c r="W33" t="n">
-        <v>-3.466013085611394</v>
-      </c>
-      <c r="X33" t="n">
-        <v>-1.035168189013058</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>-2.430844896598336</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>-2.574592254334981</v>
-      </c>
-      <c r="AA33" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>-0.08630952380952384</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>0.1204379562043796</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>-0.05115757624033546</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>0.06526933261656631</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>-0.1164269088569018</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>40</v>
-      </c>
       <c r="AH33" t="n">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="AI33" t="b">
         <v>0</v>
@@ -5056,32 +5060,30 @@
         <v>0</v>
       </c>
       <c r="AM33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN33" t="b">
         <v>0</v>
       </c>
-      <c r="AO33" t="n">
-        <v>181.13</v>
-      </c>
+      <c r="AO33" t="inlineStr"/>
       <c r="AP33" t="n">
-        <v>186.37</v>
+        <v>561.37</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5090,7 +5092,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>27.8</v>
+        <v>28.2</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5103,11 +5105,11 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>6331000</v>
+        <v>1000</v>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="K34" t="b">
         <v>0</v>
@@ -5116,7 +5118,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>6331000</v>
+        <v>1000</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -5125,62 +5127,62 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1775</v>
+        <v>95.90000152587891</v>
       </c>
       <c r="Q34" t="n">
-        <v>1775</v>
+        <v>95.90000152587891</v>
       </c>
       <c r="R34" t="n">
-        <v>3474156</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>1909</v>
+        <v>99.18000030517578</v>
       </c>
       <c r="T34" t="n">
-        <v>1953.75</v>
+        <v>112.570000076294</v>
       </c>
       <c r="U34" t="n">
-        <v>1957</v>
+        <v>113.05</v>
       </c>
       <c r="V34" t="n">
-        <v>2041.566318766276</v>
+        <v>96.51499989827474</v>
       </c>
       <c r="W34" t="n">
-        <v>-31.191327043505</v>
+        <v>-3.505159855553586</v>
       </c>
       <c r="X34" t="n">
-        <v>0.5264307119879588</v>
+        <v>0.2487847166048847</v>
       </c>
       <c r="Y34" t="n">
-        <v>-31.71775775549296</v>
+        <v>-3.753944572158471</v>
       </c>
       <c r="Z34" t="n">
-        <v>-20.79496169016637</v>
+        <v>-4.013971739369711</v>
       </c>
       <c r="AA34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB34" t="n">
-        <v>-0.03532608695652173</v>
+        <v>-0.09099524620019994</v>
       </c>
       <c r="AC34" t="n">
-        <v>-0.2013169306551642</v>
+        <v>0.1839506361219618</v>
       </c>
       <c r="AD34" t="n">
-        <v>-0.0001741393873333497</v>
+        <v>-0.05584329863101156</v>
       </c>
       <c r="AE34" t="n">
-        <v>-0.2564855542429775</v>
+        <v>0.1287820125341486</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.2563114148556441</v>
+        <v>-0.1846253111651601</v>
       </c>
       <c r="AG34" t="n">
+        <v>42</v>
+      </c>
+      <c r="AH34" t="n">
         <v>56.00000000000001</v>
       </c>
-      <c r="AH34" t="n">
-        <v>10</v>
-      </c>
       <c r="AI34" t="b">
         <v>0</v>
       </c>
@@ -5194,30 +5196,30 @@
         <v>0</v>
       </c>
       <c r="AM34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN34" t="b">
         <v>0</v>
       </c>
       <c r="AO34" t="inlineStr"/>
       <c r="AP34" t="n">
-        <v>2103.16</v>
+        <v>124.55</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5226,7 +5228,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>27.2</v>
+        <v>27.8</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5239,11 +5241,11 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="K35" t="b">
         <v>0</v>
@@ -5252,7 +5254,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -5261,61 +5263,61 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>322</v>
+        <v>153.5</v>
       </c>
       <c r="Q35" t="n">
-        <v>322</v>
+        <v>153.5</v>
       </c>
       <c r="R35" t="n">
-        <v>8624935</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>321.5</v>
+        <v>155.4</v>
       </c>
       <c r="T35" t="n">
-        <v>328.75</v>
+        <v>167.225</v>
       </c>
       <c r="U35" t="n">
-        <v>329.875</v>
+        <v>168.1</v>
       </c>
       <c r="V35" t="n">
-        <v>326.5583333333333</v>
+        <v>152.4333333333333</v>
       </c>
       <c r="W35" t="n">
-        <v>-3.05164815738425</v>
+        <v>-3.701197657807711</v>
       </c>
       <c r="X35" t="n">
-        <v>-3.324663606940946</v>
+        <v>-1.568374082771988</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.2730154495566963</v>
+        <v>-2.132823575035723</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.1186949931720043</v>
+        <v>-2.430844896598336</v>
       </c>
       <c r="AA35" t="b">
         <v>1</v>
       </c>
       <c r="AB35" t="n">
-        <v>-0.06531204644412192</v>
+        <v>-0.1023391812865497</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>0.2329317269076305</v>
       </c>
       <c r="AD35" t="n">
-        <v>-0.03016009887493354</v>
+        <v>-0.06718723371736135</v>
       </c>
       <c r="AE35" t="n">
-        <v>-0.05516862358781327</v>
+        <v>0.1777631033198173</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.02500852471287973</v>
+        <v>-0.2449503370371786</v>
       </c>
       <c r="AG35" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AH35" t="n">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="AI35" t="b">
         <v>0</v>
@@ -5324,40 +5326,38 @@
         <v>0</v>
       </c>
       <c r="AK35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM35" t="b">
         <v>1</v>
       </c>
       <c r="AN35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>177.75</v>
       </c>
       <c r="AP35" t="n">
-        <v>349.11</v>
+        <v>187.45</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5366,7 +5366,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>26.6</v>
+        <v>26.8</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5379,11 +5379,11 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>7582000</v>
+        <v>79618000</v>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K36" t="b">
         <v>1</v>
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>7582000</v>
+        <v>79618000</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -5401,61 +5401,61 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>1560</v>
+        <v>125.5</v>
       </c>
       <c r="Q36" t="n">
-        <v>1560</v>
+        <v>125.5</v>
       </c>
       <c r="R36" t="n">
-        <v>10096638</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>1613</v>
+        <v>127.5</v>
       </c>
       <c r="T36" t="n">
-        <v>1819.5</v>
+        <v>143.7</v>
       </c>
       <c r="U36" t="n">
-        <v>1835.25</v>
+        <v>145.425</v>
       </c>
       <c r="V36" t="n">
-        <v>1763.583333333333</v>
+        <v>133.6166666666667</v>
       </c>
       <c r="W36" t="n">
-        <v>-72.45623813198699</v>
+        <v>-5.870555737754358</v>
       </c>
       <c r="X36" t="n">
-        <v>-33.83914012632216</v>
+        <v>-3.491393446079607</v>
       </c>
       <c r="Y36" t="n">
-        <v>-38.61709800566483</v>
+        <v>-2.379162291674752</v>
       </c>
       <c r="Z36" t="n">
-        <v>-40.29535017487417</v>
+        <v>-2.820039030693448</v>
       </c>
       <c r="AA36" t="b">
         <v>1</v>
       </c>
       <c r="AB36" t="n">
-        <v>-0.168</v>
+        <v>-0.215625</v>
       </c>
       <c r="AC36" t="n">
-        <v>-0.1111111111111112</v>
+        <v>0.105726872246696</v>
       </c>
       <c r="AD36" t="n">
-        <v>-0.1328480524308117</v>
+        <v>-0.1804730524308116</v>
       </c>
       <c r="AE36" t="n">
-        <v>-0.1662797346989244</v>
+        <v>0.0505582486588827</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.03343168226811277</v>
+        <v>-0.2310313010896943</v>
       </c>
       <c r="AG36" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AH36" t="n">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="AI36" t="b">
         <v>0</v>
@@ -5477,23 +5477,23 @@
       </c>
       <c r="AO36" t="inlineStr"/>
       <c r="AP36" t="n">
-        <v>2173.16</v>
+        <v>179.16</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5502,7 +5502,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>25.2</v>
+        <v>25.6</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5515,20 +5515,20 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>470000</v>
+        <v>7582000</v>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="K37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" t="b">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>470000</v>
+        <v>7582000</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -5537,61 +5537,61 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>3065</v>
+        <v>1560</v>
       </c>
       <c r="Q37" t="n">
-        <v>3065</v>
+        <v>1560</v>
       </c>
       <c r="R37" t="n">
-        <v>730172</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>3137</v>
+        <v>1598</v>
       </c>
       <c r="T37" t="n">
-        <v>3188.5</v>
+        <v>1802.5</v>
       </c>
       <c r="U37" t="n">
-        <v>3209.5</v>
+        <v>1819.5</v>
       </c>
       <c r="V37" t="n">
-        <v>3041.75</v>
+        <v>1763.25</v>
       </c>
       <c r="W37" t="n">
-        <v>-28.07613189820859</v>
+        <v>-76.18148225963637</v>
       </c>
       <c r="X37" t="n">
-        <v>-23.61539468157735</v>
+        <v>-42.307608552985</v>
       </c>
       <c r="Y37" t="n">
-        <v>-4.460737216631241</v>
+        <v>-33.87387370665137</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.008477254227724</v>
+        <v>-38.61709800566484</v>
       </c>
       <c r="AA37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB37" t="n">
-        <v>-0.1205164992826399</v>
+        <v>-0.1789473684210526</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.1522556390977443</v>
+        <v>-0.01265822784810122</v>
       </c>
       <c r="AD37" t="n">
-        <v>-0.08536455171345148</v>
+        <v>-0.1437954208518643</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.09708701550993104</v>
+        <v>-0.06782685143591449</v>
       </c>
       <c r="AF37" t="n">
-        <v>-0.1824515672233825</v>
+        <v>-0.07596856941594976</v>
       </c>
       <c r="AG37" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="AH37" t="n">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="AI37" t="b">
         <v>0</v>
@@ -5606,32 +5606,30 @@
         <v>0</v>
       </c>
       <c r="AM37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN37" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>3120.17</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO37" t="inlineStr"/>
       <c r="AP37" t="n">
-        <v>3830</v>
+        <v>2155.26</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5640,7 +5638,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>24.8</v>
+        <v>25</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5653,11 +5651,11 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>4827000</v>
+        <v>6331000</v>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K38" t="b">
         <v>0</v>
@@ -5666,7 +5664,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>4827000</v>
+        <v>6331000</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -5675,61 +5673,61 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>246.5</v>
+        <v>1775</v>
       </c>
       <c r="Q38" t="n">
-        <v>246.5</v>
+        <v>1775</v>
       </c>
       <c r="R38" t="n">
-        <v>23017388</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>255</v>
+        <v>1868</v>
       </c>
       <c r="T38" t="n">
-        <v>255.275</v>
+        <v>1946.75</v>
       </c>
       <c r="U38" t="n">
-        <v>257.15</v>
+        <v>1953.75</v>
       </c>
       <c r="V38" t="n">
-        <v>230.4416666666667</v>
+        <v>2037.416666666667</v>
       </c>
       <c r="W38" t="n">
-        <v>1.643087687605117</v>
+        <v>-43.45481511940807</v>
       </c>
       <c r="X38" t="n">
-        <v>4.282222694556783</v>
+        <v>-8.269818454290421</v>
       </c>
       <c r="Y38" t="n">
-        <v>-2.639135006951665</v>
+        <v>-35.18499666511764</v>
       </c>
       <c r="Z38" t="n">
-        <v>-1.451056549604886</v>
+        <v>-31.71775775549331</v>
       </c>
       <c r="AA38" t="b">
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>-0.1320422535211268</v>
+        <v>-0.07310704960835512</v>
       </c>
       <c r="AC38" t="n">
-        <v>0.1966019417475728</v>
+        <v>-0.1230146708437178</v>
       </c>
       <c r="AD38" t="n">
-        <v>-0.09689030595193837</v>
+        <v>-0.03795510203916674</v>
       </c>
       <c r="AE38" t="n">
-        <v>0.1414333181597596</v>
+        <v>-0.178183294431531</v>
       </c>
       <c r="AF38" t="n">
-        <v>-0.2383236241116979</v>
+        <v>0.1402281923923643</v>
       </c>
       <c r="AG38" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="AH38" t="n">
-        <v>76</v>
+        <v>12</v>
       </c>
       <c r="AI38" t="b">
         <v>0</v>
@@ -5747,29 +5745,27 @@
         <v>0</v>
       </c>
       <c r="AN38" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>276.57</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO38" t="inlineStr"/>
       <c r="AP38" t="n">
-        <v>285.74</v>
+        <v>2070.79</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5778,7 +5774,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>24.4</v>
+        <v>24.8</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5791,20 +5787,20 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>79618000</v>
+        <v>2504000</v>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="K39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" t="b">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>79618000</v>
+        <v>2504000</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -5813,61 +5809,61 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>125.5</v>
+        <v>4890</v>
       </c>
       <c r="Q39" t="n">
-        <v>125.5</v>
+        <v>4890</v>
       </c>
       <c r="R39" t="n">
-        <v>88183899</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>129</v>
+        <v>4984</v>
       </c>
       <c r="T39" t="n">
-        <v>145.425</v>
+        <v>5368</v>
       </c>
       <c r="U39" t="n">
-        <v>147</v>
+        <v>5390.75</v>
       </c>
       <c r="V39" t="n">
-        <v>133.4166666666667</v>
+        <v>5522.75</v>
       </c>
       <c r="W39" t="n">
-        <v>-5.716641903854367</v>
+        <v>-162.9110538741979</v>
       </c>
       <c r="X39" t="n">
-        <v>-2.896602873160918</v>
+        <v>-70.03737391815289</v>
       </c>
       <c r="Y39" t="n">
-        <v>-2.820039030693448</v>
+        <v>-92.87367995604504</v>
       </c>
       <c r="Z39" t="n">
-        <v>-3.098257639195204</v>
+        <v>-99.510181400411</v>
       </c>
       <c r="AA39" t="b">
         <v>1</v>
       </c>
       <c r="AB39" t="n">
-        <v>-0.2006369426751592</v>
+        <v>-0.08512628624883067</v>
       </c>
       <c r="AC39" t="n">
-        <v>-0.003968253968253954</v>
+        <v>-0.05324298160696994</v>
       </c>
       <c r="AD39" t="n">
-        <v>-0.1654849951059708</v>
+        <v>-0.04997433867964229</v>
       </c>
       <c r="AE39" t="n">
-        <v>-0.05913687755606722</v>
+        <v>-0.1084116051947832</v>
       </c>
       <c r="AF39" t="n">
-        <v>-0.1063481175499036</v>
+        <v>0.05843726651514092</v>
       </c>
       <c r="AG39" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="AH39" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="AI39" t="b">
         <v>0</v>
@@ -5889,23 +5885,23 @@
       </c>
       <c r="AO39" t="inlineStr"/>
       <c r="AP39" t="n">
-        <v>180.97</v>
+        <v>6123.16</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5927,11 +5923,11 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>2504000</v>
+        <v>3281561</v>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K40" t="b">
         <v>0</v>
@@ -5940,7 +5936,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>2504000</v>
+        <v>3281561</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -5949,61 +5945,61 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>4890</v>
+        <v>1840</v>
       </c>
       <c r="Q40" t="n">
-        <v>4890</v>
+        <v>1840</v>
       </c>
       <c r="R40" t="n">
-        <v>818727</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>5047</v>
+        <v>1874</v>
       </c>
       <c r="T40" t="n">
-        <v>5390.75</v>
+        <v>2061.5</v>
       </c>
       <c r="U40" t="n">
-        <v>5421</v>
+        <v>2075.25</v>
       </c>
       <c r="V40" t="n">
-        <v>5527.333333333333</v>
+        <v>2143.447033691406</v>
       </c>
       <c r="W40" t="n">
-        <v>-146.3291353295526</v>
+        <v>-90.28944482571478</v>
       </c>
       <c r="X40" t="n">
-        <v>-46.81895392914208</v>
+        <v>-65.26326544828217</v>
       </c>
       <c r="Y40" t="n">
-        <v>-99.51018140041054</v>
+        <v>-25.02617937743261</v>
       </c>
       <c r="Z40" t="n">
-        <v>-95.17712545095225</v>
+        <v>-29.51609433477743</v>
       </c>
       <c r="AA40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB40" t="n">
-        <v>-0.1101000909918107</v>
+        <v>-0.1300236406619385</v>
       </c>
       <c r="AC40" t="n">
-        <v>-0.1451048951048951</v>
+        <v>0.03261376660334414</v>
       </c>
       <c r="AD40" t="n">
-        <v>-0.07494814342262235</v>
+        <v>-0.09487169309275012</v>
       </c>
       <c r="AE40" t="n">
-        <v>-0.2002735186927084</v>
+        <v>-0.02255485698446913</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.125325375270086</v>
+        <v>-0.07231683610828099</v>
       </c>
       <c r="AG40" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AH40" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="AI40" t="b">
         <v>0</v>
@@ -6018,30 +6014,32 @@
         <v>0</v>
       </c>
       <c r="AM40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO40" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>2123.36</v>
+      </c>
       <c r="AP40" t="n">
-        <v>5872.11</v>
+        <v>2338.16</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6050,7 +6048,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>20.4</v>
+        <v>21.6</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -6063,11 +6061,11 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1000</v>
+        <v>470000</v>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="n">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="K41" t="b">
         <v>0</v>
@@ -6076,7 +6074,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1000</v>
+        <v>470000</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -6085,61 +6083,61 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>826</v>
+        <v>3065</v>
       </c>
       <c r="Q41" t="n">
-        <v>826</v>
+        <v>3065</v>
       </c>
       <c r="R41" t="n">
-        <v>10475522</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>866.8</v>
+        <v>3126</v>
       </c>
       <c r="T41" t="n">
-        <v>1013.05</v>
+        <v>3156.75</v>
       </c>
       <c r="U41" t="n">
-        <v>1018.3</v>
+        <v>3188.5</v>
       </c>
       <c r="V41" t="n">
-        <v>961.7833333333333</v>
+        <v>3051.5</v>
       </c>
       <c r="W41" t="n">
-        <v>-50.72161287392692</v>
+        <v>-33.31778705381976</v>
       </c>
       <c r="X41" t="n">
-        <v>-15.74076083912792</v>
+        <v>-25.5558731560258</v>
       </c>
       <c r="Y41" t="n">
-        <v>-34.98085203479899</v>
+        <v>-7.76191389779396</v>
       </c>
       <c r="Z41" t="n">
-        <v>-36.16954285647221</v>
+        <v>-4.46073721663128</v>
       </c>
       <c r="AA41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>-0.1127819548872181</v>
+        <v>-0.1716216216216216</v>
       </c>
       <c r="AC41" t="n">
-        <v>-0.2244131455399061</v>
+        <v>0.2358870967741935</v>
       </c>
       <c r="AD41" t="n">
-        <v>-0.07763000731802971</v>
+        <v>-0.1364696740524333</v>
       </c>
       <c r="AE41" t="n">
-        <v>-0.2795817691277194</v>
+        <v>0.1807184731863802</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.2019517618096897</v>
+        <v>-0.3171881472388135</v>
       </c>
       <c r="AG41" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="AH41" t="n">
-        <v>8</v>
+        <v>68</v>
       </c>
       <c r="AI41" t="b">
         <v>0</v>
@@ -6154,30 +6152,32 @@
         <v>0</v>
       </c>
       <c r="AM41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO41" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>3156.95</v>
+      </c>
       <c r="AP41" t="n">
-        <v>1167.89</v>
+        <v>3571.58</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6186,7 +6186,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>19.6</v>
+        <v>19.8</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K42" t="b">
         <v>0</v>
@@ -6221,61 +6221,61 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>1100</v>
+        <v>414</v>
       </c>
       <c r="Q42" t="n">
-        <v>1100</v>
+        <v>414</v>
       </c>
       <c r="R42" t="n">
-        <v>604282</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>1130</v>
+        <v>424.5</v>
       </c>
       <c r="T42" t="n">
-        <v>1182.75</v>
+        <v>484.7</v>
       </c>
       <c r="U42" t="n">
-        <v>1189.75</v>
+        <v>488.85</v>
       </c>
       <c r="V42" t="n">
-        <v>1329.833333333333</v>
+        <v>486.525</v>
       </c>
       <c r="W42" t="n">
-        <v>-33.6205793875979</v>
+        <v>-24.45214372603164</v>
       </c>
       <c r="X42" t="n">
-        <v>-29.97258828741357</v>
+        <v>-15.73211407377383</v>
       </c>
       <c r="Y42" t="n">
-        <v>-3.647991100184328</v>
+        <v>-8.720029652257804</v>
       </c>
       <c r="Z42" t="n">
-        <v>-2.192118040303779</v>
+        <v>-9.928546608342646</v>
       </c>
       <c r="AA42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB42" t="n">
-        <v>-0.1129032258064516</v>
+        <v>-0.1670020120724346</v>
       </c>
       <c r="AC42" t="n">
-        <v>-0.2361111111111112</v>
+        <v>0.05477707006369426</v>
       </c>
       <c r="AD42" t="n">
-        <v>-0.07775127823726324</v>
+        <v>-0.1318500645032462</v>
       </c>
       <c r="AE42" t="n">
-        <v>-0.2912797346989244</v>
+        <v>-0.0003915535241190149</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.2135284564616612</v>
+        <v>-0.1314585109791272</v>
       </c>
       <c r="AG42" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AH42" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="AI42" t="b">
         <v>0</v>
@@ -6290,32 +6290,30 @@
         <v>0</v>
       </c>
       <c r="AM42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN42" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO42" t="n">
-        <v>1141.8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO42" t="inlineStr"/>
       <c r="AP42" t="n">
-        <v>1347.11</v>
+        <v>589.42</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6324,7 +6322,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>19</v>
+        <v>19.4</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6337,11 +6335,11 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>3281561</v>
+        <v>1000</v>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="K43" t="b">
         <v>0</v>
@@ -6350,7 +6348,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3281561</v>
+        <v>1000</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -6359,61 +6357,61 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>1840</v>
+        <v>1100</v>
       </c>
       <c r="Q43" t="n">
-        <v>1840</v>
+        <v>1100</v>
       </c>
       <c r="R43" t="n">
-        <v>4704079</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>1875</v>
+        <v>1119</v>
       </c>
       <c r="T43" t="n">
-        <v>2075.25</v>
+        <v>1174.75</v>
       </c>
       <c r="U43" t="n">
-        <v>2090.75</v>
+        <v>1182.75</v>
       </c>
       <c r="V43" t="n">
-        <v>2142.478466796875</v>
+        <v>1325.416666666667</v>
       </c>
       <c r="W43" t="n">
-        <v>-88.52281493870146</v>
+        <v>-34.42748812810032</v>
       </c>
       <c r="X43" t="n">
-        <v>-59.00672060392436</v>
+        <v>-30.86356825555092</v>
       </c>
       <c r="Y43" t="n">
-        <v>-29.51609433477709</v>
+        <v>-3.563919872549398</v>
       </c>
       <c r="Z43" t="n">
-        <v>-31.17828486980208</v>
+        <v>-3.647991100184328</v>
       </c>
       <c r="AA43" t="b">
         <v>1</v>
       </c>
       <c r="AB43" t="n">
-        <v>-0.1441860465116279</v>
+        <v>-0.126984126984127</v>
       </c>
       <c r="AC43" t="n">
-        <v>-0.04467501617741476</v>
+        <v>-0.1941391941391941</v>
       </c>
       <c r="AD43" t="n">
-        <v>-0.1090340989424395</v>
+        <v>-0.0918321794149386</v>
       </c>
       <c r="AE43" t="n">
-        <v>-0.09984363976522803</v>
+        <v>-0.2493078177270074</v>
       </c>
       <c r="AF43" t="n">
-        <v>-0.009190459177211507</v>
+        <v>0.1574756383120688</v>
       </c>
       <c r="AG43" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="AH43" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="AI43" t="b">
         <v>0</v>
@@ -6431,29 +6429,29 @@
         <v>1</v>
       </c>
       <c r="AN43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO43" t="n">
-        <v>2174.88</v>
+        <v>1141.8</v>
       </c>
       <c r="AP43" t="n">
-        <v>2362.63</v>
+        <v>1308.68</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6462,7 +6460,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>18.8</v>
+        <v>18.2</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6475,11 +6473,11 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>201900</v>
+        <v>1000</v>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="K44" t="b">
         <v>0</v>
@@ -6488,7 +6486,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>201900</v>
+        <v>1000</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
@@ -6497,62 +6495,62 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>16010</v>
+        <v>826</v>
       </c>
       <c r="Q44" t="n">
-        <v>16010</v>
+        <v>826</v>
       </c>
       <c r="R44" t="n">
-        <v>257879</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>16177</v>
+        <v>851.6</v>
       </c>
       <c r="T44" t="n">
-        <v>18008</v>
+        <v>1005.8</v>
       </c>
       <c r="U44" t="n">
-        <v>18198.5</v>
+        <v>1013.05</v>
       </c>
       <c r="V44" t="n">
-        <v>17154.75</v>
+        <v>959.5666666666667</v>
       </c>
       <c r="W44" t="n">
-        <v>-653.0660529011802</v>
+        <v>-54.69348962362608</v>
       </c>
       <c r="X44" t="n">
-        <v>-461.2584187191773</v>
+        <v>-23.53130659602756</v>
       </c>
       <c r="Y44" t="n">
-        <v>-191.8076341820029</v>
+        <v>-31.16218302759852</v>
       </c>
       <c r="Z44" t="n">
-        <v>-233.9971574775291</v>
+        <v>-34.98085203479899</v>
       </c>
       <c r="AA44" t="b">
         <v>1</v>
       </c>
       <c r="AB44" t="n">
-        <v>-0.1922300706357215</v>
+        <v>-0.149330587023687</v>
       </c>
       <c r="AC44" t="n">
-        <v>0.08948621980265403</v>
+        <v>-0.1386861313868614</v>
       </c>
       <c r="AD44" t="n">
-        <v>-0.1570781230665331</v>
+        <v>-0.1141786394544986</v>
       </c>
       <c r="AE44" t="n">
-        <v>0.03431759621484076</v>
+        <v>-0.1938547549746746</v>
       </c>
       <c r="AF44" t="n">
-        <v>-0.1913957192813739</v>
+        <v>0.07967611552017606</v>
       </c>
       <c r="AG44" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH44" t="n">
         <v>10</v>
       </c>
-      <c r="AH44" t="n">
-        <v>57.99999999999999</v>
-      </c>
       <c r="AI44" t="b">
         <v>0</v>
       </c>
@@ -6569,29 +6567,27 @@
         <v>1</v>
       </c>
       <c r="AN44" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO44" t="n">
-        <v>18187.36</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO44" t="inlineStr"/>
       <c r="AP44" t="n">
-        <v>23008.16</v>
+        <v>1139.26</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6600,7 +6596,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>17.8</v>
+        <v>18</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6613,11 +6609,11 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>5143000</v>
+        <v>478000</v>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="K45" t="b">
         <v>0</v>
@@ -6626,7 +6622,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>5143000</v>
+        <v>478000</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
@@ -6635,61 +6631,61 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>4010</v>
+        <v>764</v>
       </c>
       <c r="Q45" t="n">
-        <v>4010</v>
+        <v>764</v>
       </c>
       <c r="R45" t="n">
-        <v>6932946</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>4151</v>
+        <v>788.8</v>
       </c>
       <c r="T45" t="n">
-        <v>4678.25</v>
+        <v>843.6</v>
       </c>
       <c r="U45" t="n">
-        <v>4728.25</v>
+        <v>850.3</v>
       </c>
       <c r="V45" t="n">
-        <v>4297</v>
+        <v>935.8</v>
       </c>
       <c r="W45" t="n">
-        <v>-183.8243712372605</v>
+        <v>-29.02271865090165</v>
       </c>
       <c r="X45" t="n">
-        <v>-98.6212320238939</v>
+        <v>-21.78708474720425</v>
       </c>
       <c r="Y45" t="n">
-        <v>-85.2031392133666</v>
+        <v>-7.235633903697405</v>
       </c>
       <c r="Z45" t="n">
-        <v>-90.32850634505149</v>
+        <v>-6.64112264341037</v>
       </c>
       <c r="AA45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>-0.1996007984031936</v>
+        <v>-0.1492204899777283</v>
       </c>
       <c r="AC45" t="n">
-        <v>0.08967391304347827</v>
+        <v>-0.2509803921568627</v>
       </c>
       <c r="AD45" t="n">
-        <v>-0.1644488508340052</v>
+        <v>-0.1140685424085399</v>
       </c>
       <c r="AE45" t="n">
-        <v>0.034505289455665</v>
+        <v>-0.306149015744676</v>
       </c>
       <c r="AF45" t="n">
-        <v>-0.1989541402896702</v>
+        <v>0.1920804733361361</v>
       </c>
       <c r="AG45" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="AH45" t="n">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="AI45" t="b">
         <v>0</v>
@@ -6704,30 +6700,32 @@
         <v>0</v>
       </c>
       <c r="AM45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO45" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>846.51</v>
+      </c>
       <c r="AP45" t="n">
-        <v>5883.42</v>
+        <v>975.79</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6736,7 +6734,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>17.4</v>
+        <v>17.6</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6749,11 +6747,11 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1000</v>
+        <v>5143000</v>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="K46" t="b">
         <v>0</v>
@@ -6762,7 +6760,7 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>1000</v>
+        <v>5143000</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
@@ -6771,61 +6769,61 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>1980</v>
+        <v>4010</v>
       </c>
       <c r="Q46" t="n">
-        <v>1980</v>
+        <v>4010</v>
       </c>
       <c r="R46" t="n">
-        <v>2228594</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>1999</v>
+        <v>4103</v>
       </c>
       <c r="T46" t="n">
-        <v>2194.5</v>
+        <v>4619.75</v>
       </c>
       <c r="U46" t="n">
-        <v>2214.25</v>
+        <v>4678.25</v>
       </c>
       <c r="V46" t="n">
-        <v>2127.25</v>
+        <v>4308.583333333333</v>
       </c>
       <c r="W46" t="n">
-        <v>-66.02132919008454</v>
+        <v>-190.4685026834113</v>
       </c>
       <c r="X46" t="n">
-        <v>-29.98641012823243</v>
+        <v>-116.9906861557974</v>
       </c>
       <c r="Y46" t="n">
-        <v>-36.03491906185211</v>
+        <v>-73.47781652761395</v>
       </c>
       <c r="Z46" t="n">
-        <v>-40.29112695807616</v>
+        <v>-85.20313921336663</v>
       </c>
       <c r="AA46" t="b">
         <v>1</v>
       </c>
       <c r="AB46" t="n">
-        <v>-0.1663157894736842</v>
+        <v>-0.2258687258687259</v>
       </c>
       <c r="AC46" t="n">
-        <v>-0.05714285714285716</v>
+        <v>0.2096530920060331</v>
       </c>
       <c r="AD46" t="n">
-        <v>-0.1311638419044958</v>
+        <v>-0.1907167782995375</v>
       </c>
       <c r="AE46" t="n">
-        <v>-0.1123114807306704</v>
+        <v>0.1544844684182198</v>
       </c>
       <c r="AF46" t="n">
-        <v>-0.01885236117382538</v>
+        <v>-0.3452012467177573</v>
       </c>
       <c r="AG46" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="AH46" t="n">
-        <v>20</v>
+        <v>57.99999999999999</v>
       </c>
       <c r="AI46" t="b">
         <v>0</v>
@@ -6847,23 +6845,23 @@
       </c>
       <c r="AO46" t="inlineStr"/>
       <c r="AP46" t="n">
-        <v>2665.79</v>
+        <v>5826.84</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6872,7 +6870,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>16.2</v>
+        <v>17.4</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6885,11 +6883,11 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>478000</v>
+        <v>2887848</v>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="K47" t="b">
         <v>0</v>
@@ -6898,7 +6896,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>478000</v>
+        <v>2887848</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
@@ -6907,61 +6905,61 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>764</v>
+        <v>1875</v>
       </c>
       <c r="Q47" t="n">
-        <v>764</v>
+        <v>1875</v>
       </c>
       <c r="R47" t="n">
-        <v>1925674</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>802.8</v>
+        <v>1920</v>
       </c>
       <c r="T47" t="n">
-        <v>850.3</v>
+        <v>2239</v>
       </c>
       <c r="U47" t="n">
-        <v>857.1</v>
+        <v>2257.5</v>
       </c>
       <c r="V47" t="n">
-        <v>940.0666666666667</v>
+        <v>2167.916666666667</v>
       </c>
       <c r="W47" t="n">
-        <v>-26.61929891469026</v>
+        <v>-107.5096521184209</v>
       </c>
       <c r="X47" t="n">
-        <v>-19.97817627127996</v>
+        <v>-56.06220321837168</v>
       </c>
       <c r="Y47" t="n">
-        <v>-6.641122643410299</v>
+        <v>-51.44744890004927</v>
       </c>
       <c r="Z47" t="n">
-        <v>-3.874339081718187</v>
+        <v>-58.99771901609137</v>
       </c>
       <c r="AA47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB47" t="n">
-        <v>-0.1511111111111111</v>
+        <v>-0.1648106904231625</v>
       </c>
       <c r="AC47" t="n">
-        <v>-0.3178571428571428</v>
+        <v>-0.1534988713318285</v>
       </c>
       <c r="AD47" t="n">
-        <v>-0.1159591635419227</v>
+        <v>-0.1296587428539742</v>
       </c>
       <c r="AE47" t="n">
-        <v>-0.3730257664449561</v>
+        <v>-0.2086674949196418</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.2570666029030334</v>
+        <v>0.0790087520656676</v>
       </c>
       <c r="AG47" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AH47" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AI47" t="b">
         <v>0</v>
@@ -6976,32 +6974,30 @@
         <v>0</v>
       </c>
       <c r="AM47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN47" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO47" t="n">
-        <v>838.87</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO47" t="inlineStr"/>
       <c r="AP47" t="n">
-        <v>988.84</v>
+        <v>2723.16</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7010,7 +7006,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>15.2</v>
+        <v>17.2</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -7023,11 +7019,11 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>2887848</v>
+        <v>201900</v>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="K48" t="b">
         <v>0</v>
@@ -7036,7 +7032,7 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>2887848</v>
+        <v>201900</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
@@ -7045,61 +7041,61 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>1875</v>
+        <v>16010</v>
       </c>
       <c r="Q48" t="n">
-        <v>1875</v>
+        <v>16010</v>
       </c>
       <c r="R48" t="n">
-        <v>2078527</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>1948</v>
+        <v>16083</v>
       </c>
       <c r="T48" t="n">
-        <v>2257.5</v>
+        <v>17763.25</v>
       </c>
       <c r="U48" t="n">
-        <v>2278.75</v>
+        <v>18008</v>
       </c>
       <c r="V48" t="n">
-        <v>2173.583333333333</v>
+        <v>17201.08333333333</v>
       </c>
       <c r="W48" t="n">
-        <v>-102.1980600094507</v>
+        <v>-640.9248364591585</v>
       </c>
       <c r="X48" t="n">
-        <v>-43.20034099335948</v>
+        <v>-497.1917022671736</v>
       </c>
       <c r="Y48" t="n">
-        <v>-58.99771901609125</v>
+        <v>-143.733134191985</v>
       </c>
       <c r="Z48" t="n">
-        <v>-62.41437946930179</v>
+        <v>-191.8076341820029</v>
       </c>
       <c r="AA48" t="b">
         <v>1</v>
       </c>
       <c r="AB48" t="n">
-        <v>-0.1847826086956522</v>
+        <v>-0.2341545084907917</v>
       </c>
       <c r="AC48" t="n">
-        <v>-0.1279069767441861</v>
+        <v>0.2101284958427816</v>
       </c>
       <c r="AD48" t="n">
-        <v>-0.1496306611264638</v>
+        <v>-0.1990025609216033</v>
       </c>
       <c r="AE48" t="n">
-        <v>-0.1830756003319993</v>
+        <v>0.1549598722549683</v>
       </c>
       <c r="AF48" t="n">
-        <v>0.03344493920553548</v>
+        <v>-0.3539624331765716</v>
       </c>
       <c r="AG48" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AH48" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="AI48" t="b">
         <v>0</v>
@@ -7117,17 +7113,19 @@
         <v>1</v>
       </c>
       <c r="AN48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO48" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>17643.02</v>
+      </c>
       <c r="AP48" t="n">
-        <v>2647.63</v>
+        <v>22125.53</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -7146,7 +7144,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -7187,55 +7185,55 @@
         <v>4795</v>
       </c>
       <c r="R49" t="n">
-        <v>475249</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>5009</v>
+        <v>4936</v>
       </c>
       <c r="T49" t="n">
+        <v>5549.75</v>
+      </c>
+      <c r="U49" t="n">
         <v>5598.25</v>
       </c>
-      <c r="U49" t="n">
-        <v>5648.25</v>
-      </c>
       <c r="V49" t="n">
-        <v>6213.166666666667</v>
+        <v>6194.166666666667</v>
       </c>
       <c r="W49" t="n">
-        <v>-316.2208937230052</v>
+        <v>-320.9953367468215</v>
       </c>
       <c r="X49" t="n">
-        <v>-252.1344951354536</v>
+        <v>-265.9066634577269</v>
       </c>
       <c r="Y49" t="n">
-        <v>-64.08639858755168</v>
+        <v>-55.08867328909463</v>
       </c>
       <c r="Z49" t="n">
-        <v>-61.90850408488279</v>
+        <v>-64.08639858755203</v>
       </c>
       <c r="AA49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB49" t="n">
-        <v>-0.1725625539257981</v>
+        <v>-0.1682567215958369</v>
       </c>
       <c r="AC49" t="n">
-        <v>-0.2501954652071932</v>
+        <v>-0.1920808761583824</v>
       </c>
       <c r="AD49" t="n">
-        <v>-0.1374106063566097</v>
+        <v>-0.1331047740266486</v>
       </c>
       <c r="AE49" t="n">
-        <v>-0.3053640887950064</v>
+        <v>-0.2472494997461957</v>
       </c>
       <c r="AF49" t="n">
-        <v>0.1679534824383967</v>
+        <v>0.1141447257195471</v>
       </c>
       <c r="AG49" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AH49" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AI49" t="b">
         <v>0</v>
@@ -7250,32 +7248,32 @@
         <v>0</v>
       </c>
       <c r="AM49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN49" t="b">
         <v>1</v>
       </c>
       <c r="AO49" t="n">
-        <v>5523.84</v>
+        <v>5418.35</v>
       </c>
       <c r="AP49" t="n">
-        <v>6610.53</v>
+        <v>6789.47</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7284,7 +7282,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>14.6</v>
+        <v>15.4</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7301,7 +7299,7 @@
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K50" t="b">
         <v>0</v>
@@ -7319,61 +7317,61 @@
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>414</v>
+        <v>1980</v>
       </c>
       <c r="Q50" t="n">
-        <v>414</v>
+        <v>1980</v>
       </c>
       <c r="R50" t="n">
-        <v>32213621</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>431.2</v>
+        <v>1995</v>
       </c>
       <c r="T50" t="n">
-        <v>488.85</v>
+        <v>2171.5</v>
       </c>
       <c r="U50" t="n">
-        <v>493.95</v>
+        <v>2194.5</v>
       </c>
       <c r="V50" t="n">
-        <v>486.1666666666667</v>
+        <v>2127.916666666667</v>
       </c>
       <c r="W50" t="n">
-        <v>-23.48065326905203</v>
+        <v>-67.67686704560629</v>
       </c>
       <c r="X50" t="n">
-        <v>-13.55210666070938</v>
+        <v>-37.52450151170718</v>
       </c>
       <c r="Y50" t="n">
-        <v>-9.928546608342643</v>
+        <v>-30.15236553389911</v>
       </c>
       <c r="Z50" t="n">
-        <v>-10.16689694697374</v>
+        <v>-36.03491906185214</v>
       </c>
       <c r="AA50" t="b">
         <v>1</v>
       </c>
       <c r="AB50" t="n">
-        <v>-0.1976744186046512</v>
+        <v>-0.1885245901639344</v>
       </c>
       <c r="AC50" t="n">
-        <v>-0.05045871559633031</v>
+        <v>0.02061855670103085</v>
       </c>
       <c r="AD50" t="n">
-        <v>-0.1625224710354628</v>
+        <v>-0.153372642594746</v>
       </c>
       <c r="AE50" t="n">
-        <v>-0.1056273391841436</v>
+        <v>-0.03455006688678242</v>
       </c>
       <c r="AF50" t="n">
-        <v>-0.05689513185131923</v>
+        <v>-0.1188225757079636</v>
       </c>
       <c r="AG50" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AH50" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AI50" t="b">
         <v>0</v>
@@ -7393,15 +7391,17 @@
       <c r="AN50" t="b">
         <v>0</v>
       </c>
-      <c r="AO50" t="inlineStr"/>
+      <c r="AO50" t="n">
+        <v>2320.56</v>
+      </c>
       <c r="AP50" t="n">
-        <v>575.79</v>
+        <v>2526.58</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -7420,7 +7420,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>14.4</v>
+        <v>14.2</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7461,55 +7461,55 @@
         <v>450</v>
       </c>
       <c r="R51" t="n">
-        <v>1225780</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>481.6</v>
+        <v>467.6</v>
       </c>
       <c r="T51" t="n">
+        <v>542.3</v>
+      </c>
+      <c r="U51" t="n">
         <v>550.05</v>
       </c>
-      <c r="U51" t="n">
-        <v>558.45</v>
-      </c>
       <c r="V51" t="n">
-        <v>543.2583333333333</v>
+        <v>543.6416666666667</v>
       </c>
       <c r="W51" t="n">
-        <v>-28.27015938495214</v>
+        <v>-30.78187537546307</v>
       </c>
       <c r="X51" t="n">
-        <v>-15.01912680568043</v>
+        <v>-18.17167651963695</v>
       </c>
       <c r="Y51" t="n">
-        <v>-13.25103257927171</v>
+        <v>-12.61019885582613</v>
       </c>
       <c r="Z51" t="n">
-        <v>-11.92112440263781</v>
+        <v>-13.25103257927172</v>
       </c>
       <c r="AA51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB51" t="n">
-        <v>-0.2718446601941747</v>
+        <v>-0.2561983471074381</v>
       </c>
       <c r="AC51" t="n">
-        <v>0.003344481605351168</v>
+        <v>0.05386416861826704</v>
       </c>
       <c r="AD51" t="n">
-        <v>-0.2366927126249864</v>
+        <v>-0.2210463995382497</v>
       </c>
       <c r="AE51" t="n">
-        <v>-0.0518241419824621</v>
+        <v>-0.001304454969546232</v>
       </c>
       <c r="AF51" t="n">
-        <v>-0.1848685706425243</v>
+        <v>-0.2197419445687034</v>
       </c>
       <c r="AG51" t="n">
         <v>2</v>
       </c>
       <c r="AH51" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AI51" t="b">
         <v>0</v>
@@ -7524,14 +7524,14 @@
         <v>0</v>
       </c>
       <c r="AM51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN51" t="b">
         <v>0</v>
       </c>
       <c r="AO51" t="inlineStr"/>
       <c r="AP51" t="n">
-        <v>710.3200000000001</v>
+        <v>687.16</v>
       </c>
     </row>
   </sheetData>

--- a/output/daily_screen_latest.xlsx
+++ b/output/daily_screen_latest.xlsx
@@ -643,26 +643,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>57.2</v>
+        <v>79.2</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -671,15 +671,15 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261027</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1000</v>
+        <v>5163000</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="K2" t="b">
         <v>0</v>
@@ -688,7 +688,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1000</v>
+        <v>5163000</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -697,61 +697,61 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>567</v>
+        <v>19.75</v>
       </c>
       <c r="Q2" t="n">
-        <v>567</v>
+        <v>19.75</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>49445359</v>
       </c>
       <c r="S2" t="n">
-        <v>561.2</v>
+        <v>19.60999984741211</v>
       </c>
       <c r="T2" t="n">
-        <v>547.2</v>
+        <v>19.22750005722046</v>
       </c>
       <c r="U2" t="n">
-        <v>543.3</v>
+        <v>19.17250003814697</v>
       </c>
       <c r="V2" t="n">
-        <v>496.8083333333333</v>
+        <v>19.0966667175293</v>
       </c>
       <c r="W2" t="n">
-        <v>10.63567921537594</v>
+        <v>0.177092070138702</v>
       </c>
       <c r="X2" t="n">
-        <v>12.80653017454735</v>
+        <v>0.1431692211206022</v>
       </c>
       <c r="Y2" t="n">
-        <v>-2.170850959171409</v>
+        <v>0.03392284901809978</v>
       </c>
       <c r="Z2" t="n">
-        <v>-2.36357013646005</v>
+        <v>0.02959210337651869</v>
       </c>
       <c r="AA2" t="b">
         <v>1</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.1595092024539877</v>
+        <v>0.05898125490451966</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.3263157894736841</v>
+        <v>0.04221631687873639</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.1946611500231761</v>
+        <v>0.09462843648173025</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.2711471658858708</v>
+        <v>-0.06577667121755248</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.07648601586269477</v>
+        <v>0.1604051076992827</v>
       </c>
       <c r="AG2" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="AH2" t="n">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="AI2" t="b">
         <v>1</v>
@@ -760,19 +760,21 @@
         <v>1</v>
       </c>
       <c r="AK2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM2" t="b">
         <v>1</v>
       </c>
       <c r="AN2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>591.95</v>
+        <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
@@ -783,7 +785,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -802,7 +804,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>49</v>
+        <v>49.8</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -811,7 +813,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261027</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -843,10 +845,10 @@
         <v>100.5</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2631762</v>
       </c>
       <c r="S3" t="n">
-        <v>100.1199996948242</v>
+        <v>100.2199996948242</v>
       </c>
       <c r="T3" t="n">
         <v>99.55000038146973</v>
@@ -855,19 +857,19 @@
         <v>99.55000038146973</v>
       </c>
       <c r="V3" t="n">
-        <v>95.24666671752929</v>
+        <v>95.58166669209798</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3582787592283694</v>
+        <v>0.3254133939909707</v>
       </c>
       <c r="X3" t="n">
-        <v>0.5125065110629193</v>
+        <v>0.4750878876485288</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.15422775183455</v>
+        <v>-0.1496744936575581</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.1580429564758122</v>
+        <v>-0.154227751834549</v>
       </c>
       <c r="AA3" t="b">
         <v>1</v>
@@ -876,22 +878,22 @@
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.2271062042440113</v>
+        <v>0.2499999762767589</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.03515194756918838</v>
+        <v>0.03564718157721058</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.171937580656198</v>
+        <v>0.14200698818047</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.1367856330870096</v>
+        <v>-0.1063598066032594</v>
       </c>
       <c r="AG3" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AH3" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="AI3" t="b">
         <v>1</v>
@@ -921,26 +923,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>56.6</v>
+        <v>45.2</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -949,24 +951,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261027</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>6899000</v>
+        <v>1000</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="K4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="b">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>6899000</v>
+        <v>1000</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -975,110 +977,112 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1115</v>
+        <v>247.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>1115</v>
+        <v>247.5</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>52590870</v>
       </c>
       <c r="S4" t="n">
-        <v>1172</v>
+        <v>245.8</v>
       </c>
       <c r="T4" t="n">
-        <v>1182.5</v>
+        <v>247.4</v>
       </c>
       <c r="U4" t="n">
-        <v>1178.75</v>
+        <v>247.825</v>
       </c>
       <c r="V4" t="n">
-        <v>1063.866666666667</v>
+        <v>250.5666666666667</v>
       </c>
       <c r="W4" t="n">
-        <v>1.320303042777368</v>
+        <v>-0.8782501790202843</v>
       </c>
       <c r="X4" t="n">
-        <v>23.78773744156464</v>
+        <v>-1.511174030151229</v>
       </c>
       <c r="Y4" t="n">
-        <v>-22.46743439878727</v>
+        <v>0.6329238511309445</v>
       </c>
       <c r="Z4" t="n">
-        <v>-18.67261691272811</v>
+        <v>0.3504920876932991</v>
       </c>
       <c r="AA4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.07211538461538458</v>
+        <v>-0.033203125</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.3782447466007417</v>
+        <v>0.04430379746835444</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.107267332184573</v>
+        <v>0.002444056577210585</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.3230761230129284</v>
+        <v>-0.06368919062793443</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.2158087908283555</v>
+        <v>0.06613324720514502</v>
       </c>
       <c r="AG4" t="n">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="AH4" t="n">
-        <v>84</v>
+        <v>26</v>
       </c>
       <c r="AI4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN4" t="b">
         <v>0</v>
       </c>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
+      </c>
+      <c r="AP4" t="n">
+        <v>250.39</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>56</v>
+        <v>43.6</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1087,24 +1091,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261027</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>8937000</v>
+        <v>1000</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="K5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="b">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>8937000</v>
+        <v>1000</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -1113,101 +1117,103 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1265</v>
+        <v>327.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>1265</v>
+        <v>327.5</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>15061382</v>
       </c>
       <c r="S5" t="n">
-        <v>1311</v>
+        <v>324.1</v>
       </c>
       <c r="T5" t="n">
-        <v>1373</v>
+        <v>327.05</v>
       </c>
       <c r="U5" t="n">
-        <v>1368</v>
+        <v>327.75</v>
       </c>
       <c r="V5" t="n">
-        <v>1203.733333333333</v>
+        <v>327</v>
       </c>
       <c r="W5" t="n">
-        <v>-6.951878699073632</v>
+        <v>-1.983141244730632</v>
       </c>
       <c r="X5" t="n">
-        <v>26.70561918620492</v>
+        <v>-2.976000201994802</v>
       </c>
       <c r="Y5" t="n">
-        <v>-33.65749788527854</v>
+        <v>0.9928589572641697</v>
       </c>
       <c r="Z5" t="n">
-        <v>-33.08600806370702</v>
+        <v>0.4017946625205115</v>
       </c>
       <c r="AA5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.08583690987124459</v>
+        <v>-0.04099560761346999</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.2961065573770492</v>
+        <v>0.05815831987075937</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.120988857440433</v>
+        <v>-0.005348426036259402</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.2409379337892359</v>
+        <v>-0.04983466822552951</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.1199490763488029</v>
+        <v>0.04448624218927011</v>
       </c>
       <c r="AG5" t="n">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="AH5" t="n">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="AI5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN5" t="b">
         <v>0</v>
       </c>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
+      </c>
+      <c r="AP5" t="n">
+        <v>338.03</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1216,7 +1222,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>54</v>
+        <v>56.8</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1225,15 +1231,15 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261027</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>8895000</v>
+        <v>6979000</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K6" t="b">
         <v>1</v>
@@ -1242,70 +1248,70 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>8348000</v>
+        <v>6899000</v>
       </c>
       <c r="N6" t="n">
-        <v>547000</v>
+        <v>80000</v>
       </c>
       <c r="O6" t="n">
-        <v>0.06552467656923815</v>
+        <v>0.01159588346137121</v>
       </c>
       <c r="P6" t="n">
-        <v>654</v>
+        <v>1080</v>
       </c>
       <c r="Q6" t="n">
-        <v>654</v>
+        <v>1080</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>9249607</v>
       </c>
       <c r="S6" t="n">
-        <v>664.4</v>
+        <v>1138</v>
       </c>
       <c r="T6" t="n">
-        <v>704.1</v>
+        <v>1179.5</v>
       </c>
       <c r="U6" t="n">
-        <v>706.05</v>
+        <v>1182.5</v>
       </c>
       <c r="V6" t="n">
-        <v>637.25</v>
+        <v>1069.716666666667</v>
       </c>
       <c r="W6" t="n">
-        <v>-8.727033407240924</v>
+        <v>-9.108023708924975</v>
       </c>
       <c r="X6" t="n">
-        <v>3.949825889250339</v>
+        <v>17.20858521146671</v>
       </c>
       <c r="Y6" t="n">
-        <v>-12.67685929649126</v>
+        <v>-26.31660892039169</v>
       </c>
       <c r="Z6" t="n">
-        <v>-13.38460034911353</v>
+        <v>-22.46743439878727</v>
       </c>
       <c r="AA6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.05627705627705626</v>
+        <v>-0.05263157894736847</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.1805054151624548</v>
+        <v>0.4814814814814814</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.02112510870786788</v>
+        <v>-0.01698439737015789</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.1253367915746415</v>
+        <v>0.3734884933851925</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.1464619002825094</v>
+        <v>-0.3904728907553504</v>
       </c>
       <c r="AG6" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="AH6" t="n">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
@@ -1320,30 +1326,30 @@
         <v>0</v>
       </c>
       <c r="AM6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="b">
         <v>0</v>
       </c>
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="n">
-        <v>745.74</v>
+        <v>1209.74</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1352,24 +1358,24 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>49.8</v>
+        <v>56</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261027</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>19689000</v>
+        <v>9968000</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K7" t="b">
         <v>1</v>
@@ -1378,70 +1384,70 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>19689000</v>
+        <v>8895000</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1073000</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.1206295671725689</v>
       </c>
       <c r="P7" t="n">
-        <v>1085</v>
+        <v>651</v>
       </c>
       <c r="Q7" t="n">
-        <v>1085</v>
+        <v>651</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>25585620</v>
       </c>
       <c r="S7" t="n">
-        <v>1089</v>
+        <v>660.6</v>
       </c>
       <c r="T7" t="n">
-        <v>1182.25</v>
+        <v>702</v>
       </c>
       <c r="U7" t="n">
-        <v>1184</v>
+        <v>704.1</v>
       </c>
       <c r="V7" t="n">
-        <v>1055.733333333333</v>
+        <v>639.7833333333333</v>
       </c>
       <c r="W7" t="n">
-        <v>-19.97839359683894</v>
+        <v>-10.54664407871689</v>
       </c>
       <c r="X7" t="n">
-        <v>2.322377524709275</v>
+        <v>1.050531895656891</v>
       </c>
       <c r="Y7" t="n">
-        <v>-22.30077112154822</v>
+        <v>-11.59717597437379</v>
       </c>
       <c r="Z7" t="n">
-        <v>-26.25141602093878</v>
+        <v>-12.67685929649126</v>
       </c>
       <c r="AA7" t="b">
         <v>1</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.03125</v>
+        <v>-0.06060606060606055</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.4201570680628273</v>
+        <v>0.3046092184368738</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.00390194756918838</v>
+        <v>-0.02495887902884997</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.364988444475014</v>
+        <v>0.196616230340585</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.3610864969058256</v>
+        <v>-0.2215751093694349</v>
       </c>
       <c r="AG7" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="AH7" t="n">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -1463,23 +1469,23 @@
       </c>
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="n">
-        <v>1262.37</v>
+        <v>752.6799999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1488,102 +1494,102 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>49.8</v>
+        <v>54.6</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261027</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1000</v>
+        <v>13046000</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="K8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="b">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1000</v>
+        <v>12671000</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>375000</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.0295951385052482</v>
       </c>
       <c r="P8" t="n">
-        <v>290.5</v>
+        <v>2400</v>
       </c>
       <c r="Q8" t="n">
-        <v>290.5</v>
+        <v>2400</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>35766965</v>
       </c>
       <c r="S8" t="n">
-        <v>295</v>
+        <v>2399</v>
       </c>
       <c r="T8" t="n">
-        <v>257.2</v>
+        <v>2476.5</v>
       </c>
       <c r="U8" t="n">
-        <v>253.35</v>
+        <v>2481.5</v>
       </c>
       <c r="V8" t="n">
-        <v>205.425</v>
+        <v>2424.348356119792</v>
       </c>
       <c r="W8" t="n">
-        <v>19.42547337056578</v>
+        <v>-25.50850595834754</v>
       </c>
       <c r="X8" t="n">
-        <v>20.2207276979978</v>
+        <v>-11.47065173465664</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.7952543274320192</v>
+        <v>-14.0378542236909</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.138377291406485</v>
+        <v>-17.90009387185703</v>
       </c>
       <c r="AA8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.360655737704918</v>
+        <v>-0.04000000000000004</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.024390243902439</v>
+        <v>0.09412034967687477</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.3958076852741064</v>
+        <v>-0.004352818422789451</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.9692216203146258</v>
+        <v>-0.01387263841941411</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.5734139350405194</v>
+        <v>0.009519819996624657</v>
       </c>
       <c r="AG8" t="n">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="AH8" t="n">
-        <v>98</v>
+        <v>32</v>
       </c>
       <c r="AI8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="b">
         <v>0</v>
@@ -1592,34 +1598,32 @@
         <v>0</v>
       </c>
       <c r="AM8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN8" t="b">
         <v>1</v>
       </c>
       <c r="AO8" t="n">
-        <v>299.8</v>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>2558.4</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>2555.53</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1628,7 +1632,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>49.2</v>
+        <v>53.40000000000001</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1637,15 +1641,15 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261027</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>7224000</v>
+        <v>8937000</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K9" t="b">
         <v>1</v>
@@ -1654,7 +1658,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>7224000</v>
+        <v>8937000</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1663,67 +1667,67 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1420</v>
+        <v>1255</v>
       </c>
       <c r="Q9" t="n">
-        <v>1420</v>
+        <v>1255</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>10348912</v>
       </c>
       <c r="S9" t="n">
-        <v>1504</v>
+        <v>1286</v>
       </c>
       <c r="T9" t="n">
-        <v>1599.75</v>
+        <v>1375.25</v>
       </c>
       <c r="U9" t="n">
-        <v>1600.75</v>
+        <v>1373</v>
       </c>
       <c r="V9" t="n">
-        <v>1479.666666666667</v>
+        <v>1210</v>
       </c>
       <c r="W9" t="n">
-        <v>-29.94233351305093</v>
+        <v>-14.10378787195941</v>
       </c>
       <c r="X9" t="n">
-        <v>16.77037513293451</v>
+        <v>18.543737774572</v>
       </c>
       <c r="Y9" t="n">
-        <v>-46.71270864598544</v>
+        <v>-32.64752564653142</v>
       </c>
       <c r="Z9" t="n">
-        <v>-44.54088823811603</v>
+        <v>-33.65749788527849</v>
       </c>
       <c r="AA9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0.01388888888888884</v>
+        <v>0.03719008264462809</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.2566371681415929</v>
+        <v>0.4277588168373152</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.02126305868029954</v>
+        <v>0.07283726422183867</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.2014685445537796</v>
+        <v>0.3197658287410263</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.1802054858734801</v>
+        <v>-0.2469285645191877</v>
       </c>
       <c r="AG9" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AH9" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
       </c>
       <c r="AJ9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK9" t="b">
         <v>0</v>
@@ -1732,30 +1736,32 @@
         <v>0</v>
       </c>
       <c r="AM9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN9" t="b">
         <v>0</v>
       </c>
       <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="n">
-        <v>1649.21</v>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1764,7 +1770,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1773,24 +1779,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261027</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>12671000</v>
+        <v>1000</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="K10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="b">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>12671000</v>
+        <v>1000</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1799,67 +1805,67 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2385</v>
+        <v>278.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>2385</v>
+        <v>278.5</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>18593088</v>
       </c>
       <c r="S10" t="n">
-        <v>2403</v>
+        <v>292.8</v>
       </c>
       <c r="T10" t="n">
-        <v>2481.5</v>
+        <v>260.675</v>
       </c>
       <c r="U10" t="n">
-        <v>2485.25</v>
+        <v>257.2</v>
       </c>
       <c r="V10" t="n">
-        <v>2420.907405598958</v>
+        <v>207.7916666666667</v>
       </c>
       <c r="W10" t="n">
-        <v>-25.86128205082832</v>
+        <v>16.1382156177246</v>
       </c>
       <c r="X10" t="n">
-        <v>-7.961188179207749</v>
+        <v>19.40422528194312</v>
       </c>
       <c r="Y10" t="n">
-        <v>-17.90009387162057</v>
+        <v>-3.266009664218522</v>
       </c>
       <c r="Z10" t="n">
-        <v>-19.55105125688571</v>
+        <v>-0.7952543274320227</v>
       </c>
       <c r="AA10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.03048780487804881</v>
+        <v>0.332535885167464</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.04913187713647793</v>
+        <v>1.04029304029304</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.004664142691139572</v>
+        <v>0.3681830667446746</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.00603674645133534</v>
+        <v>0.9323000521967513</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.01070088914247491</v>
+        <v>-0.5641169854520767</v>
       </c>
       <c r="AG10" t="n">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="AH10" t="n">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="AI10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK10" t="b">
         <v>0</v>
@@ -1868,32 +1874,34 @@
         <v>0</v>
       </c>
       <c r="AM10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="b">
         <v>1</v>
       </c>
       <c r="AO10" t="n">
-        <v>2590.11</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>2601.58</v>
+        <v>315.26</v>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1902,102 +1910,102 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>44.8</v>
+        <v>46.8</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261027</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2512000</v>
+        <v>7556450</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="K11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="b">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2512000</v>
+        <v>6587450</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>969000</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>0.1470978906860773</v>
       </c>
       <c r="P11" t="n">
-        <v>6070</v>
+        <v>269</v>
       </c>
       <c r="Q11" t="n">
-        <v>6070</v>
+        <v>269</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>25732274</v>
       </c>
       <c r="S11" t="n">
-        <v>6377</v>
+        <v>266.3</v>
       </c>
       <c r="T11" t="n">
-        <v>6777.75</v>
+        <v>286.55</v>
       </c>
       <c r="U11" t="n">
-        <v>6765.75</v>
+        <v>288.3</v>
       </c>
       <c r="V11" t="n">
-        <v>5661.25</v>
+        <v>266.5</v>
       </c>
       <c r="W11" t="n">
-        <v>-71.76099867335688</v>
+        <v>-6.439246733244204</v>
       </c>
       <c r="X11" t="n">
-        <v>104.2466442512411</v>
+        <v>-3.198326649822184</v>
       </c>
       <c r="Y11" t="n">
-        <v>-176.0076429245979</v>
+        <v>-3.24092008342202</v>
       </c>
       <c r="Z11" t="n">
-        <v>-165.5550832657782</v>
+        <v>-4.489412957966038</v>
       </c>
       <c r="AA11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.04116638078902235</v>
+        <v>-0.1151315789473685</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.8011869436201779</v>
+        <v>0.2658823529411765</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.07631832835821073</v>
+        <v>-0.07948439737015789</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.7460183200323647</v>
+        <v>0.1578893648448876</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.6696999916741539</v>
+        <v>-0.2373737622150455</v>
       </c>
       <c r="AG11" t="n">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="AH11" t="n">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="AI11" t="b">
         <v>0</v>
       </c>
       <c r="AJ11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="b">
         <v>0</v>
@@ -2006,22 +2014,22 @@
         <v>0</v>
       </c>
       <c r="AM11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO11" t="inlineStr"/>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>305.58</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>329.47</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2040,7 +2048,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>42.59999999999999</v>
+        <v>46</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2049,7 +2057,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261027</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -2075,58 +2083,58 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1260</v>
+        <v>1285</v>
       </c>
       <c r="Q12" t="n">
-        <v>1260</v>
+        <v>1285</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2121638</v>
       </c>
       <c r="S12" t="n">
-        <v>1315</v>
+        <v>1291</v>
       </c>
       <c r="T12" t="n">
+        <v>1400.25</v>
+      </c>
+      <c r="U12" t="n">
         <v>1396.25</v>
       </c>
-      <c r="U12" t="n">
-        <v>1394</v>
-      </c>
       <c r="V12" t="n">
-        <v>1278.259367879232</v>
+        <v>1285.028885904948</v>
       </c>
       <c r="W12" t="n">
-        <v>-25.97483346481295</v>
+        <v>-30.09157402581354</v>
       </c>
       <c r="X12" t="n">
-        <v>15.37503427525873</v>
+        <v>6.281712615044271</v>
       </c>
       <c r="Y12" t="n">
-        <v>-41.34986774007168</v>
+        <v>-36.37328664085781</v>
       </c>
       <c r="Z12" t="n">
-        <v>-40.78723373989933</v>
+        <v>-41.34986774007167</v>
       </c>
       <c r="AA12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.03703703703703698</v>
+        <v>0.06639004149377592</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.3264202682494393</v>
+        <v>0.4621730953688772</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.07218898460622536</v>
+        <v>0.1020372230709865</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.271251644661626</v>
+        <v>0.3541801072725883</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.1990626600554006</v>
+        <v>-0.2521428842016018</v>
       </c>
       <c r="AG12" t="n">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="AH12" t="n">
         <v>80</v>
@@ -2144,7 +2152,7 @@
         <v>0</v>
       </c>
       <c r="AM12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN12" t="b">
         <v>0</v>
@@ -2159,17 +2167,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2178,7 +2186,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>41.8</v>
+        <v>45.2</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2187,15 +2195,15 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261027</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>6003000</v>
+        <v>1000</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="K13" t="b">
         <v>0</v>
@@ -2204,7 +2212,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>6003000</v>
+        <v>1000</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -2213,84 +2221,82 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>190</v>
+        <v>520</v>
       </c>
       <c r="Q13" t="n">
-        <v>190</v>
+        <v>520</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>45376020</v>
       </c>
       <c r="S13" t="n">
-        <v>188.8</v>
+        <v>555.8</v>
       </c>
       <c r="T13" t="n">
-        <v>186.5</v>
+        <v>549.55</v>
       </c>
       <c r="U13" t="n">
-        <v>186.025</v>
+        <v>547.2</v>
       </c>
       <c r="V13" t="n">
-        <v>185.1833333333333</v>
+        <v>498.7333333333333</v>
       </c>
       <c r="W13" t="n">
-        <v>1.157026691460175</v>
+        <v>4.908876771783525</v>
       </c>
       <c r="X13" t="n">
-        <v>0.4105411366101419</v>
+        <v>11.22699949399457</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.7464855548500327</v>
+        <v>-6.318122722211049</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.7794898520532512</v>
+        <v>-2.170850959171391</v>
       </c>
       <c r="AA13" t="b">
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.05263157894736836</v>
+        <v>0.09936575052854124</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.1176470588235294</v>
+        <v>0.2855377008652658</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.08778352651655674</v>
+        <v>0.1350129321057518</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.06247843523571617</v>
+        <v>0.1775447127689769</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.02530509128084057</v>
+        <v>-0.04253178066322505</v>
       </c>
       <c r="AG13" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="AH13" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="AI13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="b">
         <v>1</v>
       </c>
       <c r="AK13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="b">
         <v>0</v>
       </c>
       <c r="AN13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>591.76</v>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
@@ -2301,17 +2307,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2320,7 +2326,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>41.59999999999999</v>
+        <v>43</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2329,24 +2335,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261027</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>3921000</v>
+        <v>19689000</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="K14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="b">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3921000</v>
+        <v>19689000</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2355,67 +2361,67 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>89.80000305175781</v>
+        <v>1060</v>
       </c>
       <c r="Q14" t="n">
-        <v>89.80000305175781</v>
+        <v>1060</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>29758483</v>
       </c>
       <c r="S14" t="n">
-        <v>90.66000061035156</v>
+        <v>1077</v>
       </c>
       <c r="T14" t="n">
-        <v>88.51000099182129</v>
+        <v>1177.25</v>
       </c>
       <c r="U14" t="n">
-        <v>88.23500099182129</v>
+        <v>1182.25</v>
       </c>
       <c r="V14" t="n">
-        <v>84.93166681925456</v>
+        <v>1061.933333333333</v>
       </c>
       <c r="W14" t="n">
-        <v>1.185346965630188</v>
+        <v>-23.38602191958125</v>
       </c>
       <c r="X14" t="n">
-        <v>1.704950917155769</v>
+        <v>-2.819302364148833</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.5196039515255806</v>
+        <v>-20.56671955543242</v>
       </c>
       <c r="Z14" t="n">
-        <v>-0.365699409226389</v>
+        <v>-22.30077112154821</v>
       </c>
       <c r="AA14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.06524317676030389</v>
+        <v>-0.08620689655172409</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.06904765537806923</v>
+        <v>0.5406976744186047</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.1003951243294923</v>
+        <v>-0.0505597149745135</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.01387903179025596</v>
+        <v>0.4327046863223158</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.08651609253923631</v>
+        <v>-0.4832644012968293</v>
       </c>
       <c r="AG14" t="n">
-        <v>92</v>
+        <v>50</v>
       </c>
       <c r="AH14" t="n">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="AI14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="b">
         <v>0</v>
@@ -2424,34 +2430,30 @@
         <v>0</v>
       </c>
       <c r="AM14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN14" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>95.73</v>
-      </c>
-      <c r="AP14" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="n">
+        <v>1308.42</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2460,7 +2462,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>41</v>
+        <v>42.2</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2469,15 +2471,15 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261027</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>4328000</v>
+        <v>4827000</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K15" t="b">
         <v>0</v>
@@ -2486,7 +2488,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>4328000</v>
+        <v>4827000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2495,67 +2497,67 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>5070</v>
+        <v>248</v>
       </c>
       <c r="Q15" t="n">
-        <v>5070</v>
+        <v>248</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>16776474</v>
       </c>
       <c r="S15" t="n">
-        <v>5040</v>
+        <v>250.6</v>
       </c>
       <c r="T15" t="n">
-        <v>5321.5</v>
+        <v>253.575</v>
       </c>
       <c r="U15" t="n">
-        <v>5311</v>
+        <v>253.775</v>
       </c>
       <c r="V15" t="n">
-        <v>5341.409090169271</v>
+        <v>232.8083333333333</v>
       </c>
       <c r="W15" t="n">
-        <v>-94.82468511148818</v>
+        <v>-0.4276564339809283</v>
       </c>
       <c r="X15" t="n">
-        <v>-23.75543770033998</v>
+        <v>2.707088558435337</v>
       </c>
       <c r="Y15" t="n">
-        <v>-71.0692474111482</v>
+        <v>-3.134744992416265</v>
       </c>
       <c r="Z15" t="n">
-        <v>-86.4422419341677</v>
+        <v>-3.165791552069547</v>
       </c>
       <c r="AA15" t="b">
         <v>1</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.04320987654320985</v>
+        <v>-0.01587301587301593</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.1549094406875071</v>
+        <v>0.4850299401197604</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.07836182411239823</v>
+        <v>0.01977416570419466</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.09974081709969385</v>
+        <v>0.3770369520234715</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.02137899298729562</v>
+        <v>-0.3572627863192769</v>
       </c>
       <c r="AG15" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="AH15" t="n">
-        <v>52</v>
+        <v>84</v>
       </c>
       <c r="AI15" t="b">
         <v>0</v>
       </c>
       <c r="AJ15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="b">
         <v>0</v>
@@ -2570,28 +2572,26 @@
         <v>1</v>
       </c>
       <c r="AO15" t="n">
-        <v>5871.06</v>
-      </c>
-      <c r="AP15" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>283.71</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>251.87</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2600,7 +2600,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>40</v>
+        <v>42.2</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2609,15 +2609,15 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261027</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>501000</v>
+        <v>1000</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="K16" t="b">
         <v>0</v>
@@ -2626,7 +2626,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>501000</v>
+        <v>1000</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2635,67 +2635,67 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>224.5</v>
+        <v>6000</v>
       </c>
       <c r="Q16" t="n">
-        <v>224.5</v>
+        <v>6000</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2773940</v>
       </c>
       <c r="S16" t="n">
-        <v>236.2</v>
+        <v>6099</v>
       </c>
       <c r="T16" t="n">
-        <v>237.35</v>
+        <v>6451</v>
       </c>
       <c r="U16" t="n">
-        <v>237.225</v>
+        <v>6460.5</v>
       </c>
       <c r="V16" t="n">
-        <v>224.4833333333333</v>
+        <v>6000.348087565104</v>
       </c>
       <c r="W16" t="n">
-        <v>-1.103629597366393</v>
+        <v>-124.2560250752931</v>
       </c>
       <c r="X16" t="n">
-        <v>2.303562950058372</v>
+        <v>-31.00814777542713</v>
       </c>
       <c r="Y16" t="n">
-        <v>-3.407192547424765</v>
+        <v>-93.24787729986599</v>
       </c>
       <c r="Z16" t="n">
-        <v>-2.605867250738623</v>
+        <v>-93.08022660698904</v>
       </c>
       <c r="AA16" t="b">
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.01126126126126126</v>
+        <v>-0.03069466882067851</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.2335164835164836</v>
+        <v>0.5726762853585796</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.04641320883044964</v>
+        <v>0.004952512756532079</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.1783478599286703</v>
+        <v>0.4646832972622907</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.1319346510982207</v>
+        <v>-0.4597307845057587</v>
       </c>
       <c r="AG16" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH16" t="n">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="AI16" t="b">
         <v>0</v>
       </c>
       <c r="AJ16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="b">
         <v>0</v>
@@ -2710,28 +2710,26 @@
         <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>263.11</v>
-      </c>
-      <c r="AP16" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>7056</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>6719.74</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2740,7 +2738,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>39.2</v>
+        <v>40.8</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2749,15 +2747,15 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261027</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>5163000</v>
+        <v>3921000</v>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K17" t="b">
         <v>0</v>
@@ -2766,7 +2764,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>5163000</v>
+        <v>3921000</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2775,84 +2773,82 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>19.54999923706055</v>
+        <v>87.69999694824219</v>
       </c>
       <c r="Q17" t="n">
-        <v>19.54999923706055</v>
+        <v>87.69999694824219</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2870815</v>
       </c>
       <c r="S17" t="n">
-        <v>19.55999984741211</v>
+        <v>90</v>
       </c>
       <c r="T17" t="n">
-        <v>19.17250003814697</v>
+        <v>88.7550006866455</v>
       </c>
       <c r="U17" t="n">
-        <v>19.12750005722046</v>
+        <v>88.51000099182129</v>
       </c>
       <c r="V17" t="n">
-        <v>19.08333339691162</v>
+        <v>85.06666679382325</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1642806122425959</v>
+        <v>0.7265338970744608</v>
       </c>
       <c r="X17" t="n">
-        <v>0.1346885088660775</v>
+        <v>1.509267513139483</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.02959210337651844</v>
+        <v>-0.782733616065022</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.04473508551324581</v>
+        <v>-0.5196039515255642</v>
       </c>
       <c r="AA17" t="b">
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.04825735318707736</v>
+        <v>0.05917866806624894</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.02894732826634461</v>
+        <v>0.1017587767511641</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.08340930075626574</v>
+        <v>0.09482584964345953</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0.02622129532146866</v>
+        <v>-0.006234211345124807</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.1096305960777344</v>
+        <v>0.1010600609885843</v>
       </c>
       <c r="AG17" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AH17" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AI17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="b">
         <v>1</v>
       </c>
       <c r="AK17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="b">
         <v>0</v>
       </c>
       <c r="AN17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>96.65000000000001</v>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
@@ -2863,17 +2859,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2882,7 +2878,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>38.8</v>
+        <v>39.8</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2891,15 +2887,15 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261027</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1000</v>
+        <v>6003000</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="K18" t="b">
         <v>0</v>
@@ -2908,7 +2904,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1000</v>
+        <v>6003000</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2917,91 +2913,95 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>6175</v>
+        <v>190.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>6175</v>
+        <v>190.5</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>22637098</v>
       </c>
       <c r="S18" t="n">
-        <v>6148</v>
+        <v>190.9</v>
       </c>
       <c r="T18" t="n">
-        <v>6460.5</v>
+        <v>187.025</v>
       </c>
       <c r="U18" t="n">
-        <v>6472</v>
+        <v>186.5</v>
       </c>
       <c r="V18" t="n">
-        <v>5963.933964029948</v>
+        <v>185.5333333333333</v>
       </c>
       <c r="W18" t="n">
-        <v>-100.7764050574497</v>
+        <v>1.290218095677432</v>
       </c>
       <c r="X18" t="n">
-        <v>-7.696178450460646</v>
+        <v>0.5864765284235762</v>
       </c>
       <c r="Y18" t="n">
-        <v>-93.08022660698902</v>
+        <v>0.7037415672538554</v>
       </c>
       <c r="Z18" t="n">
-        <v>-106.9145326951619</v>
+        <v>0.7464855548500338</v>
       </c>
       <c r="AA18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>-0.03590944574551136</v>
+        <v>0.05833333333333335</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.5977954506216152</v>
+        <v>0.1238938053097345</v>
       </c>
       <c r="AD18" t="n">
-        <v>-0.0007574981763229793</v>
+        <v>0.09398051491054393</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.5426268270338019</v>
+        <v>0.01590081721344561</v>
       </c>
       <c r="AF18" t="n">
-        <v>-0.5433843252101249</v>
+        <v>0.07807969769709833</v>
       </c>
       <c r="AG18" t="n">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="AH18" t="n">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="AI18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="b">
         <v>0</v>
       </c>
-      <c r="AO18" t="n">
-        <v>7224.75</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>6490.53</v>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3020,7 +3020,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>36.6</v>
+        <v>39.40000000000001</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261027</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -3055,58 +3055,58 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1560</v>
+        <v>1465</v>
       </c>
       <c r="Q19" t="n">
-        <v>1560</v>
+        <v>1465</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>5098695</v>
       </c>
       <c r="S19" t="n">
-        <v>1570</v>
+        <v>1558</v>
       </c>
       <c r="T19" t="n">
+        <v>1593.5</v>
+      </c>
+      <c r="U19" t="n">
         <v>1597.25</v>
       </c>
-      <c r="U19" t="n">
-        <v>1602</v>
-      </c>
       <c r="V19" t="n">
-        <v>1326.033333333333</v>
+        <v>1336.133333333333</v>
       </c>
       <c r="W19" t="n">
-        <v>13.84320185960064</v>
+        <v>-0.9548431396262913</v>
       </c>
       <c r="X19" t="n">
-        <v>36.6404846773729</v>
+        <v>29.12141911397305</v>
       </c>
       <c r="Y19" t="n">
-        <v>-22.79728281777226</v>
+        <v>-30.07626225359935</v>
       </c>
       <c r="Z19" t="n">
-        <v>-22.85454564331965</v>
+        <v>-22.79728281777225</v>
       </c>
       <c r="AA19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>-0.05740181268882172</v>
+        <v>-0.04870129870129869</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.7218543046357615</v>
+        <v>0.7054714784633294</v>
       </c>
       <c r="AD19" t="n">
-        <v>-0.02224986511963334</v>
+        <v>-0.0130541171240881</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.6666856810479482</v>
+        <v>0.5974784903670405</v>
       </c>
       <c r="AF19" t="n">
-        <v>-0.6889355461675816</v>
+        <v>-0.6105326074911286</v>
       </c>
       <c r="AG19" t="n">
-        <v>57.99999999999999</v>
+        <v>70</v>
       </c>
       <c r="AH19" t="n">
         <v>92</v>
@@ -3124,32 +3124,30 @@
         <v>0</v>
       </c>
       <c r="AM19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>1818.96</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO19" t="inlineStr"/>
       <c r="AP19" t="n">
-        <v>1579.21</v>
+        <v>1665.26</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>美律</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3158,24 +3156,24 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>36.2</v>
+        <v>39.4</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261027</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1000</v>
+        <v>6537000</v>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="K20" t="b">
         <v>0</v>
@@ -3184,76 +3182,76 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1000</v>
+        <v>6457000</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>0.01238965463837696</v>
       </c>
       <c r="P20" t="n">
-        <v>79.40000152587891</v>
+        <v>3130</v>
       </c>
       <c r="Q20" t="n">
-        <v>79.40000152587891</v>
+        <v>3130</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2778810</v>
       </c>
       <c r="S20" t="n">
-        <v>79.86000061035156</v>
+        <v>3196</v>
       </c>
       <c r="T20" t="n">
-        <v>78.96999969482422</v>
+        <v>3363.75</v>
       </c>
       <c r="U20" t="n">
-        <v>78.90499954223633</v>
+        <v>3380.75</v>
       </c>
       <c r="V20" t="n">
-        <v>77.88492647806804</v>
+        <v>3185.9912109375</v>
       </c>
       <c r="W20" t="n">
-        <v>0.4632227407964393</v>
+        <v>-64.94596194307451</v>
       </c>
       <c r="X20" t="n">
-        <v>0.6299568234198029</v>
+        <v>-33.7312883593824</v>
       </c>
       <c r="Y20" t="n">
-        <v>-0.1667340826233635</v>
+        <v>-31.2146735836921</v>
       </c>
       <c r="Z20" t="n">
-        <v>-0.05979653250630002</v>
+        <v>-32.99125700943229</v>
       </c>
       <c r="AA20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.01664536590469434</v>
+        <v>-0.09798270893371763</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.02022837095074759</v>
+        <v>0.5028965429281285</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.05179731347388272</v>
+        <v>-0.06233552735650705</v>
       </c>
       <c r="AE20" t="n">
-        <v>-0.03494025263706568</v>
+        <v>0.3949035548318396</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.08673756611094841</v>
+        <v>-0.4572390821883466</v>
       </c>
       <c r="AG20" t="n">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="AH20" t="n">
-        <v>22</v>
+        <v>86</v>
       </c>
       <c r="AI20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="b">
         <v>0</v>
@@ -3262,34 +3260,32 @@
         <v>0</v>
       </c>
       <c r="AM20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN20" t="b">
         <v>1</v>
       </c>
       <c r="AO20" t="n">
-        <v>81.31</v>
-      </c>
-      <c r="AP20" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>3486.82</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>3801.05</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3298,7 +3294,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>35.4</v>
+        <v>38.2</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3307,15 +3303,15 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261027</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>2185000</v>
+        <v>501000</v>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="K21" t="b">
         <v>0</v>
@@ -3324,7 +3320,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>2185000</v>
+        <v>501000</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -3333,61 +3329,61 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q21" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>24203493</v>
       </c>
       <c r="S21" t="n">
-        <v>221.3</v>
+        <v>229.8</v>
       </c>
       <c r="T21" t="n">
-        <v>231.7</v>
+        <v>236.95</v>
       </c>
       <c r="U21" t="n">
-        <v>232.35</v>
+        <v>237.35</v>
       </c>
       <c r="V21" t="n">
-        <v>213.8083333333333</v>
+        <v>225.2333333333333</v>
       </c>
       <c r="W21" t="n">
-        <v>-3.539802223704925</v>
+        <v>-3.163724079880438</v>
       </c>
       <c r="X21" t="n">
-        <v>0.01536129278935316</v>
+        <v>1.210105544070594</v>
       </c>
       <c r="Y21" t="n">
-        <v>-3.555163516494278</v>
+        <v>-4.373829623951033</v>
       </c>
       <c r="Z21" t="n">
-        <v>-3.365732392324016</v>
+        <v>-3.407192547424745</v>
       </c>
       <c r="AA21" t="b">
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>-0.05701754385964908</v>
+        <v>-0.0357142857142857</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.2990936555891239</v>
+        <v>0.263157894736842</v>
       </c>
       <c r="AD21" t="n">
-        <v>-0.0218655962904607</v>
+        <v>-6.710413707511353e-05</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.2439250320013107</v>
+        <v>0.1551649066405532</v>
       </c>
       <c r="AF21" t="n">
-        <v>-0.2657906282917714</v>
+        <v>-0.1552320107776283</v>
       </c>
       <c r="AG21" t="n">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="AH21" t="n">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="AI21" t="b">
         <v>0</v>
@@ -3407,27 +3403,25 @@
       <c r="AN21" t="b">
         <v>0</v>
       </c>
-      <c r="AO21" t="n">
-        <v>255.42</v>
-      </c>
+      <c r="AO21" t="inlineStr"/>
       <c r="AP21" t="n">
-        <v>246.08</v>
+        <v>244.55</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>美律</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3436,7 +3430,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3445,15 +3439,15 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261027</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>919000</v>
+        <v>1000</v>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="K22" t="b">
         <v>0</v>
@@ -3462,7 +3456,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>919000</v>
+        <v>1000</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -3471,103 +3465,103 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2335</v>
+        <v>79</v>
       </c>
       <c r="Q22" t="n">
-        <v>2335</v>
+        <v>79</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>3330822</v>
       </c>
       <c r="S22" t="n">
-        <v>2338</v>
+        <v>79.8</v>
       </c>
       <c r="T22" t="n">
-        <v>2361</v>
+        <v>79.01999969482422</v>
       </c>
       <c r="U22" t="n">
-        <v>2369.25</v>
+        <v>78.96999969482422</v>
       </c>
       <c r="V22" t="n">
-        <v>2083.667254638672</v>
+        <v>77.91400044759115</v>
       </c>
       <c r="W22" t="n">
-        <v>5.997368772541449</v>
+        <v>0.3045901583546424</v>
       </c>
       <c r="X22" t="n">
-        <v>4.473262756096712</v>
+        <v>0.5648834904067714</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.524106016444737</v>
+        <v>-0.260293332052129</v>
       </c>
       <c r="Z22" t="n">
-        <v>-0.1619235922681259</v>
+        <v>-0.1667340826233643</v>
       </c>
       <c r="AA22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>-0.06599999999999995</v>
+        <v>0.01282051282051277</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.7547228711658851</v>
+        <v>0.02258009818447304</v>
       </c>
       <c r="AD22" t="n">
-        <v>-0.03084805243081157</v>
+        <v>0.04846769439772336</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.6995542475780718</v>
+        <v>-0.08541288991181584</v>
       </c>
       <c r="AF22" t="n">
-        <v>-0.7304023000088834</v>
+        <v>0.1338805843095392</v>
       </c>
       <c r="AG22" t="n">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="AH22" t="n">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="AI22" t="b">
         <v>0</v>
       </c>
       <c r="AJ22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
-      <c r="AP22" t="n">
-        <v>2627.37</v>
+        <v>1</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>82</v>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3576,7 +3570,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>33.4</v>
+        <v>35.8</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3585,24 +3579,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261027</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1000</v>
+        <v>23519000</v>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="K23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="b">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1000</v>
+        <v>23519000</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -3611,61 +3605,61 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>245</v>
+        <v>521</v>
       </c>
       <c r="Q23" t="n">
-        <v>245</v>
+        <v>521</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>31814660</v>
       </c>
       <c r="S23" t="n">
-        <v>244.2</v>
+        <v>520</v>
       </c>
       <c r="T23" t="n">
-        <v>247.825</v>
+        <v>578.65</v>
       </c>
       <c r="U23" t="n">
-        <v>248.225</v>
+        <v>581.25</v>
       </c>
       <c r="V23" t="n">
-        <v>250.3916666666667</v>
+        <v>567.2416666666667</v>
       </c>
       <c r="W23" t="n">
-        <v>-1.318912905240666</v>
+        <v>-20.42398382588908</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.669404992933951</v>
+        <v>-8.987720670222682</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.3504920876932855</v>
+        <v>-11.4362631556664</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.2496176986635734</v>
+        <v>-14.26674574116766</v>
       </c>
       <c r="AA23" t="b">
         <v>1</v>
       </c>
       <c r="AB23" t="n">
-        <v>-0.03162055335968383</v>
+        <v>-0.09075043630017454</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.02941176470588225</v>
+        <v>0.02761341222879676</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.003531394209504546</v>
+        <v>-0.05510325472296396</v>
       </c>
       <c r="AE23" t="n">
-        <v>-0.02575685888193102</v>
+        <v>-0.08037957586749211</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.02928825309143557</v>
+        <v>0.02527632114452816</v>
       </c>
       <c r="AG23" t="n">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="AH23" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AI23" t="b">
         <v>0</v>
@@ -3674,10 +3668,10 @@
         <v>0</v>
       </c>
       <c r="AK23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="b">
         <v>1</v>
@@ -3685,29 +3679,25 @@
       <c r="AN23" t="b">
         <v>0</v>
       </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
+      <c r="AO23" t="inlineStr"/>
       <c r="AP23" t="n">
-        <v>258.97</v>
+        <v>640.6799999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3716,24 +3706,24 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>33</v>
+        <v>35.6</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261027</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>6457000</v>
+        <v>969000</v>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="K24" t="b">
         <v>0</v>
@@ -3742,70 +3732,70 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>6457000</v>
+        <v>919000</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>0.0544069640914037</v>
       </c>
       <c r="P24" t="n">
-        <v>3145</v>
+        <v>2250</v>
       </c>
       <c r="Q24" t="n">
-        <v>3145</v>
+        <v>2250</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1223000</v>
       </c>
       <c r="S24" t="n">
-        <v>3234</v>
+        <v>2321</v>
       </c>
       <c r="T24" t="n">
-        <v>3380.75</v>
+        <v>2343.5</v>
       </c>
       <c r="U24" t="n">
-        <v>3393</v>
+        <v>2361</v>
       </c>
       <c r="V24" t="n">
-        <v>3168.535294596354</v>
+        <v>2100.230332438151</v>
       </c>
       <c r="W24" t="n">
-        <v>-58.91887697289167</v>
+        <v>-2.166083020384121</v>
       </c>
       <c r="X24" t="n">
-        <v>-25.92761996345932</v>
+        <v>3.145393600799783</v>
       </c>
       <c r="Y24" t="n">
-        <v>-32.99125700943235</v>
+        <v>-5.311476621183904</v>
       </c>
       <c r="Z24" t="n">
-        <v>-32.82779203802981</v>
+        <v>1.524106016444781</v>
       </c>
       <c r="AA24" t="b">
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>-0.07227138643067843</v>
+        <v>-0.1346153846153846</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.4123468961285974</v>
+        <v>0.791094203859015</v>
       </c>
       <c r="AD24" t="n">
-        <v>-0.03711943886149005</v>
+        <v>-0.098968203038174</v>
       </c>
       <c r="AE24" t="n">
-        <v>0.3571782725407842</v>
+        <v>0.6831012157627261</v>
       </c>
       <c r="AF24" t="n">
-        <v>-0.3942977114022742</v>
+        <v>-0.7820694188009001</v>
       </c>
       <c r="AG24" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="AH24" t="n">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="AI24" t="b">
         <v>0</v>
@@ -3826,26 +3816,26 @@
         <v>1</v>
       </c>
       <c r="AO24" t="n">
-        <v>3522.4</v>
+        <v>2313</v>
       </c>
       <c r="AP24" t="n">
-        <v>3718.16</v>
+        <v>2628.42</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3854,7 +3844,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3863,24 +3853,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261027</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>852000</v>
+        <v>7224000</v>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="K25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" t="b">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>852000</v>
+        <v>7224000</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3889,61 +3879,61 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>7585</v>
+        <v>1280</v>
       </c>
       <c r="Q25" t="n">
-        <v>7585</v>
+        <v>1280</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>16360844</v>
       </c>
       <c r="S25" t="n">
-        <v>7749</v>
+        <v>1434</v>
       </c>
       <c r="T25" t="n">
-        <v>8040.25</v>
+        <v>1590.75</v>
       </c>
       <c r="U25" t="n">
-        <v>8079.75</v>
+        <v>1599.75</v>
       </c>
       <c r="V25" t="n">
-        <v>6394.083333333333</v>
+        <v>1484</v>
       </c>
       <c r="W25" t="n">
-        <v>9.323164990708392</v>
+        <v>-54.33387915327785</v>
       </c>
       <c r="X25" t="n">
-        <v>149.5449455464794</v>
+        <v>2.5495242756921</v>
       </c>
       <c r="Y25" t="n">
-        <v>-140.221780555771</v>
+        <v>-56.88340342896995</v>
       </c>
       <c r="Z25" t="n">
-        <v>-143.1665015854005</v>
+        <v>-46.71270864598551</v>
       </c>
       <c r="AA25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>-0.09432835820895524</v>
+        <v>-0.1232876712328768</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.0724043715847</v>
+        <v>0.2549019607843137</v>
       </c>
       <c r="AD25" t="n">
-        <v>-0.05917641063976686</v>
+        <v>-0.08764048965566618</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.017235747996886</v>
+        <v>0.1469089726880248</v>
       </c>
       <c r="AF25" t="n">
-        <v>-1.076412158636653</v>
+        <v>-0.234549462343691</v>
       </c>
       <c r="AG25" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AH25" t="n">
-        <v>100</v>
+        <v>56.00000000000001</v>
       </c>
       <c r="AI25" t="b">
         <v>0</v>
@@ -3958,30 +3948,30 @@
         <v>0</v>
       </c>
       <c r="AM25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="b">
         <v>0</v>
       </c>
       <c r="AO25" t="inlineStr"/>
       <c r="AP25" t="n">
-        <v>8864.209999999999</v>
+        <v>1822.11</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3990,7 +3980,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>31.2</v>
+        <v>34.2</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3999,15 +3989,15 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261027</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1000</v>
+        <v>2512000</v>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="K26" t="b">
         <v>0</v>
@@ -4016,7 +4006,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1000</v>
+        <v>2512000</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -4025,61 +4015,61 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>3495</v>
+        <v>5860</v>
       </c>
       <c r="Q26" t="n">
-        <v>3495</v>
+        <v>5860</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2418770</v>
       </c>
       <c r="S26" t="n">
-        <v>3611</v>
+        <v>6237</v>
       </c>
       <c r="T26" t="n">
-        <v>3851.5</v>
+        <v>6750.25</v>
       </c>
       <c r="U26" t="n">
-        <v>3862.5</v>
+        <v>6777.75</v>
       </c>
       <c r="V26" t="n">
-        <v>3768.57890218099</v>
+        <v>5703.75</v>
       </c>
       <c r="W26" t="n">
-        <v>-92.25524040679875</v>
+        <v>-130.9699905806601</v>
       </c>
       <c r="X26" t="n">
-        <v>-21.40092614023082</v>
+        <v>57.20331728485951</v>
       </c>
       <c r="Y26" t="n">
-        <v>-70.85431426656794</v>
+        <v>-188.1733078655196</v>
       </c>
       <c r="Z26" t="n">
-        <v>-70.82136378615128</v>
+        <v>-176.0076429245972</v>
       </c>
       <c r="AA26" t="b">
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>-0.05921938088829071</v>
+        <v>-0.08580343213728547</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.1307599125693282</v>
+        <v>0.7703927492447129</v>
       </c>
       <c r="AD26" t="n">
-        <v>-0.02406743331910233</v>
+        <v>-0.05015625056007489</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.0755912889815149</v>
+        <v>0.662399761148424</v>
       </c>
       <c r="AF26" t="n">
-        <v>-0.09965872230061723</v>
+        <v>-0.7125560117084989</v>
       </c>
       <c r="AG26" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="AH26" t="n">
-        <v>50</v>
+        <v>94</v>
       </c>
       <c r="AI26" t="b">
         <v>0</v>
@@ -4101,23 +4091,23 @@
       </c>
       <c r="AO26" t="inlineStr"/>
       <c r="AP26" t="n">
-        <v>4135.26</v>
+        <v>7857.11</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4126,7 +4116,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4135,24 +4125,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261027</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>23519000</v>
+        <v>4328000</v>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="K27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" t="b">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>23519000</v>
+        <v>4328000</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -4161,61 +4151,61 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>507</v>
+        <v>4750</v>
       </c>
       <c r="Q27" t="n">
-        <v>507</v>
+        <v>4750</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>4884266</v>
       </c>
       <c r="S27" t="n">
-        <v>522.6</v>
+        <v>4965</v>
       </c>
       <c r="T27" t="n">
-        <v>581.25</v>
+        <v>5308</v>
       </c>
       <c r="U27" t="n">
-        <v>584.45</v>
+        <v>5321.5</v>
       </c>
       <c r="V27" t="n">
-        <v>567.0083333333333</v>
+        <v>5352.55302734375</v>
       </c>
       <c r="W27" t="n">
-        <v>-20.39540062247374</v>
+        <v>-129.6942209169702</v>
       </c>
       <c r="X27" t="n">
-        <v>-6.128654881306069</v>
+        <v>-44.94319434366626</v>
       </c>
       <c r="Y27" t="n">
-        <v>-14.26674574116768</v>
+        <v>-84.75102657330389</v>
       </c>
       <c r="Z27" t="n">
-        <v>-14.81368144928829</v>
+        <v>-71.06924741114788</v>
       </c>
       <c r="AA27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>-0.1120840630472855</v>
+        <v>-0.05378486055776888</v>
       </c>
       <c r="AC27" t="n">
-        <v>-0.09946714031971582</v>
+        <v>0.1638266687866305</v>
       </c>
       <c r="AD27" t="n">
-        <v>-0.07693211547809709</v>
+        <v>-0.01813767898055829</v>
       </c>
       <c r="AE27" t="n">
-        <v>-0.1546357639075291</v>
+        <v>0.05583368069034167</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.077703648429432</v>
+        <v>-0.07397135967089996</v>
       </c>
       <c r="AG27" t="n">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="AH27" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="AI27" t="b">
         <v>0</v>
@@ -4230,30 +4220,30 @@
         <v>0</v>
       </c>
       <c r="AM27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN27" t="b">
         <v>0</v>
       </c>
       <c r="AO27" t="inlineStr"/>
       <c r="AP27" t="n">
-        <v>651.16</v>
+        <v>5637.37</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>新日興</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4262,7 +4252,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>31</v>
+        <v>32.4</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4271,15 +4261,15 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261027</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1740000</v>
+        <v>1000</v>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="K28" t="b">
         <v>0</v>
@@ -4288,7 +4278,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1740000</v>
+        <v>1000</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -4297,61 +4287,61 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>172.5</v>
+        <v>3495</v>
       </c>
       <c r="Q28" t="n">
-        <v>172.5</v>
+        <v>3495</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1220036</v>
       </c>
       <c r="S28" t="n">
-        <v>175.8</v>
+        <v>3567</v>
       </c>
       <c r="T28" t="n">
-        <v>173.95</v>
+        <v>3838.25</v>
       </c>
       <c r="U28" t="n">
-        <v>174.35</v>
+        <v>3851.5</v>
       </c>
       <c r="V28" t="n">
-        <v>183.8319684346517</v>
+        <v>3780.441471354167</v>
       </c>
       <c r="W28" t="n">
-        <v>-0.6912703768403219</v>
+        <v>-102.2465385033634</v>
       </c>
       <c r="X28" t="n">
-        <v>-1.393660974293531</v>
+        <v>-37.57004861285846</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.7023905974532094</v>
+        <v>-64.6764898905049</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.204778636812404</v>
+        <v>-70.85431426656697</v>
       </c>
       <c r="AA28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB28" t="n">
-        <v>-0.04432132963988922</v>
+        <v>-0.07047872340425532</v>
       </c>
       <c r="AC28" t="n">
-        <v>-0.0177614212681948</v>
+        <v>0.2557280918933262</v>
       </c>
       <c r="AD28" t="n">
-        <v>-0.009169382070700838</v>
+        <v>-0.03483154182704473</v>
       </c>
       <c r="AE28" t="n">
-        <v>-0.07293004485600807</v>
+        <v>0.1477351037970374</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.06376066278530723</v>
+        <v>-0.1825666456240821</v>
       </c>
       <c r="AG28" t="n">
-        <v>64</v>
+        <v>57.99999999999999</v>
       </c>
       <c r="AH28" t="n">
-        <v>18</v>
+        <v>57.99999999999999</v>
       </c>
       <c r="AI28" t="b">
         <v>0</v>
@@ -4360,40 +4350,36 @@
         <v>0</v>
       </c>
       <c r="AK28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN28" t="b">
         <v>0</v>
       </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
+      <c r="AO28" t="inlineStr"/>
       <c r="AP28" t="n">
-        <v>178.03</v>
+        <v>4131.32</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4402,7 +4388,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>29.4</v>
+        <v>32.2</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4411,7 +4397,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261027</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -4419,7 +4405,7 @@
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K29" t="b">
         <v>0</v>
@@ -4437,61 +4423,61 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>322</v>
+        <v>161.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>322</v>
+        <v>161.5</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>12632328</v>
       </c>
       <c r="S29" t="n">
-        <v>321.5</v>
+        <v>162</v>
       </c>
       <c r="T29" t="n">
-        <v>327.75</v>
+        <v>174.375</v>
       </c>
       <c r="U29" t="n">
-        <v>328.75</v>
+        <v>174.95</v>
       </c>
       <c r="V29" t="n">
-        <v>326.7</v>
+        <v>162.0916666666667</v>
       </c>
       <c r="W29" t="n">
-        <v>-2.822420278790332</v>
+        <v>-3.563183790212435</v>
       </c>
       <c r="X29" t="n">
-        <v>-3.224214941310815</v>
+        <v>-1.341056779954871</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.4017946625204831</v>
+        <v>-2.222127010257564</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.2730154495566866</v>
+        <v>-2.708527820507965</v>
       </c>
       <c r="AA29" t="b">
         <v>1</v>
       </c>
       <c r="AB29" t="n">
-        <v>-0.05847953216374269</v>
+        <v>-0.06647398843930641</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.02711323763955353</v>
+        <v>0.2142857142857142</v>
       </c>
       <c r="AD29" t="n">
-        <v>-0.02332758459455431</v>
+        <v>-0.03082680686209582</v>
       </c>
       <c r="AE29" t="n">
-        <v>-0.02805538594825974</v>
+        <v>0.1062927261894253</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.00472780135370543</v>
+        <v>-0.1371195330515211</v>
       </c>
       <c r="AG29" t="n">
-        <v>56.00000000000001</v>
+        <v>62</v>
       </c>
       <c r="AH29" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="AI29" t="b">
         <v>0</v>
@@ -4500,40 +4486,38 @@
         <v>0</v>
       </c>
       <c r="AK29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM29" t="b">
         <v>1</v>
       </c>
       <c r="AN29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>186.69</v>
       </c>
       <c r="AP29" t="n">
-        <v>347.55</v>
+        <v>184.05</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4542,7 +4526,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>29.2</v>
+        <v>30.6</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4551,15 +4535,15 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261027</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1000</v>
+        <v>852000</v>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="K30" t="b">
         <v>0</v>
@@ -4568,7 +4552,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1000</v>
+        <v>852000</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -4577,61 +4561,61 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>161</v>
+        <v>7430</v>
       </c>
       <c r="Q30" t="n">
-        <v>161</v>
+        <v>7430</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2365460</v>
       </c>
       <c r="S30" t="n">
-        <v>162.4</v>
+        <v>7669</v>
       </c>
       <c r="T30" t="n">
-        <v>174.95</v>
+        <v>7992.5</v>
       </c>
       <c r="U30" t="n">
-        <v>175.55</v>
+        <v>8040.25</v>
       </c>
       <c r="V30" t="n">
-        <v>161.6166666666667</v>
+        <v>6463</v>
       </c>
       <c r="W30" t="n">
-        <v>-3.494052847898416</v>
+        <v>-30.32926562784814</v>
       </c>
       <c r="X30" t="n">
-        <v>-0.7855250273904424</v>
+        <v>113.5701033116136</v>
       </c>
       <c r="Y30" t="n">
-        <v>-2.708527820507974</v>
+        <v>-143.8993689394617</v>
       </c>
       <c r="Z30" t="n">
-        <v>-3.080522060934389</v>
+        <v>-140.2217805557706</v>
       </c>
       <c r="AA30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>-0.06936416184971095</v>
+        <v>-0.1138938580799046</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.09152542372881345</v>
+        <v>1.254931714719272</v>
       </c>
       <c r="AD30" t="n">
-        <v>-0.03421221428052257</v>
+        <v>-0.07824667650269401</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.03635680014100018</v>
+        <v>1.146938726622983</v>
       </c>
       <c r="AF30" t="n">
-        <v>-0.07056901442152275</v>
+        <v>-1.225185403125677</v>
       </c>
       <c r="AG30" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AH30" t="n">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="AI30" t="b">
         <v>0</v>
@@ -4646,32 +4630,30 @@
         <v>0</v>
       </c>
       <c r="AM30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="b">
         <v>0</v>
       </c>
-      <c r="AO30" t="n">
-        <v>191.59</v>
-      </c>
+      <c r="AO30" t="inlineStr"/>
       <c r="AP30" t="n">
-        <v>187.68</v>
+        <v>9117.110000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>6271</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4680,7 +4662,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>28.8</v>
+        <v>30.4</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4689,24 +4671,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261027</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>6587450</v>
+        <v>2185000</v>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="K31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" t="b">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>6587450</v>
+        <v>2185000</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -4715,61 +4697,61 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>262.5</v>
+        <v>207.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>262.5</v>
+        <v>207.5</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2029174</v>
       </c>
       <c r="S31" t="n">
-        <v>265.2</v>
+        <v>217.7</v>
       </c>
       <c r="T31" t="n">
-        <v>288.3</v>
+        <v>230.65</v>
       </c>
       <c r="U31" t="n">
-        <v>291.025</v>
+        <v>231.7</v>
       </c>
       <c r="V31" t="n">
-        <v>265.5583333333333</v>
+        <v>214.7833333333333</v>
       </c>
       <c r="W31" t="n">
-        <v>-6.877509586932717</v>
+        <v>-5.031170467372135</v>
       </c>
       <c r="X31" t="n">
-        <v>-2.388096628966672</v>
+        <v>-0.9939450592429452</v>
       </c>
       <c r="Y31" t="n">
-        <v>-4.489412957966046</v>
+        <v>-4.03722540812919</v>
       </c>
       <c r="Z31" t="n">
-        <v>-4.955413911295141</v>
+        <v>-3.555163516494277</v>
       </c>
       <c r="AA31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>-0.1719242902208202</v>
+        <v>-0.09190371991247259</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.1122881355932204</v>
+        <v>0.3926174496644295</v>
       </c>
       <c r="AD31" t="n">
-        <v>-0.1367723426516319</v>
+        <v>-0.05625653833526201</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.0571195120054071</v>
+        <v>0.2846244615681406</v>
       </c>
       <c r="AF31" t="n">
-        <v>-0.193891854657039</v>
+        <v>-0.3408809999034026</v>
       </c>
       <c r="AG31" t="n">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="AH31" t="n">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="AI31" t="b">
         <v>0</v>
@@ -4784,32 +4766,30 @@
         <v>0</v>
       </c>
       <c r="AM31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN31" t="b">
         <v>0</v>
       </c>
-      <c r="AO31" t="n">
-        <v>313.43</v>
-      </c>
+      <c r="AO31" t="inlineStr"/>
       <c r="AP31" t="n">
-        <v>331.16</v>
+        <v>253.37</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4818,7 +4798,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>28.4</v>
+        <v>29.4</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4827,15 +4807,15 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261027</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>4827000</v>
+        <v>1000</v>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="n">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="K32" t="b">
         <v>0</v>
@@ -4844,7 +4824,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>4827000</v>
+        <v>1000</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -4853,61 +4833,61 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>246.5</v>
+        <v>97</v>
       </c>
       <c r="Q32" t="n">
-        <v>246.5</v>
+        <v>97</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>29635220</v>
       </c>
       <c r="S32" t="n">
-        <v>252.6</v>
+        <v>98.08000030517579</v>
       </c>
       <c r="T32" t="n">
-        <v>253.775</v>
+        <v>112.070000076294</v>
       </c>
       <c r="U32" t="n">
-        <v>255.275</v>
+        <v>112.570000076294</v>
       </c>
       <c r="V32" t="n">
-        <v>231.4583333333333</v>
+        <v>96.91666653951009</v>
       </c>
       <c r="W32" t="n">
-        <v>0.3249832544698563</v>
+        <v>-3.765448703309048</v>
       </c>
       <c r="X32" t="n">
-        <v>3.490774806539403</v>
+        <v>-0.5540619673779018</v>
       </c>
       <c r="Y32" t="n">
-        <v>-3.165791552069547</v>
+        <v>-3.211386735931146</v>
       </c>
       <c r="Z32" t="n">
-        <v>-2.639135006951672</v>
+        <v>-3.753944572158471</v>
       </c>
       <c r="AA32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB32" t="n">
-        <v>-0.108499095840868</v>
+        <v>-0.09345794392523366</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.3288409703504043</v>
+        <v>0.3305898212576277</v>
       </c>
       <c r="AD32" t="n">
-        <v>-0.07334714827167965</v>
+        <v>-0.05781076234802307</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.273672346762591</v>
+        <v>0.2225968331613388</v>
       </c>
       <c r="AF32" t="n">
-        <v>-0.3470194950342707</v>
+        <v>-0.2804075955093619</v>
       </c>
       <c r="AG32" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="AH32" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="AI32" t="b">
         <v>0</v>
@@ -4922,32 +4902,30 @@
         <v>0</v>
       </c>
       <c r="AM32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN32" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>282.49</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO32" t="inlineStr"/>
       <c r="AP32" t="n">
-        <v>259.66</v>
+        <v>127.86</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4956,7 +4934,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>28.4</v>
+        <v>29.2</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4965,15 +4943,15 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261027</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>654000</v>
+        <v>3281561</v>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="K33" t="b">
         <v>0</v>
@@ -4982,7 +4960,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>654000</v>
+        <v>3281561</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
@@ -4991,61 +4969,61 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>438.5</v>
+        <v>1950</v>
       </c>
       <c r="Q33" t="n">
-        <v>438.5</v>
+        <v>1950</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>5074575</v>
       </c>
       <c r="S33" t="n">
-        <v>462.5</v>
+        <v>1887</v>
       </c>
       <c r="T33" t="n">
-        <v>499.65</v>
+        <v>2053.75</v>
       </c>
       <c r="U33" t="n">
-        <v>502.3</v>
+        <v>2061.5</v>
       </c>
       <c r="V33" t="n">
-        <v>460.275</v>
+        <v>2147.254701741536</v>
       </c>
       <c r="W33" t="n">
-        <v>-16.13210472828047</v>
+        <v>-77.05922734449655</v>
       </c>
       <c r="X33" t="n">
-        <v>-6.76799141458519</v>
+        <v>-67.62245782752514</v>
       </c>
       <c r="Y33" t="n">
-        <v>-9.364113313695277</v>
+        <v>-9.43676951697141</v>
       </c>
       <c r="Z33" t="n">
-        <v>-8.966476439567781</v>
+        <v>-25.0261793774325</v>
       </c>
       <c r="AA33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB33" t="n">
-        <v>-0.1078331637843337</v>
+        <v>-0.07363420427553447</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.312874251497006</v>
+        <v>0.1327068171657442</v>
       </c>
       <c r="AD33" t="n">
-        <v>-0.07268121621514534</v>
+        <v>-0.03798702269832388</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.2577056279091927</v>
+        <v>0.0247138290694553</v>
       </c>
       <c r="AF33" t="n">
-        <v>-0.3303868441243381</v>
+        <v>-0.06270085176777918</v>
       </c>
       <c r="AG33" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="AH33" t="n">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="AI33" t="b">
         <v>0</v>
@@ -5060,30 +5038,32 @@
         <v>0</v>
       </c>
       <c r="AM33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO33" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>2059.2</v>
+      </c>
       <c r="AP33" t="n">
-        <v>561.37</v>
+        <v>2224.21</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5101,15 +5081,15 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261027</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1000</v>
+        <v>6331000</v>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="n">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="K34" t="b">
         <v>0</v>
@@ -5118,7 +5098,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1000</v>
+        <v>6331000</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -5127,61 +5107,61 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>95.90000152587891</v>
+        <v>1760</v>
       </c>
       <c r="Q34" t="n">
-        <v>95.90000152587891</v>
+        <v>1760</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>4381870</v>
       </c>
       <c r="S34" t="n">
-        <v>99.18000030517578</v>
+        <v>1819</v>
       </c>
       <c r="T34" t="n">
-        <v>112.570000076294</v>
+        <v>1940.25</v>
       </c>
       <c r="U34" t="n">
-        <v>113.05</v>
+        <v>1946.75</v>
       </c>
       <c r="V34" t="n">
-        <v>96.51499989827474</v>
+        <v>2035.166666666667</v>
       </c>
       <c r="W34" t="n">
-        <v>-3.505159855553586</v>
+        <v>-52.52698428004737</v>
       </c>
       <c r="X34" t="n">
-        <v>0.2487847166048847</v>
+        <v>-17.12125161944208</v>
       </c>
       <c r="Y34" t="n">
-        <v>-3.753944572158471</v>
+        <v>-35.4057326606053</v>
       </c>
       <c r="Z34" t="n">
-        <v>-4.013971739369711</v>
+        <v>-35.18499666511754</v>
       </c>
       <c r="AA34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>-0.09099524620019994</v>
+        <v>-0.06878306878306883</v>
       </c>
       <c r="AC34" t="n">
-        <v>0.1839506361219618</v>
+        <v>-0.0712401055408971</v>
       </c>
       <c r="AD34" t="n">
-        <v>-0.05584329863101156</v>
+        <v>-0.03313588720585825</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.1287820125341486</v>
+        <v>-0.179233093637186</v>
       </c>
       <c r="AF34" t="n">
-        <v>-0.1846253111651601</v>
+        <v>0.1460972064313277</v>
       </c>
       <c r="AG34" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AH34" t="n">
-        <v>56.00000000000001</v>
+        <v>10</v>
       </c>
       <c r="AI34" t="b">
         <v>0</v>
@@ -5196,30 +5176,30 @@
         <v>0</v>
       </c>
       <c r="AM34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="b">
         <v>0</v>
       </c>
       <c r="AO34" t="inlineStr"/>
       <c r="AP34" t="n">
-        <v>124.55</v>
+        <v>2084.74</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5228,7 +5208,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>27.8</v>
+        <v>26.6</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5237,15 +5217,15 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261027</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K35" t="b">
         <v>0</v>
@@ -5254,7 +5234,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -5263,61 +5243,61 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>153.5</v>
+        <v>1140</v>
       </c>
       <c r="Q35" t="n">
-        <v>153.5</v>
+        <v>1140</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2087205</v>
       </c>
       <c r="S35" t="n">
-        <v>155.4</v>
+        <v>1114</v>
       </c>
       <c r="T35" t="n">
-        <v>167.225</v>
+        <v>1170.25</v>
       </c>
       <c r="U35" t="n">
-        <v>168.1</v>
+        <v>1174.75</v>
       </c>
       <c r="V35" t="n">
-        <v>152.4333333333333</v>
+        <v>1322.333333333333</v>
       </c>
       <c r="W35" t="n">
-        <v>-3.701197657807711</v>
+        <v>-29.69084508133437</v>
       </c>
       <c r="X35" t="n">
-        <v>-1.568374082771988</v>
+        <v>-30.62902362070781</v>
       </c>
       <c r="Y35" t="n">
-        <v>-2.132823575035723</v>
+        <v>0.9381785393734354</v>
       </c>
       <c r="Z35" t="n">
-        <v>-2.430844896598336</v>
+        <v>-3.563919872549384</v>
       </c>
       <c r="AA35" t="b">
         <v>1</v>
       </c>
       <c r="AB35" t="n">
-        <v>-0.1023391812865497</v>
+        <v>-0.07317073170731703</v>
       </c>
       <c r="AC35" t="n">
-        <v>0.2329317269076305</v>
+        <v>-0.1396226415094339</v>
       </c>
       <c r="AD35" t="n">
-        <v>-0.06718723371736135</v>
+        <v>-0.03752355013010644</v>
       </c>
       <c r="AE35" t="n">
-        <v>0.1777631033198173</v>
+        <v>-0.2476156296057228</v>
       </c>
       <c r="AF35" t="n">
-        <v>-0.2449503370371786</v>
+        <v>0.2100920794756164</v>
       </c>
       <c r="AG35" t="n">
-        <v>38</v>
+        <v>56.00000000000001</v>
       </c>
       <c r="AH35" t="n">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="AI35" t="b">
         <v>0</v>
@@ -5326,38 +5306,40 @@
         <v>0</v>
       </c>
       <c r="AK35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM35" t="b">
         <v>1</v>
       </c>
       <c r="AN35" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>177.75</v>
+        <v>0</v>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP35" t="n">
-        <v>187.45</v>
+        <v>1241.84</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5366,96 +5348,96 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>26.8</v>
+        <v>26</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261027</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>79618000</v>
+        <v>5233000</v>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="K36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36" t="b">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>79618000</v>
+        <v>5143000</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>90000</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>0.0174995139023916</v>
       </c>
       <c r="P36" t="n">
-        <v>125.5</v>
+        <v>3960</v>
       </c>
       <c r="Q36" t="n">
-        <v>125.5</v>
+        <v>3960</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>13034792</v>
       </c>
       <c r="S36" t="n">
-        <v>127.5</v>
+        <v>4054</v>
       </c>
       <c r="T36" t="n">
-        <v>143.7</v>
+        <v>4558.5</v>
       </c>
       <c r="U36" t="n">
-        <v>145.425</v>
+        <v>4619.75</v>
       </c>
       <c r="V36" t="n">
-        <v>133.6166666666667</v>
+        <v>4322.083333333333</v>
       </c>
       <c r="W36" t="n">
-        <v>-5.870555737754358</v>
+        <v>-195.9146058391852</v>
       </c>
       <c r="X36" t="n">
-        <v>-3.491393446079607</v>
+        <v>-132.775470092475</v>
       </c>
       <c r="Y36" t="n">
-        <v>-2.379162291674752</v>
+        <v>-63.13913574671025</v>
       </c>
       <c r="Z36" t="n">
-        <v>-2.820039030693448</v>
+        <v>-73.4778165276139</v>
       </c>
       <c r="AA36" t="b">
         <v>1</v>
       </c>
       <c r="AB36" t="n">
-        <v>-0.215625</v>
+        <v>-0.23625843780135</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.105726872246696</v>
+        <v>0.2571428571428571</v>
       </c>
       <c r="AD36" t="n">
-        <v>-0.1804730524308116</v>
+        <v>-0.2006112562241394</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.0505582486588827</v>
+        <v>0.1491498690465682</v>
       </c>
       <c r="AF36" t="n">
-        <v>-0.2310313010896943</v>
+        <v>-0.3497611252707077</v>
       </c>
       <c r="AG36" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AH36" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="AI36" t="b">
         <v>0</v>
@@ -5475,25 +5457,27 @@
       <c r="AN36" t="b">
         <v>0</v>
       </c>
-      <c r="AO36" t="inlineStr"/>
+      <c r="AO36" t="n">
+        <v>4672.8</v>
+      </c>
       <c r="AP36" t="n">
-        <v>179.16</v>
+        <v>5915</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5502,7 +5486,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>25.6</v>
+        <v>25.4</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5511,24 +5495,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261027</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>7582000</v>
+        <v>5000</v>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="K37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" t="b">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>7582000</v>
+        <v>5000</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -5537,61 +5521,61 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>1560</v>
+        <v>150</v>
       </c>
       <c r="Q37" t="n">
-        <v>1560</v>
+        <v>150</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>6905267</v>
       </c>
       <c r="S37" t="n">
-        <v>1598</v>
+        <v>153.9</v>
       </c>
       <c r="T37" t="n">
-        <v>1802.5</v>
+        <v>166.075</v>
       </c>
       <c r="U37" t="n">
-        <v>1819.5</v>
+        <v>167.225</v>
       </c>
       <c r="V37" t="n">
-        <v>1763.25</v>
+        <v>153.0583333333333</v>
       </c>
       <c r="W37" t="n">
-        <v>-76.18148225963637</v>
+        <v>-4.16129569147904</v>
       </c>
       <c r="X37" t="n">
-        <v>-42.307608552985</v>
+        <v>-2.0869584045134</v>
       </c>
       <c r="Y37" t="n">
-        <v>-33.87387370665137</v>
+        <v>-2.07433728696564</v>
       </c>
       <c r="Z37" t="n">
-        <v>-38.61709800566484</v>
+        <v>-2.132823575035722</v>
       </c>
       <c r="AA37" t="b">
         <v>1</v>
       </c>
       <c r="AB37" t="n">
-        <v>-0.1789473684210526</v>
+        <v>-0.1329479768786127</v>
       </c>
       <c r="AC37" t="n">
-        <v>-0.01265822784810122</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AD37" t="n">
-        <v>-0.1437954208518643</v>
+        <v>-0.09730079530140212</v>
       </c>
       <c r="AE37" t="n">
-        <v>-0.06782685143591449</v>
+        <v>0.2253403452370444</v>
       </c>
       <c r="AF37" t="n">
-        <v>-0.07596856941594976</v>
+        <v>-0.3226411405384465</v>
       </c>
       <c r="AG37" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="AH37" t="n">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="AI37" t="b">
         <v>0</v>
@@ -5609,27 +5593,29 @@
         <v>1</v>
       </c>
       <c r="AN37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO37" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>173.4</v>
+      </c>
       <c r="AP37" t="n">
-        <v>2155.26</v>
+        <v>191.42</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5638,7 +5624,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>25</v>
+        <v>25.2</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5647,24 +5633,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261027</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>6331000</v>
+        <v>79618000</v>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" t="b">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>6331000</v>
+        <v>79618000</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -5673,61 +5659,61 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>1775</v>
+        <v>122.5</v>
       </c>
       <c r="Q38" t="n">
-        <v>1775</v>
+        <v>122.5</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>126613595</v>
       </c>
       <c r="S38" t="n">
-        <v>1868</v>
+        <v>125.7</v>
       </c>
       <c r="T38" t="n">
-        <v>1946.75</v>
+        <v>141.825</v>
       </c>
       <c r="U38" t="n">
-        <v>1953.75</v>
+        <v>143.7</v>
       </c>
       <c r="V38" t="n">
-        <v>2037.416666666667</v>
+        <v>133.95</v>
       </c>
       <c r="W38" t="n">
-        <v>-43.45481511940807</v>
+        <v>-6.165346641740683</v>
       </c>
       <c r="X38" t="n">
-        <v>-8.269818454290421</v>
+        <v>-4.026184085211822</v>
       </c>
       <c r="Y38" t="n">
-        <v>-35.18499666511764</v>
+        <v>-2.139162556528861</v>
       </c>
       <c r="Z38" t="n">
-        <v>-31.71775775549331</v>
+        <v>-2.379162291674752</v>
       </c>
       <c r="AA38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB38" t="n">
-        <v>-0.07310704960835512</v>
+        <v>-0.234375</v>
       </c>
       <c r="AC38" t="n">
-        <v>-0.1230146708437178</v>
+        <v>0.1951219512195121</v>
       </c>
       <c r="AD38" t="n">
-        <v>-0.03795510203916674</v>
+        <v>-0.1987278184227894</v>
       </c>
       <c r="AE38" t="n">
-        <v>-0.178183294431531</v>
+        <v>0.08712896312322327</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.1402281923923643</v>
+        <v>-0.2858567815460127</v>
       </c>
       <c r="AG38" t="n">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="AH38" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="AI38" t="b">
         <v>0</v>
@@ -5742,30 +5728,32 @@
         <v>0</v>
       </c>
       <c r="AM38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN38" t="b">
         <v>0</v>
       </c>
-      <c r="AO38" t="inlineStr"/>
+      <c r="AO38" t="n">
+        <v>146.75</v>
+      </c>
       <c r="AP38" t="n">
-        <v>2070.79</v>
+        <v>174.34</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5774,7 +5762,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>24.8</v>
+        <v>24.6</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5783,24 +5771,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261027</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2504000</v>
+        <v>7582000</v>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="K39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" t="b">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>2504000</v>
+        <v>7582000</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -5809,61 +5797,61 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>4890</v>
+        <v>1510</v>
       </c>
       <c r="Q39" t="n">
-        <v>4890</v>
+        <v>1510</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>18473608</v>
       </c>
       <c r="S39" t="n">
-        <v>4984</v>
+        <v>1572</v>
       </c>
       <c r="T39" t="n">
-        <v>5368</v>
+        <v>1783</v>
       </c>
       <c r="U39" t="n">
-        <v>5390.75</v>
+        <v>1802.5</v>
       </c>
       <c r="V39" t="n">
-        <v>5522.75</v>
+        <v>1763.5</v>
       </c>
       <c r="W39" t="n">
-        <v>-162.9110538741979</v>
+        <v>-82.43149098345225</v>
       </c>
       <c r="X39" t="n">
-        <v>-70.03737391815289</v>
+        <v>-50.33238503907849</v>
       </c>
       <c r="Y39" t="n">
-        <v>-92.87367995604504</v>
+        <v>-32.09910594437376</v>
       </c>
       <c r="Z39" t="n">
-        <v>-99.510181400411</v>
+        <v>-33.87387370665132</v>
       </c>
       <c r="AA39" t="b">
         <v>1</v>
       </c>
       <c r="AB39" t="n">
-        <v>-0.08512628624883067</v>
+        <v>-0.2052631578947368</v>
       </c>
       <c r="AC39" t="n">
-        <v>-0.05324298160696994</v>
+        <v>0.01003344481605351</v>
       </c>
       <c r="AD39" t="n">
-        <v>-0.04997433867964229</v>
+        <v>-0.1696159763175262</v>
       </c>
       <c r="AE39" t="n">
-        <v>-0.1084116051947832</v>
+        <v>-0.09795954328023537</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.05843726651514092</v>
+        <v>-0.07165643303729086</v>
       </c>
       <c r="AG39" t="n">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="AH39" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AI39" t="b">
         <v>0</v>
@@ -5885,23 +5873,23 @@
       </c>
       <c r="AO39" t="inlineStr"/>
       <c r="AP39" t="n">
-        <v>6123.16</v>
+        <v>2197.37</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5910,7 +5898,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>21.6</v>
+        <v>22.8</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5919,15 +5907,15 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261027</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>3281561</v>
+        <v>654000</v>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="K40" t="b">
         <v>0</v>
@@ -5936,7 +5924,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3281561</v>
+        <v>654000</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -5945,61 +5933,61 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>1840</v>
+        <v>420.5</v>
       </c>
       <c r="Q40" t="n">
-        <v>1840</v>
+        <v>420.5</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>4114718</v>
       </c>
       <c r="S40" t="n">
-        <v>1874</v>
+        <v>449.8</v>
       </c>
       <c r="T40" t="n">
-        <v>2061.5</v>
+        <v>495.825</v>
       </c>
       <c r="U40" t="n">
-        <v>2075.25</v>
+        <v>499.65</v>
       </c>
       <c r="V40" t="n">
-        <v>2143.447033691406</v>
+        <v>462.2666666666667</v>
       </c>
       <c r="W40" t="n">
-        <v>-90.28944482571478</v>
+        <v>-19.62717931946963</v>
       </c>
       <c r="X40" t="n">
-        <v>-65.26326544828217</v>
+        <v>-9.339828995562229</v>
       </c>
       <c r="Y40" t="n">
-        <v>-25.02617937743261</v>
+        <v>-10.2873503239074</v>
       </c>
       <c r="Z40" t="n">
-        <v>-29.51609433477743</v>
+        <v>-9.364113313695203</v>
       </c>
       <c r="AA40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>-0.1300236406619385</v>
+        <v>-0.1539235412474849</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.03261376660334414</v>
+        <v>0.3970099667774087</v>
       </c>
       <c r="AD40" t="n">
-        <v>-0.09487169309275012</v>
+        <v>-0.1182763596702743</v>
       </c>
       <c r="AE40" t="n">
-        <v>-0.02255485698446913</v>
+        <v>0.2890169786811199</v>
       </c>
       <c r="AF40" t="n">
-        <v>-0.07231683610828099</v>
+        <v>-0.4072933383513941</v>
       </c>
       <c r="AG40" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="AH40" t="n">
-        <v>32</v>
+        <v>76</v>
       </c>
       <c r="AI40" t="b">
         <v>0</v>
@@ -6014,32 +6002,30 @@
         <v>0</v>
       </c>
       <c r="AM40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN40" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO40" t="n">
-        <v>2123.36</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO40" t="inlineStr"/>
       <c r="AP40" t="n">
-        <v>2338.16</v>
+        <v>590.29</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>3376</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>新日興</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6048,7 +6034,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>21.6</v>
+        <v>22.6</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -6057,15 +6043,15 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261027</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>470000</v>
+        <v>1740000</v>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="K41" t="b">
         <v>0</v>
@@ -6074,7 +6060,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>470000</v>
+        <v>1740000</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -6083,61 +6069,61 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>3065</v>
+        <v>157.5</v>
       </c>
       <c r="Q41" t="n">
-        <v>3065</v>
+        <v>157.5</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>7250912</v>
       </c>
       <c r="S41" t="n">
-        <v>3126</v>
+        <v>172.7</v>
       </c>
       <c r="T41" t="n">
-        <v>3156.75</v>
+        <v>173</v>
       </c>
       <c r="U41" t="n">
-        <v>3188.5</v>
+        <v>173.95</v>
       </c>
       <c r="V41" t="n">
-        <v>3051.5</v>
+        <v>183.7011975606283</v>
       </c>
       <c r="W41" t="n">
-        <v>-33.31778705381976</v>
+        <v>-2.56679779765625</v>
       </c>
       <c r="X41" t="n">
-        <v>-25.5558731560258</v>
+        <v>-1.628288338966192</v>
       </c>
       <c r="Y41" t="n">
-        <v>-7.76191389779396</v>
+        <v>-0.9385094586900582</v>
       </c>
       <c r="Z41" t="n">
-        <v>-4.46073721663128</v>
+        <v>0.702390597453298</v>
       </c>
       <c r="AA41" t="b">
         <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>-0.1716216216216216</v>
+        <v>-0.1076487252124646</v>
       </c>
       <c r="AC41" t="n">
-        <v>0.2358870967741935</v>
+        <v>-0.04745346402203299</v>
       </c>
       <c r="AD41" t="n">
-        <v>-0.1364696740524333</v>
+        <v>-0.07200154363525402</v>
       </c>
       <c r="AE41" t="n">
-        <v>0.1807184731863802</v>
+        <v>-0.1554464521183219</v>
       </c>
       <c r="AF41" t="n">
-        <v>-0.3171881472388135</v>
+        <v>0.08344490848306785</v>
       </c>
       <c r="AG41" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="AH41" t="n">
-        <v>68</v>
+        <v>14</v>
       </c>
       <c r="AI41" t="b">
         <v>0</v>
@@ -6158,16 +6144,16 @@
         <v>1</v>
       </c>
       <c r="AO41" t="n">
-        <v>3156.95</v>
+        <v>168.21</v>
       </c>
       <c r="AP41" t="n">
-        <v>3571.58</v>
+        <v>190.32</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -6186,7 +6172,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>19.8</v>
+        <v>21.6</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6195,7 +6181,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261027</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -6221,61 +6207,61 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>414</v>
+        <v>441</v>
       </c>
       <c r="Q42" t="n">
-        <v>414</v>
+        <v>441</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>43888538</v>
       </c>
       <c r="S42" t="n">
-        <v>424.5</v>
+        <v>425.5</v>
       </c>
       <c r="T42" t="n">
+        <v>481</v>
+      </c>
+      <c r="U42" t="n">
         <v>484.7</v>
       </c>
-      <c r="U42" t="n">
-        <v>488.85</v>
-      </c>
       <c r="V42" t="n">
-        <v>486.525</v>
+        <v>487.9833333333333</v>
       </c>
       <c r="W42" t="n">
-        <v>-24.45214372603164</v>
+        <v>-21.52003481416489</v>
       </c>
       <c r="X42" t="n">
-        <v>-15.73211407377383</v>
+        <v>-16.88969822185205</v>
       </c>
       <c r="Y42" t="n">
-        <v>-8.720029652257804</v>
+        <v>-4.63033659231284</v>
       </c>
       <c r="Z42" t="n">
-        <v>-9.928546608342646</v>
+        <v>-8.7200296522578</v>
       </c>
       <c r="AA42" t="b">
         <v>1</v>
       </c>
       <c r="AB42" t="n">
-        <v>-0.1670020120724346</v>
+        <v>-0.1436893203883495</v>
       </c>
       <c r="AC42" t="n">
-        <v>0.05477707006369426</v>
+        <v>0.2475247524752475</v>
       </c>
       <c r="AD42" t="n">
-        <v>-0.1318500645032462</v>
+        <v>-0.1080421388111389</v>
       </c>
       <c r="AE42" t="n">
-        <v>-0.0003915535241190149</v>
+        <v>0.1395317643789586</v>
       </c>
       <c r="AF42" t="n">
-        <v>-0.1314585109791272</v>
+        <v>-0.2475739031900975</v>
       </c>
       <c r="AG42" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AH42" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="AI42" t="b">
         <v>0</v>
@@ -6293,27 +6279,29 @@
         <v>1</v>
       </c>
       <c r="AN42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO42" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>493.92</v>
+      </c>
       <c r="AP42" t="n">
-        <v>589.42</v>
+        <v>545.11</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6322,7 +6310,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6331,15 +6319,15 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261027</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1000</v>
+        <v>470000</v>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="K43" t="b">
         <v>0</v>
@@ -6348,7 +6336,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>1000</v>
+        <v>470000</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -6357,61 +6345,61 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>1100</v>
+        <v>2910</v>
       </c>
       <c r="Q43" t="n">
-        <v>1100</v>
+        <v>2910</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>510702</v>
       </c>
       <c r="S43" t="n">
-        <v>1119</v>
+        <v>3073</v>
       </c>
       <c r="T43" t="n">
-        <v>1174.75</v>
+        <v>3128.5</v>
       </c>
       <c r="U43" t="n">
-        <v>1182.75</v>
+        <v>3156.75</v>
       </c>
       <c r="V43" t="n">
-        <v>1325.416666666667</v>
+        <v>3060.5</v>
       </c>
       <c r="W43" t="n">
-        <v>-34.42748812810032</v>
+        <v>-53.34120822180239</v>
       </c>
       <c r="X43" t="n">
-        <v>-30.86356825555092</v>
+        <v>-31.11294016918112</v>
       </c>
       <c r="Y43" t="n">
-        <v>-3.563919872549398</v>
+        <v>-22.22826805262127</v>
       </c>
       <c r="Z43" t="n">
-        <v>-3.647991100184328</v>
+        <v>-7.76191389779396</v>
       </c>
       <c r="AA43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>-0.126984126984127</v>
+        <v>-0.162589928057554</v>
       </c>
       <c r="AC43" t="n">
-        <v>-0.1941391941391941</v>
+        <v>0.2278481012658229</v>
       </c>
       <c r="AD43" t="n">
-        <v>-0.0918321794149386</v>
+        <v>-0.1269427464803434</v>
       </c>
       <c r="AE43" t="n">
-        <v>-0.2493078177270074</v>
+        <v>0.119855113169534</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.1574756383120688</v>
+        <v>-0.2467978596498774</v>
       </c>
       <c r="AG43" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="AH43" t="n">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="AI43" t="b">
         <v>0</v>
@@ -6426,22 +6414,22 @@
         <v>0</v>
       </c>
       <c r="AM43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN43" t="b">
         <v>1</v>
       </c>
       <c r="AO43" t="n">
-        <v>1141.8</v>
+        <v>3160.26</v>
       </c>
       <c r="AP43" t="n">
-        <v>1308.68</v>
+        <v>3540</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6469,7 +6457,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261027</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -6495,61 +6483,61 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>826</v>
+        <v>814</v>
       </c>
       <c r="Q44" t="n">
-        <v>826</v>
+        <v>814</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>11961472</v>
       </c>
       <c r="S44" t="n">
-        <v>851.6</v>
+        <v>838</v>
       </c>
       <c r="T44" t="n">
+        <v>999</v>
+      </c>
+      <c r="U44" t="n">
         <v>1005.8</v>
       </c>
-      <c r="U44" t="n">
-        <v>1013.05</v>
-      </c>
       <c r="V44" t="n">
-        <v>959.5666666666667</v>
+        <v>958.7333333333333</v>
       </c>
       <c r="W44" t="n">
-        <v>-54.69348962362608</v>
+        <v>-57.42235528703225</v>
       </c>
       <c r="X44" t="n">
-        <v>-23.53130659602756</v>
+        <v>-30.3095163342285</v>
       </c>
       <c r="Y44" t="n">
+        <v>-27.11283895280375</v>
+      </c>
+      <c r="Z44" t="n">
         <v>-31.16218302759852</v>
       </c>
-      <c r="Z44" t="n">
-        <v>-34.98085203479899</v>
-      </c>
       <c r="AA44" t="b">
         <v>1</v>
       </c>
       <c r="AB44" t="n">
-        <v>-0.149330587023687</v>
+        <v>-0.1431578947368422</v>
       </c>
       <c r="AC44" t="n">
-        <v>-0.1386861313868614</v>
+        <v>-0.05787037037037035</v>
       </c>
       <c r="AD44" t="n">
-        <v>-0.1141786394544986</v>
+        <v>-0.1075107131596316</v>
       </c>
       <c r="AE44" t="n">
-        <v>-0.1938547549746746</v>
+        <v>-0.1658633584666592</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.07967611552017606</v>
+        <v>0.05835264530702766</v>
       </c>
       <c r="AG44" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AH44" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AI44" t="b">
         <v>0</v>
@@ -6571,23 +6559,23 @@
       </c>
       <c r="AO44" t="inlineStr"/>
       <c r="AP44" t="n">
-        <v>1139.26</v>
+        <v>1142.74</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6596,7 +6584,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>18</v>
+        <v>17.6</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6605,15 +6593,15 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261027</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>478000</v>
+        <v>1000</v>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="K45" t="b">
         <v>0</v>
@@ -6622,7 +6610,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>478000</v>
+        <v>1000</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
@@ -6631,61 +6619,61 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>764</v>
+        <v>1955</v>
       </c>
       <c r="Q45" t="n">
-        <v>764</v>
+        <v>1955</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>3620562</v>
       </c>
       <c r="S45" t="n">
-        <v>788.8</v>
+        <v>1985</v>
       </c>
       <c r="T45" t="n">
-        <v>843.6</v>
+        <v>2153</v>
       </c>
       <c r="U45" t="n">
-        <v>850.3</v>
+        <v>2171.5</v>
       </c>
       <c r="V45" t="n">
-        <v>935.8</v>
+        <v>2129.916666666667</v>
       </c>
       <c r="W45" t="n">
-        <v>-29.02271865090165</v>
+        <v>-69.92818045076706</v>
       </c>
       <c r="X45" t="n">
-        <v>-21.78708474720425</v>
+        <v>-44.00523729951917</v>
       </c>
       <c r="Y45" t="n">
-        <v>-7.235633903697405</v>
+        <v>-25.92294315124789</v>
       </c>
       <c r="Z45" t="n">
-        <v>-6.64112264341037</v>
+        <v>-30.15236553389909</v>
       </c>
       <c r="AA45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB45" t="n">
-        <v>-0.1492204899777283</v>
+        <v>-0.1591397849462366</v>
       </c>
       <c r="AC45" t="n">
-        <v>-0.2509803921568627</v>
+        <v>0.06539509536784749</v>
       </c>
       <c r="AD45" t="n">
-        <v>-0.1140685424085399</v>
+        <v>-0.123492603369026</v>
       </c>
       <c r="AE45" t="n">
-        <v>-0.306149015744676</v>
+        <v>-0.04259789272844139</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.1920804733361361</v>
+        <v>-0.08089471064058462</v>
       </c>
       <c r="AG45" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="AH45" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="AI45" t="b">
         <v>0</v>
@@ -6700,32 +6688,32 @@
         <v>0</v>
       </c>
       <c r="AM45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN45" t="b">
         <v>1</v>
       </c>
       <c r="AO45" t="n">
-        <v>846.51</v>
+        <v>2248.25</v>
       </c>
       <c r="AP45" t="n">
-        <v>975.79</v>
+        <v>2503.42</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6734,7 +6722,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>17.6</v>
+        <v>17.4</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6743,15 +6731,15 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261027</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>5143000</v>
+        <v>2504000</v>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="K46" t="b">
         <v>0</v>
@@ -6760,7 +6748,7 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>5143000</v>
+        <v>2504000</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
@@ -6769,61 +6757,61 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>4010</v>
+        <v>4790</v>
       </c>
       <c r="Q46" t="n">
-        <v>4010</v>
+        <v>4790</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>857431</v>
       </c>
       <c r="S46" t="n">
-        <v>4103</v>
+        <v>4895</v>
       </c>
       <c r="T46" t="n">
-        <v>4619.75</v>
+        <v>5326.5</v>
       </c>
       <c r="U46" t="n">
-        <v>4678.25</v>
+        <v>5368</v>
       </c>
       <c r="V46" t="n">
-        <v>4308.583333333333</v>
+        <v>5522.75</v>
       </c>
       <c r="W46" t="n">
-        <v>-190.4685026834113</v>
+        <v>-181.4637122785407</v>
       </c>
       <c r="X46" t="n">
-        <v>-116.9906861557974</v>
+        <v>-92.32264159023076</v>
       </c>
       <c r="Y46" t="n">
-        <v>-73.47781652761395</v>
+        <v>-89.14107068830994</v>
       </c>
       <c r="Z46" t="n">
-        <v>-85.20313921336663</v>
+        <v>-92.87367995604467</v>
       </c>
       <c r="AA46" t="b">
         <v>1</v>
       </c>
       <c r="AB46" t="n">
-        <v>-0.2258687258687259</v>
+        <v>-0.1476868327402135</v>
       </c>
       <c r="AC46" t="n">
-        <v>0.2096530920060331</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>-0.1907167782995375</v>
+        <v>-0.112039651163003</v>
       </c>
       <c r="AE46" t="n">
-        <v>0.1544844684182198</v>
+        <v>-0.1079929880962889</v>
       </c>
       <c r="AF46" t="n">
-        <v>-0.3452012467177573</v>
+        <v>-0.004046663066714085</v>
       </c>
       <c r="AG46" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="AH46" t="n">
-        <v>57.99999999999999</v>
+        <v>16</v>
       </c>
       <c r="AI46" t="b">
         <v>0</v>
@@ -6845,23 +6833,23 @@
       </c>
       <c r="AO46" t="inlineStr"/>
       <c r="AP46" t="n">
-        <v>5826.84</v>
+        <v>5979.74</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6870,7 +6858,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>17.4</v>
+        <v>16.8</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6879,15 +6867,15 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261027</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>2887848</v>
+        <v>957000</v>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="K47" t="b">
         <v>0</v>
@@ -6896,7 +6884,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>2887848</v>
+        <v>957000</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
@@ -6905,61 +6893,61 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>1875</v>
+        <v>467.5</v>
       </c>
       <c r="Q47" t="n">
-        <v>1875</v>
+        <v>467.5</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>782307</v>
       </c>
       <c r="S47" t="n">
-        <v>1920</v>
+        <v>465.1</v>
       </c>
       <c r="T47" t="n">
-        <v>2239</v>
+        <v>536.175</v>
       </c>
       <c r="U47" t="n">
-        <v>2257.5</v>
+        <v>542.3</v>
       </c>
       <c r="V47" t="n">
-        <v>2167.916666666667</v>
+        <v>545.025</v>
       </c>
       <c r="W47" t="n">
-        <v>-107.5096521184209</v>
+        <v>-29.813879631237</v>
       </c>
       <c r="X47" t="n">
-        <v>-56.06220321837168</v>
+        <v>-20.50011714195697</v>
       </c>
       <c r="Y47" t="n">
-        <v>-51.44744890004927</v>
+        <v>-9.313762489280034</v>
       </c>
       <c r="Z47" t="n">
-        <v>-58.99771901609137</v>
+        <v>-12.61019885582612</v>
       </c>
       <c r="AA47" t="b">
         <v>1</v>
       </c>
       <c r="AB47" t="n">
-        <v>-0.1648106904231625</v>
+        <v>-0.2076271186440678</v>
       </c>
       <c r="AC47" t="n">
-        <v>-0.1534988713318285</v>
+        <v>0.2158647594278285</v>
       </c>
       <c r="AD47" t="n">
-        <v>-0.1296587428539742</v>
+        <v>-0.1719799370668572</v>
       </c>
       <c r="AE47" t="n">
-        <v>-0.2086674949196418</v>
+        <v>0.1078717713315396</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.0790087520656676</v>
+        <v>-0.2798517083983968</v>
       </c>
       <c r="AG47" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="AH47" t="n">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="AI47" t="b">
         <v>0</v>
@@ -6981,13 +6969,13 @@
       </c>
       <c r="AO47" t="inlineStr"/>
       <c r="AP47" t="n">
-        <v>2723.16</v>
+        <v>635.29</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -7006,7 +6994,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>17.2</v>
+        <v>16.6</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -7015,7 +7003,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261027</t>
         </is>
       </c>
       <c r="H48" t="n">
@@ -7041,61 +7029,61 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>16010</v>
+        <v>16015</v>
       </c>
       <c r="Q48" t="n">
-        <v>16010</v>
+        <v>16015</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>373678</v>
       </c>
       <c r="S48" t="n">
-        <v>16083</v>
+        <v>16090</v>
       </c>
       <c r="T48" t="n">
+        <v>17550</v>
+      </c>
+      <c r="U48" t="n">
         <v>17763.25</v>
       </c>
-      <c r="U48" t="n">
-        <v>18008</v>
-      </c>
       <c r="V48" t="n">
-        <v>17201.08333333333</v>
+        <v>17252.83333333333</v>
       </c>
       <c r="W48" t="n">
-        <v>-640.9248364591585</v>
+        <v>-616.1500488829661</v>
       </c>
       <c r="X48" t="n">
-        <v>-497.1917022671736</v>
+        <v>-520.9833715903321</v>
       </c>
       <c r="Y48" t="n">
+        <v>-95.16667729263395</v>
+      </c>
+      <c r="Z48" t="n">
         <v>-143.733134191985</v>
       </c>
-      <c r="Z48" t="n">
-        <v>-191.8076341820029</v>
-      </c>
       <c r="AA48" t="b">
         <v>1</v>
       </c>
       <c r="AB48" t="n">
-        <v>-0.2341545084907917</v>
+        <v>-0.2103057199211046</v>
       </c>
       <c r="AC48" t="n">
-        <v>0.2101284958427816</v>
+        <v>0.2405112316034081</v>
       </c>
       <c r="AD48" t="n">
-        <v>-0.1990025609216033</v>
+        <v>-0.174658538343894</v>
       </c>
       <c r="AE48" t="n">
-        <v>0.1549598722549683</v>
+        <v>0.1325182435071193</v>
       </c>
       <c r="AF48" t="n">
-        <v>-0.3539624331765716</v>
+        <v>-0.3071767818510133</v>
       </c>
       <c r="AG48" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AH48" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AI48" t="b">
         <v>0</v>
@@ -7116,26 +7104,26 @@
         <v>1</v>
       </c>
       <c r="AO48" t="n">
-        <v>17643.02</v>
+        <v>17104.02</v>
       </c>
       <c r="AP48" t="n">
-        <v>22125.53</v>
+        <v>21450.79</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -7144,7 +7132,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>16</v>
+        <v>10.2</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -7153,15 +7141,15 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261027</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>93000</v>
+        <v>2887848</v>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="K49" t="b">
         <v>0</v>
@@ -7170,7 +7158,7 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>93000</v>
+        <v>2887848</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
@@ -7179,61 +7167,61 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>4795</v>
+        <v>1735</v>
       </c>
       <c r="Q49" t="n">
-        <v>4795</v>
+        <v>1735</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>5643357</v>
       </c>
       <c r="S49" t="n">
-        <v>4936</v>
+        <v>1872</v>
       </c>
       <c r="T49" t="n">
-        <v>5549.75</v>
+        <v>2208.75</v>
       </c>
       <c r="U49" t="n">
-        <v>5598.25</v>
+        <v>2239</v>
       </c>
       <c r="V49" t="n">
-        <v>6194.166666666667</v>
+        <v>2162</v>
       </c>
       <c r="W49" t="n">
-        <v>-320.9953367468215</v>
+        <v>-124.0828601908347</v>
       </c>
       <c r="X49" t="n">
-        <v>-265.9066634577269</v>
+        <v>-69.66633461286429</v>
       </c>
       <c r="Y49" t="n">
-        <v>-55.08867328909463</v>
+        <v>-54.41652557797042</v>
       </c>
       <c r="Z49" t="n">
-        <v>-64.08639858755203</v>
+        <v>-51.44744890004927</v>
       </c>
       <c r="AA49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>-0.1682567215958369</v>
+        <v>-0.2585470085470085</v>
       </c>
       <c r="AC49" t="n">
-        <v>-0.1920808761583824</v>
+        <v>-0.1698564593301436</v>
       </c>
       <c r="AD49" t="n">
-        <v>-0.1331047740266486</v>
+        <v>-0.2228998269697979</v>
       </c>
       <c r="AE49" t="n">
-        <v>-0.2472494997461957</v>
+        <v>-0.2778494474264325</v>
       </c>
       <c r="AF49" t="n">
-        <v>0.1141447257195471</v>
+        <v>0.05494962045663454</v>
       </c>
       <c r="AG49" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="AH49" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AI49" t="b">
         <v>0</v>
@@ -7248,32 +7236,30 @@
         <v>0</v>
       </c>
       <c r="AM49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN49" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO49" t="n">
-        <v>5418.35</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO49" t="inlineStr"/>
       <c r="AP49" t="n">
-        <v>6789.47</v>
+        <v>2838.68</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7282,24 +7268,24 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>15.4</v>
+        <v>10.2</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Sell</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261027</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1000</v>
+        <v>378000</v>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="K50" t="b">
         <v>0</v>
@@ -7308,70 +7294,70 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>1000</v>
+        <v>478000</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>-100000</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>-0.2092050209205021</v>
       </c>
       <c r="P50" t="n">
-        <v>1980</v>
+        <v>775</v>
       </c>
       <c r="Q50" t="n">
-        <v>1980</v>
+        <v>775</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1494384</v>
       </c>
       <c r="S50" t="n">
-        <v>1995</v>
+        <v>781.2</v>
       </c>
       <c r="T50" t="n">
-        <v>2171.5</v>
+        <v>837.75</v>
       </c>
       <c r="U50" t="n">
-        <v>2194.5</v>
+        <v>843.6</v>
       </c>
       <c r="V50" t="n">
-        <v>2127.916666666667</v>
+        <v>932.3666666666667</v>
       </c>
       <c r="W50" t="n">
-        <v>-67.67686704560629</v>
+        <v>-28.74550961295142</v>
       </c>
       <c r="X50" t="n">
-        <v>-37.52450151170718</v>
+        <v>-23.17876972035369</v>
       </c>
       <c r="Y50" t="n">
-        <v>-30.15236553389911</v>
+        <v>-5.566739892597738</v>
       </c>
       <c r="Z50" t="n">
-        <v>-36.03491906185214</v>
+        <v>-7.235633903697401</v>
       </c>
       <c r="AA50" t="b">
         <v>1</v>
       </c>
       <c r="AB50" t="n">
-        <v>-0.1885245901639344</v>
+        <v>-0.1311659192825112</v>
       </c>
       <c r="AC50" t="n">
-        <v>0.02061855670103085</v>
+        <v>-0.2099898063200816</v>
       </c>
       <c r="AD50" t="n">
-        <v>-0.153372642594746</v>
+        <v>-0.09551873770530062</v>
       </c>
       <c r="AE50" t="n">
-        <v>-0.03455006688678242</v>
+        <v>-0.3179827944163705</v>
       </c>
       <c r="AF50" t="n">
-        <v>-0.1188225757079636</v>
+        <v>0.2224640567110698</v>
       </c>
       <c r="AG50" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="AH50" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="AI50" t="b">
         <v>0</v>
@@ -7389,29 +7375,29 @@
         <v>1</v>
       </c>
       <c r="AN50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO50" t="n">
-        <v>2320.56</v>
+        <v>838.55</v>
       </c>
       <c r="AP50" t="n">
-        <v>2526.58</v>
+        <v>963.05</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7420,24 +7406,24 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>14.2</v>
+        <v>5.8</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Sell</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261027</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>957000</v>
+        <v>85000</v>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="K51" t="b">
         <v>0</v>
@@ -7446,70 +7432,70 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>957000</v>
+        <v>93000</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>-8000</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>-0.08602150537634409</v>
       </c>
       <c r="P51" t="n">
-        <v>450</v>
+        <v>4775</v>
       </c>
       <c r="Q51" t="n">
-        <v>450</v>
+        <v>4775</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>568234</v>
       </c>
       <c r="S51" t="n">
-        <v>467.6</v>
+        <v>4859</v>
       </c>
       <c r="T51" t="n">
-        <v>542.3</v>
+        <v>5488.75</v>
       </c>
       <c r="U51" t="n">
-        <v>550.05</v>
+        <v>5549.75</v>
       </c>
       <c r="V51" t="n">
-        <v>543.6416666666667</v>
+        <v>6183.5</v>
       </c>
       <c r="W51" t="n">
-        <v>-30.78187537546307</v>
+        <v>-318.5925976831195</v>
       </c>
       <c r="X51" t="n">
-        <v>-18.17167651963695</v>
+        <v>-276.4438503028055</v>
       </c>
       <c r="Y51" t="n">
-        <v>-12.61019885582613</v>
+        <v>-42.14874738031403</v>
       </c>
       <c r="Z51" t="n">
-        <v>-13.25103257927172</v>
+        <v>-55.08867328909457</v>
       </c>
       <c r="AA51" t="b">
         <v>1</v>
       </c>
       <c r="AB51" t="n">
-        <v>-0.2561983471074381</v>
+        <v>-0.2035029190992493</v>
       </c>
       <c r="AC51" t="n">
-        <v>0.05386416861826704</v>
+        <v>-0.1181902123730378</v>
       </c>
       <c r="AD51" t="n">
-        <v>-0.2210463995382497</v>
+        <v>-0.1678557375220388</v>
       </c>
       <c r="AE51" t="n">
-        <v>-0.001304454969546232</v>
+        <v>-0.2261832004693267</v>
       </c>
       <c r="AF51" t="n">
-        <v>-0.2197419445687034</v>
+        <v>0.05832746294728797</v>
       </c>
       <c r="AG51" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="AH51" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="AI51" t="b">
         <v>0</v>
@@ -7527,11 +7513,13 @@
         <v>1</v>
       </c>
       <c r="AN51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO51" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>5252.5</v>
+      </c>
       <c r="AP51" t="n">
-        <v>687.16</v>
+        <v>6601.32</v>
       </c>
     </row>
   </sheetData>

--- a/output/daily_screen_latest.xlsx
+++ b/output/daily_screen_latest.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -703,7 +703,7 @@
         <v>19.75</v>
       </c>
       <c r="R2" t="n">
-        <v>49445359</v>
+        <v>49291390</v>
       </c>
       <c r="S2" t="n">
         <v>19.60999984741211</v>
@@ -813,7 +813,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -845,7 +845,7 @@
         <v>100.5</v>
       </c>
       <c r="R3" t="n">
-        <v>2631762</v>
+        <v>2617057</v>
       </c>
       <c r="S3" t="n">
         <v>100.2199996948242</v>
@@ -951,7 +951,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -983,7 +983,7 @@
         <v>247.5</v>
       </c>
       <c r="R4" t="n">
-        <v>52590870</v>
+        <v>52105881</v>
       </c>
       <c r="S4" t="n">
         <v>245.8</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1123,7 +1123,7 @@
         <v>327.5</v>
       </c>
       <c r="R5" t="n">
-        <v>15061382</v>
+        <v>14877430</v>
       </c>
       <c r="S5" t="n">
         <v>324.1</v>
@@ -1222,7 +1222,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>56.8</v>
+        <v>58.2</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1231,15 +1231,15 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>6979000</v>
+        <v>7636000</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K6" t="b">
         <v>1</v>
@@ -1248,13 +1248,13 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>6899000</v>
+        <v>6979000</v>
       </c>
       <c r="N6" t="n">
-        <v>80000</v>
+        <v>657000</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01159588346137121</v>
+        <v>0.09413956154176815</v>
       </c>
       <c r="P6" t="n">
         <v>1080</v>
@@ -1263,7 +1263,7 @@
         <v>1080</v>
       </c>
       <c r="R6" t="n">
-        <v>9249607</v>
+        <v>8987041</v>
       </c>
       <c r="S6" t="n">
         <v>1138</v>
@@ -1367,11 +1367,11 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>9968000</v>
+        <v>11944000</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
@@ -1384,13 +1384,13 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>8895000</v>
+        <v>9968000</v>
       </c>
       <c r="N7" t="n">
-        <v>1073000</v>
+        <v>1976000</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1206295671725689</v>
+        <v>0.1982343499197432</v>
       </c>
       <c r="P7" t="n">
         <v>651</v>
@@ -1399,7 +1399,7 @@
         <v>651</v>
       </c>
       <c r="R7" t="n">
-        <v>25585620</v>
+        <v>25176454</v>
       </c>
       <c r="S7" t="n">
         <v>660.6</v>
@@ -1480,12 +1480,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1494,24 +1494,24 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>54.6</v>
+        <v>53.40000000000001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>13046000</v>
+        <v>8937000</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K8" t="b">
         <v>1</v>
@@ -1520,76 +1520,76 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>12671000</v>
+        <v>8937000</v>
       </c>
       <c r="N8" t="n">
-        <v>375000</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0295951385052482</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2400</v>
+        <v>1255</v>
       </c>
       <c r="Q8" t="n">
-        <v>2400</v>
+        <v>1255</v>
       </c>
       <c r="R8" t="n">
-        <v>35766965</v>
+        <v>10198034</v>
       </c>
       <c r="S8" t="n">
-        <v>2399</v>
+        <v>1286</v>
       </c>
       <c r="T8" t="n">
-        <v>2476.5</v>
+        <v>1375.25</v>
       </c>
       <c r="U8" t="n">
-        <v>2481.5</v>
+        <v>1373</v>
       </c>
       <c r="V8" t="n">
-        <v>2424.348356119792</v>
+        <v>1210</v>
       </c>
       <c r="W8" t="n">
-        <v>-25.50850595834754</v>
+        <v>-14.10378787195941</v>
       </c>
       <c r="X8" t="n">
-        <v>-11.47065173465664</v>
+        <v>18.543737774572</v>
       </c>
       <c r="Y8" t="n">
-        <v>-14.0378542236909</v>
+        <v>-32.64752564653142</v>
       </c>
       <c r="Z8" t="n">
-        <v>-17.90009387185703</v>
+        <v>-33.65749788527849</v>
       </c>
       <c r="AA8" t="b">
         <v>1</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.04000000000000004</v>
+        <v>0.03719008264462809</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.09412034967687477</v>
+        <v>0.4277588168373152</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0.004352818422789451</v>
+        <v>0.07283726422183867</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0.01387263841941411</v>
+        <v>0.3197658287410263</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.009519819996624657</v>
+        <v>-0.2469285645191877</v>
       </c>
       <c r="AG8" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AH8" t="n">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
       <c r="AJ8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK8" t="b">
         <v>0</v>
@@ -1601,13 +1601,13 @@
         <v>1</v>
       </c>
       <c r="AN8" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>2558.4</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>2555.53</v>
+        <v>0</v>
+      </c>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -1618,12 +1618,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1632,24 +1632,24 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53.40000000000001</v>
+        <v>51.8</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>8937000</v>
+        <v>19739000</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K9" t="b">
         <v>1</v>
@@ -1658,76 +1658,76 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>8937000</v>
+        <v>19689000</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>0.002539489054802174</v>
       </c>
       <c r="P9" t="n">
-        <v>1255</v>
+        <v>1060</v>
       </c>
       <c r="Q9" t="n">
-        <v>1255</v>
+        <v>1060</v>
       </c>
       <c r="R9" t="n">
-        <v>10348912</v>
+        <v>29151623</v>
       </c>
       <c r="S9" t="n">
-        <v>1286</v>
+        <v>1077</v>
       </c>
       <c r="T9" t="n">
-        <v>1375.25</v>
+        <v>1177.25</v>
       </c>
       <c r="U9" t="n">
-        <v>1373</v>
+        <v>1182.25</v>
       </c>
       <c r="V9" t="n">
-        <v>1210</v>
+        <v>1061.933333333333</v>
       </c>
       <c r="W9" t="n">
-        <v>-14.10378787195941</v>
+        <v>-23.38602191958125</v>
       </c>
       <c r="X9" t="n">
-        <v>18.543737774572</v>
+        <v>-2.819302364148833</v>
       </c>
       <c r="Y9" t="n">
-        <v>-32.64752564653142</v>
+        <v>-20.56671955543242</v>
       </c>
       <c r="Z9" t="n">
-        <v>-33.65749788527849</v>
+        <v>-22.30077112154821</v>
       </c>
       <c r="AA9" t="b">
         <v>1</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.03719008264462809</v>
+        <v>-0.08620689655172409</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.4277588168373152</v>
+        <v>0.5406976744186047</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.07283726422183867</v>
+        <v>-0.0505597149745135</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.3197658287410263</v>
+        <v>0.4327046863223158</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.2469285645191877</v>
+        <v>-0.4832644012968293</v>
       </c>
       <c r="AG9" t="n">
+        <v>50</v>
+      </c>
+      <c r="AH9" t="n">
         <v>88</v>
       </c>
-      <c r="AH9" t="n">
-        <v>78</v>
-      </c>
       <c r="AI9" t="b">
         <v>0</v>
       </c>
       <c r="AJ9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="b">
         <v>0</v>
@@ -1742,10 +1742,8 @@
         <v>0</v>
       </c>
       <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+      <c r="AP9" t="n">
+        <v>1308.42</v>
       </c>
     </row>
     <row r="10">
@@ -1779,7 +1777,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1811,7 +1809,7 @@
         <v>278.5</v>
       </c>
       <c r="R10" t="n">
-        <v>18593088</v>
+        <v>18438940</v>
       </c>
       <c r="S10" t="n">
         <v>292.8</v>
@@ -1896,12 +1894,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1910,102 +1908,102 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>46.8</v>
+        <v>46</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>7556450</v>
+        <v>121000</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="K11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="b">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>6587450</v>
+        <v>121000</v>
       </c>
       <c r="N11" t="n">
-        <v>969000</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1470978906860773</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>269</v>
+        <v>1285</v>
       </c>
       <c r="Q11" t="n">
-        <v>269</v>
+        <v>1285</v>
       </c>
       <c r="R11" t="n">
-        <v>25732274</v>
+        <v>2066666</v>
       </c>
       <c r="S11" t="n">
-        <v>266.3</v>
+        <v>1291</v>
       </c>
       <c r="T11" t="n">
-        <v>286.55</v>
+        <v>1400.25</v>
       </c>
       <c r="U11" t="n">
-        <v>288.3</v>
+        <v>1396.25</v>
       </c>
       <c r="V11" t="n">
-        <v>266.5</v>
+        <v>1285.028885904948</v>
       </c>
       <c r="W11" t="n">
-        <v>-6.439246733244204</v>
+        <v>-30.09157402581354</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.198326649822184</v>
+        <v>6.281712615044271</v>
       </c>
       <c r="Y11" t="n">
-        <v>-3.24092008342202</v>
+        <v>-36.37328664085781</v>
       </c>
       <c r="Z11" t="n">
-        <v>-4.489412957966038</v>
+        <v>-41.34986774007167</v>
       </c>
       <c r="AA11" t="b">
         <v>1</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0.1151315789473685</v>
+        <v>0.06639004149377592</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.2658823529411765</v>
+        <v>0.4621730953688772</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0.07948439737015789</v>
+        <v>0.1020372230709865</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.1578893648448876</v>
+        <v>0.3541801072725883</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.2373737622150455</v>
+        <v>-0.2521428842016018</v>
       </c>
       <c r="AG11" t="n">
-        <v>36</v>
+        <v>96</v>
       </c>
       <c r="AH11" t="n">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="AI11" t="b">
         <v>0</v>
       </c>
       <c r="AJ11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK11" t="b">
         <v>0</v>
@@ -2017,13 +2015,13 @@
         <v>1</v>
       </c>
       <c r="AN11" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>305.58</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>329.47</v>
+        <v>0</v>
+      </c>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -2034,12 +2032,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2048,7 +2046,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>46</v>
+        <v>45.2</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2057,15 +2055,15 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>121000</v>
+        <v>1000</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="K12" t="b">
         <v>0</v>
@@ -2074,7 +2072,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>121000</v>
+        <v>1000</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -2083,61 +2081,61 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1285</v>
+        <v>520</v>
       </c>
       <c r="Q12" t="n">
-        <v>1285</v>
+        <v>520</v>
       </c>
       <c r="R12" t="n">
-        <v>2121638</v>
+        <v>44188301</v>
       </c>
       <c r="S12" t="n">
-        <v>1291</v>
+        <v>555.8</v>
       </c>
       <c r="T12" t="n">
-        <v>1400.25</v>
+        <v>549.55</v>
       </c>
       <c r="U12" t="n">
-        <v>1396.25</v>
+        <v>547.2</v>
       </c>
       <c r="V12" t="n">
-        <v>1285.028885904948</v>
+        <v>498.7333333333333</v>
       </c>
       <c r="W12" t="n">
-        <v>-30.09157402581354</v>
+        <v>4.908876771783525</v>
       </c>
       <c r="X12" t="n">
-        <v>6.281712615044271</v>
+        <v>11.22699949399457</v>
       </c>
       <c r="Y12" t="n">
-        <v>-36.37328664085781</v>
+        <v>-6.318122722211049</v>
       </c>
       <c r="Z12" t="n">
-        <v>-41.34986774007167</v>
+        <v>-2.170850959171391</v>
       </c>
       <c r="AA12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.06639004149377592</v>
+        <v>0.09936575052854124</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.4621730953688772</v>
+        <v>0.2855377008652658</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.1020372230709865</v>
+        <v>0.1350129321057518</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.3541801072725883</v>
+        <v>0.1775447127689769</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.2521428842016018</v>
+        <v>-0.04253178066322505</v>
       </c>
       <c r="AG12" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AH12" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="AI12" t="b">
         <v>0</v>
@@ -2152,12 +2150,14 @@
         <v>0</v>
       </c>
       <c r="AM12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO12" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>591.76</v>
+      </c>
       <c r="AP12" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -2172,12 +2172,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2186,7 +2186,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>45.2</v>
+        <v>44.6</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2195,24 +2195,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1000</v>
+        <v>13046000</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="K13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="b">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1000</v>
+        <v>13046000</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -2221,67 +2221,67 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>520</v>
+        <v>2400</v>
       </c>
       <c r="Q13" t="n">
-        <v>520</v>
+        <v>2400</v>
       </c>
       <c r="R13" t="n">
-        <v>45376020</v>
+        <v>33964182</v>
       </c>
       <c r="S13" t="n">
-        <v>555.8</v>
+        <v>2399</v>
       </c>
       <c r="T13" t="n">
-        <v>549.55</v>
+        <v>2476.5</v>
       </c>
       <c r="U13" t="n">
-        <v>547.2</v>
+        <v>2481.5</v>
       </c>
       <c r="V13" t="n">
-        <v>498.7333333333333</v>
+        <v>2424.348356119792</v>
       </c>
       <c r="W13" t="n">
-        <v>4.908876771783525</v>
+        <v>-25.50850595855854</v>
       </c>
       <c r="X13" t="n">
-        <v>11.22699949399457</v>
+        <v>-11.47065173507779</v>
       </c>
       <c r="Y13" t="n">
-        <v>-6.318122722211049</v>
+        <v>-14.03785422348076</v>
       </c>
       <c r="Z13" t="n">
-        <v>-2.170850959171391</v>
+        <v>-17.90009387162073</v>
       </c>
       <c r="AA13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.09936575052854124</v>
+        <v>-0.04000000000000004</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.2855377008652658</v>
+        <v>0.09412034967687477</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.1350129321057518</v>
+        <v>-0.004352818422789451</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.1775447127689769</v>
+        <v>-0.01387263841941411</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.04253178066322505</v>
+        <v>0.009519819996624657</v>
       </c>
       <c r="AG13" t="n">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AH13" t="n">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="AI13" t="b">
         <v>0</v>
       </c>
       <c r="AJ13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="b">
         <v>0</v>
@@ -2290,18 +2290,16 @@
         <v>0</v>
       </c>
       <c r="AM13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN13" t="b">
         <v>1</v>
       </c>
       <c r="AO13" t="n">
-        <v>591.76</v>
-      </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>2558.4</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>2555.53</v>
       </c>
     </row>
     <row r="14">
@@ -2312,12 +2310,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2326,7 +2324,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>43</v>
+        <v>42.2</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2335,24 +2333,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>19689000</v>
+        <v>4827000</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="K14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="b">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>19689000</v>
+        <v>4827000</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2361,61 +2359,61 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1060</v>
+        <v>248</v>
       </c>
       <c r="Q14" t="n">
-        <v>1060</v>
+        <v>248</v>
       </c>
       <c r="R14" t="n">
-        <v>29758483</v>
+        <v>16611569</v>
       </c>
       <c r="S14" t="n">
-        <v>1077</v>
+        <v>250.6</v>
       </c>
       <c r="T14" t="n">
-        <v>1177.25</v>
+        <v>253.575</v>
       </c>
       <c r="U14" t="n">
-        <v>1182.25</v>
+        <v>253.775</v>
       </c>
       <c r="V14" t="n">
-        <v>1061.933333333333</v>
+        <v>232.8083333333333</v>
       </c>
       <c r="W14" t="n">
-        <v>-23.38602191958125</v>
+        <v>-0.4276564339809283</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.819302364148833</v>
+        <v>2.707088558435337</v>
       </c>
       <c r="Y14" t="n">
-        <v>-20.56671955543242</v>
+        <v>-3.134744992416265</v>
       </c>
       <c r="Z14" t="n">
-        <v>-22.30077112154821</v>
+        <v>-3.165791552069547</v>
       </c>
       <c r="AA14" t="b">
         <v>1</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0.08620689655172409</v>
+        <v>-0.01587301587301593</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.5406976744186047</v>
+        <v>0.4850299401197604</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0.0505597149745135</v>
+        <v>0.01977416570419466</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.4327046863223158</v>
+        <v>0.3770369520234715</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.4832644012968293</v>
+        <v>-0.3572627863192769</v>
       </c>
       <c r="AG14" t="n">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="AH14" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="AI14" t="b">
         <v>0</v>
@@ -2433,11 +2431,13 @@
         <v>1</v>
       </c>
       <c r="AN14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>283.71</v>
+      </c>
       <c r="AP14" t="n">
-        <v>1308.42</v>
+        <v>251.87</v>
       </c>
     </row>
     <row r="15">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2471,15 +2471,15 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>4827000</v>
+        <v>1000</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="K15" t="b">
         <v>0</v>
@@ -2488,7 +2488,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>4827000</v>
+        <v>1000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2497,61 +2497,61 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>248</v>
+        <v>6000</v>
       </c>
       <c r="Q15" t="n">
-        <v>248</v>
+        <v>6000</v>
       </c>
       <c r="R15" t="n">
-        <v>16776474</v>
+        <v>2633916</v>
       </c>
       <c r="S15" t="n">
-        <v>250.6</v>
+        <v>6099</v>
       </c>
       <c r="T15" t="n">
-        <v>253.575</v>
+        <v>6451</v>
       </c>
       <c r="U15" t="n">
-        <v>253.775</v>
+        <v>6460.5</v>
       </c>
       <c r="V15" t="n">
-        <v>232.8083333333333</v>
+        <v>6000.348087565104</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.4276564339809283</v>
+        <v>-124.2560250752931</v>
       </c>
       <c r="X15" t="n">
-        <v>2.707088558435337</v>
+        <v>-31.00814777542721</v>
       </c>
       <c r="Y15" t="n">
-        <v>-3.134744992416265</v>
+        <v>-93.24787729986591</v>
       </c>
       <c r="Z15" t="n">
-        <v>-3.165791552069547</v>
+        <v>-93.08022660698893</v>
       </c>
       <c r="AA15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0.01587301587301593</v>
+        <v>-0.03069466882067851</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.4850299401197604</v>
+        <v>0.5726762853585796</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.01977416570419466</v>
+        <v>0.004952512756532079</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.3770369520234715</v>
+        <v>0.4646832972622907</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.3572627863192769</v>
+        <v>-0.4597307845057587</v>
       </c>
       <c r="AG15" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AH15" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="AI15" t="b">
         <v>0</v>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="AM15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>283.71</v>
+        <v>7056</v>
       </c>
       <c r="AP15" t="n">
-        <v>251.87</v>
+        <v>6719.74</v>
       </c>
     </row>
     <row r="16">
@@ -2586,12 +2586,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2600,7 +2600,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>42.2</v>
+        <v>40.8</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2609,15 +2609,15 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1000</v>
+        <v>3921000</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="K16" t="b">
         <v>0</v>
@@ -2626,7 +2626,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1000</v>
+        <v>3921000</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2635,67 +2635,67 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>6000</v>
+        <v>87.69999694824219</v>
       </c>
       <c r="Q16" t="n">
-        <v>6000</v>
+        <v>87.69999694824219</v>
       </c>
       <c r="R16" t="n">
-        <v>2773940</v>
+        <v>2831267</v>
       </c>
       <c r="S16" t="n">
-        <v>6099</v>
+        <v>90</v>
       </c>
       <c r="T16" t="n">
-        <v>6451</v>
+        <v>88.7550006866455</v>
       </c>
       <c r="U16" t="n">
-        <v>6460.5</v>
+        <v>88.51000099182129</v>
       </c>
       <c r="V16" t="n">
-        <v>6000.348087565104</v>
+        <v>85.06666679382325</v>
       </c>
       <c r="W16" t="n">
-        <v>-124.2560250752931</v>
+        <v>0.7265338970744608</v>
       </c>
       <c r="X16" t="n">
-        <v>-31.00814777542713</v>
+        <v>1.509267513139483</v>
       </c>
       <c r="Y16" t="n">
-        <v>-93.24787729986599</v>
+        <v>-0.782733616065022</v>
       </c>
       <c r="Z16" t="n">
-        <v>-93.08022660698904</v>
+        <v>-0.5196039515255642</v>
       </c>
       <c r="AA16" t="b">
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>-0.03069466882067851</v>
+        <v>0.05917866806624894</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.5726762853585796</v>
+        <v>0.1017587767511641</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.004952512756532079</v>
+        <v>0.09482584964345953</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.4646832972622907</v>
+        <v>-0.006234211345124807</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.4597307845057587</v>
+        <v>0.1010600609885843</v>
       </c>
       <c r="AG16" t="n">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="AH16" t="n">
-        <v>90</v>
+        <v>34</v>
       </c>
       <c r="AI16" t="b">
         <v>0</v>
       </c>
       <c r="AJ16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK16" t="b">
         <v>0</v>
@@ -2707,13 +2707,15 @@
         <v>0</v>
       </c>
       <c r="AN16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO16" t="n">
-        <v>7056</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>6719.74</v>
+        <v>96.65000000000001</v>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -2724,12 +2726,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2738,7 +2740,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>40.8</v>
+        <v>39.8</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2747,15 +2749,15 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>3921000</v>
+        <v>6003000</v>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K17" t="b">
         <v>0</v>
@@ -2764,7 +2766,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3921000</v>
+        <v>6003000</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2773,82 +2775,84 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>87.69999694824219</v>
+        <v>190.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>87.69999694824219</v>
+        <v>190.5</v>
       </c>
       <c r="R17" t="n">
-        <v>2870815</v>
+        <v>22416629</v>
       </c>
       <c r="S17" t="n">
+        <v>190.9</v>
+      </c>
+      <c r="T17" t="n">
+        <v>187.025</v>
+      </c>
+      <c r="U17" t="n">
+        <v>186.5</v>
+      </c>
+      <c r="V17" t="n">
+        <v>185.5333333333333</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.290218095677432</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.5864765284235762</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.7037415672538554</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.7464855548500338</v>
+      </c>
+      <c r="AA17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.05833333333333335</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0.1238938053097345</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.09398051491054393</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0.01590081721344561</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0.07807969769709833</v>
+      </c>
+      <c r="AG17" t="n">
         <v>90</v>
       </c>
-      <c r="T17" t="n">
-        <v>88.7550006866455</v>
-      </c>
-      <c r="U17" t="n">
-        <v>88.51000099182129</v>
-      </c>
-      <c r="V17" t="n">
-        <v>85.06666679382325</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0.7265338970744608</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.509267513139483</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>-0.782733616065022</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>-0.5196039515255642</v>
-      </c>
-      <c r="AA17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0.05917866806624894</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0.1017587767511641</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0.09482584964345953</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>-0.006234211345124807</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0.1010600609885843</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>94</v>
-      </c>
       <c r="AH17" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AI17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ17" t="b">
         <v>1</v>
       </c>
       <c r="AK17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM17" t="b">
         <v>0</v>
       </c>
       <c r="AN17" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>96.65000000000001</v>
+        <v>0</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
@@ -2864,12 +2868,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2882,20 +2886,20 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>6003000</v>
+        <v>923000</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="K18" t="b">
         <v>0</v>
@@ -2904,82 +2908,82 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>6003000</v>
+        <v>852000</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>71000</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="P18" t="n">
-        <v>190.5</v>
+        <v>7430</v>
       </c>
       <c r="Q18" t="n">
-        <v>190.5</v>
+        <v>7430</v>
       </c>
       <c r="R18" t="n">
-        <v>22637098</v>
+        <v>2291700</v>
       </c>
       <c r="S18" t="n">
-        <v>190.9</v>
+        <v>7669</v>
       </c>
       <c r="T18" t="n">
-        <v>187.025</v>
+        <v>7992.5</v>
       </c>
       <c r="U18" t="n">
-        <v>186.5</v>
+        <v>8040.25</v>
       </c>
       <c r="V18" t="n">
-        <v>185.5333333333333</v>
+        <v>6463</v>
       </c>
       <c r="W18" t="n">
-        <v>1.290218095677432</v>
+        <v>-30.32926562784814</v>
       </c>
       <c r="X18" t="n">
-        <v>0.5864765284235762</v>
+        <v>113.5701033116136</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.7037415672538554</v>
+        <v>-143.8993689394617</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.7464855548500338</v>
+        <v>-140.2217805557706</v>
       </c>
       <c r="AA18" t="b">
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.05833333333333335</v>
+        <v>-0.1138938580799046</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.1238938053097345</v>
+        <v>1.254931714719272</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.09398051491054393</v>
+        <v>-0.07824667650269401</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.01590081721344561</v>
+        <v>1.146938726622983</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.07807969769709833</v>
+        <v>-1.225185403125677</v>
       </c>
       <c r="AG18" t="n">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="AH18" t="n">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="AI18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="b">
         <v>0</v>
@@ -2987,15 +2991,9 @@
       <c r="AN18" t="b">
         <v>0</v>
       </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
-      <c r="AP18" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+      <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="n">
+        <v>9117.110000000001</v>
       </c>
     </row>
     <row r="19">
@@ -3029,7 +3027,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -3037,7 +3035,7 @@
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K19" t="b">
         <v>0</v>
@@ -3061,7 +3059,7 @@
         <v>1465</v>
       </c>
       <c r="R19" t="n">
-        <v>5098695</v>
+        <v>4969284</v>
       </c>
       <c r="S19" t="n">
         <v>1558</v>
@@ -3142,12 +3140,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3156,24 +3154,24 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>39.4</v>
+        <v>38.2</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>6537000</v>
+        <v>501000</v>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="K20" t="b">
         <v>0</v>
@@ -3182,70 +3180,70 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>6457000</v>
+        <v>501000</v>
       </c>
       <c r="N20" t="n">
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0.01238965463837696</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>3130</v>
+        <v>216</v>
       </c>
       <c r="Q20" t="n">
-        <v>3130</v>
+        <v>216</v>
       </c>
       <c r="R20" t="n">
-        <v>2778810</v>
+        <v>23777890</v>
       </c>
       <c r="S20" t="n">
-        <v>3196</v>
+        <v>229.8</v>
       </c>
       <c r="T20" t="n">
-        <v>3363.75</v>
+        <v>236.95</v>
       </c>
       <c r="U20" t="n">
-        <v>3380.75</v>
+        <v>237.35</v>
       </c>
       <c r="V20" t="n">
-        <v>3185.9912109375</v>
+        <v>225.2333333333333</v>
       </c>
       <c r="W20" t="n">
-        <v>-64.94596194307451</v>
+        <v>-3.163724079880438</v>
       </c>
       <c r="X20" t="n">
-        <v>-33.7312883593824</v>
+        <v>1.210105544070594</v>
       </c>
       <c r="Y20" t="n">
-        <v>-31.2146735836921</v>
+        <v>-4.373829623951033</v>
       </c>
       <c r="Z20" t="n">
-        <v>-32.99125700943229</v>
+        <v>-3.407192547424745</v>
       </c>
       <c r="AA20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>-0.09798270893371763</v>
+        <v>-0.0357142857142857</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.5028965429281285</v>
+        <v>0.263157894736842</v>
       </c>
       <c r="AD20" t="n">
-        <v>-0.06233552735650705</v>
+        <v>-6.710413707511353e-05</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.3949035548318396</v>
+        <v>0.1551649066405532</v>
       </c>
       <c r="AF20" t="n">
-        <v>-0.4572390821883466</v>
+        <v>-0.1552320107776283</v>
       </c>
       <c r="AG20" t="n">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="AH20" t="n">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="AI20" t="b">
         <v>0</v>
@@ -3260,16 +3258,14 @@
         <v>0</v>
       </c>
       <c r="AM20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>3486.82</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO20" t="inlineStr"/>
       <c r="AP20" t="n">
-        <v>3801.05</v>
+        <v>244.55</v>
       </c>
     </row>
     <row r="21">
@@ -3280,12 +3276,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3294,24 +3290,24 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>38.2</v>
+        <v>37.2</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>501000</v>
+        <v>1126000</v>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K21" t="b">
         <v>0</v>
@@ -3320,70 +3316,70 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>501000</v>
+        <v>969000</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>157000</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>0.1620227038183694</v>
       </c>
       <c r="P21" t="n">
-        <v>216</v>
+        <v>2250</v>
       </c>
       <c r="Q21" t="n">
-        <v>216</v>
+        <v>2250</v>
       </c>
       <c r="R21" t="n">
-        <v>24203493</v>
+        <v>1195174</v>
       </c>
       <c r="S21" t="n">
-        <v>229.8</v>
+        <v>2321</v>
       </c>
       <c r="T21" t="n">
-        <v>236.95</v>
+        <v>2343.5</v>
       </c>
       <c r="U21" t="n">
-        <v>237.35</v>
+        <v>2361</v>
       </c>
       <c r="V21" t="n">
-        <v>225.2333333333333</v>
+        <v>2100.230332438151</v>
       </c>
       <c r="W21" t="n">
-        <v>-3.163724079880438</v>
+        <v>-2.166083020384121</v>
       </c>
       <c r="X21" t="n">
-        <v>1.210105544070594</v>
+        <v>3.145393600799783</v>
       </c>
       <c r="Y21" t="n">
-        <v>-4.373829623951033</v>
+        <v>-5.311476621183904</v>
       </c>
       <c r="Z21" t="n">
-        <v>-3.407192547424745</v>
+        <v>1.524106016444781</v>
       </c>
       <c r="AA21" t="b">
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>-0.0357142857142857</v>
+        <v>-0.1346153846153846</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.263157894736842</v>
+        <v>0.791094203859015</v>
       </c>
       <c r="AD21" t="n">
-        <v>-6.710413707511353e-05</v>
+        <v>-0.098968203038174</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.1551649066405532</v>
+        <v>0.6831012157627261</v>
       </c>
       <c r="AF21" t="n">
-        <v>-0.1552320107776283</v>
+        <v>-0.7820694188009001</v>
       </c>
       <c r="AG21" t="n">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="AH21" t="n">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="AI21" t="b">
         <v>0</v>
@@ -3401,11 +3397,13 @@
         <v>0</v>
       </c>
       <c r="AN21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO21" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>2313</v>
+      </c>
       <c r="AP21" t="n">
-        <v>244.55</v>
+        <v>2628.42</v>
       </c>
     </row>
     <row r="22">
@@ -3439,7 +3437,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -3471,7 +3469,7 @@
         <v>79</v>
       </c>
       <c r="R22" t="n">
-        <v>3330822</v>
+        <v>3315166</v>
       </c>
       <c r="S22" t="n">
         <v>79.8</v>
@@ -3556,12 +3554,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3570,7 +3568,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>35.8</v>
+        <v>36.4</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3579,15 +3577,15 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>23519000</v>
+        <v>7556450</v>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K23" t="b">
         <v>1</v>
@@ -3596,7 +3594,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>23519000</v>
+        <v>7556450</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -3605,61 +3603,61 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>521</v>
+        <v>269</v>
       </c>
       <c r="Q23" t="n">
-        <v>521</v>
+        <v>269</v>
       </c>
       <c r="R23" t="n">
-        <v>31814660</v>
+        <v>25315766</v>
       </c>
       <c r="S23" t="n">
-        <v>520</v>
+        <v>266.3</v>
       </c>
       <c r="T23" t="n">
-        <v>578.65</v>
+        <v>286.55</v>
       </c>
       <c r="U23" t="n">
-